--- a/data/CEM.MI.xlsx
+++ b/data/CEM.MI.xlsx
@@ -44,103 +44,103 @@
     <t xml:space="preserve">CEM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68035984039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55656242370605</t>
+    <t xml:space="preserve">4.68036079406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55656290054321</t>
   </si>
   <si>
     <t xml:space="preserve">4.48867273330688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32893371582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22111034393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32494020462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2889986038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29299259185791</t>
+    <t xml:space="preserve">4.32893323898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22110939025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3249397277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28899955749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29299163818359</t>
   </si>
   <si>
     <t xml:space="preserve">4.06137037277222</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93597531318665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97431302070618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67560029029846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83533930778503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94875383377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88006615638733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91680645942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87846851348877</t>
+    <t xml:space="preserve">3.93597507476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97431254386902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6756010055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83534002304077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94875335693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88006663322449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91680693626404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87846875190735</t>
   </si>
   <si>
     <t xml:space="preserve">3.74588561058044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93437767028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87367630004883</t>
+    <t xml:space="preserve">3.93437814712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87367725372314</t>
   </si>
   <si>
     <t xml:space="preserve">3.73789858818054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57815933227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59892582893372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61969089508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35133004188538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15005803108215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25069403648376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13088941574097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20916199684143</t>
+    <t xml:space="preserve">3.57816004753113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59892559051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61969184875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35132908821106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15005850791931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25069355964661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13088965415955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20916175842285</t>
   </si>
   <si>
     <t xml:space="preserve">3.44238066673279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36251139640808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47592639923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55419874191284</t>
+    <t xml:space="preserve">3.36251091957092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47592687606812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55419850349426</t>
   </si>
   <si>
     <t xml:space="preserve">3.34653782844543</t>
@@ -149,10 +149,10 @@
     <t xml:space="preserve">3.39126420021057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36730337142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23951244354248</t>
+    <t xml:space="preserve">3.36730360984802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2395122051239</t>
   </si>
   <si>
     <t xml:space="preserve">3.29222631454468</t>
@@ -161,25 +161,25 @@
     <t xml:space="preserve">3.40244626998901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58614611625671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63406825065613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55579566955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64365243911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56058835983276</t>
+    <t xml:space="preserve">3.58614563941956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63406848907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55579614639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64365267753601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56058812141418</t>
   </si>
   <si>
     <t xml:space="preserve">3.52065324783325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49829006195068</t>
+    <t xml:space="preserve">3.4982898235321</t>
   </si>
   <si>
     <t xml:space="preserve">3.52544498443604</t>
@@ -188,10 +188,10 @@
     <t xml:space="preserve">3.54940629005432</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75227522850037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61330151557922</t>
+    <t xml:space="preserve">3.75227499008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61330246925354</t>
   </si>
   <si>
     <t xml:space="preserve">3.75387215614319</t>
@@ -200,151 +200,151 @@
     <t xml:space="preserve">3.83214473724365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6708083152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70754861831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65802907943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51745820045471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57017207145691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50947165489197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54301643371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57975697517395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45196485519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41043305397034</t>
+    <t xml:space="preserve">3.67080807685852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70754766464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65802955627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51745867729187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57017254829407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50947117805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5430166721344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57975649833679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45196580886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41043329238892</t>
   </si>
   <si>
     <t xml:space="preserve">3.37529039382935</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60052275657654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48551082611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5446138381958</t>
+    <t xml:space="preserve">3.60052227973938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48551058769226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54461431503296</t>
   </si>
   <si>
     <t xml:space="preserve">3.59573030471802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77943086624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74428868293762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8577024936676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73949575424194</t>
+    <t xml:space="preserve">3.7794303894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74428820610046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85770320892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73949599266052</t>
   </si>
   <si>
     <t xml:space="preserve">3.74907994270325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70595049858093</t>
+    <t xml:space="preserve">3.70595073699951</t>
   </si>
   <si>
     <t xml:space="preserve">3.69317150115967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67719745635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79700231552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66601634025574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70115828514099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62608122825623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6740026473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64205551147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53023767471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45835423469543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47432851791382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53193688392639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62187051773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7575888633728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7608585357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87531971931458</t>
+    <t xml:space="preserve">3.67719793319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7970027923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66601538658142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70115852355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62608098983765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67400312423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64205479621887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53023719787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45835447311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4743287563324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53193759918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62187004089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75758862495422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76085901260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87531924247742</t>
   </si>
   <si>
     <t xml:space="preserve">3.88349556922913</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77720999717712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75431847572327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70526313781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66929006576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59734344482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5842616558075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55646371841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38640809059143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31119132041931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29810929298401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1967306137085</t>
+    <t xml:space="preserve">3.77721071243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75431799888611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70526385307312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66929030418396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59734320640564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58426189422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55646419525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38640856742859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31119155883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29810976982117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19673013687134</t>
   </si>
   <si>
     <t xml:space="preserve">3.15912127494812</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">3.00705194473267</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15421605110168</t>
+    <t xml:space="preserve">3.15421628952026</t>
   </si>
   <si>
     <t xml:space="preserve">3.0348494052887</t>
@@ -362,46 +362,46 @@
     <t xml:space="preserve">3.22289252281189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35207009315491</t>
+    <t xml:space="preserve">3.35206985473633</t>
   </si>
   <si>
     <t xml:space="preserve">3.10679626464844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8288197517395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82064390182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84026598930359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93510484695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04302549362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9579975605011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79611659049988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76341366767883</t>
+    <t xml:space="preserve">2.82882022857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82064437866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84026575088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9351053237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04302525520325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95799732208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79611682891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76341390609741</t>
   </si>
   <si>
     <t xml:space="preserve">2.76831889152527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84844160079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87787461280823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04138994216919</t>
+    <t xml:space="preserve">2.84844207763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87787508964539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04139041900635</t>
   </si>
   <si>
     <t xml:space="preserve">3.00051164627075</t>
@@ -410,19 +410,19 @@
     <t xml:space="preserve">3.21144652366638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13295888900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07572841644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97434878349304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10843181610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97598385810852</t>
+    <t xml:space="preserve">3.13295912742615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07572865486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9743492603302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10843133926392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9759840965271</t>
   </si>
   <si>
     <t xml:space="preserve">2.92856454849243</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">3.18037867546082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15585112571716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18855428695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09862089157104</t>
+    <t xml:space="preserve">3.15585088729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18855476379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09862065315247</t>
   </si>
   <si>
     <t xml:space="preserve">3.12151265144348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02503895759583</t>
+    <t xml:space="preserve">3.02503871917725</t>
   </si>
   <si>
     <t xml:space="preserve">3.11660766601562</t>
@@ -455,64 +455,64 @@
     <t xml:space="preserve">3.23760914802551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28012323379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32263731956482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43546319007874</t>
+    <t xml:space="preserve">3.28012299537659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32263708114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43546295166016</t>
   </si>
   <si>
     <t xml:space="preserve">3.40602970123291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46653079986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43709802627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44854426383972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67910099029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64639806747437</t>
+    <t xml:space="preserve">3.46653032302856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43709778785706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44854402542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67910051345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64639830589294</t>
   </si>
   <si>
     <t xml:space="preserve">3.71834444999695</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69545292854309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74450731277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85242772102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80827736854553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82299494743347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80337238311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74287223815918</t>
+    <t xml:space="preserve">3.69545245170593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74450778961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8524272441864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80827879905701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82299470901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80337309837341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7428719997406</t>
   </si>
   <si>
     <t xml:space="preserve">3.62350559234619</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56627559661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47470641136169</t>
+    <t xml:space="preserve">3.56627535820007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47470664978027</t>
   </si>
   <si>
     <t xml:space="preserve">3.51558566093445</t>
@@ -521,112 +521,112 @@
     <t xml:space="preserve">3.65947890281677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60551905632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54501795768738</t>
+    <t xml:space="preserve">3.60551929473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54501819610596</t>
   </si>
   <si>
     <t xml:space="preserve">3.64803338050842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64476323127747</t>
+    <t xml:space="preserve">3.64476299285889</t>
   </si>
   <si>
     <t xml:space="preserve">3.38804316520691</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4828827381134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45344948768616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4338276386261</t>
+    <t xml:space="preserve">3.48288249969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45344972610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43382716178894</t>
   </si>
   <si>
     <t xml:space="preserve">3.5074098110199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56464052200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55482959747314</t>
+    <t xml:space="preserve">3.56464028358459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55482935905457</t>
   </si>
   <si>
     <t xml:space="preserve">3.56300520896912</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48451781272888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54338312149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62514114379883</t>
+    <t xml:space="preserve">3.48451805114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5433828830719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62514090538025</t>
   </si>
   <si>
     <t xml:space="preserve">3.5908031463623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64149260520935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68891167640686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66111421585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6872763633728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53684186935425</t>
+    <t xml:space="preserve">3.64149236679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68891191482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66111445426941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68727660179138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53684258460999</t>
   </si>
   <si>
     <t xml:space="preserve">3.63004636764526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63822269439697</t>
+    <t xml:space="preserve">3.63822221755981</t>
   </si>
   <si>
     <t xml:space="preserve">3.43873286247253</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41747641563416</t>
+    <t xml:space="preserve">3.417475938797</t>
   </si>
   <si>
     <t xml:space="preserve">3.41911149024963</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33571815490723</t>
+    <t xml:space="preserve">3.33571791648865</t>
   </si>
   <si>
     <t xml:space="preserve">3.37169170379639</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27521753311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22125744819641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20981121063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17710852622986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21308159828186</t>
+    <t xml:space="preserve">3.27521729469299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22125720977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2098114490509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17710781097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21308135986328</t>
   </si>
   <si>
     <t xml:space="preserve">3.14767527580261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11333703994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00541710853577</t>
+    <t xml:space="preserve">3.11333727836609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00541687011719</t>
   </si>
   <si>
     <t xml:space="preserve">3.01686310768127</t>
@@ -635,22 +635,22 @@
     <t xml:space="preserve">2.95309162139893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91875338554382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96453785896301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96780848503113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95636224746704</t>
+    <t xml:space="preserve">2.9187536239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96453762054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96780800819397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95636200904846</t>
   </si>
   <si>
     <t xml:space="preserve">3.04793095588684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17220258712769</t>
+    <t xml:space="preserve">3.17220282554626</t>
   </si>
   <si>
     <t xml:space="preserve">3.18691921234131</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">3.3193666934967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23433899879456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45835471153259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48778772354126</t>
+    <t xml:space="preserve">3.2343385219574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45835494995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4877872467041</t>
   </si>
   <si>
     <t xml:space="preserve">3.4518141746521</t>
@@ -674,31 +674,31 @@
     <t xml:space="preserve">3.49923419952393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57281613349915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4501793384552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61369490623474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67746591567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58916711807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70362854003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48615264892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33244824409485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28666353225708</t>
+    <t xml:space="preserve">3.57281565666199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45017910003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61369442939758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67746686935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58916783332825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70362877845764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4861524105072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33244800567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2866632938385</t>
   </si>
   <si>
     <t xml:space="preserve">3.22943329811096</t>
@@ -707,49 +707,49 @@
     <t xml:space="preserve">3.27031207084656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24741983413696</t>
+    <t xml:space="preserve">3.24741959571838</t>
   </si>
   <si>
     <t xml:space="preserve">3.23106789588928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23270320892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26213645935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27685260772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23597383499146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00122785568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04701137542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12876844406128</t>
+    <t xml:space="preserve">3.2327036857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26213622093201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27685284614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23597359657288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00122690200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04701042175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12876892089844</t>
   </si>
   <si>
     <t xml:space="preserve">4.16964817047119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1778244972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06336212158203</t>
+    <t xml:space="preserve">4.17782354354858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06336307525635</t>
   </si>
   <si>
     <t xml:space="preserve">3.95707750320435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19417524337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28410816192627</t>
+    <t xml:space="preserve">4.19417572021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28410863876343</t>
   </si>
   <si>
     <t xml:space="preserve">4.34542751312256</t>
@@ -758,10 +758,10 @@
     <t xml:space="preserve">4.47215175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43944787979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41083335876465</t>
+    <t xml:space="preserve">4.43944835662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41083288192749</t>
   </si>
   <si>
     <t xml:space="preserve">4.41492128372192</t>
@@ -770,76 +770,76 @@
     <t xml:space="preserve">4.37404251098633</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26775741577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39039373397827</t>
+    <t xml:space="preserve">4.26775693893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39039421081543</t>
   </si>
   <si>
     <t xml:space="preserve">4.3617787361145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37812995910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38630628585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56208562850952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42718505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32907629013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25549411773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25140571594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30046129226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34951448440552</t>
+    <t xml:space="preserve">4.37813091278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.386305809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56208467483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42718458175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3290753364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25549364089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25140523910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30046081542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34951496124268</t>
   </si>
   <si>
     <t xml:space="preserve">4.24322986602783</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24731779098511</t>
+    <t xml:space="preserve">4.24731826782227</t>
   </si>
   <si>
     <t xml:space="preserve">4.21052694320679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14512062072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10424184799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22279071807861</t>
+    <t xml:space="preserve">4.1451210975647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10424137115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22279024124146</t>
   </si>
   <si>
     <t xml:space="preserve">4.40674495697021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36586713790894</t>
+    <t xml:space="preserve">4.36586666107178</t>
   </si>
   <si>
     <t xml:space="preserve">4.27593278884888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30454778671265</t>
+    <t xml:space="preserve">4.30454874038696</t>
   </si>
   <si>
     <t xml:space="preserve">4.28002119064331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44762468338013</t>
+    <t xml:space="preserve">4.44762420654297</t>
   </si>
   <si>
     <t xml:space="preserve">4.52938270568848</t>
@@ -848,31 +848,31 @@
     <t xml:space="preserve">4.51711893081665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52120685577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68063402175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66019439697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71333742141724</t>
+    <t xml:space="preserve">4.52120637893677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68063449859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66019487380981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71333694458008</t>
   </si>
   <si>
     <t xml:space="preserve">4.7337760925293</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81962203979492</t>
+    <t xml:space="preserve">4.81962251663208</t>
   </si>
   <si>
     <t xml:space="preserve">4.81144714355469</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65201902389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34133911132812</t>
+    <t xml:space="preserve">4.65201807022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34133958816528</t>
   </si>
   <si>
     <t xml:space="preserve">4.33725118637085</t>
@@ -887,52 +887,52 @@
     <t xml:space="preserve">4.44966459274292</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41633367538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37467002868652</t>
+    <t xml:space="preserve">4.41633319854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37466955184937</t>
   </si>
   <si>
     <t xml:space="preserve">4.36633729934692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30384206771851</t>
+    <t xml:space="preserve">4.30384159088135</t>
   </si>
   <si>
     <t xml:space="preserve">4.27467775344849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25801229476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31634187698364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26634550094604</t>
+    <t xml:space="preserve">4.25801181793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31634092330933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26634454727173</t>
   </si>
   <si>
     <t xml:space="preserve">4.20801591873169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33300638198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37050342559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3455057144165</t>
+    <t xml:space="preserve">4.33300590515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37050294876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34550619125366</t>
   </si>
   <si>
     <t xml:space="preserve">4.39133548736572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29967546463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4288330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39966869354248</t>
+    <t xml:space="preserve">4.29967594146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42883253097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39966917037964</t>
   </si>
   <si>
     <t xml:space="preserve">4.3955020904541</t>
@@ -944,16 +944,16 @@
     <t xml:space="preserve">4.46633005142212</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48299503326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56632280349731</t>
+    <t xml:space="preserve">4.48299551010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56632232666016</t>
   </si>
   <si>
     <t xml:space="preserve">4.40800046920776</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34967184066772</t>
+    <t xml:space="preserve">4.34967231750488</t>
   </si>
   <si>
     <t xml:space="preserve">4.69131326675415</t>
@@ -962,22 +962,22 @@
     <t xml:space="preserve">4.58298778533936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85380029678345</t>
+    <t xml:space="preserve">4.85380077362061</t>
   </si>
   <si>
     <t xml:space="preserve">4.99962282180786</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05795240402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10794878005981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24960422515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28710174560547</t>
+    <t xml:space="preserve">5.0579514503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10794830322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24960374832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28710079193115</t>
   </si>
   <si>
     <t xml:space="preserve">5.25377035140991</t>
@@ -989,37 +989,37 @@
     <t xml:space="preserve">5.30376672744751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29960012435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34543037414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30793333053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22877216339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29126739501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29543399810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16211080551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01628828048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05378532409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12461376190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20377397537231</t>
+    <t xml:space="preserve">5.29959964752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34542989730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30793237686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22877264022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29126644134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29543352127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16211128234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01628875732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05378580093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12461423873901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20377445220947</t>
   </si>
   <si>
     <t xml:space="preserve">5.07461738586426</t>
@@ -1028,19 +1028,19 @@
     <t xml:space="preserve">5.03295373916626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95795869827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9912896156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9621262550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90796279907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94129371643066</t>
+    <t xml:space="preserve">4.95795917510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99129009246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96212577819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90796327590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94129419326782</t>
   </si>
   <si>
     <t xml:space="preserve">4.89129781723022</t>
@@ -1049,16 +1049,16 @@
     <t xml:space="preserve">4.9037971496582</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95379304885864</t>
+    <t xml:space="preserve">4.95379257202148</t>
   </si>
   <si>
     <t xml:space="preserve">4.94545984268188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91629648208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02462100982666</t>
+    <t xml:space="preserve">4.91629552841187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02462148666382</t>
   </si>
   <si>
     <t xml:space="preserve">5.04961919784546</t>
@@ -1073,16 +1073,16 @@
     <t xml:space="preserve">5.23293876647949</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17877626419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13294649124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33293151855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26626920700073</t>
+    <t xml:space="preserve">5.17877578735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1329460144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33293056488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26626968383789</t>
   </si>
   <si>
     <t xml:space="preserve">5.22460603713989</t>
@@ -1094,16 +1094,16 @@
     <t xml:space="preserve">5.68707132339478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00371408462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80789470672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07454252243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01621294021606</t>
+    <t xml:space="preserve">6.00371360778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80789518356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0745415687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01621246337891</t>
   </si>
   <si>
     <t xml:space="preserve">6.1662015914917</t>
@@ -1115,46 +1115,46 @@
     <t xml:space="preserve">5.94121789932251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96621561050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03287744522095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99538135528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.970383644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91622066497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86205720901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92871904373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89955520629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90372228622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87455701828003</t>
+    <t xml:space="preserve">5.96621608734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03287792205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9953818321228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97038316726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91622018814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86205816268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92871952056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89955472946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90372180938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87455654144287</t>
   </si>
   <si>
     <t xml:space="preserve">5.84539270401001</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00788068771362</t>
+    <t xml:space="preserve">6.00787973403931</t>
   </si>
   <si>
     <t xml:space="preserve">5.98288202285767</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03704404830933</t>
+    <t xml:space="preserve">6.03704452514648</t>
   </si>
   <si>
     <t xml:space="preserve">6.09120750427246</t>
@@ -1163,10 +1163,10 @@
     <t xml:space="preserve">6.0287127494812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99954652786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04954385757446</t>
+    <t xml:space="preserve">5.99954700469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04954433441162</t>
   </si>
   <si>
     <t xml:space="preserve">6.07870817184448</t>
@@ -1178,7 +1178,7 @@
     <t xml:space="preserve">6.17453384399414</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19953298568726</t>
+    <t xml:space="preserve">6.1995325088501</t>
   </si>
   <si>
     <t xml:space="preserve">6.08287477493286</t>
@@ -1187,10 +1187,10 @@
     <t xml:space="preserve">6.24536275863647</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21203136444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02454614639282</t>
+    <t xml:space="preserve">6.21203088760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02454566955566</t>
   </si>
   <si>
     <t xml:space="preserve">6.09954023361206</t>
@@ -1202,40 +1202,40 @@
     <t xml:space="preserve">6.20786476135254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22036457061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14537048339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95788478851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94538497924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01204633712769</t>
+    <t xml:space="preserve">6.22036361694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14537000656128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95788335800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94538545608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01204681396484</t>
   </si>
   <si>
     <t xml:space="preserve">6.02037906646729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1162052154541</t>
+    <t xml:space="preserve">6.11620569229126</t>
   </si>
   <si>
     <t xml:space="preserve">6.06204271316528</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04121160507202</t>
+    <t xml:space="preserve">6.04121065139771</t>
   </si>
   <si>
     <t xml:space="preserve">6.14953660964966</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09537410736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35785388946533</t>
+    <t xml:space="preserve">6.09537363052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35785484313965</t>
   </si>
   <si>
     <t xml:space="preserve">6.22453022003174</t>
@@ -1256,16 +1256,16 @@
     <t xml:space="preserve">6.50784254074097</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49951028823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6578311920166</t>
+    <t xml:space="preserve">6.49950981140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65783071517944</t>
   </si>
   <si>
     <t xml:space="preserve">6.7411584854126</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59116983413696</t>
+    <t xml:space="preserve">6.5911693572998</t>
   </si>
   <si>
     <t xml:space="preserve">6.6245002746582</t>
@@ -1277,97 +1277,97 @@
     <t xml:space="preserve">6.70782804489136</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52450799942017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51617527008057</t>
+    <t xml:space="preserve">6.52450752258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51617574691772</t>
   </si>
   <si>
     <t xml:space="preserve">6.6661639213562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54950571060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44951391220093</t>
+    <t xml:space="preserve">6.54950618743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44951343536377</t>
   </si>
   <si>
     <t xml:space="preserve">6.29952478408813</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23286390304565</t>
+    <t xml:space="preserve">6.2328634262085</t>
   </si>
   <si>
     <t xml:space="preserve">5.90788793563843</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93288564682007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53284120559692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26619338989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36618614196777</t>
+    <t xml:space="preserve">5.93288612365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53284072875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26619386672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36618661880493</t>
   </si>
   <si>
     <t xml:space="preserve">6.33285522460938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1412034034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15786838531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0662088394165</t>
+    <t xml:space="preserve">6.14120292663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1578688621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06620979309082</t>
   </si>
   <si>
     <t xml:space="preserve">5.94955110549927</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13287115097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05787658691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88288927078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84955930709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81622791290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72456789016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75789880752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76623249053955</t>
+    <t xml:space="preserve">6.1328706741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0578761100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88288974761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84955883026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81622743606567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72456836700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75789833068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76623201370239</t>
   </si>
   <si>
     <t xml:space="preserve">5.68290519714355</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82456111907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86622381210327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77456426620483</t>
+    <t xml:space="preserve">5.82456064224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86622428894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77456474304199</t>
   </si>
   <si>
     <t xml:space="preserve">5.78289747238159</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79122972488403</t>
+    <t xml:space="preserve">5.79122924804688</t>
   </si>
   <si>
     <t xml:space="preserve">5.63290882110596</t>
@@ -1379,40 +1379,40 @@
     <t xml:space="preserve">5.68365526199341</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66673946380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70057058334351</t>
+    <t xml:space="preserve">5.66673898696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70057106018066</t>
   </si>
   <si>
     <t xml:space="preserve">5.48066806793213</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45529365539551</t>
+    <t xml:space="preserve">5.45529460906982</t>
   </si>
   <si>
     <t xml:space="preserve">5.54833078384399</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53987216949463</t>
+    <t xml:space="preserve">5.53987312316895</t>
   </si>
   <si>
     <t xml:space="preserve">5.74285984039307</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58216142654419</t>
+    <t xml:space="preserve">5.58216190338135</t>
   </si>
   <si>
     <t xml:space="preserve">5.6582818031311</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70902872085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77669095993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91201686859131</t>
+    <t xml:space="preserve">5.70902824401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77669048309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91201591491699</t>
   </si>
   <si>
     <t xml:space="preserve">5.9035587310791</t>
@@ -1430,13 +1430,13 @@
     <t xml:space="preserve">5.71748685836792</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81052303314209</t>
+    <t xml:space="preserve">5.81052255630493</t>
   </si>
   <si>
     <t xml:space="preserve">5.56524610519409</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50604152679443</t>
+    <t xml:space="preserve">5.50604200363159</t>
   </si>
   <si>
     <t xml:space="preserve">5.69211292266846</t>
@@ -1445,19 +1445,19 @@
     <t xml:space="preserve">5.72594499588013</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73440265655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60753488540649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51449918746948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67519807815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01351118087769</t>
+    <t xml:space="preserve">5.73440217971802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60753536224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51449966430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67519760131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01351022720337</t>
   </si>
   <si>
     <t xml:space="preserve">5.99659442901611</t>
@@ -1466,55 +1466,55 @@
     <t xml:space="preserve">5.81898069381714</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75977611541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8020658493042</t>
+    <t xml:space="preserve">5.75977563858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80206441879272</t>
   </si>
   <si>
     <t xml:space="preserve">5.79360723495483</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88664388656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87818574905396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92893266677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85281181335449</t>
+    <t xml:space="preserve">5.886643409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8781852722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92893218994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85281229019165</t>
   </si>
   <si>
     <t xml:space="preserve">5.76823377609253</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82743835449219</t>
+    <t xml:space="preserve">5.82743787765503</t>
   </si>
   <si>
     <t xml:space="preserve">5.83589649200439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42992067337036</t>
+    <t xml:space="preserve">5.42992115020752</t>
   </si>
   <si>
     <t xml:space="preserve">5.38763189315796</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33688497543335</t>
+    <t xml:space="preserve">5.33688449859619</t>
   </si>
   <si>
     <t xml:space="preserve">5.26076459884644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30305290222168</t>
+    <t xml:space="preserve">5.30305337905884</t>
   </si>
   <si>
     <t xml:space="preserve">5.43837833404541</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46375179290771</t>
+    <t xml:space="preserve">5.46375226974487</t>
   </si>
   <si>
     <t xml:space="preserve">5.44683647155762</t>
@@ -1529,13 +1529,13 @@
     <t xml:space="preserve">5.22693300247192</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14235496520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11698198318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24384832382202</t>
+    <t xml:space="preserve">5.1423544883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11698150634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24384880065918</t>
   </si>
   <si>
     <t xml:space="preserve">5.13389778137207</t>
@@ -1544,22 +1544,22 @@
     <t xml:space="preserve">5.26922225952148</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25230646133423</t>
+    <t xml:space="preserve">5.25230693817139</t>
   </si>
   <si>
     <t xml:space="preserve">5.21001720428467</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23539161682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28613758087158</t>
+    <t xml:space="preserve">5.23539113998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2861385345459</t>
   </si>
   <si>
     <t xml:space="preserve">5.31996965408325</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29459571838379</t>
+    <t xml:space="preserve">5.29459619522095</t>
   </si>
   <si>
     <t xml:space="preserve">5.48912525177002</t>
@@ -1568,22 +1568,22 @@
     <t xml:space="preserve">5.3284273147583</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16772890090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09160757064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17618608474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10852432250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91399335861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60105419158936</t>
+    <t xml:space="preserve">5.16772842407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09160804748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17618656158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10852384567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91399383544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60105466842651</t>
   </si>
   <si>
     <t xml:space="preserve">4.49956083297729</t>
@@ -1592,28 +1592,28 @@
     <t xml:space="preserve">4.567223072052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38115167617798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54185009002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5249342918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61797046661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46572971343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27119970321655</t>
+    <t xml:space="preserve">4.38115072250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5418496131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52493381500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61796998977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46572923660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27120018005371</t>
   </si>
   <si>
     <t xml:space="preserve">4.14433240890503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22045278549194</t>
+    <t xml:space="preserve">4.22045230865479</t>
   </si>
   <si>
     <t xml:space="preserve">4.09358549118042</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">4.39806652069092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53339195251465</t>
+    <t xml:space="preserve">4.53339147567749</t>
   </si>
   <si>
     <t xml:space="preserve">4.59259605407715</t>
@@ -1640,31 +1640,31 @@
     <t xml:space="preserve">4.63488578796387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41498184204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49110317230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42344045639038</t>
+    <t xml:space="preserve">4.41498231887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49110269546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42343997955322</t>
   </si>
   <si>
     <t xml:space="preserve">4.43189764022827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29657316207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33886194229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19507884979248</t>
+    <t xml:space="preserve">4.29657363891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33886241912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19507932662964</t>
   </si>
   <si>
     <t xml:space="preserve">4.0470666885376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08512735366821</t>
+    <t xml:space="preserve">4.08512783050537</t>
   </si>
   <si>
     <t xml:space="preserve">4.10627174377441</t>
@@ -1676,16 +1676,16 @@
     <t xml:space="preserve">4.2373685836792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21622371673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16124725341797</t>
+    <t xml:space="preserve">4.216224193573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16124820709229</t>
   </si>
   <si>
     <t xml:space="preserve">4.10204315185547</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03860950469971</t>
+    <t xml:space="preserve">4.03860902786255</t>
   </si>
   <si>
     <t xml:space="preserve">4.30503082275391</t>
@@ -1697,19 +1697,19 @@
     <t xml:space="preserve">4.14010286331177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05129623413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14856147766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08935594558716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03437995910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94557332992554</t>
+    <t xml:space="preserve">4.05129671096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14856100082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08935642242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0343804359436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94557309150696</t>
   </si>
   <si>
     <t xml:space="preserve">4.35577774047852</t>
@@ -1718,19 +1718,19 @@
     <t xml:space="preserve">4.3134880065918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4826455116272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65180158615112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79558420181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7871265411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82095766067505</t>
+    <t xml:space="preserve">4.48264503479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65180110931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7955846786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78712606430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82095813751221</t>
   </si>
   <si>
     <t xml:space="preserve">4.86324691772461</t>
@@ -1742,16 +1742,16 @@
     <t xml:space="preserve">4.88862085342407</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95628309249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00703048706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01548767089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03240346908569</t>
+    <t xml:space="preserve">4.95628356933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00702953338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0154881477356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03240251541138</t>
   </si>
   <si>
     <t xml:space="preserve">5.05777645111084</t>
@@ -1763,7 +1763,7 @@
     <t xml:space="preserve">4.97319841384888</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20155954360962</t>
+    <t xml:space="preserve">5.20156002044678</t>
   </si>
   <si>
     <t xml:space="preserve">5.12543916702271</t>
@@ -1772,22 +1772,22 @@
     <t xml:space="preserve">5.15927076339722</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21847486495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34534311294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27767992019653</t>
+    <t xml:space="preserve">5.21847534179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3453426361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27767944335938</t>
   </si>
   <si>
     <t xml:space="preserve">5.40454721450806</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39609050750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47221040725708</t>
+    <t xml:space="preserve">5.39609003067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47220993041992</t>
   </si>
   <si>
     <t xml:space="preserve">5.49758338928223</t>
@@ -1802,31 +1802,31 @@
     <t xml:space="preserve">4.98165655136108</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11462450027466</t>
+    <t xml:space="preserve">5.11462497711182</t>
   </si>
   <si>
     <t xml:space="preserve">5.13193321228027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0194296836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01077508926392</t>
+    <t xml:space="preserve">5.01942873001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01077461242676</t>
   </si>
   <si>
     <t xml:space="preserve">5.06270027160645</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08866214752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09731674194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14058828353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21847534179688</t>
+    <t xml:space="preserve">5.08866262435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0973162651062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14058780670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21847581863403</t>
   </si>
   <si>
     <t xml:space="preserve">5.20116710662842</t>
@@ -1835,22 +1835,22 @@
     <t xml:space="preserve">5.17520380020142</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22712993621826</t>
+    <t xml:space="preserve">5.2271294593811</t>
   </si>
   <si>
     <t xml:space="preserve">5.26174640655518</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23578405380249</t>
+    <t xml:space="preserve">5.23578357696533</t>
   </si>
   <si>
     <t xml:space="preserve">5.25309228897095</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33963346481323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46079254150391</t>
+    <t xml:space="preserve">5.33963394165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46079206466675</t>
   </si>
   <si>
     <t xml:space="preserve">5.54733467102051</t>
@@ -1865,19 +1865,19 @@
     <t xml:space="preserve">5.40886735916138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57329702377319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52137184143066</t>
+    <t xml:space="preserve">5.57329750061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52137231826782</t>
   </si>
   <si>
     <t xml:space="preserve">5.47810077667236</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64253091812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76368951797485</t>
+    <t xml:space="preserve">5.64252996444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7636890411377</t>
   </si>
   <si>
     <t xml:space="preserve">5.74638080596924</t>
@@ -1898,97 +1898,97 @@
     <t xml:space="preserve">5.59925937652588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49540901184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45213842391968</t>
+    <t xml:space="preserve">5.49540948867798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45213890075684</t>
   </si>
   <si>
     <t xml:space="preserve">5.56464242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73772621154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51271772384644</t>
+    <t xml:space="preserve">5.73772668838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51271724700928</t>
   </si>
   <si>
     <t xml:space="preserve">5.24443769454956</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1838583946228</t>
+    <t xml:space="preserve">5.18385791778564</t>
   </si>
   <si>
     <t xml:space="preserve">5.28770923614502</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19251298904419</t>
+    <t xml:space="preserve">5.19251251220703</t>
   </si>
   <si>
     <t xml:space="preserve">5.1232795715332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27040100097656</t>
+    <t xml:space="preserve">5.27040004730225</t>
   </si>
   <si>
     <t xml:space="preserve">5.08000802993774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14924192428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16654968261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15789556503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29636240005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53868007659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44348478317261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48675537109375</t>
+    <t xml:space="preserve">5.14924097061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16655015945435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15789651870728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29636335372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53868055343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44348430633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48675489425659</t>
   </si>
   <si>
     <t xml:space="preserve">5.40021324157715</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36559629440308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32232570648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38290500640869</t>
+    <t xml:space="preserve">5.36559677124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32232618331909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38290452957153</t>
   </si>
   <si>
     <t xml:space="preserve">5.02808284759521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04539108276367</t>
+    <t xml:space="preserve">5.04539155960083</t>
   </si>
   <si>
     <t xml:space="preserve">5.16222333908081</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03933382034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10597133636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15270376205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20895624160767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27905416488647</t>
+    <t xml:space="preserve">5.03933334350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10597038269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15270328521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20895576477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27905464172363</t>
   </si>
   <si>
     <t xml:space="preserve">5.34569215774536</t>
@@ -1997,25 +1997,25 @@
     <t xml:space="preserve">5.32665252685547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27992010116577</t>
+    <t xml:space="preserve">5.27991962432861</t>
   </si>
   <si>
     <t xml:space="preserve">5.30588245391846</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26780414581299</t>
+    <t xml:space="preserve">5.26780462265015</t>
   </si>
   <si>
     <t xml:space="preserve">5.34742307662964</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21934080123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34309530258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48502445220947</t>
+    <t xml:space="preserve">5.21934127807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34309577941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48502397537231</t>
   </si>
   <si>
     <t xml:space="preserve">5.4391565322876</t>
@@ -2027,7 +2027,7 @@
     <t xml:space="preserve">5.51791000366211</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61656761169434</t>
+    <t xml:space="preserve">5.61656713485718</t>
   </si>
   <si>
     <t xml:space="preserve">5.51617908477783</t>
@@ -2042,49 +2042,49 @@
     <t xml:space="preserve">5.46771574020386</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44434976577759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46944665908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78099679946899</t>
+    <t xml:space="preserve">5.44435024261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46944713592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78099727630615</t>
   </si>
   <si>
     <t xml:space="preserve">6.02331495285034</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04062271118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04927730560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94456148147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76974725723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78272819519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75416946411133</t>
+    <t xml:space="preserve">6.0406231880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04927682876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94456100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76974678039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78272867202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75416994094849</t>
   </si>
   <si>
     <t xml:space="preserve">5.74118757247925</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73945665359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81042242050171</t>
+    <t xml:space="preserve">5.73945713043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81042194366455</t>
   </si>
   <si>
     <t xml:space="preserve">5.90561819076538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9333119392395</t>
+    <t xml:space="preserve">5.93331146240234</t>
   </si>
   <si>
     <t xml:space="preserve">5.94109964370728</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">5.9108099937439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92638826370239</t>
+    <t xml:space="preserve">5.92638778686523</t>
   </si>
   <si>
     <t xml:space="preserve">5.85369253158569</t>
@@ -2105,34 +2105,34 @@
     <t xml:space="preserve">5.68060874938965</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73253393173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81907606124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90648317337036</t>
+    <t xml:space="preserve">5.73253440856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81907558441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9064826965332</t>
   </si>
   <si>
     <t xml:space="preserve">5.70570611953735</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57502746582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75589990615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81561374664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76022720336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73513031005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72041797637939</t>
+    <t xml:space="preserve">5.57502794265747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75590085983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81561422348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7602276802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73512983322144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72041749954224</t>
   </si>
   <si>
     <t xml:space="preserve">5.69791698455811</t>
@@ -2141,61 +2141,61 @@
     <t xml:space="preserve">5.69272470474243</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62868404388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75936126708984</t>
+    <t xml:space="preserve">5.62868452072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75936222076416</t>
   </si>
   <si>
     <t xml:space="preserve">5.65810775756836</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57243156433105</t>
+    <t xml:space="preserve">5.57243204116821</t>
   </si>
   <si>
     <t xml:space="preserve">5.62522220611572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67282009124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58195114135742</t>
+    <t xml:space="preserve">5.6728196144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58195066452026</t>
   </si>
   <si>
     <t xml:space="preserve">5.58454751968384</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6451268196106</t>
+    <t xml:space="preserve">5.64512586593628</t>
   </si>
   <si>
     <t xml:space="preserve">5.72561120986938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61483716964722</t>
+    <t xml:space="preserve">5.61483669281006</t>
   </si>
   <si>
     <t xml:space="preserve">5.60704851150513</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65291547775269</t>
+    <t xml:space="preserve">5.65291595458984</t>
   </si>
   <si>
     <t xml:space="preserve">5.6555118560791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75503492355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84071159362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00600624084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92811870574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87619352340698</t>
+    <t xml:space="preserve">5.75503444671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84071111679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00600576400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92811822891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87619304656982</t>
   </si>
   <si>
     <t xml:space="preserve">5.71436023712158</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">5.4218487739563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36213541030884</t>
+    <t xml:space="preserve">5.36213445663452</t>
   </si>
   <si>
     <t xml:space="preserve">5.19510841369629</t>
@@ -2213,7 +2213,7 @@
     <t xml:space="preserve">5.040198802948</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15443420410156</t>
+    <t xml:space="preserve">5.1544337272644</t>
   </si>
   <si>
     <t xml:space="preserve">5.18039703369141</t>
@@ -2222,55 +2222,55 @@
     <t xml:space="preserve">4.79615068435669</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24358129501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30113124847412</t>
+    <t xml:space="preserve">4.24358081817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30113172531128</t>
   </si>
   <si>
     <t xml:space="preserve">4.30718946456909</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94501161575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11073923110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98092699050903</t>
+    <t xml:space="preserve">3.94501113891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11073970794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9809262752533</t>
   </si>
   <si>
     <t xml:space="preserve">3.77452373504639</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89438462257385</t>
+    <t xml:space="preserve">3.89438438415527</t>
   </si>
   <si>
     <t xml:space="preserve">4.17564535140991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8238525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97486853599548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07006406784058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27387046813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11766290664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05665063858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25699520111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30978536605835</t>
+    <t xml:space="preserve">3.82385277748108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97486805915833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07006454467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27387094497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11766242980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05665016174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25699472427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30978584289551</t>
   </si>
   <si>
     <t xml:space="preserve">4.37036514282227</t>
@@ -2282,19 +2282,19 @@
     <t xml:space="preserve">4.32709407806396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45690727233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61268186569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48286962509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62999057769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56941080093384</t>
+    <t xml:space="preserve">4.45690679550171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6126823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48286914825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6299901008606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.569411277771</t>
   </si>
   <si>
     <t xml:space="preserve">4.57806539535522</t>
@@ -2303,10 +2303,10 @@
     <t xml:space="preserve">4.5261402130127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50017786026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74249505996704</t>
+    <t xml:space="preserve">4.50017738342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74249458312988</t>
   </si>
   <si>
     <t xml:space="preserve">4.76845741271973</t>
@@ -2315,25 +2315,25 @@
     <t xml:space="preserve">4.79441976547241</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94154167175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91557788848877</t>
+    <t xml:space="preserve">4.94154119491577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91557884216309</t>
   </si>
   <si>
     <t xml:space="preserve">4.83769130706787</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58671998977661</t>
+    <t xml:space="preserve">4.58671951293945</t>
   </si>
   <si>
     <t xml:space="preserve">4.55210304260254</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62133693695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6732611656189</t>
+    <t xml:space="preserve">4.62133646011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67326211929321</t>
   </si>
   <si>
     <t xml:space="preserve">4.80307483673096</t>
@@ -2354,13 +2354,13 @@
     <t xml:space="preserve">4.91848993301392</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10493135452271</t>
+    <t xml:space="preserve">5.10493087768555</t>
   </si>
   <si>
     <t xml:space="preserve">5.22034692764282</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19371223449707</t>
+    <t xml:space="preserve">5.19371271133423</t>
   </si>
   <si>
     <t xml:space="preserve">5.39790964126587</t>
@@ -2369,10 +2369,10 @@
     <t xml:space="preserve">5.44229984283447</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3002495765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52220392227173</t>
+    <t xml:space="preserve">5.30025005340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52220344543457</t>
   </si>
   <si>
     <t xml:space="preserve">5.49556922912598</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">5.72640037536621</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81518220901489</t>
+    <t xml:space="preserve">5.81518268585205</t>
   </si>
   <si>
     <t xml:space="preserve">5.63761949539185</t>
@@ -2393,10 +2393,10 @@
     <t xml:space="preserve">5.30912780761719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27361631393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23810338973999</t>
+    <t xml:space="preserve">5.27361583709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23810291290283</t>
   </si>
   <si>
     <t xml:space="preserve">5.55771636962891</t>
@@ -2405,22 +2405,22 @@
     <t xml:space="preserve">5.73527908325195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61098480224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65537595748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68201017379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61986351013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64649820327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71752262115479</t>
+    <t xml:space="preserve">5.61098527908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65537548065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68201065063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61986303329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64649772644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71752309799194</t>
   </si>
   <si>
     <t xml:space="preserve">5.5843505859375</t>
@@ -2432,7 +2432,7 @@
     <t xml:space="preserve">5.53108167648315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4600567817688</t>
+    <t xml:space="preserve">5.46005725860596</t>
   </si>
   <si>
     <t xml:space="preserve">5.35351943969727</t>
@@ -2441,19 +2441,19 @@
     <t xml:space="preserve">5.42454433441162</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41566562652588</t>
+    <t xml:space="preserve">5.41566610336304</t>
   </si>
   <si>
     <t xml:space="preserve">5.31800603866577</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3890323638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29137182235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21146821975708</t>
+    <t xml:space="preserve">5.38903188705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29137277603149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21146869659424</t>
   </si>
   <si>
     <t xml:space="preserve">5.36239719390869</t>
@@ -2468,10 +2468,10 @@
     <t xml:space="preserve">5.37127542495728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48669099807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59322881698608</t>
+    <t xml:space="preserve">5.48669052124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59322929382324</t>
   </si>
   <si>
     <t xml:space="preserve">5.53995990753174</t>
@@ -2486,10 +2486,10 @@
     <t xml:space="preserve">5.34464073181152</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28249359130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20259094238281</t>
+    <t xml:space="preserve">5.28249311447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20259046554565</t>
   </si>
   <si>
     <t xml:space="preserve">5.32688426971436</t>
@@ -2510,7 +2510,7 @@
     <t xml:space="preserve">5.16707801818848</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18483400344849</t>
+    <t xml:space="preserve">5.18483448028564</t>
   </si>
   <si>
     <t xml:space="preserve">5.02502727508545</t>
@@ -2519,7 +2519,7 @@
     <t xml:space="preserve">4.90073394775391</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61663341522217</t>
+    <t xml:space="preserve">4.61663293838501</t>
   </si>
   <si>
     <t xml:space="preserve">4.72317123413086</t>
@@ -2528,31 +2528,31 @@
     <t xml:space="preserve">4.85634279251099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99839353561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0072717666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89185523986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98951530456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90396356582642</t>
+    <t xml:space="preserve">4.99839401245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00727128982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89185571670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98951435089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90396308898926</t>
   </si>
   <si>
     <t xml:space="preserve">6.01050138473511</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01938009262085</t>
+    <t xml:space="preserve">6.01937961578369</t>
   </si>
   <si>
     <t xml:space="preserve">5.99274492263794</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09928226470947</t>
+    <t xml:space="preserve">6.09928274154663</t>
   </si>
   <si>
     <t xml:space="preserve">6.10816097259521</t>
@@ -2561,16 +2561,16 @@
     <t xml:space="preserve">6.35674905776978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18806409835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2413330078125</t>
+    <t xml:space="preserve">6.188063621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24133348464966</t>
   </si>
   <si>
     <t xml:space="preserve">6.28572368621826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3212366104126</t>
+    <t xml:space="preserve">6.32123613357544</t>
   </si>
   <si>
     <t xml:space="preserve">6.25021123886108</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">6.08152627944946</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06377029418945</t>
+    <t xml:space="preserve">6.06376981735229</t>
   </si>
   <si>
     <t xml:space="preserve">6.05489253997803</t>
@@ -2597,52 +2597,52 @@
     <t xml:space="preserve">5.98386669158936</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96611022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93947649002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94835424423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92172050476074</t>
+    <t xml:space="preserve">5.96611070632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93947601318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94835376739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92172002792358</t>
   </si>
   <si>
     <t xml:space="preserve">5.912841796875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23245429992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46328639984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33011436462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27684545516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20582103729248</t>
+    <t xml:space="preserve">6.23245477676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46328687667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33011388778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27684593200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20582008361816</t>
   </si>
   <si>
     <t xml:space="preserve">6.04601383209229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37450504302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12591695785522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21469831466675</t>
+    <t xml:space="preserve">6.37450551986694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12591743469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21469926834106</t>
   </si>
   <si>
     <t xml:space="preserve">6.17918634414673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26796770095825</t>
+    <t xml:space="preserve">6.26796722412109</t>
   </si>
   <si>
     <t xml:space="preserve">6.48104286193848</t>
@@ -2651,40 +2651,40 @@
     <t xml:space="preserve">6.66748428344727</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01373100280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43988275527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54641914367676</t>
+    <t xml:space="preserve">7.01373147964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43988227844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54641962051392</t>
   </si>
   <si>
     <t xml:space="preserve">7.59968948364258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63520240783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68846940994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52866315841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31558799743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30670976638794</t>
+    <t xml:space="preserve">7.63520193099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68846988677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52866268157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31558847427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30670928955078</t>
   </si>
   <si>
     <t xml:space="preserve">7.18241596221924</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29783153533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13802528381348</t>
+    <t xml:space="preserve">7.29783201217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13802576065063</t>
   </si>
   <si>
     <t xml:space="preserve">7.04924345016479</t>
@@ -2696,22 +2696,22 @@
     <t xml:space="preserve">7.21792888641357</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35109996795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48427391052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59080982208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58193254470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65295696258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51090669631958</t>
+    <t xml:space="preserve">7.3511004447937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48427295684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59081029891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58193206787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65295791625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5109076499939</t>
   </si>
   <si>
     <t xml:space="preserve">7.45763826370239</t>
@@ -2720,16 +2720,16 @@
     <t xml:space="preserve">7.17353820800781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61744403839111</t>
+    <t xml:space="preserve">7.61744451522827</t>
   </si>
   <si>
     <t xml:space="preserve">7.67959213256836</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76837301254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9370584487915</t>
+    <t xml:space="preserve">7.76837253570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93705654144287</t>
   </si>
   <si>
     <t xml:space="preserve">8.19452381134033</t>
@@ -2738,7 +2738,7 @@
     <t xml:space="preserve">8.09686470031738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99920511245728</t>
+    <t xml:space="preserve">7.99920463562012</t>
   </si>
   <si>
     <t xml:space="preserve">8.17676734924316</t>
@@ -2750,7 +2750,7 @@
     <t xml:space="preserve">7.99032640457153</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08798503875732</t>
+    <t xml:space="preserve">8.08798599243164</t>
   </si>
   <si>
     <t xml:space="preserve">8.05247402191162</t>
@@ -2762,7 +2762,7 @@
     <t xml:space="preserve">8.00808334350586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07910919189453</t>
+    <t xml:space="preserve">8.07910823822021</t>
   </si>
   <si>
     <t xml:space="preserve">8.14125537872314</t>
@@ -2771,34 +2771,34 @@
     <t xml:space="preserve">8.07023048400879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15013217926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38984298706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23891448974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44311237335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38096523284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51413822174072</t>
+    <t xml:space="preserve">8.15013313293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38984394073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23891544342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44311141967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3809642791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51413726806641</t>
   </si>
   <si>
     <t xml:space="preserve">8.43423461914062</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64730930328369</t>
+    <t xml:space="preserve">8.64730834960938</t>
   </si>
   <si>
     <t xml:space="preserve">8.42535495758057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47014427185059</t>
+    <t xml:space="preserve">8.47014331817627</t>
   </si>
   <si>
     <t xml:space="preserve">8.60530662536621</t>
@@ -2810,7 +2810,7 @@
     <t xml:space="preserve">8.4160795211792</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3710241317749</t>
+    <t xml:space="preserve">8.37102603912354</t>
   </si>
   <si>
     <t xml:space="preserve">8.56025123596191</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">8.62332725524902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75849056243896</t>
+    <t xml:space="preserve">8.75848960876465</t>
   </si>
   <si>
     <t xml:space="preserve">8.6593713760376</t>
@@ -2843,7 +2843,7 @@
     <t xml:space="preserve">8.47915554046631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50618648529053</t>
+    <t xml:space="preserve">8.50618743896484</t>
   </si>
   <si>
     <t xml:space="preserve">8.51519775390625</t>
@@ -2852,10 +2852,10 @@
     <t xml:space="preserve">8.5332202911377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46113300323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27190685272217</t>
+    <t xml:space="preserve">8.4611349105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27190780639648</t>
   </si>
   <si>
     <t xml:space="preserve">8.10971355438232</t>
@@ -2873,61 +2873,61 @@
     <t xml:space="preserve">8.05564785003662</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95652866363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00158214569092</t>
+    <t xml:space="preserve">7.95652914047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00158309936523</t>
   </si>
   <si>
     <t xml:space="preserve">7.74928140640259</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85741138458252</t>
+    <t xml:space="preserve">7.8574104309082</t>
   </si>
   <si>
     <t xml:space="preserve">7.78532409667969</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83938837051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74027061462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99257230758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92048597335815</t>
+    <t xml:space="preserve">7.83938932418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74027013778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99257135391235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.920485496521</t>
   </si>
   <si>
     <t xml:space="preserve">8.1727876663208</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29893970489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16377735137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21784210205078</t>
+    <t xml:space="preserve">8.2989387512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16377830505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2178430557251</t>
   </si>
   <si>
     <t xml:space="preserve">7.96553993225098</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60510778427124</t>
+    <t xml:space="preserve">7.60510730743408</t>
   </si>
   <si>
     <t xml:space="preserve">8.07366943359375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24487400054932</t>
+    <t xml:space="preserve">8.244873046875</t>
   </si>
   <si>
     <t xml:space="preserve">8.12773513793945</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48816680908203</t>
+    <t xml:space="preserve">8.48816585540771</t>
   </si>
   <si>
     <t xml:space="preserve">8.38904762268066</t>
@@ -2939,25 +2939,25 @@
     <t xml:space="preserve">8.33498191833496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71343517303467</t>
+    <t xml:space="preserve">8.71343612670898</t>
   </si>
   <si>
     <t xml:space="preserve">8.63233852386475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23586463928223</t>
+    <t xml:space="preserve">8.23586368560791</t>
   </si>
   <si>
     <t xml:space="preserve">8.30795097351074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64134883880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77651119232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55123996734619</t>
+    <t xml:space="preserve">8.64134979248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77651023864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55124282836914</t>
   </si>
   <si>
     <t xml:space="preserve">8.49717712402344</t>
@@ -2969,10 +2969,10 @@
     <t xml:space="preserve">8.19982051849365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03762626647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92949724197388</t>
+    <t xml:space="preserve">8.03762722015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92949771881104</t>
   </si>
   <si>
     <t xml:space="preserve">7.98356151580811</t>
@@ -2981,37 +2981,37 @@
     <t xml:space="preserve">8.01960468292236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88444232940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56906509399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63214159011841</t>
+    <t xml:space="preserve">7.8844428062439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56906461715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63214015960693</t>
   </si>
   <si>
     <t xml:space="preserve">7.57807588577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55104446411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65917253494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67719554901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72224903106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76730298995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71323776245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9385085105896</t>
+    <t xml:space="preserve">7.55104351043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65917301177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67719459533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72224760055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7673020362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71323823928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93850755691528</t>
   </si>
   <si>
     <t xml:space="preserve">8.22685241699219</t>
@@ -3029,25 +3029,25 @@
     <t xml:space="preserve">8.18179798126221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02861595153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80334568023682</t>
+    <t xml:space="preserve">8.02861499786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80334520339966</t>
   </si>
   <si>
     <t xml:space="preserve">7.69521570205688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61411905288696</t>
+    <t xml:space="preserve">7.6141185760498</t>
   </si>
   <si>
     <t xml:space="preserve">7.37983798980713</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33478450775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37082815170288</t>
+    <t xml:space="preserve">7.33478498458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37082767486572</t>
   </si>
   <si>
     <t xml:space="preserve">7.46093559265137</t>
@@ -3056,19 +3056,19 @@
     <t xml:space="preserve">7.36181688308716</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35280656814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4429144859314</t>
+    <t xml:space="preserve">7.35280609130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44291400909424</t>
   </si>
   <si>
     <t xml:space="preserve">7.65016174316406</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46994590759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39786052703857</t>
+    <t xml:space="preserve">7.46994638442993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39786005020142</t>
   </si>
   <si>
     <t xml:space="preserve">7.3257737159729</t>
@@ -3077,10 +3077,10 @@
     <t xml:space="preserve">7.27170896530151</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30775213241577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29874134063721</t>
+    <t xml:space="preserve">7.30775165557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29874181747437</t>
   </si>
   <si>
     <t xml:space="preserve">7.26269865036011</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">7.54203224182129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64115047454834</t>
+    <t xml:space="preserve">7.6411509513855</t>
   </si>
   <si>
     <t xml:space="preserve">7.62312984466553</t>
@@ -3104,13 +3104,13 @@
     <t xml:space="preserve">7.31676292419434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38884878158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45192527770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96534204483032</t>
+    <t xml:space="preserve">7.38884925842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4519248008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96534252166748</t>
   </si>
   <si>
     <t xml:space="preserve">6.92929887771606</t>
@@ -3134,16 +3134,16 @@
     <t xml:space="preserve">6.94732046127319</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88424444198608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90226602554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28071975708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22665548324585</t>
+    <t xml:space="preserve">6.88424491882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90226650238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28071928024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22665500640869</t>
   </si>
   <si>
     <t xml:space="preserve">7.03742837905884</t>
@@ -3152,13 +3152,13 @@
     <t xml:space="preserve">7.14555788040161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19962215423584</t>
+    <t xml:space="preserve">7.199622631073</t>
   </si>
   <si>
     <t xml:space="preserve">7.00138521194458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07347106933594</t>
+    <t xml:space="preserve">7.0734715461731</t>
   </si>
   <si>
     <t xml:space="preserve">6.80314826965332</t>
@@ -3167,13 +3167,13 @@
     <t xml:space="preserve">6.74007225036621</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66798639297485</t>
+    <t xml:space="preserve">6.6679859161377</t>
   </si>
   <si>
     <t xml:space="preserve">6.3616189956665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59590005874634</t>
+    <t xml:space="preserve">6.59589958190918</t>
   </si>
   <si>
     <t xml:space="preserve">6.41568374633789</t>
@@ -3182,7 +3182,7 @@
     <t xml:space="preserve">6.32557582855225</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13634872436523</t>
+    <t xml:space="preserve">6.13634920120239</t>
   </si>
   <si>
     <t xml:space="preserve">5.85701513290405</t>
@@ -3197,19 +3197,19 @@
     <t xml:space="preserve">6.28052186965942</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09129524230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14535999298096</t>
+    <t xml:space="preserve">6.09129571914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14536046981812</t>
   </si>
   <si>
     <t xml:space="preserve">6.3526086807251</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23546838760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46974802017212</t>
+    <t xml:space="preserve">6.2354679107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46974849700928</t>
   </si>
   <si>
     <t xml:space="preserve">6.3886513710022</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">6.37062978744507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28953218460083</t>
+    <t xml:space="preserve">6.28953266143799</t>
   </si>
   <si>
     <t xml:space="preserve">6.31656503677368</t>
@@ -3230,13 +3230,13 @@
     <t xml:space="preserve">6.11832761764526</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12733888626099</t>
+    <t xml:space="preserve">6.12733840942383</t>
   </si>
   <si>
     <t xml:space="preserve">6.27151107788086</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26250028610229</t>
+    <t xml:space="preserve">6.26249980926514</t>
   </si>
   <si>
     <t xml:space="preserve">6.18140316009521</t>
@@ -3245,22 +3245,22 @@
     <t xml:space="preserve">6.29854345321655</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17239284515381</t>
+    <t xml:space="preserve">6.17239236831665</t>
   </si>
   <si>
     <t xml:space="preserve">5.84800386428833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86602544784546</t>
+    <t xml:space="preserve">5.86602592468262</t>
   </si>
   <si>
     <t xml:space="preserve">5.920090675354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89305782318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93811225891113</t>
+    <t xml:space="preserve">5.89305830001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93811178207397</t>
   </si>
   <si>
     <t xml:space="preserve">5.88404703140259</t>
@@ -3269,40 +3269,40 @@
     <t xml:space="preserve">6.10030603408813</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21744680404663</t>
+    <t xml:space="preserve">6.21744632720947</t>
   </si>
   <si>
     <t xml:space="preserve">6.06426286697388</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98316621780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94712257385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0192084312439</t>
+    <t xml:space="preserve">5.98316526412964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9471230506897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01920890808105</t>
   </si>
   <si>
     <t xml:space="preserve">5.99217700958252</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96514368057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97415447235107</t>
+    <t xml:space="preserve">5.96514415740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97415542602539</t>
   </si>
   <si>
     <t xml:space="preserve">5.9561333656311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08228492736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07327365875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03723049163818</t>
+    <t xml:space="preserve">6.08228445053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07327318191528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03723001480103</t>
   </si>
   <si>
     <t xml:space="preserve">6.04001379013062</t>
@@ -3311,19 +3311,19 @@
     <t xml:space="preserve">5.94737577438354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96590328216553</t>
+    <t xml:space="preserve">5.96590280532837</t>
   </si>
   <si>
     <t xml:space="preserve">6.16044425964355</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28087329864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22529029846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20676279067993</t>
+    <t xml:space="preserve">6.28087377548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22528982162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20676231384277</t>
   </si>
   <si>
     <t xml:space="preserve">6.17897176742554</t>
@@ -3341,13 +3341,13 @@
     <t xml:space="preserve">6.00295877456665</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81768226623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83620977401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9288477897644</t>
+    <t xml:space="preserve">5.81768274307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83621025085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92884826660156</t>
   </si>
   <si>
     <t xml:space="preserve">5.8917932510376</t>
@@ -3368,19 +3368,19 @@
     <t xml:space="preserve">5.68798828125</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78062677383423</t>
+    <t xml:space="preserve">5.78062629699707</t>
   </si>
   <si>
     <t xml:space="preserve">5.73430776596069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72504377365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34522724151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4471287727356</t>
+    <t xml:space="preserve">5.72504425048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34522676467896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44712924957275</t>
   </si>
   <si>
     <t xml:space="preserve">5.6046142578125</t>
@@ -3392,10 +3392,10 @@
     <t xml:space="preserve">5.51197528839111</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85473775863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55829477310181</t>
+    <t xml:space="preserve">5.85473728179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55829524993896</t>
   </si>
   <si>
     <t xml:space="preserve">5.71578073501587</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">5.66019725799561</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87326526641846</t>
+    <t xml:space="preserve">5.8732647895813</t>
   </si>
   <si>
     <t xml:space="preserve">5.66946077346802</t>
@@ -3431,16 +3431,16 @@
     <t xml:space="preserve">5.53976774215698</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49344778060913</t>
+    <t xml:space="preserve">5.49344825744629</t>
   </si>
   <si>
     <t xml:space="preserve">5.47492074966431</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37301874160767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39154672622681</t>
+    <t xml:space="preserve">5.37301921844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39154624938965</t>
   </si>
   <si>
     <t xml:space="preserve">5.35449075698853</t>
@@ -3461,10 +3461,10 @@
     <t xml:space="preserve">5.19700622558594</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25258922576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38228225708008</t>
+    <t xml:space="preserve">5.25258874893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38228273391724</t>
   </si>
   <si>
     <t xml:space="preserve">5.13215923309326</t>
@@ -3482,34 +3482,34 @@
     <t xml:space="preserve">5.2340612411499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08583974838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05804872512817</t>
+    <t xml:space="preserve">5.08583927154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05804824829102</t>
   </si>
   <si>
     <t xml:space="preserve">5.01172924041748</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02099323272705</t>
+    <t xml:space="preserve">5.02099370956421</t>
   </si>
   <si>
     <t xml:space="preserve">5.1784782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04878425598145</t>
+    <t xml:space="preserve">5.0487847328186</t>
   </si>
   <si>
     <t xml:space="preserve">5.15068674087524</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00246524810791</t>
+    <t xml:space="preserve">5.00246572494507</t>
   </si>
   <si>
     <t xml:space="preserve">4.8635082244873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91909074783325</t>
+    <t xml:space="preserve">4.91909122467041</t>
   </si>
   <si>
     <t xml:space="preserve">4.97467374801636</t>
@@ -3530,13 +3530,13 @@
     <t xml:space="preserve">5.45639324188232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52123975753784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29890823364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46565675735474</t>
+    <t xml:space="preserve">5.52123928070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29890775680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46565723419189</t>
   </si>
   <si>
     <t xml:space="preserve">5.56755924224854</t>
@@ -3545,7 +3545,7 @@
     <t xml:space="preserve">5.67872476577759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76209926605225</t>
+    <t xml:space="preserve">5.76209878921509</t>
   </si>
   <si>
     <t xml:space="preserve">5.90105676651001</t>
@@ -3572,7 +3572,7 @@
     <t xml:space="preserve">5.64166975021362</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88252878189087</t>
+    <t xml:space="preserve">5.88252830505371</t>
   </si>
   <si>
     <t xml:space="preserve">5.99369478225708</t>
@@ -3581,7 +3581,7 @@
     <t xml:space="preserve">5.98443126678467</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91032028198242</t>
+    <t xml:space="preserve">5.91032075881958</t>
   </si>
   <si>
     <t xml:space="preserve">6.44762229919434</t>
@@ -3605,13 +3605,13 @@
     <t xml:space="preserve">6.89228582382202</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96639633178711</t>
+    <t xml:space="preserve">6.96639680862427</t>
   </si>
   <si>
     <t xml:space="preserve">7.23504734039307</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34621334075928</t>
+    <t xml:space="preserve">7.34621286392212</t>
   </si>
   <si>
     <t xml:space="preserve">7.38326835632324</t>
@@ -3626,10 +3626,10 @@
     <t xml:space="preserve">7.48517084121704</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42958784103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55928134918213</t>
+    <t xml:space="preserve">7.42958831787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55928087234497</t>
   </si>
   <si>
     <t xml:space="preserve">7.39253282546997</t>
@@ -3638,7 +3638,7 @@
     <t xml:space="preserve">7.59633636474609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54075336456299</t>
+    <t xml:space="preserve">7.54075384140015</t>
   </si>
   <si>
     <t xml:space="preserve">7.64265584945679</t>
@@ -3659,10 +3659,10 @@
     <t xml:space="preserve">7.58707237243652</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45737981796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43885135650635</t>
+    <t xml:space="preserve">7.45737934112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43885087966919</t>
   </si>
   <si>
     <t xml:space="preserve">7.08682632446289</t>
@@ -3671,16 +3671,16 @@
     <t xml:space="preserve">7.32768535614014</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10535383224487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18872785568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42032384872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30915784835815</t>
+    <t xml:space="preserve">7.10535335540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18872833251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42032432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30915832519531</t>
   </si>
   <si>
     <t xml:space="preserve">7.29063034057617</t>
@@ -3701,28 +3701,28 @@
     <t xml:space="preserve">7.27210235595703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20725631713867</t>
+    <t xml:space="preserve">7.20725584030151</t>
   </si>
   <si>
     <t xml:space="preserve">7.33694934844971</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31842184066772</t>
+    <t xml:space="preserve">7.31842231750488</t>
   </si>
   <si>
     <t xml:space="preserve">7.26283884048462</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12388181686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04977083206177</t>
+    <t xml:space="preserve">7.12388134002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04977130889893</t>
   </si>
   <si>
     <t xml:space="preserve">6.98492383956909</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07756185531616</t>
+    <t xml:space="preserve">7.07756233215332</t>
   </si>
   <si>
     <t xml:space="preserve">7.22578382492065</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">7.15167284011841</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11461782455444</t>
+    <t xml:space="preserve">7.11461734771729</t>
   </si>
   <si>
     <t xml:space="preserve">7.05903482437134</t>
@@ -70165,7 +70165,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6929398148</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>154065</v>
@@ -70186,6 +70186,32 @@
         <v>1630</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.6912962963</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>309675</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>15.8199996948242</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>16.1200008392334</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>16</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>1625</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CEM.MI.xlsx
+++ b/data/CEM.MI.xlsx
@@ -44,79 +44,79 @@
     <t xml:space="preserve">CEM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68035936355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55656290054321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48867273330688</t>
+    <t xml:space="preserve">4.68035984039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5565619468689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48867321014404</t>
   </si>
   <si>
     <t xml:space="preserve">4.32893419265747</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22110939025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32494115829468</t>
+    <t xml:space="preserve">4.22110986709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32494068145752</t>
   </si>
   <si>
     <t xml:space="preserve">4.2889986038208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29299211502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06137037277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93597531318665</t>
+    <t xml:space="preserve">4.29299259185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06137084960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9359757900238</t>
   </si>
   <si>
     <t xml:space="preserve">3.97431254386902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67560052871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83533954620361</t>
+    <t xml:space="preserve">3.67560029029846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83533930778503</t>
   </si>
   <si>
     <t xml:space="preserve">3.94875383377075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88006663322449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91680645942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87846899032593</t>
+    <t xml:space="preserve">3.88006687164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9168062210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87846922874451</t>
   </si>
   <si>
     <t xml:space="preserve">3.74588561058044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93437838554382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87367677688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73789858818054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57815933227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59892559051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61969208717346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3513298034668</t>
+    <t xml:space="preserve">3.93437719345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87367701530457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7378990650177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57815957069397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59892582893372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61969184875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35132932662964</t>
   </si>
   <si>
     <t xml:space="preserve">3.15005826950073</t>
@@ -125,25 +125,25 @@
     <t xml:space="preserve">3.25069403648376</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13088965415955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20916175842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44238066673279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36251139640808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4759259223938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55419874191284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34653735160828</t>
+    <t xml:space="preserve">3.13088893890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20916199684143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44238090515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3625111579895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47592639923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55419850349426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34653759002686</t>
   </si>
   <si>
     <t xml:space="preserve">3.39126420021057</t>
@@ -158,10 +158,10 @@
     <t xml:space="preserve">3.29222631454468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40244626998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58614611625671</t>
+    <t xml:space="preserve">3.40244650840759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58614587783813</t>
   </si>
   <si>
     <t xml:space="preserve">3.63406825065613</t>
@@ -173,73 +173,73 @@
     <t xml:space="preserve">3.64365220069885</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56058764457703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52065300941467</t>
+    <t xml:space="preserve">3.56058812141418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52065324783325</t>
   </si>
   <si>
     <t xml:space="preserve">3.4982898235321</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52544546127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54940605163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75227522850037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61330199241638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75387239456177</t>
+    <t xml:space="preserve">3.52544522285461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54940581321716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75227546691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61330270767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75387191772461</t>
   </si>
   <si>
     <t xml:space="preserve">3.83214449882507</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67080760002136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70754837989807</t>
+    <t xml:space="preserve">3.67080807685852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70754885673523</t>
   </si>
   <si>
     <t xml:space="preserve">3.65802884101868</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51745820045471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57017254829407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50947189331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54301691055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57975625991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45196557044983</t>
+    <t xml:space="preserve">3.51745843887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57017207145691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50947141647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5430166721344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57975673675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45196533203125</t>
   </si>
   <si>
     <t xml:space="preserve">3.41043329238892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37529015541077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60052227973938</t>
+    <t xml:space="preserve">3.37529039382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60052251815796</t>
   </si>
   <si>
     <t xml:space="preserve">3.48551058769226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54461431503296</t>
+    <t xml:space="preserve">3.54461455345154</t>
   </si>
   <si>
     <t xml:space="preserve">3.59573078155518</t>
@@ -248,31 +248,31 @@
     <t xml:space="preserve">3.77943086624146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7442889213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85770297050476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73949575424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74908065795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70595073699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69317150115967</t>
+    <t xml:space="preserve">3.74428915977478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85770320892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73949599266052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74908041954041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70595026016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69317173957825</t>
   </si>
   <si>
     <t xml:space="preserve">3.67719769477844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79700231552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66601634025574</t>
+    <t xml:space="preserve">3.7970027923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66601586341858</t>
   </si>
   <si>
     <t xml:space="preserve">3.70115828514099</t>
@@ -281,82 +281,82 @@
     <t xml:space="preserve">3.6260814666748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6740026473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64205527305603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53023743629456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45835494995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4743287563324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53193736076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62187027931213</t>
+    <t xml:space="preserve">3.67400217056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64205503463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53023767471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45835447311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47432851791382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53193712234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62187004089355</t>
   </si>
   <si>
     <t xml:space="preserve">3.75758838653564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76085925102234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87532019615173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88349580764771</t>
+    <t xml:space="preserve">3.76085901260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87531971931458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88349533081055</t>
   </si>
   <si>
     <t xml:space="preserve">3.77721047401428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75431871414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70526385307312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66929054260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59734344482422</t>
+    <t xml:space="preserve">3.75431847572327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70526361465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6692898273468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59734296798706</t>
   </si>
   <si>
     <t xml:space="preserve">3.5842616558075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55646371841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38640809059143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31119084358215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29811000823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19673013687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15912175178528</t>
+    <t xml:space="preserve">3.55646395683289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38640832901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31119108200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29810976982117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19672989845276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15912127494812</t>
   </si>
   <si>
     <t xml:space="preserve">3.00705194473267</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15421605110168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03484916687012</t>
+    <t xml:space="preserve">3.15421581268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0348494052887</t>
   </si>
   <si>
     <t xml:space="preserve">3.22289252281189</t>
@@ -365,28 +365,28 @@
     <t xml:space="preserve">3.35206985473633</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10679626464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82881951332092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82064390182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84026598930359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93510484695435</t>
+    <t xml:space="preserve">3.1067967414856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8288197517395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82064414024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84026622772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93510508537292</t>
   </si>
   <si>
     <t xml:space="preserve">3.04302525520325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95799732208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79611706733704</t>
+    <t xml:space="preserve">2.95799708366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79611659049988</t>
   </si>
   <si>
     <t xml:space="preserve">2.76341366767883</t>
@@ -395,10 +395,10 @@
     <t xml:space="preserve">2.76831912994385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84844183921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87787485122681</t>
+    <t xml:space="preserve">2.84844207763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87787461280823</t>
   </si>
   <si>
     <t xml:space="preserve">3.04139018058777</t>
@@ -407,10 +407,10 @@
     <t xml:space="preserve">3.00051140785217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21144652366638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13295888900757</t>
+    <t xml:space="preserve">3.21144676208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13295936584473</t>
   </si>
   <si>
     <t xml:space="preserve">3.07572865486145</t>
@@ -422,19 +422,19 @@
     <t xml:space="preserve">3.1084315776825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9759840965271</t>
+    <t xml:space="preserve">2.97598385810852</t>
   </si>
   <si>
     <t xml:space="preserve">2.92856454849243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17547297477722</t>
+    <t xml:space="preserve">3.1754732131958</t>
   </si>
   <si>
     <t xml:space="preserve">3.18037867546082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15585136413574</t>
+    <t xml:space="preserve">3.15585112571716</t>
   </si>
   <si>
     <t xml:space="preserve">3.18855428695679</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">3.12151288986206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02503848075867</t>
+    <t xml:space="preserve">3.0250391960144</t>
   </si>
   <si>
     <t xml:space="preserve">3.11660742759705</t>
@@ -458,31 +458,31 @@
     <t xml:space="preserve">3.28012299537659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32263708114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43546319007874</t>
+    <t xml:space="preserve">3.32263731956482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43546295166016</t>
   </si>
   <si>
     <t xml:space="preserve">3.40603017807007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46653032302856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43709802627563</t>
+    <t xml:space="preserve">3.46653079986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43709778785706</t>
   </si>
   <si>
     <t xml:space="preserve">3.44854378700256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67910122871399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64639782905579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71834444999695</t>
+    <t xml:space="preserve">3.67910099029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64639806747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71834468841553</t>
   </si>
   <si>
     <t xml:space="preserve">3.69545269012451</t>
@@ -494,19 +494,19 @@
     <t xml:space="preserve">3.85242795944214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80827879905701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82299470901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80337333679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7428719997406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62350583076477</t>
+    <t xml:space="preserve">3.80827808380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82299518585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80337285995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74287223815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62350559234619</t>
   </si>
   <si>
     <t xml:space="preserve">3.56627535820007</t>
@@ -518,13 +518,13 @@
     <t xml:space="preserve">3.51558542251587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65947890281677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60551905632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54501819610596</t>
+    <t xml:space="preserve">3.65947914123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60551929473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54501843452454</t>
   </si>
   <si>
     <t xml:space="preserve">3.64803266525269</t>
@@ -533,13 +533,13 @@
     <t xml:space="preserve">3.64476275444031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38804340362549</t>
+    <t xml:space="preserve">3.38804364204407</t>
   </si>
   <si>
     <t xml:space="preserve">3.48288249969482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45344924926758</t>
+    <t xml:space="preserve">3.45344948768616</t>
   </si>
   <si>
     <t xml:space="preserve">3.43382716178894</t>
@@ -548,40 +548,40 @@
     <t xml:space="preserve">3.5074098110199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56464028358459</t>
+    <t xml:space="preserve">3.56464004516602</t>
   </si>
   <si>
     <t xml:space="preserve">3.55482888221741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56300497055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4845175743103</t>
+    <t xml:space="preserve">3.56300520896912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48451781272888</t>
   </si>
   <si>
     <t xml:space="preserve">3.54338312149048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62514090538025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5908031463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64149260520935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6889123916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66111516952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68727684020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53684282302856</t>
+    <t xml:space="preserve">3.62514114379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59080266952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64149284362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68891215324402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66111493110657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68727707862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53684306144714</t>
   </si>
   <si>
     <t xml:space="preserve">3.63004636764526</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">3.63822221755981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43873238563538</t>
+    <t xml:space="preserve">3.43873286247253</t>
   </si>
   <si>
     <t xml:space="preserve">3.41747617721558</t>
@@ -602,55 +602,55 @@
     <t xml:space="preserve">3.33571839332581</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37169170379639</t>
+    <t xml:space="preserve">3.37169194221497</t>
   </si>
   <si>
     <t xml:space="preserve">3.27521777153015</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22125720977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20981121063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17710781097412</t>
+    <t xml:space="preserve">3.22125744819641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2098114490509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1771080493927</t>
   </si>
   <si>
     <t xml:space="preserve">3.21308159828186</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14767527580261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11333727836609</t>
+    <t xml:space="preserve">3.14767551422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11333703994751</t>
   </si>
   <si>
     <t xml:space="preserve">3.00541687011719</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0168628692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95309209823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9187536239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96453785896301</t>
+    <t xml:space="preserve">3.01686310768127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9530918598175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91875338554382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96453738212585</t>
   </si>
   <si>
     <t xml:space="preserve">2.96780848503113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95636200904846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04793095588684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17220258712769</t>
+    <t xml:space="preserve">2.95636224746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04793047904968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17220282554626</t>
   </si>
   <si>
     <t xml:space="preserve">3.18691945075989</t>
@@ -659,52 +659,52 @@
     <t xml:space="preserve">3.3193666934967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23433899879456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45835542678833</t>
+    <t xml:space="preserve">3.2343385219574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45835518836975</t>
   </si>
   <si>
     <t xml:space="preserve">3.48778772354126</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45181465148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49923419952393</t>
+    <t xml:space="preserve">3.45181441307068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4992344379425</t>
   </si>
   <si>
     <t xml:space="preserve">3.57281565666199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45017862319946</t>
+    <t xml:space="preserve">3.45017886161804</t>
   </si>
   <si>
     <t xml:space="preserve">3.61369490623474</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67746663093567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58916807174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70362877845764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48615264892578</t>
+    <t xml:space="preserve">3.67746615409851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58916735649109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70362830162048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4861524105072</t>
   </si>
   <si>
     <t xml:space="preserve">3.33244824409485</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28666400909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22943329811096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27031230926514</t>
+    <t xml:space="preserve">3.28666377067566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22943305969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2703115940094</t>
   </si>
   <si>
     <t xml:space="preserve">3.24741983413696</t>
@@ -719,28 +719,28 @@
     <t xml:space="preserve">3.26213622093201</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27685236930847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23597359657288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00122690200806</t>
+    <t xml:space="preserve">3.27685260772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23597383499146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00122737884521</t>
   </si>
   <si>
     <t xml:space="preserve">4.04701137542725</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1287693977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16964769363403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17782306671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06336259841919</t>
+    <t xml:space="preserve">4.12877035140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16964817047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17782354354858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06336307525635</t>
   </si>
   <si>
     <t xml:space="preserve">3.95707750320435</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">4.28410863876343</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34542798995972</t>
+    <t xml:space="preserve">4.34542751312256</t>
   </si>
   <si>
     <t xml:space="preserve">4.4721508026123</t>
@@ -779,28 +779,28 @@
     <t xml:space="preserve">4.3617787361145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37812995910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38630628585815</t>
+    <t xml:space="preserve">4.37813091278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.386305809021</t>
   </si>
   <si>
     <t xml:space="preserve">4.56208562850952</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42718553543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3290753364563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25549364089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25140523910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30046081542969</t>
+    <t xml:space="preserve">4.42718458175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32907581329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2554931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25140571594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30046033859253</t>
   </si>
   <si>
     <t xml:space="preserve">4.34951496124268</t>
@@ -809,10 +809,10 @@
     <t xml:space="preserve">4.24322986602783</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24731779098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21052646636963</t>
+    <t xml:space="preserve">4.24731826782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21052694320679</t>
   </si>
   <si>
     <t xml:space="preserve">4.1451210975647</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">4.10424137115479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2227897644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40674591064453</t>
+    <t xml:space="preserve">4.22279024124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40674543380737</t>
   </si>
   <si>
     <t xml:space="preserve">4.36586618423462</t>
@@ -833,16 +833,16 @@
     <t xml:space="preserve">4.27593326568604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3045482635498</t>
+    <t xml:space="preserve">4.30454778671265</t>
   </si>
   <si>
     <t xml:space="preserve">4.28002071380615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44762372970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52938175201416</t>
+    <t xml:space="preserve">4.44762420654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52938222885132</t>
   </si>
   <si>
     <t xml:space="preserve">4.51711893081665</t>
@@ -854,22 +854,22 @@
     <t xml:space="preserve">4.68063402175903</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66019439697266</t>
+    <t xml:space="preserve">4.66019487380981</t>
   </si>
   <si>
     <t xml:space="preserve">4.71333742141724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7337760925293</t>
+    <t xml:space="preserve">4.73377656936646</t>
   </si>
   <si>
     <t xml:space="preserve">4.81962251663208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81144666671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65201950073242</t>
+    <t xml:space="preserve">4.81144714355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65201854705811</t>
   </si>
   <si>
     <t xml:space="preserve">4.34133911132812</t>
@@ -881,13 +881,13 @@
     <t xml:space="preserve">4.25958108901978</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40383386611938</t>
+    <t xml:space="preserve">4.40383434295654</t>
   </si>
   <si>
     <t xml:space="preserve">4.44966411590576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41633367538452</t>
+    <t xml:space="preserve">4.41633415222168</t>
   </si>
   <si>
     <t xml:space="preserve">4.37467050552368</t>
@@ -896,58 +896,58 @@
     <t xml:space="preserve">4.36633729934692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30384159088135</t>
+    <t xml:space="preserve">4.30384206771851</t>
   </si>
   <si>
     <t xml:space="preserve">4.27467727661133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25801181793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31634092330933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26634407043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20801639556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33300590515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3705039024353</t>
+    <t xml:space="preserve">4.25801229476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31634044647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26634502410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20801734924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33300638198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37050342559814</t>
   </si>
   <si>
     <t xml:space="preserve">4.3455057144165</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39133596420288</t>
+    <t xml:space="preserve">4.39133548736572</t>
   </si>
   <si>
     <t xml:space="preserve">4.29967546463013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42883348464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39966869354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3955020904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38300323486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46633052825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48299551010132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.566321849823</t>
+    <t xml:space="preserve">4.4288330078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39966821670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39550161361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38300275802612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46633005142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48299646377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56632232666016</t>
   </si>
   <si>
     <t xml:space="preserve">4.40800094604492</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">5.05795192718506</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10794830322266</t>
+    <t xml:space="preserve">5.1079478263855</t>
   </si>
   <si>
     <t xml:space="preserve">5.24960374832153</t>
@@ -980,97 +980,97 @@
     <t xml:space="preserve">5.28710079193115</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25377082824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41625785827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30376625061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29960012435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34543085098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30793237686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22877216339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29126739501953</t>
+    <t xml:space="preserve">5.25377035140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41625738143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30376672744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29960107803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34543037414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30793285369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22877264022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29126691818237</t>
   </si>
   <si>
     <t xml:space="preserve">5.29543399810791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16211080551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01628828048706</t>
+    <t xml:space="preserve">5.16211032867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0162878036499</t>
   </si>
   <si>
     <t xml:space="preserve">5.05378484725952</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12461376190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20377397537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07461643218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03295373916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95795869827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99129009246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96212530136108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90796279907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94129371643066</t>
+    <t xml:space="preserve">5.1246132850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20377349853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0746169090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0329532623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95795965194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9912896156311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9621262550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90796327590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94129419326782</t>
   </si>
   <si>
     <t xml:space="preserve">4.89129781723022</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90379667282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95379257202148</t>
+    <t xml:space="preserve">4.9037971496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95379304885864</t>
   </si>
   <si>
     <t xml:space="preserve">4.94545984268188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91629600524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02462100982666</t>
+    <t xml:space="preserve">4.91629648208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02462148666382</t>
   </si>
   <si>
     <t xml:space="preserve">5.04961919784546</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11628103256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17460966110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23293876647949</t>
+    <t xml:space="preserve">5.1162805557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17461061477661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23293924331665</t>
   </si>
   <si>
     <t xml:space="preserve">5.17877626419067</t>
@@ -1082,19 +1082,19 @@
     <t xml:space="preserve">5.33293104171753</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26626968383789</t>
+    <t xml:space="preserve">5.26626920700073</t>
   </si>
   <si>
     <t xml:space="preserve">5.22460603713989</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5829119682312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6870698928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00371408462524</t>
+    <t xml:space="preserve">5.58291149139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68707036972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00371313095093</t>
   </si>
   <si>
     <t xml:space="preserve">5.80789470672607</t>
@@ -1103,25 +1103,25 @@
     <t xml:space="preserve">6.0745415687561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01621246337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16620111465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89122295379639</t>
+    <t xml:space="preserve">6.01621341705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16620254516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89122247695923</t>
   </si>
   <si>
     <t xml:space="preserve">5.94121837615967</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96621704101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03287744522095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99538135528564</t>
+    <t xml:space="preserve">5.96621656417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03287839889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9953818321228</t>
   </si>
   <si>
     <t xml:space="preserve">5.97038269042969</t>
@@ -1145,34 +1145,34 @@
     <t xml:space="preserve">5.87455749511719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84539222717285</t>
+    <t xml:space="preserve">5.84539270401001</t>
   </si>
   <si>
     <t xml:space="preserve">6.00788068771362</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98288154602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03704500198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0912070274353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02871227264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99954748153687</t>
+    <t xml:space="preserve">5.98288202285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03704452514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09120655059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02871179580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99954795837402</t>
   </si>
   <si>
     <t xml:space="preserve">6.04954433441162</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07870817184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29119157791138</t>
+    <t xml:space="preserve">6.07870864868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29119205474854</t>
   </si>
   <si>
     <t xml:space="preserve">6.17453336715698</t>
@@ -1184,37 +1184,37 @@
     <t xml:space="preserve">6.08287477493286</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24536180496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21203136444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02454566955566</t>
+    <t xml:space="preserve">6.24536228179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21203184127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02454519271851</t>
   </si>
   <si>
     <t xml:space="preserve">6.09954023361206</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1828670501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2078652381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22036457061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14536952972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95788431167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94538450241089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01204681396484</t>
+    <t xml:space="preserve">6.18286657333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20786476135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22036504745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14537000656128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95788383483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94538545608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01204633712769</t>
   </si>
   <si>
     <t xml:space="preserve">6.02037858963013</t>
@@ -1223,34 +1223,34 @@
     <t xml:space="preserve">6.11620569229126</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06204271316528</t>
+    <t xml:space="preserve">6.06204319000244</t>
   </si>
   <si>
     <t xml:space="preserve">6.04121065139771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1495361328125</t>
+    <t xml:space="preserve">6.14953660964966</t>
   </si>
   <si>
     <t xml:space="preserve">6.09537363052368</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35785388946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22452974319458</t>
+    <t xml:space="preserve">6.35785436630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22453022003174</t>
   </si>
   <si>
     <t xml:space="preserve">6.28285932540894</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58283710479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61616802215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57450342178345</t>
+    <t xml:space="preserve">6.58283662796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6161675453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57450389862061</t>
   </si>
   <si>
     <t xml:space="preserve">6.50784301757812</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">6.49950981140137</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6578311920166</t>
+    <t xml:space="preserve">6.65783071517944</t>
   </si>
   <si>
     <t xml:space="preserve">6.7411584854126</t>
@@ -1268,22 +1268,22 @@
     <t xml:space="preserve">6.59116983413696</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6245002746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6328330039978</t>
+    <t xml:space="preserve">6.62449979782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63283252716064</t>
   </si>
   <si>
     <t xml:space="preserve">6.7078275680542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52450799942017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51617527008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66616439819336</t>
+    <t xml:space="preserve">6.52450752258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51617479324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66616296768188</t>
   </si>
   <si>
     <t xml:space="preserve">6.54950618743896</t>
@@ -1298,10 +1298,10 @@
     <t xml:space="preserve">6.2328634262085</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90788745880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93288612365723</t>
+    <t xml:space="preserve">5.90788793563843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93288564682007</t>
   </si>
   <si>
     <t xml:space="preserve">6.53284072875977</t>
@@ -1310,10 +1310,10 @@
     <t xml:space="preserve">6.26619386672974</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36618614196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33285522460938</t>
+    <t xml:space="preserve">6.36618566513062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33285617828369</t>
   </si>
   <si>
     <t xml:space="preserve">6.14120388031006</t>
@@ -1322,76 +1322,76 @@
     <t xml:space="preserve">6.1578688621521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06620931625366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94955158233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13287115097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0578761100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88288927078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84955930709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81622791290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72456836700439</t>
+    <t xml:space="preserve">6.0662088394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94955110549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1328706741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05787658691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88288974761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84955883026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81622743606567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72456884384155</t>
   </si>
   <si>
     <t xml:space="preserve">5.75789880752563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76623106002808</t>
+    <t xml:space="preserve">5.76623153686523</t>
   </si>
   <si>
     <t xml:space="preserve">5.68290519714355</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82456016540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86622476577759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77456426620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78289747238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79122924804688</t>
+    <t xml:space="preserve">5.82456111907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86622428894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77456474304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78289699554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79123020172119</t>
   </si>
   <si>
     <t xml:space="preserve">5.6329083442688</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6498236656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68365526199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66673946380615</t>
+    <t xml:space="preserve">5.64982414245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68365573883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66673898696899</t>
   </si>
   <si>
     <t xml:space="preserve">5.70057106018066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48066806793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45529460906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54833030700684</t>
+    <t xml:space="preserve">5.48066759109497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45529413223267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54833078384399</t>
   </si>
   <si>
     <t xml:space="preserve">5.53987312316895</t>
@@ -1400,25 +1400,25 @@
     <t xml:space="preserve">5.74286031723022</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58216190338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6582818031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70902872085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77669191360474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91201639175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9035587310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89510011672974</t>
+    <t xml:space="preserve">5.58216142654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65828275680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70902919769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77669143676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91201686859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90355825424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89510059356689</t>
   </si>
   <si>
     <t xml:space="preserve">5.75131797790527</t>
@@ -1427,34 +1427,34 @@
     <t xml:space="preserve">5.78514909744263</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71748733520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81052303314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56524562835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50604200363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69211292266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72594451904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73440217971802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60753536224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51449966430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6751971244812</t>
+    <t xml:space="preserve">5.71748685836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81052350997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56524610519409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50604104995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69211339950562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72594499588013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73440265655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60753440856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51449918746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67519807815552</t>
   </si>
   <si>
     <t xml:space="preserve">6.01351022720337</t>
@@ -1463,31 +1463,31 @@
     <t xml:space="preserve">5.99659490585327</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81898164749146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75977611541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80206489562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79360675811768</t>
+    <t xml:space="preserve">5.81898069381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75977563858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80206537246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79360723495483</t>
   </si>
   <si>
     <t xml:space="preserve">5.88664293289185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87818479537964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92893266677856</t>
+    <t xml:space="preserve">5.87818574905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92893218994141</t>
   </si>
   <si>
     <t xml:space="preserve">5.85281181335449</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76823377609253</t>
+    <t xml:space="preserve">5.76823425292969</t>
   </si>
   <si>
     <t xml:space="preserve">5.82743835449219</t>
@@ -1502,31 +1502,31 @@
     <t xml:space="preserve">5.3876314163208</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33688497543335</t>
+    <t xml:space="preserve">5.33688449859619</t>
   </si>
   <si>
     <t xml:space="preserve">5.26076459884644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30305433273315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43837928771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46375274658203</t>
+    <t xml:space="preserve">5.303053855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43837833404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46375226974487</t>
   </si>
   <si>
     <t xml:space="preserve">5.44683694839478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35380077362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3707160949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22693347930908</t>
+    <t xml:space="preserve">5.35380029678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37071561813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22693300247192</t>
   </si>
   <si>
     <t xml:space="preserve">5.14235496520996</t>
@@ -1535,28 +1535,28 @@
     <t xml:space="preserve">5.11698198318481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24384880065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13389778137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26922178268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25230646133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21001768112183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23539066314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28613805770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31996965408325</t>
+    <t xml:space="preserve">5.24384927749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13389730453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26922273635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25230741500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21001720428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23539113998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28613758087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31996917724609</t>
   </si>
   <si>
     <t xml:space="preserve">5.29459571838379</t>
@@ -1568,19 +1568,19 @@
     <t xml:space="preserve">5.32842683792114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16772937774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09160804748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17618608474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10852384567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91399335861206</t>
+    <t xml:space="preserve">5.16772890090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09160757064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17618560791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10852336883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91399383544922</t>
   </si>
   <si>
     <t xml:space="preserve">4.60105466842651</t>
@@ -1589,10 +1589,10 @@
     <t xml:space="preserve">4.49956083297729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56722259521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38115119934082</t>
+    <t xml:space="preserve">4.56722354888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3811502456665</t>
   </si>
   <si>
     <t xml:space="preserve">4.5418496131897</t>
@@ -1604,22 +1604,22 @@
     <t xml:space="preserve">4.61796998977661</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4657301902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27119970321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14433240890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22045183181763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09358549118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20353651046753</t>
+    <t xml:space="preserve">4.46572923660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27120065689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14433193206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22045230865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09358501434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20353698730469</t>
   </si>
   <si>
     <t xml:space="preserve">4.15701913833618</t>
@@ -1628,28 +1628,28 @@
     <t xml:space="preserve">4.39806652069092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53339147567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59259605407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6095118522644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63488531112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41498231887817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49110269546509</t>
+    <t xml:space="preserve">4.53339195251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59259653091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60951232910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63488578796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41498279571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49110221862793</t>
   </si>
   <si>
     <t xml:space="preserve">4.42344045639038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43189764022827</t>
+    <t xml:space="preserve">4.43189811706543</t>
   </si>
   <si>
     <t xml:space="preserve">4.2965726852417</t>
@@ -1658,58 +1658,58 @@
     <t xml:space="preserve">4.33886194229126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19507932662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04706716537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08512830734253</t>
+    <t xml:space="preserve">4.19507884979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04706764221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08512735366821</t>
   </si>
   <si>
     <t xml:space="preserve">4.10627174377441</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15279006958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2373685836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21622323989868</t>
+    <t xml:space="preserve">4.15279054641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23736810684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.216224193573</t>
   </si>
   <si>
     <t xml:space="preserve">4.16124820709229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10204362869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03860950469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30503129959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2542839050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14010334014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0512957572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14856147766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08935642242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03437995910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94557309150696</t>
+    <t xml:space="preserve">4.10204315185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03860902786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30503082275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25428342819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14010286331177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05129671096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14856100082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08935594558716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0343804359436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9455738067627</t>
   </si>
   <si>
     <t xml:space="preserve">4.35577774047852</t>
@@ -1727,46 +1727,46 @@
     <t xml:space="preserve">4.79558420181274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7871265411377</t>
+    <t xml:space="preserve">4.78712606430054</t>
   </si>
   <si>
     <t xml:space="preserve">4.82095813751221</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86324644088745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90553569793701</t>
+    <t xml:space="preserve">4.86324691772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90553617477417</t>
   </si>
   <si>
     <t xml:space="preserve">4.88862037658691</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95628261566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00703001022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01548719406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03240299224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.057776927948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99011421203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97319841384888</t>
+    <t xml:space="preserve">4.95628309249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00702953338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01548767089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03240346908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05777645111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99011468887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97319889068604</t>
   </si>
   <si>
     <t xml:space="preserve">5.20155954360962</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12543964385986</t>
+    <t xml:space="preserve">5.12543916702271</t>
   </si>
   <si>
     <t xml:space="preserve">5.15927076339722</t>
@@ -1775,10 +1775,10 @@
     <t xml:space="preserve">5.21847534179688</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34534311294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27767992019653</t>
+    <t xml:space="preserve">5.3453426361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27768039703369</t>
   </si>
   <si>
     <t xml:space="preserve">5.40454769134521</t>
@@ -1787,16 +1787,16 @@
     <t xml:space="preserve">5.39609003067017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47220993041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49758386611938</t>
+    <t xml:space="preserve">5.47220945358276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49758291244507</t>
   </si>
   <si>
     <t xml:space="preserve">5.42146301269531</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41300582885742</t>
+    <t xml:space="preserve">5.41300535202026</t>
   </si>
   <si>
     <t xml:space="preserve">4.98165655136108</t>
@@ -1805,7 +1805,7 @@
     <t xml:space="preserve">5.11462497711182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13193273544312</t>
+    <t xml:space="preserve">5.13193321228027</t>
   </si>
   <si>
     <t xml:space="preserve">5.01942920684814</t>
@@ -1814,10 +1814,10 @@
     <t xml:space="preserve">5.01077461242676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06269979476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08866262435913</t>
+    <t xml:space="preserve">5.06269931793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08866310119629</t>
   </si>
   <si>
     <t xml:space="preserve">5.09731674194336</t>
@@ -1835,22 +1835,22 @@
     <t xml:space="preserve">5.2271294593811</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26174592971802</t>
+    <t xml:space="preserve">5.26174640655518</t>
   </si>
   <si>
     <t xml:space="preserve">5.23578405380249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25309181213379</t>
+    <t xml:space="preserve">5.25309228897095</t>
   </si>
   <si>
     <t xml:space="preserve">5.33963394165039</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46079206466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54733467102051</t>
+    <t xml:space="preserve">5.46079254150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54733419418335</t>
   </si>
   <si>
     <t xml:space="preserve">5.42617607116699</t>
@@ -1871,13 +1871,13 @@
     <t xml:space="preserve">5.47810077667236</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64253044128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76368856430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74638032913208</t>
+    <t xml:space="preserve">5.64253091812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7636890411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74637985229492</t>
   </si>
   <si>
     <t xml:space="preserve">5.72907209396362</t>
@@ -1886,13 +1886,13 @@
     <t xml:space="preserve">5.65118455886841</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7031102180481</t>
+    <t xml:space="preserve">5.70310974121094</t>
   </si>
   <si>
     <t xml:space="preserve">5.66849374771118</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59925937652588</t>
+    <t xml:space="preserve">5.59925889968872</t>
   </si>
   <si>
     <t xml:space="preserve">5.49540901184082</t>
@@ -1901,73 +1901,73 @@
     <t xml:space="preserve">5.45213842391968</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56464242935181</t>
+    <t xml:space="preserve">5.56464290618896</t>
   </si>
   <si>
     <t xml:space="preserve">5.73772621154785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51271724700928</t>
+    <t xml:space="preserve">5.51271772384644</t>
   </si>
   <si>
     <t xml:space="preserve">5.24443769454956</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1838583946228</t>
+    <t xml:space="preserve">5.18385791778564</t>
   </si>
   <si>
     <t xml:space="preserve">5.28770923614502</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19251298904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12327909469604</t>
+    <t xml:space="preserve">5.19251251220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12327861785889</t>
   </si>
   <si>
     <t xml:space="preserve">5.2704005241394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08000802993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14924192428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16654968261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15789604187012</t>
+    <t xml:space="preserve">5.0800085067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14924144744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16655015945435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15789556503296</t>
   </si>
   <si>
     <t xml:space="preserve">5.29636287689209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53868055343628</t>
+    <t xml:space="preserve">5.53868007659912</t>
   </si>
   <si>
     <t xml:space="preserve">5.44348430633545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48675489425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40021371841431</t>
+    <t xml:space="preserve">5.48675537109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40021324157715</t>
   </si>
   <si>
     <t xml:space="preserve">5.36559629440308</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32232570648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38290452957153</t>
+    <t xml:space="preserve">5.32232522964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38290500640869</t>
   </si>
   <si>
     <t xml:space="preserve">5.02808284759521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04539108276367</t>
+    <t xml:space="preserve">5.04539203643799</t>
   </si>
   <si>
     <t xml:space="preserve">5.16222381591797</t>
@@ -1976,10 +1976,10 @@
     <t xml:space="preserve">5.03933382034302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10597085952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15270328521729</t>
+    <t xml:space="preserve">5.10597133636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15270376205444</t>
   </si>
   <si>
     <t xml:space="preserve">5.20895528793335</t>
@@ -2003,31 +2003,31 @@
     <t xml:space="preserve">5.26780414581299</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34742259979248</t>
+    <t xml:space="preserve">5.34742212295532</t>
   </si>
   <si>
     <t xml:space="preserve">5.21934080123901</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34309577941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48502349853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43915700912476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3179988861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51791000366211</t>
+    <t xml:space="preserve">5.3430962562561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48502397537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4391565322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31799840927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51791048049927</t>
   </si>
   <si>
     <t xml:space="preserve">5.61656761169434</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51617860794067</t>
+    <t xml:space="preserve">5.51617956161499</t>
   </si>
   <si>
     <t xml:space="preserve">5.46252298355103</t>
@@ -2036,13 +2036,13 @@
     <t xml:space="preserve">5.42271423339844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46771574020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44434976577759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46944713592529</t>
+    <t xml:space="preserve">5.4677152633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44434928894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46944665908813</t>
   </si>
   <si>
     <t xml:space="preserve">5.78099727630615</t>
@@ -2051,10 +2051,10 @@
     <t xml:space="preserve">6.02331447601318</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04062366485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04927682876587</t>
+    <t xml:space="preserve">6.0406231880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04927730560303</t>
   </si>
   <si>
     <t xml:space="preserve">5.94456195831299</t>
@@ -2063,19 +2063,19 @@
     <t xml:space="preserve">5.76974678039551</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78272867202759</t>
+    <t xml:space="preserve">5.78272914886475</t>
   </si>
   <si>
     <t xml:space="preserve">5.75416994094849</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74118852615356</t>
+    <t xml:space="preserve">5.74118804931641</t>
   </si>
   <si>
     <t xml:space="preserve">5.73945713043213</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81042146682739</t>
+    <t xml:space="preserve">5.81042194366455</t>
   </si>
   <si>
     <t xml:space="preserve">5.90561771392822</t>
@@ -2087,31 +2087,31 @@
     <t xml:space="preserve">5.94109964370728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91081047058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92638778686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85369253158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85628986358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68060874938965</t>
+    <t xml:space="preserve">5.9108099937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92638826370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85369205474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85628938674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68060922622681</t>
   </si>
   <si>
     <t xml:space="preserve">5.73253440856934</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81907558441162</t>
+    <t xml:space="preserve">5.81907606124878</t>
   </si>
   <si>
     <t xml:space="preserve">5.90648317337036</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70570611953735</t>
+    <t xml:space="preserve">5.7057056427002</t>
   </si>
   <si>
     <t xml:space="preserve">5.57502794265747</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">5.75590038299561</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81561422348022</t>
+    <t xml:space="preserve">5.81561470031738</t>
   </si>
   <si>
     <t xml:space="preserve">5.76022815704346</t>
@@ -2132,28 +2132,28 @@
     <t xml:space="preserve">5.72041845321655</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69791698455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69272518157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62868452072144</t>
+    <t xml:space="preserve">5.69791746139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69272565841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62868404388428</t>
   </si>
   <si>
     <t xml:space="preserve">5.75936222076416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65810823440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57243156433105</t>
+    <t xml:space="preserve">5.6581072807312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57243204116821</t>
   </si>
   <si>
     <t xml:space="preserve">5.62522220611572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6728196144104</t>
+    <t xml:space="preserve">5.67282009124756</t>
   </si>
   <si>
     <t xml:space="preserve">5.58195114135742</t>
@@ -2165,19 +2165,19 @@
     <t xml:space="preserve">5.64512634277344</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72561120986938</t>
+    <t xml:space="preserve">5.72561073303223</t>
   </si>
   <si>
     <t xml:space="preserve">5.61483669281006</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60704851150513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65291595458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6555118560791</t>
+    <t xml:space="preserve">5.60704898834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65291547775269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65551137924194</t>
   </si>
   <si>
     <t xml:space="preserve">5.75503540039062</t>
@@ -2186,25 +2186,25 @@
     <t xml:space="preserve">5.84071159362793</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00600576400757</t>
+    <t xml:space="preserve">6.00600624084473</t>
   </si>
   <si>
     <t xml:space="preserve">5.92811870574951</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87619304656982</t>
+    <t xml:space="preserve">5.87619400024414</t>
   </si>
   <si>
     <t xml:space="preserve">5.71436023712158</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4218487739563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36213493347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19510889053345</t>
+    <t xml:space="preserve">5.42184782028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36213445663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19510936737061</t>
   </si>
   <si>
     <t xml:space="preserve">5.040198802948</t>
@@ -2213,85 +2213,85 @@
     <t xml:space="preserve">5.15443420410156</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18039655685425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79615068435669</t>
+    <t xml:space="preserve">5.18039703369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79615116119385</t>
   </si>
   <si>
     <t xml:space="preserve">4.24358081817627</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30113077163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30718946456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94501161575317</t>
+    <t xml:space="preserve">4.30113124847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30718898773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94501137733459</t>
   </si>
   <si>
     <t xml:space="preserve">4.11073923110962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98092603683472</t>
+    <t xml:space="preserve">3.98092579841614</t>
   </si>
   <si>
     <t xml:space="preserve">3.77452349662781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89438486099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17564535140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82385301589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97486805915833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07006454467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27387094497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11766290664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05665063858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25699472427368</t>
+    <t xml:space="preserve">3.89438438415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17564582824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82385277748108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97486782073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07006406784058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27386999130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11766242980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05665016174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25699520111084</t>
   </si>
   <si>
     <t xml:space="preserve">4.30978584289551</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37036514282227</t>
+    <t xml:space="preserve">4.37036561965942</t>
   </si>
   <si>
     <t xml:space="preserve">4.17131805419922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32709360122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45690631866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61268186569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48286914825439</t>
+    <t xml:space="preserve">4.32709407806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45690679550171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6126823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48286867141724</t>
   </si>
   <si>
     <t xml:space="preserve">4.6299901008606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56941175460815</t>
+    <t xml:space="preserve">4.569411277771</t>
   </si>
   <si>
     <t xml:space="preserve">4.57806539535522</t>
@@ -2300,7 +2300,7 @@
     <t xml:space="preserve">4.52614068984985</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50017738342285</t>
+    <t xml:space="preserve">4.50017786026001</t>
   </si>
   <si>
     <t xml:space="preserve">4.74249458312988</t>
@@ -2312,10 +2312,10 @@
     <t xml:space="preserve">4.79442024230957</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94154119491577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91557836532593</t>
+    <t xml:space="preserve">4.94154071807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91557884216309</t>
   </si>
   <si>
     <t xml:space="preserve">4.83769130706787</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">4.67326211929321</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80307531356812</t>
+    <t xml:space="preserve">4.80307483673096</t>
   </si>
   <si>
     <t xml:space="preserve">4.90961217880249</t>
@@ -70304,7 +70304,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6912615741</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>92400</v>
@@ -70325,6 +70325,32 @@
         <v>1633</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6912962963</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>133873</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>15.7600002288818</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>15.4399995803833</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>15.7600002288818</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>15.6400003433228</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>1595</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CEM.MI.xlsx
+++ b/data/CEM.MI.xlsx
@@ -56,16 +56,16 @@
     <t xml:space="preserve">4.32893371582031</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22110986709595</t>
+    <t xml:space="preserve">4.22111034393311</t>
   </si>
   <si>
     <t xml:space="preserve">4.3249397277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28899908065796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29299259185791</t>
+    <t xml:space="preserve">4.2889986038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29299211502075</t>
   </si>
   <si>
     <t xml:space="preserve">4.06137084960938</t>
@@ -74,31 +74,31 @@
     <t xml:space="preserve">3.93597507476807</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97431302070618</t>
+    <t xml:space="preserve">3.97431230545044</t>
   </si>
   <si>
     <t xml:space="preserve">3.67560005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83534026145935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94875407218933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88006615638733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91680669784546</t>
+    <t xml:space="preserve">3.83533978462219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94875431060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88006639480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91680693626404</t>
   </si>
   <si>
     <t xml:space="preserve">3.87846922874451</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74588561058044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93437838554382</t>
+    <t xml:space="preserve">3.74588537216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93437814712524</t>
   </si>
   <si>
     <t xml:space="preserve">3.87367677688599</t>
@@ -107,19 +107,19 @@
     <t xml:space="preserve">3.73789811134338</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57815957069397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59892511367798</t>
+    <t xml:space="preserve">3.57815909385681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59892535209656</t>
   </si>
   <si>
     <t xml:space="preserve">3.6196916103363</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3513298034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15005803108215</t>
+    <t xml:space="preserve">3.35133004188538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15005826950073</t>
   </si>
   <si>
     <t xml:space="preserve">3.25069403648376</t>
@@ -128,13 +128,13 @@
     <t xml:space="preserve">3.13088941574097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20916199684143</t>
+    <t xml:space="preserve">3.20916175842285</t>
   </si>
   <si>
     <t xml:space="preserve">3.44238066673279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3625111579895</t>
+    <t xml:space="preserve">3.36251139640808</t>
   </si>
   <si>
     <t xml:space="preserve">3.47592663764954</t>
@@ -146,49 +146,49 @@
     <t xml:space="preserve">3.3465371131897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39126396179199</t>
+    <t xml:space="preserve">3.39126443862915</t>
   </si>
   <si>
     <t xml:space="preserve">3.36730360984802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23951244354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29222655296326</t>
+    <t xml:space="preserve">3.2395122051239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29222631454468</t>
   </si>
   <si>
     <t xml:space="preserve">3.40244650840759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58614563941956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63406777381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55579590797424</t>
+    <t xml:space="preserve">3.58614659309387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63406801223755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5557963848114</t>
   </si>
   <si>
     <t xml:space="preserve">3.64365243911743</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56058835983276</t>
+    <t xml:space="preserve">3.56058812141418</t>
   </si>
   <si>
     <t xml:space="preserve">3.52065300941467</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49828958511353</t>
+    <t xml:space="preserve">3.49829006195068</t>
   </si>
   <si>
     <t xml:space="preserve">3.52544569969177</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54940629005432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75227475166321</t>
+    <t xml:space="preserve">3.54940605163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75227451324463</t>
   </si>
   <si>
     <t xml:space="preserve">3.61330199241638</t>
@@ -197,85 +197,85 @@
     <t xml:space="preserve">3.75387191772461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83214426040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67080807685852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70754766464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65802884101868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51745772361755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57017254829407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50947141647339</t>
+    <t xml:space="preserve">3.83214449882507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6708083152771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70754837989807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6580286026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51745820045471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57017230987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50947165489197</t>
   </si>
   <si>
     <t xml:space="preserve">3.5430166721344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57975697517395</t>
+    <t xml:space="preserve">3.57975649833679</t>
   </si>
   <si>
     <t xml:space="preserve">3.45196557044983</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41043257713318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37529063224792</t>
+    <t xml:space="preserve">3.41043305397034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37529039382935</t>
   </si>
   <si>
     <t xml:space="preserve">3.60052299499512</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48551034927368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54461407661438</t>
+    <t xml:space="preserve">3.4855101108551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54461359977722</t>
   </si>
   <si>
     <t xml:space="preserve">3.59573006629944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77943062782288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74428796768188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85770320892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73949670791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74908018112183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70595026016235</t>
+    <t xml:space="preserve">3.77943086624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74428868293762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85770344734192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7394962310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74907970428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70595049858093</t>
   </si>
   <si>
     <t xml:space="preserve">3.69317173957825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67719769477844</t>
+    <t xml:space="preserve">3.6771981716156</t>
   </si>
   <si>
     <t xml:space="preserve">3.79700231552124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.666015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70115876197815</t>
+    <t xml:space="preserve">3.66601586341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70115828514099</t>
   </si>
   <si>
     <t xml:space="preserve">3.62608098983765</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">3.6740026473999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64205551147461</t>
+    <t xml:space="preserve">3.64205527305603</t>
   </si>
   <si>
     <t xml:space="preserve">3.53023767471313</t>
@@ -293,46 +293,46 @@
     <t xml:space="preserve">3.45835471153259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47432851791382</t>
+    <t xml:space="preserve">3.4743287563324</t>
   </si>
   <si>
     <t xml:space="preserve">3.53193712234497</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62187075614929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7575888633728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76085805892944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87531995773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88349533081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77721047401428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75431847572327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70526385307312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66929030418396</t>
+    <t xml:space="preserve">3.62187051773071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75758910179138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76085877418518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87532043457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88349580764771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7772102355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75431823730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70526337623596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66929054260254</t>
   </si>
   <si>
     <t xml:space="preserve">3.59734344482422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5842616558075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55646395683289</t>
+    <t xml:space="preserve">3.58426189422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55646419525146</t>
   </si>
   <si>
     <t xml:space="preserve">3.38640832901001</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">3.29810976982117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19673013687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15912103652954</t>
+    <t xml:space="preserve">3.19672989845276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15912127494812</t>
   </si>
   <si>
     <t xml:space="preserve">3.00705170631409</t>
@@ -356,19 +356,19 @@
     <t xml:space="preserve">3.15421581268311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03484964370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22289276123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35207009315491</t>
+    <t xml:space="preserve">3.0348494052887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22289228439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35206985473633</t>
   </si>
   <si>
     <t xml:space="preserve">3.10679650306702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82882046699524</t>
+    <t xml:space="preserve">2.82881999015808</t>
   </si>
   <si>
     <t xml:space="preserve">2.82064414024353</t>
@@ -380,10 +380,10 @@
     <t xml:space="preserve">2.93510508537292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04302501678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95799708366394</t>
+    <t xml:space="preserve">3.04302549362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9579975605011</t>
   </si>
   <si>
     <t xml:space="preserve">2.79611659049988</t>
@@ -392,22 +392,22 @@
     <t xml:space="preserve">2.76341390609741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76831912994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84844183921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87787461280823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04139018058777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00051164627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21144652366638</t>
+    <t xml:space="preserve">2.76831889152527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84844160079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87787485122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04139041900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00051140785217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2114462852478</t>
   </si>
   <si>
     <t xml:space="preserve">3.13295912742615</t>
@@ -416,13 +416,13 @@
     <t xml:space="preserve">3.07572865486145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9743492603302</t>
+    <t xml:space="preserve">2.97434878349304</t>
   </si>
   <si>
     <t xml:space="preserve">3.1084315776825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97598433494568</t>
+    <t xml:space="preserve">2.9759840965271</t>
   </si>
   <si>
     <t xml:space="preserve">2.92856431007385</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">3.18037867546082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15585112571716</t>
+    <t xml:space="preserve">3.15585088729858</t>
   </si>
   <si>
     <t xml:space="preserve">3.18855452537537</t>
@@ -449,16 +449,16 @@
     <t xml:space="preserve">3.02503871917725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11660766601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23760914802551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28012299537659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32263731956482</t>
+    <t xml:space="preserve">3.11660742759705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23760867118835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28012323379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32263708114624</t>
   </si>
   <si>
     <t xml:space="preserve">3.43546271324158</t>
@@ -476,70 +476,70 @@
     <t xml:space="preserve">3.44854426383972</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67910099029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64639854431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71834468841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69545269012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74450707435608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8524272441864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80827879905701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82299494743347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80337285995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74287223815918</t>
+    <t xml:space="preserve">3.67910075187683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64639806747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71834516525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69545245170593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74450731277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85242700576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80827808380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82299470901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80337309837341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74287271499634</t>
   </si>
   <si>
     <t xml:space="preserve">3.62350606918335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56627559661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47470664978027</t>
+    <t xml:space="preserve">3.56627535820007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47470641136169</t>
   </si>
   <si>
     <t xml:space="preserve">3.51558566093445</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65947890281677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60551953315735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54501843452454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64803314208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64476275444031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38804364204407</t>
+    <t xml:space="preserve">3.65947937965393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60551929473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54501819610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64803266525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64476299285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38804340362549</t>
   </si>
   <si>
     <t xml:space="preserve">3.4828827381134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45344924926758</t>
+    <t xml:space="preserve">3.45344948768616</t>
   </si>
   <si>
     <t xml:space="preserve">3.4338276386261</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">3.50740933418274</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56464052200317</t>
+    <t xml:space="preserve">3.56464076042175</t>
   </si>
   <si>
     <t xml:space="preserve">3.55482935905457</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">3.56300497055054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4845175743103</t>
+    <t xml:space="preserve">3.48451781272888</t>
   </si>
   <si>
     <t xml:space="preserve">3.54338335990906</t>
@@ -566,148 +566,148 @@
     <t xml:space="preserve">3.62514114379883</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59080290794373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64149236679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68891191482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66111493110657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68727731704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53684258460999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63004589080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63822245597839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43873286247253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.417475938797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41911172866821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33571791648865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37169194221497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27521753311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22125720977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20981121063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1771080493927</t>
+    <t xml:space="preserve">3.59080266952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64149284362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68891215324402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66111469268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68727707862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53684282302856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63004612922668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63822221755981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43873262405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41747617721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41911149024963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33571815490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37169170379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27521729469299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22125768661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2098114490509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17710828781128</t>
   </si>
   <si>
     <t xml:space="preserve">3.21308183670044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14767551422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11333680152893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00541734695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0168628692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95309162139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9187536239624</t>
+    <t xml:space="preserve">3.14767527580261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11333727836609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00541687011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01686310768127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9530918598175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91875338554382</t>
   </si>
   <si>
     <t xml:space="preserve">2.96453809738159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96780800819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95636200904846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04793047904968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17220306396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18691945075989</t>
+    <t xml:space="preserve">2.96780824661255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95636224746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04793071746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17220258712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18691921234131</t>
   </si>
   <si>
     <t xml:space="preserve">3.3193666934967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2343385219574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45835494995117</t>
+    <t xml:space="preserve">3.23433876037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45835518836975</t>
   </si>
   <si>
     <t xml:space="preserve">3.48778748512268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45181441307068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49923419952393</t>
+    <t xml:space="preserve">3.4518141746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49923396110535</t>
   </si>
   <si>
     <t xml:space="preserve">3.57281589508057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45017910003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61369442939758</t>
+    <t xml:space="preserve">3.45017886161804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61369466781616</t>
   </si>
   <si>
     <t xml:space="preserve">3.67746591567993</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58916735649109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70362877845764</t>
+    <t xml:space="preserve">3.58916711807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70362901687622</t>
   </si>
   <si>
     <t xml:space="preserve">3.4861524105072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33244824409485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28666377067566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22943329811096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27031207084656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24741983413696</t>
+    <t xml:space="preserve">3.33244800567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28666353225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22943353652954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27031230926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24741959571838</t>
   </si>
   <si>
     <t xml:space="preserve">3.23106813430786</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">3.26213622093201</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27685236930847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23597359657288</t>
+    <t xml:space="preserve">3.27685260772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23597383499146</t>
   </si>
   <si>
     <t xml:space="preserve">4.0012264251709</t>
@@ -737,16 +737,16 @@
     <t xml:space="preserve">4.16964817047119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17782354354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06336259841919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95707821846008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19417524337769</t>
+    <t xml:space="preserve">4.17782402038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06336307525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9570779800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19417572021484</t>
   </si>
   <si>
     <t xml:space="preserve">4.28410863876343</t>
@@ -761,13 +761,13 @@
     <t xml:space="preserve">4.43944835662842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41083335876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41492176055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37404251098633</t>
+    <t xml:space="preserve">4.41083383560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41492128372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37404203414917</t>
   </si>
   <si>
     <t xml:space="preserve">4.26775693893433</t>
@@ -776,10 +776,10 @@
     <t xml:space="preserve">4.39039421081543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3617787361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37813091278076</t>
+    <t xml:space="preserve">4.36177825927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3781304359436</t>
   </si>
   <si>
     <t xml:space="preserve">4.38630628585815</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">4.56208515167236</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42718458175659</t>
+    <t xml:space="preserve">4.42718505859375</t>
   </si>
   <si>
     <t xml:space="preserve">4.32907581329346</t>
@@ -803,28 +803,28 @@
     <t xml:space="preserve">4.30046033859253</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34951448440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24323034286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24731779098511</t>
+    <t xml:space="preserve">4.34951400756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24322986602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24731826782227</t>
   </si>
   <si>
     <t xml:space="preserve">4.21052694320679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14512014389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10424089431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22279024124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40674495697021</t>
+    <t xml:space="preserve">4.14512062072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10424184799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2227897644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40674543380737</t>
   </si>
   <si>
     <t xml:space="preserve">4.36586666107178</t>
@@ -833,13 +833,13 @@
     <t xml:space="preserve">4.27593326568604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3045482635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28002071380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44762372970581</t>
+    <t xml:space="preserve">4.30454778671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28002119064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44762420654297</t>
   </si>
   <si>
     <t xml:space="preserve">4.52938222885132</t>
@@ -851,16 +851,16 @@
     <t xml:space="preserve">4.52120685577393</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68063354492188</t>
+    <t xml:space="preserve">4.68063449859619</t>
   </si>
   <si>
     <t xml:space="preserve">4.66019439697266</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71333742141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73377656936646</t>
+    <t xml:space="preserve">4.71333694458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7337760925293</t>
   </si>
   <si>
     <t xml:space="preserve">4.81962251663208</t>
@@ -869,46 +869,46 @@
     <t xml:space="preserve">4.81144666671753</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65201854705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34133911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33725118637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25958156585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40383386611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44966459274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41633415222168</t>
+    <t xml:space="preserve">4.65201902389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34133958816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33725166320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25958108901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40383434295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44966411590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41633367538452</t>
   </si>
   <si>
     <t xml:space="preserve">4.37467002868652</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36633682250977</t>
+    <t xml:space="preserve">4.36633729934692</t>
   </si>
   <si>
     <t xml:space="preserve">4.30384206771851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27467775344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25801229476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31634044647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26634454727173</t>
+    <t xml:space="preserve">4.27467823028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25801277160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31634092330933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26634359359741</t>
   </si>
   <si>
     <t xml:space="preserve">4.20801591873169</t>
@@ -917,40 +917,40 @@
     <t xml:space="preserve">4.33300638198853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37050342559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3455057144165</t>
+    <t xml:space="preserve">4.37050294876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34550619125366</t>
   </si>
   <si>
     <t xml:space="preserve">4.39133548736572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29967594146729</t>
+    <t xml:space="preserve">4.29967546463013</t>
   </si>
   <si>
     <t xml:space="preserve">4.42883253097534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39966726303101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39550161361694</t>
+    <t xml:space="preserve">4.39966821670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39550113677979</t>
   </si>
   <si>
     <t xml:space="preserve">4.38300275802612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46633005142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48299503326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56632232666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40800094604492</t>
+    <t xml:space="preserve">4.46632957458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48299551010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.566321849823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40800142288208</t>
   </si>
   <si>
     <t xml:space="preserve">4.34967136383057</t>
@@ -965,34 +965,34 @@
     <t xml:space="preserve">4.85380029678345</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9996223449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05795192718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10794878005981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24960517883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28710079193115</t>
+    <t xml:space="preserve">4.99962282180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05795240402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10794830322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24960470199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28710031509399</t>
   </si>
   <si>
     <t xml:space="preserve">5.25376987457275</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41625881195068</t>
+    <t xml:space="preserve">5.41625785827637</t>
   </si>
   <si>
     <t xml:space="preserve">5.30376672744751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29960012435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34542989730835</t>
+    <t xml:space="preserve">5.29960060119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34543037414551</t>
   </si>
   <si>
     <t xml:space="preserve">5.30793285369873</t>
@@ -1001,10 +1001,10 @@
     <t xml:space="preserve">5.22877216339111</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29126787185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29543399810791</t>
+    <t xml:space="preserve">5.29126739501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29543352127075</t>
   </si>
   <si>
     <t xml:space="preserve">5.16211080551147</t>
@@ -1013,37 +1013,37 @@
     <t xml:space="preserve">5.0162878036499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05378580093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12461376190186</t>
+    <t xml:space="preserve">5.05378532409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1246132850647</t>
   </si>
   <si>
     <t xml:space="preserve">5.20377397537231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07461786270142</t>
+    <t xml:space="preserve">5.07461738586426</t>
   </si>
   <si>
     <t xml:space="preserve">5.03295373916626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95795917510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9912896156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96212577819824</t>
+    <t xml:space="preserve">4.95795965194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99129009246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96212530136108</t>
   </si>
   <si>
     <t xml:space="preserve">4.90796279907227</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94129419326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89129829406738</t>
+    <t xml:space="preserve">4.94129371643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89129781723022</t>
   </si>
   <si>
     <t xml:space="preserve">4.90379667282104</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">5.02462148666382</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0496187210083</t>
+    <t xml:space="preserve">5.04961824417114</t>
   </si>
   <si>
     <t xml:space="preserve">5.11628103256226</t>
@@ -1073,37 +1073,37 @@
     <t xml:space="preserve">5.23293876647949</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17877674102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13294553756714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33293199539185</t>
+    <t xml:space="preserve">5.17877626419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1329460144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33293151855469</t>
   </si>
   <si>
     <t xml:space="preserve">5.26626968383789</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22460603713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58291149139404</t>
+    <t xml:space="preserve">5.22460699081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5829119682312</t>
   </si>
   <si>
     <t xml:space="preserve">5.68707132339478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00371360778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80789566040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07454204559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01621246337891</t>
+    <t xml:space="preserve">6.00371313095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80789518356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07454252243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01621294021606</t>
   </si>
   <si>
     <t xml:space="preserve">6.1662015914917</t>
@@ -1115,10 +1115,10 @@
     <t xml:space="preserve">5.94121837615967</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96621608734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03287887573242</t>
+    <t xml:space="preserve">5.96621656417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03287839889526</t>
   </si>
   <si>
     <t xml:space="preserve">5.99538135528564</t>
@@ -1130,19 +1130,19 @@
     <t xml:space="preserve">5.91622018814087</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86205768585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92871999740601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89955568313599</t>
+    <t xml:space="preserve">5.86205720901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92871952056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89955520629883</t>
   </si>
   <si>
     <t xml:space="preserve">5.90372180938721</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87455701828003</t>
+    <t xml:space="preserve">5.87455749511719</t>
   </si>
   <si>
     <t xml:space="preserve">5.84539222717285</t>
@@ -1151,34 +1151,34 @@
     <t xml:space="preserve">6.00788021087646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98288202285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03704452514648</t>
+    <t xml:space="preserve">5.98288249969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03704404830933</t>
   </si>
   <si>
     <t xml:space="preserve">6.09120750427246</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02871179580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99954700469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0495433807373</t>
+    <t xml:space="preserve">6.02871227264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99954748153687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04954385757446</t>
   </si>
   <si>
     <t xml:space="preserve">6.07870817184448</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29119300842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1745343208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19953203201294</t>
+    <t xml:space="preserve">6.29119253158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17453384399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1995325088501</t>
   </si>
   <si>
     <t xml:space="preserve">6.08287477493286</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">6.24536228179932</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21203136444092</t>
+    <t xml:space="preserve">6.21203184127808</t>
   </si>
   <si>
     <t xml:space="preserve">6.02454471588135</t>
@@ -1196,28 +1196,28 @@
     <t xml:space="preserve">6.0995397567749</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18286657333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2078652381897</t>
+    <t xml:space="preserve">6.1828670501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20786476135254</t>
   </si>
   <si>
     <t xml:space="preserve">6.22036409378052</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14536952972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95788383483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94538497924805</t>
+    <t xml:space="preserve">6.14537000656128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95788431167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94538545608521</t>
   </si>
   <si>
     <t xml:space="preserve">6.012047290802</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02037954330444</t>
+    <t xml:space="preserve">6.02037906646729</t>
   </si>
   <si>
     <t xml:space="preserve">6.11620569229126</t>
@@ -1226,28 +1226,28 @@
     <t xml:space="preserve">6.06204319000244</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04121112823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1495361328125</t>
+    <t xml:space="preserve">6.04121160507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14953660964966</t>
   </si>
   <si>
     <t xml:space="preserve">6.09537410736084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35785341262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2245306968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28285980224609</t>
+    <t xml:space="preserve">6.35785293579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22453117370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28285932540894</t>
   </si>
   <si>
     <t xml:space="preserve">6.58283710479736</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6161675453186</t>
+    <t xml:space="preserve">6.61616706848145</t>
   </si>
   <si>
     <t xml:space="preserve">6.57450342178345</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">6.50784206390381</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49951076507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65783023834229</t>
+    <t xml:space="preserve">6.49951028823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6578311920166</t>
   </si>
   <si>
     <t xml:space="preserve">6.7411584854126</t>
@@ -1268,7 +1268,7 @@
     <t xml:space="preserve">6.5911693572998</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62449932098389</t>
+    <t xml:space="preserve">6.62449979782104</t>
   </si>
   <si>
     <t xml:space="preserve">6.63283348083496</t>
@@ -1277,13 +1277,13 @@
     <t xml:space="preserve">6.70782709121704</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52450799942017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51617527008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6661639213562</t>
+    <t xml:space="preserve">6.52450752258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51617574691772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66616439819336</t>
   </si>
   <si>
     <t xml:space="preserve">6.54950618743896</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">6.44951343536377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29952478408813</t>
+    <t xml:space="preserve">6.29952430725098</t>
   </si>
   <si>
     <t xml:space="preserve">6.2328634262085</t>
@@ -1307,58 +1307,58 @@
     <t xml:space="preserve">6.53284072875977</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26619386672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36618661880493</t>
+    <t xml:space="preserve">6.26619338989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36618709564209</t>
   </si>
   <si>
     <t xml:space="preserve">6.33285570144653</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14120292663574</t>
+    <t xml:space="preserve">6.1412034034729</t>
   </si>
   <si>
     <t xml:space="preserve">6.1578688621521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06620931625366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94955158233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13287019729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05787563323975</t>
+    <t xml:space="preserve">6.0662088394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94955062866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1328706741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0578761100769</t>
   </si>
   <si>
     <t xml:space="preserve">5.88288927078247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84955883026123</t>
+    <t xml:space="preserve">5.84955930709839</t>
   </si>
   <si>
     <t xml:space="preserve">5.81622838973999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72456884384155</t>
+    <t xml:space="preserve">5.72456836700439</t>
   </si>
   <si>
     <t xml:space="preserve">5.75789880752563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76623249053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68290519714355</t>
+    <t xml:space="preserve">5.76623153686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6829047203064</t>
   </si>
   <si>
     <t xml:space="preserve">5.82456016540527</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86622476577759</t>
+    <t xml:space="preserve">5.86622428894043</t>
   </si>
   <si>
     <t xml:space="preserve">5.77456474304199</t>
@@ -1367,10 +1367,10 @@
     <t xml:space="preserve">5.78289747238159</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79122972488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63290882110596</t>
+    <t xml:space="preserve">5.79122924804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63290929794312</t>
   </si>
   <si>
     <t xml:space="preserve">5.64982414245605</t>
@@ -1388,46 +1388,46 @@
     <t xml:space="preserve">5.48066759109497</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45529460906982</t>
+    <t xml:space="preserve">5.45529413223267</t>
   </si>
   <si>
     <t xml:space="preserve">5.54833078384399</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53987312316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74285984039307</t>
+    <t xml:space="preserve">5.53987216949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74286031723022</t>
   </si>
   <si>
     <t xml:space="preserve">5.58216190338135</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6582818031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70902824401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77669191360474</t>
+    <t xml:space="preserve">5.65828227996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70902872085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77669143676758</t>
   </si>
   <si>
     <t xml:space="preserve">5.91201639175415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9035587310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89510107040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75131797790527</t>
+    <t xml:space="preserve">5.90355920791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89510059356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75131845474243</t>
   </si>
   <si>
     <t xml:space="preserve">5.78514909744263</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71748685836792</t>
+    <t xml:space="preserve">5.71748733520508</t>
   </si>
   <si>
     <t xml:space="preserve">5.81052303314209</t>
@@ -1436,28 +1436,28 @@
     <t xml:space="preserve">5.56524610519409</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50604152679443</t>
+    <t xml:space="preserve">5.50604104995728</t>
   </si>
   <si>
     <t xml:space="preserve">5.69211339950562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72594499588013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73440217971802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60753536224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51449918746948</t>
+    <t xml:space="preserve">5.72594451904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73440265655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60753583908081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51449871063232</t>
   </si>
   <si>
     <t xml:space="preserve">5.67519807815552</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01350975036621</t>
+    <t xml:space="preserve">6.01351070404053</t>
   </si>
   <si>
     <t xml:space="preserve">5.99659490585327</t>
@@ -1469,37 +1469,37 @@
     <t xml:space="preserve">5.75977563858032</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80206489562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79360675811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88664293289185</t>
+    <t xml:space="preserve">5.80206441879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79360771179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.886643409729</t>
   </si>
   <si>
     <t xml:space="preserve">5.87818479537964</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92893171310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85281229019165</t>
+    <t xml:space="preserve">5.92893218994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85281181335449</t>
   </si>
   <si>
     <t xml:space="preserve">5.76823377609253</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82743787765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83589601516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42992115020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38763189315796</t>
+    <t xml:space="preserve">5.82743883132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83589649200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42992067337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3876314163208</t>
   </si>
   <si>
     <t xml:space="preserve">5.33688497543335</t>
@@ -1508,49 +1508,49 @@
     <t xml:space="preserve">5.26076412200928</t>
   </si>
   <si>
-    <t xml:space="preserve">5.303053855896</t>
+    <t xml:space="preserve">5.30305433273315</t>
   </si>
   <si>
     <t xml:space="preserve">5.43837881088257</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46375274658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44683647155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35380077362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3707160949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22693300247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14235544204712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11698198318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2438497543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13389730453491</t>
+    <t xml:space="preserve">5.46375179290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44683694839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35380029678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37071561813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22693347930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14235496520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11698246002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24384927749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13389778137207</t>
   </si>
   <si>
     <t xml:space="preserve">5.26922225952148</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25230693817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21001672744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23539113998413</t>
+    <t xml:space="preserve">5.25230646133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21001720428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23539066314697</t>
   </si>
   <si>
     <t xml:space="preserve">5.28613805770874</t>
@@ -1562,13 +1562,13 @@
     <t xml:space="preserve">5.29459571838379</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48912477493286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32842826843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16772890090942</t>
+    <t xml:space="preserve">5.48912525177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32842779159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16772842407227</t>
   </si>
   <si>
     <t xml:space="preserve">5.09160757064819</t>
@@ -1580,31 +1580,31 @@
     <t xml:space="preserve">5.10852384567261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91399335861206</t>
+    <t xml:space="preserve">4.91399383544922</t>
   </si>
   <si>
     <t xml:space="preserve">4.60105419158936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49956035614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56722354888916</t>
+    <t xml:space="preserve">4.49955987930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.567223072052</t>
   </si>
   <si>
     <t xml:space="preserve">4.38115072250366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5418496131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5249342918396</t>
+    <t xml:space="preserve">4.54185009002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52493381500244</t>
   </si>
   <si>
     <t xml:space="preserve">4.61797046661377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46572875976562</t>
+    <t xml:space="preserve">4.46572923660278</t>
   </si>
   <si>
     <t xml:space="preserve">4.27119922637939</t>
@@ -1616,13 +1616,13 @@
     <t xml:space="preserve">4.22045183181763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09358549118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20353651046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15701913833618</t>
+    <t xml:space="preserve">4.09358596801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20353698730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15701866149902</t>
   </si>
   <si>
     <t xml:space="preserve">4.39806699752808</t>
@@ -1631,10 +1631,10 @@
     <t xml:space="preserve">4.53339195251465</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59259653091431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60951232910156</t>
+    <t xml:space="preserve">4.59259605407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6095118522644</t>
   </si>
   <si>
     <t xml:space="preserve">4.63488578796387</t>
@@ -1649,16 +1649,16 @@
     <t xml:space="preserve">4.42344045639038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43189764022827</t>
+    <t xml:space="preserve">4.43189811706543</t>
   </si>
   <si>
     <t xml:space="preserve">4.2965726852417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33886241912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19507884979248</t>
+    <t xml:space="preserve">4.33886289596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19507932662964</t>
   </si>
   <si>
     <t xml:space="preserve">4.04706716537476</t>
@@ -1679,19 +1679,19 @@
     <t xml:space="preserve">4.21622371673584</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16124773025513</t>
+    <t xml:space="preserve">4.16124725341797</t>
   </si>
   <si>
     <t xml:space="preserve">4.10204267501831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03860902786255</t>
+    <t xml:space="preserve">4.03860950469971</t>
   </si>
   <si>
     <t xml:space="preserve">4.30503034591675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2542839050293</t>
+    <t xml:space="preserve">4.25428342819214</t>
   </si>
   <si>
     <t xml:space="preserve">4.14010286331177</t>
@@ -1706,28 +1706,28 @@
     <t xml:space="preserve">4.08935594558716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0343804359436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94557285308838</t>
+    <t xml:space="preserve">4.03438091278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94557309150696</t>
   </si>
   <si>
     <t xml:space="preserve">4.35577774047852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31348896026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4826455116272</t>
+    <t xml:space="preserve">4.31348848342896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48264503479004</t>
   </si>
   <si>
     <t xml:space="preserve">4.65180158615112</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7955846786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7871265411377</t>
+    <t xml:space="preserve">4.79558420181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78712606430054</t>
   </si>
   <si>
     <t xml:space="preserve">4.82095766067505</t>
@@ -1748,67 +1748,67 @@
     <t xml:space="preserve">5.00703001022339</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0154881477356</t>
+    <t xml:space="preserve">5.01548767089844</t>
   </si>
   <si>
     <t xml:space="preserve">5.03240346908569</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05777740478516</t>
+    <t xml:space="preserve">5.05777645111084</t>
   </si>
   <si>
     <t xml:space="preserve">4.99011421203613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97319889068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20156002044678</t>
+    <t xml:space="preserve">4.97319841384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20155954360962</t>
   </si>
   <si>
     <t xml:space="preserve">5.12543869018555</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15927028656006</t>
+    <t xml:space="preserve">5.1592698097229</t>
   </si>
   <si>
     <t xml:space="preserve">5.21847581863403</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3453426361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27768087387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40454769134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39608955383301</t>
+    <t xml:space="preserve">5.34534311294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27767992019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4045467376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39609003067017</t>
   </si>
   <si>
     <t xml:space="preserve">5.47220993041992</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49758434295654</t>
+    <t xml:space="preserve">5.49758338928223</t>
   </si>
   <si>
     <t xml:space="preserve">5.42146301269531</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41300630569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98165655136108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11462497711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13193368911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01942920684814</t>
+    <t xml:space="preserve">5.41300582885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98165607452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11462545394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13193321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0194296836853</t>
   </si>
   <si>
     <t xml:space="preserve">5.0107741355896</t>
@@ -1838,7 +1838,7 @@
     <t xml:space="preserve">5.26174592971802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23578357696533</t>
+    <t xml:space="preserve">5.23578405380249</t>
   </si>
   <si>
     <t xml:space="preserve">5.25309228897095</t>
@@ -1850,19 +1850,19 @@
     <t xml:space="preserve">5.46079254150391</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54733371734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42617607116699</t>
+    <t xml:space="preserve">5.54733419418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42617559432983</t>
   </si>
   <si>
     <t xml:space="preserve">5.330979347229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40886688232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57329750061035</t>
+    <t xml:space="preserve">5.40886735916138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57329702377319</t>
   </si>
   <si>
     <t xml:space="preserve">5.52137184143066</t>
@@ -1874,34 +1874,34 @@
     <t xml:space="preserve">5.64253044128418</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7636890411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74638080596924</t>
+    <t xml:space="preserve">5.76368856430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74638032913208</t>
   </si>
   <si>
     <t xml:space="preserve">5.72907209396362</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65118455886841</t>
+    <t xml:space="preserve">5.65118503570557</t>
   </si>
   <si>
     <t xml:space="preserve">5.7031102180481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66849279403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59925889968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49540948867798</t>
+    <t xml:space="preserve">5.66849327087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59925937652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49540901184082</t>
   </si>
   <si>
     <t xml:space="preserve">5.45213890075684</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56464290618896</t>
+    <t xml:space="preserve">5.56464242935181</t>
   </si>
   <si>
     <t xml:space="preserve">5.73772668838501</t>
@@ -1913,31 +1913,31 @@
     <t xml:space="preserve">5.2444372177124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1838583946228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28770875930786</t>
+    <t xml:space="preserve">5.18385791778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28770923614502</t>
   </si>
   <si>
     <t xml:space="preserve">5.19251251220703</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12327861785889</t>
+    <t xml:space="preserve">5.1232795715332</t>
   </si>
   <si>
     <t xml:space="preserve">5.2704005241394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0800085067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14924144744873</t>
+    <t xml:space="preserve">5.08000802993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14924192428589</t>
   </si>
   <si>
     <t xml:space="preserve">5.16655015945435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15789604187012</t>
+    <t xml:space="preserve">5.1578950881958</t>
   </si>
   <si>
     <t xml:space="preserve">5.29636240005493</t>
@@ -1949,13 +1949,13 @@
     <t xml:space="preserve">5.44348382949829</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48675537109375</t>
+    <t xml:space="preserve">5.48675584793091</t>
   </si>
   <si>
     <t xml:space="preserve">5.40021324157715</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36559677124023</t>
+    <t xml:space="preserve">5.36559629440308</t>
   </si>
   <si>
     <t xml:space="preserve">5.32232570648193</t>
@@ -1964,13 +1964,13 @@
     <t xml:space="preserve">5.38290500640869</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02808284759521</t>
+    <t xml:space="preserve">5.02808237075806</t>
   </si>
   <si>
     <t xml:space="preserve">5.04539203643799</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16222286224365</t>
+    <t xml:space="preserve">5.16222333908081</t>
   </si>
   <si>
     <t xml:space="preserve">5.03933334350586</t>
@@ -1979,22 +1979,22 @@
     <t xml:space="preserve">5.10597085952759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15270376205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20895576477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27905511856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3456916809082</t>
+    <t xml:space="preserve">5.15270328521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20895528793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27905464172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34569215774536</t>
   </si>
   <si>
     <t xml:space="preserve">5.32665252685547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27991914749146</t>
+    <t xml:space="preserve">5.27991962432861</t>
   </si>
   <si>
     <t xml:space="preserve">5.30588245391846</t>
@@ -2003,7 +2003,7 @@
     <t xml:space="preserve">5.26780414581299</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34742212295532</t>
+    <t xml:space="preserve">5.34742259979248</t>
   </si>
   <si>
     <t xml:space="preserve">5.21934080123901</t>
@@ -2012,7 +2012,7 @@
     <t xml:space="preserve">5.34309577941895</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48502397537231</t>
+    <t xml:space="preserve">5.48502445220947</t>
   </si>
   <si>
     <t xml:space="preserve">5.43915700912476</t>
@@ -2021,16 +2021,16 @@
     <t xml:space="preserve">5.31799840927124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51791048049927</t>
+    <t xml:space="preserve">5.51791000366211</t>
   </si>
   <si>
     <t xml:space="preserve">5.61656761169434</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51617956161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46252250671387</t>
+    <t xml:space="preserve">5.51617908477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46252298355103</t>
   </si>
   <si>
     <t xml:space="preserve">5.42271375656128</t>
@@ -2039,10 +2039,10 @@
     <t xml:space="preserve">5.46771574020386</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44434881210327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46944713592529</t>
+    <t xml:space="preserve">5.44434976577759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46944665908813</t>
   </si>
   <si>
     <t xml:space="preserve">5.78099727630615</t>
@@ -2057,7 +2057,7 @@
     <t xml:space="preserve">6.04927682876587</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94456195831299</t>
+    <t xml:space="preserve">5.94456100463867</t>
   </si>
   <si>
     <t xml:space="preserve">5.76974725723267</t>
@@ -2072,7 +2072,7 @@
     <t xml:space="preserve">5.74118804931641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73945760726929</t>
+    <t xml:space="preserve">5.73945713043213</t>
   </si>
   <si>
     <t xml:space="preserve">5.81042242050171</t>
@@ -2084,13 +2084,13 @@
     <t xml:space="preserve">5.93331098556519</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94110012054443</t>
+    <t xml:space="preserve">5.94109964370728</t>
   </si>
   <si>
     <t xml:space="preserve">5.91081047058105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92638826370239</t>
+    <t xml:space="preserve">5.92638874053955</t>
   </si>
   <si>
     <t xml:space="preserve">5.85369253158569</t>
@@ -2099,25 +2099,25 @@
     <t xml:space="preserve">5.85628938674927</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68060922622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73253345489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81907558441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90648365020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70570611953735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57502794265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75590038299561</t>
+    <t xml:space="preserve">5.68060874938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73253393173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81907606124878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90648317337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70570659637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57502746582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75590085983276</t>
   </si>
   <si>
     <t xml:space="preserve">5.81561374664307</t>
@@ -2132,7 +2132,7 @@
     <t xml:space="preserve">5.72041845321655</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69791793823242</t>
+    <t xml:space="preserve">5.69791698455811</t>
   </si>
   <si>
     <t xml:space="preserve">5.69272518157959</t>
@@ -2141,22 +2141,22 @@
     <t xml:space="preserve">5.62868404388428</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75936222076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65810775756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57243156433105</t>
+    <t xml:space="preserve">5.75936269760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65810823440552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5724310874939</t>
   </si>
   <si>
     <t xml:space="preserve">5.62522220611572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67282056808472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58195114135742</t>
+    <t xml:space="preserve">5.6728196144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58195066452026</t>
   </si>
   <si>
     <t xml:space="preserve">5.58454751968384</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">5.64512634277344</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72561073303223</t>
+    <t xml:space="preserve">5.72561025619507</t>
   </si>
   <si>
     <t xml:space="preserve">5.61483716964722</t>
@@ -2174,25 +2174,25 @@
     <t xml:space="preserve">5.60704851150513</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65291547775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65551137924194</t>
+    <t xml:space="preserve">5.65291595458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6555118560791</t>
   </si>
   <si>
     <t xml:space="preserve">5.75503540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84071159362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00600624084473</t>
+    <t xml:space="preserve">5.84071111679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00600671768188</t>
   </si>
   <si>
     <t xml:space="preserve">5.92811870574951</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87619352340698</t>
+    <t xml:space="preserve">5.87619400024414</t>
   </si>
   <si>
     <t xml:space="preserve">5.71436023712158</t>
@@ -2210,52 +2210,52 @@
     <t xml:space="preserve">5.040198802948</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15443468093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18039655685425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79615116119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24358081817627</t>
+    <t xml:space="preserve">5.15443420410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18039703369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79615068435669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24358177185059</t>
   </si>
   <si>
     <t xml:space="preserve">4.30113124847412</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30718994140625</t>
+    <t xml:space="preserve">4.30718946456909</t>
   </si>
   <si>
     <t xml:space="preserve">3.94501137733459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11073875427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98092675209045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77452373504639</t>
+    <t xml:space="preserve">4.11073923110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9809262752533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77452397346497</t>
   </si>
   <si>
     <t xml:space="preserve">3.89438486099243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17564582824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82385301589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97486877441406</t>
+    <t xml:space="preserve">4.17564535140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82385277748108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97486853599548</t>
   </si>
   <si>
     <t xml:space="preserve">4.07006454467773</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27386999130249</t>
+    <t xml:space="preserve">4.27387046813965</t>
   </si>
   <si>
     <t xml:space="preserve">4.11766195297241</t>
@@ -2264,16 +2264,16 @@
     <t xml:space="preserve">4.05665016174316</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25699520111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30978536605835</t>
+    <t xml:space="preserve">4.256995677948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30978584289551</t>
   </si>
   <si>
     <t xml:space="preserve">4.37036466598511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17131900787354</t>
+    <t xml:space="preserve">4.17131853103638</t>
   </si>
   <si>
     <t xml:space="preserve">4.32709407806396</t>
@@ -2282,40 +2282,40 @@
     <t xml:space="preserve">4.45690679550171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6126823425293</t>
+    <t xml:space="preserve">4.61268186569214</t>
   </si>
   <si>
     <t xml:space="preserve">4.48286914825439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6299901008606</t>
+    <t xml:space="preserve">4.62999057769775</t>
   </si>
   <si>
     <t xml:space="preserve">4.569411277771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57806491851807</t>
+    <t xml:space="preserve">4.57806539535522</t>
   </si>
   <si>
     <t xml:space="preserve">4.52614068984985</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50017786026001</t>
+    <t xml:space="preserve">4.50017738342285</t>
   </si>
   <si>
     <t xml:space="preserve">4.74249505996704</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76845741271973</t>
+    <t xml:space="preserve">4.76845788955688</t>
   </si>
   <si>
     <t xml:space="preserve">4.79442024230957</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94154119491577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91557836532593</t>
+    <t xml:space="preserve">4.94154167175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91557931900024</t>
   </si>
   <si>
     <t xml:space="preserve">4.83769083023071</t>
@@ -2339,10 +2339,10 @@
     <t xml:space="preserve">4.90961265563965</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73204898834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8829779624939</t>
+    <t xml:space="preserve">4.73204946517944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88297748565674</t>
   </si>
   <si>
     <t xml:space="preserve">4.91849040985107</t>
@@ -2351,10 +2351,10 @@
     <t xml:space="preserve">5.10493087768555</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22034692764282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19371271133423</t>
+    <t xml:space="preserve">5.22034740447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19371223449707</t>
   </si>
   <si>
     <t xml:space="preserve">5.39790916442871</t>
@@ -2372,7 +2372,7 @@
     <t xml:space="preserve">5.49556922912598</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60210657119751</t>
+    <t xml:space="preserve">5.60210704803467</t>
   </si>
   <si>
     <t xml:space="preserve">5.72640037536621</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">5.55771636962891</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73527908325195</t>
+    <t xml:space="preserve">5.73527860641479</t>
   </si>
   <si>
     <t xml:space="preserve">5.61098527908325</t>
@@ -2414,10 +2414,10 @@
     <t xml:space="preserve">5.64649772644043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71752262115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5843505859375</t>
+    <t xml:space="preserve">5.71752309799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58435010910034</t>
   </si>
   <si>
     <t xml:space="preserve">5.56659460067749</t>
@@ -2432,10 +2432,10 @@
     <t xml:space="preserve">5.35351943969727</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42454385757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41566610336304</t>
+    <t xml:space="preserve">5.42454433441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41566562652588</t>
   </si>
   <si>
     <t xml:space="preserve">5.31800603866577</t>
@@ -2447,10 +2447,10 @@
     <t xml:space="preserve">5.29137182235718</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2114691734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36239719390869</t>
+    <t xml:space="preserve">5.21146869659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36239671707153</t>
   </si>
   <si>
     <t xml:space="preserve">5.255859375</t>
@@ -2459,16 +2459,16 @@
     <t xml:space="preserve">5.26473760604858</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37127590179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48669147491455</t>
+    <t xml:space="preserve">5.37127542495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48669099807739</t>
   </si>
   <si>
     <t xml:space="preserve">5.59322881698608</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5399603843689</t>
+    <t xml:space="preserve">5.53995990753174</t>
   </si>
   <si>
     <t xml:space="preserve">5.50444746017456</t>
@@ -2483,16 +2483,16 @@
     <t xml:space="preserve">5.28249359130859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20259094238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32688426971436</t>
+    <t xml:space="preserve">5.2025899887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32688522338867</t>
   </si>
   <si>
     <t xml:space="preserve">5.33576345443726</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24698162078857</t>
+    <t xml:space="preserve">5.24698114395142</t>
   </si>
   <si>
     <t xml:space="preserve">5.15819931030273</t>
@@ -2507,7 +2507,7 @@
     <t xml:space="preserve">5.18483448028564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02502727508545</t>
+    <t xml:space="preserve">5.02502775192261</t>
   </si>
   <si>
     <t xml:space="preserve">4.90073394775391</t>
@@ -2552,13 +2552,13 @@
     <t xml:space="preserve">6.10816097259521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35674905776978</t>
+    <t xml:space="preserve">6.35674810409546</t>
   </si>
   <si>
     <t xml:space="preserve">6.18806409835815</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2413330078125</t>
+    <t xml:space="preserve">6.24133253097534</t>
   </si>
   <si>
     <t xml:space="preserve">6.28572368621826</t>
@@ -2585,34 +2585,34 @@
     <t xml:space="preserve">6.06377077102661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05489158630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98386669158936</t>
+    <t xml:space="preserve">6.05489206314087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98386716842651</t>
   </si>
   <si>
     <t xml:space="preserve">5.96611022949219</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93947649002075</t>
+    <t xml:space="preserve">5.93947601318359</t>
   </si>
   <si>
     <t xml:space="preserve">5.94835472106934</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92172050476074</t>
+    <t xml:space="preserve">5.92172002792358</t>
   </si>
   <si>
     <t xml:space="preserve">5.91284132003784</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23245525360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46328687667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33011388778687</t>
+    <t xml:space="preserve">6.23245477676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46328639984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33011436462402</t>
   </si>
   <si>
     <t xml:space="preserve">6.27684593200684</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">6.04601383209229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37450504302979</t>
+    <t xml:space="preserve">6.37450551986694</t>
   </si>
   <si>
     <t xml:space="preserve">6.12591695785522</t>
@@ -2633,7 +2633,7 @@
     <t xml:space="preserve">6.21469926834106</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17918586730957</t>
+    <t xml:space="preserve">6.17918634414673</t>
   </si>
   <si>
     <t xml:space="preserve">6.26796770095825</t>
@@ -2642,19 +2642,19 @@
     <t xml:space="preserve">6.48104333877563</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66748428344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01373195648193</t>
+    <t xml:space="preserve">6.66748380661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01373147964478</t>
   </si>
   <si>
     <t xml:space="preserve">7.43988132476807</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54641962051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59968852996826</t>
+    <t xml:space="preserve">7.54641914367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59968900680542</t>
   </si>
   <si>
     <t xml:space="preserve">7.63520193099976</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">7.30670881271362</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18241596221924</t>
+    <t xml:space="preserve">7.1824164390564</t>
   </si>
   <si>
     <t xml:space="preserve">7.29783201217651</t>
@@ -2687,25 +2687,25 @@
     <t xml:space="preserve">7.19129467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21792840957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3511004447937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4842734336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59081029891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58193254470825</t>
+    <t xml:space="preserve">7.21792888641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35110092163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48427391052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59081077575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58193206787109</t>
   </si>
   <si>
     <t xml:space="preserve">7.65295648574829</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51090669631958</t>
+    <t xml:space="preserve">7.51090717315674</t>
   </si>
   <si>
     <t xml:space="preserve">7.45763874053955</t>
@@ -2717,22 +2717,22 @@
     <t xml:space="preserve">7.61744403839111</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67959117889404</t>
+    <t xml:space="preserve">7.6795916557312</t>
   </si>
   <si>
     <t xml:space="preserve">7.76837253570557</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93705749511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19452476501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09686470031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99920463562012</t>
+    <t xml:space="preserve">7.93705797195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19452381134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09686374664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99920511245728</t>
   </si>
   <si>
     <t xml:space="preserve">8.17676734924316</t>
@@ -2741,13 +2741,13 @@
     <t xml:space="preserve">8.20340156555176</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99032640457153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08798599243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05247402191162</t>
+    <t xml:space="preserve">7.99032688140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08798694610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0524730682373</t>
   </si>
   <si>
     <t xml:space="preserve">8.04359722137451</t>
@@ -2765,7 +2765,7 @@
     <t xml:space="preserve">8.07022953033447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15013313293457</t>
+    <t xml:space="preserve">8.15013408660889</t>
   </si>
   <si>
     <t xml:space="preserve">8.38984298706055</t>
@@ -2774,46 +2774,46 @@
     <t xml:space="preserve">8.23891353607178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44311141967773</t>
+    <t xml:space="preserve">8.44311237335205</t>
   </si>
   <si>
     <t xml:space="preserve">8.3809642791748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51413726806641</t>
+    <t xml:space="preserve">8.51413631439209</t>
   </si>
   <si>
     <t xml:space="preserve">8.43423366546631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64730930328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42535591125488</t>
+    <t xml:space="preserve">8.64730834960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4253568649292</t>
   </si>
   <si>
     <t xml:space="preserve">8.47014331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60530567169189</t>
+    <t xml:space="preserve">8.60530662536621</t>
   </si>
   <si>
     <t xml:space="preserve">8.43410015106201</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41608047485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37102603912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56025218963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31696128845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42509078979492</t>
+    <t xml:space="preserve">8.4160795211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37102508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56025314331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31695938110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42508983612061</t>
   </si>
   <si>
     <t xml:space="preserve">8.62332725524902</t>
@@ -2822,13 +2822,13 @@
     <t xml:space="preserve">8.75848960876465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65937042236328</t>
+    <t xml:space="preserve">8.6593713760376</t>
   </si>
   <si>
     <t xml:space="preserve">8.70442485809326</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74046802520752</t>
+    <t xml:space="preserve">8.7404670715332</t>
   </si>
   <si>
     <t xml:space="preserve">8.68640327453613</t>
@@ -2837,13 +2837,13 @@
     <t xml:space="preserve">8.47915554046631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50618648529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51519870758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53321933746338</t>
+    <t xml:space="preserve">8.50618743896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51519775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5332202911377</t>
   </si>
   <si>
     <t xml:space="preserve">8.46113395690918</t>
@@ -2858,7 +2858,7 @@
     <t xml:space="preserve">8.15476608276367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08267974853516</t>
+    <t xml:space="preserve">8.08268070220947</t>
   </si>
   <si>
     <t xml:space="preserve">8.0466365814209</t>
@@ -2870,13 +2870,13 @@
     <t xml:space="preserve">7.95652914047241</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00158405303955</t>
+    <t xml:space="preserve">8.00158309936523</t>
   </si>
   <si>
     <t xml:space="preserve">7.74928140640259</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85741090774536</t>
+    <t xml:space="preserve">7.8574104309082</t>
   </si>
   <si>
     <t xml:space="preserve">7.78532457351685</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">7.74027013778687</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99257183074951</t>
+    <t xml:space="preserve">7.99257278442383</t>
   </si>
   <si>
     <t xml:space="preserve">7.92048597335815</t>
@@ -2906,46 +2906,46 @@
     <t xml:space="preserve">8.21784114837646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96554040908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60510778427124</t>
+    <t xml:space="preserve">7.96553993225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6051082611084</t>
   </si>
   <si>
     <t xml:space="preserve">8.07366943359375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.244873046875</t>
+    <t xml:space="preserve">8.24487400054932</t>
   </si>
   <si>
     <t xml:space="preserve">8.12773513793945</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48816585540771</t>
+    <t xml:space="preserve">8.4881649017334</t>
   </si>
   <si>
     <t xml:space="preserve">8.38904762268066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35300540924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33498287200928</t>
+    <t xml:space="preserve">8.35300445556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33498382568359</t>
   </si>
   <si>
     <t xml:space="preserve">8.71343517303467</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63233757019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23586368560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30795001983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64134979248047</t>
+    <t xml:space="preserve">8.63233852386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23586463928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30795097351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64134883880615</t>
   </si>
   <si>
     <t xml:space="preserve">8.77651119232178</t>
@@ -2966,16 +2966,16 @@
     <t xml:space="preserve">8.03762626647949</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92949628829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98356151580811</t>
+    <t xml:space="preserve">7.92949724197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98356199264526</t>
   </si>
   <si>
     <t xml:space="preserve">8.01960468292236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8844428062439</t>
+    <t xml:space="preserve">7.88444328308105</t>
   </si>
   <si>
     <t xml:space="preserve">7.56906509399414</t>
@@ -2993,19 +2993,19 @@
     <t xml:space="preserve">7.65917301177979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67719507217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72224807739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76730251312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71323823928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93850755691528</t>
+    <t xml:space="preserve">7.67719554901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72224855422974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7673020362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71323871612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93850803375244</t>
   </si>
   <si>
     <t xml:space="preserve">8.2268533706665</t>
@@ -3020,16 +3020,16 @@
     <t xml:space="preserve">8.38003635406494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18179798126221</t>
+    <t xml:space="preserve">8.18179893493652</t>
   </si>
   <si>
     <t xml:space="preserve">8.02861595153809</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80334520339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69521522521973</t>
+    <t xml:space="preserve">7.8033447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69521570205688</t>
   </si>
   <si>
     <t xml:space="preserve">7.61411905288696</t>
@@ -3038,7 +3038,7 @@
     <t xml:space="preserve">7.37983798980713</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33478498458862</t>
+    <t xml:space="preserve">7.33478450775146</t>
   </si>
   <si>
     <t xml:space="preserve">7.37082767486572</t>
@@ -3050,55 +3050,55 @@
     <t xml:space="preserve">7.36181735992432</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35280656814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44291400909424</t>
+    <t xml:space="preserve">7.35280609130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4429144859314</t>
   </si>
   <si>
     <t xml:space="preserve">7.65016174316406</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46994590759277</t>
+    <t xml:space="preserve">7.46994638442993</t>
   </si>
   <si>
     <t xml:space="preserve">7.39786005020142</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32577419281006</t>
+    <t xml:space="preserve">7.3257737159729</t>
   </si>
   <si>
     <t xml:space="preserve">7.27170848846436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30775213241577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29874181747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26269817352295</t>
+    <t xml:space="preserve">7.30775165557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29874134063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26269865036011</t>
   </si>
   <si>
     <t xml:space="preserve">7.54203271865845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6411509513855</t>
+    <t xml:space="preserve">7.64115047454834</t>
   </si>
   <si>
     <t xml:space="preserve">7.62312984466553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53302192687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52401161193848</t>
+    <t xml:space="preserve">7.53302145004272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52401113510132</t>
   </si>
   <si>
     <t xml:space="preserve">7.31676292419434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38884925842285</t>
+    <t xml:space="preserve">7.38884973526001</t>
   </si>
   <si>
     <t xml:space="preserve">7.4519248008728</t>
@@ -3110,7 +3110,7 @@
     <t xml:space="preserve">6.92929887771606</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02841758728027</t>
+    <t xml:space="preserve">7.02841806411743</t>
   </si>
   <si>
     <t xml:space="preserve">6.89325571060181</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">7.0103964805603</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12753629684448</t>
+    <t xml:space="preserve">7.12753582000732</t>
   </si>
   <si>
     <t xml:space="preserve">7.11852550506592</t>
@@ -3143,28 +3143,28 @@
     <t xml:space="preserve">7.03742790222168</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14555740356445</t>
+    <t xml:space="preserve">7.14555788040161</t>
   </si>
   <si>
     <t xml:space="preserve">7.19962215423584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00138473510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0734715461731</t>
+    <t xml:space="preserve">7.00138521194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07347106933594</t>
   </si>
   <si>
     <t xml:space="preserve">6.80314779281616</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74007225036621</t>
+    <t xml:space="preserve">6.74007177352905</t>
   </si>
   <si>
     <t xml:space="preserve">6.6679859161377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36161851882935</t>
+    <t xml:space="preserve">6.36161947250366</t>
   </si>
   <si>
     <t xml:space="preserve">6.59589958190918</t>
@@ -3176,7 +3176,7 @@
     <t xml:space="preserve">6.32557582855225</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13634872436523</t>
+    <t xml:space="preserve">6.13634920120239</t>
   </si>
   <si>
     <t xml:space="preserve">5.85701465606689</t>
@@ -3185,7 +3185,7 @@
     <t xml:space="preserve">5.83899307250977</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01019859313965</t>
+    <t xml:space="preserve">6.01019811630249</t>
   </si>
   <si>
     <t xml:space="preserve">6.28052139282227</t>
@@ -3206,13 +3206,13 @@
     <t xml:space="preserve">6.46974849700928</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38865089416504</t>
+    <t xml:space="preserve">6.38865184783936</t>
   </si>
   <si>
     <t xml:space="preserve">6.37062978744507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28953266143799</t>
+    <t xml:space="preserve">6.28953313827515</t>
   </si>
   <si>
     <t xml:space="preserve">6.31656551361084</t>
@@ -3227,19 +3227,19 @@
     <t xml:space="preserve">6.12733840942383</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27151155471802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26249980926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18140316009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29854345321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17239236831665</t>
+    <t xml:space="preserve">6.27151107788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26250028610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18140363693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29854297637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17239189147949</t>
   </si>
   <si>
     <t xml:space="preserve">5.84800386428833</t>
@@ -3248,10 +3248,10 @@
     <t xml:space="preserve">5.86602544784546</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92009019851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89305734634399</t>
+    <t xml:space="preserve">5.920090675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89305782318115</t>
   </si>
   <si>
     <t xml:space="preserve">5.93811178207397</t>
@@ -3275,13 +3275,13 @@
     <t xml:space="preserve">5.94712257385254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01920890808105</t>
+    <t xml:space="preserve">6.0192084312439</t>
   </si>
   <si>
     <t xml:space="preserve">5.99217653274536</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96514415740967</t>
+    <t xml:space="preserve">5.96514368057251</t>
   </si>
   <si>
     <t xml:space="preserve">5.97415542602539</t>
@@ -3290,10 +3290,10 @@
     <t xml:space="preserve">5.95613384246826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08228445053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07327365875244</t>
+    <t xml:space="preserve">6.08228492736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07327318191528</t>
   </si>
   <si>
     <t xml:space="preserve">6.03723001480103</t>
@@ -70498,7 +70498,7 @@
     </row>
     <row r="2510">
       <c r="A2510" s="1" t="n">
-        <v>45973.6911226852</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B2510" t="n">
         <v>87590</v>
@@ -70519,6 +70519,32 @@
         <v>1637</v>
       </c>
       <c r="H2510" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" s="1" t="n">
+        <v>45974.6911111111</v>
+      </c>
+      <c r="B2511" t="n">
+        <v>193186</v>
+      </c>
+      <c r="C2511" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="D2511" t="n">
+        <v>15.6800003051758</v>
+      </c>
+      <c r="E2511" t="n">
+        <v>15.8000001907349</v>
+      </c>
+      <c r="F2511" t="n">
+        <v>15.9799995422363</v>
+      </c>
+      <c r="G2511" t="s">
+        <v>1630</v>
+      </c>
+      <c r="H2511" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CEM.MI.xlsx
+++ b/data/CEM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="1645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1646" uniqueCount="1646">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,154 +38,154 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70432138442993</t>
+    <t xml:space="preserve">4.70432043075562</t>
   </si>
   <si>
     <t xml:space="preserve">CEM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68036031723022</t>
+    <t xml:space="preserve">4.68036079406738</t>
   </si>
   <si>
     <t xml:space="preserve">4.5565619468689</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48867321014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32893419265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22110939025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3249397277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2889986038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29299211502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06137132644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93597459793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97431302070618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67560029029846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83534026145935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94875383377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88006615638733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91680598258972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87846875190735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74588561058044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93437767028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87367653846741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73789834976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57815957069397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59892511367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6196916103363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35132932662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15005850791931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25069332122803</t>
+    <t xml:space="preserve">4.48867273330688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32893323898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22110986709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32494020462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28899812698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29299259185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06136989593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93597483634949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97431206703186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67560076713562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83533954620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94875478744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88006711006165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91680645942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87846970558167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7458860874176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93437814712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87367701530457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73789882659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57815933227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59892559051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61969184875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35132956504822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15005826950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25069379806519</t>
   </si>
   <si>
     <t xml:space="preserve">3.13088965415955</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20916199684143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44238090515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36251163482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47592663764954</t>
+    <t xml:space="preserve">3.20916175842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44238066673279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3625111579895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47592616081238</t>
   </si>
   <si>
     <t xml:space="preserve">3.55419850349426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34653759002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39126420021057</t>
+    <t xml:space="preserve">3.34653735160828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39126443862915</t>
   </si>
   <si>
     <t xml:space="preserve">3.3673038482666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2395122051239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29222631454468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40244603157043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58614635467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63406777381897</t>
+    <t xml:space="preserve">3.23951268196106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2922260761261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40244626998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58614587783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63406825065613</t>
   </si>
   <si>
     <t xml:space="preserve">3.55579590797424</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64365243911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56058835983276</t>
+    <t xml:space="preserve">3.64365267753601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56058812141418</t>
   </si>
   <si>
     <t xml:space="preserve">3.52065324783325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49828934669495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52544546127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54940605163574</t>
+    <t xml:space="preserve">3.49828958511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52544569969177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54940581321716</t>
   </si>
   <si>
     <t xml:space="preserve">3.75227522850037</t>
@@ -194,37 +194,37 @@
     <t xml:space="preserve">3.61330199241638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75387287139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83214449882507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67080807685852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70754790306091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65802907943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51745820045471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57017207145691</t>
+    <t xml:space="preserve">3.75387215614319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83214473724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6708083152771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70754861831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6580286026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51745843887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57017254829407</t>
   </si>
   <si>
     <t xml:space="preserve">3.50947165489197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5430166721344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57975673675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45196580886841</t>
+    <t xml:space="preserve">3.54301691055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57975649833679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45196557044983</t>
   </si>
   <si>
     <t xml:space="preserve">3.41043305397034</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">3.37529039382935</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60052227973938</t>
+    <t xml:space="preserve">3.60052275657654</t>
   </si>
   <si>
     <t xml:space="preserve">3.48551034927368</t>
@@ -242,103 +242,103 @@
     <t xml:space="preserve">3.54461407661438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59573030471802</t>
+    <t xml:space="preserve">3.5957305431366</t>
   </si>
   <si>
     <t xml:space="preserve">3.77943086624146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74428796768188</t>
+    <t xml:space="preserve">3.7442889213562</t>
   </si>
   <si>
     <t xml:space="preserve">3.85770320892334</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73949599266052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74907970428467</t>
+    <t xml:space="preserve">3.73949575424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74908041954041</t>
   </si>
   <si>
     <t xml:space="preserve">3.70595073699951</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69317150115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67719841003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79700207710266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66601610183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70115852355957</t>
+    <t xml:space="preserve">3.69317221641541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67719769477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79700255393982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66601634025574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70115876197815</t>
   </si>
   <si>
     <t xml:space="preserve">3.62608098983765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67400217056274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64205479621887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53023719787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45835494995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47432899475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53193712234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62187027931213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75758838653564</t>
+    <t xml:space="preserve">3.67400288581848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64205527305603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53023767471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45835447311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4743287563324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53193736076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62187051773071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75758862495422</t>
   </si>
   <si>
     <t xml:space="preserve">3.76085877418518</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87531924247742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88349580764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77721047401428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75431799888611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70526361465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6692898273468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59734344482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58426189422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55646443367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38640856742859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31119132041931</t>
+    <t xml:space="preserve">3.87531971931458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88349533081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77720999717712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75431871414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70526385307312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66929006576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5973436832428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58426141738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55646419525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38640832901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31119108200073</t>
   </si>
   <si>
     <t xml:space="preserve">3.29810953140259</t>
@@ -347,58 +347,58 @@
     <t xml:space="preserve">3.19673013687134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15912127494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00705170631409</t>
+    <t xml:space="preserve">3.1591215133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00705218315125</t>
   </si>
   <si>
     <t xml:space="preserve">3.15421605110168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03484916687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22289252281189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35207009315491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10679650306702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82881999015808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82064390182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84026622772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93510508537292</t>
+    <t xml:space="preserve">3.0348494052887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22289228439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35206985473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10679626464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8288197517395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82064437866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84026598930359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93510484695435</t>
   </si>
   <si>
     <t xml:space="preserve">3.04302525520325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9579975605011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79611706733704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76341390609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76831889152527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84844160079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87787437438965</t>
+    <t xml:space="preserve">2.95799732208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79611682891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76341366767883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76831912994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84844207763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87787485122681</t>
   </si>
   <si>
     <t xml:space="preserve">3.04139041900635</t>
@@ -407,34 +407,34 @@
     <t xml:space="preserve">3.00051140785217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2114462852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13295888900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07572865486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97434902191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10843205451965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97598385810852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92856454849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1754732131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18037843704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15585064888</t>
+    <t xml:space="preserve">3.21144676208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13295912742615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07572841644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97434878349304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10843133926392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97598433494568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92856478691101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17547297477722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18037891387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15585088729858</t>
   </si>
   <si>
     <t xml:space="preserve">3.18855428695679</t>
@@ -446,70 +446,70 @@
     <t xml:space="preserve">3.12151288986206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02503871917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11660742759705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23760890960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28012299537659</t>
+    <t xml:space="preserve">3.02503848075867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11660766601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23760914802551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28012323379517</t>
   </si>
   <si>
     <t xml:space="preserve">3.32263708114624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43546295166016</t>
+    <t xml:space="preserve">3.43546342849731</t>
   </si>
   <si>
     <t xml:space="preserve">3.40602970123291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46653008460999</t>
+    <t xml:space="preserve">3.46653079986572</t>
   </si>
   <si>
     <t xml:space="preserve">3.43709802627563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44854402542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67910146713257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64639759063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71834444999695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69545292854309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74450755119324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8524272441864</t>
+    <t xml:space="preserve">3.44854426383972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67910075187683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64639854431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71834468841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69545269012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7445068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85242748260498</t>
   </si>
   <si>
     <t xml:space="preserve">3.80827808380127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82299423217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80337333679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74287223815918</t>
+    <t xml:space="preserve">3.82299518585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80337262153625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74287176132202</t>
   </si>
   <si>
     <t xml:space="preserve">3.62350630760193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56627535820007</t>
+    <t xml:space="preserve">3.56627488136292</t>
   </si>
   <si>
     <t xml:space="preserve">3.47470664978027</t>
@@ -518,16 +518,16 @@
     <t xml:space="preserve">3.51558542251587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65947914123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60551881790161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54501867294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64803266525269</t>
+    <t xml:space="preserve">3.65947890281677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60551905632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54501843452454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64803314208984</t>
   </si>
   <si>
     <t xml:space="preserve">3.64476299285889</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">3.48288249969482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45344972610474</t>
+    <t xml:space="preserve">3.45344948768616</t>
   </si>
   <si>
     <t xml:space="preserve">3.43382740020752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50740957260132</t>
+    <t xml:space="preserve">3.5074098110199</t>
   </si>
   <si>
     <t xml:space="preserve">3.56464028358459</t>
@@ -554,37 +554,37 @@
     <t xml:space="preserve">3.55482912063599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56300449371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4845175743103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5433828830719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62514114379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59080266952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64149284362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68891167640686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66111421585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68727684020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53684258460999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63004660606384</t>
+    <t xml:space="preserve">3.56300520896912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48451733589172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54338359832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62514090538025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59080290794373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64149212837219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68891215324402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66111493110657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68727707862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53684306144714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63004589080811</t>
   </si>
   <si>
     <t xml:space="preserve">3.63822221755981</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">3.43873286247253</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41747617721558</t>
+    <t xml:space="preserve">3.417475938797</t>
   </si>
   <si>
     <t xml:space="preserve">3.41911149024963</t>
@@ -602,19 +602,19 @@
     <t xml:space="preserve">3.33571815490723</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37169170379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27521753311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22125744819641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20981121063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17710781097412</t>
+    <t xml:space="preserve">3.37169218063354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27521800994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22125720977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2098114490509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1771080493927</t>
   </si>
   <si>
     <t xml:space="preserve">3.21308159828186</t>
@@ -623,13 +623,13 @@
     <t xml:space="preserve">3.14767551422119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11333727836609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00541710853577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01686334609985</t>
+    <t xml:space="preserve">3.11333680152893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00541687011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01686310768127</t>
   </si>
   <si>
     <t xml:space="preserve">2.9530918598175</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">2.9187536239624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96453809738159</t>
+    <t xml:space="preserve">2.96453785896301</t>
   </si>
   <si>
     <t xml:space="preserve">2.96780824661255</t>
@@ -650,31 +650,31 @@
     <t xml:space="preserve">3.04793071746826</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17220282554626</t>
+    <t xml:space="preserve">3.17220258712769</t>
   </si>
   <si>
     <t xml:space="preserve">3.18691921234131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31936645507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2343385219574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45835542678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48778748512268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45181465148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49923419952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57281565666199</t>
+    <t xml:space="preserve">3.3193666934967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23433876037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45835471153259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48778772354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45181441307068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4992344379425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57281541824341</t>
   </si>
   <si>
     <t xml:space="preserve">3.45017886161804</t>
@@ -686,25 +686,25 @@
     <t xml:space="preserve">3.67746615409851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58916711807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70362854003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48615264892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33244824409485</t>
+    <t xml:space="preserve">3.58916807174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7036292552948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48615288734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33244848251343</t>
   </si>
   <si>
     <t xml:space="preserve">3.28666353225708</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22943353652954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27031207084656</t>
+    <t xml:space="preserve">3.22943329811096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27031183242798</t>
   </si>
   <si>
     <t xml:space="preserve">3.24741959571838</t>
@@ -716,109 +716,109 @@
     <t xml:space="preserve">3.23270344734192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26213598251343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27685284614563</t>
+    <t xml:space="preserve">3.26213669776917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27685236930847</t>
   </si>
   <si>
     <t xml:space="preserve">3.23597359657288</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00122690200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04701089859009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1287693977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16964817047119</t>
+    <t xml:space="preserve">4.00122737884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04701137542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12876892089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16964721679688</t>
   </si>
   <si>
     <t xml:space="preserve">4.17782354354858</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06336307525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95707821846008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19417524337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28410863876343</t>
+    <t xml:space="preserve">4.06336259841919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95707750320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19417476654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28410816192627</t>
   </si>
   <si>
     <t xml:space="preserve">4.34542751312256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47215175628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43944787979126</t>
+    <t xml:space="preserve">4.47215127944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43944835662842</t>
   </si>
   <si>
     <t xml:space="preserve">4.41083335876465</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41492176055908</t>
+    <t xml:space="preserve">4.41492080688477</t>
   </si>
   <si>
     <t xml:space="preserve">4.37404203414917</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26775741577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39039373397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3617787361145</t>
+    <t xml:space="preserve">4.26775789260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39039421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36177921295166</t>
   </si>
   <si>
     <t xml:space="preserve">4.3781304359436</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38630628585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56208515167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42718458175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32907485961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25549364089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25140523910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30046033859253</t>
+    <t xml:space="preserve">4.386305809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56208562850952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42718505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3290753364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2554931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25140476226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30046081542969</t>
   </si>
   <si>
     <t xml:space="preserve">4.34951543807983</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24323034286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24731779098511</t>
+    <t xml:space="preserve">4.24322986602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24731826782227</t>
   </si>
   <si>
     <t xml:space="preserve">4.21052646636963</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14512062072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1042423248291</t>
+    <t xml:space="preserve">4.14512157440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10424184799194</t>
   </si>
   <si>
     <t xml:space="preserve">4.2227897644043</t>
@@ -830,25 +830,25 @@
     <t xml:space="preserve">4.36586666107178</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27593278884888</t>
+    <t xml:space="preserve">4.27593326568604</t>
   </si>
   <si>
     <t xml:space="preserve">4.30454874038696</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28002119064331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44762468338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52938222885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51711797714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52120685577393</t>
+    <t xml:space="preserve">4.28002071380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44762420654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.529381275177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51711893081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52120637893677</t>
   </si>
   <si>
     <t xml:space="preserve">4.68063402175903</t>
@@ -857,28 +857,28 @@
     <t xml:space="preserve">4.66019439697266</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71333694458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73377704620361</t>
+    <t xml:space="preserve">4.71333742141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73377656936646</t>
   </si>
   <si>
     <t xml:space="preserve">4.81962203979492</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81144666671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65201902389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34133863449097</t>
+    <t xml:space="preserve">4.81144714355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65201950073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34133958816528</t>
   </si>
   <si>
     <t xml:space="preserve">4.33725118637085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25958108901978</t>
+    <t xml:space="preserve">4.25958156585693</t>
   </si>
   <si>
     <t xml:space="preserve">4.40383434295654</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">4.44966459274292</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41633367538452</t>
+    <t xml:space="preserve">4.41633415222168</t>
   </si>
   <si>
     <t xml:space="preserve">4.37467002868652</t>
@@ -896,16 +896,16 @@
     <t xml:space="preserve">4.36633682250977</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30384206771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27467775344849</t>
+    <t xml:space="preserve">4.30384159088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27467727661133</t>
   </si>
   <si>
     <t xml:space="preserve">4.25801181793213</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31634044647217</t>
+    <t xml:space="preserve">4.31634140014648</t>
   </si>
   <si>
     <t xml:space="preserve">4.26634454727173</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">4.33300638198853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3705039024353</t>
+    <t xml:space="preserve">4.37050437927246</t>
   </si>
   <si>
     <t xml:space="preserve">4.34550523757935</t>
@@ -926,28 +926,28 @@
     <t xml:space="preserve">4.39133548736572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29967546463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42883253097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39966821670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39550161361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38300275802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46632957458496</t>
+    <t xml:space="preserve">4.29967594146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42883348464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39966869354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3955020904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38300228118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46633005142212</t>
   </si>
   <si>
     <t xml:space="preserve">4.48299551010132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56632280349731</t>
+    <t xml:space="preserve">4.566321849823</t>
   </si>
   <si>
     <t xml:space="preserve">4.40800142288208</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">4.34967184066772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69131326675415</t>
+    <t xml:space="preserve">4.69131278991699</t>
   </si>
   <si>
     <t xml:space="preserve">4.58298778533936</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">4.85380029678345</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99962282180786</t>
+    <t xml:space="preserve">4.99962329864502</t>
   </si>
   <si>
     <t xml:space="preserve">5.05795192718506</t>
@@ -974,49 +974,49 @@
     <t xml:space="preserve">5.10794830322266</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24960470199585</t>
+    <t xml:space="preserve">5.24960422515869</t>
   </si>
   <si>
     <t xml:space="preserve">5.28710126876831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25377035140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41625785827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30376625061035</t>
+    <t xml:space="preserve">5.25377082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41625881195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30376672744751</t>
   </si>
   <si>
     <t xml:space="preserve">5.29960012435913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34542942047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30793237686157</t>
+    <t xml:space="preserve">5.34543037414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30793285369873</t>
   </si>
   <si>
     <t xml:space="preserve">5.22877216339111</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29126691818237</t>
+    <t xml:space="preserve">5.29126739501953</t>
   </si>
   <si>
     <t xml:space="preserve">5.29543399810791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16211080551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01628875732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05378580093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12461423873901</t>
+    <t xml:space="preserve">5.16211128234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01628828048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05378532409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1246132850647</t>
   </si>
   <si>
     <t xml:space="preserve">5.20377445220947</t>
@@ -1031,10 +1031,10 @@
     <t xml:space="preserve">4.95795917510986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9912896156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96212577819824</t>
+    <t xml:space="preserve">4.99129056930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96212530136108</t>
   </si>
   <si>
     <t xml:space="preserve">4.90796279907227</t>
@@ -1046,61 +1046,61 @@
     <t xml:space="preserve">4.89129734039307</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90379762649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9537935256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94545936584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91629552841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02462148666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04961919784546</t>
+    <t xml:space="preserve">4.9037971496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95379304885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94546031951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91629600524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02462100982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0496187210083</t>
   </si>
   <si>
     <t xml:space="preserve">5.1162805557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17460966110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23293828964233</t>
+    <t xml:space="preserve">5.17461013793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23293924331665</t>
   </si>
   <si>
     <t xml:space="preserve">5.17877626419067</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13294649124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33293151855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26626968383789</t>
+    <t xml:space="preserve">5.1329460144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33293104171753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26627016067505</t>
   </si>
   <si>
     <t xml:space="preserve">5.22460603713989</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58291292190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68707036972046</t>
+    <t xml:space="preserve">5.58291149139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68707084655762</t>
   </si>
   <si>
     <t xml:space="preserve">6.00371408462524</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80789518356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07454204559326</t>
+    <t xml:space="preserve">5.80789470672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07454252243042</t>
   </si>
   <si>
     <t xml:space="preserve">6.01621294021606</t>
@@ -1109,31 +1109,31 @@
     <t xml:space="preserve">6.1662015914917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89122295379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94121885299683</t>
+    <t xml:space="preserve">5.89122247695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94121837615967</t>
   </si>
   <si>
     <t xml:space="preserve">5.96621704101562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03287744522095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99538087844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.970383644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91621971130371</t>
+    <t xml:space="preserve">6.03287792205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9953818321228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97038269042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91622066497803</t>
   </si>
   <si>
     <t xml:space="preserve">5.86205768585205</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92871952056885</t>
+    <t xml:space="preserve">5.92871904373169</t>
   </si>
   <si>
     <t xml:space="preserve">5.89955472946167</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">5.90372133255005</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87455749511719</t>
+    <t xml:space="preserve">5.87455701828003</t>
   </si>
   <si>
     <t xml:space="preserve">5.84539270401001</t>
@@ -1151,40 +1151,40 @@
     <t xml:space="preserve">6.00788021087646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98288202285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03704500198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0912070274353</t>
+    <t xml:space="preserve">5.98288154602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03704452514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09120750427246</t>
   </si>
   <si>
     <t xml:space="preserve">6.02871227264404</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99954748153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04954385757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07870817184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29119253158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1745343208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1995325088501</t>
+    <t xml:space="preserve">5.99954700469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04954433441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07870864868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29119205474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17453336715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19953298568726</t>
   </si>
   <si>
     <t xml:space="preserve">6.08287525177002</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24536275863647</t>
+    <t xml:space="preserve">6.24536228179932</t>
   </si>
   <si>
     <t xml:space="preserve">6.21203136444092</t>
@@ -1196,13 +1196,13 @@
     <t xml:space="preserve">6.09954023361206</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18286752700806</t>
+    <t xml:space="preserve">6.18286657333374</t>
   </si>
   <si>
     <t xml:space="preserve">6.20786476135254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22036409378052</t>
+    <t xml:space="preserve">6.22036504745483</t>
   </si>
   <si>
     <t xml:space="preserve">6.14536952972412</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">5.94538497924805</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01204681396484</t>
+    <t xml:space="preserve">6.01204633712769</t>
   </si>
   <si>
     <t xml:space="preserve">6.02037906646729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11620616912842</t>
+    <t xml:space="preserve">6.1162052154541</t>
   </si>
   <si>
     <t xml:space="preserve">6.06204271316528</t>
@@ -1229,19 +1229,19 @@
     <t xml:space="preserve">6.04121112823486</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1495361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09537363052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35785436630249</t>
+    <t xml:space="preserve">6.14953660964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09537410736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35785388946533</t>
   </si>
   <si>
     <t xml:space="preserve">6.22452974319458</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28285884857178</t>
+    <t xml:space="preserve">6.28285932540894</t>
   </si>
   <si>
     <t xml:space="preserve">6.58283662796021</t>
@@ -1250,13 +1250,13 @@
     <t xml:space="preserve">6.61616802215576</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57450437545776</t>
+    <t xml:space="preserve">6.57450389862061</t>
   </si>
   <si>
     <t xml:space="preserve">6.50784254074097</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49951076507568</t>
+    <t xml:space="preserve">6.49950981140137</t>
   </si>
   <si>
     <t xml:space="preserve">6.6578311920166</t>
@@ -1265,73 +1265,73 @@
     <t xml:space="preserve">6.7411584854126</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5911693572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6245002746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63283348083496</t>
+    <t xml:space="preserve">6.59116983413696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62450075149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6328330039978</t>
   </si>
   <si>
     <t xml:space="preserve">6.70782804489136</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52450704574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51617527008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66616344451904</t>
+    <t xml:space="preserve">6.52450799942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51617574691772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66616296768188</t>
   </si>
   <si>
     <t xml:space="preserve">6.54950618743896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44951343536377</t>
+    <t xml:space="preserve">6.44951295852661</t>
   </si>
   <si>
     <t xml:space="preserve">6.29952478408813</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2328634262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90788793563843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93288612365723</t>
+    <t xml:space="preserve">6.23286294937134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90788745880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93288564682007</t>
   </si>
   <si>
     <t xml:space="preserve">6.53284120559692</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26619434356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36618614196777</t>
+    <t xml:space="preserve">6.26619386672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36618661880493</t>
   </si>
   <si>
     <t xml:space="preserve">6.33285570144653</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14120292663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1578688621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0662088394165</t>
+    <t xml:space="preserve">6.1412034034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15786838531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06620931625366</t>
   </si>
   <si>
     <t xml:space="preserve">5.94955062866211</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1328706741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0578761100769</t>
+    <t xml:space="preserve">6.13287115097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05787658691406</t>
   </si>
   <si>
     <t xml:space="preserve">5.88288927078247</t>
@@ -1343,22 +1343,22 @@
     <t xml:space="preserve">5.81622838973999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72456836700439</t>
+    <t xml:space="preserve">5.72456884384155</t>
   </si>
   <si>
     <t xml:space="preserve">5.75789880752563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76623201370239</t>
+    <t xml:space="preserve">5.76623153686523</t>
   </si>
   <si>
     <t xml:space="preserve">5.6829047203064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82456016540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86622381210327</t>
+    <t xml:space="preserve">5.82456064224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86622428894043</t>
   </si>
   <si>
     <t xml:space="preserve">5.77456426620483</t>
@@ -1373,100 +1373,100 @@
     <t xml:space="preserve">5.6329083442688</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64982461929321</t>
+    <t xml:space="preserve">5.64982414245605</t>
   </si>
   <si>
     <t xml:space="preserve">5.68365526199341</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66673898696899</t>
+    <t xml:space="preserve">5.66673946380615</t>
   </si>
   <si>
     <t xml:space="preserve">5.70057106018066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48066806793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45529413223267</t>
+    <t xml:space="preserve">5.48066711425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45529460906982</t>
   </si>
   <si>
     <t xml:space="preserve">5.54833030700684</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53987216949463</t>
+    <t xml:space="preserve">5.53987264633179</t>
   </si>
   <si>
     <t xml:space="preserve">5.74286031723022</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58216142654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65828227996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70902919769287</t>
+    <t xml:space="preserve">5.58216190338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6582818031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70902872085571</t>
   </si>
   <si>
     <t xml:space="preserve">5.77669191360474</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91201639175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9035587310791</t>
+    <t xml:space="preserve">5.91201686859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90355920791626</t>
   </si>
   <si>
     <t xml:space="preserve">5.89510059356689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75131797790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78514909744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71748638153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81052207946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56524562835693</t>
+    <t xml:space="preserve">5.75131893157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78514957427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71748685836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81052350997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56524515151978</t>
   </si>
   <si>
     <t xml:space="preserve">5.50604152679443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69211292266846</t>
+    <t xml:space="preserve">5.69211339950562</t>
   </si>
   <si>
     <t xml:space="preserve">5.72594451904297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73440217971802</t>
+    <t xml:space="preserve">5.73440265655518</t>
   </si>
   <si>
     <t xml:space="preserve">5.60753488540649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51449871063232</t>
+    <t xml:space="preserve">5.51449918746948</t>
   </si>
   <si>
     <t xml:space="preserve">5.67519807815552</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01351022720337</t>
+    <t xml:space="preserve">6.01351070404053</t>
   </si>
   <si>
     <t xml:space="preserve">5.99659490585327</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81898069381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75977563858032</t>
+    <t xml:space="preserve">5.81898021697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75977611541748</t>
   </si>
   <si>
     <t xml:space="preserve">5.80206489562988</t>
@@ -1493,19 +1493,19 @@
     <t xml:space="preserve">5.82743835449219</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83589649200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42992115020752</t>
+    <t xml:space="preserve">5.83589696884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42992067337036</t>
   </si>
   <si>
     <t xml:space="preserve">5.3876314163208</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33688497543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26076412200928</t>
+    <t xml:space="preserve">5.33688545227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26076459884644</t>
   </si>
   <si>
     <t xml:space="preserve">5.303053855896</t>
@@ -1517,40 +1517,40 @@
     <t xml:space="preserve">5.46375226974487</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44683599472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35379981994629</t>
+    <t xml:space="preserve">5.44683694839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35380077362061</t>
   </si>
   <si>
     <t xml:space="preserve">5.3707160949707</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22693252563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14235496520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11698150634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24384880065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13389682769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26922225952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25230646133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21001720428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23539066314697</t>
+    <t xml:space="preserve">5.22693300247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1423544883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11698198318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24384832382202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13389730453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26922178268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25230693817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21001768112183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23539113998413</t>
   </si>
   <si>
     <t xml:space="preserve">5.28613805770874</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">5.31996870040894</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29459524154663</t>
+    <t xml:space="preserve">5.29459571838379</t>
   </si>
   <si>
     <t xml:space="preserve">5.48912525177002</t>
@@ -1568,52 +1568,52 @@
     <t xml:space="preserve">5.32842683792114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16772794723511</t>
+    <t xml:space="preserve">5.16772890090942</t>
   </si>
   <si>
     <t xml:space="preserve">5.09160757064819</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17618608474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10852336883545</t>
+    <t xml:space="preserve">5.17618656158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10852432250977</t>
   </si>
   <si>
     <t xml:space="preserve">4.91399335861206</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60105419158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49956130981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56722402572632</t>
+    <t xml:space="preserve">4.60105466842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49956035614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.567223072052</t>
   </si>
   <si>
     <t xml:space="preserve">4.38115119934082</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54185009002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52493476867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61797046661377</t>
+    <t xml:space="preserve">4.5418496131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52493381500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61796998977661</t>
   </si>
   <si>
     <t xml:space="preserve">4.46572971343994</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27120018005371</t>
+    <t xml:space="preserve">4.27119970321655</t>
   </si>
   <si>
     <t xml:space="preserve">4.14433240890503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22045278549194</t>
+    <t xml:space="preserve">4.22045183181763</t>
   </si>
   <si>
     <t xml:space="preserve">4.09358549118042</t>
@@ -1622,10 +1622,10 @@
     <t xml:space="preserve">4.20353698730469</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15701961517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39806747436523</t>
+    <t xml:space="preserve">4.15701913833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39806604385376</t>
   </si>
   <si>
     <t xml:space="preserve">4.53339195251465</t>
@@ -1634,40 +1634,40 @@
     <t xml:space="preserve">4.59259653091431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6095118522644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63488578796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41498184204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49110317230225</t>
+    <t xml:space="preserve">4.60951280593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63488531112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41498231887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49110269546509</t>
   </si>
   <si>
     <t xml:space="preserve">4.42344045639038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43189811706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2965726852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33886241912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19507884979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04706716537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08512735366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10627222061157</t>
+    <t xml:space="preserve">4.43189764022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29657316207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33886194229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19507932662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0470666885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08512687683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10627174377441</t>
   </si>
   <si>
     <t xml:space="preserve">4.15278959274292</t>
@@ -1676,25 +1676,25 @@
     <t xml:space="preserve">4.2373685836792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21622371673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16124820709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10204267501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03860998153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30503129959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25428438186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14010381698608</t>
+    <t xml:space="preserve">4.21622467041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16124773025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10204362869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03860950469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30503082275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2542839050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14010334014893</t>
   </si>
   <si>
     <t xml:space="preserve">4.05129623413086</t>
@@ -1706,13 +1706,13 @@
     <t xml:space="preserve">4.08935689926147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0343804359436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9455738067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35577774047852</t>
+    <t xml:space="preserve">4.03437995910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94557285308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35577821731567</t>
   </si>
   <si>
     <t xml:space="preserve">4.3134880065918</t>
@@ -1724,7 +1724,7 @@
     <t xml:space="preserve">4.65180110931396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79558420181274</t>
+    <t xml:space="preserve">4.7955846786499</t>
   </si>
   <si>
     <t xml:space="preserve">4.7871265411377</t>
@@ -1733,19 +1733,19 @@
     <t xml:space="preserve">4.82095718383789</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86324644088745</t>
+    <t xml:space="preserve">4.86324691772461</t>
   </si>
   <si>
     <t xml:space="preserve">4.90553617477417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88861989974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95628309249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00702953338623</t>
+    <t xml:space="preserve">4.88862085342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95628356933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00703048706055</t>
   </si>
   <si>
     <t xml:space="preserve">5.01548719406128</t>
@@ -1754,13 +1754,13 @@
     <t xml:space="preserve">5.03240299224854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05777645111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99011373519897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97319889068604</t>
+    <t xml:space="preserve">5.05777740478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99011421203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97319841384888</t>
   </si>
   <si>
     <t xml:space="preserve">5.20155954360962</t>
@@ -1775,37 +1775,37 @@
     <t xml:space="preserve">5.21847486495972</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34534215927124</t>
+    <t xml:space="preserve">5.34534311294556</t>
   </si>
   <si>
     <t xml:space="preserve">5.27767992019653</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4045467376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39608907699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47220993041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49758338928223</t>
+    <t xml:space="preserve">5.40454769134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39609003067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47220945358276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49758434295654</t>
   </si>
   <si>
     <t xml:space="preserve">5.42146301269531</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41300535202026</t>
+    <t xml:space="preserve">5.41300582885742</t>
   </si>
   <si>
     <t xml:space="preserve">4.98165607452393</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11462497711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13193273544312</t>
+    <t xml:space="preserve">5.11462450027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13193321228027</t>
   </si>
   <si>
     <t xml:space="preserve">5.01942920684814</t>
@@ -1817,7 +1817,7 @@
     <t xml:space="preserve">5.06269979476929</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08866262435913</t>
+    <t xml:space="preserve">5.08866310119629</t>
   </si>
   <si>
     <t xml:space="preserve">5.0973162651062</t>
@@ -1826,28 +1826,25 @@
     <t xml:space="preserve">5.14058780670166</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21847534179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20116710662842</t>
+    <t xml:space="preserve">5.20116758346558</t>
   </si>
   <si>
     <t xml:space="preserve">5.17520380020142</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22712898254395</t>
+    <t xml:space="preserve">5.2271294593811</t>
   </si>
   <si>
     <t xml:space="preserve">5.26174640655518</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23578357696533</t>
+    <t xml:space="preserve">5.23578405380249</t>
   </si>
   <si>
     <t xml:space="preserve">5.25309181213379</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33963346481323</t>
+    <t xml:space="preserve">5.33963394165039</t>
   </si>
   <si>
     <t xml:space="preserve">5.46079254150391</t>
@@ -1859,31 +1856,31 @@
     <t xml:space="preserve">5.42617607116699</t>
   </si>
   <si>
-    <t xml:space="preserve">5.330979347229</t>
+    <t xml:space="preserve">5.33097982406616</t>
   </si>
   <si>
     <t xml:space="preserve">5.40886735916138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57329654693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52137136459351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47810029983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64252996444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76368856430054</t>
+    <t xml:space="preserve">5.57329750061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52137184143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47810077667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64253091812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7636890411377</t>
   </si>
   <si>
     <t xml:space="preserve">5.74638032913208</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72907257080078</t>
+    <t xml:space="preserve">5.72907209396362</t>
   </si>
   <si>
     <t xml:space="preserve">5.65118455886841</t>
@@ -1892,7 +1889,7 @@
     <t xml:space="preserve">5.70310974121094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66849279403687</t>
+    <t xml:space="preserve">5.66849374771118</t>
   </si>
   <si>
     <t xml:space="preserve">5.59925937652588</t>
@@ -1904,10 +1901,10 @@
     <t xml:space="preserve">5.45213794708252</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56464242935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73772621154785</t>
+    <t xml:space="preserve">5.56464290618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73772668838501</t>
   </si>
   <si>
     <t xml:space="preserve">5.51271724700928</t>
@@ -1916,7 +1913,7 @@
     <t xml:space="preserve">5.24443769454956</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18385744094849</t>
+    <t xml:space="preserve">5.1838583946228</t>
   </si>
   <si>
     <t xml:space="preserve">5.2877082824707</t>
@@ -1925,7 +1922,7 @@
     <t xml:space="preserve">5.19251298904419</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12327861785889</t>
+    <t xml:space="preserve">5.1232795715332</t>
   </si>
   <si>
     <t xml:space="preserve">5.2704005241394</t>
@@ -1940,7 +1937,7 @@
     <t xml:space="preserve">5.16655015945435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1578950881958</t>
+    <t xml:space="preserve">5.15789604187012</t>
   </si>
   <si>
     <t xml:space="preserve">5.29636287689209</t>
@@ -1949,7 +1946,7 @@
     <t xml:space="preserve">5.53868007659912</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44348382949829</t>
+    <t xml:space="preserve">5.44348430633545</t>
   </si>
   <si>
     <t xml:space="preserve">5.48675537109375</t>
@@ -1961,10 +1958,10 @@
     <t xml:space="preserve">5.36559629440308</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32232522964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38290452957153</t>
+    <t xml:space="preserve">5.32232570648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38290500640869</t>
   </si>
   <si>
     <t xml:space="preserve">5.02808284759521</t>
@@ -1973,31 +1970,31 @@
     <t xml:space="preserve">5.04539155960083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16222381591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03933334350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10597038269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15270376205444</t>
+    <t xml:space="preserve">5.16222333908081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03933382034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10597085952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15270328521729</t>
   </si>
   <si>
     <t xml:space="preserve">5.20895528793335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27905416488647</t>
+    <t xml:space="preserve">5.27905464172363</t>
   </si>
   <si>
     <t xml:space="preserve">5.3456916809082</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32665252685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27991962432861</t>
+    <t xml:space="preserve">5.32665348052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27992010116577</t>
   </si>
   <si>
     <t xml:space="preserve">5.30588245391846</t>
@@ -2009,19 +2006,19 @@
     <t xml:space="preserve">5.34742259979248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21934127807617</t>
+    <t xml:space="preserve">5.21934032440186</t>
   </si>
   <si>
     <t xml:space="preserve">5.34309530258179</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48502445220947</t>
+    <t xml:space="preserve">5.48502397537231</t>
   </si>
   <si>
     <t xml:space="preserve">5.4391565322876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31799840927124</t>
+    <t xml:space="preserve">5.31799793243408</t>
   </si>
   <si>
     <t xml:space="preserve">5.51791048049927</t>
@@ -2033,7 +2030,7 @@
     <t xml:space="preserve">5.51617956161499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46252393722534</t>
+    <t xml:space="preserve">5.46252346038818</t>
   </si>
   <si>
     <t xml:space="preserve">5.42271423339844</t>
@@ -2042,13 +2039,13 @@
     <t xml:space="preserve">5.46771574020386</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44434976577759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46944618225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78099775314331</t>
+    <t xml:space="preserve">5.44434928894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46944665908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78099727630615</t>
   </si>
   <si>
     <t xml:space="preserve">6.02331447601318</t>
@@ -2057,7 +2054,7 @@
     <t xml:space="preserve">6.0406231880188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04927682876587</t>
+    <t xml:space="preserve">6.04927730560303</t>
   </si>
   <si>
     <t xml:space="preserve">5.94456195831299</t>
@@ -2066,16 +2063,16 @@
     <t xml:space="preserve">5.76974678039551</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78272867202759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75416946411133</t>
+    <t xml:space="preserve">5.78272819519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75416994094849</t>
   </si>
   <si>
     <t xml:space="preserve">5.74118804931641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73945665359497</t>
+    <t xml:space="preserve">5.73945713043213</t>
   </si>
   <si>
     <t xml:space="preserve">5.81042194366455</t>
@@ -2084,139 +2081,139 @@
     <t xml:space="preserve">5.90561771392822</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93331146240234</t>
+    <t xml:space="preserve">5.93331098556519</t>
   </si>
   <si>
     <t xml:space="preserve">5.94109964370728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91081047058105</t>
+    <t xml:space="preserve">5.9108099937439</t>
   </si>
   <si>
     <t xml:space="preserve">5.92638826370239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85369300842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85628890991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68060922622681</t>
+    <t xml:space="preserve">5.85369205474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85628938674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68060874938965</t>
   </si>
   <si>
     <t xml:space="preserve">5.73253440856934</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81907606124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9064826965332</t>
+    <t xml:space="preserve">5.81907558441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90648317337036</t>
   </si>
   <si>
     <t xml:space="preserve">5.70570611953735</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57502746582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75590085983276</t>
+    <t xml:space="preserve">5.57502794265747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75590038299561</t>
   </si>
   <si>
     <t xml:space="preserve">5.81561374664307</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7602276802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73513031005859</t>
+    <t xml:space="preserve">5.76022720336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73512983322144</t>
   </si>
   <si>
     <t xml:space="preserve">5.72041797637939</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69791746139526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69272518157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62868356704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75936269760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65810823440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5724310874939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62522220611572</t>
+    <t xml:space="preserve">5.69791793823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69272470474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62868404388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75936222076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65810775756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57243204116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62522268295288</t>
   </si>
   <si>
     <t xml:space="preserve">5.6728196144104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58195114135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58454751968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64512634277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72561073303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61483716964722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60704851150513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65291547775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65551137924194</t>
+    <t xml:space="preserve">5.58195066452026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.584547996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6451268196106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72561120986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61483669281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60704898834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65291595458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6555118560791</t>
   </si>
   <si>
     <t xml:space="preserve">5.75503492355347</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84071159362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00600624084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92811822891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87619352340698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71436071395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42184829711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36213541030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19510889053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04019927978516</t>
+    <t xml:space="preserve">5.84071111679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00600671768188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92811870574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87619304656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71436023712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42184925079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36213493347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19510841369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.040198802948</t>
   </si>
   <si>
     <t xml:space="preserve">5.15443420410156</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18039655685425</t>
+    <t xml:space="preserve">5.18039703369141</t>
   </si>
   <si>
     <t xml:space="preserve">4.79615068435669</t>
@@ -2228,34 +2225,34 @@
     <t xml:space="preserve">4.30113124847412</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30718946456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94501137733459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11073970794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9809262752533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77452373504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89438438415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17564535140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8238525390625</t>
+    <t xml:space="preserve">4.30718898773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94501161575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11073875427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98092603683472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77452397346497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89438462257385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17564582824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82385301589966</t>
   </si>
   <si>
     <t xml:space="preserve">3.97486853599548</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07006502151489</t>
+    <t xml:space="preserve">4.07006454467773</t>
   </si>
   <si>
     <t xml:space="preserve">4.27387046813965</t>
@@ -2264,25 +2261,25 @@
     <t xml:space="preserve">4.11766290664673</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05665016174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25699520111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30978584289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37036561965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17131853103638</t>
+    <t xml:space="preserve">4.05665063858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25699472427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30978536605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37036514282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17131805419922</t>
   </si>
   <si>
     <t xml:space="preserve">4.32709407806396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45690679550171</t>
+    <t xml:space="preserve">4.45690727233887</t>
   </si>
   <si>
     <t xml:space="preserve">4.61268186569214</t>
@@ -2291,7 +2288,7 @@
     <t xml:space="preserve">4.48286914825439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62999105453491</t>
+    <t xml:space="preserve">4.62999057769775</t>
   </si>
   <si>
     <t xml:space="preserve">4.56941175460815</t>
@@ -2303,7 +2300,7 @@
     <t xml:space="preserve">4.52614068984985</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50017833709717</t>
+    <t xml:space="preserve">4.50017786026001</t>
   </si>
   <si>
     <t xml:space="preserve">4.74249505996704</t>
@@ -2312,52 +2309,55 @@
     <t xml:space="preserve">4.76845741271973</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79442024230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94154119491577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91557884216309</t>
+    <t xml:space="preserve">4.79441976547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94154167175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91557788848877</t>
   </si>
   <si>
     <t xml:space="preserve">4.83769083023071</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58671951293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5521035194397</t>
+    <t xml:space="preserve">4.58671903610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55210256576538</t>
   </si>
   <si>
     <t xml:space="preserve">4.62133693695068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67326211929321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8030743598938</t>
+    <t xml:space="preserve">4.67326164245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80307483673096</t>
   </si>
   <si>
     <t xml:space="preserve">4.90961217880249</t>
   </si>
   <si>
+    <t xml:space="preserve">4.80307388305664</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.73204898834229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88297700881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91848993301392</t>
+    <t xml:space="preserve">4.88297748565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91848945617676</t>
   </si>
   <si>
     <t xml:space="preserve">5.10493087768555</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22034692764282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19371223449707</t>
+    <t xml:space="preserve">5.22034740447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19371175765991</t>
   </si>
   <si>
     <t xml:space="preserve">5.39790964126587</t>
@@ -2369,7 +2369,7 @@
     <t xml:space="preserve">5.30025005340576</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52220296859741</t>
+    <t xml:space="preserve">5.52220344543457</t>
   </si>
   <si>
     <t xml:space="preserve">5.49556922912598</t>
@@ -2378,10 +2378,10 @@
     <t xml:space="preserve">5.60210704803467</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72640085220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81518220901489</t>
+    <t xml:space="preserve">5.72640037536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81518268585205</t>
   </si>
   <si>
     <t xml:space="preserve">5.63761901855469</t>
@@ -2390,79 +2390,79 @@
     <t xml:space="preserve">5.30912780761719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27361583709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23810291290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55771589279175</t>
+    <t xml:space="preserve">5.27361631393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23810338973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55771636962891</t>
   </si>
   <si>
     <t xml:space="preserve">5.73527908325195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61098480224609</t>
+    <t xml:space="preserve">5.61098527908325</t>
   </si>
   <si>
     <t xml:space="preserve">5.65537548065186</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68200969696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61986303329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64649724960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71752262115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58435010910034</t>
+    <t xml:space="preserve">5.68201017379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61986351013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64649772644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71752309799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58435106277466</t>
   </si>
   <si>
     <t xml:space="preserve">5.56659460067749</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53108167648315</t>
+    <t xml:space="preserve">5.53108215332031</t>
   </si>
   <si>
     <t xml:space="preserve">5.46005630493164</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35351896286011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4245433807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41566562652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31800556182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38903141021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29137134552002</t>
+    <t xml:space="preserve">5.35351943969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42454433441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41566610336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31800651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38903188705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29137182235718</t>
   </si>
   <si>
     <t xml:space="preserve">5.21146821975708</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36239671707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25585889816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26473665237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37127494812012</t>
+    <t xml:space="preserve">5.36239624023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25585985183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26473712921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37127590179443</t>
   </si>
   <si>
     <t xml:space="preserve">5.48669099807739</t>
@@ -2471,22 +2471,22 @@
     <t xml:space="preserve">5.59322834014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53995943069458</t>
+    <t xml:space="preserve">5.53995990753174</t>
   </si>
   <si>
     <t xml:space="preserve">5.5044469833374</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38015365600586</t>
+    <t xml:space="preserve">5.3801531791687</t>
   </si>
   <si>
     <t xml:space="preserve">5.34464073181152</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28249359130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20259046554565</t>
+    <t xml:space="preserve">5.28249406814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20259094238281</t>
   </si>
   <si>
     <t xml:space="preserve">5.32688474655151</t>
@@ -2495,103 +2495,103 @@
     <t xml:space="preserve">5.3357629776001</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24698114395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15819931030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13156509399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16707801818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18483400344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02502727508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90073394775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61663389205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72317123413086</t>
+    <t xml:space="preserve">5.24698066711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15819978713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1315655708313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16707849502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1848349571228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02502775192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90073347091675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61663293838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72317171096802</t>
   </si>
   <si>
     <t xml:space="preserve">4.85634326934814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99839305877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0072717666626</t>
+    <t xml:space="preserve">4.99839353561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00727128982544</t>
   </si>
   <si>
     <t xml:space="preserve">4.89185571670532</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98951482772827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90396356582642</t>
+    <t xml:space="preserve">4.98951530456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90396404266357</t>
   </si>
   <si>
     <t xml:space="preserve">6.01050138473511</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01937913894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9927453994751</t>
+    <t xml:space="preserve">6.01937961578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99274492263794</t>
   </si>
   <si>
     <t xml:space="preserve">6.09928274154663</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10816049575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35674858093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.188063621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24133253097534</t>
+    <t xml:space="preserve">6.10816097259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35674905776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18806457519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">6.28572368621826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32123613357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25021076202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30347967147827</t>
+    <t xml:space="preserve">6.3212366104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25021123886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30348062515259</t>
   </si>
   <si>
     <t xml:space="preserve">6.31235790252686</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11703872680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0815258026123</t>
+    <t xml:space="preserve">6.1170392036438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08152627944946</t>
   </si>
   <si>
     <t xml:space="preserve">6.06377029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05489206314087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98386669158936</t>
+    <t xml:space="preserve">6.05489253997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9838662147522</t>
   </si>
   <si>
     <t xml:space="preserve">5.96611022949219</t>
@@ -2603,34 +2603,34 @@
     <t xml:space="preserve">5.94835376739502</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92171955108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91284132003784</t>
+    <t xml:space="preserve">5.92172002792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.912841796875</t>
   </si>
   <si>
     <t xml:space="preserve">6.23245477676392</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46328639984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33011484146118</t>
+    <t xml:space="preserve">6.46328687667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33011388778687</t>
   </si>
   <si>
     <t xml:space="preserve">6.27684545516968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20582008361816</t>
+    <t xml:space="preserve">6.20582056045532</t>
   </si>
   <si>
     <t xml:space="preserve">6.04601383209229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37450456619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12591743469238</t>
+    <t xml:space="preserve">6.37450504302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12591695785522</t>
   </si>
   <si>
     <t xml:space="preserve">6.21469831466675</t>
@@ -2639,37 +2639,37 @@
     <t xml:space="preserve">6.17918586730957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26796722412109</t>
+    <t xml:space="preserve">6.26796770095825</t>
   </si>
   <si>
     <t xml:space="preserve">6.48104286193848</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66748332977295</t>
+    <t xml:space="preserve">6.66748428344727</t>
   </si>
   <si>
     <t xml:space="preserve">7.01373147964478</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43988227844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54641962051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59968948364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63520240783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68846988677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52866363525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31558752059937</t>
+    <t xml:space="preserve">7.43988275527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54642009735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59968900680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63520193099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68847036361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52866315841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31558799743652</t>
   </si>
   <si>
     <t xml:space="preserve">7.30670976638794</t>
@@ -2678,10 +2678,10 @@
     <t xml:space="preserve">7.1824164390564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29783153533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13802528381348</t>
+    <t xml:space="preserve">7.29783201217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13802576065063</t>
   </si>
   <si>
     <t xml:space="preserve">7.04924392700195</t>
@@ -2693,13 +2693,13 @@
     <t xml:space="preserve">7.21792840957642</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35109996795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48427295684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59081029891968</t>
+    <t xml:space="preserve">7.35110092163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4842734336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59081077575684</t>
   </si>
   <si>
     <t xml:space="preserve">7.58193254470825</t>
@@ -2711,73 +2711,73 @@
     <t xml:space="preserve">7.51090717315674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45763731002808</t>
+    <t xml:space="preserve">7.45763826370239</t>
   </si>
   <si>
     <t xml:space="preserve">7.17353773117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61744451522827</t>
+    <t xml:space="preserve">7.61744499206543</t>
   </si>
   <si>
     <t xml:space="preserve">7.6795916557312</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76837348937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93705797195435</t>
+    <t xml:space="preserve">7.76837396621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93705749511719</t>
   </si>
   <si>
     <t xml:space="preserve">8.19452381134033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09686374664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99920463562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17676830291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20340156555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99032688140869</t>
+    <t xml:space="preserve">8.09686470031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99920511245728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17676734924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20340251922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99032735824585</t>
   </si>
   <si>
     <t xml:space="preserve">8.08798694610596</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0524730682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04359722137451</t>
+    <t xml:space="preserve">8.05247497558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0435962677002</t>
   </si>
   <si>
     <t xml:space="preserve">8.00808429718018</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07910919189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14125633239746</t>
+    <t xml:space="preserve">8.07910823822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14125537872314</t>
   </si>
   <si>
     <t xml:space="preserve">8.07022953033447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15013408660889</t>
+    <t xml:space="preserve">8.15013313293457</t>
   </si>
   <si>
     <t xml:space="preserve">8.38984298706055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23891448974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44311237335205</t>
+    <t xml:space="preserve">8.23891544342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44311141967773</t>
   </si>
   <si>
     <t xml:space="preserve">8.38096618652344</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">8.51413726806641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43423461914062</t>
+    <t xml:space="preserve">8.43423366546631</t>
   </si>
   <si>
     <t xml:space="preserve">8.64730930328369</t>
@@ -2798,7 +2798,7 @@
     <t xml:space="preserve">8.47014427185059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60530662536621</t>
+    <t xml:space="preserve">8.60530567169189</t>
   </si>
   <si>
     <t xml:space="preserve">8.43410110473633</t>
@@ -2810,10 +2810,10 @@
     <t xml:space="preserve">8.37102508544922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56025314331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31695938110352</t>
+    <t xml:space="preserve">8.56025123596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31696033477783</t>
   </si>
   <si>
     <t xml:space="preserve">8.42508983612061</t>
@@ -2828,10 +2828,10 @@
     <t xml:space="preserve">8.6593713760376</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70442390441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7404670715332</t>
+    <t xml:space="preserve">8.70442485809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74046802520752</t>
   </si>
   <si>
     <t xml:space="preserve">8.68640327453613</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">8.51519775390625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5332202911377</t>
+    <t xml:space="preserve">8.53321933746338</t>
   </si>
   <si>
     <t xml:space="preserve">8.46113395690918</t>
@@ -2855,10 +2855,10 @@
     <t xml:space="preserve">8.27190685272217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10971260070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15476608276367</t>
+    <t xml:space="preserve">8.10971355438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15476703643799</t>
   </si>
   <si>
     <t xml:space="preserve">8.08268070220947</t>
@@ -2867,52 +2867,52 @@
     <t xml:space="preserve">8.0466365814209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05564785003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95652914047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00158309936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7492823600769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85741138458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78532457351685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83938837051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74026918411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99257278442383</t>
+    <t xml:space="preserve">8.0556468963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95652961730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00158214569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74928140640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8574104309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78532409667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83938932418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74027013778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99257230758667</t>
   </si>
   <si>
     <t xml:space="preserve">7.92048597335815</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1727876663208</t>
+    <t xml:space="preserve">8.17278861999512</t>
   </si>
   <si>
     <t xml:space="preserve">8.29893970489502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16377830505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21784114837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96554088592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6051082611084</t>
+    <t xml:space="preserve">8.16377735137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2178430557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96553993225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60510730743408</t>
   </si>
   <si>
     <t xml:space="preserve">8.07366943359375</t>
@@ -2924,31 +2924,31 @@
     <t xml:space="preserve">8.12773513793945</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4881649017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38904666900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35300445556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33498287200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71343612670898</t>
+    <t xml:space="preserve">8.48816585540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38904762268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35300350189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33498191833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71343517303467</t>
   </si>
   <si>
     <t xml:space="preserve">8.63233852386475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23586463928223</t>
+    <t xml:space="preserve">8.23586368560791</t>
   </si>
   <si>
     <t xml:space="preserve">8.30795097351074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64134979248047</t>
+    <t xml:space="preserve">8.64134883880615</t>
   </si>
   <si>
     <t xml:space="preserve">8.77651119232178</t>
@@ -2963,16 +2963,16 @@
     <t xml:space="preserve">8.25388526916504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19982147216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03762626647949</t>
+    <t xml:space="preserve">8.19982051849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03762722015381</t>
   </si>
   <si>
     <t xml:space="preserve">7.92949724197388</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98356103897095</t>
+    <t xml:space="preserve">7.98356151580811</t>
   </si>
   <si>
     <t xml:space="preserve">8.01960468292236</t>
@@ -2981,10 +2981,10 @@
     <t xml:space="preserve">7.88444328308105</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56906414031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63214015960693</t>
+    <t xml:space="preserve">7.56906461715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63214063644409</t>
   </si>
   <si>
     <t xml:space="preserve">7.57807588577271</t>
@@ -2993,22 +2993,22 @@
     <t xml:space="preserve">7.55104398727417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65917301177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67719554901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72224855422974</t>
+    <t xml:space="preserve">7.65917348861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67719507217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72224807739258</t>
   </si>
   <si>
     <t xml:space="preserve">7.7673020362854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71323871612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93850803375244</t>
+    <t xml:space="preserve">7.71323776245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93850755691528</t>
   </si>
   <si>
     <t xml:space="preserve">8.2268533706665</t>
@@ -3017,13 +3017,13 @@
     <t xml:space="preserve">8.19080924987793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20883083343506</t>
+    <t xml:space="preserve">8.20883178710938</t>
   </si>
   <si>
     <t xml:space="preserve">8.38003635406494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18179893493652</t>
+    <t xml:space="preserve">8.18179798126221</t>
   </si>
   <si>
     <t xml:space="preserve">8.02861595153809</t>
@@ -3032,49 +3032,49 @@
     <t xml:space="preserve">7.80334568023682</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6952166557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61411905288696</t>
+    <t xml:space="preserve">7.69521617889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6141185760498</t>
   </si>
   <si>
     <t xml:space="preserve">7.37983798980713</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33478450775146</t>
+    <t xml:space="preserve">7.33478498458862</t>
   </si>
   <si>
     <t xml:space="preserve">7.37082767486572</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46093463897705</t>
+    <t xml:space="preserve">7.46093559265137</t>
   </si>
   <si>
     <t xml:space="preserve">7.36181735992432</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35280561447144</t>
+    <t xml:space="preserve">7.35280609130859</t>
   </si>
   <si>
     <t xml:space="preserve">7.4429144859314</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65016269683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46994686126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39786005020142</t>
+    <t xml:space="preserve">7.65016174316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46994638442993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39786052703857</t>
   </si>
   <si>
     <t xml:space="preserve">7.3257737159729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27170848846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30775165557861</t>
+    <t xml:space="preserve">7.27170896530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30775213241577</t>
   </si>
   <si>
     <t xml:space="preserve">7.29874134063721</t>
@@ -3083,7 +3083,7 @@
     <t xml:space="preserve">7.26269865036011</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54203271865845</t>
+    <t xml:space="preserve">7.54203224182129</t>
   </si>
   <si>
     <t xml:space="preserve">7.64115142822266</t>
@@ -3092,10 +3092,10 @@
     <t xml:space="preserve">7.62312984466553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53302097320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52401161193848</t>
+    <t xml:space="preserve">7.53302192687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52401113510132</t>
   </si>
   <si>
     <t xml:space="preserve">7.31676292419434</t>
@@ -3104,43 +3104,43 @@
     <t xml:space="preserve">7.38884925842285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45192527770996</t>
+    <t xml:space="preserve">7.4519248008728</t>
   </si>
   <si>
     <t xml:space="preserve">6.96534204483032</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92929935455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02841806411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89325571060181</t>
+    <t xml:space="preserve">6.92929840087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02841758728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89325618743896</t>
   </si>
   <si>
     <t xml:space="preserve">7.0103964805603</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12753582000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11852598190308</t>
+    <t xml:space="preserve">7.12753629684448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11852550506592</t>
   </si>
   <si>
     <t xml:space="preserve">6.94732046127319</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88424491882324</t>
+    <t xml:space="preserve">6.88424444198608</t>
   </si>
   <si>
     <t xml:space="preserve">6.90226650238037</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28071975708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22665548324585</t>
+    <t xml:space="preserve">7.28071928024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22665500640869</t>
   </si>
   <si>
     <t xml:space="preserve">7.03742837905884</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">7.14555788040161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19962215423584</t>
+    <t xml:space="preserve">7.199622631073</t>
   </si>
   <si>
     <t xml:space="preserve">7.00138521194458</t>
@@ -3158,13 +3158,13 @@
     <t xml:space="preserve">7.07347106933594</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80314779281616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74007177352905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66798639297485</t>
+    <t xml:space="preserve">6.80314826965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74007225036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6679859161377</t>
   </si>
   <si>
     <t xml:space="preserve">6.3616189956665</t>
@@ -3191,22 +3191,22 @@
     <t xml:space="preserve">6.01019811630249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28052139282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09129524230957</t>
+    <t xml:space="preserve">6.28052186965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09129571914673</t>
   </si>
   <si>
     <t xml:space="preserve">6.14535999298096</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35260820388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23546838760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46974802017212</t>
+    <t xml:space="preserve">6.3526086807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2354679107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46974849700928</t>
   </si>
   <si>
     <t xml:space="preserve">6.3886513710022</t>
@@ -3215,13 +3215,13 @@
     <t xml:space="preserve">6.37062978744507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28953313827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31656551361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02822017669678</t>
+    <t xml:space="preserve">6.28953266143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31656503677368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02821969985962</t>
   </si>
   <si>
     <t xml:space="preserve">6.11832761764526</t>
@@ -3236,13 +3236,13 @@
     <t xml:space="preserve">6.26250028610229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18140363693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29854297637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17239189147949</t>
+    <t xml:space="preserve">6.18140316009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29854345321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17239236831665</t>
   </si>
   <si>
     <t xml:space="preserve">5.84800386428833</t>
@@ -3254,19 +3254,19 @@
     <t xml:space="preserve">5.92009019851685</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89305782318115</t>
+    <t xml:space="preserve">5.89305830001831</t>
   </si>
   <si>
     <t xml:space="preserve">5.93811178207397</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88404750823975</t>
+    <t xml:space="preserve">5.88404703140259</t>
   </si>
   <si>
     <t xml:space="preserve">6.10030603408813</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21744680404663</t>
+    <t xml:space="preserve">6.21744632720947</t>
   </si>
   <si>
     <t xml:space="preserve">6.06426286697388</t>
@@ -3275,13 +3275,13 @@
     <t xml:space="preserve">5.9831657409668</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94712257385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01920890808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99217653274536</t>
+    <t xml:space="preserve">5.9471230506897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0192084312439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99217700958252</t>
   </si>
   <si>
     <t xml:space="preserve">5.96514415740967</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">5.9561333656311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08228492736816</t>
+    <t xml:space="preserve">6.08228445053101</t>
   </si>
   <si>
     <t xml:space="preserve">6.07327318191528</t>
@@ -3311,7 +3311,7 @@
     <t xml:space="preserve">5.96590328216553</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1604437828064</t>
+    <t xml:space="preserve">6.16044425964355</t>
   </si>
   <si>
     <t xml:space="preserve">6.28087329864502</t>
@@ -3320,10 +3320,10 @@
     <t xml:space="preserve">6.22529029846191</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20676231384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17897129058838</t>
+    <t xml:space="preserve">6.20676279067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17897176742554</t>
   </si>
   <si>
     <t xml:space="preserve">6.29013729095459</t>
@@ -3347,7 +3347,7 @@
     <t xml:space="preserve">5.9288477897644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89179277420044</t>
+    <t xml:space="preserve">5.8917932510376</t>
   </si>
   <si>
     <t xml:space="preserve">6.09559679031372</t>
@@ -3359,7 +3359,7 @@
     <t xml:space="preserve">5.95663928985596</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82694578170776</t>
+    <t xml:space="preserve">5.82694625854492</t>
   </si>
   <si>
     <t xml:space="preserve">5.68798828125</t>
@@ -3374,10 +3374,10 @@
     <t xml:space="preserve">5.72504377365112</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34522676467896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44712924957275</t>
+    <t xml:space="preserve">5.34522724151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4471287727356</t>
   </si>
   <si>
     <t xml:space="preserve">5.6046142578125</t>
@@ -3386,31 +3386,31 @@
     <t xml:space="preserve">5.75283527374268</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51197576522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85473728179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55829524993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71577978134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77136325836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61387825012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66019678115845</t>
+    <t xml:space="preserve">5.51197528839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85473775863647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55829477310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71578073501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77136278152466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61387777328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66019725799561</t>
   </si>
   <si>
     <t xml:space="preserve">5.87326526641846</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66946125030518</t>
+    <t xml:space="preserve">5.66946077346802</t>
   </si>
   <si>
     <t xml:space="preserve">5.80841875076294</t>
@@ -3419,13 +3419,13 @@
     <t xml:space="preserve">6.0307502746582</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04927825927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86400127410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53976726531982</t>
+    <t xml:space="preserve">6.04927778244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86400079727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53976774215698</t>
   </si>
   <si>
     <t xml:space="preserve">5.49344778060913</t>
@@ -3437,7 +3437,7 @@
     <t xml:space="preserve">5.37301874160767</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39154624938965</t>
+    <t xml:space="preserve">5.39154672622681</t>
   </si>
   <si>
     <t xml:space="preserve">5.35449075698853</t>
@@ -3452,22 +3452,22 @@
     <t xml:space="preserve">5.15995073318481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21553325653076</t>
+    <t xml:space="preserve">5.21553373336792</t>
   </si>
   <si>
     <t xml:space="preserve">5.19700622558594</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25258874893188</t>
+    <t xml:space="preserve">5.25258922576904</t>
   </si>
   <si>
     <t xml:space="preserve">5.38228225708008</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1321587562561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10436773300171</t>
+    <t xml:space="preserve">5.13215923309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10436820983887</t>
   </si>
   <si>
     <t xml:space="preserve">5.28038024902344</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">5.2340612411499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08584022521973</t>
+    <t xml:space="preserve">5.08583974838257</t>
   </si>
   <si>
     <t xml:space="preserve">5.05804872512817</t>
@@ -3500,37 +3500,37 @@
     <t xml:space="preserve">5.15068674087524</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00246572494507</t>
+    <t xml:space="preserve">5.00246524810791</t>
   </si>
   <si>
     <t xml:space="preserve">4.8635082244873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91909122467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97467422485352</t>
+    <t xml:space="preserve">4.91909074783325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97467374801636</t>
   </si>
   <si>
     <t xml:space="preserve">4.96541023254395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22479772567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3359637260437</t>
+    <t xml:space="preserve">5.22479724884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33596324920654</t>
   </si>
   <si>
     <t xml:space="preserve">5.30817174911499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45639276504517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52123928070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29890775680542</t>
+    <t xml:space="preserve">5.45639324188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52123975753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29890823364258</t>
   </si>
   <si>
     <t xml:space="preserve">5.46565675735474</t>
@@ -3542,16 +3542,16 @@
     <t xml:space="preserve">5.67872476577759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76209878921509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90105628967285</t>
+    <t xml:space="preserve">5.76209926605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90105676651001</t>
   </si>
   <si>
     <t xml:space="preserve">5.91958427429199</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70651626586914</t>
+    <t xml:space="preserve">5.70651578903198</t>
   </si>
   <si>
     <t xml:space="preserve">5.74357128143311</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">5.63240575790405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54903078079224</t>
+    <t xml:space="preserve">5.54903125762939</t>
   </si>
   <si>
     <t xml:space="preserve">5.64166975021362</t>
@@ -3587,16 +3587,16 @@
     <t xml:space="preserve">6.74406480789185</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70700883865356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79964828491211</t>
+    <t xml:space="preserve">6.70700931549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79964780807495</t>
   </si>
   <si>
     <t xml:space="preserve">6.82743883132935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79038333892822</t>
+    <t xml:space="preserve">6.79038381576538</t>
   </si>
   <si>
     <t xml:space="preserve">6.89228582382202</t>
@@ -3623,34 +3623,34 @@
     <t xml:space="preserve">7.48517084121704</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42958831787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55928087234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39253234863281</t>
+    <t xml:space="preserve">7.42958784103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55928134918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39253282546997</t>
   </si>
   <si>
     <t xml:space="preserve">7.59633636474609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54075384140015</t>
+    <t xml:space="preserve">7.54075336456299</t>
   </si>
   <si>
     <t xml:space="preserve">7.64265584945679</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50369834899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63339138031006</t>
+    <t xml:space="preserve">7.50369882583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63339185714722</t>
   </si>
   <si>
     <t xml:space="preserve">7.62412786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57780885696411</t>
+    <t xml:space="preserve">7.57780933380127</t>
   </si>
   <si>
     <t xml:space="preserve">7.58707237243652</t>
@@ -3668,13 +3668,13 @@
     <t xml:space="preserve">7.32768535614014</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10535430908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18872833251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42032432556152</t>
+    <t xml:space="preserve">7.10535383224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18872785568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42032384872437</t>
   </si>
   <si>
     <t xml:space="preserve">7.30915784835815</t>
@@ -3689,7 +3689,7 @@
     <t xml:space="preserve">7.29989433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24431180953979</t>
+    <t xml:space="preserve">7.24431133270264</t>
   </si>
   <si>
     <t xml:space="preserve">7.21651983261108</t>
@@ -3704,37 +3704,37 @@
     <t xml:space="preserve">7.33694934844971</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31842231750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26283931732178</t>
+    <t xml:space="preserve">7.31842184066772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26283884048462</t>
   </si>
   <si>
     <t xml:space="preserve">7.12388181686401</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04977130889893</t>
+    <t xml:space="preserve">7.04977083206177</t>
   </si>
   <si>
     <t xml:space="preserve">6.98492383956909</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07756233215332</t>
+    <t xml:space="preserve">7.07756185531616</t>
   </si>
   <si>
     <t xml:space="preserve">7.22578382492065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19799184799194</t>
+    <t xml:space="preserve">7.1979923248291</t>
   </si>
   <si>
     <t xml:space="preserve">7.15167284011841</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11461734771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05903434753418</t>
+    <t xml:space="preserve">7.11461782455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05903482437134</t>
   </si>
   <si>
     <t xml:space="preserve">7.06857395172119</t>
@@ -3749,34 +3749,34 @@
     <t xml:space="preserve">6.94456434249878</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86824989318848</t>
+    <t xml:space="preserve">6.86825037002563</t>
   </si>
   <si>
     <t xml:space="preserve">6.79193639755249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75377941131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84917163848877</t>
+    <t xml:space="preserve">6.75377893447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84917116165161</t>
   </si>
   <si>
     <t xml:space="preserve">6.99226045608521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95410346984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87778902053833</t>
+    <t xml:space="preserve">6.95410299301147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87778949737549</t>
   </si>
   <si>
     <t xml:space="preserve">6.98272132873535</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96364259719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03041744232178</t>
+    <t xml:space="preserve">6.96364307403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03041696548462</t>
   </si>
   <si>
     <t xml:space="preserve">7.01133871078491</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">6.78239727020264</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7251615524292</t>
+    <t xml:space="preserve">6.72516202926636</t>
   </si>
   <si>
     <t xml:space="preserve">7.00179958343506</t>
@@ -3815,19 +3815,19 @@
     <t xml:space="preserve">7.36429023742676</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28797674179077</t>
+    <t xml:space="preserve">7.28797626495361</t>
   </si>
   <si>
     <t xml:space="preserve">7.29751586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30705499649048</t>
+    <t xml:space="preserve">7.30705451965332</t>
   </si>
   <si>
     <t xml:space="preserve">7.53599691390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57415390014648</t>
+    <t xml:space="preserve">7.57415342330933</t>
   </si>
   <si>
     <t xml:space="preserve">7.66000652313232</t>
@@ -3836,10 +3836,10 @@
     <t xml:space="preserve">7.6981635093689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93664455413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98434066772461</t>
+    <t xml:space="preserve">7.93664407730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98434019088745</t>
   </si>
   <si>
     <t xml:space="preserve">8.18466472625732</t>
@@ -3857,19 +3857,19 @@
     <t xml:space="preserve">8.16558647155762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04157733917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8794093132019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97480154037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03203678131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90802717208862</t>
+    <t xml:space="preserve">8.04157638549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87940979003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9748010635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03203773498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90802669525146</t>
   </si>
   <si>
     <t xml:space="preserve">7.89848756790161</t>
@@ -3881,7 +3881,7 @@
     <t xml:space="preserve">7.84125232696533</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88894844055176</t>
+    <t xml:space="preserve">7.88894891738892</t>
   </si>
   <si>
     <t xml:space="preserve">7.78401708602905</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">7.81263399124146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85079050064087</t>
+    <t xml:space="preserve">7.85079145431519</t>
   </si>
   <si>
     <t xml:space="preserve">7.77447748184204</t>
@@ -3905,13 +3905,13 @@
     <t xml:space="preserve">7.72678184509277</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64092874526978</t>
+    <t xml:space="preserve">7.64092826843262</t>
   </si>
   <si>
     <t xml:space="preserve">7.58369255065918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38336896896362</t>
+    <t xml:space="preserve">7.38336849212646</t>
   </si>
   <si>
     <t xml:space="preserve">7.3356728553772</t>
@@ -3932,7 +3932,7 @@
     <t xml:space="preserve">7.08765268325806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15442705154419</t>
+    <t xml:space="preserve">7.15442752838135</t>
   </si>
   <si>
     <t xml:space="preserve">7.03995656967163</t>
@@ -3944,7 +3944,7 @@
     <t xml:space="preserve">7.27843761444092</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41198635101318</t>
+    <t xml:space="preserve">7.41198682785034</t>
   </si>
   <si>
     <t xml:space="preserve">7.39290809631348</t>
@@ -3965,13 +3965,13 @@
     <t xml:space="preserve">7.45014333724976</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40244770050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50737857818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70770263671875</t>
+    <t xml:space="preserve">7.40244722366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50737905502319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70770311355591</t>
   </si>
   <si>
     <t xml:space="preserve">8.20374393463135</t>
@@ -3986,10 +3986,10 @@
     <t xml:space="preserve">8.10835075378418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08927249908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36591053009033</t>
+    <t xml:space="preserve">8.08927154541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36591148376465</t>
   </si>
   <si>
     <t xml:space="preserve">8.30867481231689</t>
@@ -4007,13 +4007,13 @@
     <t xml:space="preserve">8.60439205169678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40406703948975</t>
+    <t xml:space="preserve">8.40406799316406</t>
   </si>
   <si>
     <t xml:space="preserve">8.41360664367676</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26097774505615</t>
+    <t xml:space="preserve">8.26097869873047</t>
   </si>
   <si>
     <t xml:space="preserve">8.57577323913574</t>
@@ -4028,10 +4028,10 @@
     <t xml:space="preserve">8.76655769348145</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1576681137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19582462310791</t>
+    <t xml:space="preserve">9.15766716003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19582366943359</t>
   </si>
   <si>
     <t xml:space="preserve">9.11951065063477</t>
@@ -4040,13 +4040,13 @@
     <t xml:space="preserve">9.10043144226074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09089183807373</t>
+    <t xml:space="preserve">9.09089279174805</t>
   </si>
   <si>
     <t xml:space="preserve">8.72840118408203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87149047851562</t>
+    <t xml:space="preserve">8.87148952484131</t>
   </si>
   <si>
     <t xml:space="preserve">8.90964698791504</t>
@@ -4070,7 +4070,7 @@
     <t xml:space="preserve">9.00503826141357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20536327362061</t>
+    <t xml:space="preserve">9.20536231994629</t>
   </si>
   <si>
     <t xml:space="preserve">9.45338344573975</t>
@@ -4079,25 +4079,25 @@
     <t xml:space="preserve">9.50107955932617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52969741821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57739353179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47246170043945</t>
+    <t xml:space="preserve">9.52969646453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.577392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47246265411377</t>
   </si>
   <si>
     <t xml:space="preserve">9.36752986907959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30075454711914</t>
+    <t xml:space="preserve">9.30075550079346</t>
   </si>
   <si>
     <t xml:space="preserve">9.39614772796631</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44384288787842</t>
+    <t xml:space="preserve">9.44384384155273</t>
   </si>
   <si>
     <t xml:space="preserve">9.49153995513916</t>
@@ -4109,7 +4109,7 @@
     <t xml:space="preserve">8.69978332519531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55669498443604</t>
+    <t xml:space="preserve">8.55669593811035</t>
   </si>
   <si>
     <t xml:space="preserve">8.62346935272217</t>
@@ -4118,10 +4118,10 @@
     <t xml:space="preserve">8.48038101196289</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59485149383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70932292938232</t>
+    <t xml:space="preserve">8.59485244750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70932197570801</t>
   </si>
   <si>
     <t xml:space="preserve">8.77609729766846</t>
@@ -4133,10 +4133,10 @@
     <t xml:space="preserve">8.75701904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86195087432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89056777954102</t>
+    <t xml:space="preserve">8.8619499206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89056873321533</t>
   </si>
   <si>
     <t xml:space="preserve">8.67116546630859</t>
@@ -4151,10 +4151,10 @@
     <t xml:space="preserve">8.74748039245605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0145788192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92872428894043</t>
+    <t xml:space="preserve">9.01457786560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92872524261475</t>
   </si>
   <si>
     <t xml:space="preserve">8.97642135620117</t>
@@ -4166,28 +4166,28 @@
     <t xml:space="preserve">9.46292304992676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74910068511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78725719451904</t>
+    <t xml:space="preserve">9.74909973144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78725624084473</t>
   </si>
   <si>
     <t xml:space="preserve">9.92080497741699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99711894989014</t>
+    <t xml:space="preserve">9.99711990356445</t>
   </si>
   <si>
     <t xml:space="preserve">9.69186401367188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76817798614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80633449554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63462829589844</t>
+    <t xml:space="preserve">9.7681770324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80633544921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63462924957275</t>
   </si>
   <si>
     <t xml:space="preserve">9.67278575897217</t>
@@ -4196,10 +4196,10 @@
     <t xml:space="preserve">9.59647178649902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71094226837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52015686035156</t>
+    <t xml:space="preserve">9.7109432220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52015781402588</t>
   </si>
   <si>
     <t xml:space="preserve">9.43430519104004</t>
@@ -4208,13 +4208,13 @@
     <t xml:space="preserve">9.25305938720703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28167629241943</t>
+    <t xml:space="preserve">9.28167724609375</t>
   </si>
   <si>
     <t xml:space="preserve">9.34845161437988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41522693634033</t>
+    <t xml:space="preserve">9.41522598266602</t>
   </si>
   <si>
     <t xml:space="preserve">9.48200035095215</t>
@@ -4232,7 +4232,7 @@
     <t xml:space="preserve">9.65370750427246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86357116699219</t>
+    <t xml:space="preserve">9.86357021331787</t>
   </si>
   <si>
     <t xml:space="preserve">10.0204467773438</t>
@@ -4947,6 +4947,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.2399997711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3799991607666</t>
   </si>
 </sst>
 </file>
@@ -27923,7 +27926,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G871" t="s">
-        <v>604</v>
+        <v>586</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -27949,7 +27952,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G872" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -27975,7 +27978,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G873" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -28001,7 +28004,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G874" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -28027,7 +28030,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G875" t="s">
-        <v>604</v>
+        <v>586</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -28053,7 +28056,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G876" t="s">
-        <v>604</v>
+        <v>586</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -28079,7 +28082,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G877" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -28105,7 +28108,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G878" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -28131,7 +28134,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G879" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -28157,7 +28160,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G880" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -28183,7 +28186,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G881" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -28209,7 +28212,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G882" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -28235,7 +28238,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G883" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -28261,7 +28264,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G884" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -28287,7 +28290,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G885" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -28313,7 +28316,7 @@
         <v>6.25</v>
       </c>
       <c r="G886" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -28339,7 +28342,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G887" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -28365,7 +28368,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G888" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -28391,7 +28394,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G889" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -28417,7 +28420,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G890" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -28443,7 +28446,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G891" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -28469,7 +28472,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G892" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -28495,7 +28498,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G893" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -28521,7 +28524,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G894" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -28547,7 +28550,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G895" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -28573,7 +28576,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G896" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -28599,7 +28602,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G897" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -28625,7 +28628,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G898" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -28651,7 +28654,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G899" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -28677,7 +28680,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G900" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -28703,7 +28706,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G901" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -28729,7 +28732,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G902" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -28755,7 +28758,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G903" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -28781,7 +28784,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G904" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -28807,7 +28810,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G905" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -28833,7 +28836,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G906" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -28859,7 +28862,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G907" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -28885,7 +28888,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G908" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -28911,7 +28914,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G909" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -28937,7 +28940,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G910" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -28963,7 +28966,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G911" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -28989,7 +28992,7 @@
         <v>6.25</v>
       </c>
       <c r="G912" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -29015,7 +29018,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G913" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -29041,7 +29044,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G914" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -29067,7 +29070,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G915" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -29093,7 +29096,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G916" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -29119,7 +29122,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G917" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -29171,7 +29174,7 @@
         <v>6</v>
       </c>
       <c r="G919" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -29197,7 +29200,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G920" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -29223,7 +29226,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G921" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -29249,7 +29252,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G922" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -29275,7 +29278,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G923" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -29301,7 +29304,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G924" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -29353,7 +29356,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G926" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -29405,7 +29408,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G928" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -29431,7 +29434,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G929" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -29457,7 +29460,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G930" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -29483,7 +29486,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G931" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -29535,7 +29538,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G933" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -29587,7 +29590,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G935" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -29613,7 +29616,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G936" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -29639,7 +29642,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G937" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -29665,7 +29668,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G938" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -29691,7 +29694,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G939" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -29717,7 +29720,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G940" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -29743,7 +29746,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G941" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -29769,7 +29772,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G942" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -29795,7 +29798,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G943" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -29821,7 +29824,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G944" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -29847,7 +29850,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G945" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -29873,7 +29876,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G946" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -29899,7 +29902,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G947" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -29925,7 +29928,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G948" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -29951,7 +29954,7 @@
         <v>6</v>
       </c>
       <c r="G949" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -29977,7 +29980,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G950" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -30003,7 +30006,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G951" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -30029,7 +30032,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G952" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -30055,7 +30058,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G953" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -30081,7 +30084,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G954" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -30133,7 +30136,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G956" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -30159,7 +30162,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G957" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -30185,7 +30188,7 @@
         <v>5.96500015258789</v>
       </c>
       <c r="G958" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -30211,7 +30214,7 @@
         <v>5.82299995422363</v>
       </c>
       <c r="G959" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -30237,7 +30240,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G960" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -30263,7 +30266,7 @@
         <v>5.9539999961853</v>
       </c>
       <c r="G961" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -30289,7 +30292,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G962" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -30315,7 +30318,7 @@
         <v>6.01900005340576</v>
       </c>
       <c r="G963" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -30341,7 +30344,7 @@
         <v>6</v>
       </c>
       <c r="G964" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -30367,7 +30370,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G965" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -30393,7 +30396,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G966" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -30419,7 +30422,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G967" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -30445,7 +30448,7 @@
         <v>6.17700004577637</v>
       </c>
       <c r="G968" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -30471,7 +30474,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G969" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -30497,7 +30500,7 @@
         <v>6.10099983215332</v>
       </c>
       <c r="G970" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -30523,7 +30526,7 @@
         <v>6.13100004196167</v>
       </c>
       <c r="G971" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -30549,7 +30552,7 @@
         <v>6.08699989318848</v>
       </c>
       <c r="G972" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -30575,7 +30578,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G973" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -30601,7 +30604,7 @@
         <v>6.17899990081787</v>
       </c>
       <c r="G974" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -30627,7 +30630,7 @@
         <v>6.17899990081787</v>
       </c>
       <c r="G975" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -30653,7 +30656,7 @@
         <v>6.0310001373291</v>
       </c>
       <c r="G976" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -30679,7 +30682,7 @@
         <v>6.17399978637695</v>
       </c>
       <c r="G977" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -30705,7 +30708,7 @@
         <v>6.33799982070923</v>
       </c>
       <c r="G978" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -30731,7 +30734,7 @@
         <v>6.33799982070923</v>
       </c>
       <c r="G979" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -30757,7 +30760,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G980" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -30783,7 +30786,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G981" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -30809,7 +30812,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G982" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -30835,7 +30838,7 @@
         <v>6.37599992752075</v>
       </c>
       <c r="G983" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -30861,7 +30864,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G984" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -30887,7 +30890,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G985" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -30913,7 +30916,7 @@
         <v>6.33799982070923</v>
       </c>
       <c r="G986" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -30939,7 +30942,7 @@
         <v>6.37400007247925</v>
       </c>
       <c r="G987" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -30965,7 +30968,7 @@
         <v>6.31199979782104</v>
       </c>
       <c r="G988" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -30991,7 +30994,7 @@
         <v>6.26599979400635</v>
       </c>
       <c r="G989" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -31017,7 +31020,7 @@
         <v>6.31799983978271</v>
       </c>
       <c r="G990" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -31043,7 +31046,7 @@
         <v>6.29099988937378</v>
       </c>
       <c r="G991" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -31069,7 +31072,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G992" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -31095,7 +31098,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G993" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -31121,7 +31124,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G994" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -31147,7 +31150,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G995" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -31173,7 +31176,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G996" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -31199,7 +31202,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G997" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -31225,7 +31228,7 @@
         <v>6.86899995803833</v>
       </c>
       <c r="G998" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -31251,7 +31254,7 @@
         <v>6.66699981689453</v>
       </c>
       <c r="G999" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -31277,7 +31280,7 @@
         <v>6.68200016021729</v>
       </c>
       <c r="G1000" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -31303,7 +31306,7 @@
         <v>6.64900016784668</v>
       </c>
       <c r="G1001" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -31329,7 +31332,7 @@
         <v>6.63399982452393</v>
       </c>
       <c r="G1002" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -31355,7 +31358,7 @@
         <v>6.63199996948242</v>
       </c>
       <c r="G1003" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -31381,7 +31384,7 @@
         <v>6.71400022506714</v>
       </c>
       <c r="G1004" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -31407,7 +31410,7 @@
         <v>6.82399988174438</v>
       </c>
       <c r="G1005" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -31433,7 +31436,7 @@
         <v>6.85599994659424</v>
       </c>
       <c r="G1006" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -31459,7 +31462,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1007" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -31485,7 +31488,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1008" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -31511,7 +31514,7 @@
         <v>6.84800004959106</v>
       </c>
       <c r="G1009" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -31537,7 +31540,7 @@
         <v>6.76399993896484</v>
       </c>
       <c r="G1010" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -31563,7 +31566,7 @@
         <v>6.76700019836426</v>
       </c>
       <c r="G1011" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -31589,7 +31592,7 @@
         <v>6.56400012969971</v>
       </c>
       <c r="G1012" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -31615,7 +31618,7 @@
         <v>6.62400007247925</v>
       </c>
       <c r="G1013" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -31641,7 +31644,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1014" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -31667,7 +31670,7 @@
         <v>6.72399997711182</v>
       </c>
       <c r="G1015" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -31693,7 +31696,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1016" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -31719,7 +31722,7 @@
         <v>6.59299993515015</v>
       </c>
       <c r="G1017" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -31745,7 +31748,7 @@
         <v>6.44199991226196</v>
       </c>
       <c r="G1018" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -31771,7 +31774,7 @@
         <v>6.65100002288818</v>
       </c>
       <c r="G1019" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -31797,7 +31800,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1020" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -31823,7 +31826,7 @@
         <v>6.6560001373291</v>
       </c>
       <c r="G1021" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -31849,7 +31852,7 @@
         <v>6.6269998550415</v>
       </c>
       <c r="G1022" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -31875,7 +31878,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G1023" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -31901,7 +31904,7 @@
         <v>6.58400011062622</v>
       </c>
       <c r="G1024" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -31927,7 +31930,7 @@
         <v>6.57800006866455</v>
       </c>
       <c r="G1025" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -31953,7 +31956,7 @@
         <v>6.50400018692017</v>
       </c>
       <c r="G1026" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -31979,7 +31982,7 @@
         <v>6.65500020980835</v>
       </c>
       <c r="G1027" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -32005,7 +32008,7 @@
         <v>6.53800010681152</v>
       </c>
       <c r="G1028" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -32031,7 +32034,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1029" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -32057,7 +32060,7 @@
         <v>6.43900012969971</v>
       </c>
       <c r="G1030" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -32083,7 +32086,7 @@
         <v>6.5</v>
       </c>
       <c r="G1031" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -32109,7 +32112,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G1032" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -32135,7 +32138,7 @@
         <v>6.55499982833862</v>
       </c>
       <c r="G1033" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -32161,7 +32164,7 @@
         <v>6.5</v>
       </c>
       <c r="G1034" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -32187,7 +32190,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1035" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -32213,7 +32216,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1036" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -32239,7 +32242,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1037" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -32265,7 +32268,7 @@
         <v>6.45300006866455</v>
       </c>
       <c r="G1038" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -32291,7 +32294,7 @@
         <v>6.52299976348877</v>
       </c>
       <c r="G1039" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -32317,7 +32320,7 @@
         <v>6.61600017547607</v>
       </c>
       <c r="G1040" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -32343,7 +32346,7 @@
         <v>6.48799991607666</v>
       </c>
       <c r="G1041" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -32369,7 +32372,7 @@
         <v>6.47900009155273</v>
       </c>
       <c r="G1042" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -32395,7 +32398,7 @@
         <v>6.53200006484985</v>
       </c>
       <c r="G1043" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -32421,7 +32424,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G1044" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -32447,7 +32450,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G1045" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -32473,7 +32476,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1046" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -32499,7 +32502,7 @@
         <v>6.74900007247925</v>
       </c>
       <c r="G1047" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -32525,7 +32528,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1048" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -32551,7 +32554,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1049" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -32577,7 +32580,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G1050" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -32603,7 +32606,7 @@
         <v>6.60300016403198</v>
       </c>
       <c r="G1051" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -32629,7 +32632,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G1052" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -32655,7 +32658,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G1053" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -32681,7 +32684,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G1054" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -32707,7 +32710,7 @@
         <v>6.19600009918213</v>
       </c>
       <c r="G1055" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -32733,7 +32736,7 @@
         <v>6.00299978256226</v>
       </c>
       <c r="G1056" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -32759,7 +32762,7 @@
         <v>5.82399988174438</v>
       </c>
       <c r="G1057" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -32811,7 +32814,7 @@
         <v>5.95599985122681</v>
       </c>
       <c r="G1059" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -32837,7 +32840,7 @@
         <v>5.98600006103516</v>
       </c>
       <c r="G1060" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -32863,7 +32866,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G1061" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -32889,7 +32892,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1062" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -32915,7 +32918,7 @@
         <v>4.90350008010864</v>
       </c>
       <c r="G1063" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -32941,7 +32944,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1064" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -32967,7 +32970,7 @@
         <v>4.97700023651123</v>
       </c>
       <c r="G1065" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -32993,7 +32996,7 @@
         <v>4.55849981307983</v>
       </c>
       <c r="G1066" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -33019,7 +33022,7 @@
         <v>4.75</v>
       </c>
       <c r="G1067" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -33045,7 +33048,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1068" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -33071,7 +33074,7 @@
         <v>4.75</v>
       </c>
       <c r="G1069" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -33097,7 +33100,7 @@
         <v>4.36149978637695</v>
       </c>
       <c r="G1070" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -33123,7 +33126,7 @@
         <v>4.5</v>
       </c>
       <c r="G1071" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -33149,7 +33152,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G1072" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -33175,7 +33178,7 @@
         <v>4.41849994659424</v>
       </c>
       <c r="G1073" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -33201,7 +33204,7 @@
         <v>4.59299993515015</v>
       </c>
       <c r="G1074" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -33227,7 +33230,7 @@
         <v>4.70300006866455</v>
       </c>
       <c r="G1075" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -33253,7 +33256,7 @@
         <v>4.93849992752075</v>
       </c>
       <c r="G1076" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -33279,7 +33282,7 @@
         <v>4.75799989700317</v>
       </c>
       <c r="G1077" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -33305,7 +33308,7 @@
         <v>4.6875</v>
       </c>
       <c r="G1078" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -33331,7 +33334,7 @@
         <v>4.91900014877319</v>
       </c>
       <c r="G1079" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -33357,7 +33360,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1080" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -33383,7 +33386,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1081" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -33409,7 +33412,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1082" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -33435,7 +33438,7 @@
         <v>5</v>
       </c>
       <c r="G1083" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -33461,7 +33464,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1084" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -33487,7 +33490,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1085" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -33513,7 +33516,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1086" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -33539,7 +33542,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1087" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -33565,7 +33568,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1088" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -33591,7 +33594,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1089" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -33617,7 +33620,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1090" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -33643,7 +33646,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1091" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -33669,7 +33672,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G1092" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -33695,7 +33698,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1093" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -33721,7 +33724,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1094" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -33747,7 +33750,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1095" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -33773,7 +33776,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1096" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -33799,7 +33802,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1097" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -33825,7 +33828,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1098" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -33851,7 +33854,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1099" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -33877,7 +33880,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1100" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -33903,7 +33906,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1101" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -33929,7 +33932,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1102" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -33955,7 +33958,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1103" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -33981,7 +33984,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1104" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -34007,7 +34010,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1105" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -34033,7 +34036,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1106" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -34059,7 +34062,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1107" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -34085,7 +34088,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1108" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -34111,7 +34114,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1109" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -34137,7 +34140,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1110" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -34163,7 +34166,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1111" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -70805,7 +70808,7 @@
     </row>
     <row r="2521">
       <c r="A2521" s="1" t="n">
-        <v>45988.6911805556</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B2521" t="n">
         <v>203577</v>
@@ -70826,6 +70829,32 @@
         <v>1644</v>
       </c>
       <c r="H2521" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2522">
+      <c r="A2522" s="1" t="n">
+        <v>45989.691712963</v>
+      </c>
+      <c r="B2522" t="n">
+        <v>116415</v>
+      </c>
+      <c r="C2522" t="n">
+        <v>17.4599990844727</v>
+      </c>
+      <c r="D2522" t="n">
+        <v>16.9599990844727</v>
+      </c>
+      <c r="E2522" t="n">
+        <v>17.4599990844727</v>
+      </c>
+      <c r="F2522" t="n">
+        <v>17.3799991607666</v>
+      </c>
+      <c r="G2522" t="s">
+        <v>1645</v>
+      </c>
+      <c r="H2522" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CEM.MI.xlsx
+++ b/data/CEM.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70432186126709</t>
+    <t xml:space="preserve">4.70432090759277</t>
   </si>
   <si>
     <t xml:space="preserve">CEM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68036031723022</t>
+    <t xml:space="preserve">4.68036079406738</t>
   </si>
   <si>
     <t xml:space="preserve">4.5565619468689</t>
@@ -53,28 +53,28 @@
     <t xml:space="preserve">4.48867321014404</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32893371582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22110891342163</t>
+    <t xml:space="preserve">4.32893323898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22110986709595</t>
   </si>
   <si>
     <t xml:space="preserve">4.3249397277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28899812698364</t>
+    <t xml:space="preserve">4.28899908065796</t>
   </si>
   <si>
     <t xml:space="preserve">4.29299259185791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06137037277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93597507476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97431302070618</t>
+    <t xml:space="preserve">4.06137084960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93597555160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97431325912476</t>
   </si>
   <si>
     <t xml:space="preserve">3.67560029029846</t>
@@ -86,43 +86,43 @@
     <t xml:space="preserve">3.94875431060791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88006615638733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9168062210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87846946716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74588537216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93437838554382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87367677688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73789858818054</t>
+    <t xml:space="preserve">3.88006711006165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91680645942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87846922874451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74588584899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93437814712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87367701530457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73789882659912</t>
   </si>
   <si>
     <t xml:space="preserve">3.57815957069397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59892511367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61969137191772</t>
+    <t xml:space="preserve">3.59892559051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6196916103363</t>
   </si>
   <si>
     <t xml:space="preserve">3.35133004188538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15005826950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25069403648376</t>
+    <t xml:space="preserve">3.15005850791931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25069379806519</t>
   </si>
   <si>
     <t xml:space="preserve">3.13088965415955</t>
@@ -131,61 +131,61 @@
     <t xml:space="preserve">3.20916175842285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44238090515137</t>
+    <t xml:space="preserve">3.44238114356995</t>
   </si>
   <si>
     <t xml:space="preserve">3.36251139640808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47592616081238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5541980266571</t>
+    <t xml:space="preserve">3.47592663764954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55419898033142</t>
   </si>
   <si>
     <t xml:space="preserve">3.34653759002686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39126443862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36730360984802</t>
+    <t xml:space="preserve">3.39126396179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3673038482666</t>
   </si>
   <si>
     <t xml:space="preserve">3.2395122051239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29222631454468</t>
+    <t xml:space="preserve">3.29222655296326</t>
   </si>
   <si>
     <t xml:space="preserve">3.40244650840759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58614659309387</t>
+    <t xml:space="preserve">3.58614587783813</t>
   </si>
   <si>
     <t xml:space="preserve">3.63406801223755</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55579566955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64365196228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56058812141418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52065324783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4982898235321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52544546127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54940581321716</t>
+    <t xml:space="preserve">3.55579590797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64365243911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56058740615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52065300941467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49829006195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52544498443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54940629005432</t>
   </si>
   <si>
     <t xml:space="preserve">3.75227522850037</t>
@@ -194,52 +194,52 @@
     <t xml:space="preserve">3.61330199241638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75387263298035</t>
+    <t xml:space="preserve">3.75387215614319</t>
   </si>
   <si>
     <t xml:space="preserve">3.83214473724365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6708083152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70754885673523</t>
+    <t xml:space="preserve">3.67080783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70754790306091</t>
   </si>
   <si>
     <t xml:space="preserve">3.6580286026001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51745843887329</t>
+    <t xml:space="preserve">3.51745867729187</t>
   </si>
   <si>
     <t xml:space="preserve">3.57017230987549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50947141647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54301643371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57975721359253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45196604728699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4104335308075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37529063224792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60052251815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48551058769226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54461455345154</t>
+    <t xml:space="preserve">3.50947117805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5430166721344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57975673675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45196533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41043329238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37529039382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60052275657654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48551034927368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54461407661438</t>
   </si>
   <si>
     <t xml:space="preserve">3.59573078155518</t>
@@ -248,100 +248,100 @@
     <t xml:space="preserve">3.77943015098572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74428772926331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85770273208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73949575424194</t>
+    <t xml:space="preserve">3.74428820610046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8577024936676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7394962310791</t>
   </si>
   <si>
     <t xml:space="preserve">3.74907970428467</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70595097541809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69317197799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67719793319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79700207710266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.666015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70115852355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6260814666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67400288581848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64205479621887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53023719787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45835518836975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47432851791382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53193736076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62187027931213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7575888633728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76085877418518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87531971931458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88349556922913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7772102355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75431799888611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7052640914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66929006576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59734344482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5842616558075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55646395683289</t>
+    <t xml:space="preserve">3.70595073699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69317150115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67719769477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79700255393982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6660168170929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70115900039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62608051300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67400312423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64205455780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53023767471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45835494995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47432899475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53193712234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62187051773071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75758814811707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76085805892944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.875319480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88349604606628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77720999717712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75431776046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70526361465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66929030418396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59734320640564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58426189422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55646443367004</t>
   </si>
   <si>
     <t xml:space="preserve">3.38640856742859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31119132041931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29810953140259</t>
+    <t xml:space="preserve">3.31119108200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29810929298401</t>
   </si>
   <si>
     <t xml:space="preserve">3.19673037528992</t>
@@ -350,19 +350,19 @@
     <t xml:space="preserve">3.1591215133667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00705194473267</t>
+    <t xml:space="preserve">3.00705170631409</t>
   </si>
   <si>
     <t xml:space="preserve">3.15421605110168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0348494052887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22289276123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35207009315491</t>
+    <t xml:space="preserve">3.03484916687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22289252281189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35206985473633</t>
   </si>
   <si>
     <t xml:space="preserve">3.10679650306702</t>
@@ -374,193 +374,193 @@
     <t xml:space="preserve">2.82064414024353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84026575088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9351053237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04302525520325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95799708366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79611659049988</t>
+    <t xml:space="preserve">2.84026598930359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93510508537292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04302549362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9579975605011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79611706733704</t>
   </si>
   <si>
     <t xml:space="preserve">2.76341366767883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76831889152527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84844160079956</t>
+    <t xml:space="preserve">2.76831865310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84844183921814</t>
   </si>
   <si>
     <t xml:space="preserve">2.87787461280823</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04138994216919</t>
+    <t xml:space="preserve">3.04139041900635</t>
   </si>
   <si>
     <t xml:space="preserve">3.00051116943359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21144652366638</t>
+    <t xml:space="preserve">3.2114462852478</t>
   </si>
   <si>
     <t xml:space="preserve">3.13295888900757</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07572841644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97434878349304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10843181610107</t>
+    <t xml:space="preserve">3.07572865486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97434902191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1084315776825</t>
   </si>
   <si>
     <t xml:space="preserve">2.97598433494568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92856454849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17547273635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18037867546082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15585112571716</t>
+    <t xml:space="preserve">2.92856407165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1754732131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18037819862366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15585064888</t>
   </si>
   <si>
     <t xml:space="preserve">3.18855404853821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09862041473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12151312828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02503871917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11660766601562</t>
+    <t xml:space="preserve">3.09862065315247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12151288986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02503824234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11660718917847</t>
   </si>
   <si>
     <t xml:space="preserve">3.23760914802551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28012299537659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32263708114624</t>
+    <t xml:space="preserve">3.28012251853943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32263731956482</t>
   </si>
   <si>
     <t xml:space="preserve">3.43546271324158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40602970123291</t>
+    <t xml:space="preserve">3.40603017807007</t>
   </si>
   <si>
     <t xml:space="preserve">3.46653032302856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43709802627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44854402542114</t>
+    <t xml:space="preserve">3.43709778785706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44854426383972</t>
   </si>
   <si>
     <t xml:space="preserve">3.67910099029541</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64639830589294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71834468841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69545221328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74450778961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8524272441864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80827879905701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82299518585205</t>
+    <t xml:space="preserve">3.64639759063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71834444999695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69545269012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74450707435608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85242772102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80827856063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82299470901489</t>
   </si>
   <si>
     <t xml:space="preserve">3.80337262153625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7428719997406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62350606918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56627535820007</t>
+    <t xml:space="preserve">3.74287223815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62350583076477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56627559661865</t>
   </si>
   <si>
     <t xml:space="preserve">3.47470664978027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51558566093445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65947890281677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60551881790161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54501819610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64803338050842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64476227760315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38804316520691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48288249969482</t>
+    <t xml:space="preserve">3.51558542251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65947914123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60551905632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54501843452454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64803266525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64476251602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38804364204407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48288226127625</t>
   </si>
   <si>
     <t xml:space="preserve">3.45344948768616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43382716178894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50740909576416</t>
+    <t xml:space="preserve">3.43382740020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50740957260132</t>
   </si>
   <si>
     <t xml:space="preserve">3.56464052200317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55482912063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56300449371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48451733589172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54338312149048</t>
+    <t xml:space="preserve">3.55482864379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56300473213196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4845175743103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54338335990906</t>
   </si>
   <si>
     <t xml:space="preserve">3.62514090538025</t>
@@ -569,55 +569,55 @@
     <t xml:space="preserve">3.59080290794373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64149284362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68891191482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66111469268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6872763633728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53684258460999</t>
+    <t xml:space="preserve">3.64149236679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68891215324402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66111397743225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68727684020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53684234619141</t>
   </si>
   <si>
     <t xml:space="preserve">3.63004636764526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63822174072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4387321472168</t>
+    <t xml:space="preserve">3.63822269439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43873286247253</t>
   </si>
   <si>
     <t xml:space="preserve">3.417475938797</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41911125183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33571815490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37169194221497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27521777153015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22125697135925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20981168746948</t>
+    <t xml:space="preserve">3.41911149024963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33571791648865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37169146537781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27521753311157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22125744819641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2098114490509</t>
   </si>
   <si>
     <t xml:space="preserve">3.17710828781128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21308159828186</t>
+    <t xml:space="preserve">3.21308183670044</t>
   </si>
   <si>
     <t xml:space="preserve">3.14767503738403</t>
@@ -635,70 +635,70 @@
     <t xml:space="preserve">2.95309162139893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91875338554382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96453785896301</t>
+    <t xml:space="preserve">2.9187536239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96453762054443</t>
   </si>
   <si>
     <t xml:space="preserve">2.96780824661255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95636177062988</t>
+    <t xml:space="preserve">2.95636200904846</t>
   </si>
   <si>
     <t xml:space="preserve">3.04793095588684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17220282554626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18691897392273</t>
+    <t xml:space="preserve">3.17220258712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18691921234131</t>
   </si>
   <si>
     <t xml:space="preserve">3.31936645507812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2343385219574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48778796195984</t>
+    <t xml:space="preserve">3.23433876037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48778748512268</t>
   </si>
   <si>
     <t xml:space="preserve">3.45181441307068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49923467636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57281565666199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45017910003662</t>
+    <t xml:space="preserve">3.49923396110535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57281541824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4501793384552</t>
   </si>
   <si>
     <t xml:space="preserve">3.61369466781616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67746639251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58916783332825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70362830162048</t>
+    <t xml:space="preserve">3.67746615409851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58916759490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70362901687622</t>
   </si>
   <si>
     <t xml:space="preserve">3.4861524105072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33244824409485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28666400909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22943305969238</t>
+    <t xml:space="preserve">3.33244800567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28666377067566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22943353652954</t>
   </si>
   <si>
     <t xml:space="preserve">3.27031230926514</t>
@@ -707,19 +707,19 @@
     <t xml:space="preserve">3.24741983413696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23106813430786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23270320892334</t>
+    <t xml:space="preserve">3.23106837272644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23270344734192</t>
   </si>
   <si>
     <t xml:space="preserve">3.26213622093201</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27685260772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23597359657288</t>
+    <t xml:space="preserve">3.27685284614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2359733581543</t>
   </si>
   <si>
     <t xml:space="preserve">4.0012264251709</t>
@@ -728,28 +728,28 @@
     <t xml:space="preserve">4.04701089859009</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12876892089844</t>
+    <t xml:space="preserve">4.1287693977356</t>
   </si>
   <si>
     <t xml:space="preserve">4.16964817047119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17782354354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06336307525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95707726478577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19417572021484</t>
+    <t xml:space="preserve">4.17782306671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06336259841919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9570779800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19417524337769</t>
   </si>
   <si>
     <t xml:space="preserve">4.28410863876343</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34542751312256</t>
+    <t xml:space="preserve">4.34542655944824</t>
   </si>
   <si>
     <t xml:space="preserve">4.47215127944946</t>
@@ -758,13 +758,13 @@
     <t xml:space="preserve">4.43944835662842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41083288192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41492223739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37404203414917</t>
+    <t xml:space="preserve">4.41083383560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41492128372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37404155731201</t>
   </si>
   <si>
     <t xml:space="preserve">4.26775693893433</t>
@@ -773,10 +773,10 @@
     <t xml:space="preserve">4.39039373397827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36177825927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3781304359436</t>
+    <t xml:space="preserve">4.3617787361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37813091278076</t>
   </si>
   <si>
     <t xml:space="preserve">4.38630628585815</t>
@@ -785,40 +785,40 @@
     <t xml:space="preserve">4.56208562850952</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42718458175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3290753364563</t>
+    <t xml:space="preserve">4.42718505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32907485961914</t>
   </si>
   <si>
     <t xml:space="preserve">4.2554931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25140523910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30046033859253</t>
+    <t xml:space="preserve">4.25140571594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30046129226685</t>
   </si>
   <si>
     <t xml:space="preserve">4.34951543807983</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24323034286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24731779098511</t>
+    <t xml:space="preserve">4.24322986602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24731826782227</t>
   </si>
   <si>
     <t xml:space="preserve">4.21052742004395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14512014389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10424089431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22279024124146</t>
+    <t xml:space="preserve">4.14512062072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10424184799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22279071807861</t>
   </si>
   <si>
     <t xml:space="preserve">4.40674495697021</t>
@@ -827,70 +827,70 @@
     <t xml:space="preserve">4.36586713790894</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27593374252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30454921722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28002166748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44762420654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52938270568848</t>
+    <t xml:space="preserve">4.27593326568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3045482635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28002119064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44762468338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52938222885132</t>
   </si>
   <si>
     <t xml:space="preserve">4.51711845397949</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52120590209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68063402175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66019439697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71333742141724</t>
+    <t xml:space="preserve">4.52120637893677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68063449859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66019487380981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71333694458008</t>
   </si>
   <si>
     <t xml:space="preserve">4.73377656936646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81962203979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81144666671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65201902389526</t>
+    <t xml:space="preserve">4.81962156295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81144714355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65201950073242</t>
   </si>
   <si>
     <t xml:space="preserve">4.34133911132812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33725166320801</t>
+    <t xml:space="preserve">4.33725118637085</t>
   </si>
   <si>
     <t xml:space="preserve">4.25958108901978</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40383386611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44966411590576</t>
+    <t xml:space="preserve">4.40383434295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44966459274292</t>
   </si>
   <si>
     <t xml:space="preserve">4.41633367538452</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37467050552368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36633729934692</t>
+    <t xml:space="preserve">4.37467002868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36633777618408</t>
   </si>
   <si>
     <t xml:space="preserve">4.30384206771851</t>
@@ -899,43 +899,43 @@
     <t xml:space="preserve">4.27467775344849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25801181793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31634092330933</t>
+    <t xml:space="preserve">4.25801229476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31634140014648</t>
   </si>
   <si>
     <t xml:space="preserve">4.26634502410889</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20801591873169</t>
+    <t xml:space="preserve">4.20801639556885</t>
   </si>
   <si>
     <t xml:space="preserve">4.33300590515137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37050342559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34550619125366</t>
+    <t xml:space="preserve">4.37050294876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34550523757935</t>
   </si>
   <si>
     <t xml:space="preserve">4.39133501052856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29967546463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4288330078125</t>
+    <t xml:space="preserve">4.29967498779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42883205413818</t>
   </si>
   <si>
     <t xml:space="preserve">4.39966917037964</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39550256729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38300275802612</t>
+    <t xml:space="preserve">4.39550161361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38300371170044</t>
   </si>
   <si>
     <t xml:space="preserve">4.46633005142212</t>
@@ -944,13 +944,13 @@
     <t xml:space="preserve">4.48299551010132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56632280349731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40800094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34967184066772</t>
+    <t xml:space="preserve">4.56632232666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40800046920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34967136383057</t>
   </si>
   <si>
     <t xml:space="preserve">4.69131326675415</t>
@@ -959,13 +959,13 @@
     <t xml:space="preserve">4.58298778533936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85380029678345</t>
+    <t xml:space="preserve">4.85379981994629</t>
   </si>
   <si>
     <t xml:space="preserve">4.99962282180786</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0579514503479</t>
+    <t xml:space="preserve">5.05795192718506</t>
   </si>
   <si>
     <t xml:space="preserve">5.10794830322266</t>
@@ -986,25 +986,25 @@
     <t xml:space="preserve">5.30376672744751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29960107803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34542894363403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30793237686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22877264022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29126739501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29543447494507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16211128234863</t>
+    <t xml:space="preserve">5.29959964752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34542942047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30793285369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22877216339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29126787185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29543495178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16211080551147</t>
   </si>
   <si>
     <t xml:space="preserve">5.01628828048706</t>
@@ -1013,34 +1013,34 @@
     <t xml:space="preserve">5.05378580093384</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12461376190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20377445220947</t>
+    <t xml:space="preserve">5.1246132850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20377397537231</t>
   </si>
   <si>
     <t xml:space="preserve">5.07461738586426</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03295421600342</t>
+    <t xml:space="preserve">5.0329532623291</t>
   </si>
   <si>
     <t xml:space="preserve">4.95795917510986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9912896156311</t>
+    <t xml:space="preserve">4.99129009246826</t>
   </si>
   <si>
     <t xml:space="preserve">4.96212577819824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90796327590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94129371643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89129781723022</t>
+    <t xml:space="preserve">4.90796375274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94129419326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89129734039307</t>
   </si>
   <si>
     <t xml:space="preserve">4.90379667282104</t>
@@ -1052,10 +1052,10 @@
     <t xml:space="preserve">4.9454607963562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91629600524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02462100982666</t>
+    <t xml:space="preserve">4.91629505157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02462148666382</t>
   </si>
   <si>
     <t xml:space="preserve">5.04961919784546</t>
@@ -1070,31 +1070,31 @@
     <t xml:space="preserve">5.23293876647949</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17877626419067</t>
+    <t xml:space="preserve">5.17877674102783</t>
   </si>
   <si>
     <t xml:space="preserve">5.1329460144043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33293151855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26627016067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22460603713989</t>
+    <t xml:space="preserve">5.33293104171753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26626920700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22460651397705</t>
   </si>
   <si>
     <t xml:space="preserve">5.58291244506836</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68707132339478</t>
+    <t xml:space="preserve">5.68707036972046</t>
   </si>
   <si>
     <t xml:space="preserve">6.00371360778809</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80789518356323</t>
+    <t xml:space="preserve">5.80789470672607</t>
   </si>
   <si>
     <t xml:space="preserve">6.07454204559326</t>
@@ -1103,28 +1103,28 @@
     <t xml:space="preserve">6.01621294021606</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16620206832886</t>
+    <t xml:space="preserve">6.1662015914917</t>
   </si>
   <si>
     <t xml:space="preserve">5.89122200012207</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94121885299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96621656417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03287839889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9953818321228</t>
+    <t xml:space="preserve">5.94121837615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96621608734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03287792205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99538135528564</t>
   </si>
   <si>
     <t xml:space="preserve">5.97038316726685</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91622018814087</t>
+    <t xml:space="preserve">5.91622066497803</t>
   </si>
   <si>
     <t xml:space="preserve">5.86205768585205</t>
@@ -1136,40 +1136,40 @@
     <t xml:space="preserve">5.89955520629883</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90372180938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87455749511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84539270401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00788021087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98288202285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03704500198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0912070274353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02871179580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99954700469971</t>
+    <t xml:space="preserve">5.90372085571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87455701828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84539222717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00788068771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98288154602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03704404830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09120750427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0287127494812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99954652786255</t>
   </si>
   <si>
     <t xml:space="preserve">6.04954385757446</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07870817184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29119253158569</t>
+    <t xml:space="preserve">6.07870769500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29119205474854</t>
   </si>
   <si>
     <t xml:space="preserve">6.1745343208313</t>
@@ -1178,16 +1178,16 @@
     <t xml:space="preserve">6.19953298568726</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0828742980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.245361328125</t>
+    <t xml:space="preserve">6.08287477493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24536228179932</t>
   </si>
   <si>
     <t xml:space="preserve">6.21203136444092</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02454566955566</t>
+    <t xml:space="preserve">6.02454614639282</t>
   </si>
   <si>
     <t xml:space="preserve">6.09954023361206</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">6.18286657333374</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2078652381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22036409378052</t>
+    <t xml:space="preserve">6.20786476135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22036457061768</t>
   </si>
   <si>
     <t xml:space="preserve">6.14537000656128</t>
@@ -1211,19 +1211,19 @@
     <t xml:space="preserve">5.94538545608521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01204681396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02037954330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11620569229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06204319000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04121065139771</t>
+    <t xml:space="preserve">6.012047290802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02037906646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11620473861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06204271316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04121160507202</t>
   </si>
   <si>
     <t xml:space="preserve">6.1495361328125</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">6.09537363052368</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35785388946533</t>
+    <t xml:space="preserve">6.35785436630249</t>
   </si>
   <si>
     <t xml:space="preserve">6.2245306968689</t>
@@ -1244,13 +1244,13 @@
     <t xml:space="preserve">6.58283710479736</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61616802215576</t>
+    <t xml:space="preserve">6.6161675453186</t>
   </si>
   <si>
     <t xml:space="preserve">6.57450437545776</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50784254074097</t>
+    <t xml:space="preserve">6.50784206390381</t>
   </si>
   <si>
     <t xml:space="preserve">6.49950981140137</t>
@@ -1259,40 +1259,40 @@
     <t xml:space="preserve">6.65783071517944</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74115896224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5911693572998</t>
+    <t xml:space="preserve">6.7411584854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59116888046265</t>
   </si>
   <si>
     <t xml:space="preserve">6.62449979782104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63283348083496</t>
+    <t xml:space="preserve">6.63283395767212</t>
   </si>
   <si>
     <t xml:space="preserve">6.7078275680542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52450847625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51617527008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6661639213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54950571060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44951343536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29952478408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2328634262085</t>
+    <t xml:space="preserve">6.52450752258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51617622375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66616439819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54950666427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44951295852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29952430725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23286294937134</t>
   </si>
   <si>
     <t xml:space="preserve">5.90788793563843</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">5.93288564682007</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53284025192261</t>
+    <t xml:space="preserve">6.53284120559692</t>
   </si>
   <si>
     <t xml:space="preserve">6.26619386672974</t>
@@ -1313,34 +1313,34 @@
     <t xml:space="preserve">6.33285570144653</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14120292663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15786838531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06620979309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94955062866211</t>
+    <t xml:space="preserve">6.1412034034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1578688621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06620931625366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94955158233643</t>
   </si>
   <si>
     <t xml:space="preserve">6.13287115097046</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0578761100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88289022445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84955978393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81622838973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72456789016724</t>
+    <t xml:space="preserve">6.05787658691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88288974761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84955930709839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81622791290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72456836700439</t>
   </si>
   <si>
     <t xml:space="preserve">5.75789880752563</t>
@@ -1352,40 +1352,40 @@
     <t xml:space="preserve">5.6829047203064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82456016540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86622381210327</t>
+    <t xml:space="preserve">5.82455968856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86622428894043</t>
   </si>
   <si>
     <t xml:space="preserve">5.77456426620483</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78289651870728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79122972488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6329083442688</t>
+    <t xml:space="preserve">5.78289699554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79122924804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63290882110596</t>
   </si>
   <si>
     <t xml:space="preserve">5.6498236656189</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68365478515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66673994064331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70057058334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48066759109497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45529460906982</t>
+    <t xml:space="preserve">5.68365526199341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66673946380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70057106018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48066711425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45529413223267</t>
   </si>
   <si>
     <t xml:space="preserve">5.54833078384399</t>
@@ -1394,22 +1394,22 @@
     <t xml:space="preserve">5.5398736000061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74285984039307</t>
+    <t xml:space="preserve">5.74286031723022</t>
   </si>
   <si>
     <t xml:space="preserve">5.58216142654419</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65828132629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70902872085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77669143676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91201686859131</t>
+    <t xml:space="preserve">5.6582818031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70902919769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77669095993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91201639175415</t>
   </si>
   <si>
     <t xml:space="preserve">5.9035587310791</t>
@@ -1424,28 +1424,28 @@
     <t xml:space="preserve">5.78514909744263</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71748685836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81052255630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56524610519409</t>
+    <t xml:space="preserve">5.71748733520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81052303314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56524562835693</t>
   </si>
   <si>
     <t xml:space="preserve">5.50604152679443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69211292266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72594451904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73440217971802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60753488540649</t>
+    <t xml:space="preserve">5.69211387634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72594499588013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73440313339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60753536224365</t>
   </si>
   <si>
     <t xml:space="preserve">5.51449966430664</t>
@@ -1454,43 +1454,43 @@
     <t xml:space="preserve">5.67519760131836</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01351022720337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99659538269043</t>
+    <t xml:space="preserve">6.01351070404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99659442901611</t>
   </si>
   <si>
     <t xml:space="preserve">5.81898069381714</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75977563858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80206537246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79360723495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.886643409729</t>
+    <t xml:space="preserve">5.75977516174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80206489562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79360675811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88664293289185</t>
   </si>
   <si>
     <t xml:space="preserve">5.8781852722168</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92893266677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85281181335449</t>
+    <t xml:space="preserve">5.92893218994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85281229019165</t>
   </si>
   <si>
     <t xml:space="preserve">5.76823377609253</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82743787765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83589649200439</t>
+    <t xml:space="preserve">5.82743883132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83589696884155</t>
   </si>
   <si>
     <t xml:space="preserve">5.42992115020752</t>
@@ -1499,49 +1499,49 @@
     <t xml:space="preserve">5.38763236999512</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33688497543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26076459884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30305337905884</t>
+    <t xml:space="preserve">5.33688449859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26076412200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.303053855896</t>
   </si>
   <si>
     <t xml:space="preserve">5.43837881088257</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46375274658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44683647155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35380029678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3707160949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22693252563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14235544204712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11698198318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24384927749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13389778137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26922273635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25230693817139</t>
+    <t xml:space="preserve">5.46375179290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44683599472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35379981994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37071561813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22693347930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14235496520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11698150634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24384880065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13389682769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26922178268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25230646133423</t>
   </si>
   <si>
     <t xml:space="preserve">5.21001720428467</t>
@@ -1553,16 +1553,16 @@
     <t xml:space="preserve">5.28613758087158</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31996870040894</t>
+    <t xml:space="preserve">5.31996917724609</t>
   </si>
   <si>
     <t xml:space="preserve">5.29459571838379</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48912572860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3284273147583</t>
+    <t xml:space="preserve">5.48912477493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32842779159546</t>
   </si>
   <si>
     <t xml:space="preserve">5.16772842407227</t>
@@ -1571,19 +1571,19 @@
     <t xml:space="preserve">5.09160852432251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17618560791016</t>
+    <t xml:space="preserve">5.17618608474731</t>
   </si>
   <si>
     <t xml:space="preserve">5.10852384567261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91399335861206</t>
+    <t xml:space="preserve">4.91399383544922</t>
   </si>
   <si>
     <t xml:space="preserve">4.60105466842651</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49956083297729</t>
+    <t xml:space="preserve">4.49956130981445</t>
   </si>
   <si>
     <t xml:space="preserve">4.567223072052</t>
@@ -1592,13 +1592,13 @@
     <t xml:space="preserve">4.38115072250366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5418496131897</t>
+    <t xml:space="preserve">4.54185009002686</t>
   </si>
   <si>
     <t xml:space="preserve">4.5249342918396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61797046661377</t>
+    <t xml:space="preserve">4.61796951293945</t>
   </si>
   <si>
     <t xml:space="preserve">4.46572923660278</t>
@@ -1607,16 +1607,16 @@
     <t xml:space="preserve">4.27119970321655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14433193206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22045230865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09358596801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20353698730469</t>
+    <t xml:space="preserve">4.14433240890503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22045183181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09358549118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20353651046753</t>
   </si>
   <si>
     <t xml:space="preserve">4.15701866149902</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">4.53339195251465</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59259653091431</t>
+    <t xml:space="preserve">4.59259700775146</t>
   </si>
   <si>
     <t xml:space="preserve">4.60951232910156</t>
@@ -1640,13 +1640,13 @@
     <t xml:space="preserve">4.41498231887817</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49110269546509</t>
+    <t xml:space="preserve">4.49110221862793</t>
   </si>
   <si>
     <t xml:space="preserve">4.42344045639038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43189764022827</t>
+    <t xml:space="preserve">4.43189811706543</t>
   </si>
   <si>
     <t xml:space="preserve">4.29657316207886</t>
@@ -1664,7 +1664,7 @@
     <t xml:space="preserve">4.08512735366821</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10627222061157</t>
+    <t xml:space="preserve">4.10627174377441</t>
   </si>
   <si>
     <t xml:space="preserve">4.15278959274292</t>
@@ -1673,28 +1673,28 @@
     <t xml:space="preserve">4.2373685836792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21622323989868</t>
+    <t xml:space="preserve">4.21622371673584</t>
   </si>
   <si>
     <t xml:space="preserve">4.16124773025513</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10204362869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03860950469971</t>
+    <t xml:space="preserve">4.10204315185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03860998153687</t>
   </si>
   <si>
     <t xml:space="preserve">4.30503082275391</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2542839050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14010286331177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05129623413086</t>
+    <t xml:space="preserve">4.25428342819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14010334014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0512957572937</t>
   </si>
   <si>
     <t xml:space="preserve">4.14856147766113</t>
@@ -1706,10 +1706,10 @@
     <t xml:space="preserve">4.0343804359436</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94557332992554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35577726364136</t>
+    <t xml:space="preserve">3.94557309150696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35577774047852</t>
   </si>
   <si>
     <t xml:space="preserve">4.31348848342896</t>
@@ -1721,7 +1721,7 @@
     <t xml:space="preserve">4.65180110931396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79558420181274</t>
+    <t xml:space="preserve">4.7955846786499</t>
   </si>
   <si>
     <t xml:space="preserve">4.78712606430054</t>
@@ -1733,22 +1733,22 @@
     <t xml:space="preserve">4.86324691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90553569793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88862037658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95628356933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00703048706055</t>
+    <t xml:space="preserve">4.90553665161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88862085342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95628261566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00703001022339</t>
   </si>
   <si>
     <t xml:space="preserve">5.01548767089844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03240299224854</t>
+    <t xml:space="preserve">5.03240346908569</t>
   </si>
   <si>
     <t xml:space="preserve">5.057776927948</t>
@@ -1757,25 +1757,25 @@
     <t xml:space="preserve">4.99011421203613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97319841384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20155954360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12543964385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1592698097229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21847534179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3453426361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27767992019653</t>
+    <t xml:space="preserve">4.97319793701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20156002044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12543916702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15927028656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21847629547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34534311294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27767944335938</t>
   </si>
   <si>
     <t xml:space="preserve">5.40454769134521</t>
@@ -1787,49 +1787,49 @@
     <t xml:space="preserve">5.47220993041992</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49758386611938</t>
+    <t xml:space="preserve">5.49758338928223</t>
   </si>
   <si>
     <t xml:space="preserve">5.42146301269531</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41300582885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98165655136108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11462450027466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13193273544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01942825317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01077461242676</t>
+    <t xml:space="preserve">5.41300535202026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98165607452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11462545394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13193321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0194296836853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01077508926392</t>
   </si>
   <si>
     <t xml:space="preserve">5.06269979476929</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08866214752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09731674194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1405873298645</t>
+    <t xml:space="preserve">5.08866310119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09731721878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14058780670166</t>
   </si>
   <si>
     <t xml:space="preserve">5.21847581863403</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20116662979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17520380020142</t>
+    <t xml:space="preserve">5.20116710662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17520475387573</t>
   </si>
   <si>
     <t xml:space="preserve">5.2271294593811</t>
@@ -1844,55 +1844,55 @@
     <t xml:space="preserve">5.25309181213379</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33963394165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46079254150391</t>
+    <t xml:space="preserve">5.33963489532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46079301834106</t>
   </si>
   <si>
     <t xml:space="preserve">5.54733419418335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42617559432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33097982406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40886735916138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57329750061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52137279510498</t>
+    <t xml:space="preserve">5.42617607116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.330979347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40886688232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57329654693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52137184143066</t>
   </si>
   <si>
     <t xml:space="preserve">5.47810029983521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64253091812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7636890411377</t>
+    <t xml:space="preserve">5.64252996444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76368951797485</t>
   </si>
   <si>
     <t xml:space="preserve">5.74638080596924</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72907257080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65118455886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7031102180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66849327087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59925889968872</t>
+    <t xml:space="preserve">5.72907209396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65118408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70310974121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66849374771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59925937652588</t>
   </si>
   <si>
     <t xml:space="preserve">5.49540901184082</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">5.45213890075684</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56464290618896</t>
+    <t xml:space="preserve">5.56464242935181</t>
   </si>
   <si>
     <t xml:space="preserve">5.73772668838501</t>
@@ -1910,16 +1910,16 @@
     <t xml:space="preserve">5.51271772384644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24443817138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18385791778564</t>
+    <t xml:space="preserve">5.24443769454956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1838583946228</t>
   </si>
   <si>
     <t xml:space="preserve">5.28770875930786</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19251203536987</t>
+    <t xml:space="preserve">5.19251298904419</t>
   </si>
   <si>
     <t xml:space="preserve">5.12327909469604</t>
@@ -1928,16 +1928,16 @@
     <t xml:space="preserve">5.2704005241394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08000802993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14924144744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16655015945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15789556503296</t>
+    <t xml:space="preserve">5.08000755310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14924097061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16654920578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1578950881958</t>
   </si>
   <si>
     <t xml:space="preserve">5.29636287689209</t>
@@ -1946,13 +1946,13 @@
     <t xml:space="preserve">5.53868055343628</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44348382949829</t>
+    <t xml:space="preserve">5.44348430633545</t>
   </si>
   <si>
     <t xml:space="preserve">5.48675489425659</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40021371841431</t>
+    <t xml:space="preserve">5.40021228790283</t>
   </si>
   <si>
     <t xml:space="preserve">5.36559629440308</t>
@@ -1961,22 +1961,22 @@
     <t xml:space="preserve">5.32232522964478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38290500640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02808284759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04539155960083</t>
+    <t xml:space="preserve">5.38290452957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02808332443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04539108276367</t>
   </si>
   <si>
     <t xml:space="preserve">5.16222333908081</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03933334350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10597085952759</t>
+    <t xml:space="preserve">5.03933382034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10597133636475</t>
   </si>
   <si>
     <t xml:space="preserve">5.15270376205444</t>
@@ -1985,7 +1985,7 @@
     <t xml:space="preserve">5.20895576477051</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27905464172363</t>
+    <t xml:space="preserve">5.27905416488647</t>
   </si>
   <si>
     <t xml:space="preserve">5.34569215774536</t>
@@ -1994,37 +1994,37 @@
     <t xml:space="preserve">5.32665252685547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27991962432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30588245391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26780366897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34742307662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21934032440186</t>
+    <t xml:space="preserve">5.27991914749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3058819770813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26780414581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34742212295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21934080123901</t>
   </si>
   <si>
     <t xml:space="preserve">5.34309530258179</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48502397537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4391565322876</t>
+    <t xml:space="preserve">5.48502445220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43915700912476</t>
   </si>
   <si>
     <t xml:space="preserve">5.31799840927124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51791000366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61656761169434</t>
+    <t xml:space="preserve">5.51791048049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61656808853149</t>
   </si>
   <si>
     <t xml:space="preserve">5.51617956161499</t>
@@ -2033,31 +2033,31 @@
     <t xml:space="preserve">5.46252346038818</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42271375656128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46771574020386</t>
+    <t xml:space="preserve">5.42271327972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46771621704102</t>
   </si>
   <si>
     <t xml:space="preserve">5.44434928894043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46944713592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78099679946899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02331447601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0406231880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04927730560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94456148147583</t>
+    <t xml:space="preserve">5.46944665908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78099727630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02331495285034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04062271118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04927682876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94456195831299</t>
   </si>
   <si>
     <t xml:space="preserve">5.76974678039551</t>
@@ -2066,43 +2066,43 @@
     <t xml:space="preserve">5.78272867202759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75416946411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74118852615356</t>
+    <t xml:space="preserve">5.75416994094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74118804931641</t>
   </si>
   <si>
     <t xml:space="preserve">5.73945760726929</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81042242050171</t>
+    <t xml:space="preserve">5.81042194366455</t>
   </si>
   <si>
     <t xml:space="preserve">5.90561771392822</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9333119392395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94109964370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91080951690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92638826370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85369253158569</t>
+    <t xml:space="preserve">5.93331146240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94109916687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9108099937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92638778686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85369300842285</t>
   </si>
   <si>
     <t xml:space="preserve">5.85628890991211</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68060874938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73253393173218</t>
+    <t xml:space="preserve">5.68060970306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73253440856934</t>
   </si>
   <si>
     <t xml:space="preserve">5.81907606124878</t>
@@ -2111,16 +2111,16 @@
     <t xml:space="preserve">5.90648317337036</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70570659637451</t>
+    <t xml:space="preserve">5.70570611953735</t>
   </si>
   <si>
     <t xml:space="preserve">5.57502794265747</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75590038299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81561422348022</t>
+    <t xml:space="preserve">5.75590085983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81561374664307</t>
   </si>
   <si>
     <t xml:space="preserve">5.7602276802063</t>
@@ -2135,10 +2135,10 @@
     <t xml:space="preserve">5.69791746139526</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69272470474243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62868404388428</t>
+    <t xml:space="preserve">5.69272422790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62868356704712</t>
   </si>
   <si>
     <t xml:space="preserve">5.75936269760132</t>
@@ -2147,25 +2147,25 @@
     <t xml:space="preserve">5.65810775756836</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57243204116821</t>
+    <t xml:space="preserve">5.5724310874939</t>
   </si>
   <si>
     <t xml:space="preserve">5.62522220611572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67282009124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58195114135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.584547996521</t>
+    <t xml:space="preserve">5.6728196144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58195161819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58454751968384</t>
   </si>
   <si>
     <t xml:space="preserve">5.64512634277344</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72561025619507</t>
+    <t xml:space="preserve">5.72561073303223</t>
   </si>
   <si>
     <t xml:space="preserve">5.61483716964722</t>
@@ -2174,25 +2174,25 @@
     <t xml:space="preserve">5.60704851150513</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65291500091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6555118560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75503540039062</t>
+    <t xml:space="preserve">5.65291547775269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65551137924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75503587722778</t>
   </si>
   <si>
     <t xml:space="preserve">5.84071159362793</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00600576400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92811822891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87619352340698</t>
+    <t xml:space="preserve">6.00600671768188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92811870574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87619400024414</t>
   </si>
   <si>
     <t xml:space="preserve">5.71436023712158</t>
@@ -2201,58 +2201,58 @@
     <t xml:space="preserve">5.42184829711914</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36213445663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19510889053345</t>
+    <t xml:space="preserve">5.36213541030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19510841369629</t>
   </si>
   <si>
     <t xml:space="preserve">5.04019927978516</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15443468093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18039751052856</t>
+    <t xml:space="preserve">5.1544337272644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18039655685425</t>
   </si>
   <si>
     <t xml:space="preserve">4.79615116119385</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24358081817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30113077163696</t>
+    <t xml:space="preserve">4.24358129501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30113124847412</t>
   </si>
   <si>
     <t xml:space="preserve">4.30718946456909</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94501090049744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11073923110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9809262752533</t>
+    <t xml:space="preserve">3.94501137733459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11073875427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98092579841614</t>
   </si>
   <si>
     <t xml:space="preserve">3.77452397346497</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89438533782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17564582824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82385301589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9748682975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07006406784058</t>
+    <t xml:space="preserve">3.89438438415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17564535140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82385230064392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97486805915833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07006502151489</t>
   </si>
   <si>
     <t xml:space="preserve">4.27387094497681</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">4.11766195297241</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05665016174316</t>
+    <t xml:space="preserve">4.05665063858032</t>
   </si>
   <si>
     <t xml:space="preserve">4.25699520111084</t>
@@ -2279,16 +2279,16 @@
     <t xml:space="preserve">4.32709407806396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45690631866455</t>
+    <t xml:space="preserve">4.45690727233887</t>
   </si>
   <si>
     <t xml:space="preserve">4.61268186569214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48286962509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62999057769775</t>
+    <t xml:space="preserve">4.48286914825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6299901008606</t>
   </si>
   <si>
     <t xml:space="preserve">4.569411277771</t>
@@ -2297,16 +2297,16 @@
     <t xml:space="preserve">4.57806539535522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5261402130127</t>
+    <t xml:space="preserve">4.52614068984985</t>
   </si>
   <si>
     <t xml:space="preserve">4.50017738342285</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74249505996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76845788955688</t>
+    <t xml:space="preserve">4.74249458312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76845836639404</t>
   </si>
   <si>
     <t xml:space="preserve">4.79442024230957</t>
@@ -2315,10 +2315,10 @@
     <t xml:space="preserve">4.94154167175293</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91557884216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83769178390503</t>
+    <t xml:space="preserve">4.91557836532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83769083023071</t>
   </si>
   <si>
     <t xml:space="preserve">4.58671951293945</t>
@@ -2333,19 +2333,16 @@
     <t xml:space="preserve">4.67326164245605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80307483673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90961170196533</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.8030743598938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73204898834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8829779624939</t>
+    <t xml:space="preserve">4.90961217880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73204946517944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88297700881958</t>
   </si>
   <si>
     <t xml:space="preserve">4.91848993301392</t>
@@ -2357,7 +2354,7 @@
     <t xml:space="preserve">5.22034692764282</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19371223449707</t>
+    <t xml:space="preserve">5.19371175765991</t>
   </si>
   <si>
     <t xml:space="preserve">5.39790964126587</t>
@@ -2366,16 +2363,16 @@
     <t xml:space="preserve">5.44230031967163</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30025005340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52220344543457</t>
+    <t xml:space="preserve">5.30024909973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52220296859741</t>
   </si>
   <si>
     <t xml:space="preserve">5.49556922912598</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60210657119751</t>
+    <t xml:space="preserve">5.60210704803467</t>
   </si>
   <si>
     <t xml:space="preserve">5.72640085220337</t>
@@ -2384,7 +2381,7 @@
     <t xml:space="preserve">5.81518268585205</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63761949539185</t>
+    <t xml:space="preserve">5.63761854171753</t>
   </si>
   <si>
     <t xml:space="preserve">5.30912828445435</t>
@@ -2393,7 +2390,7 @@
     <t xml:space="preserve">5.27361583709717</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23810291290283</t>
+    <t xml:space="preserve">5.23810338973999</t>
   </si>
   <si>
     <t xml:space="preserve">5.55771636962891</t>
@@ -2402,58 +2399,58 @@
     <t xml:space="preserve">5.73527908325195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61098527908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65537548065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68201065063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61986351013184</t>
+    <t xml:space="preserve">5.61098480224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65537595748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68201017379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61986255645752</t>
   </si>
   <si>
     <t xml:space="preserve">5.64649772644043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71752262115479</t>
+    <t xml:space="preserve">5.71752214431763</t>
   </si>
   <si>
     <t xml:space="preserve">5.5843505859375</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56659412384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53108167648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46005725860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35351943969727</t>
+    <t xml:space="preserve">5.56659460067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.531081199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46005630493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35351896286011</t>
   </si>
   <si>
     <t xml:space="preserve">5.42454385757446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41566610336304</t>
+    <t xml:space="preserve">5.41566562652588</t>
   </si>
   <si>
     <t xml:space="preserve">5.31800603866577</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38903188705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29137229919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21146869659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36239719390869</t>
+    <t xml:space="preserve">5.38903141021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29137134552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21146774291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36239671707153</t>
   </si>
   <si>
     <t xml:space="preserve">5.255859375</t>
@@ -2462,16 +2459,16 @@
     <t xml:space="preserve">5.26473712921143</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37127542495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48669052124023</t>
+    <t xml:space="preserve">5.37127494812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48669099807739</t>
   </si>
   <si>
     <t xml:space="preserve">5.59322881698608</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53995990753174</t>
+    <t xml:space="preserve">5.53995943069458</t>
   </si>
   <si>
     <t xml:space="preserve">5.5044469833374</t>
@@ -2483,13 +2480,13 @@
     <t xml:space="preserve">5.34464073181152</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28249359130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20259094238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32688426971436</t>
+    <t xml:space="preserve">5.28249311447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2025899887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32688474655151</t>
   </si>
   <si>
     <t xml:space="preserve">5.3357629776001</t>
@@ -2501,25 +2498,25 @@
     <t xml:space="preserve">5.15819978713989</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13156604766846</t>
+    <t xml:space="preserve">5.13156509399414</t>
   </si>
   <si>
     <t xml:space="preserve">5.16707801818848</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18483448028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02502775192261</t>
+    <t xml:space="preserve">5.18483400344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02502727508545</t>
   </si>
   <si>
     <t xml:space="preserve">4.90073394775391</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61663293838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72317171096802</t>
+    <t xml:space="preserve">4.61663341522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72317123413086</t>
   </si>
   <si>
     <t xml:space="preserve">4.85634279251099</t>
@@ -2531,52 +2528,52 @@
     <t xml:space="preserve">5.00727128982544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89185571670532</t>
+    <t xml:space="preserve">4.89185619354248</t>
   </si>
   <si>
     <t xml:space="preserve">4.98951482772827</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90396356582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01050186157227</t>
+    <t xml:space="preserve">5.90396404266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01050138473511</t>
   </si>
   <si>
     <t xml:space="preserve">6.01937961578369</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99274492263794</t>
+    <t xml:space="preserve">5.9927453994751</t>
   </si>
   <si>
     <t xml:space="preserve">6.09928274154663</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10816144943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35674905776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18806409835815</t>
+    <t xml:space="preserve">6.10816097259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35674858093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.188063621521</t>
   </si>
   <si>
     <t xml:space="preserve">6.24133348464966</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28572368621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32123613357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25021076202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30348062515259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31235790252686</t>
+    <t xml:space="preserve">6.2857232093811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3212366104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25021123886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30347919464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31235837936401</t>
   </si>
   <si>
     <t xml:space="preserve">6.11703872680664</t>
@@ -2588,22 +2585,22 @@
     <t xml:space="preserve">6.06376981735229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05489253997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98386669158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96611070632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93947649002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94835424423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92171955108643</t>
+    <t xml:space="preserve">6.05489158630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98386716842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96610975265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93947601318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94835376739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92172002792358</t>
   </si>
   <si>
     <t xml:space="preserve">5.912841796875</t>
@@ -2612,34 +2609,34 @@
     <t xml:space="preserve">6.23245477676392</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46328687667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33011436462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27684593200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20582056045532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04601430892944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37450551986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12591743469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21469879150391</t>
+    <t xml:space="preserve">6.46328639984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33011484146118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27684545516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20582008361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04601335525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37450456619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12591695785522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21469831466675</t>
   </si>
   <si>
     <t xml:space="preserve">6.17918586730957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26796770095825</t>
+    <t xml:space="preserve">6.26796722412109</t>
   </si>
   <si>
     <t xml:space="preserve">6.48104286193848</t>
@@ -2651,37 +2648,37 @@
     <t xml:space="preserve">7.01373147964478</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43988227844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54641962051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59968900680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6352014541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68846940994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52866315841675</t>
+    <t xml:space="preserve">7.43988275527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54641914367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59968852996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63520193099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68846988677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52866268157959</t>
   </si>
   <si>
     <t xml:space="preserve">7.31558799743652</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30670881271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18241596221924</t>
+    <t xml:space="preserve">7.30670976638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1824164390564</t>
   </si>
   <si>
     <t xml:space="preserve">7.29783201217651</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13802528381348</t>
+    <t xml:space="preserve">7.13802480697632</t>
   </si>
   <si>
     <t xml:space="preserve">7.04924345016479</t>
@@ -2690,10 +2687,10 @@
     <t xml:space="preserve">7.19129467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21792888641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35109996795654</t>
+    <t xml:space="preserve">7.21792840957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3511004447937</t>
   </si>
   <si>
     <t xml:space="preserve">7.48427295684814</t>
@@ -2702,31 +2699,31 @@
     <t xml:space="preserve">7.59081029891968</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58193254470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65295791625977</t>
+    <t xml:space="preserve">7.58193159103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65295743942261</t>
   </si>
   <si>
     <t xml:space="preserve">7.5109076499939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45763874053955</t>
+    <t xml:space="preserve">7.45763826370239</t>
   </si>
   <si>
     <t xml:space="preserve">7.17353773117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61744451522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67959117889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76837301254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93705749511719</t>
+    <t xml:space="preserve">7.61744499206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6795916557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76837253570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93705892562866</t>
   </si>
   <si>
     <t xml:space="preserve">8.19452476501465</t>
@@ -2735,79 +2732,79 @@
     <t xml:space="preserve">8.09686470031738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99920558929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17676734924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20340251922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99032735824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08798503875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05247497558594</t>
+    <t xml:space="preserve">7.99920606613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17676830291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20340156555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99032688140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08798599243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05247402191162</t>
   </si>
   <si>
     <t xml:space="preserve">8.0435962677002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00808238983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0791072845459</t>
+    <t xml:space="preserve">8.00808334350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07910919189453</t>
   </si>
   <si>
     <t xml:space="preserve">8.14125537872314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07023143768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15013313293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38984394073486</t>
+    <t xml:space="preserve">8.07022953033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1501350402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38984298706055</t>
   </si>
   <si>
     <t xml:space="preserve">8.23891448974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44311141967773</t>
+    <t xml:space="preserve">8.44311332702637</t>
   </si>
   <si>
     <t xml:space="preserve">8.38096523284912</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51413822174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43423461914062</t>
+    <t xml:space="preserve">8.51413726806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43423366546631</t>
   </si>
   <si>
     <t xml:space="preserve">8.64730930328369</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42535495758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47014331817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60530567169189</t>
+    <t xml:space="preserve">8.42535591125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47014427185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60530662536621</t>
   </si>
   <si>
     <t xml:space="preserve">8.43410110473633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4160795211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37102603912354</t>
+    <t xml:space="preserve">8.41608047485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37102508544922</t>
   </si>
   <si>
     <t xml:space="preserve">8.56025218963623</t>
@@ -2816,7 +2813,10 @@
     <t xml:space="preserve">8.31696033477783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42509078979492</t>
+    <t xml:space="preserve">8.42508983612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44311237335205</t>
   </si>
   <si>
     <t xml:space="preserve">8.62332725524902</t>
@@ -2825,16 +2825,16 @@
     <t xml:space="preserve">8.75848960876465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6593713760376</t>
+    <t xml:space="preserve">8.65937042236328</t>
   </si>
   <si>
     <t xml:space="preserve">8.70442485809326</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7404670715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68640232086182</t>
+    <t xml:space="preserve">8.74046802520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68640327453613</t>
   </si>
   <si>
     <t xml:space="preserve">8.47915554046631</t>
@@ -2846,13 +2846,13 @@
     <t xml:space="preserve">8.51519775390625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53321933746338</t>
+    <t xml:space="preserve">8.5332202911377</t>
   </si>
   <si>
     <t xml:space="preserve">8.46113395690918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27190685272217</t>
+    <t xml:space="preserve">8.27190780639648</t>
   </si>
   <si>
     <t xml:space="preserve">8.10971260070801</t>
@@ -2864,10 +2864,10 @@
     <t xml:space="preserve">8.08268070220947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04663753509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05564785003662</t>
+    <t xml:space="preserve">8.0466365814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05564880371094</t>
   </si>
   <si>
     <t xml:space="preserve">7.95652914047241</t>
@@ -2876,16 +2876,16 @@
     <t xml:space="preserve">8.00158309936523</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74928140640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85740995407104</t>
+    <t xml:space="preserve">7.74928188323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8574104309082</t>
   </si>
   <si>
     <t xml:space="preserve">7.78532457351685</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83938837051392</t>
+    <t xml:space="preserve">7.83938932418823</t>
   </si>
   <si>
     <t xml:space="preserve">7.74027013778687</t>
@@ -2897,10 +2897,10 @@
     <t xml:space="preserve">7.92048597335815</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1727876663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2989387512207</t>
+    <t xml:space="preserve">8.17278861999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29893970489502</t>
   </si>
   <si>
     <t xml:space="preserve">8.16377735137939</t>
@@ -2909,16 +2909,16 @@
     <t xml:space="preserve">8.21784210205078</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96554040908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60510730743408</t>
+    <t xml:space="preserve">7.96553993225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60510778427124</t>
   </si>
   <si>
     <t xml:space="preserve">8.07366943359375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.244873046875</t>
+    <t xml:space="preserve">8.24487400054932</t>
   </si>
   <si>
     <t xml:space="preserve">8.12773418426514</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">8.48816585540771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38904857635498</t>
+    <t xml:space="preserve">8.38904762268066</t>
   </si>
   <si>
     <t xml:space="preserve">8.35300445556641</t>
@@ -2942,13 +2942,13 @@
     <t xml:space="preserve">8.63233852386475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23586368560791</t>
+    <t xml:space="preserve">8.23586463928223</t>
   </si>
   <si>
     <t xml:space="preserve">8.30795001983643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64134883880615</t>
+    <t xml:space="preserve">8.64134979248047</t>
   </si>
   <si>
     <t xml:space="preserve">8.77651119232178</t>
@@ -2960,10 +2960,10 @@
     <t xml:space="preserve">8.49717712402344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25388526916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19982051849365</t>
+    <t xml:space="preserve">8.25388622283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19982147216797</t>
   </si>
   <si>
     <t xml:space="preserve">8.03762626647949</t>
@@ -2972,52 +2972,52 @@
     <t xml:space="preserve">7.92949724197388</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98356151580811</t>
+    <t xml:space="preserve">7.98356103897095</t>
   </si>
   <si>
     <t xml:space="preserve">8.01960468292236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8844428062439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56906461715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63214063644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57807636260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55104398727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65917301177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67719507217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72224760055542</t>
+    <t xml:space="preserve">7.88444232940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56906509399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63214111328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57807588577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55104446411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65917253494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67719459533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72224950790405</t>
   </si>
   <si>
     <t xml:space="preserve">7.76730251312256</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71323823928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93850755691528</t>
+    <t xml:space="preserve">7.71323776245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93850898742676</t>
   </si>
   <si>
     <t xml:space="preserve">8.22685241699219</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19081020355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20883083343506</t>
+    <t xml:space="preserve">8.19080924987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20882987976074</t>
   </si>
   <si>
     <t xml:space="preserve">8.38003635406494</t>
@@ -3026,10 +3026,10 @@
     <t xml:space="preserve">8.18179893493652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02861595153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80334520339966</t>
+    <t xml:space="preserve">8.02861499786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80334568023682</t>
   </si>
   <si>
     <t xml:space="preserve">7.69521570205688</t>
@@ -3041,7 +3041,7 @@
     <t xml:space="preserve">7.37983798980713</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33478498458862</t>
+    <t xml:space="preserve">7.33478450775146</t>
   </si>
   <si>
     <t xml:space="preserve">7.37082815170288</t>
@@ -3053,19 +3053,19 @@
     <t xml:space="preserve">7.36181688308716</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35280609130859</t>
+    <t xml:space="preserve">7.35280561447144</t>
   </si>
   <si>
     <t xml:space="preserve">7.4429144859314</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6501612663269</t>
+    <t xml:space="preserve">7.65016222000122</t>
   </si>
   <si>
     <t xml:space="preserve">7.46994638442993</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39786052703857</t>
+    <t xml:space="preserve">7.39786005020142</t>
   </si>
   <si>
     <t xml:space="preserve">7.3257737159729</t>
@@ -3074,7 +3074,7 @@
     <t xml:space="preserve">7.27170848846436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30775213241577</t>
+    <t xml:space="preserve">7.30775165557861</t>
   </si>
   <si>
     <t xml:space="preserve">7.29874181747437</t>
@@ -3086,16 +3086,16 @@
     <t xml:space="preserve">7.54203271865845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64115142822266</t>
+    <t xml:space="preserve">7.64115047454834</t>
   </si>
   <si>
     <t xml:space="preserve">7.62313032150269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53302240371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52401161193848</t>
+    <t xml:space="preserve">7.53302145004272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52401113510132</t>
   </si>
   <si>
     <t xml:space="preserve">7.31676292419434</t>
@@ -3104,7 +3104,7 @@
     <t xml:space="preserve">7.38884925842285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4519248008728</t>
+    <t xml:space="preserve">7.45192527770996</t>
   </si>
   <si>
     <t xml:space="preserve">6.96534204483032</t>
@@ -3113,7 +3113,7 @@
     <t xml:space="preserve">6.92929887771606</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02841711044312</t>
+    <t xml:space="preserve">7.02841806411743</t>
   </si>
   <si>
     <t xml:space="preserve">6.89325571060181</t>
@@ -3122,22 +3122,22 @@
     <t xml:space="preserve">7.01039600372314</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12753629684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11852550506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94732093811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88424444198608</t>
+    <t xml:space="preserve">7.12753582000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11852598190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94732046127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88424491882324</t>
   </si>
   <si>
     <t xml:space="preserve">6.90226650238037</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28071928024292</t>
+    <t xml:space="preserve">7.28071975708008</t>
   </si>
   <si>
     <t xml:space="preserve">7.22665548324585</t>
@@ -3146,22 +3146,22 @@
     <t xml:space="preserve">7.03742837905884</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14555788040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19962215423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00138521194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0734715461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80314826965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74007225036621</t>
+    <t xml:space="preserve">7.14555740356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.199622631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00138568878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07347106933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80314779281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74007177352905</t>
   </si>
   <si>
     <t xml:space="preserve">6.66798639297485</t>
@@ -3170,10 +3170,10 @@
     <t xml:space="preserve">6.3616189956665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59589958190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41568374633789</t>
+    <t xml:space="preserve">6.59590005874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41568422317505</t>
   </si>
   <si>
     <t xml:space="preserve">6.32557582855225</t>
@@ -3185,10 +3185,10 @@
     <t xml:space="preserve">5.85701465606689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83899259567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01019811630249</t>
+    <t xml:space="preserve">5.83899307250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01019859313965</t>
   </si>
   <si>
     <t xml:space="preserve">6.28052139282227</t>
@@ -3197,19 +3197,19 @@
     <t xml:space="preserve">6.09129571914673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14535999298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3526086807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2354679107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46974849700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38865089416504</t>
+    <t xml:space="preserve">6.1453595161438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35260820388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23546838760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46974802017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3886513710022</t>
   </si>
   <si>
     <t xml:space="preserve">6.37062978744507</t>
@@ -3224,7 +3224,7 @@
     <t xml:space="preserve">6.02821969985962</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11832714080811</t>
+    <t xml:space="preserve">6.11832761764526</t>
   </si>
   <si>
     <t xml:space="preserve">6.12733840942383</t>
@@ -3254,7 +3254,7 @@
     <t xml:space="preserve">5.92009019851685</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89305830001831</t>
+    <t xml:space="preserve">5.89305734634399</t>
   </si>
   <si>
     <t xml:space="preserve">5.93811178207397</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">6.10030603408813</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21744680404663</t>
+    <t xml:space="preserve">6.21744632720947</t>
   </si>
   <si>
     <t xml:space="preserve">6.06426286697388</t>
@@ -3275,7 +3275,7 @@
     <t xml:space="preserve">5.9831657409668</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94712257385254</t>
+    <t xml:space="preserve">5.94712209701538</t>
   </si>
   <si>
     <t xml:space="preserve">6.0192084312439</t>
@@ -3284,22 +3284,22 @@
     <t xml:space="preserve">5.99217700958252</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96514415740967</t>
+    <t xml:space="preserve">5.96514368057251</t>
   </si>
   <si>
     <t xml:space="preserve">5.97415494918823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95613384246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08228445053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07327318191528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03723049163818</t>
+    <t xml:space="preserve">5.9561333656311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08228492736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07327365875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03723001480103</t>
   </si>
   <si>
     <t xml:space="preserve">6.04001379013062</t>
@@ -3308,22 +3308,22 @@
     <t xml:space="preserve">5.94737577438354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96590328216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1604437828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28087329864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22529029846191</t>
+    <t xml:space="preserve">5.96590280532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16044425964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28087377548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22528982162476</t>
   </si>
   <si>
     <t xml:space="preserve">6.20676231384277</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17897129058838</t>
+    <t xml:space="preserve">6.17897176742554</t>
   </si>
   <si>
     <t xml:space="preserve">6.29013729095459</t>
@@ -3338,16 +3338,16 @@
     <t xml:space="preserve">6.00295877456665</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81768226623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83620977401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9288477897644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89179277420044</t>
+    <t xml:space="preserve">5.81768274307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83621025085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92884826660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8917932510376</t>
   </si>
   <si>
     <t xml:space="preserve">6.09559679031372</t>
@@ -3359,19 +3359,19 @@
     <t xml:space="preserve">5.95663928985596</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82694578170776</t>
+    <t xml:space="preserve">5.82694625854492</t>
   </si>
   <si>
     <t xml:space="preserve">5.68798828125</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78062677383423</t>
+    <t xml:space="preserve">5.78062629699707</t>
   </si>
   <si>
     <t xml:space="preserve">5.73430776596069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72504377365112</t>
+    <t xml:space="preserve">5.72504425048828</t>
   </si>
   <si>
     <t xml:space="preserve">5.34522676467896</t>
@@ -3386,7 +3386,7 @@
     <t xml:space="preserve">5.75283527374268</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51197576522827</t>
+    <t xml:space="preserve">5.51197528839111</t>
   </si>
   <si>
     <t xml:space="preserve">5.85473728179932</t>
@@ -3395,22 +3395,22 @@
     <t xml:space="preserve">5.55829524993896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71577978134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77136325836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61387825012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66019678115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87326526641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66946125030518</t>
+    <t xml:space="preserve">5.71578073501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77136278152466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61387777328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66019725799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8732647895813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66946077346802</t>
   </si>
   <si>
     <t xml:space="preserve">5.80841875076294</t>
@@ -3419,22 +3419,22 @@
     <t xml:space="preserve">6.0307502746582</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04927825927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86400127410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53976726531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49344778060913</t>
+    <t xml:space="preserve">6.04927778244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86400079727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53976774215698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49344825744629</t>
   </si>
   <si>
     <t xml:space="preserve">5.47492074966431</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37301874160767</t>
+    <t xml:space="preserve">5.37301921844482</t>
   </si>
   <si>
     <t xml:space="preserve">5.39154624938965</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">5.15995073318481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21553325653076</t>
+    <t xml:space="preserve">5.21553373336792</t>
   </si>
   <si>
     <t xml:space="preserve">5.19700622558594</t>
@@ -3461,13 +3461,13 @@
     <t xml:space="preserve">5.25258874893188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38228225708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1321587562561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10436773300171</t>
+    <t xml:space="preserve">5.38228273391724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13215923309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10436820983887</t>
   </si>
   <si>
     <t xml:space="preserve">5.28038024902344</t>
@@ -3479,22 +3479,22 @@
     <t xml:space="preserve">5.2340612411499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08584022521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05804872512817</t>
+    <t xml:space="preserve">5.08583927154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05804824829102</t>
   </si>
   <si>
     <t xml:space="preserve">5.01172924041748</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02099323272705</t>
+    <t xml:space="preserve">5.02099370956421</t>
   </si>
   <si>
     <t xml:space="preserve">5.1784782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04878425598145</t>
+    <t xml:space="preserve">5.0487847328186</t>
   </si>
   <si>
     <t xml:space="preserve">5.15068674087524</t>
@@ -3509,22 +3509,22 @@
     <t xml:space="preserve">4.91909122467041</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97467422485352</t>
+    <t xml:space="preserve">4.97467374801636</t>
   </si>
   <si>
     <t xml:space="preserve">4.96541023254395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22479772567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3359637260437</t>
+    <t xml:space="preserve">5.22479724884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33596324920654</t>
   </si>
   <si>
     <t xml:space="preserve">5.30817174911499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45639276504517</t>
+    <t xml:space="preserve">5.45639324188232</t>
   </si>
   <si>
     <t xml:space="preserve">5.52123928070068</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">5.29890775680542</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46565675735474</t>
+    <t xml:space="preserve">5.46565723419189</t>
   </si>
   <si>
     <t xml:space="preserve">5.56755924224854</t>
@@ -3545,13 +3545,13 @@
     <t xml:space="preserve">5.76209878921509</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90105628967285</t>
+    <t xml:space="preserve">5.90105676651001</t>
   </si>
   <si>
     <t xml:space="preserve">5.91958427429199</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70651626586914</t>
+    <t xml:space="preserve">5.70651578903198</t>
   </si>
   <si>
     <t xml:space="preserve">5.74357128143311</t>
@@ -3563,13 +3563,13 @@
     <t xml:space="preserve">5.63240575790405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54903078079224</t>
+    <t xml:space="preserve">5.54903125762939</t>
   </si>
   <si>
     <t xml:space="preserve">5.64166975021362</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88252878189087</t>
+    <t xml:space="preserve">5.88252830505371</t>
   </si>
   <si>
     <t xml:space="preserve">5.99369478225708</t>
@@ -3578,7 +3578,7 @@
     <t xml:space="preserve">5.98443126678467</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91032028198242</t>
+    <t xml:space="preserve">5.91032075881958</t>
   </si>
   <si>
     <t xml:space="preserve">6.44762229919434</t>
@@ -3587,28 +3587,28 @@
     <t xml:space="preserve">6.74406480789185</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70700883865356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79964828491211</t>
+    <t xml:space="preserve">6.70700931549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79964780807495</t>
   </si>
   <si>
     <t xml:space="preserve">6.82743883132935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79038333892822</t>
+    <t xml:space="preserve">6.79038381576538</t>
   </si>
   <si>
     <t xml:space="preserve">6.89228582382202</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96639633178711</t>
+    <t xml:space="preserve">6.96639680862427</t>
   </si>
   <si>
     <t xml:space="preserve">7.23504734039307</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34621334075928</t>
+    <t xml:space="preserve">7.34621286392212</t>
   </si>
   <si>
     <t xml:space="preserve">7.38326835632324</t>
@@ -3629,7 +3629,7 @@
     <t xml:space="preserve">7.55928087234497</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39253234863281</t>
+    <t xml:space="preserve">7.39253282546997</t>
   </si>
   <si>
     <t xml:space="preserve">7.59633636474609</t>
@@ -3641,25 +3641,25 @@
     <t xml:space="preserve">7.64265584945679</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50369834899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63339138031006</t>
+    <t xml:space="preserve">7.50369882583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63339185714722</t>
   </si>
   <si>
     <t xml:space="preserve">7.62412786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57780885696411</t>
+    <t xml:space="preserve">7.57780933380127</t>
   </si>
   <si>
     <t xml:space="preserve">7.58707237243652</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45737981796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43885135650635</t>
+    <t xml:space="preserve">7.45737934112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43885087966919</t>
   </si>
   <si>
     <t xml:space="preserve">7.08682632446289</t>
@@ -3668,7 +3668,7 @@
     <t xml:space="preserve">7.32768535614014</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10535430908203</t>
+    <t xml:space="preserve">7.10535335540771</t>
   </si>
   <si>
     <t xml:space="preserve">7.18872833251953</t>
@@ -3677,7 +3677,7 @@
     <t xml:space="preserve">7.42032432556152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30915784835815</t>
+    <t xml:space="preserve">7.30915832519531</t>
   </si>
   <si>
     <t xml:space="preserve">7.29063034057617</t>
@@ -3689,7 +3689,7 @@
     <t xml:space="preserve">7.29989433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24431180953979</t>
+    <t xml:space="preserve">7.24431133270264</t>
   </si>
   <si>
     <t xml:space="preserve">7.21651983261108</t>
@@ -3698,7 +3698,7 @@
     <t xml:space="preserve">7.27210235595703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20725631713867</t>
+    <t xml:space="preserve">7.20725584030151</t>
   </si>
   <si>
     <t xml:space="preserve">7.33694934844971</t>
@@ -3707,10 +3707,10 @@
     <t xml:space="preserve">7.31842231750488</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26283931732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12388181686401</t>
+    <t xml:space="preserve">7.26283884048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12388134002686</t>
   </si>
   <si>
     <t xml:space="preserve">7.04977130889893</t>
@@ -3725,7 +3725,7 @@
     <t xml:space="preserve">7.22578382492065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19799184799194</t>
+    <t xml:space="preserve">7.1979923248291</t>
   </si>
   <si>
     <t xml:space="preserve">7.15167284011841</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">7.11461734771729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05903434753418</t>
+    <t xml:space="preserve">7.05903482437134</t>
   </si>
   <si>
     <t xml:space="preserve">7.06857395172119</t>
@@ -3749,34 +3749,34 @@
     <t xml:space="preserve">6.94456434249878</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86824989318848</t>
+    <t xml:space="preserve">6.86825037002563</t>
   </si>
   <si>
     <t xml:space="preserve">6.79193639755249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75377941131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84917163848877</t>
+    <t xml:space="preserve">6.75377893447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84917116165161</t>
   </si>
   <si>
     <t xml:space="preserve">6.99226045608521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95410346984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87778902053833</t>
+    <t xml:space="preserve">6.95410299301147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87778949737549</t>
   </si>
   <si>
     <t xml:space="preserve">6.98272132873535</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96364259719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03041744232178</t>
+    <t xml:space="preserve">6.96364307403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03041696548462</t>
   </si>
   <si>
     <t xml:space="preserve">7.01133871078491</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">6.78239727020264</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7251615524292</t>
+    <t xml:space="preserve">6.72516202926636</t>
   </si>
   <si>
     <t xml:space="preserve">7.00179958343506</t>
@@ -3815,19 +3815,19 @@
     <t xml:space="preserve">7.36429023742676</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28797674179077</t>
+    <t xml:space="preserve">7.28797626495361</t>
   </si>
   <si>
     <t xml:space="preserve">7.29751586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30705499649048</t>
+    <t xml:space="preserve">7.30705451965332</t>
   </si>
   <si>
     <t xml:space="preserve">7.53599691390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57415390014648</t>
+    <t xml:space="preserve">7.57415342330933</t>
   </si>
   <si>
     <t xml:space="preserve">7.66000652313232</t>
@@ -3836,10 +3836,10 @@
     <t xml:space="preserve">7.6981635093689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93664455413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98434066772461</t>
+    <t xml:space="preserve">7.93664407730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98434019088745</t>
   </si>
   <si>
     <t xml:space="preserve">8.18466472625732</t>
@@ -3857,19 +3857,19 @@
     <t xml:space="preserve">8.16558647155762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04157733917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8794093132019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97480154037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03203678131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90802717208862</t>
+    <t xml:space="preserve">8.04157638549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87940979003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9748010635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03203773498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90802669525146</t>
   </si>
   <si>
     <t xml:space="preserve">7.89848756790161</t>
@@ -3881,7 +3881,7 @@
     <t xml:space="preserve">7.84125232696533</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88894844055176</t>
+    <t xml:space="preserve">7.88894891738892</t>
   </si>
   <si>
     <t xml:space="preserve">7.78401708602905</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">7.81263399124146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85079050064087</t>
+    <t xml:space="preserve">7.85079145431519</t>
   </si>
   <si>
     <t xml:space="preserve">7.77447748184204</t>
@@ -3905,13 +3905,13 @@
     <t xml:space="preserve">7.72678184509277</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64092874526978</t>
+    <t xml:space="preserve">7.64092826843262</t>
   </si>
   <si>
     <t xml:space="preserve">7.58369255065918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38336896896362</t>
+    <t xml:space="preserve">7.38336849212646</t>
   </si>
   <si>
     <t xml:space="preserve">7.3356728553772</t>
@@ -3932,7 +3932,7 @@
     <t xml:space="preserve">7.08765268325806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15442705154419</t>
+    <t xml:space="preserve">7.15442752838135</t>
   </si>
   <si>
     <t xml:space="preserve">7.03995656967163</t>
@@ -3944,7 +3944,7 @@
     <t xml:space="preserve">7.27843761444092</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41198635101318</t>
+    <t xml:space="preserve">7.41198682785034</t>
   </si>
   <si>
     <t xml:space="preserve">7.39290809631348</t>
@@ -3965,13 +3965,13 @@
     <t xml:space="preserve">7.45014333724976</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40244770050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50737857818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70770263671875</t>
+    <t xml:space="preserve">7.40244722366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50737905502319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70770311355591</t>
   </si>
   <si>
     <t xml:space="preserve">8.20374393463135</t>
@@ -3986,10 +3986,10 @@
     <t xml:space="preserve">8.10835075378418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08927249908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36591053009033</t>
+    <t xml:space="preserve">8.08927154541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36591148376465</t>
   </si>
   <si>
     <t xml:space="preserve">8.30867481231689</t>
@@ -4007,13 +4007,13 @@
     <t xml:space="preserve">8.60439205169678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40406703948975</t>
+    <t xml:space="preserve">8.40406799316406</t>
   </si>
   <si>
     <t xml:space="preserve">8.41360664367676</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26097774505615</t>
+    <t xml:space="preserve">8.26097869873047</t>
   </si>
   <si>
     <t xml:space="preserve">8.57577323913574</t>
@@ -4028,10 +4028,10 @@
     <t xml:space="preserve">8.76655769348145</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1576681137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19582462310791</t>
+    <t xml:space="preserve">9.15766716003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19582366943359</t>
   </si>
   <si>
     <t xml:space="preserve">9.11951065063477</t>
@@ -4040,13 +4040,13 @@
     <t xml:space="preserve">9.10043144226074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09089183807373</t>
+    <t xml:space="preserve">9.09089279174805</t>
   </si>
   <si>
     <t xml:space="preserve">8.72840118408203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87149047851562</t>
+    <t xml:space="preserve">8.87148952484131</t>
   </si>
   <si>
     <t xml:space="preserve">8.90964698791504</t>
@@ -4070,7 +4070,7 @@
     <t xml:space="preserve">9.00503826141357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20536327362061</t>
+    <t xml:space="preserve">9.20536231994629</t>
   </si>
   <si>
     <t xml:space="preserve">9.45338344573975</t>
@@ -4079,25 +4079,25 @@
     <t xml:space="preserve">9.50107955932617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52969741821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57739353179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47246170043945</t>
+    <t xml:space="preserve">9.52969646453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.577392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47246265411377</t>
   </si>
   <si>
     <t xml:space="preserve">9.36752986907959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30075454711914</t>
+    <t xml:space="preserve">9.30075550079346</t>
   </si>
   <si>
     <t xml:space="preserve">9.39614772796631</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44384288787842</t>
+    <t xml:space="preserve">9.44384384155273</t>
   </si>
   <si>
     <t xml:space="preserve">9.49153995513916</t>
@@ -4109,7 +4109,7 @@
     <t xml:space="preserve">8.69978332519531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55669498443604</t>
+    <t xml:space="preserve">8.55669593811035</t>
   </si>
   <si>
     <t xml:space="preserve">8.62346935272217</t>
@@ -4118,10 +4118,10 @@
     <t xml:space="preserve">8.48038101196289</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59485149383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70932292938232</t>
+    <t xml:space="preserve">8.59485244750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70932197570801</t>
   </si>
   <si>
     <t xml:space="preserve">8.77609729766846</t>
@@ -4133,10 +4133,10 @@
     <t xml:space="preserve">8.75701904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86195087432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89056777954102</t>
+    <t xml:space="preserve">8.8619499206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89056873321533</t>
   </si>
   <si>
     <t xml:space="preserve">8.67116546630859</t>
@@ -4151,10 +4151,10 @@
     <t xml:space="preserve">8.74748039245605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0145788192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92872428894043</t>
+    <t xml:space="preserve">9.01457786560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92872524261475</t>
   </si>
   <si>
     <t xml:space="preserve">8.97642135620117</t>
@@ -4166,28 +4166,28 @@
     <t xml:space="preserve">9.46292304992676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74910068511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78725719451904</t>
+    <t xml:space="preserve">9.74909973144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78725624084473</t>
   </si>
   <si>
     <t xml:space="preserve">9.92080497741699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99711894989014</t>
+    <t xml:space="preserve">9.99711990356445</t>
   </si>
   <si>
     <t xml:space="preserve">9.69186401367188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76817798614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80633449554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63462829589844</t>
+    <t xml:space="preserve">9.7681770324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80633544921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63462924957275</t>
   </si>
   <si>
     <t xml:space="preserve">9.67278575897217</t>
@@ -4196,10 +4196,10 @@
     <t xml:space="preserve">9.59647178649902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71094226837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52015686035156</t>
+    <t xml:space="preserve">9.7109432220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52015781402588</t>
   </si>
   <si>
     <t xml:space="preserve">9.43430519104004</t>
@@ -4208,13 +4208,13 @@
     <t xml:space="preserve">9.25305938720703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28167629241943</t>
+    <t xml:space="preserve">9.28167724609375</t>
   </si>
   <si>
     <t xml:space="preserve">9.34845161437988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41522693634033</t>
+    <t xml:space="preserve">9.41522598266602</t>
   </si>
   <si>
     <t xml:space="preserve">9.48200035095215</t>
@@ -4232,7 +4232,7 @@
     <t xml:space="preserve">9.65370750427246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86357116699219</t>
+    <t xml:space="preserve">9.86357021331787</t>
   </si>
   <si>
     <t xml:space="preserve">10.0204467773438</t>
@@ -34169,7 +34169,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1111" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -34195,7 +34195,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1112" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -34221,7 +34221,7 @@
         <v>5.5</v>
       </c>
       <c r="G1113" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -34247,7 +34247,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1114" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -34273,7 +34273,7 @@
         <v>5.75</v>
       </c>
       <c r="G1115" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -34299,7 +34299,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1116" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -34325,7 +34325,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1117" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -34351,7 +34351,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1118" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -34377,7 +34377,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1119" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -34403,7 +34403,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1120" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -34429,7 +34429,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1121" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -34455,7 +34455,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G1122" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -34481,7 +34481,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G1123" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -34507,7 +34507,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1124" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -34533,7 +34533,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1125" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -34559,7 +34559,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G1126" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -34585,7 +34585,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G1127" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -34611,7 +34611,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1128" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -34637,7 +34637,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1129" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -34663,7 +34663,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1130" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -34689,7 +34689,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G1131" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -34715,7 +34715,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1132" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -34741,7 +34741,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1133" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -34767,7 +34767,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G1134" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -34793,7 +34793,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1135" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -34819,7 +34819,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1136" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -34845,7 +34845,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1137" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -34871,7 +34871,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1138" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -34897,7 +34897,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1139" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -34923,7 +34923,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1140" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -34949,7 +34949,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1141" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -34975,7 +34975,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1142" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -35001,7 +35001,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1143" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -35027,7 +35027,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1144" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -35053,7 +35053,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G1145" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -35079,7 +35079,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1146" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -35105,7 +35105,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1147" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -35131,7 +35131,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1148" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -35157,7 +35157,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G1149" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -35183,7 +35183,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1150" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -35209,7 +35209,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1151" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -35235,7 +35235,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1152" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -35261,7 +35261,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G1153" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -35287,7 +35287,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1154" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -35313,7 +35313,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G1155" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -35339,7 +35339,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1156" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -35365,7 +35365,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G1157" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -35391,7 +35391,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G1158" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -35417,7 +35417,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1159" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -35443,7 +35443,7 @@
         <v>5.75</v>
       </c>
       <c r="G1160" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -35469,7 +35469,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1161" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -35495,7 +35495,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1162" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -35521,7 +35521,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1163" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -35547,7 +35547,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1164" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -35573,7 +35573,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1165" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -35599,7 +35599,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G1166" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -35625,7 +35625,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1167" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -35651,7 +35651,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1168" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -35677,7 +35677,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1169" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -35703,7 +35703,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1170" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -35729,7 +35729,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1171" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -35755,7 +35755,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1172" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -35781,7 +35781,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1173" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -35807,7 +35807,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1174" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -35833,7 +35833,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1175" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -35859,7 +35859,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1176" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -35885,7 +35885,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1177" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -35911,7 +35911,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1178" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -35937,7 +35937,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1179" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -35963,7 +35963,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1180" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -35989,7 +35989,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1181" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -36015,7 +36015,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1182" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -36041,7 +36041,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1183" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -36067,7 +36067,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1184" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -36093,7 +36093,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1185" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -36119,7 +36119,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1186" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -36145,7 +36145,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G1187" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -36171,7 +36171,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1188" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -36197,7 +36197,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1189" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -36223,7 +36223,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G1190" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -36249,7 +36249,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1191" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -36275,7 +36275,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G1192" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -36301,7 +36301,7 @@
         <v>6</v>
       </c>
       <c r="G1193" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -36327,7 +36327,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1194" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -36353,7 +36353,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1195" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -36379,7 +36379,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1196" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -36405,7 +36405,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1197" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -36431,7 +36431,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1198" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -36457,7 +36457,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1199" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -36483,7 +36483,7 @@
         <v>6</v>
       </c>
       <c r="G1200" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -36509,7 +36509,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G1201" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -36535,7 +36535,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1202" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -36561,7 +36561,7 @@
         <v>6</v>
       </c>
       <c r="G1203" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -36587,7 +36587,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G1204" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -36613,7 +36613,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1205" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -36639,7 +36639,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1206" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -36665,7 +36665,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1207" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -36691,7 +36691,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1208" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -36717,7 +36717,7 @@
         <v>5.75</v>
       </c>
       <c r="G1209" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -36743,7 +36743,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1210" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -36769,7 +36769,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1211" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -36795,7 +36795,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1212" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -36821,7 +36821,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1213" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -36847,7 +36847,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1214" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -36873,7 +36873,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1215" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -36899,7 +36899,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G1216" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -36925,7 +36925,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1217" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -36951,7 +36951,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1218" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -36977,7 +36977,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1219" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -37003,7 +37003,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1220" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -37029,7 +37029,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1221" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -37055,7 +37055,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1222" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -37081,7 +37081,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G1223" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -37107,7 +37107,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1224" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -37133,7 +37133,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1225" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -37159,7 +37159,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1226" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -37185,7 +37185,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1227" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -37211,7 +37211,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1228" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -37237,7 +37237,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1229" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -37263,7 +37263,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1230" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -37289,7 +37289,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1231" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -37315,7 +37315,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1232" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -37341,7 +37341,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1233" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -37367,7 +37367,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G1234" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -37393,7 +37393,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1235" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -37419,7 +37419,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1236" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -37445,7 +37445,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G1237" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -37471,7 +37471,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1238" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -37497,7 +37497,7 @@
         <v>6.75</v>
       </c>
       <c r="G1239" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -37523,7 +37523,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1240" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -37549,7 +37549,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1241" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -37575,7 +37575,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1242" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -37601,7 +37601,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1243" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -37627,7 +37627,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1244" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -37653,7 +37653,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1245" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -37679,7 +37679,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1246" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -37705,7 +37705,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G1247" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -37731,7 +37731,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1248" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -37757,7 +37757,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1249" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -37783,7 +37783,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G1250" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -37809,7 +37809,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G1251" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -37835,7 +37835,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1252" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -37861,7 +37861,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1253" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -37887,7 +37887,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1254" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -37913,7 +37913,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1255" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -37939,7 +37939,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G1256" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -37965,7 +37965,7 @@
         <v>6.75</v>
       </c>
       <c r="G1257" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -37991,7 +37991,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1258" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -38017,7 +38017,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1259" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -38043,7 +38043,7 @@
         <v>6.75</v>
       </c>
       <c r="G1260" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -38069,7 +38069,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1261" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -38095,7 +38095,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1262" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -38121,7 +38121,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1263" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -38147,7 +38147,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1264" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -38173,7 +38173,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1265" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -38199,7 +38199,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1266" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -38225,7 +38225,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1267" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -38251,7 +38251,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1268" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -38277,7 +38277,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1269" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -38303,7 +38303,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1270" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -38329,7 +38329,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1271" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -38355,7 +38355,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1272" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -38381,7 +38381,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1273" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -38407,7 +38407,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1274" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -38433,7 +38433,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1275" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -38459,7 +38459,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1276" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -38485,7 +38485,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1277" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -38511,7 +38511,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1278" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -38537,7 +38537,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G1279" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -38563,7 +38563,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1280" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -38589,7 +38589,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1281" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -38615,7 +38615,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1282" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -38641,7 +38641,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1283" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -38667,7 +38667,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G1284" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -38693,7 +38693,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G1285" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -38719,7 +38719,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1286" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -38745,7 +38745,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1287" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -38771,7 +38771,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1288" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -38797,7 +38797,7 @@
         <v>7</v>
       </c>
       <c r="G1289" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -38823,7 +38823,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1290" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -38849,7 +38849,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1291" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -38875,7 +38875,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1292" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -38901,7 +38901,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1293" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -38927,7 +38927,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1294" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -38953,7 +38953,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1295" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -38979,7 +38979,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1296" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -39005,7 +39005,7 @@
         <v>8.5</v>
       </c>
       <c r="G1297" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -39031,7 +39031,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1298" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -39057,7 +39057,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1299" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -39083,7 +39083,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1300" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -39109,7 +39109,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1301" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -39135,7 +39135,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1302" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -39161,7 +39161,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1303" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -39187,7 +39187,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1304" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -39213,7 +39213,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1305" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -39239,7 +39239,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1306" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -39265,7 +39265,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G1307" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -39291,7 +39291,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1308" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -39317,7 +39317,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1309" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -39343,7 +39343,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1310" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -39369,7 +39369,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1311" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -39395,7 +39395,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1312" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -39421,7 +39421,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1313" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -39447,7 +39447,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1314" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -39473,7 +39473,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G1315" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -39499,7 +39499,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1316" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -39525,7 +39525,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1317" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -39551,7 +39551,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1318" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -39577,7 +39577,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1319" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -39603,7 +39603,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1320" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -39629,7 +39629,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1321" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -39655,7 +39655,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1322" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -39681,7 +39681,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1323" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -39707,7 +39707,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1324" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -39733,7 +39733,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1325" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -39759,7 +39759,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1326" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -39785,7 +39785,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G1327" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -39811,7 +39811,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1328" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -39837,7 +39837,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1329" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -39863,7 +39863,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G1330" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -39889,7 +39889,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1331" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -39915,7 +39915,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1332" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -39941,7 +39941,7 @@
         <v>8.75</v>
       </c>
       <c r="G1333" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -39967,7 +39967,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1334" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -39993,7 +39993,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G1335" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -40019,7 +40019,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1336" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -40045,7 +40045,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G1337" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -40071,7 +40071,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G1338" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -40097,7 +40097,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1339" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -40123,7 +40123,7 @@
         <v>9</v>
       </c>
       <c r="G1340" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -40149,7 +40149,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G1341" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -40175,7 +40175,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G1342" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -40201,7 +40201,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1343" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -40227,7 +40227,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G1344" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -40253,7 +40253,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1345" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -40279,7 +40279,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1346" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -40305,7 +40305,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1347" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -40331,7 +40331,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1348" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -40357,7 +40357,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G1349" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -40383,7 +40383,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G1350" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -40409,7 +40409,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1351" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -40435,7 +40435,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G1352" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -40461,7 +40461,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G1353" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -40487,7 +40487,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G1354" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -40513,7 +40513,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1355" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -40539,7 +40539,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G1356" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -40565,7 +40565,7 @@
         <v>9.5</v>
       </c>
       <c r="G1357" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -40591,7 +40591,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G1358" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -40617,7 +40617,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G1359" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -40643,7 +40643,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G1360" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -40669,7 +40669,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G1361" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -40695,7 +40695,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G1362" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -40721,7 +40721,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G1363" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -40747,7 +40747,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1364" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -40773,7 +40773,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G1365" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -40799,7 +40799,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G1366" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -40825,7 +40825,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1367" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -40851,7 +40851,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G1368" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -40877,7 +40877,7 @@
         <v>9.5</v>
       </c>
       <c r="G1369" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -40903,7 +40903,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G1370" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -40929,7 +40929,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1371" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -40955,7 +40955,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G1372" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -40981,7 +40981,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G1373" t="s">
-        <v>921</v>
+        <v>934</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -41007,7 +41007,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1374" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -41319,7 +41319,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1386" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -42151,7 +42151,7 @@
         <v>9.5</v>
       </c>
       <c r="G1418" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -42333,7 +42333,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G1425" t="s">
-        <v>921</v>
+        <v>934</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -42437,7 +42437,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1429" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -42463,7 +42463,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G1430" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -42593,7 +42593,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1435" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -42827,7 +42827,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1444" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -70889,7 +70889,7 @@
     </row>
     <row r="2524">
       <c r="A2524" s="1" t="n">
-        <v>45993.6932638889</v>
+        <v>45993.3333333333</v>
       </c>
       <c r="B2524" t="n">
         <v>161473</v>
@@ -70910,6 +70910,32 @@
         <v>1646</v>
       </c>
       <c r="H2524" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2525">
+      <c r="A2525" s="1" t="n">
+        <v>45994.691099537</v>
+      </c>
+      <c r="B2525" t="n">
+        <v>134648</v>
+      </c>
+      <c r="C2525" t="n">
+        <v>17.5599994659424</v>
+      </c>
+      <c r="D2525" t="n">
+        <v>17.0599994659424</v>
+      </c>
+      <c r="E2525" t="n">
+        <v>17.4400005340576</v>
+      </c>
+      <c r="F2525" t="n">
+        <v>17.2399997711182</v>
+      </c>
+      <c r="G2525" t="s">
+        <v>1644</v>
+      </c>
+      <c r="H2525" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CEM.MI.xlsx
+++ b/data/CEM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="1659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="1660">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70432138442993</t>
+    <t xml:space="preserve">4.70432043075562</t>
   </si>
   <si>
     <t xml:space="preserve">CEM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68036079406738</t>
+    <t xml:space="preserve">4.68035984039307</t>
   </si>
   <si>
     <t xml:space="preserve">4.55656242370605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48867321014404</t>
+    <t xml:space="preserve">4.48867273330688</t>
   </si>
   <si>
     <t xml:space="preserve">4.32893419265747</t>
@@ -59,73 +59,73 @@
     <t xml:space="preserve">4.22110939025879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32494020462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2889986038208</t>
+    <t xml:space="preserve">4.32494068145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28899908065796</t>
   </si>
   <si>
     <t xml:space="preserve">4.29299259185791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06137084960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93597531318665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9743127822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67560005187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83533883094788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94875383377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88006663322449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9168062210083</t>
+    <t xml:space="preserve">4.06137037277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93597555160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97431325912476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67560052871704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83533978462219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94875431060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88006615638733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91680598258972</t>
   </si>
   <si>
     <t xml:space="preserve">3.87846899032593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74588537216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93437767028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87367630004883</t>
+    <t xml:space="preserve">3.74588561058044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93437790870667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87367653846741</t>
   </si>
   <si>
     <t xml:space="preserve">3.73789834976196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57815933227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59892511367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61969184875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3513298034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15005779266357</t>
+    <t xml:space="preserve">3.57815980911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59892582893372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6196916103363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35133028030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15005826950073</t>
   </si>
   <si>
     <t xml:space="preserve">3.25069403648376</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13088965415955</t>
+    <t xml:space="preserve">3.13088941574097</t>
   </si>
   <si>
     <t xml:space="preserve">3.20916175842285</t>
@@ -134,22 +134,22 @@
     <t xml:space="preserve">3.44238090515137</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3625111579895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47592639923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55419874191284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34653759002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39126396179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3673038482666</t>
+    <t xml:space="preserve">3.36251163482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47592687606812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55419850349426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34653735160828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39126420021057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36730360984802</t>
   </si>
   <si>
     <t xml:space="preserve">3.2395122051239</t>
@@ -158,16 +158,16 @@
     <t xml:space="preserve">3.29222631454468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40244650840759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58614659309387</t>
+    <t xml:space="preserve">3.40244579315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58614587783813</t>
   </si>
   <si>
     <t xml:space="preserve">3.63406801223755</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5557963848114</t>
+    <t xml:space="preserve">3.55579590797424</t>
   </si>
   <si>
     <t xml:space="preserve">3.64365220069885</t>
@@ -182,28 +182,28 @@
     <t xml:space="preserve">3.49829006195068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52544522285461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54940605163574</t>
+    <t xml:space="preserve">3.52544498443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5494065284729</t>
   </si>
   <si>
     <t xml:space="preserve">3.75227499008179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61330223083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75387239456177</t>
+    <t xml:space="preserve">3.61330199241638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75387215614319</t>
   </si>
   <si>
     <t xml:space="preserve">3.83214473724365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67080807685852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70754790306091</t>
+    <t xml:space="preserve">3.67080879211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70754766464233</t>
   </si>
   <si>
     <t xml:space="preserve">3.65802907943726</t>
@@ -218,10 +218,10 @@
     <t xml:space="preserve">3.50947117805481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54301691055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57975649833679</t>
+    <t xml:space="preserve">3.5430166721344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57975673675537</t>
   </si>
   <si>
     <t xml:space="preserve">3.45196533203125</t>
@@ -230,97 +230,97 @@
     <t xml:space="preserve">3.41043329238892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37529039382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60052275657654</t>
+    <t xml:space="preserve">3.37529063224792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60052251815796</t>
   </si>
   <si>
     <t xml:space="preserve">3.48551034927368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5446138381958</t>
+    <t xml:space="preserve">3.54461431503296</t>
   </si>
   <si>
     <t xml:space="preserve">3.59573030471802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77943062782288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74428796768188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85770297050476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7394962310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74907994270325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70595026016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69317173957825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67719769477844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7970027923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66601634025574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70115828514099</t>
+    <t xml:space="preserve">3.7794303894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74428844451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85770320892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73949551582336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74908041954041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70595073699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69317150115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67719745635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79700231552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66601610183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70115900039673</t>
   </si>
   <si>
     <t xml:space="preserve">3.6260814666748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67400240898132</t>
+    <t xml:space="preserve">3.67400336265564</t>
   </si>
   <si>
     <t xml:space="preserve">3.64205503463745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53023743629456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45835471153259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47432947158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53193736076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62187075614929</t>
+    <t xml:space="preserve">3.53023815155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45835494995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47432899475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53193712234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62187027931213</t>
   </si>
   <si>
     <t xml:space="preserve">3.75758862495422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76085829734802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87531924247742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88349604606628</t>
+    <t xml:space="preserve">3.76085901260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.875319480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88349580764771</t>
   </si>
   <si>
     <t xml:space="preserve">3.7772102355957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75431799888611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70526385307312</t>
+    <t xml:space="preserve">3.75431823730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70526337623596</t>
   </si>
   <si>
     <t xml:space="preserve">3.66929030418396</t>
@@ -329,28 +329,28 @@
     <t xml:space="preserve">3.59734344482422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58426117897034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5564649105072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38640809059143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31119132041931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29810953140259</t>
+    <t xml:space="preserve">3.58426213264465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55646419525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38640832901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31119108200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29811000823975</t>
   </si>
   <si>
     <t xml:space="preserve">3.19673013687134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15912127494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00705170631409</t>
+    <t xml:space="preserve">3.1591215133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00705194473267</t>
   </si>
   <si>
     <t xml:space="preserve">3.15421628952026</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">3.22289252281189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35206985473633</t>
+    <t xml:space="preserve">3.35206937789917</t>
   </si>
   <si>
     <t xml:space="preserve">3.10679650306702</t>
@@ -371,43 +371,43 @@
     <t xml:space="preserve">2.82882022857666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82064437866211</t>
+    <t xml:space="preserve">2.82064390182495</t>
   </si>
   <si>
     <t xml:space="preserve">2.84026598930359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9351053237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04302525520325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95799708366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79611706733704</t>
+    <t xml:space="preserve">2.93510484695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04302573204041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95799732208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79611682891846</t>
   </si>
   <si>
     <t xml:space="preserve">2.76341414451599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76831889152527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84844136238098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87787485122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04139041900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00051164627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21144652366638</t>
+    <t xml:space="preserve">2.76831912994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84844183921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87787437438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04139018058777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00051140785217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2114462852478</t>
   </si>
   <si>
     <t xml:space="preserve">3.13295912742615</t>
@@ -416,46 +416,46 @@
     <t xml:space="preserve">3.07572841644287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97434902191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10843205451965</t>
+    <t xml:space="preserve">2.97434878349304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1084315776825</t>
   </si>
   <si>
     <t xml:space="preserve">2.97598385810852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92856431007385</t>
+    <t xml:space="preserve">2.92856454849243</t>
   </si>
   <si>
     <t xml:space="preserve">3.17547297477722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18037819862366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15585112571716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18855404853821</t>
+    <t xml:space="preserve">3.18037867546082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15585088729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18855452537537</t>
   </si>
   <si>
     <t xml:space="preserve">3.09862089157104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1215124130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02503848075867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11660766601562</t>
+    <t xml:space="preserve">3.12151265144348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02503895759583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11660742759705</t>
   </si>
   <si>
     <t xml:space="preserve">3.23760890960693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28012299537659</t>
+    <t xml:space="preserve">3.28012347221375</t>
   </si>
   <si>
     <t xml:space="preserve">3.32263731956482</t>
@@ -464,64 +464,64 @@
     <t xml:space="preserve">3.43546271324158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40602970123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46653032302856</t>
+    <t xml:space="preserve">3.40603017807007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46653079986572</t>
   </si>
   <si>
     <t xml:space="preserve">3.43709778785706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44854378700256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67910122871399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64639735221863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71834421157837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69545269012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74450731277466</t>
+    <t xml:space="preserve">3.44854426383972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67910099029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64639782905579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71834468841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69545221328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74450659751892</t>
   </si>
   <si>
     <t xml:space="preserve">3.8524272441864</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80827832221985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82299399375916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80337309837341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7428719997406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62350630760193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56627535820007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47470664978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51558542251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65947937965393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60551929473877</t>
+    <t xml:space="preserve">3.80827903747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82299518585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80337262153625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74287223815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62350606918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56627511978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47470641136169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51558589935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65947914123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60551905632019</t>
   </si>
   <si>
     <t xml:space="preserve">3.54501867294312</t>
@@ -530,43 +530,43 @@
     <t xml:space="preserve">3.64803290367126</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64476275444031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38804316520691</t>
+    <t xml:space="preserve">3.64476299285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38804340362549</t>
   </si>
   <si>
     <t xml:space="preserve">3.4828827381134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45344948768616</t>
+    <t xml:space="preserve">3.45344924926758</t>
   </si>
   <si>
     <t xml:space="preserve">3.4338276386261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50740957260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56464076042175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55482888221741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56300473213196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48451781272888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54338312149048</t>
+    <t xml:space="preserve">3.5074098110199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56464052200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55482912063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56300497055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4845175743103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54338335990906</t>
   </si>
   <si>
     <t xml:space="preserve">3.62514066696167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5908031463623</t>
+    <t xml:space="preserve">3.59080290794373</t>
   </si>
   <si>
     <t xml:space="preserve">3.64149260520935</t>
@@ -575,76 +575,76 @@
     <t xml:space="preserve">3.68891215324402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66111445426941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68727731704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53684282302856</t>
+    <t xml:space="preserve">3.66111397743225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68727779388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53684234619141</t>
   </si>
   <si>
     <t xml:space="preserve">3.63004636764526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63822245597839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43873310089111</t>
+    <t xml:space="preserve">3.63822221755981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43873286247253</t>
   </si>
   <si>
     <t xml:space="preserve">3.417475938797</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41911172866821</t>
+    <t xml:space="preserve">3.41911125183105</t>
   </si>
   <si>
     <t xml:space="preserve">3.33571791648865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37169146537781</t>
+    <t xml:space="preserve">3.37169170379639</t>
   </si>
   <si>
     <t xml:space="preserve">3.27521777153015</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22125744819641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20981121063232</t>
+    <t xml:space="preserve">3.22125768661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20981097221375</t>
   </si>
   <si>
     <t xml:space="preserve">3.1771080493927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21308183670044</t>
+    <t xml:space="preserve">3.21308207511902</t>
   </si>
   <si>
     <t xml:space="preserve">3.14767527580261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11333680152893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00541663169861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0168628692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9530918598175</t>
+    <t xml:space="preserve">3.11333727836609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00541710853577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01686310768127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95309209823608</t>
   </si>
   <si>
     <t xml:space="preserve">2.9187536239624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96453785896301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96780824661255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95636200904846</t>
+    <t xml:space="preserve">2.96453762054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96780776977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95636224746704</t>
   </si>
   <si>
     <t xml:space="preserve">3.04793071746826</t>
@@ -656,43 +656,43 @@
     <t xml:space="preserve">3.18691921234131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3193666934967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23433876037598</t>
+    <t xml:space="preserve">3.31936645507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23433828353882</t>
   </si>
   <si>
     <t xml:space="preserve">3.48778748512268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45181465148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49923419952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57281613349915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45017886161804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61369466781616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67746639251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58916783332825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70362877845764</t>
+    <t xml:space="preserve">3.45181441307068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49923372268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57281565666199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4501793384552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61369514465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67746591567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58916687965393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7036292552948</t>
   </si>
   <si>
     <t xml:space="preserve">3.4861524105072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33244800567627</t>
+    <t xml:space="preserve">3.33244824409485</t>
   </si>
   <si>
     <t xml:space="preserve">3.28666353225708</t>
@@ -701,28 +701,28 @@
     <t xml:space="preserve">3.22943305969238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27031254768372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24741959571838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23106813430786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23270320892334</t>
+    <t xml:space="preserve">3.27031207084656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24741983413696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23106837272644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2327036857605</t>
   </si>
   <si>
     <t xml:space="preserve">3.26213622093201</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27685260772705</t>
+    <t xml:space="preserve">3.27685236930847</t>
   </si>
   <si>
     <t xml:space="preserve">3.23597383499146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00122690200806</t>
+    <t xml:space="preserve">4.0012264251709</t>
   </si>
   <si>
     <t xml:space="preserve">4.04701089859009</t>
@@ -737,175 +737,175 @@
     <t xml:space="preserve">4.17782354354858</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06336259841919</t>
+    <t xml:space="preserve">4.06336355209351</t>
   </si>
   <si>
     <t xml:space="preserve">3.95707774162292</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19417476654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28410863876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34542751312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47215127944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43944835662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41083288192749</t>
+    <t xml:space="preserve">4.19417524337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28410816192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34542798995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47215175628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43944883346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41083383560181</t>
   </si>
   <si>
     <t xml:space="preserve">4.41492128372192</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37404203414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26775741577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39039325714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36177921295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37813091278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38630628585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56208610534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42718458175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3290753364563</t>
+    <t xml:space="preserve">4.37404251098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26775693893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39039373397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3617787361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3781304359436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38630533218384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56208562850952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42718505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32907629013062</t>
   </si>
   <si>
     <t xml:space="preserve">4.25549364089966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25140523910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30046033859253</t>
+    <t xml:space="preserve">4.25140571594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30046081542969</t>
   </si>
   <si>
     <t xml:space="preserve">4.34951543807983</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24322986602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24731826782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21052694320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14512014389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1042423248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22279071807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40674448013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36586618423462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27593278884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30454778671265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28002166748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44762468338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52938270568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51711845397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52120637893677</t>
+    <t xml:space="preserve">4.24323034286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24731731414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21052646636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1451210975647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10424089431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22279024124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40674495697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36586666107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27593231201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3045482635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28002071380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44762420654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52938222885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51711797714233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52120733261108</t>
   </si>
   <si>
     <t xml:space="preserve">4.68063402175903</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66019487380981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71333646774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73377656936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81962203979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81144666671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65201950073242</t>
+    <t xml:space="preserve">4.66019535064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71333742141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73377704620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81962251663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81144571304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65201902389526</t>
   </si>
   <si>
     <t xml:space="preserve">4.34133958816528</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33725118637085</t>
+    <t xml:space="preserve">4.33725070953369</t>
   </si>
   <si>
     <t xml:space="preserve">4.25958108901978</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4038348197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44966459274292</t>
+    <t xml:space="preserve">4.40383434295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44966506958008</t>
   </si>
   <si>
     <t xml:space="preserve">4.41633367538452</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37466955184937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36633777618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30384254455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27467775344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25801181793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31634140014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26634454727173</t>
+    <t xml:space="preserve">4.37467002868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36633729934692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30384206771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27467823028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25801229476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31634092330933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26634502410889</t>
   </si>
   <si>
     <t xml:space="preserve">4.20801591873169</t>
@@ -923,49 +923,49 @@
     <t xml:space="preserve">4.39133548736572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29967594146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42883205413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39966869354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39550161361694</t>
+    <t xml:space="preserve">4.29967498779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42883253097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39966821670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3955020904541</t>
   </si>
   <si>
     <t xml:space="preserve">4.38300275802612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46632957458496</t>
+    <t xml:space="preserve">4.46633005142212</t>
   </si>
   <si>
     <t xml:space="preserve">4.48299551010132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56632232666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40800046920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34967136383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69131278991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58298826217651</t>
+    <t xml:space="preserve">4.566321849823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40800094604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34967231750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69131326675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58298778533936</t>
   </si>
   <si>
     <t xml:space="preserve">4.85380029678345</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9996223449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0579514503479</t>
+    <t xml:space="preserve">4.99962329864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05795240402222</t>
   </si>
   <si>
     <t xml:space="preserve">5.10794830322266</t>
@@ -974,19 +974,19 @@
     <t xml:space="preserve">5.24960422515869</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28710079193115</t>
+    <t xml:space="preserve">5.28710126876831</t>
   </si>
   <si>
     <t xml:space="preserve">5.25377035140991</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41625833511353</t>
+    <t xml:space="preserve">5.41625881195068</t>
   </si>
   <si>
     <t xml:space="preserve">5.30376672744751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29960060119629</t>
+    <t xml:space="preserve">5.29960012435913</t>
   </si>
   <si>
     <t xml:space="preserve">5.34543037414551</t>
@@ -995,10 +995,10 @@
     <t xml:space="preserve">5.30793285369873</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22877216339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29126691818237</t>
+    <t xml:space="preserve">5.22877264022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29126787185669</t>
   </si>
   <si>
     <t xml:space="preserve">5.29543399810791</t>
@@ -1007,34 +1007,34 @@
     <t xml:space="preserve">5.16211080551147</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01628875732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.053786277771</t>
+    <t xml:space="preserve">5.01628828048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05378580093384</t>
   </si>
   <si>
     <t xml:space="preserve">5.12461376190186</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20377445220947</t>
+    <t xml:space="preserve">5.20377397537231</t>
   </si>
   <si>
     <t xml:space="preserve">5.07461786270142</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03295373916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95795917510986</t>
+    <t xml:space="preserve">5.03295421600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95795965194702</t>
   </si>
   <si>
     <t xml:space="preserve">4.99129009246826</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9621262550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90796279907227</t>
+    <t xml:space="preserve">4.96212530136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90796327590942</t>
   </si>
   <si>
     <t xml:space="preserve">4.94129371643066</t>
@@ -1043,10 +1043,10 @@
     <t xml:space="preserve">4.89129781723022</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90379762649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95379257202148</t>
+    <t xml:space="preserve">4.9037971496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95379304885864</t>
   </si>
   <si>
     <t xml:space="preserve">4.94545984268188</t>
@@ -1058,16 +1058,16 @@
     <t xml:space="preserve">5.02462100982666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0496187210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1162805557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17460918426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23293876647949</t>
+    <t xml:space="preserve">5.04961919784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11628103256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17460966110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23293828964233</t>
   </si>
   <si>
     <t xml:space="preserve">5.17877578735352</t>
@@ -1076,10 +1076,10 @@
     <t xml:space="preserve">5.1329460144043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33293151855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26626920700073</t>
+    <t xml:space="preserve">5.33293056488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26626968383789</t>
   </si>
   <si>
     <t xml:space="preserve">5.22460651397705</t>
@@ -1088,28 +1088,28 @@
     <t xml:space="preserve">5.58291244506836</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68707036972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00371360778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80789470672607</t>
+    <t xml:space="preserve">5.68707132339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00371408462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80789518356323</t>
   </si>
   <si>
     <t xml:space="preserve">6.0745415687561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01621246337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16620111465454</t>
+    <t xml:space="preserve">6.01621198654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1662015914917</t>
   </si>
   <si>
     <t xml:space="preserve">5.89122247695923</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94121885299683</t>
+    <t xml:space="preserve">5.94121837615967</t>
   </si>
   <si>
     <t xml:space="preserve">5.96621608734131</t>
@@ -1118,25 +1118,25 @@
     <t xml:space="preserve">6.03287792205811</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99538230895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97038316726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91622066497803</t>
+    <t xml:space="preserve">5.99538135528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97038269042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91622018814087</t>
   </si>
   <si>
     <t xml:space="preserve">5.86205768585205</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92871904373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89955472946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90372180938721</t>
+    <t xml:space="preserve">5.92871999740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89955425262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90372133255005</t>
   </si>
   <si>
     <t xml:space="preserve">5.87455701828003</t>
@@ -1145,52 +1145,52 @@
     <t xml:space="preserve">5.84539270401001</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00788068771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98288249969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03704404830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09120750427246</t>
+    <t xml:space="preserve">6.00788021087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98288106918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03704452514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0912070274353</t>
   </si>
   <si>
     <t xml:space="preserve">6.02871227264404</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99954748153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0495433807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07870817184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29119205474854</t>
+    <t xml:space="preserve">5.99954652786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04954385757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07870864868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29119253158569</t>
   </si>
   <si>
     <t xml:space="preserve">6.1745343208313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1995325088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08287525177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24536180496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21203184127808</t>
+    <t xml:space="preserve">6.19953298568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0828742980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24536275863647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21203136444092</t>
   </si>
   <si>
     <t xml:space="preserve">6.02454566955566</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09954071044922</t>
+    <t xml:space="preserve">6.0995397567749</t>
   </si>
   <si>
     <t xml:space="preserve">6.1828670501709</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">6.2078652381897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22036457061768</t>
+    <t xml:space="preserve">6.22036409378052</t>
   </si>
   <si>
     <t xml:space="preserve">6.14537000656128</t>
@@ -1211,88 +1211,88 @@
     <t xml:space="preserve">5.94538497924805</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01204633712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02037906646729</t>
+    <t xml:space="preserve">6.012047290802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02037954330444</t>
   </si>
   <si>
     <t xml:space="preserve">6.1162052154541</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06204319000244</t>
+    <t xml:space="preserve">6.06204271316528</t>
   </si>
   <si>
     <t xml:space="preserve">6.04121112823486</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1495361328125</t>
+    <t xml:space="preserve">6.14953565597534</t>
   </si>
   <si>
     <t xml:space="preserve">6.09537410736084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35785436630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22453022003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28285932540894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58283662796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61616802215576</t>
+    <t xml:space="preserve">6.35785388946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2245306968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28285980224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58283758163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61616849899292</t>
   </si>
   <si>
     <t xml:space="preserve">6.57450389862061</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50784206390381</t>
+    <t xml:space="preserve">6.50784254074097</t>
   </si>
   <si>
     <t xml:space="preserve">6.49951028823853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6578311920166</t>
+    <t xml:space="preserve">6.65783071517944</t>
   </si>
   <si>
     <t xml:space="preserve">6.7411584854126</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59116983413696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6245002746582</t>
+    <t xml:space="preserve">6.5911693572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62449979782104</t>
   </si>
   <si>
     <t xml:space="preserve">6.6328330039978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70782804489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52450752258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51617527008057</t>
+    <t xml:space="preserve">6.7078275680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52450799942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51617574691772</t>
   </si>
   <si>
     <t xml:space="preserve">6.6661639213562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54950571060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44951295852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29952526092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23286294937134</t>
+    <t xml:space="preserve">6.54950618743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44951391220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29952478408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2328634262085</t>
   </si>
   <si>
     <t xml:space="preserve">5.90788745880127</t>
@@ -1301,19 +1301,19 @@
     <t xml:space="preserve">5.93288564682007</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53284168243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26619386672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36618566513062</t>
+    <t xml:space="preserve">6.53284120559692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26619434356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36618661880493</t>
   </si>
   <si>
     <t xml:space="preserve">6.33285522460938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1412034034729</t>
+    <t xml:space="preserve">6.14120388031006</t>
   </si>
   <si>
     <t xml:space="preserve">6.1578688621521</t>
@@ -1322,52 +1322,52 @@
     <t xml:space="preserve">6.0662088394165</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94955110549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13287115097046</t>
+    <t xml:space="preserve">5.94955062866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1328706741333</t>
   </si>
   <si>
     <t xml:space="preserve">6.05787658691406</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88289022445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84955835342407</t>
+    <t xml:space="preserve">5.88288974761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84955883026123</t>
   </si>
   <si>
     <t xml:space="preserve">5.81622791290283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72456789016724</t>
+    <t xml:space="preserve">5.72456836700439</t>
   </si>
   <si>
     <t xml:space="preserve">5.75789880752563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76623249053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68290519714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82456064224243</t>
+    <t xml:space="preserve">5.76623201370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6829047203064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82455968856812</t>
   </si>
   <si>
     <t xml:space="preserve">5.86622428894043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77456426620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78289699554443</t>
+    <t xml:space="preserve">5.77456378936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78289747238159</t>
   </si>
   <si>
     <t xml:space="preserve">5.79122924804688</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63290882110596</t>
+    <t xml:space="preserve">5.6329083442688</t>
   </si>
   <si>
     <t xml:space="preserve">5.64982414245605</t>
@@ -1379,82 +1379,82 @@
     <t xml:space="preserve">5.66673946380615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70057153701782</t>
+    <t xml:space="preserve">5.70057058334351</t>
   </si>
   <si>
     <t xml:space="preserve">5.48066806793213</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45529365539551</t>
+    <t xml:space="preserve">5.45529413223267</t>
   </si>
   <si>
     <t xml:space="preserve">5.54833078384399</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53987264633179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74285984039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58216094970703</t>
+    <t xml:space="preserve">5.53987216949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74286031723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58216190338135</t>
   </si>
   <si>
     <t xml:space="preserve">5.65828227996826</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70902872085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77669191360474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91201686859131</t>
+    <t xml:space="preserve">5.70902967453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77669143676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91201639175415</t>
   </si>
   <si>
     <t xml:space="preserve">5.9035587310791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89510059356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75131845474243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78515005111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71748685836792</t>
+    <t xml:space="preserve">5.89510107040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75131797790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78514909744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71748638153076</t>
   </si>
   <si>
     <t xml:space="preserve">5.81052255630493</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56524515151978</t>
+    <t xml:space="preserve">5.56524610519409</t>
   </si>
   <si>
     <t xml:space="preserve">5.50604152679443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69211292266846</t>
+    <t xml:space="preserve">5.69211339950562</t>
   </si>
   <si>
     <t xml:space="preserve">5.72594451904297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73440313339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60753536224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51449918746948</t>
+    <t xml:space="preserve">5.73440265655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60753488540649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51449966430664</t>
   </si>
   <si>
     <t xml:space="preserve">5.67519807815552</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01351070404053</t>
+    <t xml:space="preserve">6.01351118087769</t>
   </si>
   <si>
     <t xml:space="preserve">5.99659490585327</t>
@@ -1463,25 +1463,25 @@
     <t xml:space="preserve">5.81898069381714</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75977516174316</t>
+    <t xml:space="preserve">5.75977563858032</t>
   </si>
   <si>
     <t xml:space="preserve">5.80206537246704</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79360723495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88664293289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87818574905396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92893314361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85281181335449</t>
+    <t xml:space="preserve">5.79360675811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.886643409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8781852722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92893218994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85281229019165</t>
   </si>
   <si>
     <t xml:space="preserve">5.76823377609253</t>
@@ -1490,40 +1490,40 @@
     <t xml:space="preserve">5.82743835449219</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83589601516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42992067337036</t>
+    <t xml:space="preserve">5.83589696884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42992115020752</t>
   </si>
   <si>
     <t xml:space="preserve">5.38763189315796</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33688449859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26076459884644</t>
+    <t xml:space="preserve">5.33688497543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26076364517212</t>
   </si>
   <si>
     <t xml:space="preserve">5.303053855896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43837785720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46375274658203</t>
+    <t xml:space="preserve">5.43837881088257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46375226974487</t>
   </si>
   <si>
     <t xml:space="preserve">5.44683647155762</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35380077362061</t>
+    <t xml:space="preserve">5.35380029678345</t>
   </si>
   <si>
     <t xml:space="preserve">5.37071657180786</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22693300247192</t>
+    <t xml:space="preserve">5.22693347930908</t>
   </si>
   <si>
     <t xml:space="preserve">5.14235496520996</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">5.11698150634766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24384927749634</t>
+    <t xml:space="preserve">5.24384880065918</t>
   </si>
   <si>
     <t xml:space="preserve">5.13389730453491</t>
@@ -1544,52 +1544,52 @@
     <t xml:space="preserve">5.25230646133423</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21001720428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23539113998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28613805770874</t>
+    <t xml:space="preserve">5.21001768112183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23539018630981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2861385345459</t>
   </si>
   <si>
     <t xml:space="preserve">5.31996917724609</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29459619522095</t>
+    <t xml:space="preserve">5.29459571838379</t>
   </si>
   <si>
     <t xml:space="preserve">5.48912525177002</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3284273147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16772890090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09160757064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17618608474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10852336883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91399335861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60105419158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49956130981445</t>
+    <t xml:space="preserve">5.32842636108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16772842407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09160804748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17618656158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10852384567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91399431228638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60105466842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49956035614014</t>
   </si>
   <si>
     <t xml:space="preserve">4.567223072052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38115119934082</t>
+    <t xml:space="preserve">4.38115072250366</t>
   </si>
   <si>
     <t xml:space="preserve">4.5418496131897</t>
@@ -1598,7 +1598,7 @@
     <t xml:space="preserve">4.5249342918396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61797046661377</t>
+    <t xml:space="preserve">4.61796998977661</t>
   </si>
   <si>
     <t xml:space="preserve">4.46572971343994</t>
@@ -1607,13 +1607,13 @@
     <t xml:space="preserve">4.27119970321655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14433193206787</t>
+    <t xml:space="preserve">4.14433240890503</t>
   </si>
   <si>
     <t xml:space="preserve">4.22045230865479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09358501434326</t>
+    <t xml:space="preserve">4.09358549118042</t>
   </si>
   <si>
     <t xml:space="preserve">4.20353698730469</t>
@@ -1622,55 +1622,55 @@
     <t xml:space="preserve">4.15701913833618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39806652069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53339147567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59259700775146</t>
+    <t xml:space="preserve">4.39806699752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53339242935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59259653091431</t>
   </si>
   <si>
     <t xml:space="preserve">4.60951232910156</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63488531112671</t>
+    <t xml:space="preserve">4.63488578796387</t>
   </si>
   <si>
     <t xml:space="preserve">4.41498231887817</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49110269546509</t>
+    <t xml:space="preserve">4.49110221862793</t>
   </si>
   <si>
     <t xml:space="preserve">4.42343997955322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43189811706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2965726852417</t>
+    <t xml:space="preserve">4.43189764022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29657316207886</t>
   </si>
   <si>
     <t xml:space="preserve">4.33886241912842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19507932662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04706764221191</t>
+    <t xml:space="preserve">4.19507884979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04706716537476</t>
   </si>
   <si>
     <t xml:space="preserve">4.08512735366821</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10627174377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15278911590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23736810684204</t>
+    <t xml:space="preserve">4.10627222061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15278959274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2373685836792</t>
   </si>
   <si>
     <t xml:space="preserve">4.21622371673584</t>
@@ -1679,7 +1679,7 @@
     <t xml:space="preserve">4.16124773025513</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10204315185547</t>
+    <t xml:space="preserve">4.10204267501831</t>
   </si>
   <si>
     <t xml:space="preserve">4.03860998153687</t>
@@ -1688,10 +1688,10 @@
     <t xml:space="preserve">4.30503082275391</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2542839050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14010334014893</t>
+    <t xml:space="preserve">4.25428438186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14010286331177</t>
   </si>
   <si>
     <t xml:space="preserve">4.0512957572937</t>
@@ -1706,22 +1706,22 @@
     <t xml:space="preserve">4.0343804359436</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94557332992554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35577821731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31348848342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4826455116272</t>
+    <t xml:space="preserve">3.9455738067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35577726364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3134880065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48264503479004</t>
   </si>
   <si>
     <t xml:space="preserve">4.65180110931396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7955846786499</t>
+    <t xml:space="preserve">4.79558420181274</t>
   </si>
   <si>
     <t xml:space="preserve">4.78712606430054</t>
@@ -1730,16 +1730,16 @@
     <t xml:space="preserve">4.82095766067505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86324691772461</t>
+    <t xml:space="preserve">4.86324644088745</t>
   </si>
   <si>
     <t xml:space="preserve">4.90553617477417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88862037658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95628309249878</t>
+    <t xml:space="preserve">4.88862085342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95628261566162</t>
   </si>
   <si>
     <t xml:space="preserve">5.00703001022339</t>
@@ -1748,88 +1748,88 @@
     <t xml:space="preserve">5.01548719406128</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03240299224854</t>
+    <t xml:space="preserve">5.03240346908569</t>
   </si>
   <si>
     <t xml:space="preserve">5.057776927948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99011468887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97319889068604</t>
+    <t xml:space="preserve">4.99011421203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97319841384888</t>
   </si>
   <si>
     <t xml:space="preserve">5.20155954360962</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12543916702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15927028656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21847581863403</t>
+    <t xml:space="preserve">5.12544012069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15927076339722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21847534179688</t>
   </si>
   <si>
     <t xml:space="preserve">5.3453426361084</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27768039703369</t>
+    <t xml:space="preserve">5.27767944335938</t>
   </si>
   <si>
     <t xml:space="preserve">5.40454721450806</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39609003067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47220993041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49758338928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42146348953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41300535202026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98165607452393</t>
+    <t xml:space="preserve">5.39608907699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47220945358276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49758434295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42146253585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41300487518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98165702819824</t>
   </si>
   <si>
     <t xml:space="preserve">5.11462497711182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13193273544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01942920684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01077556610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06269931793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08866262435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0973162651062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14058828353882</t>
+    <t xml:space="preserve">5.13193321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01942873001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01077508926392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0627007484436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08866214752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09731674194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1405873298645</t>
   </si>
   <si>
     <t xml:space="preserve">5.20116710662842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17520427703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22712898254395</t>
+    <t xml:space="preserve">5.17520380020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2271294593811</t>
   </si>
   <si>
     <t xml:space="preserve">5.26174640655518</t>
@@ -1841,10 +1841,10 @@
     <t xml:space="preserve">5.25309228897095</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33963441848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46079206466675</t>
+    <t xml:space="preserve">5.33963346481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46079301834106</t>
   </si>
   <si>
     <t xml:space="preserve">5.54733467102051</t>
@@ -1853,19 +1853,19 @@
     <t xml:space="preserve">5.42617607116699</t>
   </si>
   <si>
-    <t xml:space="preserve">5.330979347229</t>
+    <t xml:space="preserve">5.33097982406616</t>
   </si>
   <si>
     <t xml:space="preserve">5.40886735916138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57329702377319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52137231826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47810125350952</t>
+    <t xml:space="preserve">5.57329654693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52137136459351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47810077667236</t>
   </si>
   <si>
     <t xml:space="preserve">5.64253044128418</t>
@@ -1874,67 +1874,67 @@
     <t xml:space="preserve">5.7636890411377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74638032913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72907209396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65118455886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7031102180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66849327087402</t>
+    <t xml:space="preserve">5.74638080596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72907257080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65118503570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70310974121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66849279403687</t>
   </si>
   <si>
     <t xml:space="preserve">5.59925937652588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49540948867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45213842391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56464195251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73772668838501</t>
+    <t xml:space="preserve">5.49540901184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45213890075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56464338302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73772621154785</t>
   </si>
   <si>
     <t xml:space="preserve">5.51271772384644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24443769454956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1838583946228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28770923614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19251251220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1232795715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27040147781372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08000755310059</t>
+    <t xml:space="preserve">5.24443817138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18385791778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2877082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19251298904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12327909469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2704005241394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08000802993774</t>
   </si>
   <si>
     <t xml:space="preserve">5.14924144744873</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16654968261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15789556503296</t>
+    <t xml:space="preserve">5.1665506362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15789604187012</t>
   </si>
   <si>
     <t xml:space="preserve">5.29636287689209</t>
@@ -1943,10 +1943,10 @@
     <t xml:space="preserve">5.53868007659912</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44348430633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48675441741943</t>
+    <t xml:space="preserve">5.44348382949829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48675489425659</t>
   </si>
   <si>
     <t xml:space="preserve">5.40021324157715</t>
@@ -1958,13 +1958,13 @@
     <t xml:space="preserve">5.32232522964478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38290500640869</t>
+    <t xml:space="preserve">5.38290405273438</t>
   </si>
   <si>
     <t xml:space="preserve">5.02808284759521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04539108276367</t>
+    <t xml:space="preserve">5.04539155960083</t>
   </si>
   <si>
     <t xml:space="preserve">5.16222333908081</t>
@@ -1973,10 +1973,10 @@
     <t xml:space="preserve">5.03933334350586</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10597133636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15270376205444</t>
+    <t xml:space="preserve">5.10597085952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15270328521729</t>
   </si>
   <si>
     <t xml:space="preserve">5.20895576477051</t>
@@ -1985,7 +1985,7 @@
     <t xml:space="preserve">5.27905416488647</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34569215774536</t>
+    <t xml:space="preserve">5.3456916809082</t>
   </si>
   <si>
     <t xml:space="preserve">5.32665252685547</t>
@@ -1994,19 +1994,19 @@
     <t xml:space="preserve">5.27992010116577</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3058819770813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26780414581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34742212295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21934080123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34309482574463</t>
+    <t xml:space="preserve">5.30588293075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26780462265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34742259979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21934032440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34309530258179</t>
   </si>
   <si>
     <t xml:space="preserve">5.48502397537231</t>
@@ -2018,22 +2018,22 @@
     <t xml:space="preserve">5.3179988861084</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51791000366211</t>
+    <t xml:space="preserve">5.51791095733643</t>
   </si>
   <si>
     <t xml:space="preserve">5.61656761169434</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51617956161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46252250671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42271375656128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46771621704102</t>
+    <t xml:space="preserve">5.51617908477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46252298355103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42271423339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46771574020386</t>
   </si>
   <si>
     <t xml:space="preserve">5.44434976577759</t>
@@ -2045,43 +2045,43 @@
     <t xml:space="preserve">5.78099727630615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02331447601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0406231880188</t>
+    <t xml:space="preserve">6.0233154296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04062366485596</t>
   </si>
   <si>
     <t xml:space="preserve">6.04927730560303</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94456148147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76974630355835</t>
+    <t xml:space="preserve">5.94456195831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76974725723267</t>
   </si>
   <si>
     <t xml:space="preserve">5.78272867202759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75416946411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74118757247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73945760726929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81042242050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90561771392822</t>
+    <t xml:space="preserve">5.75416898727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74118804931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73945713043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81042146682739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90561723709106</t>
   </si>
   <si>
     <t xml:space="preserve">5.93331146240234</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94109964370728</t>
+    <t xml:space="preserve">5.94110012054443</t>
   </si>
   <si>
     <t xml:space="preserve">5.91081047058105</t>
@@ -2090,19 +2090,19 @@
     <t xml:space="preserve">5.92638826370239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85369300842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85628890991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68060970306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73253393173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81907558441162</t>
+    <t xml:space="preserve">5.85369253158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85628938674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68060922622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73253440856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81907606124878</t>
   </si>
   <si>
     <t xml:space="preserve">5.90648317337036</t>
@@ -2111,46 +2111,46 @@
     <t xml:space="preserve">5.70570611953735</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57502794265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75590038299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81561374664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7602276802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73513078689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72041797637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69791698455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69272470474243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62868404388428</t>
+    <t xml:space="preserve">5.57502746582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75590085983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81561422348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76022720336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73513031005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72041845321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69791746139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69272518157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62868356704712</t>
   </si>
   <si>
     <t xml:space="preserve">5.75936222076416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65810775756836</t>
+    <t xml:space="preserve">5.65810823440552</t>
   </si>
   <si>
     <t xml:space="preserve">5.57243156433105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62522220611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6728196144104</t>
+    <t xml:space="preserve">5.62522268295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67282009124756</t>
   </si>
   <si>
     <t xml:space="preserve">5.58195066452026</t>
@@ -2162,10 +2162,10 @@
     <t xml:space="preserve">5.6451268196106</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72561073303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61483716964722</t>
+    <t xml:space="preserve">5.72561120986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61483669281006</t>
   </si>
   <si>
     <t xml:space="preserve">5.60704851150513</t>
@@ -2180,19 +2180,19 @@
     <t xml:space="preserve">5.75503540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84071159362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00600576400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92811870574951</t>
+    <t xml:space="preserve">5.84071111679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00600624084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92811822891235</t>
   </si>
   <si>
     <t xml:space="preserve">5.87619304656982</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71436071395874</t>
+    <t xml:space="preserve">5.71436023712158</t>
   </si>
   <si>
     <t xml:space="preserve">5.4218487739563</t>
@@ -2207,61 +2207,61 @@
     <t xml:space="preserve">5.04019927978516</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1544337272644</t>
+    <t xml:space="preserve">5.15443420410156</t>
   </si>
   <si>
     <t xml:space="preserve">5.18039655685425</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79615020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24358081817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30113124847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30718946456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94501161575317</t>
+    <t xml:space="preserve">4.79615116119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24358129501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30113172531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30718994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94501090049744</t>
   </si>
   <si>
     <t xml:space="preserve">4.11073923110962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9809262752533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77452349662781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89438438415527</t>
+    <t xml:space="preserve">3.98092651367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77452373504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89438462257385</t>
   </si>
   <si>
     <t xml:space="preserve">4.17564487457275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82385230064392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97486805915833</t>
+    <t xml:space="preserve">3.82385277748108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9748682975769</t>
   </si>
   <si>
     <t xml:space="preserve">4.07006502151489</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27387094497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11766242980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05665063858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25699472427368</t>
+    <t xml:space="preserve">4.27387046813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11766290664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05665016174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.256995677948</t>
   </si>
   <si>
     <t xml:space="preserve">4.30978584289551</t>
@@ -2270,16 +2270,16 @@
     <t xml:space="preserve">4.37036514282227</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17131805419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32709407806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45690727233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6126823425293</t>
+    <t xml:space="preserve">4.17131853103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32709360122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45690679550171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61268186569214</t>
   </si>
   <si>
     <t xml:space="preserve">4.48286914825439</t>
@@ -2291,94 +2291,94 @@
     <t xml:space="preserve">4.56941175460815</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57806491851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5261402130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50017738342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74249458312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76845741271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79442024230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94154167175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91557788848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83769083023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58671998977661</t>
+    <t xml:space="preserve">4.57806539535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52613973617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50017786026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74249505996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76845788955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79441976547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94154119491577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91557836532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83769130706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58671951293945</t>
   </si>
   <si>
     <t xml:space="preserve">4.55210304260254</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62133693695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6732611656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80307388305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90961170196533</t>
+    <t xml:space="preserve">4.62133646011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67326164245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80307483673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90961217880249</t>
   </si>
   <si>
     <t xml:space="preserve">4.8030743598938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73204946517944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88297700881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91849040985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10493135452271</t>
+    <t xml:space="preserve">4.73204851150513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88297748565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91848945617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10493087768555</t>
   </si>
   <si>
     <t xml:space="preserve">5.22034692764282</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19371175765991</t>
+    <t xml:space="preserve">5.19371223449707</t>
   </si>
   <si>
     <t xml:space="preserve">5.39790964126587</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44229984283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3002495765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52220392227173</t>
+    <t xml:space="preserve">5.44230031967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30025005340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52220296859741</t>
   </si>
   <si>
     <t xml:space="preserve">5.49556922912598</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60210657119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72640037536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81518268585205</t>
+    <t xml:space="preserve">5.60210704803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72640085220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81518220901489</t>
   </si>
   <si>
     <t xml:space="preserve">5.63761949539185</t>
@@ -2387,10 +2387,10 @@
     <t xml:space="preserve">5.30912828445435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27361631393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23810386657715</t>
+    <t xml:space="preserve">5.27361583709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23810291290283</t>
   </si>
   <si>
     <t xml:space="preserve">5.55771636962891</t>
@@ -2399,19 +2399,19 @@
     <t xml:space="preserve">5.73527956008911</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61098480224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65537595748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68201017379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61986351013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64649820327759</t>
+    <t xml:space="preserve">5.61098527908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65537548065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68200969696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61986303329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64649772644043</t>
   </si>
   <si>
     <t xml:space="preserve">5.71752262115479</t>
@@ -2426,34 +2426,34 @@
     <t xml:space="preserve">5.53108167648315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46005630493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35351943969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42454433441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41566562652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31800651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38903188705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29137182235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21146821975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36239671707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25585985183716</t>
+    <t xml:space="preserve">5.4600567817688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35351896286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42454385757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41566610336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31800603866577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38903141021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29137134552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21146869659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36239719390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.255859375</t>
   </si>
   <si>
     <t xml:space="preserve">5.26473712921143</t>
@@ -2471,22 +2471,22 @@
     <t xml:space="preserve">5.53995990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50444746017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3801531791687</t>
+    <t xml:space="preserve">5.5044469833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38015365600586</t>
   </si>
   <si>
     <t xml:space="preserve">5.34464073181152</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28249359130859</t>
+    <t xml:space="preserve">5.28249406814575</t>
   </si>
   <si>
     <t xml:space="preserve">5.20259094238281</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32688426971436</t>
+    <t xml:space="preserve">5.32688474655151</t>
   </si>
   <si>
     <t xml:space="preserve">5.3357629776001</t>
@@ -2507,19 +2507,19 @@
     <t xml:space="preserve">5.18483448028564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02502727508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90073442459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61663293838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72317171096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85634279251099</t>
+    <t xml:space="preserve">5.02502775192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90073394775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61663341522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72317123413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85634326934814</t>
   </si>
   <si>
     <t xml:space="preserve">4.99839305877686</t>
@@ -2531,31 +2531,31 @@
     <t xml:space="preserve">4.89185571670532</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98951578140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90396404266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01050090789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01938009262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99274492263794</t>
+    <t xml:space="preserve">4.98951530456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90396356582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01050138473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01937961578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9927453994751</t>
   </si>
   <si>
     <t xml:space="preserve">6.09928274154663</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10816097259521</t>
+    <t xml:space="preserve">6.10816049575806</t>
   </si>
   <si>
     <t xml:space="preserve">6.35674905776978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18806409835815</t>
+    <t xml:space="preserve">6.188063621521</t>
   </si>
   <si>
     <t xml:space="preserve">6.2413330078125</t>
@@ -2564,43 +2564,43 @@
     <t xml:space="preserve">6.28572368621826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32123708724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25021171569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30347967147827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31235837936401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11703872680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08152675628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06377029418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05489253997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98386716842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96611022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93947649002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94835424423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92172050476074</t>
+    <t xml:space="preserve">6.32123613357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25021123886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30348014831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31235790252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1170392036438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08152627944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06377077102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05489206314087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98386669158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96611070632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93947696685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94835376739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92172002792358</t>
   </si>
   <si>
     <t xml:space="preserve">5.912841796875</t>
@@ -2612,25 +2612,25 @@
     <t xml:space="preserve">6.46328639984131</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33011436462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27684497833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20582056045532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04601335525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37450504302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12591695785522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21469831466675</t>
+    <t xml:space="preserve">6.33011484146118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27684545516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20582008361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04601383209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37450456619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12591791152954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21469879150391</t>
   </si>
   <si>
     <t xml:space="preserve">6.17918586730957</t>
@@ -2639,112 +2639,112 @@
     <t xml:space="preserve">6.26796770095825</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48104333877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66748428344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01373147964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4398832321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54641914367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59968852996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6352014541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68846940994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52866315841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31558799743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3067102432251</t>
+    <t xml:space="preserve">6.48104286193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66748332977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01373195648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43988275527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54641962051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59968948364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63520240783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68846988677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52866363525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31558752059937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30670976638794</t>
   </si>
   <si>
     <t xml:space="preserve">7.1824164390564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29783201217651</t>
+    <t xml:space="preserve">7.29783153533936</t>
   </si>
   <si>
     <t xml:space="preserve">7.13802528381348</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04924345016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19129371643066</t>
+    <t xml:space="preserve">7.04924392700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19129419326782</t>
   </si>
   <si>
     <t xml:space="preserve">7.21792840957642</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3511004447937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48427391052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59080982208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58193254470825</t>
+    <t xml:space="preserve">7.35109949111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4842734336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59081029891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58193302154541</t>
   </si>
   <si>
     <t xml:space="preserve">7.65295696258545</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51090669631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45763826370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17353820800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61744499206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67959213256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76837301254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9370584487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19452381134033</t>
+    <t xml:space="preserve">7.51090717315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45763731002808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17353773117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61744451522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67959117889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76837396621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93705797195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19452285766602</t>
   </si>
   <si>
     <t xml:space="preserve">8.09686374664307</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99920511245728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17676734924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20340251922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99032640457153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08798503875732</t>
+    <t xml:space="preserve">7.99920463562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17676830291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20340156555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99032688140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08798599243164</t>
   </si>
   <si>
     <t xml:space="preserve">8.0524730682373</t>
@@ -2774,22 +2774,22 @@
     <t xml:space="preserve">8.23891448974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44311332702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38096523284912</t>
+    <t xml:space="preserve">8.44311141967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38096618652344</t>
   </si>
   <si>
     <t xml:space="preserve">8.51413726806641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43423366546631</t>
+    <t xml:space="preserve">8.43423461914062</t>
   </si>
   <si>
     <t xml:space="preserve">8.64730930328369</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42535495758057</t>
+    <t xml:space="preserve">8.42535591125488</t>
   </si>
   <si>
     <t xml:space="preserve">8.47014427185059</t>
@@ -2804,16 +2804,16 @@
     <t xml:space="preserve">8.4160795211792</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3710241317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56025123596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31696033477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42509078979492</t>
+    <t xml:space="preserve">8.37102508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56025314331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31695938110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42508983612061</t>
   </si>
   <si>
     <t xml:space="preserve">8.44311237335205</t>
@@ -2822,16 +2822,16 @@
     <t xml:space="preserve">8.62332725524902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75849056243896</t>
+    <t xml:space="preserve">8.75848960876465</t>
   </si>
   <si>
     <t xml:space="preserve">8.6593713760376</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70442485809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74046802520752</t>
+    <t xml:space="preserve">8.70442390441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7404670715332</t>
   </si>
   <si>
     <t xml:space="preserve">8.68640327453613</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">8.47915554046631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50618648529053</t>
+    <t xml:space="preserve">8.50618839263916</t>
   </si>
   <si>
     <t xml:space="preserve">8.51519775390625</t>
@@ -2849,16 +2849,16 @@
     <t xml:space="preserve">8.5332202911377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46113300323486</t>
+    <t xml:space="preserve">8.46113395690918</t>
   </si>
   <si>
     <t xml:space="preserve">8.27190685272217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10971355438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15476703643799</t>
+    <t xml:space="preserve">8.10971260070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15476608276367</t>
   </si>
   <si>
     <t xml:space="preserve">8.08268070220947</t>
@@ -2870,28 +2870,28 @@
     <t xml:space="preserve">8.05564785003662</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95652866363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00158214569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74928140640259</t>
+    <t xml:space="preserve">7.95652914047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00158309936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7492823600769</t>
   </si>
   <si>
     <t xml:space="preserve">7.85741138458252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78532409667969</t>
+    <t xml:space="preserve">7.78532457351685</t>
   </si>
   <si>
     <t xml:space="preserve">7.83938837051392</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74027061462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99257230758667</t>
+    <t xml:space="preserve">7.74026918411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99257278442383</t>
   </si>
   <si>
     <t xml:space="preserve">7.92048597335815</t>
@@ -2903,16 +2903,16 @@
     <t xml:space="preserve">8.29893970489502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16377735137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21784210205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96553993225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60510778427124</t>
+    <t xml:space="preserve">8.16377830505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21784114837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96554088592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6051082611084</t>
   </si>
   <si>
     <t xml:space="preserve">8.07366943359375</t>
@@ -2924,19 +2924,19 @@
     <t xml:space="preserve">8.12773513793945</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48816680908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38904762268066</t>
+    <t xml:space="preserve">8.4881649017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38904666900635</t>
   </si>
   <si>
     <t xml:space="preserve">8.35300445556641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33498191833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71343517303467</t>
+    <t xml:space="preserve">8.33498287200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71343612670898</t>
   </si>
   <si>
     <t xml:space="preserve">8.63233852386475</t>
@@ -2948,13 +2948,13 @@
     <t xml:space="preserve">8.30795097351074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64134883880615</t>
+    <t xml:space="preserve">8.64134979248047</t>
   </si>
   <si>
     <t xml:space="preserve">8.77651119232178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55123996734619</t>
+    <t xml:space="preserve">8.55124187469482</t>
   </si>
   <si>
     <t xml:space="preserve">8.49717712402344</t>
@@ -2963,7 +2963,7 @@
     <t xml:space="preserve">8.25388526916504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19982051849365</t>
+    <t xml:space="preserve">8.19982147216797</t>
   </si>
   <si>
     <t xml:space="preserve">8.03762626647949</t>
@@ -2972,46 +2972,46 @@
     <t xml:space="preserve">7.92949724197388</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98356151580811</t>
+    <t xml:space="preserve">7.98356103897095</t>
   </si>
   <si>
     <t xml:space="preserve">8.01960468292236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88444232940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56906509399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63214159011841</t>
+    <t xml:space="preserve">7.88444328308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56906414031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63214015960693</t>
   </si>
   <si>
     <t xml:space="preserve">7.57807588577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55104446411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65917253494263</t>
+    <t xml:space="preserve">7.55104398727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65917301177979</t>
   </si>
   <si>
     <t xml:space="preserve">7.67719554901123</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72224903106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76730298995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71323776245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9385085105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22685241699219</t>
+    <t xml:space="preserve">7.72224855422974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7673020362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71323871612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93850803375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2268533706665</t>
   </si>
   <si>
     <t xml:space="preserve">8.19080924987793</t>
@@ -3023,7 +3023,7 @@
     <t xml:space="preserve">8.38003635406494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18179798126221</t>
+    <t xml:space="preserve">8.18179893493652</t>
   </si>
   <si>
     <t xml:space="preserve">8.02861595153809</t>
@@ -3032,7 +3032,7 @@
     <t xml:space="preserve">7.80334568023682</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69521570205688</t>
+    <t xml:space="preserve">7.6952166557312</t>
   </si>
   <si>
     <t xml:space="preserve">7.61411905288696</t>
@@ -3044,37 +3044,37 @@
     <t xml:space="preserve">7.33478450775146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37082815170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46093559265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36181688308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35280656814575</t>
+    <t xml:space="preserve">7.37082767486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46093463897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36181735992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35280561447144</t>
   </si>
   <si>
     <t xml:space="preserve">7.4429144859314</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65016174316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46994590759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39786052703857</t>
+    <t xml:space="preserve">7.65016269683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46994686126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39786005020142</t>
   </si>
   <si>
     <t xml:space="preserve">7.3257737159729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27170896530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30775213241577</t>
+    <t xml:space="preserve">7.27170848846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30775165557861</t>
   </si>
   <si>
     <t xml:space="preserve">7.29874134063721</t>
@@ -3083,25 +3083,25 @@
     <t xml:space="preserve">7.26269865036011</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54203224182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64115047454834</t>
+    <t xml:space="preserve">7.54203271865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64115142822266</t>
   </si>
   <si>
     <t xml:space="preserve">7.62312984466553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53302145004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52401113510132</t>
+    <t xml:space="preserve">7.53302097320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52401161193848</t>
   </si>
   <si>
     <t xml:space="preserve">7.31676292419434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38884878158569</t>
+    <t xml:space="preserve">7.38884925842285</t>
   </si>
   <si>
     <t xml:space="preserve">7.45192527770996</t>
@@ -3110,31 +3110,31 @@
     <t xml:space="preserve">6.96534204483032</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92929887771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02841758728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89325618743896</t>
+    <t xml:space="preserve">6.92929935455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02841806411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89325571060181</t>
   </si>
   <si>
     <t xml:space="preserve">7.0103964805603</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12753629684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11852550506592</t>
+    <t xml:space="preserve">7.12753582000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11852598190308</t>
   </si>
   <si>
     <t xml:space="preserve">6.94732046127319</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88424444198608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90226602554321</t>
+    <t xml:space="preserve">6.88424491882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90226650238037</t>
   </si>
   <si>
     <t xml:space="preserve">7.28071975708008</t>
@@ -3158,10 +3158,10 @@
     <t xml:space="preserve">7.07347106933594</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80314826965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74007225036621</t>
+    <t xml:space="preserve">6.80314779281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74007177352905</t>
   </si>
   <si>
     <t xml:space="preserve">6.66798639297485</t>
@@ -3170,7 +3170,7 @@
     <t xml:space="preserve">6.3616189956665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59590005874634</t>
+    <t xml:space="preserve">6.59589958190918</t>
   </si>
   <si>
     <t xml:space="preserve">6.41568374633789</t>
@@ -3179,7 +3179,7 @@
     <t xml:space="preserve">6.32557582855225</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13634872436523</t>
+    <t xml:space="preserve">6.13634920120239</t>
   </si>
   <si>
     <t xml:space="preserve">5.85701513290405</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">6.01019811630249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28052186965942</t>
+    <t xml:space="preserve">6.28052139282227</t>
   </si>
   <si>
     <t xml:space="preserve">6.09129524230957</t>
@@ -3200,7 +3200,7 @@
     <t xml:space="preserve">6.14535999298096</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3526086807251</t>
+    <t xml:space="preserve">6.35260820388794</t>
   </si>
   <si>
     <t xml:space="preserve">6.23546838760376</t>
@@ -3215,19 +3215,19 @@
     <t xml:space="preserve">6.37062978744507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28953218460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31656503677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02821969985962</t>
+    <t xml:space="preserve">6.28953313827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31656551361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02822017669678</t>
   </si>
   <si>
     <t xml:space="preserve">6.11832761764526</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12733888626099</t>
+    <t xml:space="preserve">6.12733840942383</t>
   </si>
   <si>
     <t xml:space="preserve">6.27151107788086</t>
@@ -3236,13 +3236,13 @@
     <t xml:space="preserve">6.26250028610229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18140316009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29854345321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17239284515381</t>
+    <t xml:space="preserve">6.18140363693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29854297637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17239189147949</t>
   </si>
   <si>
     <t xml:space="preserve">5.84800386428833</t>
@@ -3251,16 +3251,16 @@
     <t xml:space="preserve">5.86602544784546</t>
   </si>
   <si>
-    <t xml:space="preserve">5.920090675354</t>
+    <t xml:space="preserve">5.92009019851685</t>
   </si>
   <si>
     <t xml:space="preserve">5.89305782318115</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93811225891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88404703140259</t>
+    <t xml:space="preserve">5.93811178207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88404750823975</t>
   </si>
   <si>
     <t xml:space="preserve">6.10030603408813</t>
@@ -3272,22 +3272,22 @@
     <t xml:space="preserve">6.06426286697388</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98316621780396</t>
+    <t xml:space="preserve">5.9831657409668</t>
   </si>
   <si>
     <t xml:space="preserve">5.94712257385254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0192084312439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99217700958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96514368057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97415447235107</t>
+    <t xml:space="preserve">6.01920890808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99217653274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96514415740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97415494918823</t>
   </si>
   <si>
     <t xml:space="preserve">5.9561333656311</t>
@@ -3296,10 +3296,10 @@
     <t xml:space="preserve">6.08228492736816</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07327365875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03723049163818</t>
+    <t xml:space="preserve">6.07327318191528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03723001480103</t>
   </si>
   <si>
     <t xml:space="preserve">6.04001379013062</t>
@@ -3311,7 +3311,7 @@
     <t xml:space="preserve">5.96590328216553</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16044425964355</t>
+    <t xml:space="preserve">6.1604437828064</t>
   </si>
   <si>
     <t xml:space="preserve">6.28087329864502</t>
@@ -3320,10 +3320,10 @@
     <t xml:space="preserve">6.22529029846191</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20676279067993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17897176742554</t>
+    <t xml:space="preserve">6.20676231384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17897129058838</t>
   </si>
   <si>
     <t xml:space="preserve">6.29013729095459</t>
@@ -3347,7 +3347,7 @@
     <t xml:space="preserve">5.9288477897644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8917932510376</t>
+    <t xml:space="preserve">5.89179277420044</t>
   </si>
   <si>
     <t xml:space="preserve">6.09559679031372</t>
@@ -3359,7 +3359,7 @@
     <t xml:space="preserve">5.95663928985596</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82694625854492</t>
+    <t xml:space="preserve">5.82694578170776</t>
   </si>
   <si>
     <t xml:space="preserve">5.68798828125</t>
@@ -3374,10 +3374,10 @@
     <t xml:space="preserve">5.72504377365112</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34522724151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4471287727356</t>
+    <t xml:space="preserve">5.34522676467896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44712924957275</t>
   </si>
   <si>
     <t xml:space="preserve">5.6046142578125</t>
@@ -3386,31 +3386,31 @@
     <t xml:space="preserve">5.75283527374268</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51197528839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85473775863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55829477310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71578073501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77136278152466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61387777328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66019725799561</t>
+    <t xml:space="preserve">5.51197576522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85473728179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55829524993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71577978134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77136325836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61387825012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66019678115845</t>
   </si>
   <si>
     <t xml:space="preserve">5.87326526641846</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66946077346802</t>
+    <t xml:space="preserve">5.66946125030518</t>
   </si>
   <si>
     <t xml:space="preserve">5.80841875076294</t>
@@ -3419,13 +3419,13 @@
     <t xml:space="preserve">6.0307502746582</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04927778244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86400079727173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53976774215698</t>
+    <t xml:space="preserve">6.04927825927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86400127410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53976726531982</t>
   </si>
   <si>
     <t xml:space="preserve">5.49344778060913</t>
@@ -3437,7 +3437,7 @@
     <t xml:space="preserve">5.37301874160767</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39154672622681</t>
+    <t xml:space="preserve">5.39154624938965</t>
   </si>
   <si>
     <t xml:space="preserve">5.35449075698853</t>
@@ -3452,22 +3452,22 @@
     <t xml:space="preserve">5.15995073318481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21553373336792</t>
+    <t xml:space="preserve">5.21553325653076</t>
   </si>
   <si>
     <t xml:space="preserve">5.19700622558594</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25258922576904</t>
+    <t xml:space="preserve">5.25258874893188</t>
   </si>
   <si>
     <t xml:space="preserve">5.38228225708008</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13215923309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10436820983887</t>
+    <t xml:space="preserve">5.1321587562561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10436773300171</t>
   </si>
   <si>
     <t xml:space="preserve">5.28038024902344</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">5.2340612411499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08583974838257</t>
+    <t xml:space="preserve">5.08584022521973</t>
   </si>
   <si>
     <t xml:space="preserve">5.05804872512817</t>
@@ -3500,37 +3500,37 @@
     <t xml:space="preserve">5.15068674087524</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00246524810791</t>
+    <t xml:space="preserve">5.00246572494507</t>
   </si>
   <si>
     <t xml:space="preserve">4.8635082244873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91909074783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97467374801636</t>
+    <t xml:space="preserve">4.91909122467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97467422485352</t>
   </si>
   <si>
     <t xml:space="preserve">4.96541023254395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22479724884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33596324920654</t>
+    <t xml:space="preserve">5.22479772567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3359637260437</t>
   </si>
   <si>
     <t xml:space="preserve">5.30817174911499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45639324188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52123975753784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29890823364258</t>
+    <t xml:space="preserve">5.45639276504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52123928070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29890775680542</t>
   </si>
   <si>
     <t xml:space="preserve">5.46565675735474</t>
@@ -3542,16 +3542,16 @@
     <t xml:space="preserve">5.67872476577759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76209926605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90105676651001</t>
+    <t xml:space="preserve">5.76209878921509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90105628967285</t>
   </si>
   <si>
     <t xml:space="preserve">5.91958427429199</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70651578903198</t>
+    <t xml:space="preserve">5.70651626586914</t>
   </si>
   <si>
     <t xml:space="preserve">5.74357128143311</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">5.63240575790405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54903125762939</t>
+    <t xml:space="preserve">5.54903078079224</t>
   </si>
   <si>
     <t xml:space="preserve">5.64166975021362</t>
@@ -3587,16 +3587,16 @@
     <t xml:space="preserve">6.74406480789185</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70700931549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79964780807495</t>
+    <t xml:space="preserve">6.70700883865356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79964828491211</t>
   </si>
   <si>
     <t xml:space="preserve">6.82743883132935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79038381576538</t>
+    <t xml:space="preserve">6.79038333892822</t>
   </si>
   <si>
     <t xml:space="preserve">6.89228582382202</t>
@@ -3623,34 +3623,34 @@
     <t xml:space="preserve">7.48517084121704</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42958784103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55928134918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39253282546997</t>
+    <t xml:space="preserve">7.42958831787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55928087234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39253234863281</t>
   </si>
   <si>
     <t xml:space="preserve">7.59633636474609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54075336456299</t>
+    <t xml:space="preserve">7.54075384140015</t>
   </si>
   <si>
     <t xml:space="preserve">7.64265584945679</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50369882583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63339185714722</t>
+    <t xml:space="preserve">7.50369834899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63339138031006</t>
   </si>
   <si>
     <t xml:space="preserve">7.62412786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57780933380127</t>
+    <t xml:space="preserve">7.57780885696411</t>
   </si>
   <si>
     <t xml:space="preserve">7.58707237243652</t>
@@ -3668,13 +3668,13 @@
     <t xml:space="preserve">7.32768535614014</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10535383224487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18872785568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42032384872437</t>
+    <t xml:space="preserve">7.10535430908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18872833251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42032432556152</t>
   </si>
   <si>
     <t xml:space="preserve">7.30915784835815</t>
@@ -3689,7 +3689,7 @@
     <t xml:space="preserve">7.29989433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24431133270264</t>
+    <t xml:space="preserve">7.24431180953979</t>
   </si>
   <si>
     <t xml:space="preserve">7.21651983261108</t>
@@ -3704,37 +3704,37 @@
     <t xml:space="preserve">7.33694934844971</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31842184066772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26283884048462</t>
+    <t xml:space="preserve">7.31842231750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26283931732178</t>
   </si>
   <si>
     <t xml:space="preserve">7.12388181686401</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04977083206177</t>
+    <t xml:space="preserve">7.04977130889893</t>
   </si>
   <si>
     <t xml:space="preserve">6.98492383956909</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07756185531616</t>
+    <t xml:space="preserve">7.07756233215332</t>
   </si>
   <si>
     <t xml:space="preserve">7.22578382492065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1979923248291</t>
+    <t xml:space="preserve">7.19799184799194</t>
   </si>
   <si>
     <t xml:space="preserve">7.15167284011841</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11461782455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05903482437134</t>
+    <t xml:space="preserve">7.11461734771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05903434753418</t>
   </si>
   <si>
     <t xml:space="preserve">7.06857395172119</t>
@@ -3749,34 +3749,34 @@
     <t xml:space="preserve">6.94456434249878</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86825037002563</t>
+    <t xml:space="preserve">6.86824989318848</t>
   </si>
   <si>
     <t xml:space="preserve">6.79193639755249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75377893447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84917116165161</t>
+    <t xml:space="preserve">6.75377941131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84917163848877</t>
   </si>
   <si>
     <t xml:space="preserve">6.99226045608521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95410299301147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87778949737549</t>
+    <t xml:space="preserve">6.95410346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87778902053833</t>
   </si>
   <si>
     <t xml:space="preserve">6.98272132873535</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96364307403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03041696548462</t>
+    <t xml:space="preserve">6.96364259719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03041744232178</t>
   </si>
   <si>
     <t xml:space="preserve">7.01133871078491</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">6.78239727020264</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72516202926636</t>
+    <t xml:space="preserve">6.7251615524292</t>
   </si>
   <si>
     <t xml:space="preserve">7.00179958343506</t>
@@ -3815,19 +3815,19 @@
     <t xml:space="preserve">7.36429023742676</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28797626495361</t>
+    <t xml:space="preserve">7.28797674179077</t>
   </si>
   <si>
     <t xml:space="preserve">7.29751586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30705451965332</t>
+    <t xml:space="preserve">7.30705499649048</t>
   </si>
   <si>
     <t xml:space="preserve">7.53599691390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57415342330933</t>
+    <t xml:space="preserve">7.57415390014648</t>
   </si>
   <si>
     <t xml:space="preserve">7.66000652313232</t>
@@ -3836,10 +3836,10 @@
     <t xml:space="preserve">7.6981635093689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93664407730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98434019088745</t>
+    <t xml:space="preserve">7.93664455413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98434066772461</t>
   </si>
   <si>
     <t xml:space="preserve">8.18466472625732</t>
@@ -3857,19 +3857,19 @@
     <t xml:space="preserve">8.16558647155762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04157638549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87940979003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9748010635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03203773498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90802669525146</t>
+    <t xml:space="preserve">8.04157733917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8794093132019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97480154037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03203678131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90802717208862</t>
   </si>
   <si>
     <t xml:space="preserve">7.89848756790161</t>
@@ -3881,7 +3881,7 @@
     <t xml:space="preserve">7.84125232696533</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88894891738892</t>
+    <t xml:space="preserve">7.88894844055176</t>
   </si>
   <si>
     <t xml:space="preserve">7.78401708602905</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">7.81263399124146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85079145431519</t>
+    <t xml:space="preserve">7.85079050064087</t>
   </si>
   <si>
     <t xml:space="preserve">7.77447748184204</t>
@@ -3905,13 +3905,13 @@
     <t xml:space="preserve">7.72678184509277</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64092826843262</t>
+    <t xml:space="preserve">7.64092874526978</t>
   </si>
   <si>
     <t xml:space="preserve">7.58369255065918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38336849212646</t>
+    <t xml:space="preserve">7.38336896896362</t>
   </si>
   <si>
     <t xml:space="preserve">7.3356728553772</t>
@@ -3932,7 +3932,7 @@
     <t xml:space="preserve">7.08765268325806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15442752838135</t>
+    <t xml:space="preserve">7.15442705154419</t>
   </si>
   <si>
     <t xml:space="preserve">7.03995656967163</t>
@@ -3944,7 +3944,7 @@
     <t xml:space="preserve">7.27843761444092</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41198682785034</t>
+    <t xml:space="preserve">7.41198635101318</t>
   </si>
   <si>
     <t xml:space="preserve">7.39290809631348</t>
@@ -3965,13 +3965,13 @@
     <t xml:space="preserve">7.45014333724976</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40244722366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50737905502319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70770311355591</t>
+    <t xml:space="preserve">7.40244770050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50737857818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70770263671875</t>
   </si>
   <si>
     <t xml:space="preserve">8.20374393463135</t>
@@ -3986,10 +3986,10 @@
     <t xml:space="preserve">8.10835075378418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08927154541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36591148376465</t>
+    <t xml:space="preserve">8.08927249908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36591053009033</t>
   </si>
   <si>
     <t xml:space="preserve">8.30867481231689</t>
@@ -4007,13 +4007,13 @@
     <t xml:space="preserve">8.60439205169678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40406799316406</t>
+    <t xml:space="preserve">8.40406703948975</t>
   </si>
   <si>
     <t xml:space="preserve">8.41360664367676</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26097869873047</t>
+    <t xml:space="preserve">8.26097774505615</t>
   </si>
   <si>
     <t xml:space="preserve">8.57577323913574</t>
@@ -4028,10 +4028,10 @@
     <t xml:space="preserve">8.76655769348145</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15766716003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19582366943359</t>
+    <t xml:space="preserve">9.1576681137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19582462310791</t>
   </si>
   <si>
     <t xml:space="preserve">9.11951065063477</t>
@@ -4040,13 +4040,13 @@
     <t xml:space="preserve">9.10043144226074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09089279174805</t>
+    <t xml:space="preserve">9.09089183807373</t>
   </si>
   <si>
     <t xml:space="preserve">8.72840118408203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87148952484131</t>
+    <t xml:space="preserve">8.87149047851562</t>
   </si>
   <si>
     <t xml:space="preserve">8.90964698791504</t>
@@ -4070,7 +4070,7 @@
     <t xml:space="preserve">9.00503826141357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20536231994629</t>
+    <t xml:space="preserve">9.20536327362061</t>
   </si>
   <si>
     <t xml:space="preserve">9.45338344573975</t>
@@ -4079,25 +4079,25 @@
     <t xml:space="preserve">9.50107955932617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52969646453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.577392578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47246265411377</t>
+    <t xml:space="preserve">9.52969741821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57739353179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47246170043945</t>
   </si>
   <si>
     <t xml:space="preserve">9.36752986907959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30075550079346</t>
+    <t xml:space="preserve">9.30075454711914</t>
   </si>
   <si>
     <t xml:space="preserve">9.39614772796631</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44384384155273</t>
+    <t xml:space="preserve">9.44384288787842</t>
   </si>
   <si>
     <t xml:space="preserve">9.49153995513916</t>
@@ -4109,7 +4109,7 @@
     <t xml:space="preserve">8.69978332519531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55669593811035</t>
+    <t xml:space="preserve">8.55669498443604</t>
   </si>
   <si>
     <t xml:space="preserve">8.62346935272217</t>
@@ -4118,10 +4118,10 @@
     <t xml:space="preserve">8.48038101196289</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59485244750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70932197570801</t>
+    <t xml:space="preserve">8.59485149383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70932292938232</t>
   </si>
   <si>
     <t xml:space="preserve">8.77609729766846</t>
@@ -4133,10 +4133,10 @@
     <t xml:space="preserve">8.75701904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8619499206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89056873321533</t>
+    <t xml:space="preserve">8.86195087432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89056777954102</t>
   </si>
   <si>
     <t xml:space="preserve">8.67116546630859</t>
@@ -4151,10 +4151,10 @@
     <t xml:space="preserve">8.74748039245605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01457786560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92872524261475</t>
+    <t xml:space="preserve">9.0145788192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92872428894043</t>
   </si>
   <si>
     <t xml:space="preserve">8.97642135620117</t>
@@ -4166,28 +4166,28 @@
     <t xml:space="preserve">9.46292304992676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74909973144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78725624084473</t>
+    <t xml:space="preserve">9.74910068511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78725719451904</t>
   </si>
   <si>
     <t xml:space="preserve">9.92080497741699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99711990356445</t>
+    <t xml:space="preserve">9.99711894989014</t>
   </si>
   <si>
     <t xml:space="preserve">9.69186401367188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7681770324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80633544921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63462924957275</t>
+    <t xml:space="preserve">9.76817798614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80633449554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63462829589844</t>
   </si>
   <si>
     <t xml:space="preserve">9.67278575897217</t>
@@ -4196,10 +4196,10 @@
     <t xml:space="preserve">9.59647178649902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7109432220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52015781402588</t>
+    <t xml:space="preserve">9.71094226837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52015686035156</t>
   </si>
   <si>
     <t xml:space="preserve">9.43430519104004</t>
@@ -4208,13 +4208,13 @@
     <t xml:space="preserve">9.25305938720703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28167724609375</t>
+    <t xml:space="preserve">9.28167629241943</t>
   </si>
   <si>
     <t xml:space="preserve">9.34845161437988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41522598266602</t>
+    <t xml:space="preserve">9.41522693634033</t>
   </si>
   <si>
     <t xml:space="preserve">9.48200035095215</t>
@@ -4232,7 +4232,7 @@
     <t xml:space="preserve">9.65370750427246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86357021331787</t>
+    <t xml:space="preserve">9.86357116699219</t>
   </si>
   <si>
     <t xml:space="preserve">10.0204467773438</t>
@@ -4989,6 +4989,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.8999996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8600006103516</t>
   </si>
 </sst>
 </file>
@@ -71289,7 +71292,7 @@
     </row>
     <row r="2538">
       <c r="A2538" s="1" t="n">
-        <v>46013.6912384259</v>
+        <v>46013.3333333333</v>
       </c>
       <c r="B2538" t="n">
         <v>152275</v>
@@ -71310,6 +71313,32 @@
         <v>1658</v>
       </c>
       <c r="H2538" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2539">
+      <c r="A2539" s="1" t="n">
+        <v>46014.69125</v>
+      </c>
+      <c r="B2539" t="n">
+        <v>54883</v>
+      </c>
+      <c r="C2539" t="n">
+        <v>18.9599990844727</v>
+      </c>
+      <c r="D2539" t="n">
+        <v>18.7600002288818</v>
+      </c>
+      <c r="E2539" t="n">
+        <v>18.8400001525879</v>
+      </c>
+      <c r="F2539" t="n">
+        <v>18.8600006103516</v>
+      </c>
+      <c r="G2539" t="s">
+        <v>1659</v>
+      </c>
+      <c r="H2539" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CEM.MI.xlsx
+++ b/data/CEM.MI.xlsx
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70432090759277</t>
+    <t xml:space="preserve">4.70432138442993</t>
   </si>
   <si>
     <t xml:space="preserve">CEM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68036031723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55656147003174</t>
+    <t xml:space="preserve">4.68036127090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5565619468689</t>
   </si>
   <si>
     <t xml:space="preserve">4.48867273330688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32893419265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22111034393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32494068145752</t>
+    <t xml:space="preserve">4.32893323898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22110939025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3249397277832</t>
   </si>
   <si>
     <t xml:space="preserve">4.28899908065796</t>
@@ -68,73 +68,73 @@
     <t xml:space="preserve">4.29299259185791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06137084960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93597483634949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97431254386902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67560005187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83533954620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94875407218933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88006663322449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91680645942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87846875190735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7458860874176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93437814712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87367796897888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73789858818054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57815957069397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59892606735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61969137191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35132932662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15005803108215</t>
+    <t xml:space="preserve">4.06137037277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93597459793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9743127822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67560052871704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83533930778503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94875478744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88006687164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91680598258972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87846946716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74588561058044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93437767028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87367701530457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7378990650177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57815933227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59892535209656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61969184875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35132956504822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15005826950073</t>
   </si>
   <si>
     <t xml:space="preserve">3.25069379806519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13088941574097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20916175842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44238066673279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3625111579895</t>
+    <t xml:space="preserve">3.13088965415955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20916199684143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44238114356995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36251139640808</t>
   </si>
   <si>
     <t xml:space="preserve">3.47592616081238</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">3.55419850349426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34653735160828</t>
+    <t xml:space="preserve">3.34653759002686</t>
   </si>
   <si>
     <t xml:space="preserve">3.39126420021057</t>
@@ -155,163 +155,163 @@
     <t xml:space="preserve">3.23951244354248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2922260761261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40244650840759</t>
+    <t xml:space="preserve">3.29222655296326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40244626998901</t>
   </si>
   <si>
     <t xml:space="preserve">3.58614611625671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63406825065613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55579566955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64365196228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56058812141418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52065372467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4982898235321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52544546127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54940629005432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75227546691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61330223083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75387239456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83214521408081</t>
+    <t xml:space="preserve">3.63406777381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55579614639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64365243911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56058883666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52065348625183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49828958511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52544522285461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54940605163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75227475166321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61330199241638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75387167930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83214497566223</t>
   </si>
   <si>
     <t xml:space="preserve">3.67080760002136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70754790306091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65802931785583</t>
+    <t xml:space="preserve">3.70754814147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65802836418152</t>
   </si>
   <si>
     <t xml:space="preserve">3.51745796203613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57017230987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50947141647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54301643371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57975625991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45196533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41043281555176</t>
+    <t xml:space="preserve">3.57017159461975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50947165489197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54301714897156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57975673675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45196557044983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41043305397034</t>
   </si>
   <si>
     <t xml:space="preserve">3.37529039382935</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60052299499512</t>
+    <t xml:space="preserve">3.60052275657654</t>
   </si>
   <si>
     <t xml:space="preserve">3.48551034927368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54461479187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59573030471802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77943110466003</t>
+    <t xml:space="preserve">3.5446138381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59573078155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77943086624146</t>
   </si>
   <si>
     <t xml:space="preserve">3.74428844451904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8577024936676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73949575424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74907970428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70595097541809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69317126274109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6771981716156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79700207710266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.666015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70115852355957</t>
+    <t xml:space="preserve">3.85770320892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73949599266052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74908041954041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70595121383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69317173957825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67719769477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7970027923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66601634025574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70115876197815</t>
   </si>
   <si>
     <t xml:space="preserve">3.62608098983765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67400240898132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64205479621887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53023767471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45835471153259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47432827949524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53193688392639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62187004089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75758814811707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7608585357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87531995773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88349580764771</t>
+    <t xml:space="preserve">3.67400288581848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64205503463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53023743629456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45835494995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4743287563324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53193712234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62187075614929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75758862495422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76085901260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.875319480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88349556922913</t>
   </si>
   <si>
     <t xml:space="preserve">3.7772102355957</t>
@@ -326,43 +326,43 @@
     <t xml:space="preserve">3.6692898273468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59734344482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58426141738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55646371841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38640856742859</t>
+    <t xml:space="preserve">3.59734296798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58426189422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55646419525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38640832901001</t>
   </si>
   <si>
     <t xml:space="preserve">3.31119108200073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29810953140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19673037528992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15912175178528</t>
+    <t xml:space="preserve">3.29810976982117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19672989845276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1591215133667</t>
   </si>
   <si>
     <t xml:space="preserve">3.00705194473267</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15421628952026</t>
+    <t xml:space="preserve">3.15421605110168</t>
   </si>
   <si>
     <t xml:space="preserve">3.03484964370728</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22289299964905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35206985473633</t>
+    <t xml:space="preserve">3.22289228439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35206961631775</t>
   </si>
   <si>
     <t xml:space="preserve">3.10679626464844</t>
@@ -371,10 +371,10 @@
     <t xml:space="preserve">2.82881999015808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82064461708069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84026622772217</t>
+    <t xml:space="preserve">2.82064414024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84026598930359</t>
   </si>
   <si>
     <t xml:space="preserve">2.93510508537292</t>
@@ -383,16 +383,16 @@
     <t xml:space="preserve">3.04302525520325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95799684524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79611659049988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76341342926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76831912994385</t>
+    <t xml:space="preserve">2.9579975605011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79611706733704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76341366767883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76831889152527</t>
   </si>
   <si>
     <t xml:space="preserve">2.84844160079956</t>
@@ -401,19 +401,19 @@
     <t xml:space="preserve">2.87787437438965</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04139018058777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00051140785217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2114462852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13295936584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07572841644287</t>
+    <t xml:space="preserve">3.04139041900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00051164627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21144652366638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13295912742615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07572817802429</t>
   </si>
   <si>
     <t xml:space="preserve">2.97434902191162</t>
@@ -422,79 +422,79 @@
     <t xml:space="preserve">3.1084315776825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97598433494568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92856407165527</t>
+    <t xml:space="preserve">2.97598385810852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92856431007385</t>
   </si>
   <si>
     <t xml:space="preserve">3.1754732131958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18037867546082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15585112571716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18855452537537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09862041473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12151265144348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02503871917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11660718917847</t>
+    <t xml:space="preserve">3.18037843704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15585088729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18855404853821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09862065315247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12151336669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02503848075867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11660766601562</t>
   </si>
   <si>
     <t xml:space="preserve">3.23760890960693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28012299537659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32263708114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43546271324158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40603017807007</t>
+    <t xml:space="preserve">3.28012323379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32263731956482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.435462474823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40602993965149</t>
   </si>
   <si>
     <t xml:space="preserve">3.46653032302856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43709850311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44854426383972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67910146713257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64639830589294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71834468841553</t>
+    <t xml:space="preserve">3.43709826469421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44854402542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67910075187683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64639806747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71834444999695</t>
   </si>
   <si>
     <t xml:space="preserve">3.69545269012451</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74450778961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85242748260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80827856063843</t>
+    <t xml:space="preserve">3.7445068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85242676734924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80827832221985</t>
   </si>
   <si>
     <t xml:space="preserve">3.82299470901489</t>
@@ -503,181 +503,181 @@
     <t xml:space="preserve">3.80337309837341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74287271499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62350630760193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56627511978149</t>
+    <t xml:space="preserve">3.74287223815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62350583076477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56627535820007</t>
   </si>
   <si>
     <t xml:space="preserve">3.47470641136169</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51558542251587</t>
+    <t xml:space="preserve">3.51558566093445</t>
   </si>
   <si>
     <t xml:space="preserve">3.65947914123535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60551881790161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54501819610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64803338050842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64476275444031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38804364204407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48288249969482</t>
+    <t xml:space="preserve">3.60551905632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54501843452454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64803290367126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64476299285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38804316520691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4828827381134</t>
   </si>
   <si>
     <t xml:space="preserve">3.45344972610474</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43382740020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50741004943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56464004516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55482912063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56300497055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48451709747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54338359832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62514066696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59080266952515</t>
+    <t xml:space="preserve">3.4338276386261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50740957260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56464028358459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55482935905457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56300473213196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48451733589172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54338312149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62514114379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59080243110657</t>
   </si>
   <si>
     <t xml:space="preserve">3.64149236679077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6889123916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66111469268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6872763633728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53684258460999</t>
+    <t xml:space="preserve">3.68891191482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66111421585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68727684020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53684282302856</t>
   </si>
   <si>
     <t xml:space="preserve">3.63004636764526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63822197914124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43873357772827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41747570037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41911125183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33571815490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37169194221497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27521753311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22125768661499</t>
+    <t xml:space="preserve">3.63822221755981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43873310089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.417475938797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41911149024963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33571839332581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37169170379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27521777153015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22125744819641</t>
   </si>
   <si>
     <t xml:space="preserve">3.2098114490509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17710781097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21308135986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14767503738403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11333703994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00541663169861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0168628692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95309162139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91875338554382</t>
+    <t xml:space="preserve">3.1771080493927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21308183670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14767527580261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11333751678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00541687011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01686263084412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9530918598175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9187536239624</t>
   </si>
   <si>
     <t xml:space="preserve">2.96453785896301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96780824661255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95636177062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04793095588684</t>
+    <t xml:space="preserve">2.96780848503113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95636200904846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04793071746826</t>
   </si>
   <si>
     <t xml:space="preserve">3.17220258712769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18691897392273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3193666934967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23433828353882</t>
+    <t xml:space="preserve">3.18691945075989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31936645507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23433876037598</t>
   </si>
   <si>
     <t xml:space="preserve">3.45835518836975</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48778772354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45181393623352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49923419952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57281589508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45017862319946</t>
+    <t xml:space="preserve">3.48778748512268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45181465148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49923372268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57281637191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45017886161804</t>
   </si>
   <si>
     <t xml:space="preserve">3.61369514465332</t>
@@ -686,112 +686,112 @@
     <t xml:space="preserve">3.67746567726135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58916711807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70362854003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48615264892578</t>
+    <t xml:space="preserve">3.58916735649109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70362877845764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48615288734436</t>
   </si>
   <si>
     <t xml:space="preserve">3.33244800567627</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28666377067566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22943305969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27031230926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24741983413696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23106861114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2327036857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26213598251343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27685236930847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23597383499146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0012264251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04701042175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1287693977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16964721679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17782306671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06336259841919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95707774162292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19417524337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28410911560059</t>
+    <t xml:space="preserve">3.28666353225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22943329811096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27031207084656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24741959571838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23106813430786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23270344734192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26213622093201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27685284614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2359733581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00122594833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04701137542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12876892089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16964769363403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17782402038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06336212158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95707845687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19417572021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28410816192627</t>
   </si>
   <si>
     <t xml:space="preserve">4.34542798995972</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47215127944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43944835662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41083335876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41492128372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37404251098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26775646209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39039373397827</t>
+    <t xml:space="preserve">4.47215175628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43944787979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41083383560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41492080688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37404203414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26775693893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39039421081543</t>
   </si>
   <si>
     <t xml:space="preserve">4.3617787361145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3781304359436</t>
+    <t xml:space="preserve">4.37812995910645</t>
   </si>
   <si>
     <t xml:space="preserve">4.386305809021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56208562850952</t>
+    <t xml:space="preserve">4.56208515167236</t>
   </si>
   <si>
     <t xml:space="preserve">4.42718458175659</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32907629013062</t>
+    <t xml:space="preserve">4.3290753364563</t>
   </si>
   <si>
     <t xml:space="preserve">4.25549411773682</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">4.30046081542969</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34951543807983</t>
+    <t xml:space="preserve">4.34951496124268</t>
   </si>
   <si>
     <t xml:space="preserve">4.24322938919067</t>
@@ -815,85 +815,85 @@
     <t xml:space="preserve">4.21052742004395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1451210975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10424089431763</t>
+    <t xml:space="preserve">4.14512062072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10424184799194</t>
   </si>
   <si>
     <t xml:space="preserve">4.22279024124146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40674543380737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36586761474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27593326568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3045482635498</t>
+    <t xml:space="preserve">4.40674495697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36586713790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27593278884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30454778671265</t>
   </si>
   <si>
     <t xml:space="preserve">4.28002071380615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44762468338013</t>
+    <t xml:space="preserve">4.44762516021729</t>
   </si>
   <si>
     <t xml:space="preserve">4.52938222885132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51711893081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52120733261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68063354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66019439697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71333742141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73377656936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81962251663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81144666671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65201854705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34133958816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33725166320801</t>
+    <t xml:space="preserve">4.51711845397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52120637893677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68063449859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66019487380981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71333789825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7337760925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81962203979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81144618988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65201902389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34133911132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33725118637085</t>
   </si>
   <si>
     <t xml:space="preserve">4.25958156585693</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4038348197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44966506958008</t>
+    <t xml:space="preserve">4.40383386611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44966459274292</t>
   </si>
   <si>
     <t xml:space="preserve">4.41633367538452</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37467002868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36633729934692</t>
+    <t xml:space="preserve">4.37466955184937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36633682250977</t>
   </si>
   <si>
     <t xml:space="preserve">4.30384206771851</t>
@@ -902,31 +902,31 @@
     <t xml:space="preserve">4.27467775344849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25801181793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31634092330933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26634502410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20801639556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33300638198853</t>
+    <t xml:space="preserve">4.25801277160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31634140014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26634454727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20801591873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33300590515137</t>
   </si>
   <si>
     <t xml:space="preserve">4.37050342559814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34550523757935</t>
+    <t xml:space="preserve">4.3455057144165</t>
   </si>
   <si>
     <t xml:space="preserve">4.39133501052856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29967498779297</t>
+    <t xml:space="preserve">4.29967546463013</t>
   </si>
   <si>
     <t xml:space="preserve">4.4288330078125</t>
@@ -941,7 +941,7 @@
     <t xml:space="preserve">4.38300275802612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46633052825928</t>
+    <t xml:space="preserve">4.46632957458496</t>
   </si>
   <si>
     <t xml:space="preserve">4.48299503326416</t>
@@ -950,10 +950,10 @@
     <t xml:space="preserve">4.56632232666016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40800046920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34967136383057</t>
+    <t xml:space="preserve">4.40800094604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34967184066772</t>
   </si>
   <si>
     <t xml:space="preserve">4.69131326675415</t>
@@ -965,25 +965,25 @@
     <t xml:space="preserve">4.85380077362061</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9996223449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05795240402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10794830322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24960422515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28710031509399</t>
+    <t xml:space="preserve">4.99962329864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05795192718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10794878005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24960374832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28710079193115</t>
   </si>
   <si>
     <t xml:space="preserve">5.25377035140991</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41625881195068</t>
+    <t xml:space="preserve">5.41625785827637</t>
   </si>
   <si>
     <t xml:space="preserve">5.30376672744751</t>
@@ -1004,7 +1004,7 @@
     <t xml:space="preserve">5.29126787185669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29543352127075</t>
+    <t xml:space="preserve">5.29543399810791</t>
   </si>
   <si>
     <t xml:space="preserve">5.16211080551147</t>
@@ -1013,16 +1013,16 @@
     <t xml:space="preserve">5.01628828048706</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05378580093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12461376190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20377349853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0746169090271</t>
+    <t xml:space="preserve">5.05378532409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1246132850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20377397537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07461738586426</t>
   </si>
   <si>
     <t xml:space="preserve">5.03295373916626</t>
@@ -1031,49 +1031,49 @@
     <t xml:space="preserve">4.95795917510986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99129009246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96212577819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90796279907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94129371643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89129734039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90379667282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95379257202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94546031951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91629552841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02462148666382</t>
+    <t xml:space="preserve">4.99128913879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96212530136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90796375274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94129467010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89129781723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90379619598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9537935256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94545984268188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91629600524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02462100982666</t>
   </si>
   <si>
     <t xml:space="preserve">5.04961919784546</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11628007888794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17461013793945</t>
+    <t xml:space="preserve">5.11628103256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17460918426514</t>
   </si>
   <si>
     <t xml:space="preserve">5.23293876647949</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17877578735352</t>
+    <t xml:space="preserve">5.17877626419067</t>
   </si>
   <si>
     <t xml:space="preserve">5.1329460144043</t>
@@ -1082,37 +1082,37 @@
     <t xml:space="preserve">5.33293104171753</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26626968383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22460556030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58291244506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68707084655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00371360778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80789470672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07454204559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01621246337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16620206832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89122200012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94121885299683</t>
+    <t xml:space="preserve">5.26626873016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22460651397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5829119682312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68707132339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00371408462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80789518356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07454252243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01621294021606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1662015914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89122247695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94121837615967</t>
   </si>
   <si>
     <t xml:space="preserve">5.96621656417847</t>
@@ -1121,22 +1121,22 @@
     <t xml:space="preserve">6.03287792205811</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99538087844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97038269042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91622066497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86205816268921</t>
+    <t xml:space="preserve">5.99538135528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.970383644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91622018814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86205768585205</t>
   </si>
   <si>
     <t xml:space="preserve">5.92871952056885</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89955472946167</t>
+    <t xml:space="preserve">5.89955520629883</t>
   </si>
   <si>
     <t xml:space="preserve">5.90372133255005</t>
@@ -1148,58 +1148,58 @@
     <t xml:space="preserve">5.84539270401001</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00788021087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98288202285767</t>
+    <t xml:space="preserve">6.00787973403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98288249969482</t>
   </si>
   <si>
     <t xml:space="preserve">6.03704452514648</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0912070274353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02871179580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99954748153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04954385757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07870817184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29119205474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1745343208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1995325088501</t>
+    <t xml:space="preserve">6.09120750427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0287127494812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99954700469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04954433441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07870769500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29119253158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17453384399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19953298568726</t>
   </si>
   <si>
     <t xml:space="preserve">6.08287477493286</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24536180496216</t>
+    <t xml:space="preserve">6.24536228179932</t>
   </si>
   <si>
     <t xml:space="preserve">6.21203136444092</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02454566955566</t>
+    <t xml:space="preserve">6.02454519271851</t>
   </si>
   <si>
     <t xml:space="preserve">6.09954071044922</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18286752700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20786571502686</t>
+    <t xml:space="preserve">6.18286657333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20786476135254</t>
   </si>
   <si>
     <t xml:space="preserve">6.22036409378052</t>
@@ -1208,43 +1208,43 @@
     <t xml:space="preserve">6.14537000656128</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95788383483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94538545608521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01204681396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02037858963013</t>
+    <t xml:space="preserve">5.95788431167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94538497924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01204633712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02037906646729</t>
   </si>
   <si>
     <t xml:space="preserve">6.11620569229126</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06204223632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04121065139771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1495361328125</t>
+    <t xml:space="preserve">6.06204319000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04121160507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14953565597534</t>
   </si>
   <si>
     <t xml:space="preserve">6.09537363052368</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35785388946533</t>
+    <t xml:space="preserve">6.35785341262817</t>
   </si>
   <si>
     <t xml:space="preserve">6.22453022003174</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28285932540894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58283662796021</t>
+    <t xml:space="preserve">6.28285980224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58283710479736</t>
   </si>
   <si>
     <t xml:space="preserve">6.6161675453186</t>
@@ -1253,13 +1253,13 @@
     <t xml:space="preserve">6.57450389862061</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50784254074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49951028823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65783166885376</t>
+    <t xml:space="preserve">6.50784158706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49950981140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6578311920166</t>
   </si>
   <si>
     <t xml:space="preserve">6.7411584854126</t>
@@ -1268,37 +1268,37 @@
     <t xml:space="preserve">6.59116983413696</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62449932098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6328330039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70782709121704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52450799942017</t>
+    <t xml:space="preserve">6.6245002746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63283348083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7078275680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52450752258301</t>
   </si>
   <si>
     <t xml:space="preserve">6.51617527008057</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66616439819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54950571060181</t>
+    <t xml:space="preserve">6.6661639213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54950618743896</t>
   </si>
   <si>
     <t xml:space="preserve">6.44951295852661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29952430725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23286390304565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90788793563843</t>
+    <t xml:space="preserve">6.29952478408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23286294937134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90788745880127</t>
   </si>
   <si>
     <t xml:space="preserve">5.93288564682007</t>
@@ -1307,37 +1307,37 @@
     <t xml:space="preserve">6.53284072875977</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26619386672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36618614196777</t>
+    <t xml:space="preserve">6.26619434356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36618709564209</t>
   </si>
   <si>
     <t xml:space="preserve">6.33285570144653</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1412034034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15786933898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06620931625366</t>
+    <t xml:space="preserve">6.14120388031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15786838531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0662088394165</t>
   </si>
   <si>
     <t xml:space="preserve">5.94955110549927</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13287115097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05787658691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88288927078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84955883026123</t>
+    <t xml:space="preserve">6.1328706741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0578761100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88289022445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84955835342407</t>
   </si>
   <si>
     <t xml:space="preserve">5.81622791290283</t>
@@ -1349,13 +1349,13 @@
     <t xml:space="preserve">5.75789928436279</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76623153686523</t>
+    <t xml:space="preserve">5.76623201370239</t>
   </si>
   <si>
     <t xml:space="preserve">5.6829047203064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82456111907959</t>
+    <t xml:space="preserve">5.82456064224243</t>
   </si>
   <si>
     <t xml:space="preserve">5.86622428894043</t>
@@ -1364,22 +1364,22 @@
     <t xml:space="preserve">5.77456474304199</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78289699554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79122924804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63290786743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6498236656189</t>
+    <t xml:space="preserve">5.78289747238159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79123067855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6329083442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64982414245605</t>
   </si>
   <si>
     <t xml:space="preserve">5.68365526199341</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66673994064331</t>
+    <t xml:space="preserve">5.66673946380615</t>
   </si>
   <si>
     <t xml:space="preserve">5.70057106018066</t>
@@ -1388,13 +1388,13 @@
     <t xml:space="preserve">5.48066759109497</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45529460906982</t>
+    <t xml:space="preserve">5.45529365539551</t>
   </si>
   <si>
     <t xml:space="preserve">5.54833030700684</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53987264633179</t>
+    <t xml:space="preserve">5.5398736000061</t>
   </si>
   <si>
     <t xml:space="preserve">5.74285984039307</t>
@@ -1403,10 +1403,10 @@
     <t xml:space="preserve">5.58216142654419</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6582818031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70902872085571</t>
+    <t xml:space="preserve">5.65828132629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70902919769287</t>
   </si>
   <si>
     <t xml:space="preserve">5.77669095993042</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">5.89510059356689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75131845474243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78514909744263</t>
+    <t xml:space="preserve">5.75131797790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78514957427979</t>
   </si>
   <si>
     <t xml:space="preserve">5.71748638153076</t>
@@ -1433,13 +1433,13 @@
     <t xml:space="preserve">5.81052255630493</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56524610519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50604152679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69211292266846</t>
+    <t xml:space="preserve">5.56524515151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50604200363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69211387634277</t>
   </si>
   <si>
     <t xml:space="preserve">5.72594451904297</t>
@@ -1448,16 +1448,16 @@
     <t xml:space="preserve">5.73440265655518</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60753488540649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51449918746948</t>
+    <t xml:space="preserve">5.60753536224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51449966430664</t>
   </si>
   <si>
     <t xml:space="preserve">5.67519760131836</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01351070404053</t>
+    <t xml:space="preserve">6.01351118087769</t>
   </si>
   <si>
     <t xml:space="preserve">5.99659490585327</t>
@@ -1466,25 +1466,25 @@
     <t xml:space="preserve">5.81898069381714</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75977611541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80206489562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79360675811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.886643409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87818479537964</t>
+    <t xml:space="preserve">5.75977563858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80206537246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79360723495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88664293289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87818574905396</t>
   </si>
   <si>
     <t xml:space="preserve">5.92893266677856</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85281181335449</t>
+    <t xml:space="preserve">5.85281229019165</t>
   </si>
   <si>
     <t xml:space="preserve">5.76823377609253</t>
@@ -1493,25 +1493,25 @@
     <t xml:space="preserve">5.82743883132935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83589696884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42992162704468</t>
+    <t xml:space="preserve">5.83589649200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42992115020752</t>
   </si>
   <si>
     <t xml:space="preserve">5.3876314163208</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33688545227051</t>
+    <t xml:space="preserve">5.33688497543335</t>
   </si>
   <si>
     <t xml:space="preserve">5.26076459884644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30305337905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43837928771973</t>
+    <t xml:space="preserve">5.303053855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43837833404541</t>
   </si>
   <si>
     <t xml:space="preserve">5.46375226974487</t>
@@ -1520,31 +1520,31 @@
     <t xml:space="preserve">5.44683694839478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35380029678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37071657180786</t>
+    <t xml:space="preserve">5.35380077362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3707160949707</t>
   </si>
   <si>
     <t xml:space="preserve">5.22693300247192</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14235401153564</t>
+    <t xml:space="preserve">5.14235544204712</t>
   </si>
   <si>
     <t xml:space="preserve">5.11698150634766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24384832382202</t>
+    <t xml:space="preserve">5.24384880065918</t>
   </si>
   <si>
     <t xml:space="preserve">5.13389778137207</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26922273635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25230693817139</t>
+    <t xml:space="preserve">5.26922225952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25230646133423</t>
   </si>
   <si>
     <t xml:space="preserve">5.21001720428467</t>
@@ -1556,22 +1556,22 @@
     <t xml:space="preserve">5.28613805770874</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31996917724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29459619522095</t>
+    <t xml:space="preserve">5.31996965408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29459667205811</t>
   </si>
   <si>
     <t xml:space="preserve">5.48912525177002</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3284273147583</t>
+    <t xml:space="preserve">5.32842683792114</t>
   </si>
   <si>
     <t xml:space="preserve">5.16772842407227</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09160804748535</t>
+    <t xml:space="preserve">5.09160757064819</t>
   </si>
   <si>
     <t xml:space="preserve">5.17618608474731</t>
@@ -1580,37 +1580,37 @@
     <t xml:space="preserve">5.10852384567261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91399335861206</t>
+    <t xml:space="preserve">4.91399383544922</t>
   </si>
   <si>
     <t xml:space="preserve">4.60105466842651</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49956083297729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56722354888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38115072250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5418496131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52493381500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61796998977661</t>
+    <t xml:space="preserve">4.49956035614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56722259521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38115119934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54185009002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5249342918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61797046661377</t>
   </si>
   <si>
     <t xml:space="preserve">4.46572971343994</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27119970321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14433193206787</t>
+    <t xml:space="preserve">4.27119922637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14433240890503</t>
   </si>
   <si>
     <t xml:space="preserve">4.22045230865479</t>
@@ -1619,7 +1619,7 @@
     <t xml:space="preserve">4.09358549118042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20353651046753</t>
+    <t xml:space="preserve">4.20353698730469</t>
   </si>
   <si>
     <t xml:space="preserve">4.15701913833618</t>
@@ -1628,46 +1628,46 @@
     <t xml:space="preserve">4.39806652069092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53339242935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59259653091431</t>
+    <t xml:space="preserve">4.53339195251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59259605407715</t>
   </si>
   <si>
     <t xml:space="preserve">4.60951232910156</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63488578796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41498184204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49110317230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42344045639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43189811706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2965726852417</t>
+    <t xml:space="preserve">4.63488626480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41498231887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49110269546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42343997955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43189764022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29657363891602</t>
   </si>
   <si>
     <t xml:space="preserve">4.33886241912842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19507932662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0470666885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08512687683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10627222061157</t>
+    <t xml:space="preserve">4.19507884979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04706764221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08512735366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10627174377441</t>
   </si>
   <si>
     <t xml:space="preserve">4.15278959274292</t>
@@ -1676,13 +1676,13 @@
     <t xml:space="preserve">4.23736810684204</t>
   </si>
   <si>
-    <t xml:space="preserve">4.216224193573</t>
+    <t xml:space="preserve">4.21622467041016</t>
   </si>
   <si>
     <t xml:space="preserve">4.16124725341797</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10204410552979</t>
+    <t xml:space="preserve">4.10204315185547</t>
   </si>
   <si>
     <t xml:space="preserve">4.03860950469971</t>
@@ -1691,13 +1691,13 @@
     <t xml:space="preserve">4.30503129959106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2542839050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14010381698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05129623413086</t>
+    <t xml:space="preserve">4.25428342819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14010334014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0512957572937</t>
   </si>
   <si>
     <t xml:space="preserve">4.14856147766113</t>
@@ -1709,13 +1709,13 @@
     <t xml:space="preserve">4.03438091278076</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94557332992554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35577821731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3134880065918</t>
+    <t xml:space="preserve">3.94557309150696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35577774047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31348848342896</t>
   </si>
   <si>
     <t xml:space="preserve">4.48264503479004</t>
@@ -1733,7 +1733,7 @@
     <t xml:space="preserve">4.82095766067505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86324739456177</t>
+    <t xml:space="preserve">4.86324691772461</t>
   </si>
   <si>
     <t xml:space="preserve">4.90553617477417</t>
@@ -1745,19 +1745,19 @@
     <t xml:space="preserve">4.95628309249878</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00702953338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01548719406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03240299224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.057776927948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99011373519897</t>
+    <t xml:space="preserve">5.00703001022339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01548862457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03240346908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05777597427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99011421203613</t>
   </si>
   <si>
     <t xml:space="preserve">4.97319889068604</t>
@@ -1766,31 +1766,31 @@
     <t xml:space="preserve">5.20156002044678</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12543916702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15927028656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21847486495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34534311294556</t>
+    <t xml:space="preserve">5.12543964385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1592698097229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21847534179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3453426361084</t>
   </si>
   <si>
     <t xml:space="preserve">5.27767992019653</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40454721450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39608955383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47221040725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49758434295654</t>
+    <t xml:space="preserve">5.4045467376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39608907699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47220993041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49758291244507</t>
   </si>
   <si>
     <t xml:space="preserve">5.42146301269531</t>
@@ -1799,52 +1799,55 @@
     <t xml:space="preserve">5.41300535202026</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98165607452393</t>
+    <t xml:space="preserve">4.98165655136108</t>
   </si>
   <si>
     <t xml:space="preserve">5.11462497711182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13193321228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0194296836853</t>
+    <t xml:space="preserve">5.13193368911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01942920684814</t>
   </si>
   <si>
     <t xml:space="preserve">5.01077461242676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06269931793213</t>
+    <t xml:space="preserve">5.06269979476929</t>
   </si>
   <si>
     <t xml:space="preserve">5.08866262435913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0973162651062</t>
+    <t xml:space="preserve">5.09731674194336</t>
   </si>
   <si>
     <t xml:space="preserve">5.14058780670166</t>
   </si>
   <si>
+    <t xml:space="preserve">5.21847581863403</t>
+  </si>
+  <si>
     <t xml:space="preserve">5.20116710662842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17520380020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2271294593811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26174592971802</t>
+    <t xml:space="preserve">5.17520427703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22712898254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26174688339233</t>
   </si>
   <si>
     <t xml:space="preserve">5.23578405380249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25309228897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33963346481323</t>
+    <t xml:space="preserve">5.25309276580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33963394165039</t>
   </si>
   <si>
     <t xml:space="preserve">5.46079254150391</t>
@@ -1853,7 +1856,7 @@
     <t xml:space="preserve">5.54733419418335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42617607116699</t>
+    <t xml:space="preserve">5.42617559432983</t>
   </si>
   <si>
     <t xml:space="preserve">5.330979347229</t>
@@ -1868,79 +1871,79 @@
     <t xml:space="preserve">5.52137184143066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47810029983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64253091812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76368951797485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74638080596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72907257080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65118503570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7031102180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66849327087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59925937652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49540948867798</t>
+    <t xml:space="preserve">5.47810077667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64253044128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7636890411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74637985229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72907304763794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65118455886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70310974121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66849374771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59925985336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49540901184082</t>
   </si>
   <si>
     <t xml:space="preserve">5.45213842391968</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56464338302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73772621154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51271772384644</t>
+    <t xml:space="preserve">5.56464242935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73772716522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51271820068359</t>
   </si>
   <si>
     <t xml:space="preserve">5.24443769454956</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1838583946228</t>
+    <t xml:space="preserve">5.18385744094849</t>
   </si>
   <si>
     <t xml:space="preserve">5.28770875930786</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19251203536987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12327909469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2704005241394</t>
+    <t xml:space="preserve">5.19251346588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1232795715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27040004730225</t>
   </si>
   <si>
     <t xml:space="preserve">5.08000802993774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14924144744873</t>
+    <t xml:space="preserve">5.14924097061157</t>
   </si>
   <si>
     <t xml:space="preserve">5.16655015945435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15789556503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29636240005493</t>
+    <t xml:space="preserve">5.15789604187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29636287689209</t>
   </si>
   <si>
     <t xml:space="preserve">5.53868055343628</t>
@@ -1952,7 +1955,7 @@
     <t xml:space="preserve">5.48675537109375</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40021276473999</t>
+    <t xml:space="preserve">5.40021228790283</t>
   </si>
   <si>
     <t xml:space="preserve">5.36559629440308</t>
@@ -1964,7 +1967,7 @@
     <t xml:space="preserve">5.38290500640869</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02808237075806</t>
+    <t xml:space="preserve">5.02808332443237</t>
   </si>
   <si>
     <t xml:space="preserve">5.04539155960083</t>
@@ -1973,40 +1976,40 @@
     <t xml:space="preserve">5.16222333908081</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03933429718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10597085952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15270328521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20895576477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27905464172363</t>
+    <t xml:space="preserve">5.03933334350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10597038269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15270376205444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20895528793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27905416488647</t>
   </si>
   <si>
     <t xml:space="preserve">5.3456916809082</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32665300369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27992010116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30588245391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26780462265015</t>
+    <t xml:space="preserve">5.32665252685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27991962432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3058819770813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26780414581299</t>
   </si>
   <si>
     <t xml:space="preserve">5.34742307662964</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21934032440186</t>
+    <t xml:space="preserve">5.21934080123901</t>
   </si>
   <si>
     <t xml:space="preserve">5.34309530258179</t>
@@ -2024,7 +2027,7 @@
     <t xml:space="preserve">5.51791000366211</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61656713485718</t>
+    <t xml:space="preserve">5.61656761169434</t>
   </si>
   <si>
     <t xml:space="preserve">5.51617908477783</t>
@@ -2039,19 +2042,19 @@
     <t xml:space="preserve">5.46771574020386</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44434928894043</t>
+    <t xml:space="preserve">5.44434976577759</t>
   </si>
   <si>
     <t xml:space="preserve">5.46944665908813</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78099679946899</t>
+    <t xml:space="preserve">5.78099775314331</t>
   </si>
   <si>
     <t xml:space="preserve">6.02331447601318</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0406231880188</t>
+    <t xml:space="preserve">6.04062271118164</t>
   </si>
   <si>
     <t xml:space="preserve">6.04927730560303</t>
@@ -2075,10 +2078,10 @@
     <t xml:space="preserve">5.73945713043213</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81042242050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90561771392822</t>
+    <t xml:space="preserve">5.81042194366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90561819076538</t>
   </si>
   <si>
     <t xml:space="preserve">5.93331098556519</t>
@@ -2087,22 +2090,22 @@
     <t xml:space="preserve">5.94109964370728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9108099937439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92638778686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85369253158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85628938674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68060874938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73253393173218</t>
+    <t xml:space="preserve">5.91081047058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92638826370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85369300842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85628890991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68060922622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73253440856934</t>
   </si>
   <si>
     <t xml:space="preserve">5.81907558441162</t>
@@ -2111,10 +2114,10 @@
     <t xml:space="preserve">5.90648317337036</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70570611953735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57502841949463</t>
+    <t xml:space="preserve">5.7057056427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57502746582031</t>
   </si>
   <si>
     <t xml:space="preserve">5.75590085983276</t>
@@ -2129,10 +2132,10 @@
     <t xml:space="preserve">5.73513031005859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72041845321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69791746139526</t>
+    <t xml:space="preserve">5.72041797637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69791698455811</t>
   </si>
   <si>
     <t xml:space="preserve">5.69272470474243</t>
@@ -2141,16 +2144,16 @@
     <t xml:space="preserve">5.62868404388428</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75936222076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6581072807312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57243204116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62522220611572</t>
+    <t xml:space="preserve">5.75936269760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65810823440552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5724310874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62522172927856</t>
   </si>
   <si>
     <t xml:space="preserve">5.6728196144104</t>
@@ -2159,13 +2162,13 @@
     <t xml:space="preserve">5.58195114135742</t>
   </si>
   <si>
-    <t xml:space="preserve">5.584547996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6451268196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72561073303223</t>
+    <t xml:space="preserve">5.58454704284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64512586593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72561025619507</t>
   </si>
   <si>
     <t xml:space="preserve">5.61483716964722</t>
@@ -2174,7 +2177,7 @@
     <t xml:space="preserve">5.60704898834229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65291547775269</t>
+    <t xml:space="preserve">5.65291500091553</t>
   </si>
   <si>
     <t xml:space="preserve">5.6555118560791</t>
@@ -2186,31 +2189,31 @@
     <t xml:space="preserve">5.84071111679077</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00600671768188</t>
+    <t xml:space="preserve">6.00600624084473</t>
   </si>
   <si>
     <t xml:space="preserve">5.92811870574951</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87619256973267</t>
+    <t xml:space="preserve">5.87619352340698</t>
   </si>
   <si>
     <t xml:space="preserve">5.71436071395874</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4218487739563</t>
+    <t xml:space="preserve">5.42184829711914</t>
   </si>
   <si>
     <t xml:space="preserve">5.36213541030884</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19510889053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04019927978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15443420410156</t>
+    <t xml:space="preserve">5.19510936737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.040198802948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15443325042725</t>
   </si>
   <si>
     <t xml:space="preserve">5.18039703369141</t>
@@ -2222,43 +2225,43 @@
     <t xml:space="preserve">4.24358129501343</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30113124847412</t>
+    <t xml:space="preserve">4.30113172531128</t>
   </si>
   <si>
     <t xml:space="preserve">4.30718946456909</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94501066207886</t>
+    <t xml:space="preserve">3.94501137733459</t>
   </si>
   <si>
     <t xml:space="preserve">4.11073923110962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98092651367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77452397346497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89438462257385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17564582824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82385277748108</t>
+    <t xml:space="preserve">3.98092675209045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77452373504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89438390731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17564535140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8238525390625</t>
   </si>
   <si>
     <t xml:space="preserve">3.97486853599548</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07006406784058</t>
+    <t xml:space="preserve">4.07006502151489</t>
   </si>
   <si>
     <t xml:space="preserve">4.27387046813965</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11766290664673</t>
+    <t xml:space="preserve">4.11766242980957</t>
   </si>
   <si>
     <t xml:space="preserve">4.05665063858032</t>
@@ -2267,7 +2270,7 @@
     <t xml:space="preserve">4.25699520111084</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30978536605835</t>
+    <t xml:space="preserve">4.30978584289551</t>
   </si>
   <si>
     <t xml:space="preserve">4.37036514282227</t>
@@ -2276,46 +2279,46 @@
     <t xml:space="preserve">4.17131853103638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32709360122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45690727233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61268186569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48286914825439</t>
+    <t xml:space="preserve">4.32709407806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45690679550171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6126823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48286962509155</t>
   </si>
   <si>
     <t xml:space="preserve">4.6299901008606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56941175460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57806539535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5261402130127</t>
+    <t xml:space="preserve">4.569411277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57806491851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52614068984985</t>
   </si>
   <si>
     <t xml:space="preserve">4.50017786026001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7424955368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76845788955688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79441976547241</t>
+    <t xml:space="preserve">4.74249505996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76845741271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79442024230957</t>
   </si>
   <si>
     <t xml:space="preserve">4.94154167175293</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91557836532593</t>
+    <t xml:space="preserve">4.91557931900024</t>
   </si>
   <si>
     <t xml:space="preserve">4.83769130706787</t>
@@ -2324,25 +2327,25 @@
     <t xml:space="preserve">4.58671951293945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55210256576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62133646011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67326164245605</t>
+    <t xml:space="preserve">4.5521035194397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62133693695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6732611656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80307483673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90961217880249</t>
   </si>
   <si>
     <t xml:space="preserve">4.8030743598938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90961170196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80307388305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73204898834229</t>
+    <t xml:space="preserve">4.73204946517944</t>
   </si>
   <si>
     <t xml:space="preserve">4.88297748565674</t>
@@ -2351,19 +2354,19 @@
     <t xml:space="preserve">4.91848993301392</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10493135452271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22034740447998</t>
+    <t xml:space="preserve">5.10493087768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22034692764282</t>
   </si>
   <si>
     <t xml:space="preserve">5.19371223449707</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39790964126587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44229984283447</t>
+    <t xml:space="preserve">5.39791011810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44230079650879</t>
   </si>
   <si>
     <t xml:space="preserve">5.30025005340576</t>
@@ -2384,19 +2387,19 @@
     <t xml:space="preserve">5.81518268585205</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63761949539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30912780761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27361631393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23810338973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55771636962891</t>
+    <t xml:space="preserve">5.63761901855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30912828445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27361583709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23810291290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55771684646606</t>
   </si>
   <si>
     <t xml:space="preserve">5.73527908325195</t>
@@ -2405,13 +2408,13 @@
     <t xml:space="preserve">5.61098527908325</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65537548065186</t>
+    <t xml:space="preserve">5.65537643432617</t>
   </si>
   <si>
     <t xml:space="preserve">5.68201017379761</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61986303329468</t>
+    <t xml:space="preserve">5.61986351013184</t>
   </si>
   <si>
     <t xml:space="preserve">5.64649772644043</t>
@@ -2423,31 +2426,31 @@
     <t xml:space="preserve">5.5843505859375</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56659460067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53108167648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46005630493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35351896286011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42454433441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41566610336304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31800651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38903188705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29137182235718</t>
+    <t xml:space="preserve">5.56659412384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53108215332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4600567817688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35351943969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42454385757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41566562652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31800556182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3890323638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29137229919434</t>
   </si>
   <si>
     <t xml:space="preserve">5.21146821975708</t>
@@ -2459,82 +2462,82 @@
     <t xml:space="preserve">5.25585985183716</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26473712921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37127590179443</t>
+    <t xml:space="preserve">5.26473760604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37127542495728</t>
   </si>
   <si>
     <t xml:space="preserve">5.48669099807739</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59322834014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53995990753174</t>
+    <t xml:space="preserve">5.59322881698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53995943069458</t>
   </si>
   <si>
     <t xml:space="preserve">5.5044469833374</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38015365600586</t>
+    <t xml:space="preserve">5.3801531791687</t>
   </si>
   <si>
     <t xml:space="preserve">5.34464073181152</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28249406814575</t>
+    <t xml:space="preserve">5.28249311447144</t>
   </si>
   <si>
     <t xml:space="preserve">5.20259046554565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32688426971436</t>
+    <t xml:space="preserve">5.32688522338867</t>
   </si>
   <si>
     <t xml:space="preserve">5.3357629776001</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24698066711426</t>
+    <t xml:space="preserve">5.24698114395142</t>
   </si>
   <si>
     <t xml:space="preserve">5.15819978713989</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1315655708313</t>
+    <t xml:space="preserve">5.13156604766846</t>
   </si>
   <si>
     <t xml:space="preserve">5.16707849502563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1848349571228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02502727508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90073394775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61663293838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72317171096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85634326934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99839305877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0072717666626</t>
+    <t xml:space="preserve">5.18483448028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02502775192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90073442459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61663341522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7231707572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85634279251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99839401245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00727128982544</t>
   </si>
   <si>
     <t xml:space="preserve">4.89185571670532</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98951578140259</t>
+    <t xml:space="preserve">4.98951482772827</t>
   </si>
   <si>
     <t xml:space="preserve">5.90396356582642</t>
@@ -2549,19 +2552,19 @@
     <t xml:space="preserve">5.99274492263794</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09928274154663</t>
+    <t xml:space="preserve">6.09928321838379</t>
   </si>
   <si>
     <t xml:space="preserve">6.10816144943237</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35674905776978</t>
+    <t xml:space="preserve">6.35674858093262</t>
   </si>
   <si>
     <t xml:space="preserve">6.18806409835815</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2413330078125</t>
+    <t xml:space="preserve">6.24133348464966</t>
   </si>
   <si>
     <t xml:space="preserve">6.28572416305542</t>
@@ -2570,7 +2573,7 @@
     <t xml:space="preserve">6.32123613357544</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25021123886108</t>
+    <t xml:space="preserve">6.25021076202393</t>
   </si>
   <si>
     <t xml:space="preserve">6.30348014831543</t>
@@ -2582,25 +2585,25 @@
     <t xml:space="preserve">6.11703872680664</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0815258026123</t>
+    <t xml:space="preserve">6.08152627944946</t>
   </si>
   <si>
     <t xml:space="preserve">6.06377029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05489253997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98386669158936</t>
+    <t xml:space="preserve">6.05489206314087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98386716842651</t>
   </si>
   <si>
     <t xml:space="preserve">5.96611022949219</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93947649002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94835376739502</t>
+    <t xml:space="preserve">5.93947601318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94835424423218</t>
   </si>
   <si>
     <t xml:space="preserve">5.92172002792358</t>
@@ -2609,31 +2612,31 @@
     <t xml:space="preserve">5.912841796875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23245429992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46328687667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33011436462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27684545516968</t>
+    <t xml:space="preserve">6.23245477676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46328639984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33011484146118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27684593200684</t>
   </si>
   <si>
     <t xml:space="preserve">6.20582056045532</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04601383209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37450504302979</t>
+    <t xml:space="preserve">6.04601430892944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37450551986694</t>
   </si>
   <si>
     <t xml:space="preserve">6.12591695785522</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21469831466675</t>
+    <t xml:space="preserve">6.21469879150391</t>
   </si>
   <si>
     <t xml:space="preserve">6.17918586730957</t>
@@ -2642,31 +2645,31 @@
     <t xml:space="preserve">6.26796770095825</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48104333877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66748428344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01373147964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43988227844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54641962051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59968948364258</t>
+    <t xml:space="preserve">6.48104286193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66748380661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01373100280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43988275527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54641914367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59968900680542</t>
   </si>
   <si>
     <t xml:space="preserve">7.6352014541626</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68846940994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52866268157959</t>
+    <t xml:space="preserve">7.68846988677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52866363525391</t>
   </si>
   <si>
     <t xml:space="preserve">7.31558799743652</t>
@@ -2678,73 +2681,73 @@
     <t xml:space="preserve">7.18241596221924</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29783201217651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13802576065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04924392700195</t>
+    <t xml:space="preserve">7.29783153533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13802480697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04924345016479</t>
   </si>
   <si>
     <t xml:space="preserve">7.19129467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21792840957642</t>
+    <t xml:space="preserve">7.21792888641357</t>
   </si>
   <si>
     <t xml:space="preserve">7.3511004447937</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4842734336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59081077575684</t>
+    <t xml:space="preserve">7.48427295684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59081029891968</t>
   </si>
   <si>
     <t xml:space="preserve">7.58193206787109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65295743942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51090669631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45763778686523</t>
+    <t xml:space="preserve">7.65295791625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51090717315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45763826370239</t>
   </si>
   <si>
     <t xml:space="preserve">7.17353773117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61744546890259</t>
+    <t xml:space="preserve">7.61744499206543</t>
   </si>
   <si>
     <t xml:space="preserve">7.67959213256836</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76837396621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93705749511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19452381134033</t>
+    <t xml:space="preserve">7.76837301254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93705797195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19452476501465</t>
   </si>
   <si>
     <t xml:space="preserve">8.09686470031738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99920511245728</t>
+    <t xml:space="preserve">7.99920606613159</t>
   </si>
   <si>
     <t xml:space="preserve">8.17676734924316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20340251922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99032735824585</t>
+    <t xml:space="preserve">8.20340156555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99032592773438</t>
   </si>
   <si>
     <t xml:space="preserve">8.08798694610596</t>
@@ -2756,25 +2759,25 @@
     <t xml:space="preserve">8.0435962677002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00808429718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07910919189453</t>
+    <t xml:space="preserve">8.00808334350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07910823822021</t>
   </si>
   <si>
     <t xml:space="preserve">8.14125537872314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07022953033447</t>
+    <t xml:space="preserve">8.07023048400879</t>
   </si>
   <si>
     <t xml:space="preserve">8.15013313293457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38984394073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23891448974609</t>
+    <t xml:space="preserve">8.38984203338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23891353607178</t>
   </si>
   <si>
     <t xml:space="preserve">8.44311237335205</t>
@@ -2783,13 +2786,13 @@
     <t xml:space="preserve">8.38096523284912</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51413631439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43423461914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64730930328369</t>
+    <t xml:space="preserve">8.51413822174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43423366546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64730834960938</t>
   </si>
   <si>
     <t xml:space="preserve">8.42535591125488</t>
@@ -2798,7 +2801,7 @@
     <t xml:space="preserve">8.47014427185059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60530662536621</t>
+    <t xml:space="preserve">8.60530567169189</t>
   </si>
   <si>
     <t xml:space="preserve">8.43410110473633</t>
@@ -2810,16 +2813,13 @@
     <t xml:space="preserve">8.37102508544922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56025218963623</t>
+    <t xml:space="preserve">8.56025314331055</t>
   </si>
   <si>
     <t xml:space="preserve">8.31696033477783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42509078979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44311141967773</t>
+    <t xml:space="preserve">8.42508983612061</t>
   </si>
   <si>
     <t xml:space="preserve">8.62332725524902</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">8.75848960876465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6593713760376</t>
+    <t xml:space="preserve">8.65937042236328</t>
   </si>
   <si>
     <t xml:space="preserve">8.70442485809326</t>
@@ -2846,61 +2846,61 @@
     <t xml:space="preserve">8.50618743896484</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51519870758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53321933746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46113300323486</t>
+    <t xml:space="preserve">8.51519775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5332202911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46113395690918</t>
   </si>
   <si>
     <t xml:space="preserve">8.27190685272217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10971355438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1547679901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08268070220947</t>
+    <t xml:space="preserve">8.10971260070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15476608276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08267974853516</t>
   </si>
   <si>
     <t xml:space="preserve">8.0466365814209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0556468963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95652961730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00158214569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74928092956543</t>
+    <t xml:space="preserve">8.05564785003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95653009414673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00158309936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74928188323975</t>
   </si>
   <si>
     <t xml:space="preserve">7.85741138458252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78532409667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83938932418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74027061462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99257230758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92048501968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1727876663208</t>
+    <t xml:space="preserve">7.78532457351685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83938837051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74027013778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99257278442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92048597335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17278861999512</t>
   </si>
   <si>
     <t xml:space="preserve">8.29893970489502</t>
@@ -2909,13 +2909,13 @@
     <t xml:space="preserve">8.16377735137939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2178430557251</t>
+    <t xml:space="preserve">8.21784210205078</t>
   </si>
   <si>
     <t xml:space="preserve">7.96553993225098</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60510778427124</t>
+    <t xml:space="preserve">7.6051082611084</t>
   </si>
   <si>
     <t xml:space="preserve">8.07366943359375</t>
@@ -2924,22 +2924,22 @@
     <t xml:space="preserve">8.24487400054932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12773513793945</t>
+    <t xml:space="preserve">8.12773418426514</t>
   </si>
   <si>
     <t xml:space="preserve">8.48816585540771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38904857635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35300350189209</t>
+    <t xml:space="preserve">8.38904762268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35300445556641</t>
   </si>
   <si>
     <t xml:space="preserve">8.33498287200928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71343517303467</t>
+    <t xml:space="preserve">8.71343612670898</t>
   </si>
   <si>
     <t xml:space="preserve">8.63233852386475</t>
@@ -2948,10 +2948,10 @@
     <t xml:space="preserve">8.23586368560791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30795097351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64134788513184</t>
+    <t xml:space="preserve">8.30795001983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64135074615479</t>
   </si>
   <si>
     <t xml:space="preserve">8.77651119232178</t>
@@ -2969,34 +2969,34 @@
     <t xml:space="preserve">8.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03762722015381</t>
+    <t xml:space="preserve">8.03762626647949</t>
   </si>
   <si>
     <t xml:space="preserve">7.92949724197388</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98356056213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01960563659668</t>
+    <t xml:space="preserve">7.98356008529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01960468292236</t>
   </si>
   <si>
     <t xml:space="preserve">7.88444328308105</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56906414031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63214063644409</t>
+    <t xml:space="preserve">7.56906461715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63214111328125</t>
   </si>
   <si>
     <t xml:space="preserve">7.57807588577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55104351043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65917301177979</t>
+    <t xml:space="preserve">7.55104398727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65917253494263</t>
   </si>
   <si>
     <t xml:space="preserve">7.67719554901123</t>
@@ -3005,28 +3005,28 @@
     <t xml:space="preserve">7.72224855422974</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76730251312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71323823928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93850755691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22685241699219</t>
+    <t xml:space="preserve">7.76730155944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71323871612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93850803375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2268533706665</t>
   </si>
   <si>
     <t xml:space="preserve">8.19080924987793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20883178710938</t>
+    <t xml:space="preserve">8.20883083343506</t>
   </si>
   <si>
     <t xml:space="preserve">8.38003635406494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18179798126221</t>
+    <t xml:space="preserve">8.18179893493652</t>
   </si>
   <si>
     <t xml:space="preserve">8.02861595153809</t>
@@ -3038,34 +3038,34 @@
     <t xml:space="preserve">7.69521570205688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61411905288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37983751296997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33478498458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37082767486572</t>
+    <t xml:space="preserve">7.6141185760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37983798980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33478450775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37082815170288</t>
   </si>
   <si>
     <t xml:space="preserve">7.46093511581421</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36181735992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35280609130859</t>
+    <t xml:space="preserve">7.36181688308716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35280561447144</t>
   </si>
   <si>
     <t xml:space="preserve">7.4429144859314</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65016174316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46994638442993</t>
+    <t xml:space="preserve">7.65016222000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46994686126709</t>
   </si>
   <si>
     <t xml:space="preserve">7.39786005020142</t>
@@ -3074,10 +3074,10 @@
     <t xml:space="preserve">7.3257737159729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27170896530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30775213241577</t>
+    <t xml:space="preserve">7.27170848846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30775165557861</t>
   </si>
   <si>
     <t xml:space="preserve">7.29874181747437</t>
@@ -3086,16 +3086,16 @@
     <t xml:space="preserve">7.26269865036011</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54203271865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6411509513855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62312936782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53302192687988</t>
+    <t xml:space="preserve">7.54203319549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64115142822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62313032150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53302145004272</t>
   </si>
   <si>
     <t xml:space="preserve">7.52401113510132</t>
@@ -3113,55 +3113,55 @@
     <t xml:space="preserve">6.96534204483032</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92929840087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02841758728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89325618743896</t>
+    <t xml:space="preserve">6.92929887771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02841854095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89325571060181</t>
   </si>
   <si>
     <t xml:space="preserve">7.01039600372314</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12753629684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11852550506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94732093811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88424444198608</t>
+    <t xml:space="preserve">7.12753582000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11852598190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94732046127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88424491882324</t>
   </si>
   <si>
     <t xml:space="preserve">6.90226650238037</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28071928024292</t>
+    <t xml:space="preserve">7.28071975708008</t>
   </si>
   <si>
     <t xml:space="preserve">7.22665548324585</t>
   </si>
   <si>
-    <t xml:space="preserve">7.037428855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14555788040161</t>
+    <t xml:space="preserve">7.03742837905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14555740356445</t>
   </si>
   <si>
     <t xml:space="preserve">7.19962215423584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00138568878174</t>
+    <t xml:space="preserve">7.00138521194458</t>
   </si>
   <si>
     <t xml:space="preserve">7.07347106933594</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80314826965332</t>
+    <t xml:space="preserve">6.80314779281616</t>
   </si>
   <si>
     <t xml:space="preserve">6.74007225036621</t>
@@ -3170,16 +3170,16 @@
     <t xml:space="preserve">6.66798639297485</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3616189956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59589958190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41568326950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32557535171509</t>
+    <t xml:space="preserve">6.36161947250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59590005874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41568422317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32557582855225</t>
   </si>
   <si>
     <t xml:space="preserve">6.13634920120239</t>
@@ -3191,22 +3191,22 @@
     <t xml:space="preserve">5.83899307250977</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01019811630249</t>
+    <t xml:space="preserve">6.01019859313965</t>
   </si>
   <si>
     <t xml:space="preserve">6.28052139282227</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09129571914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14535999298096</t>
+    <t xml:space="preserve">6.09129524230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1453595161438</t>
   </si>
   <si>
     <t xml:space="preserve">6.35260820388794</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23546743392944</t>
+    <t xml:space="preserve">6.2354679107666</t>
   </si>
   <si>
     <t xml:space="preserve">6.46974849700928</t>
@@ -3218,13 +3218,13 @@
     <t xml:space="preserve">6.37062978744507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28953313827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31656551361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02821969985962</t>
+    <t xml:space="preserve">6.28953266143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31656503677368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02822017669678</t>
   </si>
   <si>
     <t xml:space="preserve">6.11832761764526</t>
@@ -3236,28 +3236,28 @@
     <t xml:space="preserve">6.27151107788086</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26249980926514</t>
+    <t xml:space="preserve">6.26250028610229</t>
   </si>
   <si>
     <t xml:space="preserve">6.18140316009521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29854345321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17239189147949</t>
+    <t xml:space="preserve">6.29854297637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17239236831665</t>
   </si>
   <si>
     <t xml:space="preserve">5.84800386428833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86602592468262</t>
+    <t xml:space="preserve">5.86602544784546</t>
   </si>
   <si>
     <t xml:space="preserve">5.92009019851685</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89305830001831</t>
+    <t xml:space="preserve">5.89305734634399</t>
   </si>
   <si>
     <t xml:space="preserve">5.93811178207397</t>
@@ -3275,13 +3275,13 @@
     <t xml:space="preserve">6.06426286697388</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9831657409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94712257385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01920890808105</t>
+    <t xml:space="preserve">5.98316526412964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94712209701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0192084312439</t>
   </si>
   <si>
     <t xml:space="preserve">5.99217653274536</t>
@@ -3293,13 +3293,13 @@
     <t xml:space="preserve">5.97415494918823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95613384246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08228445053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07327365875244</t>
+    <t xml:space="preserve">5.9561333656311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08228492736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07327318191528</t>
   </si>
   <si>
     <t xml:space="preserve">6.03723001480103</t>
@@ -3308,22 +3308,22 @@
     <t xml:space="preserve">6.04001379013062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94737577438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96590328216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16044425964355</t>
+    <t xml:space="preserve">5.94737529754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96590280532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1604437828064</t>
   </si>
   <si>
     <t xml:space="preserve">6.28087329864502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22529029846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20676279067993</t>
+    <t xml:space="preserve">6.22528982162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20676231384277</t>
   </si>
   <si>
     <t xml:space="preserve">6.17897176742554</t>
@@ -3344,19 +3344,19 @@
     <t xml:space="preserve">5.81768226623535</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83621025085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92884826660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8917932510376</t>
+    <t xml:space="preserve">5.83620977401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9288477897644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89179277420044</t>
   </si>
   <si>
     <t xml:space="preserve">6.09559679031372</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0122218132019</t>
+    <t xml:space="preserve">6.01222229003906</t>
   </si>
   <si>
     <t xml:space="preserve">5.95663928985596</t>
@@ -3368,7 +3368,7 @@
     <t xml:space="preserve">5.68798828125</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78062725067139</t>
+    <t xml:space="preserve">5.78062629699707</t>
   </si>
   <si>
     <t xml:space="preserve">5.73430776596069</t>
@@ -3383,7 +3383,7 @@
     <t xml:space="preserve">5.44712924957275</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60461473464966</t>
+    <t xml:space="preserve">5.6046142578125</t>
   </si>
   <si>
     <t xml:space="preserve">5.75283527374268</t>
@@ -3392,16 +3392,16 @@
     <t xml:space="preserve">5.51197576522827</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85473775863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55829477310181</t>
+    <t xml:space="preserve">5.85473728179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55829524993896</t>
   </si>
   <si>
     <t xml:space="preserve">5.71578025817871</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77136278152466</t>
+    <t xml:space="preserve">5.77136325836182</t>
   </si>
   <si>
     <t xml:space="preserve">5.61387777328491</t>
@@ -3410,13 +3410,13 @@
     <t xml:space="preserve">5.66019725799561</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87326574325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66946029663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80841827392578</t>
+    <t xml:space="preserve">5.8732647895813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66946077346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80841875076294</t>
   </si>
   <si>
     <t xml:space="preserve">6.0307502746582</t>
@@ -3425,10 +3425,10 @@
     <t xml:space="preserve">6.04927778244019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86400079727173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53976774215698</t>
+    <t xml:space="preserve">5.86400127410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53976726531982</t>
   </si>
   <si>
     <t xml:space="preserve">5.49344825744629</t>
@@ -3443,7 +3443,7 @@
     <t xml:space="preserve">5.39154624938965</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35449123382568</t>
+    <t xml:space="preserve">5.35449075698853</t>
   </si>
   <si>
     <t xml:space="preserve">5.3174352645874</t>
@@ -3458,19 +3458,19 @@
     <t xml:space="preserve">5.21553373336792</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19700574874878</t>
+    <t xml:space="preserve">5.19700622558594</t>
   </si>
   <si>
     <t xml:space="preserve">5.25258874893188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38228178024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13215923309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10436773300171</t>
+    <t xml:space="preserve">5.38228273391724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1321587562561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10436820983887</t>
   </si>
   <si>
     <t xml:space="preserve">5.28038024902344</t>
@@ -3485,10 +3485,10 @@
     <t xml:space="preserve">5.08583974838257</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05804872512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01172924041748</t>
+    <t xml:space="preserve">5.05804824829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01172971725464</t>
   </si>
   <si>
     <t xml:space="preserve">5.02099323272705</t>
@@ -3497,19 +3497,19 @@
     <t xml:space="preserve">5.1784782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04878425598145</t>
+    <t xml:space="preserve">5.0487847328186</t>
   </si>
   <si>
     <t xml:space="preserve">5.15068674087524</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00246524810791</t>
+    <t xml:space="preserve">5.00246572494507</t>
   </si>
   <si>
     <t xml:space="preserve">4.8635082244873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91909074783325</t>
+    <t xml:space="preserve">4.91909122467041</t>
   </si>
   <si>
     <t xml:space="preserve">4.97467422485352</t>
@@ -3530,7 +3530,7 @@
     <t xml:space="preserve">5.45639324188232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52123975753784</t>
+    <t xml:space="preserve">5.52123928070068</t>
   </si>
   <si>
     <t xml:space="preserve">5.29890775680542</t>
@@ -3545,10 +3545,10 @@
     <t xml:space="preserve">5.67872476577759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76209926605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90105628967285</t>
+    <t xml:space="preserve">5.76209878921509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90105676651001</t>
   </si>
   <si>
     <t xml:space="preserve">5.91958427429199</t>
@@ -3557,13 +3557,13 @@
     <t xml:space="preserve">5.70651578903198</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74357175827026</t>
+    <t xml:space="preserve">5.74357128143311</t>
   </si>
   <si>
     <t xml:space="preserve">5.65093326568604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63240528106689</t>
+    <t xml:space="preserve">5.63240575790405</t>
   </si>
   <si>
     <t xml:space="preserve">5.54903125762939</t>
@@ -3575,7 +3575,7 @@
     <t xml:space="preserve">5.88252878189087</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99369430541992</t>
+    <t xml:space="preserve">5.99369478225708</t>
   </si>
   <si>
     <t xml:space="preserve">5.98443126678467</t>
@@ -3584,7 +3584,7 @@
     <t xml:space="preserve">5.91032028198242</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44762277603149</t>
+    <t xml:space="preserve">6.44762229919434</t>
   </si>
   <si>
     <t xml:space="preserve">6.74406480789185</t>
@@ -3593,25 +3593,25 @@
     <t xml:space="preserve">6.70700931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79964780807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8274393081665</t>
+    <t xml:space="preserve">6.79964828491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82743883132935</t>
   </si>
   <si>
     <t xml:space="preserve">6.79038381576538</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89228582382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96639633178711</t>
+    <t xml:space="preserve">6.89228630065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96639680862427</t>
   </si>
   <si>
     <t xml:space="preserve">7.23504734039307</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34621334075928</t>
+    <t xml:space="preserve">7.34621286392212</t>
   </si>
   <si>
     <t xml:space="preserve">7.38326787948608</t>
@@ -3623,19 +3623,19 @@
     <t xml:space="preserve">7.52222585678101</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48517036437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42958784103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55928134918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39253234863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59633684158325</t>
+    <t xml:space="preserve">7.48517084121704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42958831787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55928087234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39253282546997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59633636474609</t>
   </si>
   <si>
     <t xml:space="preserve">7.54075384140015</t>
@@ -3647,19 +3647,19 @@
     <t xml:space="preserve">7.50369882583618</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63339233398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62412691116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57780885696411</t>
+    <t xml:space="preserve">7.63339138031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62412738800049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57780933380127</t>
   </si>
   <si>
     <t xml:space="preserve">7.58707237243652</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45737981796265</t>
+    <t xml:space="preserve">7.45737934112549</t>
   </si>
   <si>
     <t xml:space="preserve">7.43885135650635</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">7.29989433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24431133270264</t>
+    <t xml:space="preserve">7.24431180953979</t>
   </si>
   <si>
     <t xml:space="preserve">7.21651983261108</t>
@@ -3701,31 +3701,31 @@
     <t xml:space="preserve">7.27210235595703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20725631713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33694934844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31842184066772</t>
+    <t xml:space="preserve">7.20725584030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33694982528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31842231750488</t>
   </si>
   <si>
     <t xml:space="preserve">7.26283931732178</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12388181686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04977083206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98492383956909</t>
+    <t xml:space="preserve">7.12388134002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04977130889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98492431640625</t>
   </si>
   <si>
     <t xml:space="preserve">7.07756233215332</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22578382492065</t>
+    <t xml:space="preserve">7.22578430175781</t>
   </si>
   <si>
     <t xml:space="preserve">7.19799184799194</t>
@@ -3734,10 +3734,10 @@
     <t xml:space="preserve">7.15167284011841</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11461782455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05903434753418</t>
+    <t xml:space="preserve">7.11461734771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05903482437134</t>
   </si>
   <si>
     <t xml:space="preserve">7.06857395172119</t>
@@ -3752,34 +3752,34 @@
     <t xml:space="preserve">6.94456434249878</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86824989318848</t>
+    <t xml:space="preserve">6.86825037002563</t>
   </si>
   <si>
     <t xml:space="preserve">6.79193639755249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75377941131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84917163848877</t>
+    <t xml:space="preserve">6.75377893447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84917116165161</t>
   </si>
   <si>
     <t xml:space="preserve">6.99226045608521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95410346984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87778902053833</t>
+    <t xml:space="preserve">6.95410299301147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87778949737549</t>
   </si>
   <si>
     <t xml:space="preserve">6.98272132873535</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96364259719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03041744232178</t>
+    <t xml:space="preserve">6.96364307403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03041696548462</t>
   </si>
   <si>
     <t xml:space="preserve">7.01133871078491</t>
@@ -3809,7 +3809,7 @@
     <t xml:space="preserve">6.78239727020264</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7251615524292</t>
+    <t xml:space="preserve">6.72516202926636</t>
   </si>
   <si>
     <t xml:space="preserve">7.00179958343506</t>
@@ -3818,19 +3818,19 @@
     <t xml:space="preserve">7.36429023742676</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28797674179077</t>
+    <t xml:space="preserve">7.28797626495361</t>
   </si>
   <si>
     <t xml:space="preserve">7.29751586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30705499649048</t>
+    <t xml:space="preserve">7.30705451965332</t>
   </si>
   <si>
     <t xml:space="preserve">7.53599691390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57415390014648</t>
+    <t xml:space="preserve">7.57415342330933</t>
   </si>
   <si>
     <t xml:space="preserve">7.66000652313232</t>
@@ -3839,10 +3839,10 @@
     <t xml:space="preserve">7.6981635093689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93664455413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98434066772461</t>
+    <t xml:space="preserve">7.93664407730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98434019088745</t>
   </si>
   <si>
     <t xml:space="preserve">8.18466472625732</t>
@@ -3860,19 +3860,19 @@
     <t xml:space="preserve">8.16558647155762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04157733917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8794093132019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97480154037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03203678131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90802717208862</t>
+    <t xml:space="preserve">8.04157638549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87940979003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9748010635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03203773498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90802669525146</t>
   </si>
   <si>
     <t xml:space="preserve">7.89848756790161</t>
@@ -3884,7 +3884,7 @@
     <t xml:space="preserve">7.84125232696533</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88894844055176</t>
+    <t xml:space="preserve">7.88894891738892</t>
   </si>
   <si>
     <t xml:space="preserve">7.78401708602905</t>
@@ -3893,7 +3893,7 @@
     <t xml:space="preserve">7.81263399124146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85079050064087</t>
+    <t xml:space="preserve">7.85079145431519</t>
   </si>
   <si>
     <t xml:space="preserve">7.77447748184204</t>
@@ -3908,13 +3908,13 @@
     <t xml:space="preserve">7.72678184509277</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64092874526978</t>
+    <t xml:space="preserve">7.64092826843262</t>
   </si>
   <si>
     <t xml:space="preserve">7.58369255065918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38336896896362</t>
+    <t xml:space="preserve">7.38336849212646</t>
   </si>
   <si>
     <t xml:space="preserve">7.3356728553772</t>
@@ -3935,7 +3935,7 @@
     <t xml:space="preserve">7.08765268325806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15442705154419</t>
+    <t xml:space="preserve">7.15442752838135</t>
   </si>
   <si>
     <t xml:space="preserve">7.03995656967163</t>
@@ -3947,7 +3947,7 @@
     <t xml:space="preserve">7.27843761444092</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41198635101318</t>
+    <t xml:space="preserve">7.41198682785034</t>
   </si>
   <si>
     <t xml:space="preserve">7.39290809631348</t>
@@ -3968,13 +3968,13 @@
     <t xml:space="preserve">7.45014333724976</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40244770050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50737857818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70770263671875</t>
+    <t xml:space="preserve">7.40244722366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50737905502319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70770311355591</t>
   </si>
   <si>
     <t xml:space="preserve">8.20374393463135</t>
@@ -3989,10 +3989,10 @@
     <t xml:space="preserve">8.10835075378418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08927249908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36591053009033</t>
+    <t xml:space="preserve">8.08927154541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36591148376465</t>
   </si>
   <si>
     <t xml:space="preserve">8.30867481231689</t>
@@ -4010,13 +4010,13 @@
     <t xml:space="preserve">8.60439205169678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40406703948975</t>
+    <t xml:space="preserve">8.40406799316406</t>
   </si>
   <si>
     <t xml:space="preserve">8.41360664367676</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26097774505615</t>
+    <t xml:space="preserve">8.26097869873047</t>
   </si>
   <si>
     <t xml:space="preserve">8.57577323913574</t>
@@ -4031,10 +4031,10 @@
     <t xml:space="preserve">8.76655769348145</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1576681137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19582462310791</t>
+    <t xml:space="preserve">9.15766716003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19582366943359</t>
   </si>
   <si>
     <t xml:space="preserve">9.11951065063477</t>
@@ -4043,13 +4043,13 @@
     <t xml:space="preserve">9.10043144226074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09089183807373</t>
+    <t xml:space="preserve">9.09089279174805</t>
   </si>
   <si>
     <t xml:space="preserve">8.72840118408203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87149047851562</t>
+    <t xml:space="preserve">8.87148952484131</t>
   </si>
   <si>
     <t xml:space="preserve">8.90964698791504</t>
@@ -4073,7 +4073,7 @@
     <t xml:space="preserve">9.00503826141357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20536327362061</t>
+    <t xml:space="preserve">9.20536231994629</t>
   </si>
   <si>
     <t xml:space="preserve">9.45338344573975</t>
@@ -4082,25 +4082,25 @@
     <t xml:space="preserve">9.50107955932617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52969741821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57739353179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47246170043945</t>
+    <t xml:space="preserve">9.52969646453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.577392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47246265411377</t>
   </si>
   <si>
     <t xml:space="preserve">9.36752986907959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30075454711914</t>
+    <t xml:space="preserve">9.30075550079346</t>
   </si>
   <si>
     <t xml:space="preserve">9.39614772796631</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44384288787842</t>
+    <t xml:space="preserve">9.44384384155273</t>
   </si>
   <si>
     <t xml:space="preserve">9.49153995513916</t>
@@ -4112,7 +4112,7 @@
     <t xml:space="preserve">8.69978332519531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55669498443604</t>
+    <t xml:space="preserve">8.55669593811035</t>
   </si>
   <si>
     <t xml:space="preserve">8.62346935272217</t>
@@ -4121,10 +4121,10 @@
     <t xml:space="preserve">8.48038101196289</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59485149383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70932292938232</t>
+    <t xml:space="preserve">8.59485244750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70932197570801</t>
   </si>
   <si>
     <t xml:space="preserve">8.77609729766846</t>
@@ -4136,10 +4136,10 @@
     <t xml:space="preserve">8.75701904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86195087432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89056777954102</t>
+    <t xml:space="preserve">8.8619499206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89056873321533</t>
   </si>
   <si>
     <t xml:space="preserve">8.67116546630859</t>
@@ -4154,10 +4154,10 @@
     <t xml:space="preserve">8.74748039245605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0145788192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92872428894043</t>
+    <t xml:space="preserve">9.01457786560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92872524261475</t>
   </si>
   <si>
     <t xml:space="preserve">8.97642135620117</t>
@@ -4169,28 +4169,28 @@
     <t xml:space="preserve">9.46292304992676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74910068511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78725719451904</t>
+    <t xml:space="preserve">9.74909973144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78725624084473</t>
   </si>
   <si>
     <t xml:space="preserve">9.92080497741699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99711894989014</t>
+    <t xml:space="preserve">9.99711990356445</t>
   </si>
   <si>
     <t xml:space="preserve">9.69186401367188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76817798614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80633449554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63462829589844</t>
+    <t xml:space="preserve">9.7681770324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80633544921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63462924957275</t>
   </si>
   <si>
     <t xml:space="preserve">9.67278575897217</t>
@@ -4199,10 +4199,10 @@
     <t xml:space="preserve">9.59647178649902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71094226837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52015686035156</t>
+    <t xml:space="preserve">9.7109432220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52015781402588</t>
   </si>
   <si>
     <t xml:space="preserve">9.43430519104004</t>
@@ -4211,13 +4211,13 @@
     <t xml:space="preserve">9.25305938720703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28167629241943</t>
+    <t xml:space="preserve">9.28167724609375</t>
   </si>
   <si>
     <t xml:space="preserve">9.34845161437988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41522693634033</t>
+    <t xml:space="preserve">9.41522598266602</t>
   </si>
   <si>
     <t xml:space="preserve">9.48200035095215</t>
@@ -4235,7 +4235,7 @@
     <t xml:space="preserve">9.65370750427246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86357116699219</t>
+    <t xml:space="preserve">9.86357021331787</t>
   </si>
   <si>
     <t xml:space="preserve">10.0204467773438</t>
@@ -27971,7 +27971,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G871" t="s">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -27997,7 +27997,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G872" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -28023,7 +28023,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G873" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -28049,7 +28049,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G874" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -28075,7 +28075,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G875" t="s">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -28101,7 +28101,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G876" t="s">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -28127,7 +28127,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G877" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -28153,7 +28153,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G878" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -28179,7 +28179,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G879" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -28205,7 +28205,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G880" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -28231,7 +28231,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G881" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -28257,7 +28257,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G882" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -28283,7 +28283,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G883" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -28309,7 +28309,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G884" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -28335,7 +28335,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G885" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -28361,7 +28361,7 @@
         <v>6.25</v>
       </c>
       <c r="G886" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -28387,7 +28387,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G887" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -28413,7 +28413,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G888" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -28439,7 +28439,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G889" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -28465,7 +28465,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G890" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -28491,7 +28491,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G891" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -28517,7 +28517,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G892" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -28543,7 +28543,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G893" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -28569,7 +28569,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G894" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -28595,7 +28595,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G895" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -28621,7 +28621,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G896" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -28647,7 +28647,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G897" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -28673,7 +28673,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G898" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -28699,7 +28699,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G899" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -28725,7 +28725,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G900" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -28751,7 +28751,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G901" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -28777,7 +28777,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G902" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -28803,7 +28803,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G903" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -28829,7 +28829,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G904" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -28855,7 +28855,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G905" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -28881,7 +28881,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G906" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -28907,7 +28907,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G907" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -28933,7 +28933,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G908" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -28959,7 +28959,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G909" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -28985,7 +28985,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G910" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -29011,7 +29011,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G911" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -29037,7 +29037,7 @@
         <v>6.25</v>
       </c>
       <c r="G912" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -29063,7 +29063,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G913" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -29089,7 +29089,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G914" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -29115,7 +29115,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G915" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -29141,7 +29141,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G916" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -29167,7 +29167,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G917" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -29219,7 +29219,7 @@
         <v>6</v>
       </c>
       <c r="G919" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -29245,7 +29245,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G920" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -29271,7 +29271,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G921" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -29297,7 +29297,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G922" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -29323,7 +29323,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G923" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -29349,7 +29349,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G924" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -29401,7 +29401,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G926" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -29453,7 +29453,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G928" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -29479,7 +29479,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G929" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -29505,7 +29505,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G930" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -29531,7 +29531,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G931" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -29583,7 +29583,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G933" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -29635,7 +29635,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G935" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -29661,7 +29661,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G936" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -29687,7 +29687,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G937" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -29713,7 +29713,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G938" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -29739,7 +29739,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G939" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -29765,7 +29765,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G940" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -29791,7 +29791,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G941" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -29817,7 +29817,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G942" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -29843,7 +29843,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G943" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -29869,7 +29869,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G944" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -29895,7 +29895,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G945" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -29921,7 +29921,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G946" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -29947,7 +29947,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G947" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -29973,7 +29973,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G948" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -29999,7 +29999,7 @@
         <v>6</v>
       </c>
       <c r="G949" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -30025,7 +30025,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G950" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -30051,7 +30051,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G951" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -30077,7 +30077,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G952" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -30103,7 +30103,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G953" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -30129,7 +30129,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G954" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -30181,7 +30181,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G956" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -30207,7 +30207,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G957" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -30233,7 +30233,7 @@
         <v>5.96500015258789</v>
       </c>
       <c r="G958" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -30259,7 +30259,7 @@
         <v>5.82299995422363</v>
       </c>
       <c r="G959" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -30285,7 +30285,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G960" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -30311,7 +30311,7 @@
         <v>5.9539999961853</v>
       </c>
       <c r="G961" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -30337,7 +30337,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G962" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -30363,7 +30363,7 @@
         <v>6.01900005340576</v>
       </c>
       <c r="G963" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -30389,7 +30389,7 @@
         <v>6</v>
       </c>
       <c r="G964" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -30415,7 +30415,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G965" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -30441,7 +30441,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G966" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -30467,7 +30467,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G967" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -30493,7 +30493,7 @@
         <v>6.17700004577637</v>
       </c>
       <c r="G968" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -30519,7 +30519,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G969" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -30545,7 +30545,7 @@
         <v>6.10099983215332</v>
       </c>
       <c r="G970" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -30571,7 +30571,7 @@
         <v>6.13100004196167</v>
       </c>
       <c r="G971" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -30597,7 +30597,7 @@
         <v>6.08699989318848</v>
       </c>
       <c r="G972" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -30623,7 +30623,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G973" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -30649,7 +30649,7 @@
         <v>6.17899990081787</v>
       </c>
       <c r="G974" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -30675,7 +30675,7 @@
         <v>6.17899990081787</v>
       </c>
       <c r="G975" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -30701,7 +30701,7 @@
         <v>6.0310001373291</v>
       </c>
       <c r="G976" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -30727,7 +30727,7 @@
         <v>6.17399978637695</v>
       </c>
       <c r="G977" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -30753,7 +30753,7 @@
         <v>6.33799982070923</v>
       </c>
       <c r="G978" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -30779,7 +30779,7 @@
         <v>6.33799982070923</v>
       </c>
       <c r="G979" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -30805,7 +30805,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G980" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -30831,7 +30831,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G981" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -30857,7 +30857,7 @@
         <v>6.28499984741211</v>
       </c>
       <c r="G982" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -30883,7 +30883,7 @@
         <v>6.37599992752075</v>
       </c>
       <c r="G983" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -30909,7 +30909,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G984" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -30935,7 +30935,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G985" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -30961,7 +30961,7 @@
         <v>6.33799982070923</v>
       </c>
       <c r="G986" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -30987,7 +30987,7 @@
         <v>6.37400007247925</v>
       </c>
       <c r="G987" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -31013,7 +31013,7 @@
         <v>6.31199979782104</v>
       </c>
       <c r="G988" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -31039,7 +31039,7 @@
         <v>6.26599979400635</v>
       </c>
       <c r="G989" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -31065,7 +31065,7 @@
         <v>6.31799983978271</v>
       </c>
       <c r="G990" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -31091,7 +31091,7 @@
         <v>6.29099988937378</v>
       </c>
       <c r="G991" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -31117,7 +31117,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G992" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -31143,7 +31143,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G993" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -31169,7 +31169,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G994" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -31195,7 +31195,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G995" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -31221,7 +31221,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G996" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -31247,7 +31247,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G997" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -31273,7 +31273,7 @@
         <v>6.86899995803833</v>
       </c>
       <c r="G998" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -31299,7 +31299,7 @@
         <v>6.66699981689453</v>
       </c>
       <c r="G999" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -31325,7 +31325,7 @@
         <v>6.68200016021729</v>
       </c>
       <c r="G1000" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -31351,7 +31351,7 @@
         <v>6.64900016784668</v>
       </c>
       <c r="G1001" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -31377,7 +31377,7 @@
         <v>6.63399982452393</v>
       </c>
       <c r="G1002" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -31403,7 +31403,7 @@
         <v>6.63199996948242</v>
       </c>
       <c r="G1003" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -31429,7 +31429,7 @@
         <v>6.71400022506714</v>
       </c>
       <c r="G1004" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -31455,7 +31455,7 @@
         <v>6.82399988174438</v>
       </c>
       <c r="G1005" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -31481,7 +31481,7 @@
         <v>6.85599994659424</v>
       </c>
       <c r="G1006" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -31507,7 +31507,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1007" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -31533,7 +31533,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1008" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -31559,7 +31559,7 @@
         <v>6.84800004959106</v>
       </c>
       <c r="G1009" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -31585,7 +31585,7 @@
         <v>6.76399993896484</v>
       </c>
       <c r="G1010" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -31611,7 +31611,7 @@
         <v>6.76700019836426</v>
       </c>
       <c r="G1011" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -31637,7 +31637,7 @@
         <v>6.56400012969971</v>
       </c>
       <c r="G1012" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -31663,7 +31663,7 @@
         <v>6.62400007247925</v>
       </c>
       <c r="G1013" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -31689,7 +31689,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1014" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -31715,7 +31715,7 @@
         <v>6.72399997711182</v>
       </c>
       <c r="G1015" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -31741,7 +31741,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G1016" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -31767,7 +31767,7 @@
         <v>6.59299993515015</v>
       </c>
       <c r="G1017" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -31793,7 +31793,7 @@
         <v>6.44199991226196</v>
       </c>
       <c r="G1018" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -31819,7 +31819,7 @@
         <v>6.65100002288818</v>
       </c>
       <c r="G1019" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -31845,7 +31845,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1020" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -31871,7 +31871,7 @@
         <v>6.6560001373291</v>
       </c>
       <c r="G1021" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -31897,7 +31897,7 @@
         <v>6.6269998550415</v>
       </c>
       <c r="G1022" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -31923,7 +31923,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G1023" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -31949,7 +31949,7 @@
         <v>6.58400011062622</v>
       </c>
       <c r="G1024" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -31975,7 +31975,7 @@
         <v>6.57800006866455</v>
       </c>
       <c r="G1025" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -32001,7 +32001,7 @@
         <v>6.50400018692017</v>
       </c>
       <c r="G1026" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -32027,7 +32027,7 @@
         <v>6.65500020980835</v>
       </c>
       <c r="G1027" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -32053,7 +32053,7 @@
         <v>6.53800010681152</v>
       </c>
       <c r="G1028" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -32079,7 +32079,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1029" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -32105,7 +32105,7 @@
         <v>6.43900012969971</v>
       </c>
       <c r="G1030" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -32131,7 +32131,7 @@
         <v>6.5</v>
       </c>
       <c r="G1031" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -32157,7 +32157,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G1032" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -32183,7 +32183,7 @@
         <v>6.55499982833862</v>
       </c>
       <c r="G1033" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -32209,7 +32209,7 @@
         <v>6.5</v>
       </c>
       <c r="G1034" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -32235,7 +32235,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1035" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -32261,7 +32261,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1036" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -32287,7 +32287,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1037" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -32313,7 +32313,7 @@
         <v>6.45300006866455</v>
       </c>
       <c r="G1038" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -32339,7 +32339,7 @@
         <v>6.52299976348877</v>
       </c>
       <c r="G1039" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -32365,7 +32365,7 @@
         <v>6.61600017547607</v>
       </c>
       <c r="G1040" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -32391,7 +32391,7 @@
         <v>6.48799991607666</v>
       </c>
       <c r="G1041" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -32417,7 +32417,7 @@
         <v>6.47900009155273</v>
       </c>
       <c r="G1042" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -32443,7 +32443,7 @@
         <v>6.53200006484985</v>
       </c>
       <c r="G1043" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -32469,7 +32469,7 @@
         <v>6.53499984741211</v>
       </c>
       <c r="G1044" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -32495,7 +32495,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G1045" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -32521,7 +32521,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1046" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -32547,7 +32547,7 @@
         <v>6.74900007247925</v>
       </c>
       <c r="G1047" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -32573,7 +32573,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1048" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -32599,7 +32599,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1049" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -32625,7 +32625,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G1050" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -32651,7 +32651,7 @@
         <v>6.60300016403198</v>
       </c>
       <c r="G1051" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -32677,7 +32677,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G1052" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -32703,7 +32703,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G1053" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -32729,7 +32729,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G1054" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -32755,7 +32755,7 @@
         <v>6.19600009918213</v>
       </c>
       <c r="G1055" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -32781,7 +32781,7 @@
         <v>6.00299978256226</v>
       </c>
       <c r="G1056" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -32807,7 +32807,7 @@
         <v>5.82399988174438</v>
       </c>
       <c r="G1057" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -32859,7 +32859,7 @@
         <v>5.95599985122681</v>
       </c>
       <c r="G1059" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -32885,7 +32885,7 @@
         <v>5.98600006103516</v>
       </c>
       <c r="G1060" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -32911,7 +32911,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G1061" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -32937,7 +32937,7 @@
         <v>5.54199981689453</v>
       </c>
       <c r="G1062" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -32963,7 +32963,7 @@
         <v>4.90350008010864</v>
       </c>
       <c r="G1063" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -32989,7 +32989,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1064" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -33015,7 +33015,7 @@
         <v>4.97700023651123</v>
       </c>
       <c r="G1065" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -33041,7 +33041,7 @@
         <v>4.55849981307983</v>
       </c>
       <c r="G1066" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -33067,7 +33067,7 @@
         <v>4.75</v>
       </c>
       <c r="G1067" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -33093,7 +33093,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G1068" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -33119,7 +33119,7 @@
         <v>4.75</v>
       </c>
       <c r="G1069" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -33145,7 +33145,7 @@
         <v>4.36149978637695</v>
       </c>
       <c r="G1070" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -33171,7 +33171,7 @@
         <v>4.5</v>
       </c>
       <c r="G1071" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -33197,7 +33197,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G1072" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -33223,7 +33223,7 @@
         <v>4.41849994659424</v>
       </c>
       <c r="G1073" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -33249,7 +33249,7 @@
         <v>4.59299993515015</v>
       </c>
       <c r="G1074" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -33275,7 +33275,7 @@
         <v>4.70300006866455</v>
       </c>
       <c r="G1075" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -33301,7 +33301,7 @@
         <v>4.93849992752075</v>
       </c>
       <c r="G1076" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -33327,7 +33327,7 @@
         <v>4.75799989700317</v>
       </c>
       <c r="G1077" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -33353,7 +33353,7 @@
         <v>4.6875</v>
       </c>
       <c r="G1078" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -33379,7 +33379,7 @@
         <v>4.91900014877319</v>
       </c>
       <c r="G1079" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -33405,7 +33405,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1080" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -33431,7 +33431,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1081" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -33457,7 +33457,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1082" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -33483,7 +33483,7 @@
         <v>5</v>
       </c>
       <c r="G1083" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -33509,7 +33509,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1084" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -33535,7 +33535,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1085" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -33561,7 +33561,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1086" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -33587,7 +33587,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1087" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -33613,7 +33613,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1088" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -33639,7 +33639,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1089" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -33665,7 +33665,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1090" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -33691,7 +33691,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1091" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -33717,7 +33717,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G1092" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -33743,7 +33743,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1093" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -33769,7 +33769,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1094" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -33795,7 +33795,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1095" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -33821,7 +33821,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1096" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -33847,7 +33847,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1097" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -33873,7 +33873,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1098" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -33899,7 +33899,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1099" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -33925,7 +33925,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1100" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -33951,7 +33951,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1101" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -33977,7 +33977,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1102" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -34003,7 +34003,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1103" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -34029,7 +34029,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1104" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -34055,7 +34055,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1105" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -34081,7 +34081,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1106" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -34107,7 +34107,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1107" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -34133,7 +34133,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1108" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -34159,7 +34159,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1109" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -34185,7 +34185,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1110" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -34211,7 +34211,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1111" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -34237,7 +34237,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1112" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -34263,7 +34263,7 @@
         <v>5.5</v>
       </c>
       <c r="G1113" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -34289,7 +34289,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1114" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -34315,7 +34315,7 @@
         <v>5.75</v>
       </c>
       <c r="G1115" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -34341,7 +34341,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1116" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -34367,7 +34367,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1117" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -34393,7 +34393,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1118" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -34419,7 +34419,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1119" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -34445,7 +34445,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1120" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -34471,7 +34471,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1121" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -34497,7 +34497,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G1122" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -34523,7 +34523,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G1123" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -34549,7 +34549,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1124" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -34575,7 +34575,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1125" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -34601,7 +34601,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G1126" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -34627,7 +34627,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G1127" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -34653,7 +34653,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1128" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -34679,7 +34679,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1129" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -34705,7 +34705,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1130" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -34731,7 +34731,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G1131" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -34757,7 +34757,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1132" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -34783,7 +34783,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1133" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -34809,7 +34809,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G1134" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -34835,7 +34835,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1135" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -34861,7 +34861,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1136" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -34887,7 +34887,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1137" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -34913,7 +34913,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1138" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -34939,7 +34939,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1139" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -34965,7 +34965,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1140" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -34991,7 +34991,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1141" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -35017,7 +35017,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1142" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -35043,7 +35043,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1143" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -35069,7 +35069,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1144" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -35095,7 +35095,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G1145" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -35121,7 +35121,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1146" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -35147,7 +35147,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1147" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -35173,7 +35173,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1148" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -35199,7 +35199,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G1149" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -35225,7 +35225,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1150" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -35251,7 +35251,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1151" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -35277,7 +35277,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1152" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -35303,7 +35303,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G1153" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -35329,7 +35329,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1154" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -35355,7 +35355,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G1155" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -35381,7 +35381,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1156" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -35407,7 +35407,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G1157" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -35433,7 +35433,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G1158" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -35459,7 +35459,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1159" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -35485,7 +35485,7 @@
         <v>5.75</v>
       </c>
       <c r="G1160" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -35511,7 +35511,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1161" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -35537,7 +35537,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1162" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -35563,7 +35563,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1163" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -35589,7 +35589,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1164" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -35615,7 +35615,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1165" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -35641,7 +35641,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G1166" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -35667,7 +35667,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1167" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -35693,7 +35693,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1168" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -35719,7 +35719,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1169" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -35745,7 +35745,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1170" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -35771,7 +35771,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1171" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -35797,7 +35797,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1172" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -35823,7 +35823,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1173" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -35849,7 +35849,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1174" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -35875,7 +35875,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1175" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -35901,7 +35901,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1176" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -35927,7 +35927,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1177" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -35953,7 +35953,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1178" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -35979,7 +35979,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1179" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -36005,7 +36005,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1180" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -36031,7 +36031,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1181" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -36057,7 +36057,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1182" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -36083,7 +36083,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1183" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -36109,7 +36109,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1184" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -36135,7 +36135,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1185" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -36161,7 +36161,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1186" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -36187,7 +36187,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G1187" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -36213,7 +36213,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1188" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -36239,7 +36239,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1189" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -36265,7 +36265,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G1190" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -36291,7 +36291,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1191" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -36317,7 +36317,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G1192" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -36343,7 +36343,7 @@
         <v>6</v>
       </c>
       <c r="G1193" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -36369,7 +36369,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1194" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -36395,7 +36395,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1195" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -36421,7 +36421,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1196" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -36447,7 +36447,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1197" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -36473,7 +36473,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1198" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -36499,7 +36499,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1199" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -36525,7 +36525,7 @@
         <v>6</v>
       </c>
       <c r="G1200" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -36551,7 +36551,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G1201" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -36577,7 +36577,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1202" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -36603,7 +36603,7 @@
         <v>6</v>
       </c>
       <c r="G1203" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -36629,7 +36629,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G1204" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -36655,7 +36655,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1205" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -36681,7 +36681,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1206" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -36707,7 +36707,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1207" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -36733,7 +36733,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1208" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -36759,7 +36759,7 @@
         <v>5.75</v>
       </c>
       <c r="G1209" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -36785,7 +36785,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1210" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -36811,7 +36811,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1211" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -36837,7 +36837,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1212" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -36863,7 +36863,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1213" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -36889,7 +36889,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1214" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -36915,7 +36915,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1215" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -36941,7 +36941,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G1216" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -36967,7 +36967,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1217" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -36993,7 +36993,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1218" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -37019,7 +37019,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1219" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -37045,7 +37045,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1220" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -37071,7 +37071,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1221" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -37097,7 +37097,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1222" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -37123,7 +37123,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G1223" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -37149,7 +37149,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1224" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -37175,7 +37175,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1225" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -37201,7 +37201,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1226" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -37227,7 +37227,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1227" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -37253,7 +37253,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1228" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -37279,7 +37279,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1229" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -37305,7 +37305,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1230" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -37331,7 +37331,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1231" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -37357,7 +37357,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1232" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -37383,7 +37383,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1233" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -37409,7 +37409,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G1234" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -37435,7 +37435,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1235" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -37461,7 +37461,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1236" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -37487,7 +37487,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G1237" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -37513,7 +37513,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1238" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -37539,7 +37539,7 @@
         <v>6.75</v>
       </c>
       <c r="G1239" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -37565,7 +37565,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1240" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -37591,7 +37591,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1241" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -37617,7 +37617,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1242" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -37643,7 +37643,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1243" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -37669,7 +37669,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1244" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -37695,7 +37695,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1245" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -37721,7 +37721,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1246" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -37747,7 +37747,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G1247" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -37773,7 +37773,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1248" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -37799,7 +37799,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1249" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -37825,7 +37825,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G1250" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -37851,7 +37851,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G1251" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -37877,7 +37877,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1252" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -37903,7 +37903,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1253" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -37929,7 +37929,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1254" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -37955,7 +37955,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1255" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -37981,7 +37981,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G1256" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -38007,7 +38007,7 @@
         <v>6.75</v>
       </c>
       <c r="G1257" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -38033,7 +38033,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1258" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -38059,7 +38059,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1259" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -38085,7 +38085,7 @@
         <v>6.75</v>
       </c>
       <c r="G1260" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -38111,7 +38111,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1261" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -38137,7 +38137,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1262" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -38163,7 +38163,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1263" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -38189,7 +38189,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1264" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -38215,7 +38215,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1265" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -38241,7 +38241,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1266" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -38267,7 +38267,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1267" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -38293,7 +38293,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1268" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -38319,7 +38319,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1269" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -38345,7 +38345,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1270" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -38371,7 +38371,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1271" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -38397,7 +38397,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1272" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -38423,7 +38423,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1273" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -38449,7 +38449,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1274" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -38475,7 +38475,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1275" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -38501,7 +38501,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1276" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -38527,7 +38527,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1277" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -38553,7 +38553,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1278" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -38579,7 +38579,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G1279" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -38605,7 +38605,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1280" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -38631,7 +38631,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1281" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -38657,7 +38657,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1282" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -38683,7 +38683,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1283" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -38709,7 +38709,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G1284" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -38735,7 +38735,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G1285" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -38761,7 +38761,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1286" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -38787,7 +38787,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1287" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -38813,7 +38813,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1288" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -38839,7 +38839,7 @@
         <v>7</v>
       </c>
       <c r="G1289" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -38865,7 +38865,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1290" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -38891,7 +38891,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1291" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -38917,7 +38917,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1292" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -38943,7 +38943,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1293" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -38969,7 +38969,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1294" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -38995,7 +38995,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1295" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -39021,7 +39021,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1296" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -39047,7 +39047,7 @@
         <v>8.5</v>
       </c>
       <c r="G1297" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -39073,7 +39073,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1298" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -39099,7 +39099,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1299" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -39125,7 +39125,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1300" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -39151,7 +39151,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1301" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -39177,7 +39177,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1302" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -39203,7 +39203,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1303" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -39229,7 +39229,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1304" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -39255,7 +39255,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1305" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -39281,7 +39281,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1306" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -39307,7 +39307,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G1307" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -39333,7 +39333,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1308" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -39359,7 +39359,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1309" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -39385,7 +39385,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1310" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -39411,7 +39411,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1311" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -39437,7 +39437,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1312" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -39463,7 +39463,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1313" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -39489,7 +39489,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1314" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -39515,7 +39515,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G1315" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -39541,7 +39541,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1316" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -39567,7 +39567,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1317" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -39593,7 +39593,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1318" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -39619,7 +39619,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1319" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -39645,7 +39645,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1320" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -39671,7 +39671,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1321" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -39697,7 +39697,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1322" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -39723,7 +39723,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1323" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -39749,7 +39749,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1324" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -39775,7 +39775,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1325" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -39801,7 +39801,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1326" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -39827,7 +39827,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G1327" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -39853,7 +39853,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1328" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -39879,7 +39879,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1329" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -39905,7 +39905,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G1330" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -39931,7 +39931,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1331" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -39957,7 +39957,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1332" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -39983,7 +39983,7 @@
         <v>8.75</v>
       </c>
       <c r="G1333" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -40009,7 +40009,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1334" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -40035,7 +40035,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G1335" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -40061,7 +40061,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1336" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -40087,7 +40087,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G1337" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -40113,7 +40113,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G1338" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -40139,7 +40139,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1339" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -40165,7 +40165,7 @@
         <v>9</v>
       </c>
       <c r="G1340" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -40191,7 +40191,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G1341" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -40217,7 +40217,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G1342" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -40243,7 +40243,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1343" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -40269,7 +40269,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G1344" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -40295,7 +40295,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1345" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -40321,7 +40321,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1346" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -40347,7 +40347,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1347" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -40373,7 +40373,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1348" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -40399,7 +40399,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G1349" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -40425,7 +40425,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G1350" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -40451,7 +40451,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1351" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -40477,7 +40477,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G1352" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -40503,7 +40503,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G1353" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -40529,7 +40529,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G1354" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -40555,7 +40555,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1355" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -40581,7 +40581,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G1356" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -40607,7 +40607,7 @@
         <v>9.5</v>
       </c>
       <c r="G1357" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -40633,7 +40633,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G1358" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -40659,7 +40659,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G1359" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -40685,7 +40685,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G1360" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -40711,7 +40711,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G1361" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -40737,7 +40737,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G1362" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -40763,7 +40763,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G1363" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -40789,7 +40789,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1364" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -40815,7 +40815,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G1365" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -40841,7 +40841,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G1366" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -40867,7 +40867,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1367" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -40893,7 +40893,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G1368" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -40919,7 +40919,7 @@
         <v>9.5</v>
       </c>
       <c r="G1369" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -40945,7 +40945,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G1370" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -40971,7 +40971,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1371" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -40997,7 +40997,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G1372" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -41023,7 +41023,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G1373" t="s">
-        <v>935</v>
+        <v>922</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -41049,7 +41049,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1374" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -41361,7 +41361,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1386" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -42193,7 +42193,7 @@
         <v>9.5</v>
       </c>
       <c r="G1418" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -42375,7 +42375,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G1425" t="s">
-        <v>935</v>
+        <v>922</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -42479,7 +42479,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1429" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -42505,7 +42505,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G1430" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -42635,7 +42635,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1435" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -42869,7 +42869,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1444" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -71342,6 +71342,32 @@
         <v>1660</v>
       </c>
       <c r="H2539" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2540">
+      <c r="A2540" s="1" t="n">
+        <v>46020.69125</v>
+      </c>
+      <c r="B2540" t="n">
+        <v>115241</v>
+      </c>
+      <c r="C2540" t="n">
+        <v>19.1399993896484</v>
+      </c>
+      <c r="D2540" t="n">
+        <v>18.7600002288818</v>
+      </c>
+      <c r="E2540" t="n">
+        <v>18.9599990844727</v>
+      </c>
+      <c r="F2540" t="n">
+        <v>18.7999992370605</v>
+      </c>
+      <c r="G2540" t="s">
+        <v>1657</v>
+      </c>
+      <c r="H2540" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CEM.MI.xlsx
+++ b/data/CEM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1663" uniqueCount="1663">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1664" uniqueCount="1664">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">CEM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68036079406738</t>
+    <t xml:space="preserve">4.68036031723022</t>
   </si>
   <si>
     <t xml:space="preserve">4.5565619468689</t>
@@ -56,124 +56,124 @@
     <t xml:space="preserve">4.32893371582031</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22110891342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32494020462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28899955749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29299259185791</t>
+    <t xml:space="preserve">4.22110939025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32494068145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2889986038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29299306869507</t>
   </si>
   <si>
     <t xml:space="preserve">4.06137037277222</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93597531318665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97431230545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67560029029846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83533978462219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94875383377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88006615638733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91680669784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87846922874451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74588584899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93437767028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87367749214172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73789882659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57815909385681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59892535209656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6196916103363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35133004188538</t>
+    <t xml:space="preserve">3.93597483634949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97431206703186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67560076713562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83533954620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94875431060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88006567955017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9168074131012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87846875190735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74588561058044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93437814712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8736777305603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73789858818054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57815957069397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59892511367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61969137191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35132956504822</t>
   </si>
   <si>
     <t xml:space="preserve">3.15005803108215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25069379806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13088989257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20916175842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44238066673279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36251163482666</t>
+    <t xml:space="preserve">3.25069403648376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13088941574097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20916152000427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44238042831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3625111579895</t>
   </si>
   <si>
     <t xml:space="preserve">3.47592616081238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5541980266571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34653759002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39126396179199</t>
+    <t xml:space="preserve">3.55419826507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34653735160828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39126420021057</t>
   </si>
   <si>
     <t xml:space="preserve">3.3673038482666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23951244354248</t>
+    <t xml:space="preserve">3.2395122051239</t>
   </si>
   <si>
     <t xml:space="preserve">3.29222631454468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40244650840759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58614587783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63406801223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55579566955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64365220069885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56058788299561</t>
+    <t xml:space="preserve">3.40244626998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58614611625671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63406825065613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55579590797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64365243911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56058859825134</t>
   </si>
   <si>
     <t xml:space="preserve">3.52065348625183</t>
@@ -188,25 +188,25 @@
     <t xml:space="preserve">3.54940605163574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75227522850037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61330223083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75387239456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83214426040649</t>
+    <t xml:space="preserve">3.75227475166321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61330151557922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75387215614319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83214449882507</t>
   </si>
   <si>
     <t xml:space="preserve">3.67080879211426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70754861831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65802907943726</t>
+    <t xml:space="preserve">3.70754766464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65802931785583</t>
   </si>
   <si>
     <t xml:space="preserve">3.51745843887329</t>
@@ -215,46 +215,46 @@
     <t xml:space="preserve">3.57017207145691</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50947165489197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54301643371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57975697517395</t>
+    <t xml:space="preserve">3.50947141647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54301691055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57975602149963</t>
   </si>
   <si>
     <t xml:space="preserve">3.45196557044983</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41043257713318</t>
+    <t xml:space="preserve">3.41043329238892</t>
   </si>
   <si>
     <t xml:space="preserve">3.37529039382935</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60052275657654</t>
+    <t xml:space="preserve">3.60052251815796</t>
   </si>
   <si>
     <t xml:space="preserve">3.48551034927368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5446138381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59573078155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77943062782288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74428844451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85770344734192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73949599266052</t>
+    <t xml:space="preserve">3.54461407661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5957305431366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77943086624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74428868293762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8577036857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73949575424194</t>
   </si>
   <si>
     <t xml:space="preserve">3.74908018112183</t>
@@ -263,28 +263,28 @@
     <t xml:space="preserve">3.70595073699951</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69317173957825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67719745635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7970027923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.666015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70115852355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62608075141907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67400240898132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64205479621887</t>
+    <t xml:space="preserve">3.69317126274109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67719793319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7970016002655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66601610183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70115828514099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62608122825623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6740026473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64205551147461</t>
   </si>
   <si>
     <t xml:space="preserve">3.53023767471313</t>
@@ -296,46 +296,46 @@
     <t xml:space="preserve">3.47432851791382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53193736076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62187004089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75758934020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76085829734802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.875319480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88349604606628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7772102355957</t>
+    <t xml:space="preserve">3.53193712234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62187099456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75758910179138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7608585357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87531971931458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88349556922913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77720999717712</t>
   </si>
   <si>
     <t xml:space="preserve">3.75431823730469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70526361465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66929006576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59734344482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5842616558075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55646395683289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38640832901001</t>
+    <t xml:space="preserve">3.70526337623596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6692898273468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59734320640564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58426213264465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55646371841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38640809059143</t>
   </si>
   <si>
     <t xml:space="preserve">3.31119084358215</t>
@@ -344,115 +344,115 @@
     <t xml:space="preserve">3.29810976982117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19673037528992</t>
+    <t xml:space="preserve">3.19672989845276</t>
   </si>
   <si>
     <t xml:space="preserve">3.1591215133667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00705194473267</t>
+    <t xml:space="preserve">3.00705170631409</t>
   </si>
   <si>
     <t xml:space="preserve">3.15421605110168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03484988212585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22289228439331</t>
+    <t xml:space="preserve">3.03484964370728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22289252281189</t>
   </si>
   <si>
     <t xml:space="preserve">3.35206985473633</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10679650306702</t>
+    <t xml:space="preserve">3.1067967414856</t>
   </si>
   <si>
     <t xml:space="preserve">2.82881999015808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82064461708069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84026575088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9351053237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04302525520325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95799708366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7961163520813</t>
+    <t xml:space="preserve">2.82064437866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84026622772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93510484695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04302549362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95799732208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79611659049988</t>
   </si>
   <si>
     <t xml:space="preserve">2.76341366767883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76831912994385</t>
+    <t xml:space="preserve">2.76831889152527</t>
   </si>
   <si>
     <t xml:space="preserve">2.84844183921814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87787461280823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04138994216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00051164627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2114462852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13295912742615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07572865486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97434902191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1084315776825</t>
+    <t xml:space="preserve">2.87787437438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04139018058777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00051116943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21144652366638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13295888900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07572841644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97434878349304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10843181610107</t>
   </si>
   <si>
     <t xml:space="preserve">2.9759840965271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92856431007385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17547273635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18037819862366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15585112571716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18855428695679</t>
+    <t xml:space="preserve">2.92856454849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1754732131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18037867546082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15585088729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18855452537537</t>
   </si>
   <si>
     <t xml:space="preserve">3.09862041473389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12151288986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02503895759583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11660766601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23760914802551</t>
+    <t xml:space="preserve">3.12151312828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02503871917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11660742759705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23760890960693</t>
   </si>
   <si>
     <t xml:space="preserve">3.28012299537659</t>
@@ -464,106 +464,106 @@
     <t xml:space="preserve">3.43546271324158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40602993965149</t>
+    <t xml:space="preserve">3.40602970123291</t>
   </si>
   <si>
     <t xml:space="preserve">3.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43709778785706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44854402542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67910122871399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64639806747437</t>
+    <t xml:space="preserve">3.43709802627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44854354858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67910027503967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64639759063721</t>
   </si>
   <si>
     <t xml:space="preserve">3.71834516525269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69545269012451</t>
+    <t xml:space="preserve">3.69545245170593</t>
   </si>
   <si>
     <t xml:space="preserve">3.74450731277466</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85242676734924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80827784538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82299494743347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80337333679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7428719997406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62350583076477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56627535820007</t>
+    <t xml:space="preserve">3.85242795944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80827808380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82299470901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80337285995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74287247657776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62350559234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56627559661865</t>
   </si>
   <si>
     <t xml:space="preserve">3.47470641136169</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51558589935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65947914123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60551857948303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54501843452454</t>
+    <t xml:space="preserve">3.51558518409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65947937965393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60551905632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54501795768738</t>
   </si>
   <si>
     <t xml:space="preserve">3.64803314208984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64476275444031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38804316520691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4828827381134</t>
+    <t xml:space="preserve">3.64476323127747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38804364204407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48288249969482</t>
   </si>
   <si>
     <t xml:space="preserve">3.45344948768616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43382716178894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50740933418274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56464004516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55482935905457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56300449371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4845175743103</t>
+    <t xml:space="preserve">3.4338276386261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50741004943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56464028358459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55482912063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56300520896912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48451781272888</t>
   </si>
   <si>
     <t xml:space="preserve">3.54338312149048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62514042854309</t>
+    <t xml:space="preserve">3.62514066696167</t>
   </si>
   <si>
     <t xml:space="preserve">3.59080266952515</t>
@@ -572,43 +572,43 @@
     <t xml:space="preserve">3.64149236679077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6889123916626</t>
+    <t xml:space="preserve">3.68891215324402</t>
   </si>
   <si>
     <t xml:space="preserve">3.66111445426941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68727707862854</t>
+    <t xml:space="preserve">3.68727684020996</t>
   </si>
   <si>
     <t xml:space="preserve">3.53684234619141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63004612922668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63822174072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43873286247253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41747570037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41911125183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33571815490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37169194221497</t>
+    <t xml:space="preserve">3.63004684448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63822197914124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43873333930969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41747617721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41911172866821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33571839332581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37169170379639</t>
   </si>
   <si>
     <t xml:space="preserve">3.27521753311157</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22125768661499</t>
+    <t xml:space="preserve">3.22125720977783</t>
   </si>
   <si>
     <t xml:space="preserve">3.2098114490509</t>
@@ -617,13 +617,13 @@
     <t xml:space="preserve">3.17710828781128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21308183670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14767551422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11333680152893</t>
+    <t xml:space="preserve">3.21308159828186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14767527580261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11333727836609</t>
   </si>
   <si>
     <t xml:space="preserve">3.00541687011719</t>
@@ -632,13 +632,13 @@
     <t xml:space="preserve">3.01686310768127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9530918598175</t>
+    <t xml:space="preserve">2.95309209823608</t>
   </si>
   <si>
     <t xml:space="preserve">2.91875338554382</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96453785896301</t>
+    <t xml:space="preserve">2.96453762054443</t>
   </si>
   <si>
     <t xml:space="preserve">2.96780824661255</t>
@@ -650,46 +650,46 @@
     <t xml:space="preserve">3.04793095588684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17220282554626</t>
+    <t xml:space="preserve">3.17220330238342</t>
   </si>
   <si>
     <t xml:space="preserve">3.18691897392273</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31936717033386</t>
+    <t xml:space="preserve">3.3193666934967</t>
   </si>
   <si>
     <t xml:space="preserve">3.2343385219574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45835518836975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48778748512268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45181441307068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4992344379425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57281589508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45017910003662</t>
+    <t xml:space="preserve">3.45835494995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48778772354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45181465148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49923419952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57281613349915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4501793384552</t>
   </si>
   <si>
     <t xml:space="preserve">3.61369490623474</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67746591567993</t>
+    <t xml:space="preserve">3.67746567726135</t>
   </si>
   <si>
     <t xml:space="preserve">3.58916759490967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70362854003906</t>
+    <t xml:space="preserve">3.70362901687622</t>
   </si>
   <si>
     <t xml:space="preserve">3.4861524105072</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">3.33244824409485</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28666353225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22943329811096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27031230926514</t>
+    <t xml:space="preserve">3.28666377067566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22943305969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27031207084656</t>
   </si>
   <si>
     <t xml:space="preserve">3.24741983413696</t>
@@ -725,55 +725,55 @@
     <t xml:space="preserve">3.23597359657288</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0012264251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04701137542725</t>
+    <t xml:space="preserve">4.00122690200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04701089859009</t>
   </si>
   <si>
     <t xml:space="preserve">4.12876987457275</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16964769363403</t>
+    <t xml:space="preserve">4.16964817047119</t>
   </si>
   <si>
     <t xml:space="preserve">4.17782354354858</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06336355209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95707774162292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19417524337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28410816192627</t>
+    <t xml:space="preserve">4.06336212158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95707750320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19417572021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28410863876343</t>
   </si>
   <si>
     <t xml:space="preserve">4.3454270362854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47215223312378</t>
+    <t xml:space="preserve">4.47215175628662</t>
   </si>
   <si>
     <t xml:space="preserve">4.43944835662842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41083383560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41492080688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37404298782349</t>
+    <t xml:space="preserve">4.41083335876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41492128372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37404203414917</t>
   </si>
   <si>
     <t xml:space="preserve">4.26775693893433</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39039468765259</t>
+    <t xml:space="preserve">4.39039373397827</t>
   </si>
   <si>
     <t xml:space="preserve">4.3617787361145</t>
@@ -782,25 +782,25 @@
     <t xml:space="preserve">4.3781304359436</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38630533218384</t>
+    <t xml:space="preserve">4.386305809021</t>
   </si>
   <si>
     <t xml:space="preserve">4.56208515167236</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42718458175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32907629013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25549364089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25140523910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30046033859253</t>
+    <t xml:space="preserve">4.42718505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3290753364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2554931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25140571594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30046081542969</t>
   </si>
   <si>
     <t xml:space="preserve">4.34951496124268</t>
@@ -812,46 +812,46 @@
     <t xml:space="preserve">4.24731826782227</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21052742004395</t>
+    <t xml:space="preserve">4.21052694320679</t>
   </si>
   <si>
     <t xml:space="preserve">4.14512062072754</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10424137115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2227897644043</t>
+    <t xml:space="preserve">4.10424184799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22279071807861</t>
   </si>
   <si>
     <t xml:space="preserve">4.40674543380737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36586618423462</t>
+    <t xml:space="preserve">4.36586666107178</t>
   </si>
   <si>
     <t xml:space="preserve">4.27593278884888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30454778671265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28002119064331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44762420654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.529381275177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51711893081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52120685577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68063354492188</t>
+    <t xml:space="preserve">4.3045482635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28002071380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44762468338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52938222885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51711940765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52120590209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68063449859619</t>
   </si>
   <si>
     <t xml:space="preserve">4.66019487380981</t>
@@ -869,22 +869,22 @@
     <t xml:space="preserve">4.81144666671753</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65201807022095</t>
+    <t xml:space="preserve">4.65201950073242</t>
   </si>
   <si>
     <t xml:space="preserve">4.34133863449097</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33725118637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25958156585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40383386611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44966411590576</t>
+    <t xml:space="preserve">4.33725070953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25958108901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40383434295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44966459274292</t>
   </si>
   <si>
     <t xml:space="preserve">4.41633367538452</t>
@@ -896,25 +896,25 @@
     <t xml:space="preserve">4.36633682250977</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30384159088135</t>
+    <t xml:space="preserve">4.30384254455566</t>
   </si>
   <si>
     <t xml:space="preserve">4.27467775344849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25801229476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31634140014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26634502410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20801687240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33300638198853</t>
+    <t xml:space="preserve">4.25801181793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31634092330933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26634454727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20801639556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33300590515137</t>
   </si>
   <si>
     <t xml:space="preserve">4.3705039024353</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">4.34550523757935</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39133501052856</t>
+    <t xml:space="preserve">4.39133548736572</t>
   </si>
   <si>
     <t xml:space="preserve">4.29967546463013</t>
@@ -932,16 +932,16 @@
     <t xml:space="preserve">4.42883205413818</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39966821670532</t>
+    <t xml:space="preserve">4.39966869354248</t>
   </si>
   <si>
     <t xml:space="preserve">4.3955020904541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38300228118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46632957458496</t>
+    <t xml:space="preserve">4.38300275802612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46633005142212</t>
   </si>
   <si>
     <t xml:space="preserve">4.48299503326416</t>
@@ -950,61 +950,61 @@
     <t xml:space="preserve">4.56632232666016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40800046920776</t>
+    <t xml:space="preserve">4.40800094604492</t>
   </si>
   <si>
     <t xml:space="preserve">4.34967136383057</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69131278991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5829873085022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85380077362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99962329864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05795192718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10794830322266</t>
+    <t xml:space="preserve">4.69131326675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58298778533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85380029678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99962282180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0579514503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1079478263855</t>
   </si>
   <si>
     <t xml:space="preserve">5.24960422515869</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28710126876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25377035140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41625785827637</t>
+    <t xml:space="preserve">5.28710031509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25376987457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41625833511353</t>
   </si>
   <si>
     <t xml:space="preserve">5.30376672744751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29959964752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34542989730835</t>
+    <t xml:space="preserve">5.29960060119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34543037414551</t>
   </si>
   <si>
     <t xml:space="preserve">5.30793285369873</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22877216339111</t>
+    <t xml:space="preserve">5.22877264022827</t>
   </si>
   <si>
     <t xml:space="preserve">5.29126739501953</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29543352127075</t>
+    <t xml:space="preserve">5.29543399810791</t>
   </si>
   <si>
     <t xml:space="preserve">5.16211080551147</t>
@@ -1013,10 +1013,10 @@
     <t xml:space="preserve">5.01628828048706</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05378532409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12461376190186</t>
+    <t xml:space="preserve">5.05378580093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1246132850647</t>
   </si>
   <si>
     <t xml:space="preserve">5.20377397537231</t>
@@ -1025,13 +1025,13 @@
     <t xml:space="preserve">5.07461738586426</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0329532623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95795965194702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99129009246826</t>
+    <t xml:space="preserve">5.03295373916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95795869827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99129056930542</t>
   </si>
   <si>
     <t xml:space="preserve">4.96212530136108</t>
@@ -1046,46 +1046,46 @@
     <t xml:space="preserve">4.89129781723022</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90379667282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9537935256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94545984268188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91629600524902</t>
+    <t xml:space="preserve">4.90379762649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95379304885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94545936584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91629648208618</t>
   </si>
   <si>
     <t xml:space="preserve">5.02462100982666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04961919784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1162805557251</t>
+    <t xml:space="preserve">5.04961824417114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11628007888794</t>
   </si>
   <si>
     <t xml:space="preserve">5.17460966110229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23293876647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17877578735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1329460144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33293104171753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26626968383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22460651397705</t>
+    <t xml:space="preserve">5.23293828964233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17877626419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13294506072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33293151855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26626920700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22460603713989</t>
   </si>
   <si>
     <t xml:space="preserve">5.58291244506836</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">5.68707132339478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00371360778809</t>
+    <t xml:space="preserve">6.00371313095093</t>
   </si>
   <si>
     <t xml:space="preserve">5.80789470672607</t>
@@ -1103,25 +1103,25 @@
     <t xml:space="preserve">6.0745415687561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01621341705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16620206832886</t>
+    <t xml:space="preserve">6.01621198654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1662015914917</t>
   </si>
   <si>
     <t xml:space="preserve">5.89122200012207</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94121885299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96621608734131</t>
+    <t xml:space="preserve">5.94121837615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96621656417847</t>
   </si>
   <si>
     <t xml:space="preserve">6.03287792205811</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9953818321228</t>
+    <t xml:space="preserve">5.99538040161133</t>
   </si>
   <si>
     <t xml:space="preserve">5.97038269042969</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">5.91622018814087</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86205816268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92871952056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89955520629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90372133255005</t>
+    <t xml:space="preserve">5.86205720901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92871904373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89955472946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90372085571289</t>
   </si>
   <si>
     <t xml:space="preserve">5.87455701828003</t>
@@ -1148,55 +1148,55 @@
     <t xml:space="preserve">5.84539222717285</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00788021087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98288202285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03704500198364</t>
+    <t xml:space="preserve">6.00788068771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98288154602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03704452514648</t>
   </si>
   <si>
     <t xml:space="preserve">6.0912070274353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02871179580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99954748153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0495433807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07870864868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29119253158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17453384399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1995325088501</t>
+    <t xml:space="preserve">6.02871227264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99954795837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04954385757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07870769500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29119205474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1745343208313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19953203201294</t>
   </si>
   <si>
     <t xml:space="preserve">6.08287477493286</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24536180496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21203184127808</t>
+    <t xml:space="preserve">6.24536275863647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21203136444092</t>
   </si>
   <si>
     <t xml:space="preserve">6.02454566955566</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09954023361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18286752700806</t>
+    <t xml:space="preserve">6.0995397567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1828670501709</t>
   </si>
   <si>
     <t xml:space="preserve">6.2078652381897</t>
@@ -1205,13 +1205,13 @@
     <t xml:space="preserve">6.22036409378052</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14537000656128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95788383483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94538545608521</t>
+    <t xml:space="preserve">6.14536905288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95788431167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94538497924805</t>
   </si>
   <si>
     <t xml:space="preserve">6.01204681396484</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">6.02037954330444</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11620569229126</t>
+    <t xml:space="preserve">6.1162052154541</t>
   </si>
   <si>
     <t xml:space="preserve">6.06204319000244</t>
@@ -1229,7 +1229,7 @@
     <t xml:space="preserve">6.04121065139771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14953660964966</t>
+    <t xml:space="preserve">6.1495361328125</t>
   </si>
   <si>
     <t xml:space="preserve">6.09537363052368</t>
@@ -1238,7 +1238,7 @@
     <t xml:space="preserve">6.35785388946533</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22453022003174</t>
+    <t xml:space="preserve">6.2245306968689</t>
   </si>
   <si>
     <t xml:space="preserve">6.28285932540894</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">6.58283710479736</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61616802215576</t>
+    <t xml:space="preserve">6.6161675453186</t>
   </si>
   <si>
     <t xml:space="preserve">6.57450389862061</t>
@@ -1256,25 +1256,25 @@
     <t xml:space="preserve">6.50784254074097</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49951028823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65783071517944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7411584854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59116888046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62449979782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63283348083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7078275680542</t>
+    <t xml:space="preserve">6.49950981140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6578311920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74115896224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5911693572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6245002746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6328330039978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70782804489136</t>
   </si>
   <si>
     <t xml:space="preserve">6.52450799942017</t>
@@ -1286,58 +1286,58 @@
     <t xml:space="preserve">6.66616439819336</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54950666427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44951295852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29952478408813</t>
+    <t xml:space="preserve">6.54950618743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44951391220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29952526092529</t>
   </si>
   <si>
     <t xml:space="preserve">6.2328634262085</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90788745880127</t>
+    <t xml:space="preserve">5.90788793563843</t>
   </si>
   <si>
     <t xml:space="preserve">5.93288612365723</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53284168243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26619482040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36618614196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33285617828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14120388031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15786838531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06620931625366</t>
+    <t xml:space="preserve">6.53284120559692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26619434356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36618566513062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33285570144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1412034034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1578688621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06620836257935</t>
   </si>
   <si>
     <t xml:space="preserve">5.94955110549927</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13287162780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05787706375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88288974761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84955883026123</t>
+    <t xml:space="preserve">6.13287019729614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05787563323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88288879394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84955835342407</t>
   </si>
   <si>
     <t xml:space="preserve">5.81622791290283</t>
@@ -1352,43 +1352,43 @@
     <t xml:space="preserve">5.76623153686523</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68290424346924</t>
+    <t xml:space="preserve">5.68290519714355</t>
   </si>
   <si>
     <t xml:space="preserve">5.82456016540527</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86622476577759</t>
+    <t xml:space="preserve">5.86622381210327</t>
   </si>
   <si>
     <t xml:space="preserve">5.77456426620483</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78289651870728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79122972488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63290786743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6498236656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68365526199341</t>
+    <t xml:space="preserve">5.78289747238159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79122924804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63290929794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64982414245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68365478515625</t>
   </si>
   <si>
     <t xml:space="preserve">5.66673994064331</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70057058334351</t>
+    <t xml:space="preserve">5.70057106018066</t>
   </si>
   <si>
     <t xml:space="preserve">5.48066806793213</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45529413223267</t>
+    <t xml:space="preserve">5.45529460906982</t>
   </si>
   <si>
     <t xml:space="preserve">5.54833078384399</t>
@@ -1397,22 +1397,22 @@
     <t xml:space="preserve">5.53987312316895</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74286031723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58216190338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65828132629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70902919769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77669095993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91201591491699</t>
+    <t xml:space="preserve">5.74286079406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58216142654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6582818031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70902872085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77669191360474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91201639175415</t>
   </si>
   <si>
     <t xml:space="preserve">5.9035587310791</t>
@@ -1421,13 +1421,13 @@
     <t xml:space="preserve">5.89510059356689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75131797790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78514862060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71748638153076</t>
+    <t xml:space="preserve">5.75131845474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78514957427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71748685836792</t>
   </si>
   <si>
     <t xml:space="preserve">5.81052303314209</t>
@@ -1439,40 +1439,40 @@
     <t xml:space="preserve">5.50604152679443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69211339950562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72594451904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73440217971802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60753536224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51449918746948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67519807815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01351022720337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99659442901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81898021697998</t>
+    <t xml:space="preserve">5.69211387634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72594499588013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73440313339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60753488540649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51449966430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67519760131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01351118087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99659538269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81898069381714</t>
   </si>
   <si>
     <t xml:space="preserve">5.75977563858032</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80206489562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79360675811768</t>
+    <t xml:space="preserve">5.80206537246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79360771179199</t>
   </si>
   <si>
     <t xml:space="preserve">5.88664293289185</t>
@@ -1484,52 +1484,52 @@
     <t xml:space="preserve">5.92893171310425</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85281181335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76823329925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82743835449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83589649200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42992115020752</t>
+    <t xml:space="preserve">5.85281276702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76823377609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82743787765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83589601516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4299201965332</t>
   </si>
   <si>
     <t xml:space="preserve">5.38763189315796</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33688497543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26076459884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30305433273315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43837881088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46375274658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44683599472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35380077362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3707160949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22693300247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14235544204712</t>
+    <t xml:space="preserve">5.33688449859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26076412200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30305337905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43837833404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46375226974487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44683647155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35379981994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37071561813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22693347930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14235496520996</t>
   </si>
   <si>
     <t xml:space="preserve">5.11698198318481</t>
@@ -1538,22 +1538,22 @@
     <t xml:space="preserve">5.24384832382202</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13389730453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2692232131958</t>
+    <t xml:space="preserve">5.1338963508606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26922273635864</t>
   </si>
   <si>
     <t xml:space="preserve">5.25230646133423</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21001720428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23539066314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2861385345459</t>
+    <t xml:space="preserve">5.21001672744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23539161682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28613758087158</t>
   </si>
   <si>
     <t xml:space="preserve">5.31996917724609</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">5.29459571838379</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48912525177002</t>
+    <t xml:space="preserve">5.48912620544434</t>
   </si>
   <si>
     <t xml:space="preserve">5.3284273147583</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">5.16772842407227</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09160804748535</t>
+    <t xml:space="preserve">5.09160852432251</t>
   </si>
   <si>
     <t xml:space="preserve">5.17618608474731</t>
@@ -1580,10 +1580,10 @@
     <t xml:space="preserve">5.10852336883545</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91399431228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60105419158936</t>
+    <t xml:space="preserve">4.91399383544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60105466842651</t>
   </si>
   <si>
     <t xml:space="preserve">4.49956083297729</t>
@@ -1592,61 +1592,61 @@
     <t xml:space="preserve">4.567223072052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38115119934082</t>
+    <t xml:space="preserve">4.3811502456665</t>
   </si>
   <si>
     <t xml:space="preserve">4.54185009002686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5249342918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61796951293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46572923660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27120018005371</t>
+    <t xml:space="preserve">4.52493381500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61796998977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46572971343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27119970321655</t>
   </si>
   <si>
     <t xml:space="preserve">4.14433240890503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22045230865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09358549118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20353746414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15701913833618</t>
+    <t xml:space="preserve">4.22045278549194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09358501434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20353698730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15701866149902</t>
   </si>
   <si>
     <t xml:space="preserve">4.39806652069092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53339147567749</t>
+    <t xml:space="preserve">4.53339195251465</t>
   </si>
   <si>
     <t xml:space="preserve">4.59259653091431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60951232910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63488578796387</t>
+    <t xml:space="preserve">4.6095118522644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63488531112671</t>
   </si>
   <si>
     <t xml:space="preserve">4.41498184204102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49110221862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42343997955322</t>
+    <t xml:space="preserve">4.49110269546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42344045639038</t>
   </si>
   <si>
     <t xml:space="preserve">4.43189764022827</t>
@@ -1655,40 +1655,40 @@
     <t xml:space="preserve">4.2965726852417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33886241912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19507884979248</t>
+    <t xml:space="preserve">4.33886194229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19507932662964</t>
   </si>
   <si>
     <t xml:space="preserve">4.0470666885376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08512735366821</t>
+    <t xml:space="preserve">4.08512687683105</t>
   </si>
   <si>
     <t xml:space="preserve">4.10627222061157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15279006958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23736906051636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21622276306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16124820709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10204362869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03860950469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30503129959106</t>
+    <t xml:space="preserve">4.15278911590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23736810684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21622323989868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16124725341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10204315185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03860902786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30503082275391</t>
   </si>
   <si>
     <t xml:space="preserve">4.25428438186646</t>
@@ -1697,79 +1697,79 @@
     <t xml:space="preserve">4.14010334014893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0512957572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14856100082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08935642242432</t>
+    <t xml:space="preserve">4.05129623413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14856147766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08935689926147</t>
   </si>
   <si>
     <t xml:space="preserve">4.03438091278076</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94557309150696</t>
+    <t xml:space="preserve">3.94557356834412</t>
   </si>
   <si>
     <t xml:space="preserve">4.35577774047852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31348848342896</t>
+    <t xml:space="preserve">4.31348896026611</t>
   </si>
   <si>
     <t xml:space="preserve">4.48264503479004</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65180110931396</t>
+    <t xml:space="preserve">4.65180158615112</t>
   </si>
   <si>
     <t xml:space="preserve">4.7955846786499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7871265411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82095766067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86324691772461</t>
+    <t xml:space="preserve">4.78712606430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82095813751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86324739456177</t>
   </si>
   <si>
     <t xml:space="preserve">4.90553617477417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88862037658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95628261566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00703001022339</t>
+    <t xml:space="preserve">4.88862085342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95628213882446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00703048706055</t>
   </si>
   <si>
     <t xml:space="preserve">5.01548767089844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03240346908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05777645111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99011421203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97319793701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20156002044678</t>
+    <t xml:space="preserve">5.03240299224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.057776927948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99011468887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97319889068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20155954360962</t>
   </si>
   <si>
     <t xml:space="preserve">5.12543916702271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15927076339722</t>
+    <t xml:space="preserve">5.15927028656006</t>
   </si>
   <si>
     <t xml:space="preserve">5.21847534179688</t>
@@ -1778,22 +1778,22 @@
     <t xml:space="preserve">5.34534311294556</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27767992019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40454769134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39609003067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47221040725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49758338928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42146348953247</t>
+    <t xml:space="preserve">5.27767944335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40454721450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39608955383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47220993041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49758386611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.421462059021</t>
   </si>
   <si>
     <t xml:space="preserve">5.41300535202026</t>
@@ -1802,19 +1802,19 @@
     <t xml:space="preserve">4.98165655136108</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11462497711182</t>
+    <t xml:space="preserve">5.11462450027466</t>
   </si>
   <si>
     <t xml:space="preserve">5.13193321228027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01942873001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01077508926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06269979476929</t>
+    <t xml:space="preserve">5.01942920684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01077461242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06269931793213</t>
   </si>
   <si>
     <t xml:space="preserve">5.08866214752197</t>
@@ -1823,13 +1823,13 @@
     <t xml:space="preserve">5.09731674194336</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1405873298645</t>
+    <t xml:space="preserve">5.14058780670166</t>
   </si>
   <si>
     <t xml:space="preserve">5.20116710662842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17520380020142</t>
+    <t xml:space="preserve">5.17520427703857</t>
   </si>
   <si>
     <t xml:space="preserve">5.2271294593811</t>
@@ -1838,7 +1838,7 @@
     <t xml:space="preserve">5.26174640655518</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23578405380249</t>
+    <t xml:space="preserve">5.23578357696533</t>
   </si>
   <si>
     <t xml:space="preserve">5.25309181213379</t>
@@ -1847,13 +1847,13 @@
     <t xml:space="preserve">5.33963394165039</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46079254150391</t>
+    <t xml:space="preserve">5.46079206466675</t>
   </si>
   <si>
     <t xml:space="preserve">5.54733467102051</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42617607116699</t>
+    <t xml:space="preserve">5.42617559432983</t>
   </si>
   <si>
     <t xml:space="preserve">5.330979347229</t>
@@ -1865,43 +1865,43 @@
     <t xml:space="preserve">5.57329654693604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52137184143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47810125350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64253044128418</t>
+    <t xml:space="preserve">5.52137231826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47810029983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64253091812134</t>
   </si>
   <si>
     <t xml:space="preserve">5.7636890411377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74637985229492</t>
+    <t xml:space="preserve">5.7463812828064</t>
   </si>
   <si>
     <t xml:space="preserve">5.72907209396362</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65118503570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70310974121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66849279403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59925985336304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49540948867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45213842391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56464195251465</t>
+    <t xml:space="preserve">5.65118455886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70311069488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66849327087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59925937652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49540901184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45213794708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56464242935181</t>
   </si>
   <si>
     <t xml:space="preserve">5.73772668838501</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">5.1838583946228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28770875930786</t>
+    <t xml:space="preserve">5.28770923614502</t>
   </si>
   <si>
     <t xml:space="preserve">5.19251298904419</t>
@@ -1928,70 +1928,70 @@
     <t xml:space="preserve">5.2704005241394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0800085067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14924192428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16654968261719</t>
+    <t xml:space="preserve">5.08000802993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14924144744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16655015945435</t>
   </si>
   <si>
     <t xml:space="preserve">5.15789556503296</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29636240005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53867959976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44348478317261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48675441741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40021324157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36559629440308</t>
+    <t xml:space="preserve">5.29636287689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53868007659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44348382949829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48675489425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40021276473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36559677124023</t>
   </si>
   <si>
     <t xml:space="preserve">5.32232570648193</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38290405273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02808332443237</t>
+    <t xml:space="preserve">5.38290500640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02808284759521</t>
   </si>
   <si>
     <t xml:space="preserve">5.04539155960083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16222381591797</t>
+    <t xml:space="preserve">5.16222286224365</t>
   </si>
   <si>
     <t xml:space="preserve">5.03933334350586</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10597038269043</t>
+    <t xml:space="preserve">5.10597133636475</t>
   </si>
   <si>
     <t xml:space="preserve">5.15270328521729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20895528793335</t>
+    <t xml:space="preserve">5.20895576477051</t>
   </si>
   <si>
     <t xml:space="preserve">5.27905464172363</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34569215774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32665300369263</t>
+    <t xml:space="preserve">5.3456916809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32665252685547</t>
   </si>
   <si>
     <t xml:space="preserve">5.27992010116577</t>
@@ -2003,10 +2003,10 @@
     <t xml:space="preserve">5.26780366897583</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34742212295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21934127807617</t>
+    <t xml:space="preserve">5.34742259979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21934080123901</t>
   </si>
   <si>
     <t xml:space="preserve">5.34309530258179</t>
@@ -2018,16 +2018,16 @@
     <t xml:space="preserve">5.4391565322876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3179988861084</t>
+    <t xml:space="preserve">5.31799840927124</t>
   </si>
   <si>
     <t xml:space="preserve">5.51791000366211</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61656713485718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51617908477783</t>
+    <t xml:space="preserve">5.61656808853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51617956161499</t>
   </si>
   <si>
     <t xml:space="preserve">5.46252346038818</t>
@@ -2039,34 +2039,34 @@
     <t xml:space="preserve">5.46771574020386</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44434928894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46944713592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78099727630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02331447601318</t>
+    <t xml:space="preserve">5.44434976577759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46944618225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78099775314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02331495285034</t>
   </si>
   <si>
     <t xml:space="preserve">6.0406231880188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04927682876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94456195831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76974630355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78272867202759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75416994094849</t>
+    <t xml:space="preserve">6.04927635192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94456148147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76974678039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78272819519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75416946411133</t>
   </si>
   <si>
     <t xml:space="preserve">5.74118757247925</t>
@@ -2078,16 +2078,16 @@
     <t xml:space="preserve">5.81042194366455</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90561819076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9333119392395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94110012054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91081047058105</t>
+    <t xml:space="preserve">5.90561771392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93331098556519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94109964370728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9108099937439</t>
   </si>
   <si>
     <t xml:space="preserve">5.92638778686523</t>
@@ -2096,13 +2096,13 @@
     <t xml:space="preserve">5.85369300842285</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85628843307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68060970306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73253488540649</t>
+    <t xml:space="preserve">5.85628890991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68060874938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73253440856934</t>
   </si>
   <si>
     <t xml:space="preserve">5.81907606124878</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">5.90648317337036</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70570611953735</t>
+    <t xml:space="preserve">5.7057056427002</t>
   </si>
   <si>
     <t xml:space="preserve">5.57502794265747</t>
@@ -2120,91 +2120,91 @@
     <t xml:space="preserve">5.75590038299561</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81561374664307</t>
+    <t xml:space="preserve">5.81561422348022</t>
   </si>
   <si>
     <t xml:space="preserve">5.76022720336914</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73513031005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72041797637939</t>
+    <t xml:space="preserve">5.73513078689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72041845321655</t>
   </si>
   <si>
     <t xml:space="preserve">5.69791746139526</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69272470474243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62868404388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75936222076416</t>
+    <t xml:space="preserve">5.69272422790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62868356704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.759361743927</t>
   </si>
   <si>
     <t xml:space="preserve">5.65810823440552</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57243204116821</t>
+    <t xml:space="preserve">5.57243156433105</t>
   </si>
   <si>
     <t xml:space="preserve">5.62522220611572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6728196144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58195114135742</t>
+    <t xml:space="preserve">5.67282009124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58195161819458</t>
   </si>
   <si>
     <t xml:space="preserve">5.58454751968384</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64512586593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72561120986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61483669281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60704851150513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65291595458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65551137924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75503492355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84071111679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00600624084473</t>
+    <t xml:space="preserve">5.6451268196106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72561073303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61483716964722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60704898834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65291547775269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6555118560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75503540039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84071159362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00600671768188</t>
   </si>
   <si>
     <t xml:space="preserve">5.92811870574951</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87619400024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71436023712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42184925079346</t>
+    <t xml:space="preserve">5.87619352340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71436071395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4218487739563</t>
   </si>
   <si>
     <t xml:space="preserve">5.36213445663452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19510889053345</t>
+    <t xml:space="preserve">5.19510793685913</t>
   </si>
   <si>
     <t xml:space="preserve">5.04019927978516</t>
@@ -2213,10 +2213,10 @@
     <t xml:space="preserve">5.15443420410156</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18039655685425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79615068435669</t>
+    <t xml:space="preserve">5.18039703369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79615020751953</t>
   </si>
   <si>
     <t xml:space="preserve">4.24358081817627</t>
@@ -2225,7 +2225,7 @@
     <t xml:space="preserve">4.30113124847412</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30718946456909</t>
+    <t xml:space="preserve">4.30718898773193</t>
   </si>
   <si>
     <t xml:space="preserve">3.94501161575317</t>
@@ -2234,13 +2234,13 @@
     <t xml:space="preserve">4.11073923110962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98092603683472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77452349662781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89438462257385</t>
+    <t xml:space="preserve">3.98092651367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77452373504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89438486099243</t>
   </si>
   <si>
     <t xml:space="preserve">4.17564535140991</t>
@@ -2249,31 +2249,31 @@
     <t xml:space="preserve">3.82385277748108</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97486853599548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07006502151489</t>
+    <t xml:space="preserve">3.9748682975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07006406784058</t>
   </si>
   <si>
     <t xml:space="preserve">4.27387094497681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11766242980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05665016174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25699472427368</t>
+    <t xml:space="preserve">4.11766290664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05665063858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.256995677948</t>
   </si>
   <si>
     <t xml:space="preserve">4.30978584289551</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37036561965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17131853103638</t>
+    <t xml:space="preserve">4.37036514282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17131900787354</t>
   </si>
   <si>
     <t xml:space="preserve">4.32709360122681</t>
@@ -2282,70 +2282,70 @@
     <t xml:space="preserve">4.45690679550171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61268138885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48286914825439</t>
+    <t xml:space="preserve">4.61268186569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48286867141724</t>
   </si>
   <si>
     <t xml:space="preserve">4.62999105453491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.569411277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57806539535522</t>
+    <t xml:space="preserve">4.56941175460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57806491851807</t>
   </si>
   <si>
     <t xml:space="preserve">4.52614068984985</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50017786026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74249410629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76845741271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79441928863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94154119491577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91557884216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83769130706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58671951293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5521035194397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62133646011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67326164245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80307483673096</t>
+    <t xml:space="preserve">4.50017738342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74249505996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76845836639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79442024230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94154167175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91557836532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83769083023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58671998977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55210304260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62133693695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6732611656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8030743598938</t>
   </si>
   <si>
     <t xml:space="preserve">4.90961217880249</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73204851150513</t>
+    <t xml:space="preserve">4.73204898834229</t>
   </si>
   <si>
     <t xml:space="preserve">4.88297748565674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91848945617676</t>
+    <t xml:space="preserve">4.91849040985107</t>
   </si>
   <si>
     <t xml:space="preserve">5.10493087768555</t>
@@ -2354,7 +2354,7 @@
     <t xml:space="preserve">5.22034645080566</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19371223449707</t>
+    <t xml:space="preserve">5.19371175765991</t>
   </si>
   <si>
     <t xml:space="preserve">5.39790964126587</t>
@@ -2363,67 +2363,67 @@
     <t xml:space="preserve">5.44230031967163</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3002495765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52220296859741</t>
+    <t xml:space="preserve">5.30025005340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52220344543457</t>
   </si>
   <si>
     <t xml:space="preserve">5.49556922912598</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60210704803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72640085220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81518220901489</t>
+    <t xml:space="preserve">5.60210657119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72640132904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81518268585205</t>
   </si>
   <si>
     <t xml:space="preserve">5.63761949539185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30912780761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27361536026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23810291290283</t>
+    <t xml:space="preserve">5.30912828445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27361583709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23810338973999</t>
   </si>
   <si>
     <t xml:space="preserve">5.55771636962891</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73527908325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61098527908325</t>
+    <t xml:space="preserve">5.73527956008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61098480224609</t>
   </si>
   <si>
     <t xml:space="preserve">5.65537595748901</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68200969696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61986351013184</t>
+    <t xml:space="preserve">5.68201017379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61986255645752</t>
   </si>
   <si>
     <t xml:space="preserve">5.64649772644043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71752214431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58435106277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56659460067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53108215332031</t>
+    <t xml:space="preserve">5.71752262115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5843505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56659412384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53108167648315</t>
   </si>
   <si>
     <t xml:space="preserve">5.4600567817688</t>
@@ -2432,13 +2432,13 @@
     <t xml:space="preserve">5.35351896286011</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42454385757446</t>
+    <t xml:space="preserve">5.42454433441162</t>
   </si>
   <si>
     <t xml:space="preserve">5.41566610336304</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31800651550293</t>
+    <t xml:space="preserve">5.31800603866577</t>
   </si>
   <si>
     <t xml:space="preserve">5.38903141021729</t>
@@ -2447,10 +2447,10 @@
     <t xml:space="preserve">5.29137182235718</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2114691734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36239719390869</t>
+    <t xml:space="preserve">5.21146869659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36239671707153</t>
   </si>
   <si>
     <t xml:space="preserve">5.255859375</t>
@@ -2459,19 +2459,19 @@
     <t xml:space="preserve">5.26473760604858</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37127590179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48669099807739</t>
+    <t xml:space="preserve">5.37127542495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48669052124023</t>
   </si>
   <si>
     <t xml:space="preserve">5.59322881698608</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53995990753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5044469833374</t>
+    <t xml:space="preserve">5.53995943069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50444746017456</t>
   </si>
   <si>
     <t xml:space="preserve">5.3801531791687</t>
@@ -2480,7 +2480,7 @@
     <t xml:space="preserve">5.34464073181152</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28249406814575</t>
+    <t xml:space="preserve">5.28249311447144</t>
   </si>
   <si>
     <t xml:space="preserve">5.20259046554565</t>
@@ -2495,52 +2495,52 @@
     <t xml:space="preserve">5.24698114395142</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15820026397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13156604766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16707801818848</t>
+    <t xml:space="preserve">5.15819931030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1315655708313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16707849502563</t>
   </si>
   <si>
     <t xml:space="preserve">5.18483448028564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02502775192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90073347091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61663341522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72317123413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85634326934814</t>
+    <t xml:space="preserve">5.02502727508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90073394775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61663293838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72317171096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85634279251099</t>
   </si>
   <si>
     <t xml:space="preserve">4.99839401245117</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00727128982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89185571670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98951530456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90396356582642</t>
+    <t xml:space="preserve">5.0072717666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89185619354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98951482772827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90396404266357</t>
   </si>
   <si>
     <t xml:space="preserve">6.01050138473511</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01937961578369</t>
+    <t xml:space="preserve">6.01938009262085</t>
   </si>
   <si>
     <t xml:space="preserve">5.9927453994751</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">6.10816097259521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35674905776978</t>
+    <t xml:space="preserve">6.35674858093262</t>
   </si>
   <si>
     <t xml:space="preserve">6.18806409835815</t>
@@ -2561,22 +2561,22 @@
     <t xml:space="preserve">6.2413330078125</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28572368621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3212366104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25021123886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30348014831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31235837936401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1170392036438</t>
+    <t xml:space="preserve">6.2857232093811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32123613357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25021171569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30347967147827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31235885620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11703872680664</t>
   </si>
   <si>
     <t xml:space="preserve">6.08152675628662</t>
@@ -2588,25 +2588,25 @@
     <t xml:space="preserve">6.05489206314087</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98386669158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96611022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93947696685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94835376739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92172002792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.912841796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23245525360107</t>
+    <t xml:space="preserve">5.98386716842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96611070632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93947601318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94835424423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92172050476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91284132003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23245477676392</t>
   </si>
   <si>
     <t xml:space="preserve">6.46328639984131</t>
@@ -2615,10 +2615,10 @@
     <t xml:space="preserve">6.33011436462402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27684545516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20582008361816</t>
+    <t xml:space="preserve">6.27684593200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20581960678101</t>
   </si>
   <si>
     <t xml:space="preserve">6.04601383209229</t>
@@ -2633,10 +2633,10 @@
     <t xml:space="preserve">6.21469879150391</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17918586730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26796817779541</t>
+    <t xml:space="preserve">6.17918634414673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26796722412109</t>
   </si>
   <si>
     <t xml:space="preserve">6.48104333877563</t>
@@ -2645,52 +2645,52 @@
     <t xml:space="preserve">6.66748380661011</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01373195648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43988227844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54641962051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59968948364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6352014541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68846893310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52866363525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31558752059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30670881271362</t>
+    <t xml:space="preserve">7.01373147964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43988275527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54641914367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59968900680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63520193099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68846988677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52866315841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31558799743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30670976638794</t>
   </si>
   <si>
     <t xml:space="preserve">7.18241596221924</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29783248901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13802576065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04924440383911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19129467010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21792888641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35109996795654</t>
+    <t xml:space="preserve">7.29783201217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13802528381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04924392700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19129419326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21792840957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3511004447937</t>
   </si>
   <si>
     <t xml:space="preserve">7.48427295684814</t>
@@ -2699,31 +2699,31 @@
     <t xml:space="preserve">7.59081029891968</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58193206787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65295696258545</t>
+    <t xml:space="preserve">7.58193159103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65295791625977</t>
   </si>
   <si>
     <t xml:space="preserve">7.51090717315674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45763778686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17353773117065</t>
+    <t xml:space="preserve">7.45763826370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17353820800781</t>
   </si>
   <si>
     <t xml:space="preserve">7.61744451522827</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67959117889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7683744430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93705797195435</t>
+    <t xml:space="preserve">7.6795916557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76837253570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9370584487915</t>
   </si>
   <si>
     <t xml:space="preserve">8.19452381134033</t>
@@ -2735,16 +2735,16 @@
     <t xml:space="preserve">7.99920463562012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17676830291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20340251922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99032688140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08798694610596</t>
+    <t xml:space="preserve">8.17676734924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20340156555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99032735824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08798503875732</t>
   </si>
   <si>
     <t xml:space="preserve">8.0524730682373</t>
@@ -2771,13 +2771,13 @@
     <t xml:space="preserve">8.38984298706055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23891353607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44311141967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38096523284912</t>
+    <t xml:space="preserve">8.23891448974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44311237335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3809642791748</t>
   </si>
   <si>
     <t xml:space="preserve">8.51413726806641</t>
@@ -2795,25 +2795,25 @@
     <t xml:space="preserve">8.47014427185059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60530662536621</t>
+    <t xml:space="preserve">8.60530757904053</t>
   </si>
   <si>
     <t xml:space="preserve">8.43410110473633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4160795211792</t>
+    <t xml:space="preserve">8.41608047485352</t>
   </si>
   <si>
     <t xml:space="preserve">8.37102603912354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56025218963623</t>
+    <t xml:space="preserve">8.56025123596191</t>
   </si>
   <si>
     <t xml:space="preserve">8.31696033477783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42509078979492</t>
+    <t xml:space="preserve">8.42509174346924</t>
   </si>
   <si>
     <t xml:space="preserve">8.62332725524902</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">8.75849056243896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65937042236328</t>
+    <t xml:space="preserve">8.6593713760376</t>
   </si>
   <si>
     <t xml:space="preserve">8.70442485809326</t>
@@ -2834,10 +2834,10 @@
     <t xml:space="preserve">8.68640327453613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47915458679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50618743896484</t>
+    <t xml:space="preserve">8.47915554046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50618648529053</t>
   </si>
   <si>
     <t xml:space="preserve">8.51519775390625</t>
@@ -2849,25 +2849,25 @@
     <t xml:space="preserve">8.46113395690918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27190685272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10971260070801</t>
+    <t xml:space="preserve">8.27190780639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10971355438232</t>
   </si>
   <si>
     <t xml:space="preserve">8.15476608276367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08267974853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04663753509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05564785003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95653009414673</t>
+    <t xml:space="preserve">8.08268070220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0466365814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05564880371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95652914047241</t>
   </si>
   <si>
     <t xml:space="preserve">8.00158405303955</t>
@@ -2879,25 +2879,25 @@
     <t xml:space="preserve">7.8574104309082</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78532457351685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83938789367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74027061462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99257230758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92048645019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1727876663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29893970489502</t>
+    <t xml:space="preserve">7.78532409667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83938837051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74027109146118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99257135391235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.920485496521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17278671264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2989387512207</t>
   </si>
   <si>
     <t xml:space="preserve">8.16377830505371</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">7.96553993225098</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6051082611084</t>
+    <t xml:space="preserve">7.60510778427124</t>
   </si>
   <si>
     <t xml:space="preserve">8.07366943359375</t>
@@ -2921,7 +2921,7 @@
     <t xml:space="preserve">8.12773418426514</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48816680908203</t>
+    <t xml:space="preserve">8.48816585540771</t>
   </si>
   <si>
     <t xml:space="preserve">8.38904666900635</t>
@@ -2933,13 +2933,13 @@
     <t xml:space="preserve">8.33498191833496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7134370803833</t>
+    <t xml:space="preserve">8.71343612670898</t>
   </si>
   <si>
     <t xml:space="preserve">8.63233852386475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23586368560791</t>
+    <t xml:space="preserve">8.23586463928223</t>
   </si>
   <si>
     <t xml:space="preserve">8.30795001983643</t>
@@ -2969,70 +2969,70 @@
     <t xml:space="preserve">7.92949771881104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98356056213379</t>
+    <t xml:space="preserve">7.98356151580811</t>
   </si>
   <si>
     <t xml:space="preserve">8.01960372924805</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88444375991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56906461715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63214063644409</t>
+    <t xml:space="preserve">7.88444185256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56906509399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63214015960693</t>
   </si>
   <si>
     <t xml:space="preserve">7.57807588577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55104351043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65917301177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67719554901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72224807739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7673020362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71323871612549</t>
+    <t xml:space="preserve">7.55104398727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65917253494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67719459533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72224855422974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76730298995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71323823928833</t>
   </si>
   <si>
     <t xml:space="preserve">7.93850755691528</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22685241699219</t>
+    <t xml:space="preserve">8.22685146331787</t>
   </si>
   <si>
     <t xml:space="preserve">8.19080924987793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20883178710938</t>
+    <t xml:space="preserve">8.20883083343506</t>
   </si>
   <si>
     <t xml:space="preserve">8.38003635406494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18179798126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02861595153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8033447265625</t>
+    <t xml:space="preserve">8.18179893493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02861499786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80334520339966</t>
   </si>
   <si>
     <t xml:space="preserve">7.69521570205688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61411905288696</t>
+    <t xml:space="preserve">7.6141185760498</t>
   </si>
   <si>
     <t xml:space="preserve">7.37983798980713</t>
@@ -3041,10 +3041,10 @@
     <t xml:space="preserve">7.33478450775146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37082767486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46093511581421</t>
+    <t xml:space="preserve">7.37082815170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46093559265137</t>
   </si>
   <si>
     <t xml:space="preserve">7.36181688308716</t>
@@ -3053,19 +3053,19 @@
     <t xml:space="preserve">7.35280609130859</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4429144859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65016222000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46994638442993</t>
+    <t xml:space="preserve">7.44291400909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65016174316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46994590759277</t>
   </si>
   <si>
     <t xml:space="preserve">7.39786005020142</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32577419281006</t>
+    <t xml:space="preserve">7.3257737159729</t>
   </si>
   <si>
     <t xml:space="preserve">7.27170896530151</t>
@@ -3080,19 +3080,19 @@
     <t xml:space="preserve">7.26269865036011</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54203271865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64115142822266</t>
+    <t xml:space="preserve">7.54203224182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6411509513855</t>
   </si>
   <si>
     <t xml:space="preserve">7.62312984466553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53302145004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52401113510132</t>
+    <t xml:space="preserve">7.53302097320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52401065826416</t>
   </si>
   <si>
     <t xml:space="preserve">7.31676292419434</t>
@@ -3104,25 +3104,25 @@
     <t xml:space="preserve">7.45192527770996</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96534204483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92929887771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02841806411743</t>
+    <t xml:space="preserve">6.96534252166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92929935455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02841758728027</t>
   </si>
   <si>
     <t xml:space="preserve">6.89325571060181</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01039600372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12753582000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11852598190308</t>
+    <t xml:space="preserve">7.0103964805603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12753629684448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11852550506592</t>
   </si>
   <si>
     <t xml:space="preserve">6.94732046127319</t>
@@ -3146,34 +3146,34 @@
     <t xml:space="preserve">7.14555740356445</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19962215423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00138473510742</t>
+    <t xml:space="preserve">7.199622631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00138521194458</t>
   </si>
   <si>
     <t xml:space="preserve">7.0734715461731</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80314779281616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74007272720337</t>
+    <t xml:space="preserve">6.80314826965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74007177352905</t>
   </si>
   <si>
     <t xml:space="preserve">6.66798639297485</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36161947250366</t>
+    <t xml:space="preserve">6.3616189956665</t>
   </si>
   <si>
     <t xml:space="preserve">6.59589958190918</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41568422317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3255763053894</t>
+    <t xml:space="preserve">6.41568374633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32557582855225</t>
   </si>
   <si>
     <t xml:space="preserve">6.13634920120239</t>
@@ -3182,7 +3182,7 @@
     <t xml:space="preserve">5.85701465606689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83899307250977</t>
+    <t xml:space="preserve">5.83899354934692</t>
   </si>
   <si>
     <t xml:space="preserve">6.01019811630249</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">6.28052186965942</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09129524230957</t>
+    <t xml:space="preserve">6.09129571914673</t>
   </si>
   <si>
     <t xml:space="preserve">6.14535999298096</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">6.2354679107666</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46974849700928</t>
+    <t xml:space="preserve">6.46974802017212</t>
   </si>
   <si>
     <t xml:space="preserve">6.3886513710022</t>
@@ -3218,13 +3218,13 @@
     <t xml:space="preserve">6.31656503677368</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02822017669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11832809448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12733793258667</t>
+    <t xml:space="preserve">6.02821969985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11832761764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12733840942383</t>
   </si>
   <si>
     <t xml:space="preserve">6.27151107788086</t>
@@ -3233,28 +3233,28 @@
     <t xml:space="preserve">6.26249980926514</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18140268325806</t>
+    <t xml:space="preserve">6.18140316009521</t>
   </si>
   <si>
     <t xml:space="preserve">6.29854297637939</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17239236831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84800338745117</t>
+    <t xml:space="preserve">6.17239284515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84800386428833</t>
   </si>
   <si>
     <t xml:space="preserve">5.86602592468262</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92009019851685</t>
+    <t xml:space="preserve">5.920090675354</t>
   </si>
   <si>
     <t xml:space="preserve">5.89305782318115</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93811178207397</t>
+    <t xml:space="preserve">5.93811225891113</t>
   </si>
   <si>
     <t xml:space="preserve">5.88404703140259</t>
@@ -3269,19 +3269,19 @@
     <t xml:space="preserve">6.06426286697388</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98316526412964</t>
+    <t xml:space="preserve">5.9831657409668</t>
   </si>
   <si>
     <t xml:space="preserve">5.94712257385254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0192084312439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99217653274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96514368057251</t>
+    <t xml:space="preserve">6.01920890808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99217700958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96514415740967</t>
   </si>
   <si>
     <t xml:space="preserve">5.97415494918823</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">6.08228492736816</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07327318191528</t>
+    <t xml:space="preserve">6.07327365875244</t>
   </si>
   <si>
     <t xml:space="preserve">6.03723001480103</t>
@@ -3302,16 +3302,16 @@
     <t xml:space="preserve">6.04001379013062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94737529754639</t>
+    <t xml:space="preserve">5.94737577438354</t>
   </si>
   <si>
     <t xml:space="preserve">5.96590280532837</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1604437828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28087329864502</t>
+    <t xml:space="preserve">6.16044425964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28087377548218</t>
   </si>
   <si>
     <t xml:space="preserve">6.22528982162476</t>
@@ -3335,16 +3335,16 @@
     <t xml:space="preserve">6.00295877456665</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81768226623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83620977401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9288477897644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89179277420044</t>
+    <t xml:space="preserve">5.81768274307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83621025085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92884826660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8917932510376</t>
   </si>
   <si>
     <t xml:space="preserve">6.09559679031372</t>
@@ -3368,7 +3368,7 @@
     <t xml:space="preserve">5.73430776596069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72504377365112</t>
+    <t xml:space="preserve">5.72504425048828</t>
   </si>
   <si>
     <t xml:space="preserve">5.34522676467896</t>
@@ -3383,7 +3383,7 @@
     <t xml:space="preserve">5.75283527374268</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51197576522827</t>
+    <t xml:space="preserve">5.51197528839111</t>
   </si>
   <si>
     <t xml:space="preserve">5.85473728179932</t>
@@ -3392,10 +3392,10 @@
     <t xml:space="preserve">5.55829524993896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71578025817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77136325836182</t>
+    <t xml:space="preserve">5.71578073501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77136278152466</t>
   </si>
   <si>
     <t xml:space="preserve">5.61387777328491</t>
@@ -3419,10 +3419,10 @@
     <t xml:space="preserve">6.04927778244019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86400127410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53976726531982</t>
+    <t xml:space="preserve">5.86400079727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53976774215698</t>
   </si>
   <si>
     <t xml:space="preserve">5.49344825744629</t>
@@ -3431,7 +3431,7 @@
     <t xml:space="preserve">5.47492074966431</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37301874160767</t>
+    <t xml:space="preserve">5.37301921844482</t>
   </si>
   <si>
     <t xml:space="preserve">5.39154624938965</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">5.38228273391724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1321587562561</t>
+    <t xml:space="preserve">5.13215923309326</t>
   </si>
   <si>
     <t xml:space="preserve">5.10436820983887</t>
@@ -3476,16 +3476,16 @@
     <t xml:space="preserve">5.2340612411499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08583974838257</t>
+    <t xml:space="preserve">5.08583927154541</t>
   </si>
   <si>
     <t xml:space="preserve">5.05804824829102</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01172971725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02099323272705</t>
+    <t xml:space="preserve">5.01172924041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02099370956421</t>
   </si>
   <si>
     <t xml:space="preserve">5.1784782409668</t>
@@ -3506,7 +3506,7 @@
     <t xml:space="preserve">4.91909122467041</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97467422485352</t>
+    <t xml:space="preserve">4.97467374801636</t>
   </si>
   <si>
     <t xml:space="preserve">4.96541023254395</t>
@@ -3530,7 +3530,7 @@
     <t xml:space="preserve">5.29890775680542</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46565675735474</t>
+    <t xml:space="preserve">5.46565723419189</t>
   </si>
   <si>
     <t xml:space="preserve">5.56755924224854</t>
@@ -3566,7 +3566,7 @@
     <t xml:space="preserve">5.64166975021362</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88252878189087</t>
+    <t xml:space="preserve">5.88252830505371</t>
   </si>
   <si>
     <t xml:space="preserve">5.99369478225708</t>
@@ -3575,7 +3575,7 @@
     <t xml:space="preserve">5.98443126678467</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91032028198242</t>
+    <t xml:space="preserve">5.91032075881958</t>
   </si>
   <si>
     <t xml:space="preserve">6.44762229919434</t>
@@ -3587,7 +3587,7 @@
     <t xml:space="preserve">6.70700931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79964828491211</t>
+    <t xml:space="preserve">6.79964780807495</t>
   </si>
   <si>
     <t xml:space="preserve">6.82743883132935</t>
@@ -3596,7 +3596,7 @@
     <t xml:space="preserve">6.79038381576538</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89228630065918</t>
+    <t xml:space="preserve">6.89228582382202</t>
   </si>
   <si>
     <t xml:space="preserve">6.96639680862427</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">7.34621286392212</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38326787948608</t>
+    <t xml:space="preserve">7.38326835632324</t>
   </si>
   <si>
     <t xml:space="preserve">7.46664333343506</t>
@@ -3641,10 +3641,10 @@
     <t xml:space="preserve">7.50369882583618</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63339138031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62412738800049</t>
+    <t xml:space="preserve">7.63339185714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62412786483765</t>
   </si>
   <si>
     <t xml:space="preserve">7.57780933380127</t>
@@ -3656,7 +3656,7 @@
     <t xml:space="preserve">7.45737934112549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43885135650635</t>
+    <t xml:space="preserve">7.43885087966919</t>
   </si>
   <si>
     <t xml:space="preserve">7.08682632446289</t>
@@ -3665,7 +3665,7 @@
     <t xml:space="preserve">7.32768535614014</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10535383224487</t>
+    <t xml:space="preserve">7.10535335540771</t>
   </si>
   <si>
     <t xml:space="preserve">7.18872833251953</t>
@@ -3674,10 +3674,10 @@
     <t xml:space="preserve">7.42032432556152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30915784835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29062986373901</t>
+    <t xml:space="preserve">7.30915832519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29063034057617</t>
   </si>
   <si>
     <t xml:space="preserve">7.16093683242798</t>
@@ -3686,7 +3686,7 @@
     <t xml:space="preserve">7.29989433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24431180953979</t>
+    <t xml:space="preserve">7.24431133270264</t>
   </si>
   <si>
     <t xml:space="preserve">7.21651983261108</t>
@@ -3698,13 +3698,13 @@
     <t xml:space="preserve">7.20725584030151</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33694982528687</t>
+    <t xml:space="preserve">7.33694934844971</t>
   </si>
   <si>
     <t xml:space="preserve">7.31842231750488</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26283931732178</t>
+    <t xml:space="preserve">7.26283884048462</t>
   </si>
   <si>
     <t xml:space="preserve">7.12388134002686</t>
@@ -3713,16 +3713,16 @@
     <t xml:space="preserve">7.04977130889893</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98492431640625</t>
+    <t xml:space="preserve">6.98492383956909</t>
   </si>
   <si>
     <t xml:space="preserve">7.07756233215332</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22578430175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19799184799194</t>
+    <t xml:space="preserve">7.22578382492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1979923248291</t>
   </si>
   <si>
     <t xml:space="preserve">7.15167284011841</t>
@@ -5001,6 +5001,9 @@
   </si>
   <si>
     <t xml:space="preserve">19.2199993133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5400009155273</t>
   </si>
 </sst>
 </file>
@@ -71457,10 +71460,10 @@
     </row>
     <row r="2544">
       <c r="A2544" s="1" t="n">
-        <v>46028.6911805556</v>
+        <v>46028.3333333333</v>
       </c>
       <c r="B2544" t="n">
-        <v>106466</v>
+        <v>118570</v>
       </c>
       <c r="C2544" t="n">
         <v>19.5599994659424</v>
@@ -71478,6 +71481,32 @@
         <v>1662</v>
       </c>
       <c r="H2544" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2545">
+      <c r="A2545" s="1" t="n">
+        <v>46029.6912615741</v>
+      </c>
+      <c r="B2545" t="n">
+        <v>151429</v>
+      </c>
+      <c r="C2545" t="n">
+        <v>19.7600002288818</v>
+      </c>
+      <c r="D2545" t="n">
+        <v>19.2800006866455</v>
+      </c>
+      <c r="E2545" t="n">
+        <v>19.4200000762939</v>
+      </c>
+      <c r="F2545" t="n">
+        <v>19.5400009155273</v>
+      </c>
+      <c r="G2545" t="s">
+        <v>1663</v>
+      </c>
+      <c r="H2545" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CEM.MI.xlsx
+++ b/data/CEM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="1666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1667" uniqueCount="1667">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70432090759277</t>
+    <t xml:space="preserve">4.70432138442993</t>
   </si>
   <si>
     <t xml:space="preserve">CEM.MI</t>
@@ -47,34 +47,34 @@
     <t xml:space="preserve">4.68035984039307</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55656242370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48867273330688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32893323898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22110939025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32493925094604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28899908065796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29299211502075</t>
+    <t xml:space="preserve">4.5565619468689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48867321014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32893371582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22110986709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32494068145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28899955749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29299259185791</t>
   </si>
   <si>
     <t xml:space="preserve">4.06137037277222</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93597531318665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97431206703186</t>
+    <t xml:space="preserve">3.9359757900238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97431254386902</t>
   </si>
   <si>
     <t xml:space="preserve">3.67560052871704</t>
@@ -83,154 +83,154 @@
     <t xml:space="preserve">3.83533978462219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94875431060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88006711006165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9168062210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87846922874451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74588632583618</t>
+    <t xml:space="preserve">3.94875407218933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88006615638733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91680574417114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87846851348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74588513374329</t>
   </si>
   <si>
     <t xml:space="preserve">3.93437814712524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87367725372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73789834976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57816004753113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59892559051514</t>
+    <t xml:space="preserve">3.87367677688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73789811134338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57815957069397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59892535209656</t>
   </si>
   <si>
     <t xml:space="preserve">3.6196916103363</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3513298034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15005779266357</t>
+    <t xml:space="preserve">3.35132956504822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15005826950073</t>
   </si>
   <si>
     <t xml:space="preserve">3.25069403648376</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13088941574097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20916152000427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44238114356995</t>
+    <t xml:space="preserve">3.13088965415955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20916199684143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44238066673279</t>
   </si>
   <si>
     <t xml:space="preserve">3.36251139640808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4759259223938</t>
+    <t xml:space="preserve">3.47592687606812</t>
   </si>
   <si>
     <t xml:space="preserve">3.55419850349426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34653759002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39126420021057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36730360984802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2395122051239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29222655296326</t>
+    <t xml:space="preserve">3.34653735160828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39126396179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3673038482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23951268196106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29222631454468</t>
   </si>
   <si>
     <t xml:space="preserve">3.40244626998901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58614587783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63406801223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55579614639282</t>
+    <t xml:space="preserve">3.58614611625671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63406848907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5557963848114</t>
   </si>
   <si>
     <t xml:space="preserve">3.64365196228027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56058764457703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52065348625183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49829030036926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52544474601746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54940581321716</t>
+    <t xml:space="preserve">3.56058859825134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52065324783325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4982898235321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52544569969177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54940605163574</t>
   </si>
   <si>
     <t xml:space="preserve">3.75227499008179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61330223083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75387263298035</t>
+    <t xml:space="preserve">3.61330199241638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75387191772461</t>
   </si>
   <si>
     <t xml:space="preserve">3.83214426040649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67080783843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70754766464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65802836418152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51745772361755</t>
+    <t xml:space="preserve">3.67080855369568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70754837989807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6580286026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51745843887329</t>
   </si>
   <si>
     <t xml:space="preserve">3.57017230987549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50947117805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54301643371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57975649833679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45196557044983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41043329238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37529063224792</t>
+    <t xml:space="preserve">3.50947213172913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54301691055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57975625991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45196533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41043281555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37529015541077</t>
   </si>
   <si>
     <t xml:space="preserve">3.60052299499512</t>
@@ -239,88 +239,88 @@
     <t xml:space="preserve">3.48551034927368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54461407661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5957305431366</t>
+    <t xml:space="preserve">3.54461431503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59573030471802</t>
   </si>
   <si>
     <t xml:space="preserve">3.77943062782288</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74428796768188</t>
+    <t xml:space="preserve">3.74428844451904</t>
   </si>
   <si>
     <t xml:space="preserve">3.85770297050476</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73949599266052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74907994270325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70595073699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69317197799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67719745635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7970027923584</t>
+    <t xml:space="preserve">3.7394962310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74908018112183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70595097541809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69317173957825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67719769477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79700255393982</t>
   </si>
   <si>
     <t xml:space="preserve">3.66601538658142</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70115804672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62608122825623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67400312423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64205551147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53023767471313</t>
+    <t xml:space="preserve">3.70115876197815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62608098983765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67400288581848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64205479621887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53023719787598</t>
   </si>
   <si>
     <t xml:space="preserve">3.45835494995117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4743287563324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53193736076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62187051773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75758814811707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76085948944092</t>
+    <t xml:space="preserve">3.47432851791382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53193712234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62187027931213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7575888633728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7608585357666</t>
   </si>
   <si>
     <t xml:space="preserve">3.875319480896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88349604606628</t>
+    <t xml:space="preserve">3.88349556922913</t>
   </si>
   <si>
     <t xml:space="preserve">3.77721047401428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75431823730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70526361465454</t>
+    <t xml:space="preserve">3.75431847572327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7052640914917</t>
   </si>
   <si>
     <t xml:space="preserve">3.6692898273468</t>
@@ -329,13 +329,13 @@
     <t xml:space="preserve">3.59734344482422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5842616558075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55646419525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38640832901001</t>
+    <t xml:space="preserve">3.58426237106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55646395683289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38640856742859</t>
   </si>
   <si>
     <t xml:space="preserve">3.31119132041931</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">3.29810976982117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19672989845276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1591215133667</t>
+    <t xml:space="preserve">3.19673037528992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15912199020386</t>
   </si>
   <si>
     <t xml:space="preserve">3.00705194473267</t>
@@ -359,13 +359,13 @@
     <t xml:space="preserve">3.03484916687012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22289276123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35207009315491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10679650306702</t>
+    <t xml:space="preserve">3.22289228439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35207033157349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10679626464844</t>
   </si>
   <si>
     <t xml:space="preserve">2.82882022857666</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">2.82064414024353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84026622772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93510484695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04302501678467</t>
+    <t xml:space="preserve">2.84026575088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9351053237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04302525520325</t>
   </si>
   <si>
     <t xml:space="preserve">2.95799708366394</t>
@@ -389,91 +389,91 @@
     <t xml:space="preserve">2.79611659049988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76341366767883</t>
+    <t xml:space="preserve">2.76341390609741</t>
   </si>
   <si>
     <t xml:space="preserve">2.76831936836243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84844207763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87787437438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04139018058777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00051164627075</t>
+    <t xml:space="preserve">2.84844183921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87787413597107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04139041900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00051140785217</t>
   </si>
   <si>
     <t xml:space="preserve">3.21144676208496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13295912742615</t>
+    <t xml:space="preserve">3.13295936584473</t>
   </si>
   <si>
     <t xml:space="preserve">3.07572841644287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97434854507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1084315776825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97598385810852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92856431007385</t>
+    <t xml:space="preserve">2.97434878349304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10843181610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97598433494568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92856454849243</t>
   </si>
   <si>
     <t xml:space="preserve">3.17547297477722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18037867546082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15585064888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18855404853821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09862065315247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12151312828064</t>
+    <t xml:space="preserve">3.18037843704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15585112571716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18855428695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09862041473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12151288986206</t>
   </si>
   <si>
     <t xml:space="preserve">3.02503871917725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11660718917847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23760890960693</t>
+    <t xml:space="preserve">3.11660742759705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23760914802551</t>
   </si>
   <si>
     <t xml:space="preserve">3.28012299537659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32263731956482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.435462474823</t>
+    <t xml:space="preserve">3.32263684272766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43546295166016</t>
   </si>
   <si>
     <t xml:space="preserve">3.40602993965149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46653032302856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43709802627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44854402542114</t>
+    <t xml:space="preserve">3.46653056144714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43709826469421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44854426383972</t>
   </si>
   <si>
     <t xml:space="preserve">3.67910099029541</t>
@@ -485,61 +485,61 @@
     <t xml:space="preserve">3.71834492683411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69545292854309</t>
+    <t xml:space="preserve">3.69545221328735</t>
   </si>
   <si>
     <t xml:space="preserve">3.74450707435608</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85242795944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80827808380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82299447059631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80337309837341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74287247657776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62350535392761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56627535820007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47470664978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51558542251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65947890281677</t>
+    <t xml:space="preserve">3.85242748260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80827856063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82299494743347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80337333679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74287176132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62350606918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56627511978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47470641136169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51558566093445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65947937965393</t>
   </si>
   <si>
     <t xml:space="preserve">3.60551905632019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54501867294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64803314208984</t>
+    <t xml:space="preserve">3.54501819610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64803290367126</t>
   </si>
   <si>
     <t xml:space="preserve">3.64476275444031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38804388046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48288249969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45344996452332</t>
+    <t xml:space="preserve">3.38804340362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48288226127625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45344948768616</t>
   </si>
   <si>
     <t xml:space="preserve">3.43382740020752</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">3.50740933418274</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56464004516602</t>
+    <t xml:space="preserve">3.56464028358459</t>
   </si>
   <si>
     <t xml:space="preserve">3.55482912063599</t>
@@ -557,64 +557,64 @@
     <t xml:space="preserve">3.56300497055054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4845175743103</t>
+    <t xml:space="preserve">3.48451781272888</t>
   </si>
   <si>
     <t xml:space="preserve">3.54338312149048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62514090538025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59080266952515</t>
+    <t xml:space="preserve">3.62514114379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59080290794373</t>
   </si>
   <si>
     <t xml:space="preserve">3.64149236679077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68891215324402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66111493110657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68727684020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53684282302856</t>
+    <t xml:space="preserve">3.68891263008118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66111469268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68727707862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53684234619141</t>
   </si>
   <si>
     <t xml:space="preserve">3.63004636764526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63822197914124</t>
+    <t xml:space="preserve">3.63822221755981</t>
   </si>
   <si>
     <t xml:space="preserve">3.43873310089111</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41747546195984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41911101341248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33571791648865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37169218063354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27521729469299</t>
+    <t xml:space="preserve">3.417475938797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41911125183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33571863174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37169194221497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27521753311157</t>
   </si>
   <si>
     <t xml:space="preserve">3.22125744819641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20981121063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17710781097412</t>
+    <t xml:space="preserve">3.20981097221375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1771080493927</t>
   </si>
   <si>
     <t xml:space="preserve">3.21308183670044</t>
@@ -626,16 +626,16 @@
     <t xml:space="preserve">3.11333703994751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00541687011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01686310768127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95309162139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91875386238098</t>
+    <t xml:space="preserve">3.00541710853577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01686263084412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9530918598175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9187536239624</t>
   </si>
   <si>
     <t xml:space="preserve">2.96453762054443</t>
@@ -644,64 +644,64 @@
     <t xml:space="preserve">2.96780848503113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95636177062988</t>
+    <t xml:space="preserve">2.95636224746704</t>
   </si>
   <si>
     <t xml:space="preserve">3.04793071746826</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17220306396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18691921234131</t>
+    <t xml:space="preserve">3.17220282554626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18691897392273</t>
   </si>
   <si>
     <t xml:space="preserve">3.31936645507812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23433876037598</t>
+    <t xml:space="preserve">3.2343385219574</t>
   </si>
   <si>
     <t xml:space="preserve">3.45835518836975</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48778748512268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4518141746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49923396110535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57281589508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45017910003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61369514465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67746615409851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58916711807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70362854003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48615288734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33244848251343</t>
+    <t xml:space="preserve">3.4877872467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45181441307068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49923419952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57281637191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45017886161804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61369490623474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67746591567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58916759490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70362877845764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48615217208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33244824409485</t>
   </si>
   <si>
     <t xml:space="preserve">3.28666377067566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22943353652954</t>
+    <t xml:space="preserve">3.22943329811096</t>
   </si>
   <si>
     <t xml:space="preserve">3.27031207084656</t>
@@ -710,52 +710,52 @@
     <t xml:space="preserve">3.24741983413696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23106861114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2327036857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26213645935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27685236930847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23597359657288</t>
+    <t xml:space="preserve">3.23106837272644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23270344734192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26213622093201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27685260772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2359733581543</t>
   </si>
   <si>
     <t xml:space="preserve">4.0012264251709</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04701089859009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1287693977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16964769363403</t>
+    <t xml:space="preserve">4.04701042175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12876892089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16964817047119</t>
   </si>
   <si>
     <t xml:space="preserve">4.17782402038574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06336212158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9570779800415</t>
+    <t xml:space="preserve">4.06336259841919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95707774162292</t>
   </si>
   <si>
     <t xml:space="preserve">4.19417524337769</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28410863876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3454270362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47215175628662</t>
+    <t xml:space="preserve">4.28410911560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34542798995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47215127944946</t>
   </si>
   <si>
     <t xml:space="preserve">4.43944883346558</t>
@@ -764,22 +764,22 @@
     <t xml:space="preserve">4.41083288192749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41492176055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37404251098633</t>
+    <t xml:space="preserve">4.41492128372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37404298782349</t>
   </si>
   <si>
     <t xml:space="preserve">4.26775693893433</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39039373397827</t>
+    <t xml:space="preserve">4.39039468765259</t>
   </si>
   <si>
     <t xml:space="preserve">4.3617787361145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37812995910645</t>
+    <t xml:space="preserve">4.3781304359436</t>
   </si>
   <si>
     <t xml:space="preserve">4.38630533218384</t>
@@ -788,64 +788,64 @@
     <t xml:space="preserve">4.56208562850952</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42718410491943</t>
+    <t xml:space="preserve">4.42718458175659</t>
   </si>
   <si>
     <t xml:space="preserve">4.32907629013062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2554931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25140571594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30046033859253</t>
+    <t xml:space="preserve">4.25549364089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25140523910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30046081542969</t>
   </si>
   <si>
     <t xml:space="preserve">4.34951496124268</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24322891235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24731826782227</t>
+    <t xml:space="preserve">4.24323034286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24731874465942</t>
   </si>
   <si>
     <t xml:space="preserve">4.21052646636963</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14512014389038</t>
+    <t xml:space="preserve">4.14512062072754</t>
   </si>
   <si>
     <t xml:space="preserve">4.10424137115479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22279071807861</t>
+    <t xml:space="preserve">4.22279024124146</t>
   </si>
   <si>
     <t xml:space="preserve">4.40674543380737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36586666107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27593278884888</t>
+    <t xml:space="preserve">4.36586618423462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27593231201172</t>
   </si>
   <si>
     <t xml:space="preserve">4.30454778671265</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28002119064331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44762468338013</t>
+    <t xml:space="preserve">4.28002071380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44762420654297</t>
   </si>
   <si>
     <t xml:space="preserve">4.52938222885132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51711797714233</t>
+    <t xml:space="preserve">4.51711893081665</t>
   </si>
   <si>
     <t xml:space="preserve">4.52120685577393</t>
@@ -857,46 +857,46 @@
     <t xml:space="preserve">4.66019487380981</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71333694458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7337760925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81962299346924</t>
+    <t xml:space="preserve">4.71333742141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73377752304077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81962251663208</t>
   </si>
   <si>
     <t xml:space="preserve">4.81144666671753</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65201950073242</t>
+    <t xml:space="preserve">4.65201854705811</t>
   </si>
   <si>
     <t xml:space="preserve">4.34133911132812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33725214004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25958108901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4038348197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44966459274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41633415222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37467002868652</t>
+    <t xml:space="preserve">4.33725118637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25958156585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40383434295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44966411590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41633367538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37467050552368</t>
   </si>
   <si>
     <t xml:space="preserve">4.36633682250977</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30384254455566</t>
+    <t xml:space="preserve">4.30384206771851</t>
   </si>
   <si>
     <t xml:space="preserve">4.27467775344849</t>
@@ -917,31 +917,31 @@
     <t xml:space="preserve">4.33300685882568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37050437927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3455057144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39133501052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29967594146729</t>
+    <t xml:space="preserve">4.37050342559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34550523757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39133548736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29967546463013</t>
   </si>
   <si>
     <t xml:space="preserve">4.4288330078125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39966869354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3955020904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38300323486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46633052825928</t>
+    <t xml:space="preserve">4.39966821670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39550161361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38300275802612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46632957458496</t>
   </si>
   <si>
     <t xml:space="preserve">4.48299551010132</t>
@@ -956,61 +956,61 @@
     <t xml:space="preserve">4.34967184066772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69131326675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58298778533936</t>
+    <t xml:space="preserve">4.69131278991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5829873085022</t>
   </si>
   <si>
     <t xml:space="preserve">4.85380029678345</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99962329864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05795192718506</t>
+    <t xml:space="preserve">4.9996223449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0579514503479</t>
   </si>
   <si>
     <t xml:space="preserve">5.1079478263855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24960422515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28710126876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25376987457275</t>
+    <t xml:space="preserve">5.24960374832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28710079193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25377035140991</t>
   </si>
   <si>
     <t xml:space="preserve">5.41625785827637</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30376625061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29960012435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34542989730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30793333053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22877216339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29126787185669</t>
+    <t xml:space="preserve">5.30376672744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29960060119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34543037414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30793285369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22877168655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29126739501953</t>
   </si>
   <si>
     <t xml:space="preserve">5.29543399810791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16211080551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0162878036499</t>
+    <t xml:space="preserve">5.16210985183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01628828048706</t>
   </si>
   <si>
     <t xml:space="preserve">5.05378532409668</t>
@@ -1022,43 +1022,43 @@
     <t xml:space="preserve">5.20377397537231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07461738586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03295373916626</t>
+    <t xml:space="preserve">5.0746169090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0329532623291</t>
   </si>
   <si>
     <t xml:space="preserve">4.95795917510986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9912896156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96212577819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90796279907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94129323959351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89129686355591</t>
+    <t xml:space="preserve">4.99129009246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9621262550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90796327590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94129419326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89129781723022</t>
   </si>
   <si>
     <t xml:space="preserve">4.9037971496582</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9537935256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94546031951904</t>
+    <t xml:space="preserve">4.95379304885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9454607963562</t>
   </si>
   <si>
     <t xml:space="preserve">4.91629600524902</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02462100982666</t>
+    <t xml:space="preserve">5.02462148666382</t>
   </si>
   <si>
     <t xml:space="preserve">5.04961919784546</t>
@@ -1067,10 +1067,10 @@
     <t xml:space="preserve">5.11628103256226</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17460918426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23293828964233</t>
+    <t xml:space="preserve">5.17461013793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23293924331665</t>
   </si>
   <si>
     <t xml:space="preserve">5.17877578735352</t>
@@ -1079,10 +1079,10 @@
     <t xml:space="preserve">5.1329460144043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33293151855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26626968383789</t>
+    <t xml:space="preserve">5.33293104171753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26626920700073</t>
   </si>
   <si>
     <t xml:space="preserve">5.22460556030273</t>
@@ -1091,25 +1091,25 @@
     <t xml:space="preserve">5.5829119682312</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68707132339478</t>
+    <t xml:space="preserve">5.68707084655762</t>
   </si>
   <si>
     <t xml:space="preserve">6.00371360778809</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80789422988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0745415687561</t>
+    <t xml:space="preserve">5.80789518356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07454204559326</t>
   </si>
   <si>
     <t xml:space="preserve">6.01621294021606</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1662015914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89122247695923</t>
+    <t xml:space="preserve">6.16620206832886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89122200012207</t>
   </si>
   <si>
     <t xml:space="preserve">5.94121789932251</t>
@@ -1118,10 +1118,10 @@
     <t xml:space="preserve">5.96621656417847</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03287792205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99538040161133</t>
+    <t xml:space="preserve">6.03287839889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99538135528564</t>
   </si>
   <si>
     <t xml:space="preserve">5.97038269042969</t>
@@ -1133,19 +1133,19 @@
     <t xml:space="preserve">5.86205768585205</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92871904373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89955425262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90372085571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87455654144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84539222717285</t>
+    <t xml:space="preserve">5.92871999740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89955472946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90372133255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87455701828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84539175033569</t>
   </si>
   <si>
     <t xml:space="preserve">6.00788021087646</t>
@@ -1154,28 +1154,28 @@
     <t xml:space="preserve">5.98288202285767</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03704404830933</t>
+    <t xml:space="preserve">6.03704500198364</t>
   </si>
   <si>
     <t xml:space="preserve">6.0912070274353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02871131896973</t>
+    <t xml:space="preserve">6.02871227264404</t>
   </si>
   <si>
     <t xml:space="preserve">5.99954700469971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04954433441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07870817184448</t>
+    <t xml:space="preserve">6.04954385757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0787091255188</t>
   </si>
   <si>
     <t xml:space="preserve">6.29119205474854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17453479766846</t>
+    <t xml:space="preserve">6.17453384399414</t>
   </si>
   <si>
     <t xml:space="preserve">6.1995325088501</t>
@@ -1184,34 +1184,34 @@
     <t xml:space="preserve">6.08287477493286</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24536275863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21203184127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02454566955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09954023361206</t>
+    <t xml:space="preserve">6.24536228179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21203136444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02454471588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0995397567749</t>
   </si>
   <si>
     <t xml:space="preserve">6.1828670501709</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2078652381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22036457061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14536952972412</t>
+    <t xml:space="preserve">6.20786571502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22036409378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14537000656128</t>
   </si>
   <si>
     <t xml:space="preserve">5.95788431167603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94538450241089</t>
+    <t xml:space="preserve">5.94538545608521</t>
   </si>
   <si>
     <t xml:space="preserve">6.01204681396484</t>
@@ -1223,37 +1223,37 @@
     <t xml:space="preserve">6.11620569229126</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06204223632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04121112823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14953660964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09537267684937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35785341262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22453022003174</t>
+    <t xml:space="preserve">6.06204271316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04121065139771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1495361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09537410736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35785436630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2245306968689</t>
   </si>
   <si>
     <t xml:space="preserve">6.28285932540894</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58283805847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61616802215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57450437545776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50784254074097</t>
+    <t xml:space="preserve">6.58283662796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6161675453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57450389862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50784301757812</t>
   </si>
   <si>
     <t xml:space="preserve">6.49951028823853</t>
@@ -1265,55 +1265,55 @@
     <t xml:space="preserve">6.7411584854126</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59116888046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6245002746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63283348083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70782804489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52450704574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51617574691772</t>
+    <t xml:space="preserve">6.5911693572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62449979782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63283252716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70782709121704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52450799942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51617527008057</t>
   </si>
   <si>
     <t xml:space="preserve">6.6661639213562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54950618743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44951391220093</t>
+    <t xml:space="preserve">6.54950666427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44951343536377</t>
   </si>
   <si>
     <t xml:space="preserve">6.29952478408813</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23286294937134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90788745880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93288564682007</t>
+    <t xml:space="preserve">6.2328634262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90788841247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93288612365723</t>
   </si>
   <si>
     <t xml:space="preserve">6.53284072875977</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26619338989258</t>
+    <t xml:space="preserve">6.26619386672974</t>
   </si>
   <si>
     <t xml:space="preserve">6.36618614196777</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33285474777222</t>
+    <t xml:space="preserve">6.33285522460938</t>
   </si>
   <si>
     <t xml:space="preserve">6.1412034034729</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">6.1578688621521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0662088394165</t>
+    <t xml:space="preserve">6.06620931625366</t>
   </si>
   <si>
     <t xml:space="preserve">5.94955062866211</t>
@@ -1331,10 +1331,10 @@
     <t xml:space="preserve">6.1328706741333</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05787706375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88288927078247</t>
+    <t xml:space="preserve">6.05787658691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88288974761963</t>
   </si>
   <si>
     <t xml:space="preserve">5.84955883026123</t>
@@ -1343,91 +1343,91 @@
     <t xml:space="preserve">5.81622791290283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72456884384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75789880752563</t>
+    <t xml:space="preserve">5.72456836700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75789928436279</t>
   </si>
   <si>
     <t xml:space="preserve">5.76623201370239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68290519714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82456016540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86622381210327</t>
+    <t xml:space="preserve">5.6829047203064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82456111907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86622428894043</t>
   </si>
   <si>
     <t xml:space="preserve">5.77456426620483</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78289699554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79122972488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63290882110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6498236656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68365478515625</t>
+    <t xml:space="preserve">5.78289747238159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79122924804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6329083442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64982414245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68365526199341</t>
   </si>
   <si>
     <t xml:space="preserve">5.66673946380615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70057058334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48066806793213</t>
+    <t xml:space="preserve">5.70057153701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48066711425781</t>
   </si>
   <si>
     <t xml:space="preserve">5.45529413223267</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54833030700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53987312316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74285984039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58216190338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6582818031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70902919769287</t>
+    <t xml:space="preserve">5.54833078384399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53987216949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74286031723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58216094970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65828227996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70902872085571</t>
   </si>
   <si>
     <t xml:space="preserve">5.77669143676758</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91201639175415</t>
+    <t xml:space="preserve">5.91201686859131</t>
   </si>
   <si>
     <t xml:space="preserve">5.9035587310791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89510011672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75131750106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78514862060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71748638153076</t>
+    <t xml:space="preserve">5.89510107040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75131797790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78514909744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71748685836792</t>
   </si>
   <si>
     <t xml:space="preserve">5.81052303314209</t>
@@ -1436,49 +1436,49 @@
     <t xml:space="preserve">5.56524610519409</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50604152679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69211292266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72594404220581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73440265655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60753583908081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51449966430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6751971244812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01351070404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99659490585327</t>
+    <t xml:space="preserve">5.50604104995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69211339950562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72594451904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73440217971802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60753536224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51449918746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67519807815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01351022720337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99659538269043</t>
   </si>
   <si>
     <t xml:space="preserve">5.81898021697998</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75977563858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80206537246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79360628128052</t>
+    <t xml:space="preserve">5.75977611541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80206489562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79360723495483</t>
   </si>
   <si>
     <t xml:space="preserve">5.88664293289185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8781852722168</t>
+    <t xml:space="preserve">5.87818479537964</t>
   </si>
   <si>
     <t xml:space="preserve">5.92893218994141</t>
@@ -1493,124 +1493,124 @@
     <t xml:space="preserve">5.82743787765503</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83589601516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42992115020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38763189315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33688497543335</t>
+    <t xml:space="preserve">5.83589649200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42992067337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3876314163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33688449859619</t>
   </si>
   <si>
     <t xml:space="preserve">5.26076412200928</t>
   </si>
   <si>
-    <t xml:space="preserve">5.303053855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43837928771973</t>
+    <t xml:space="preserve">5.30305337905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43837833404541</t>
   </si>
   <si>
     <t xml:space="preserve">5.46375274658203</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44683647155762</t>
+    <t xml:space="preserve">5.44683742523193</t>
   </si>
   <si>
     <t xml:space="preserve">5.35380029678345</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37071657180786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22693347930908</t>
+    <t xml:space="preserve">5.3707160949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22693300247192</t>
   </si>
   <si>
     <t xml:space="preserve">5.14235544204712</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11698150634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24384880065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13389730453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2692232131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25230646133423</t>
+    <t xml:space="preserve">5.11698198318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24384927749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13389682769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26922225952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25230693817139</t>
   </si>
   <si>
     <t xml:space="preserve">5.21001720428467</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23539161682129</t>
+    <t xml:space="preserve">5.23539113998413</t>
   </si>
   <si>
     <t xml:space="preserve">5.28613758087158</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31996965408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29459619522095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48912572860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3284273147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16772842407227</t>
+    <t xml:space="preserve">5.31996917724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29459667205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48912525177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32842683792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16772890090942</t>
   </si>
   <si>
     <t xml:space="preserve">5.09160804748535</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17618656158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10852384567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9139928817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60105466842651</t>
+    <t xml:space="preserve">5.17618560791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10852336883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91399383544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60105419158936</t>
   </si>
   <si>
     <t xml:space="preserve">4.49956083297729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56722354888916</t>
+    <t xml:space="preserve">4.567223072052</t>
   </si>
   <si>
     <t xml:space="preserve">4.3811502456665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5418496131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52493381500244</t>
+    <t xml:space="preserve">4.54185009002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5249342918396</t>
   </si>
   <si>
     <t xml:space="preserve">4.61797046661377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46572971343994</t>
+    <t xml:space="preserve">4.46572923660278</t>
   </si>
   <si>
     <t xml:space="preserve">4.27119970321655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14433193206787</t>
+    <t xml:space="preserve">4.14433240890503</t>
   </si>
   <si>
     <t xml:space="preserve">4.22045230865479</t>
@@ -1622,16 +1622,16 @@
     <t xml:space="preserve">4.20353698730469</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15701913833618</t>
+    <t xml:space="preserve">4.15701866149902</t>
   </si>
   <si>
     <t xml:space="preserve">4.39806699752808</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53339242935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59259653091431</t>
+    <t xml:space="preserve">4.53339147567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59259700775146</t>
   </si>
   <si>
     <t xml:space="preserve">4.60951232910156</t>
@@ -1640,10 +1640,10 @@
     <t xml:space="preserve">4.63488626480103</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41498184204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49110317230225</t>
+    <t xml:space="preserve">4.41498231887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49110269546509</t>
   </si>
   <si>
     <t xml:space="preserve">4.42343997955322</t>
@@ -1652,16 +1652,16 @@
     <t xml:space="preserve">4.43189764022827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2965726852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33886194229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19507884979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0470666885376</t>
+    <t xml:space="preserve">4.29657316207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33886241912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19507932662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04706716537476</t>
   </si>
   <si>
     <t xml:space="preserve">4.08512687683105</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">4.10627174377441</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15278959274292</t>
+    <t xml:space="preserve">4.15279006958008</t>
   </si>
   <si>
     <t xml:space="preserve">4.23736810684204</t>
@@ -1679,61 +1679,61 @@
     <t xml:space="preserve">4.21622371673584</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16124773025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10204362869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03860855102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30503082275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2542839050293</t>
+    <t xml:space="preserve">4.16124820709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10204267501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03860902786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30503034591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25428342819214</t>
   </si>
   <si>
     <t xml:space="preserve">4.14010286331177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0512957572937</t>
+    <t xml:space="preserve">4.05129623413086</t>
   </si>
   <si>
     <t xml:space="preserve">4.14856100082397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08935594558716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03438091278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94557309150696</t>
+    <t xml:space="preserve">4.08935642242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03437995910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9455738067627</t>
   </si>
   <si>
     <t xml:space="preserve">4.35577774047852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31348848342896</t>
+    <t xml:space="preserve">4.31348896026611</t>
   </si>
   <si>
     <t xml:space="preserve">4.48264503479004</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65180158615112</t>
+    <t xml:space="preserve">4.65180110931396</t>
   </si>
   <si>
     <t xml:space="preserve">4.7955846786499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7871265411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82095766067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86324739456177</t>
+    <t xml:space="preserve">4.78712606430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82095813751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86324644088745</t>
   </si>
   <si>
     <t xml:space="preserve">4.90553665161133</t>
@@ -1742,19 +1742,19 @@
     <t xml:space="preserve">4.88862037658691</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95628261566162</t>
+    <t xml:space="preserve">4.95628309249878</t>
   </si>
   <si>
     <t xml:space="preserve">5.00703001022339</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01548719406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03240346908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05777645111084</t>
+    <t xml:space="preserve">5.01548767089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03240299224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.057776927948</t>
   </si>
   <si>
     <t xml:space="preserve">4.99011421203613</t>
@@ -1763,10 +1763,10 @@
     <t xml:space="preserve">4.97319889068604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20156002044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12543964385986</t>
+    <t xml:space="preserve">5.20155954360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12543916702271</t>
   </si>
   <si>
     <t xml:space="preserve">5.15927028656006</t>
@@ -1775,28 +1775,28 @@
     <t xml:space="preserve">5.21847581863403</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34534311294556</t>
+    <t xml:space="preserve">5.3453426361084</t>
   </si>
   <si>
     <t xml:space="preserve">5.27767992019653</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40454769134521</t>
+    <t xml:space="preserve">5.40454721450806</t>
   </si>
   <si>
     <t xml:space="preserve">5.39609003067017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47221040725708</t>
+    <t xml:space="preserve">5.47220945358276</t>
   </si>
   <si>
     <t xml:space="preserve">5.49758338928223</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42146301269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41300582885742</t>
+    <t xml:space="preserve">5.42146253585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41300535202026</t>
   </si>
   <si>
     <t xml:space="preserve">4.98165655136108</t>
@@ -1805,7 +1805,7 @@
     <t xml:space="preserve">5.11462450027466</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13193273544312</t>
+    <t xml:space="preserve">5.13193368911743</t>
   </si>
   <si>
     <t xml:space="preserve">5.01942920684814</t>
@@ -1817,34 +1817,34 @@
     <t xml:space="preserve">5.06269979476929</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08866310119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0973162651062</t>
+    <t xml:space="preserve">5.08866214752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09731674194336</t>
   </si>
   <si>
     <t xml:space="preserve">5.14058780670166</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20116662979126</t>
+    <t xml:space="preserve">5.20116758346558</t>
   </si>
   <si>
     <t xml:space="preserve">5.17520427703857</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22712993621826</t>
+    <t xml:space="preserve">5.2271294593811</t>
   </si>
   <si>
     <t xml:space="preserve">5.26174640655518</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23578310012817</t>
+    <t xml:space="preserve">5.23578357696533</t>
   </si>
   <si>
     <t xml:space="preserve">5.25309181213379</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33963394165039</t>
+    <t xml:space="preserve">5.33963441848755</t>
   </si>
   <si>
     <t xml:space="preserve">5.46079254150391</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">5.54733419418335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42617654800415</t>
+    <t xml:space="preserve">5.42617511749268</t>
   </si>
   <si>
     <t xml:space="preserve">5.330979347229</t>
@@ -1862,13 +1862,13 @@
     <t xml:space="preserve">5.40886735916138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57329654693604</t>
+    <t xml:space="preserve">5.57329750061035</t>
   </si>
   <si>
     <t xml:space="preserve">5.52137231826782</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47810077667236</t>
+    <t xml:space="preserve">5.47810125350952</t>
   </si>
   <si>
     <t xml:space="preserve">5.64253091812134</t>
@@ -1877,13 +1877,13 @@
     <t xml:space="preserve">5.7636890411377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74638080596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72907257080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65118503570557</t>
+    <t xml:space="preserve">5.74638032913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72907209396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65118455886841</t>
   </si>
   <si>
     <t xml:space="preserve">5.7031102180481</t>
@@ -1892,25 +1892,25 @@
     <t xml:space="preserve">5.66849327087402</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59925985336304</t>
+    <t xml:space="preserve">5.59925889968872</t>
   </si>
   <si>
     <t xml:space="preserve">5.49540901184082</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45213842391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56464338302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73772716522217</t>
+    <t xml:space="preserve">5.45213890075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56464242935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73772668838501</t>
   </si>
   <si>
     <t xml:space="preserve">5.51271772384644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24443769454956</t>
+    <t xml:space="preserve">5.2444372177124</t>
   </si>
   <si>
     <t xml:space="preserve">5.1838583946228</t>
@@ -1928,16 +1928,16 @@
     <t xml:space="preserve">5.2704005241394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08000755310059</t>
+    <t xml:space="preserve">5.0800085067749</t>
   </si>
   <si>
     <t xml:space="preserve">5.14924192428589</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16654968261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15789556503296</t>
+    <t xml:space="preserve">5.16655015945435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15789604187012</t>
   </si>
   <si>
     <t xml:space="preserve">5.29636287689209</t>
@@ -1946,10 +1946,10 @@
     <t xml:space="preserve">5.53868007659912</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44348430633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48675584793091</t>
+    <t xml:space="preserve">5.44348382949829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48675537109375</t>
   </si>
   <si>
     <t xml:space="preserve">5.40021324157715</t>
@@ -1964,10 +1964,10 @@
     <t xml:space="preserve">5.38290500640869</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02808237075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04539155960083</t>
+    <t xml:space="preserve">5.02808284759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04539203643799</t>
   </si>
   <si>
     <t xml:space="preserve">5.16222286224365</t>
@@ -1979,37 +1979,37 @@
     <t xml:space="preserve">5.10597085952759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15270328521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20895528793335</t>
+    <t xml:space="preserve">5.15270376205444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20895576477051</t>
   </si>
   <si>
     <t xml:space="preserve">5.27905416488647</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34569215774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32665300369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27991962432861</t>
+    <t xml:space="preserve">5.3456916809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32665252685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27991914749146</t>
   </si>
   <si>
     <t xml:space="preserve">5.30588293075562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26780462265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34742307662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21934127807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34309482574463</t>
+    <t xml:space="preserve">5.26780366897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34742212295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21934080123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34309577941895</t>
   </si>
   <si>
     <t xml:space="preserve">5.48502445220947</t>
@@ -2018,10 +2018,10 @@
     <t xml:space="preserve">5.4391565322876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3179988861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51791000366211</t>
+    <t xml:space="preserve">5.31799840927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51791048049927</t>
   </si>
   <si>
     <t xml:space="preserve">5.61656761169434</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">5.51617956161499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46252298355103</t>
+    <t xml:space="preserve">5.46252346038818</t>
   </si>
   <si>
     <t xml:space="preserve">5.42271375656128</t>
@@ -2039,7 +2039,7 @@
     <t xml:space="preserve">5.46771574020386</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44434976577759</t>
+    <t xml:space="preserve">5.44434928894043</t>
   </si>
   <si>
     <t xml:space="preserve">5.46944665908813</t>
@@ -2048,13 +2048,13 @@
     <t xml:space="preserve">5.78099727630615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02331447601318</t>
+    <t xml:space="preserve">6.02331495285034</t>
   </si>
   <si>
     <t xml:space="preserve">6.0406231880188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04927682876587</t>
+    <t xml:space="preserve">6.04927730560303</t>
   </si>
   <si>
     <t xml:space="preserve">5.94456195831299</t>
@@ -2063,28 +2063,28 @@
     <t xml:space="preserve">5.76974725723267</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78272914886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75416898727417</t>
+    <t xml:space="preserve">5.78272819519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75416994094849</t>
   </si>
   <si>
     <t xml:space="preserve">5.74118804931641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73945760726929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81042194366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90561819076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93331146240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94110012054443</t>
+    <t xml:space="preserve">5.73945713043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81042242050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90561771392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93331098556519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94109964370728</t>
   </si>
   <si>
     <t xml:space="preserve">5.91081047058105</t>
@@ -2093,25 +2093,25 @@
     <t xml:space="preserve">5.92638778686523</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85369253158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85628938674927</t>
+    <t xml:space="preserve">5.85369300842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85628890991211</t>
   </si>
   <si>
     <t xml:space="preserve">5.68060874938965</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73253440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81907606124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90648365020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7057056427002</t>
+    <t xml:space="preserve">5.73253393173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81907558441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90648317337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70570611953735</t>
   </si>
   <si>
     <t xml:space="preserve">5.57502746582031</t>
@@ -2120,40 +2120,40 @@
     <t xml:space="preserve">5.75590038299561</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81561374664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76022720336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73512983322144</t>
+    <t xml:space="preserve">5.81561422348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7602276802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73513031005859</t>
   </si>
   <si>
     <t xml:space="preserve">5.72041845321655</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69791793823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69272470474243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62868356704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.759361743927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65810775756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57243204116821</t>
+    <t xml:space="preserve">5.69791746139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69272518157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62868404388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75936222076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65810823440552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57243156433105</t>
   </si>
   <si>
     <t xml:space="preserve">5.62522220611572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67282009124756</t>
+    <t xml:space="preserve">5.67282056808472</t>
   </si>
   <si>
     <t xml:space="preserve">5.58195066452026</t>
@@ -2162,16 +2162,16 @@
     <t xml:space="preserve">5.58454751968384</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6451268196106</t>
+    <t xml:space="preserve">5.64512634277344</t>
   </si>
   <si>
     <t xml:space="preserve">5.72561073303223</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61483764648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60704898834229</t>
+    <t xml:space="preserve">5.61483669281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60704851150513</t>
   </si>
   <si>
     <t xml:space="preserve">5.65291595458984</t>
@@ -2183,34 +2183,34 @@
     <t xml:space="preserve">5.75503492355347</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84071111679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00600624084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92811822891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87619352340698</t>
+    <t xml:space="preserve">5.84071159362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00600671768188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92811870574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87619400024414</t>
   </si>
   <si>
     <t xml:space="preserve">5.71436023712158</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42184782028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36213445663452</t>
+    <t xml:space="preserve">5.42184829711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36213493347168</t>
   </si>
   <si>
     <t xml:space="preserve">5.19510889053345</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04019927978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1544337272644</t>
+    <t xml:space="preserve">5.040198802948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15443468093872</t>
   </si>
   <si>
     <t xml:space="preserve">5.18039703369141</t>
@@ -2225,55 +2225,55 @@
     <t xml:space="preserve">4.30113124847412</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30718898773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94501113891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11073970794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98092651367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77452373504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89438462257385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17564487457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82385206222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9748682975769</t>
+    <t xml:space="preserve">4.30718946456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94501137733459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11073875427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9809262752533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77452397346497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89438438415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17564582824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82385301589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97486877441406</t>
   </si>
   <si>
     <t xml:space="preserve">4.07006454467773</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27387094497681</t>
+    <t xml:space="preserve">4.27387046813965</t>
   </si>
   <si>
     <t xml:space="preserve">4.11766242980957</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05665111541748</t>
+    <t xml:space="preserve">4.05665016174316</t>
   </si>
   <si>
     <t xml:space="preserve">4.25699472427368</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30978536605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37036561965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17131900787354</t>
+    <t xml:space="preserve">4.30978584289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37036514282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17131853103638</t>
   </si>
   <si>
     <t xml:space="preserve">4.32709407806396</t>
@@ -2282,7 +2282,7 @@
     <t xml:space="preserve">4.45690679550171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61268186569214</t>
+    <t xml:space="preserve">4.6126823425293</t>
   </si>
   <si>
     <t xml:space="preserve">4.48286914825439</t>
@@ -2291,10 +2291,10 @@
     <t xml:space="preserve">4.62999057769775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56941175460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57806491851807</t>
+    <t xml:space="preserve">4.569411277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57806539535522</t>
   </si>
   <si>
     <t xml:space="preserve">4.5261402130127</t>
@@ -2309,10 +2309,10 @@
     <t xml:space="preserve">4.76845788955688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79442024230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94154119491577</t>
+    <t xml:space="preserve">4.79442071914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94154071807861</t>
   </si>
   <si>
     <t xml:space="preserve">4.91557884216309</t>
@@ -2321,10 +2321,10 @@
     <t xml:space="preserve">4.83769130706787</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58671998977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55210304260254</t>
+    <t xml:space="preserve">4.58671951293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5521035194397</t>
   </si>
   <si>
     <t xml:space="preserve">4.62133646011353</t>
@@ -2336,28 +2336,28 @@
     <t xml:space="preserve">4.80307483673096</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90961170196533</t>
+    <t xml:space="preserve">4.90961217880249</t>
   </si>
   <si>
     <t xml:space="preserve">4.8030743598938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73204851150513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8829779624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91848993301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10493087768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22034692764282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19371223449707</t>
+    <t xml:space="preserve">4.73204898834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88297748565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91849040985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10493040084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22034645080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19371271133423</t>
   </si>
   <si>
     <t xml:space="preserve">5.39790964126587</t>
@@ -2372,25 +2372,25 @@
     <t xml:space="preserve">5.52220344543457</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49556875228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60210752487183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72640085220337</t>
+    <t xml:space="preserve">5.49556970596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60210657119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72640037536621</t>
   </si>
   <si>
     <t xml:space="preserve">5.81518268585205</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63761949539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30912780761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27361583709717</t>
+    <t xml:space="preserve">5.63761901855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30912828445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27361536026001</t>
   </si>
   <si>
     <t xml:space="preserve">5.23810291290283</t>
@@ -2402,64 +2402,64 @@
     <t xml:space="preserve">5.73527908325195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61098480224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65537595748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68200969696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61986303329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64649724960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71752262115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58435106277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56659460067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53108215332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46005725860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35351896286011</t>
+    <t xml:space="preserve">5.61098527908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65537548065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68201017379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61986351013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64649772644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71752309799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5843505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56659412384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53108167648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4600567817688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35351943969727</t>
   </si>
   <si>
     <t xml:space="preserve">5.42454433441162</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4156665802002</t>
+    <t xml:space="preserve">5.41566610336304</t>
   </si>
   <si>
     <t xml:space="preserve">5.31800651550293</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38903188705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29137182235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21146869659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36239719390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26473760604858</t>
+    <t xml:space="preserve">5.38903141021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29137229919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2114691734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36239671707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25585985183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26473712921143</t>
   </si>
   <si>
     <t xml:space="preserve">5.37127542495728</t>
@@ -2468,22 +2468,22 @@
     <t xml:space="preserve">5.48669099807739</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59322881698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53995943069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50444746017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38015365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34464120864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28249359130859</t>
+    <t xml:space="preserve">5.59322929382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5399603843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5044469833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3801531791687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34464025497437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28249406814575</t>
   </si>
   <si>
     <t xml:space="preserve">5.20259046554565</t>
@@ -2492,10 +2492,10 @@
     <t xml:space="preserve">5.32688474655151</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3357629776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24698162078857</t>
+    <t xml:space="preserve">5.33576345443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24698114395142</t>
   </si>
   <si>
     <t xml:space="preserve">5.15819978713989</t>
@@ -2504,7 +2504,7 @@
     <t xml:space="preserve">5.13156604766846</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16707801818848</t>
+    <t xml:space="preserve">5.16707849502563</t>
   </si>
   <si>
     <t xml:space="preserve">5.18483448028564</t>
@@ -2513,25 +2513,25 @@
     <t xml:space="preserve">5.02502775192261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90073347091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61663293838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7231707572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85634279251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99839353561401</t>
+    <t xml:space="preserve">4.90073394775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61663246154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72317123413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85634231567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99839305877686</t>
   </si>
   <si>
     <t xml:space="preserve">5.00727128982544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89185571670532</t>
+    <t xml:space="preserve">4.89185619354248</t>
   </si>
   <si>
     <t xml:space="preserve">4.98951530456543</t>
@@ -2549,19 +2549,19 @@
     <t xml:space="preserve">5.9927453994751</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09928321838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10816049575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35674858093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18806409835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24133348464966</t>
+    <t xml:space="preserve">6.09928274154663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10816097259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35674905776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.188063621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">6.28572368621826</t>
@@ -2582,55 +2582,55 @@
     <t xml:space="preserve">6.11703872680664</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08152627944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06377029418945</t>
+    <t xml:space="preserve">6.08152675628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06377077102661</t>
   </si>
   <si>
     <t xml:space="preserve">6.05489206314087</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98386669158936</t>
+    <t xml:space="preserve">5.98386716842651</t>
   </si>
   <si>
     <t xml:space="preserve">5.96611022949219</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93947649002075</t>
+    <t xml:space="preserve">5.93947696685791</t>
   </si>
   <si>
     <t xml:space="preserve">5.94835424423218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92172050476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.912841796875</t>
+    <t xml:space="preserve">5.92172002792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91284132003784</t>
   </si>
   <si>
     <t xml:space="preserve">6.23245525360107</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46328639984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33011484146118</t>
+    <t xml:space="preserve">6.46328687667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33011436462402</t>
   </si>
   <si>
     <t xml:space="preserve">6.27684593200684</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20582008361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04601430892944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37450551986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12591743469238</t>
+    <t xml:space="preserve">6.20582056045532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04601335525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37450504302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12591695785522</t>
   </si>
   <si>
     <t xml:space="preserve">6.21469879150391</t>
@@ -2642,19 +2642,19 @@
     <t xml:space="preserve">6.26796722412109</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48104286193848</t>
+    <t xml:space="preserve">6.48104333877563</t>
   </si>
   <si>
     <t xml:space="preserve">6.66748428344727</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01373195648193</t>
+    <t xml:space="preserve">7.01373147964478</t>
   </si>
   <si>
     <t xml:space="preserve">7.43988180160522</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54641962051392</t>
+    <t xml:space="preserve">7.54642009735107</t>
   </si>
   <si>
     <t xml:space="preserve">7.59968900680542</t>
@@ -2663,16 +2663,16 @@
     <t xml:space="preserve">7.6352014541626</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68846988677979</t>
+    <t xml:space="preserve">7.68846940994263</t>
   </si>
   <si>
     <t xml:space="preserve">7.52866315841675</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31558752059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30670976638794</t>
+    <t xml:space="preserve">7.31558847427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30670881271362</t>
   </si>
   <si>
     <t xml:space="preserve">7.18241596221924</t>
@@ -2681,52 +2681,52 @@
     <t xml:space="preserve">7.29783201217651</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13802480697632</t>
+    <t xml:space="preserve">7.13802528381348</t>
   </si>
   <si>
     <t xml:space="preserve">7.04924440383911</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19129467010498</t>
+    <t xml:space="preserve">7.19129419326782</t>
   </si>
   <si>
     <t xml:space="preserve">7.21792888641357</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35109996795654</t>
+    <t xml:space="preserve">7.3511004447937</t>
   </si>
   <si>
     <t xml:space="preserve">7.48427295684814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59081077575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58193206787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65295791625977</t>
+    <t xml:space="preserve">7.59081029891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58193159103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65295743942261</t>
   </si>
   <si>
     <t xml:space="preserve">7.51090717315674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45763778686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17353773117065</t>
+    <t xml:space="preserve">7.45763826370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17353820800781</t>
   </si>
   <si>
     <t xml:space="preserve">7.61744451522827</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67959213256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7683744430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9370584487915</t>
+    <t xml:space="preserve">7.67959070205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76837348937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93705749511719</t>
   </si>
   <si>
     <t xml:space="preserve">8.19452381134033</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">8.20340156555176</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99032640457153</t>
+    <t xml:space="preserve">7.99032735824585</t>
   </si>
   <si>
     <t xml:space="preserve">8.08798599243164</t>
@@ -2753,16 +2753,16 @@
     <t xml:space="preserve">8.05247402191162</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0435962677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00808334350586</t>
+    <t xml:space="preserve">8.04359722137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00808429718018</t>
   </si>
   <si>
     <t xml:space="preserve">8.07910919189453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14125633239746</t>
+    <t xml:space="preserve">8.14125537872314</t>
   </si>
   <si>
     <t xml:space="preserve">8.07022953033447</t>
@@ -2795,16 +2795,16 @@
     <t xml:space="preserve">8.42535591125488</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47014427185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60530662536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43410110473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4160795211792</t>
+    <t xml:space="preserve">8.47014331817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60530567169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43410015106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41608047485352</t>
   </si>
   <si>
     <t xml:space="preserve">8.37102603912354</t>
@@ -2813,7 +2813,7 @@
     <t xml:space="preserve">8.56025218963623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31696033477783</t>
+    <t xml:space="preserve">8.31696128845215</t>
   </si>
   <si>
     <t xml:space="preserve">8.42509078979492</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">8.62332725524902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75849056243896</t>
+    <t xml:space="preserve">8.75848960876465</t>
   </si>
   <si>
     <t xml:space="preserve">8.65937042236328</t>
@@ -2837,16 +2837,16 @@
     <t xml:space="preserve">8.68640327453613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47915458679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50618743896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51519775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5332202911377</t>
+    <t xml:space="preserve">8.47915554046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50618648529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51519870758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53321933746338</t>
   </si>
   <si>
     <t xml:space="preserve">8.46113395690918</t>
@@ -2864,13 +2864,13 @@
     <t xml:space="preserve">8.08267974853516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04663753509521</t>
+    <t xml:space="preserve">8.0466365814209</t>
   </si>
   <si>
     <t xml:space="preserve">8.05564785003662</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95653009414673</t>
+    <t xml:space="preserve">7.95652914047241</t>
   </si>
   <si>
     <t xml:space="preserve">8.00158405303955</t>
@@ -2879,22 +2879,22 @@
     <t xml:space="preserve">7.74928140640259</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8574104309082</t>
+    <t xml:space="preserve">7.85741090774536</t>
   </si>
   <si>
     <t xml:space="preserve">7.78532457351685</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83938789367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74027061462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99257230758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92048645019531</t>
+    <t xml:space="preserve">7.83938837051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74027013778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99257183074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92048597335815</t>
   </si>
   <si>
     <t xml:space="preserve">8.1727876663208</t>
@@ -2906,40 +2906,40 @@
     <t xml:space="preserve">8.16377830505371</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21784210205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96553993225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6051082611084</t>
+    <t xml:space="preserve">8.21784114837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96554040908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60510778427124</t>
   </si>
   <si>
     <t xml:space="preserve">8.07366943359375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24487400054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12773418426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48816680908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38904666900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35300445556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33498191833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7134370803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63233852386475</t>
+    <t xml:space="preserve">8.244873046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12773513793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48816585540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38904762268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35300540924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33498287200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71343517303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63233757019043</t>
   </si>
   <si>
     <t xml:space="preserve">8.23586368560791</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">8.64134979248047</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77651023864746</t>
+    <t xml:space="preserve">8.77651119232178</t>
   </si>
   <si>
     <t xml:space="preserve">8.55124187469482</t>
@@ -2963,28 +2963,28 @@
     <t xml:space="preserve">8.25388526916504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19982051849365</t>
+    <t xml:space="preserve">8.19982147216797</t>
   </si>
   <si>
     <t xml:space="preserve">8.03762626647949</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92949771881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98356056213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01960372924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88444375991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56906461715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63214063644409</t>
+    <t xml:space="preserve">7.92949628829956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98356151580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01960468292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8844428062439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56906509399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63214111328125</t>
   </si>
   <si>
     <t xml:space="preserve">7.57807588577271</t>
@@ -2996,28 +2996,28 @@
     <t xml:space="preserve">7.65917301177979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67719554901123</t>
+    <t xml:space="preserve">7.67719507217407</t>
   </si>
   <si>
     <t xml:space="preserve">7.72224807739258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7673020362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71323871612549</t>
+    <t xml:space="preserve">7.76730251312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71323823928833</t>
   </si>
   <si>
     <t xml:space="preserve">7.93850755691528</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22685241699219</t>
+    <t xml:space="preserve">8.2268533706665</t>
   </si>
   <si>
     <t xml:space="preserve">8.19080924987793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20883178710938</t>
+    <t xml:space="preserve">8.20883083343506</t>
   </si>
   <si>
     <t xml:space="preserve">8.38003635406494</t>
@@ -3029,10 +3029,10 @@
     <t xml:space="preserve">8.02861595153809</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8033447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69521570205688</t>
+    <t xml:space="preserve">7.80334520339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69521522521973</t>
   </si>
   <si>
     <t xml:space="preserve">7.61411905288696</t>
@@ -3041,28 +3041,28 @@
     <t xml:space="preserve">7.37983798980713</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33478450775146</t>
+    <t xml:space="preserve">7.33478498458862</t>
   </si>
   <si>
     <t xml:space="preserve">7.37082767486572</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46093511581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36181688308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35280609130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4429144859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65016222000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46994638442993</t>
+    <t xml:space="preserve">7.46093559265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36181735992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35280656814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44291400909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65016174316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46994590759277</t>
   </si>
   <si>
     <t xml:space="preserve">7.39786005020142</t>
@@ -3071,40 +3071,40 @@
     <t xml:space="preserve">7.32577419281006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27170896530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30775165557861</t>
+    <t xml:space="preserve">7.27170848846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30775213241577</t>
   </si>
   <si>
     <t xml:space="preserve">7.29874181747437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26269865036011</t>
+    <t xml:space="preserve">7.26269817352295</t>
   </si>
   <si>
     <t xml:space="preserve">7.54203271865845</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64115142822266</t>
+    <t xml:space="preserve">7.6411509513855</t>
   </si>
   <si>
     <t xml:space="preserve">7.62312984466553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53302145004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52401113510132</t>
+    <t xml:space="preserve">7.53302192687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52401161193848</t>
   </si>
   <si>
     <t xml:space="preserve">7.31676292419434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38884878158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45192527770996</t>
+    <t xml:space="preserve">7.38884925842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4519248008728</t>
   </si>
   <si>
     <t xml:space="preserve">6.96534204483032</t>
@@ -3113,25 +3113,25 @@
     <t xml:space="preserve">6.92929887771606</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02841806411743</t>
+    <t xml:space="preserve">7.02841758728027</t>
   </si>
   <si>
     <t xml:space="preserve">6.89325571060181</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01039600372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12753582000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11852598190308</t>
+    <t xml:space="preserve">7.0103964805603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12753629684448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11852550506592</t>
   </si>
   <si>
     <t xml:space="preserve">6.94732046127319</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88424491882324</t>
+    <t xml:space="preserve">6.8842453956604</t>
   </si>
   <si>
     <t xml:space="preserve">6.90226650238037</t>
@@ -3143,7 +3143,7 @@
     <t xml:space="preserve">7.22665548324585</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03742837905884</t>
+    <t xml:space="preserve">7.03742790222168</t>
   </si>
   <si>
     <t xml:space="preserve">7.14555740356445</t>
@@ -3161,13 +3161,13 @@
     <t xml:space="preserve">6.80314779281616</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74007272720337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66798639297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36161947250366</t>
+    <t xml:space="preserve">6.74007225036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6679859161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36161851882935</t>
   </si>
   <si>
     <t xml:space="preserve">6.59589958190918</t>
@@ -3176,10 +3176,10 @@
     <t xml:space="preserve">6.41568422317505</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3255763053894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13634920120239</t>
+    <t xml:space="preserve">6.32557582855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13634872436523</t>
   </si>
   <si>
     <t xml:space="preserve">5.85701465606689</t>
@@ -3188,10 +3188,10 @@
     <t xml:space="preserve">5.83899307250977</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01019811630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28052186965942</t>
+    <t xml:space="preserve">6.01019859313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28052139282227</t>
   </si>
   <si>
     <t xml:space="preserve">6.09129524230957</t>
@@ -3203,13 +3203,13 @@
     <t xml:space="preserve">6.35260820388794</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2354679107666</t>
+    <t xml:space="preserve">6.23546838760376</t>
   </si>
   <si>
     <t xml:space="preserve">6.46974849700928</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3886513710022</t>
+    <t xml:space="preserve">6.38865089416504</t>
   </si>
   <si>
     <t xml:space="preserve">6.37062978744507</t>
@@ -3218,43 +3218,43 @@
     <t xml:space="preserve">6.28953266143799</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31656503677368</t>
+    <t xml:space="preserve">6.31656551361084</t>
   </si>
   <si>
     <t xml:space="preserve">6.02822017669678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11832809448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12733793258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27151107788086</t>
+    <t xml:space="preserve">6.11832761764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12733840942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27151155471802</t>
   </si>
   <si>
     <t xml:space="preserve">6.26249980926514</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18140268325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29854297637939</t>
+    <t xml:space="preserve">6.18140316009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29854345321655</t>
   </si>
   <si>
     <t xml:space="preserve">6.17239236831665</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84800338745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86602592468262</t>
+    <t xml:space="preserve">5.84800386428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86602544784546</t>
   </si>
   <si>
     <t xml:space="preserve">5.92009019851685</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89305782318115</t>
+    <t xml:space="preserve">5.89305734634399</t>
   </si>
   <si>
     <t xml:space="preserve">5.93811178207397</t>
@@ -3272,31 +3272,31 @@
     <t xml:space="preserve">6.06426286697388</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98316526412964</t>
+    <t xml:space="preserve">5.9831657409668</t>
   </si>
   <si>
     <t xml:space="preserve">5.94712257385254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0192084312439</t>
+    <t xml:space="preserve">6.01920890808105</t>
   </si>
   <si>
     <t xml:space="preserve">5.99217653274536</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96514368057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97415494918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9561333656311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08228492736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07327318191528</t>
+    <t xml:space="preserve">5.96514415740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97415542602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95613384246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08228445053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07327365875244</t>
   </si>
   <si>
     <t xml:space="preserve">6.03723001480103</t>
@@ -3305,10 +3305,10 @@
     <t xml:space="preserve">6.04001379013062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94737529754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96590280532837</t>
+    <t xml:space="preserve">5.94737577438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96590328216553</t>
   </si>
   <si>
     <t xml:space="preserve">6.1604437828064</t>
@@ -3317,13 +3317,13 @@
     <t xml:space="preserve">6.28087329864502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22528982162476</t>
+    <t xml:space="preserve">6.22529029846191</t>
   </si>
   <si>
     <t xml:space="preserve">6.20676231384277</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17897176742554</t>
+    <t xml:space="preserve">6.17897129058838</t>
   </si>
   <si>
     <t xml:space="preserve">6.29013729095459</t>
@@ -3338,13 +3338,13 @@
     <t xml:space="preserve">6.00295877456665</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81768226623535</t>
+    <t xml:space="preserve">5.81768274307251</t>
   </si>
   <si>
     <t xml:space="preserve">5.83620977401733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9288477897644</t>
+    <t xml:space="preserve">5.92884826660156</t>
   </si>
   <si>
     <t xml:space="preserve">5.89179277420044</t>
@@ -3359,13 +3359,13 @@
     <t xml:space="preserve">5.95663928985596</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82694625854492</t>
+    <t xml:space="preserve">5.82694578170776</t>
   </si>
   <si>
     <t xml:space="preserve">5.68798828125</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78062629699707</t>
+    <t xml:space="preserve">5.78062677383423</t>
   </si>
   <si>
     <t xml:space="preserve">5.73430776596069</t>
@@ -3380,7 +3380,7 @@
     <t xml:space="preserve">5.44712924957275</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6046142578125</t>
+    <t xml:space="preserve">5.60461473464966</t>
   </si>
   <si>
     <t xml:space="preserve">5.75283527374268</t>
@@ -3389,10 +3389,10 @@
     <t xml:space="preserve">5.51197576522827</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85473728179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55829524993896</t>
+    <t xml:space="preserve">5.85473775863647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55829477310181</t>
   </si>
   <si>
     <t xml:space="preserve">5.71578025817871</t>
@@ -3407,13 +3407,13 @@
     <t xml:space="preserve">5.66019725799561</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8732647895813</t>
+    <t xml:space="preserve">5.87326574325562</t>
   </si>
   <si>
     <t xml:space="preserve">5.66946077346802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80841875076294</t>
+    <t xml:space="preserve">5.80841827392578</t>
   </si>
   <si>
     <t xml:space="preserve">6.0307502746582</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">6.04927778244019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86400127410889</t>
+    <t xml:space="preserve">5.86400079727173</t>
   </si>
   <si>
     <t xml:space="preserve">5.53976726531982</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">5.15995073318481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21553373336792</t>
+    <t xml:space="preserve">5.21553325653076</t>
   </si>
   <si>
     <t xml:space="preserve">5.19700622558594</t>
@@ -3461,13 +3461,13 @@
     <t xml:space="preserve">5.25258874893188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38228273391724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1321587562561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10436820983887</t>
+    <t xml:space="preserve">5.38228178024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13215923309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10436773300171</t>
   </si>
   <si>
     <t xml:space="preserve">5.28038024902344</t>
@@ -3482,10 +3482,10 @@
     <t xml:space="preserve">5.08583974838257</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05804824829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01172971725464</t>
+    <t xml:space="preserve">5.05804872512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01172924041748</t>
   </si>
   <si>
     <t xml:space="preserve">5.02099323272705</t>
@@ -3494,13 +3494,13 @@
     <t xml:space="preserve">5.1784782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0487847328186</t>
+    <t xml:space="preserve">5.04878425598145</t>
   </si>
   <si>
     <t xml:space="preserve">5.15068674087524</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00246572494507</t>
+    <t xml:space="preserve">5.00246524810791</t>
   </si>
   <si>
     <t xml:space="preserve">4.8635082244873</t>
@@ -3509,31 +3509,31 @@
     <t xml:space="preserve">4.91909122467041</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97467422485352</t>
+    <t xml:space="preserve">4.97467374801636</t>
   </si>
   <si>
     <t xml:space="preserve">4.96541023254395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22479724884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33596324920654</t>
+    <t xml:space="preserve">5.22479772567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3359637260437</t>
   </si>
   <si>
     <t xml:space="preserve">5.30817174911499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45639324188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52123928070068</t>
+    <t xml:space="preserve">5.45639276504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52123975753784</t>
   </si>
   <si>
     <t xml:space="preserve">5.29890775680542</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46565675735474</t>
+    <t xml:space="preserve">5.46565723419189</t>
   </si>
   <si>
     <t xml:space="preserve">5.56755924224854</t>
@@ -3542,22 +3542,22 @@
     <t xml:space="preserve">5.67872476577759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76209878921509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90105676651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91958427429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70651578903198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74357128143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65093326568604</t>
+    <t xml:space="preserve">5.76209926605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90105628967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91958379745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70651626586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74357175827026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65093278884888</t>
   </si>
   <si>
     <t xml:space="preserve">5.63240575790405</t>
@@ -3572,13 +3572,13 @@
     <t xml:space="preserve">5.88252878189087</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99369478225708</t>
+    <t xml:space="preserve">5.99369430541992</t>
   </si>
   <si>
     <t xml:space="preserve">5.98443126678467</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91032028198242</t>
+    <t xml:space="preserve">5.91032075881958</t>
   </si>
   <si>
     <t xml:space="preserve">6.44762229919434</t>
@@ -3590,7 +3590,7 @@
     <t xml:space="preserve">6.70700931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79964828491211</t>
+    <t xml:space="preserve">6.79964780807495</t>
   </si>
   <si>
     <t xml:space="preserve">6.82743883132935</t>
@@ -3599,19 +3599,19 @@
     <t xml:space="preserve">6.79038381576538</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89228630065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96639680862427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23504734039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34621286392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38326787948608</t>
+    <t xml:space="preserve">6.89228582382202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96639633178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23504686355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34621334075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38326835632324</t>
   </si>
   <si>
     <t xml:space="preserve">7.46664333343506</t>
@@ -3626,13 +3626,13 @@
     <t xml:space="preserve">7.42958831787109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55928087234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39253282546997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59633636474609</t>
+    <t xml:space="preserve">7.55928134918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39253234863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59633684158325</t>
   </si>
   <si>
     <t xml:space="preserve">7.54075384140015</t>
@@ -3641,22 +3641,22 @@
     <t xml:space="preserve">7.64265584945679</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50369882583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63339138031006</t>
+    <t xml:space="preserve">7.50369834899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63339185714722</t>
   </si>
   <si>
     <t xml:space="preserve">7.62412738800049</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57780933380127</t>
+    <t xml:space="preserve">7.57780885696411</t>
   </si>
   <si>
     <t xml:space="preserve">7.58707237243652</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45737934112549</t>
+    <t xml:space="preserve">7.45737981796265</t>
   </si>
   <si>
     <t xml:space="preserve">7.43885135650635</t>
@@ -3668,10 +3668,10 @@
     <t xml:space="preserve">7.32768535614014</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10535383224487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18872833251953</t>
+    <t xml:space="preserve">7.10535430908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18872880935669</t>
   </si>
   <si>
     <t xml:space="preserve">7.42032432556152</t>
@@ -3698,31 +3698,31 @@
     <t xml:space="preserve">7.27210235595703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20725584030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33694982528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31842231750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26283931732178</t>
+    <t xml:space="preserve">7.20725631713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33694934844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31842184066772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26283884048462</t>
   </si>
   <si>
     <t xml:space="preserve">7.12388134002686</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04977130889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98492431640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07756233215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22578430175781</t>
+    <t xml:space="preserve">7.04977083206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98492383956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07756280899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22578382492065</t>
   </si>
   <si>
     <t xml:space="preserve">7.19799184799194</t>
@@ -3731,10 +3731,10 @@
     <t xml:space="preserve">7.15167284011841</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11461734771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05903482437134</t>
+    <t xml:space="preserve">7.11461782455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05903434753418</t>
   </si>
   <si>
     <t xml:space="preserve">7.06857395172119</t>
@@ -3749,34 +3749,34 @@
     <t xml:space="preserve">6.94456434249878</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86825037002563</t>
+    <t xml:space="preserve">6.86824989318848</t>
   </si>
   <si>
     <t xml:space="preserve">6.79193639755249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75377893447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84917116165161</t>
+    <t xml:space="preserve">6.75377941131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84917163848877</t>
   </si>
   <si>
     <t xml:space="preserve">6.99226045608521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95410299301147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87778949737549</t>
+    <t xml:space="preserve">6.95410346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87778902053833</t>
   </si>
   <si>
     <t xml:space="preserve">6.98272132873535</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96364307403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03041696548462</t>
+    <t xml:space="preserve">6.96364259719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03041744232178</t>
   </si>
   <si>
     <t xml:space="preserve">7.01133871078491</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">6.78239727020264</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72516202926636</t>
+    <t xml:space="preserve">6.7251615524292</t>
   </si>
   <si>
     <t xml:space="preserve">7.00179958343506</t>
@@ -3815,19 +3815,19 @@
     <t xml:space="preserve">7.36429023742676</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28797626495361</t>
+    <t xml:space="preserve">7.28797674179077</t>
   </si>
   <si>
     <t xml:space="preserve">7.29751586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30705451965332</t>
+    <t xml:space="preserve">7.30705499649048</t>
   </si>
   <si>
     <t xml:space="preserve">7.53599691390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57415342330933</t>
+    <t xml:space="preserve">7.57415390014648</t>
   </si>
   <si>
     <t xml:space="preserve">7.66000652313232</t>
@@ -3836,10 +3836,10 @@
     <t xml:space="preserve">7.6981635093689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93664407730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98434019088745</t>
+    <t xml:space="preserve">7.93664455413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98434066772461</t>
   </si>
   <si>
     <t xml:space="preserve">8.18466472625732</t>
@@ -3857,19 +3857,19 @@
     <t xml:space="preserve">8.16558647155762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04157638549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87940979003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9748010635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03203773498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90802669525146</t>
+    <t xml:space="preserve">8.04157733917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8794093132019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97480154037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03203678131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90802717208862</t>
   </si>
   <si>
     <t xml:space="preserve">7.89848756790161</t>
@@ -3881,7 +3881,7 @@
     <t xml:space="preserve">7.84125232696533</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88894891738892</t>
+    <t xml:space="preserve">7.88894844055176</t>
   </si>
   <si>
     <t xml:space="preserve">7.78401708602905</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">7.81263399124146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85079145431519</t>
+    <t xml:space="preserve">7.85079050064087</t>
   </si>
   <si>
     <t xml:space="preserve">7.77447748184204</t>
@@ -3905,13 +3905,13 @@
     <t xml:space="preserve">7.72678184509277</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64092826843262</t>
+    <t xml:space="preserve">7.64092874526978</t>
   </si>
   <si>
     <t xml:space="preserve">7.58369255065918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38336849212646</t>
+    <t xml:space="preserve">7.38336896896362</t>
   </si>
   <si>
     <t xml:space="preserve">7.3356728553772</t>
@@ -3932,7 +3932,7 @@
     <t xml:space="preserve">7.08765268325806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15442752838135</t>
+    <t xml:space="preserve">7.15442705154419</t>
   </si>
   <si>
     <t xml:space="preserve">7.03995656967163</t>
@@ -3944,7 +3944,7 @@
     <t xml:space="preserve">7.27843761444092</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41198682785034</t>
+    <t xml:space="preserve">7.41198635101318</t>
   </si>
   <si>
     <t xml:space="preserve">7.39290809631348</t>
@@ -3965,13 +3965,13 @@
     <t xml:space="preserve">7.45014333724976</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40244722366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50737905502319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70770311355591</t>
+    <t xml:space="preserve">7.40244770050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50737857818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70770263671875</t>
   </si>
   <si>
     <t xml:space="preserve">8.20374393463135</t>
@@ -3986,10 +3986,10 @@
     <t xml:space="preserve">8.10835075378418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08927154541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36591148376465</t>
+    <t xml:space="preserve">8.08927249908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36591053009033</t>
   </si>
   <si>
     <t xml:space="preserve">8.30867481231689</t>
@@ -4007,13 +4007,13 @@
     <t xml:space="preserve">8.60439205169678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40406799316406</t>
+    <t xml:space="preserve">8.40406703948975</t>
   </si>
   <si>
     <t xml:space="preserve">8.41360664367676</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26097869873047</t>
+    <t xml:space="preserve">8.26097774505615</t>
   </si>
   <si>
     <t xml:space="preserve">8.57577323913574</t>
@@ -4028,10 +4028,10 @@
     <t xml:space="preserve">8.76655769348145</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15766716003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19582366943359</t>
+    <t xml:space="preserve">9.1576681137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19582462310791</t>
   </si>
   <si>
     <t xml:space="preserve">9.11951065063477</t>
@@ -4040,13 +4040,13 @@
     <t xml:space="preserve">9.10043144226074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09089279174805</t>
+    <t xml:space="preserve">9.09089183807373</t>
   </si>
   <si>
     <t xml:space="preserve">8.72840118408203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87148952484131</t>
+    <t xml:space="preserve">8.87149047851562</t>
   </si>
   <si>
     <t xml:space="preserve">8.90964698791504</t>
@@ -4070,7 +4070,7 @@
     <t xml:space="preserve">9.00503826141357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20536231994629</t>
+    <t xml:space="preserve">9.20536327362061</t>
   </si>
   <si>
     <t xml:space="preserve">9.45338344573975</t>
@@ -4079,25 +4079,25 @@
     <t xml:space="preserve">9.50107955932617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52969646453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.577392578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47246265411377</t>
+    <t xml:space="preserve">9.52969741821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57739353179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47246170043945</t>
   </si>
   <si>
     <t xml:space="preserve">9.36752986907959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30075550079346</t>
+    <t xml:space="preserve">9.30075454711914</t>
   </si>
   <si>
     <t xml:space="preserve">9.39614772796631</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44384384155273</t>
+    <t xml:space="preserve">9.44384288787842</t>
   </si>
   <si>
     <t xml:space="preserve">9.49153995513916</t>
@@ -4109,7 +4109,7 @@
     <t xml:space="preserve">8.69978332519531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55669593811035</t>
+    <t xml:space="preserve">8.55669498443604</t>
   </si>
   <si>
     <t xml:space="preserve">8.62346935272217</t>
@@ -4118,10 +4118,10 @@
     <t xml:space="preserve">8.48038101196289</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59485244750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70932197570801</t>
+    <t xml:space="preserve">8.59485149383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70932292938232</t>
   </si>
   <si>
     <t xml:space="preserve">8.77609729766846</t>
@@ -4133,10 +4133,10 @@
     <t xml:space="preserve">8.75701904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8619499206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89056873321533</t>
+    <t xml:space="preserve">8.86195087432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89056777954102</t>
   </si>
   <si>
     <t xml:space="preserve">8.67116546630859</t>
@@ -4151,10 +4151,10 @@
     <t xml:space="preserve">8.74748039245605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01457786560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92872524261475</t>
+    <t xml:space="preserve">9.0145788192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92872428894043</t>
   </si>
   <si>
     <t xml:space="preserve">8.97642135620117</t>
@@ -4166,28 +4166,28 @@
     <t xml:space="preserve">9.46292304992676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74909973144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78725624084473</t>
+    <t xml:space="preserve">9.74910068511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78725719451904</t>
   </si>
   <si>
     <t xml:space="preserve">9.92080497741699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99711990356445</t>
+    <t xml:space="preserve">9.99711894989014</t>
   </si>
   <si>
     <t xml:space="preserve">9.69186401367188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7681770324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80633544921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63462924957275</t>
+    <t xml:space="preserve">9.76817798614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80633449554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63462829589844</t>
   </si>
   <si>
     <t xml:space="preserve">9.67278575897217</t>
@@ -4196,10 +4196,10 @@
     <t xml:space="preserve">9.59647178649902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7109432220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52015781402588</t>
+    <t xml:space="preserve">9.71094226837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52015686035156</t>
   </si>
   <si>
     <t xml:space="preserve">9.43430519104004</t>
@@ -4208,13 +4208,13 @@
     <t xml:space="preserve">9.25305938720703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28167724609375</t>
+    <t xml:space="preserve">9.28167629241943</t>
   </si>
   <si>
     <t xml:space="preserve">9.34845161437988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41522598266602</t>
+    <t xml:space="preserve">9.41522693634033</t>
   </si>
   <si>
     <t xml:space="preserve">9.48200035095215</t>
@@ -4232,7 +4232,7 @@
     <t xml:space="preserve">9.65370750427246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86357021331787</t>
+    <t xml:space="preserve">9.86357116699219</t>
   </si>
   <si>
     <t xml:space="preserve">10.0204467773438</t>
@@ -5010,6 +5010,9 @@
   </si>
   <si>
     <t xml:space="preserve">19.7399997711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1000003814697</t>
   </si>
 </sst>
 </file>
@@ -71518,7 +71521,7 @@
     </row>
     <row r="2546">
       <c r="A2546" s="1" t="n">
-        <v>46030.6909837963</v>
+        <v>46030.3333333333</v>
       </c>
       <c r="B2546" t="n">
         <v>106505</v>
@@ -71539,6 +71542,32 @@
         <v>1665</v>
       </c>
       <c r="H2546" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2547">
+      <c r="A2547" s="1" t="n">
+        <v>46031.6912268518</v>
+      </c>
+      <c r="B2547" t="n">
+        <v>180502</v>
+      </c>
+      <c r="C2547" t="n">
+        <v>20.1499996185303</v>
+      </c>
+      <c r="D2547" t="n">
+        <v>19.7000007629395</v>
+      </c>
+      <c r="E2547" t="n">
+        <v>19.7999992370605</v>
+      </c>
+      <c r="F2547" t="n">
+        <v>20.1000003814697</v>
+      </c>
+      <c r="G2547" t="s">
+        <v>1666</v>
+      </c>
+      <c r="H2547" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CEM.MI.xlsx
+++ b/data/CEM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1669" uniqueCount="1669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="1670">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,46 +38,46 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70432186126709</t>
+    <t xml:space="preserve">4.70432090759277</t>
   </si>
   <si>
     <t xml:space="preserve">CEM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68036031723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55656242370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48867273330688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32893466949463</t>
+    <t xml:space="preserve">4.68035984039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55656147003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4886736869812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32893419265747</t>
   </si>
   <si>
     <t xml:space="preserve">4.22110939025879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32494068145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28899812698364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29299306869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06137084960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93597483634949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97431254386902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6755998134613</t>
+    <t xml:space="preserve">4.32494020462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28899908065796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29299163818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06137132644653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93597507476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9743127822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67560029029846</t>
   </si>
   <si>
     <t xml:space="preserve">3.83533978462219</t>
@@ -86,139 +86,139 @@
     <t xml:space="preserve">3.94875431060791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88006591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91680645942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87846899032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74588561058044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93437767028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87367677688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7378978729248</t>
+    <t xml:space="preserve">3.88006639480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91680669784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87846946716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74588513374329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9343786239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87367701530457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73789811134338</t>
   </si>
   <si>
     <t xml:space="preserve">3.57815933227539</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5989248752594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61969232559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35132956504822</t>
+    <t xml:space="preserve">3.59892511367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6196916103363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35133004188538</t>
   </si>
   <si>
     <t xml:space="preserve">3.15005803108215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25069379806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13088941574097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20916152000427</t>
+    <t xml:space="preserve">3.25069427490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13088965415955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20916199684143</t>
   </si>
   <si>
     <t xml:space="preserve">3.44238138198853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3625111579895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47592663764954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55419850349426</t>
+    <t xml:space="preserve">3.36251139640808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4759259223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55419874191284</t>
   </si>
   <si>
     <t xml:space="preserve">3.34653735160828</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39126372337341</t>
+    <t xml:space="preserve">3.39126443862915</t>
   </si>
   <si>
     <t xml:space="preserve">3.3673038482666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23951244354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29222631454468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40244650840759</t>
+    <t xml:space="preserve">3.2395122051239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2922260761261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40244626998901</t>
   </si>
   <si>
     <t xml:space="preserve">3.58614635467529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63406848907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55579590797424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64365243911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56058788299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52065372467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49828958511353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52544522285461</t>
+    <t xml:space="preserve">3.63406801223755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55579543113708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64365220069885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56058835983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52065324783325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49829053878784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52544546127319</t>
   </si>
   <si>
     <t xml:space="preserve">3.54940581321716</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75227475166321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6133017539978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75387239456177</t>
+    <t xml:space="preserve">3.75227499008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61330199241638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75387167930603</t>
   </si>
   <si>
     <t xml:space="preserve">3.83214473724365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67080855369568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70754766464233</t>
+    <t xml:space="preserve">3.67080807685852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70754814147949</t>
   </si>
   <si>
     <t xml:space="preserve">3.65802907943726</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51745820045471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57017254829407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50947165489197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54301691055298</t>
+    <t xml:space="preserve">3.51745843887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57017302513123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50947141647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5430166721344</t>
   </si>
   <si>
     <t xml:space="preserve">3.57975673675537</t>
@@ -227,172 +227,172 @@
     <t xml:space="preserve">3.45196533203125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41043329238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37529039382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60052251815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48551058769226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54461431503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59573006629944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77943062782288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74428820610046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85770297050476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73949575424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74907994270325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70595026016235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69317221641541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67719721794128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7970027923584</t>
+    <t xml:space="preserve">3.41043305397034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3752908706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6005232334137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48551082611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54461455345154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5957305431366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77943086624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7442889213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85770273208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7394962310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74908041954041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70595049858093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69317150115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67719841003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79700183868408</t>
   </si>
   <si>
     <t xml:space="preserve">3.66601586341858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70115852355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62608075141907</t>
+    <t xml:space="preserve">3.70115900039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62608051300049</t>
   </si>
   <si>
     <t xml:space="preserve">3.6740026473999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64205527305603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53023767471313</t>
+    <t xml:space="preserve">3.64205479621887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53023791313171</t>
   </si>
   <si>
     <t xml:space="preserve">3.45835542678833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47432947158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53193736076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62187051773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7575888633728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76085877418518</t>
+    <t xml:space="preserve">3.47432899475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53193759918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62187075614929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75758838653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7608585357666</t>
   </si>
   <si>
     <t xml:space="preserve">3.87531971931458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88349604606628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77721071243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75431799888611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7052640914917</t>
+    <t xml:space="preserve">3.88349556922913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7772102355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75431847572327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70526361465454</t>
   </si>
   <si>
     <t xml:space="preserve">3.66929006576538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59734344482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58426189422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55646467208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38640832901001</t>
+    <t xml:space="preserve">3.5973436832428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5842616558075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55646443367004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38640856742859</t>
   </si>
   <si>
     <t xml:space="preserve">3.31119108200073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29810929298401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19673037528992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1591215133667</t>
+    <t xml:space="preserve">3.29810976982117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19673013687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15912127494812</t>
   </si>
   <si>
     <t xml:space="preserve">3.00705194473267</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15421605110168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03484964370728</t>
+    <t xml:space="preserve">3.15421581268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03484916687012</t>
   </si>
   <si>
     <t xml:space="preserve">3.22289252281189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35206961631775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10679626464844</t>
+    <t xml:space="preserve">3.35207009315491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10679650306702</t>
   </si>
   <si>
     <t xml:space="preserve">2.82882022857666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82064390182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84026598930359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93510484695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04302525520325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95799732208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79611706733704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76341414451599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76831889152527</t>
+    <t xml:space="preserve">2.82064414024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84026622772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93510460853577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04302501678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9579975605011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79611682891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76341366767883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76831912994385</t>
   </si>
   <si>
     <t xml:space="preserve">2.84844183921814</t>
@@ -401,10 +401,10 @@
     <t xml:space="preserve">2.87787461280823</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04138994216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00051116943359</t>
+    <t xml:space="preserve">3.04139018058777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00051140785217</t>
   </si>
   <si>
     <t xml:space="preserve">3.2114462852478</t>
@@ -419,19 +419,19 @@
     <t xml:space="preserve">2.97434878349304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1084315776825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9759840965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92856431007385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17547297477722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18037843704224</t>
+    <t xml:space="preserve">3.10843181610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97598361968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92856454849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17547273635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18037867546082</t>
   </si>
   <si>
     <t xml:space="preserve">3.15585088729858</t>
@@ -449,88 +449,88 @@
     <t xml:space="preserve">3.02503848075867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11660766601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23760914802551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28012275695801</t>
+    <t xml:space="preserve">3.11660718917847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23760890960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28012299537659</t>
   </si>
   <si>
     <t xml:space="preserve">3.32263731956482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43546295166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40602993965149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46653056144714</t>
+    <t xml:space="preserve">3.43546319007874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40602970123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4665310382843</t>
   </si>
   <si>
     <t xml:space="preserve">3.43709802627563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44854402542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67910051345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64639782905579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71834468841553</t>
+    <t xml:space="preserve">3.44854378700256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67910099029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64639830589294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71834444999695</t>
   </si>
   <si>
     <t xml:space="preserve">3.69545221328735</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74450755119324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85242772102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80827856063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82299494743347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80337285995483</t>
+    <t xml:space="preserve">3.74450731277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8524272441864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80827879905701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82299518585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80337262153625</t>
   </si>
   <si>
     <t xml:space="preserve">3.74287247657776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62350630760193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56627559661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47470641136169</t>
+    <t xml:space="preserve">3.62350535392761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56627488136292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47470688819885</t>
   </si>
   <si>
     <t xml:space="preserve">3.51558542251587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65947890281677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60551881790161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54501819610596</t>
+    <t xml:space="preserve">3.65947842597961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60551905632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5450177192688</t>
   </si>
   <si>
     <t xml:space="preserve">3.64803266525269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64476275444031</t>
+    <t xml:space="preserve">3.64476323127747</t>
   </si>
   <si>
     <t xml:space="preserve">3.38804340362549</t>
@@ -539,40 +539,40 @@
     <t xml:space="preserve">3.48288249969482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45344948768616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43382692337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5074098110199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56463980674744</t>
+    <t xml:space="preserve">3.45344996452332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4338276386261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50740957260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56464052200317</t>
   </si>
   <si>
     <t xml:space="preserve">3.55482912063599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56300520896912</t>
+    <t xml:space="preserve">3.56300497055054</t>
   </si>
   <si>
     <t xml:space="preserve">3.4845175743103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54338312149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62514114379883</t>
+    <t xml:space="preserve">3.54338359832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62514090538025</t>
   </si>
   <si>
     <t xml:space="preserve">3.59080290794373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64149284362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68891215324402</t>
+    <t xml:space="preserve">3.64149260520935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68891191482544</t>
   </si>
   <si>
     <t xml:space="preserve">3.66111469268799</t>
@@ -584,76 +584,76 @@
     <t xml:space="preserve">3.53684258460999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.630047082901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63822221755981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43873262405396</t>
+    <t xml:space="preserve">3.63004660606384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63822245597839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43873310089111</t>
   </si>
   <si>
     <t xml:space="preserve">3.41747617721558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41911149024963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33571839332581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37169146537781</t>
+    <t xml:space="preserve">3.41911101341248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33571815490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37169170379639</t>
   </si>
   <si>
     <t xml:space="preserve">3.27521753311157</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22125744819641</t>
+    <t xml:space="preserve">3.22125720977783</t>
   </si>
   <si>
     <t xml:space="preserve">3.2098114490509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17710781097412</t>
+    <t xml:space="preserve">3.17710828781128</t>
   </si>
   <si>
     <t xml:space="preserve">3.21308183670044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14767503738403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11333727836609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00541710853577</t>
+    <t xml:space="preserve">3.14767527580261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11333703994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00541687011719</t>
   </si>
   <si>
     <t xml:space="preserve">3.0168628692627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9530918598175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9187536239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96453785896301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96780824661255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95636224746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04793095588684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17220258712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18691921234131</t>
+    <t xml:space="preserve">2.95309209823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91875338554382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96453762054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96780800819397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95636200904846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04793047904968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17220282554626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18691873550415</t>
   </si>
   <si>
     <t xml:space="preserve">3.3193666934967</t>
@@ -662,46 +662,46 @@
     <t xml:space="preserve">3.2343385219574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45835518836975</t>
+    <t xml:space="preserve">3.45835494995117</t>
   </si>
   <si>
     <t xml:space="preserve">3.48778748512268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45181441307068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4992344379425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57281565666199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45017910003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61369466781616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67746591567993</t>
+    <t xml:space="preserve">3.4518141746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49923419952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57281613349915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45017886161804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61369514465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67746639251709</t>
   </si>
   <si>
     <t xml:space="preserve">3.58916759490967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70362901687622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48615264892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33244824409485</t>
+    <t xml:space="preserve">3.7036280632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4861524105072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33244800567627</t>
   </si>
   <si>
     <t xml:space="preserve">3.28666377067566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22943329811096</t>
+    <t xml:space="preserve">3.22943305969238</t>
   </si>
   <si>
     <t xml:space="preserve">3.27031207084656</t>
@@ -710,19 +710,19 @@
     <t xml:space="preserve">3.24741983413696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23106837272644</t>
+    <t xml:space="preserve">3.23106813430786</t>
   </si>
   <si>
     <t xml:space="preserve">3.23270344734192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26213598251343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27685236930847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23597383499146</t>
+    <t xml:space="preserve">3.26213645935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27685284614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23597359657288</t>
   </si>
   <si>
     <t xml:space="preserve">4.00122690200806</t>
@@ -737,10 +737,10 @@
     <t xml:space="preserve">4.16964817047119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17782306671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06336212158203</t>
+    <t xml:space="preserve">4.17782354354858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06336259841919</t>
   </si>
   <si>
     <t xml:space="preserve">3.95707750320435</t>
@@ -752,19 +752,19 @@
     <t xml:space="preserve">4.28410863876343</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3454270362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47215127944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43944835662842</t>
+    <t xml:space="preserve">4.34542655944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47215175628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43944883346558</t>
   </si>
   <si>
     <t xml:space="preserve">4.41083335876465</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41492176055908</t>
+    <t xml:space="preserve">4.41492223739624</t>
   </si>
   <si>
     <t xml:space="preserve">4.37404203414917</t>
@@ -773,37 +773,37 @@
     <t xml:space="preserve">4.26775693893433</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39039325714111</t>
+    <t xml:space="preserve">4.39039421081543</t>
   </si>
   <si>
     <t xml:space="preserve">4.3617787361145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37813138961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38630628585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56208515167236</t>
+    <t xml:space="preserve">4.37812995910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38630533218384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56208562850952</t>
   </si>
   <si>
     <t xml:space="preserve">4.42718458175659</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32907485961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25549364089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25140523910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30046033859253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34951591491699</t>
+    <t xml:space="preserve">4.3290753364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2554931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25140571594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30046081542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34951448440552</t>
   </si>
   <si>
     <t xml:space="preserve">4.24322986602783</t>
@@ -812,100 +812,100 @@
     <t xml:space="preserve">4.24731731414795</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21052646636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14512062072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1042423248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22279071807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40674543380737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36586666107178</t>
+    <t xml:space="preserve">4.21052694320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1451210975647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10424137115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2227897644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40674591064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36586713790894</t>
   </si>
   <si>
     <t xml:space="preserve">4.27593326568604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3045482635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28002119064331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44762468338013</t>
+    <t xml:space="preserve">4.30454730987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28002071380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44762420654297</t>
   </si>
   <si>
     <t xml:space="preserve">4.52938270568848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51711893081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52120637893677</t>
+    <t xml:space="preserve">4.51711797714233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52120685577393</t>
   </si>
   <si>
     <t xml:space="preserve">4.68063402175903</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66019439697266</t>
+    <t xml:space="preserve">4.66019487380981</t>
   </si>
   <si>
     <t xml:space="preserve">4.71333694458008</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73377704620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81962299346924</t>
+    <t xml:space="preserve">4.7337760925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81962251663208</t>
   </si>
   <si>
     <t xml:space="preserve">4.81144666671753</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65201902389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34133958816528</t>
+    <t xml:space="preserve">4.65201997756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34133911132812</t>
   </si>
   <si>
     <t xml:space="preserve">4.33725118637085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25958156585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40383434295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44966459274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41633415222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37467002868652</t>
+    <t xml:space="preserve">4.25958108901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40383386611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44966506958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41633367538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37467050552368</t>
   </si>
   <si>
     <t xml:space="preserve">4.36633729934692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30384254455566</t>
+    <t xml:space="preserve">4.30384159088135</t>
   </si>
   <si>
     <t xml:space="preserve">4.27467823028564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25801181793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31634140014648</t>
+    <t xml:space="preserve">4.25801229476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31634092330933</t>
   </si>
   <si>
     <t xml:space="preserve">4.26634502410889</t>
@@ -914,52 +914,52 @@
     <t xml:space="preserve">4.20801591873169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33300590515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37050342559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34550619125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39133548736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29967546463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42883253097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39966869354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39550161361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38300275802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46633005142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48299503326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.566321849823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40799999237061</t>
+    <t xml:space="preserve">4.33300638198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37050294876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3455057144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39133596420288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29967594146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42883205413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39966917037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3955020904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38300323486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46633052825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48299551010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56632232666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40800094604492</t>
   </si>
   <si>
     <t xml:space="preserve">4.34967184066772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69131278991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58298826217651</t>
+    <t xml:space="preserve">4.69131326675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58298778533936</t>
   </si>
   <si>
     <t xml:space="preserve">4.85380029678345</t>
@@ -971,16 +971,16 @@
     <t xml:space="preserve">5.0579514503479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10794878005981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24960374832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28710079193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25377082824707</t>
+    <t xml:space="preserve">5.1079478263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24960422515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28710174560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25376987457275</t>
   </si>
   <si>
     <t xml:space="preserve">5.41625833511353</t>
@@ -989,61 +989,61 @@
     <t xml:space="preserve">5.30376672744751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29960012435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34542989730835</t>
+    <t xml:space="preserve">5.29960060119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34543037414551</t>
   </si>
   <si>
     <t xml:space="preserve">5.30793237686157</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22877216339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29126787185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29543399810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16211175918579</t>
+    <t xml:space="preserve">5.22877264022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29126739501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29543447494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16211080551147</t>
   </si>
   <si>
     <t xml:space="preserve">5.0162878036499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05378580093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12461423873901</t>
+    <t xml:space="preserve">5.05378532409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12461376190186</t>
   </si>
   <si>
     <t xml:space="preserve">5.20377397537231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0746169090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03295373916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95795917510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99129056930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96212530136108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90796375274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94129419326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89129734039307</t>
+    <t xml:space="preserve">5.07461738586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0329532623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95795869827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99128913879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96212577819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90796232223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94129323959351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89129781723022</t>
   </si>
   <si>
     <t xml:space="preserve">4.90379667282104</t>
@@ -1073,13 +1073,13 @@
     <t xml:space="preserve">5.23293876647949</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17877626419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13294553756714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33293199539185</t>
+    <t xml:space="preserve">5.17877674102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1329460144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33293104171753</t>
   </si>
   <si>
     <t xml:space="preserve">5.26626968383789</t>
@@ -1091,16 +1091,16 @@
     <t xml:space="preserve">5.58291244506836</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68707036972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00371313095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80789566040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07454109191895</t>
+    <t xml:space="preserve">5.68707084655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00371360778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80789518356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07454204559326</t>
   </si>
   <si>
     <t xml:space="preserve">6.01621246337891</t>
@@ -1112,52 +1112,52 @@
     <t xml:space="preserve">5.89122200012207</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94121885299683</t>
+    <t xml:space="preserve">5.94121789932251</t>
   </si>
   <si>
     <t xml:space="preserve">5.96621656417847</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03287839889526</t>
+    <t xml:space="preserve">6.03287744522095</t>
   </si>
   <si>
     <t xml:space="preserve">5.99538135528564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97038269042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91622066497803</t>
+    <t xml:space="preserve">5.97038316726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91621971130371</t>
   </si>
   <si>
     <t xml:space="preserve">5.86205768585205</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92871904373169</t>
+    <t xml:space="preserve">5.92871952056885</t>
   </si>
   <si>
     <t xml:space="preserve">5.89955472946167</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90372133255005</t>
+    <t xml:space="preserve">5.90372180938721</t>
   </si>
   <si>
     <t xml:space="preserve">5.87455701828003</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84539270401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00788068771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98288154602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03704404830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09120750427246</t>
+    <t xml:space="preserve">5.84539222717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00787973403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98288106918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03704452514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0912070274353</t>
   </si>
   <si>
     <t xml:space="preserve">6.02871227264404</t>
@@ -1166,31 +1166,31 @@
     <t xml:space="preserve">5.99954700469971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04954385757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07870817184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29119205474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1745343208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19953203201294</t>
+    <t xml:space="preserve">6.0495433807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07870864868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29119253158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17453336715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1995325088501</t>
   </si>
   <si>
     <t xml:space="preserve">6.0828742980957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24536275863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21203184127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02454614639282</t>
+    <t xml:space="preserve">6.24536323547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21203136444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02454519271851</t>
   </si>
   <si>
     <t xml:space="preserve">6.09954023361206</t>
@@ -1199,16 +1199,16 @@
     <t xml:space="preserve">6.18286657333374</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2078652381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22036504745483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14537000656128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95788431167603</t>
+    <t xml:space="preserve">6.20786476135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22036409378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14537048339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95788288116455</t>
   </si>
   <si>
     <t xml:space="preserve">5.94538545608521</t>
@@ -1223,25 +1223,25 @@
     <t xml:space="preserve">6.1162052154541</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0620436668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04121160507202</t>
+    <t xml:space="preserve">6.06204271316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04121065139771</t>
   </si>
   <si>
     <t xml:space="preserve">6.1495361328125</t>
   </si>
   <si>
-    <t xml:space="preserve">6.095374584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35785436630249</t>
+    <t xml:space="preserve">6.09537410736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35785388946533</t>
   </si>
   <si>
     <t xml:space="preserve">6.22453022003174</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28285980224609</t>
+    <t xml:space="preserve">6.28285884857178</t>
   </si>
   <si>
     <t xml:space="preserve">6.58283710479736</t>
@@ -1250,37 +1250,37 @@
     <t xml:space="preserve">6.61616802215576</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57450389862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50784206390381</t>
+    <t xml:space="preserve">6.57450437545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50784254074097</t>
   </si>
   <si>
     <t xml:space="preserve">6.49950981140137</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65783071517944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7411584854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5911693572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6245002746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63283348083496</t>
+    <t xml:space="preserve">6.65783166885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74115896224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59116983413696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62450075149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63283395767212</t>
   </si>
   <si>
     <t xml:space="preserve">6.70782804489136</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52450752258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51617574691772</t>
+    <t xml:space="preserve">6.52450847625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51617527008057</t>
   </si>
   <si>
     <t xml:space="preserve">6.6661639213562</t>
@@ -1289,22 +1289,22 @@
     <t xml:space="preserve">6.54950666427612</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44951295852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29952430725098</t>
+    <t xml:space="preserve">6.44951343536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29952526092529</t>
   </si>
   <si>
     <t xml:space="preserve">6.23286294937134</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90788793563843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93288516998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53284072875977</t>
+    <t xml:space="preserve">5.90788745880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93288469314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53284120559692</t>
   </si>
   <si>
     <t xml:space="preserve">6.26619386672974</t>
@@ -1313,55 +1313,55 @@
     <t xml:space="preserve">6.36618614196777</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33285522460938</t>
+    <t xml:space="preserve">6.33285570144653</t>
   </si>
   <si>
     <t xml:space="preserve">6.1412034034729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1578688621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06620931625366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94955158233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13287162780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05787658691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88289022445679</t>
+    <t xml:space="preserve">6.15786838531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06620836257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94955062866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13287019729614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05787563323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88288927078247</t>
   </si>
   <si>
     <t xml:space="preserve">5.84955883026123</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81622743606567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72456789016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75789880752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76623249053955</t>
+    <t xml:space="preserve">5.81622838973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72456836700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75789928436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76623201370239</t>
   </si>
   <si>
     <t xml:space="preserve">5.68290519714355</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82456016540527</t>
+    <t xml:space="preserve">5.82456064224243</t>
   </si>
   <si>
     <t xml:space="preserve">5.86622428894043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77456426620483</t>
+    <t xml:space="preserve">5.77456474304199</t>
   </si>
   <si>
     <t xml:space="preserve">5.78289699554443</t>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">5.79122972488403</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63290929794312</t>
+    <t xml:space="preserve">5.63290882110596</t>
   </si>
   <si>
     <t xml:space="preserve">5.64982461929321</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">5.68365526199341</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66673946380615</t>
+    <t xml:space="preserve">5.66673994064331</t>
   </si>
   <si>
     <t xml:space="preserve">5.70057106018066</t>
@@ -1391,115 +1391,115 @@
     <t xml:space="preserve">5.45529460906982</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54833030700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53987312316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74285984039307</t>
+    <t xml:space="preserve">5.54833078384399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53987264633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74286079406738</t>
   </si>
   <si>
     <t xml:space="preserve">5.58216142654419</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65828227996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70902919769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77669143676758</t>
+    <t xml:space="preserve">5.65828275680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70902967453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77669191360474</t>
   </si>
   <si>
     <t xml:space="preserve">5.91201686859131</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9035587310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89510059356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75131797790527</t>
+    <t xml:space="preserve">5.90355920791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89510107040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75131845474243</t>
   </si>
   <si>
     <t xml:space="preserve">5.78514957427979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71748733520508</t>
+    <t xml:space="preserve">5.71748685836792</t>
   </si>
   <si>
     <t xml:space="preserve">5.81052303314209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56524610519409</t>
+    <t xml:space="preserve">5.56524562835693</t>
   </si>
   <si>
     <t xml:space="preserve">5.50604152679443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69211292266846</t>
+    <t xml:space="preserve">5.69211339950562</t>
   </si>
   <si>
     <t xml:space="preserve">5.72594451904297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73440265655518</t>
+    <t xml:space="preserve">5.73440313339233</t>
   </si>
   <si>
     <t xml:space="preserve">5.60753536224365</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51449966430664</t>
+    <t xml:space="preserve">5.51449918746948</t>
   </si>
   <si>
     <t xml:space="preserve">5.67519760131836</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01351118087769</t>
+    <t xml:space="preserve">6.01351022720337</t>
   </si>
   <si>
     <t xml:space="preserve">5.99659490585327</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81898069381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75977563858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80206441879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79360675811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88664388656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8781852722168</t>
+    <t xml:space="preserve">5.81898021697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75977611541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80206537246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79360723495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88664436340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87818574905396</t>
   </si>
   <si>
     <t xml:space="preserve">5.92893218994141</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85281181335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76823329925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82743787765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83589601516724</t>
+    <t xml:space="preserve">5.85281276702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76823425292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82743835449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83589649200439</t>
   </si>
   <si>
     <t xml:space="preserve">5.42992115020752</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3876314163208</t>
+    <t xml:space="preserve">5.38763093948364</t>
   </si>
   <si>
     <t xml:space="preserve">5.33688449859619</t>
@@ -1514,40 +1514,40 @@
     <t xml:space="preserve">5.43837833404541</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46375274658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44683647155762</t>
+    <t xml:space="preserve">5.46375179290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44683694839478</t>
   </si>
   <si>
     <t xml:space="preserve">5.35380029678345</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37071561813354</t>
+    <t xml:space="preserve">5.3707160949707</t>
   </si>
   <si>
     <t xml:space="preserve">5.22693300247192</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14235496520996</t>
+    <t xml:space="preserve">5.1423544883728</t>
   </si>
   <si>
     <t xml:space="preserve">5.11698150634766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24384880065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13389730453491</t>
+    <t xml:space="preserve">5.24384832382202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13389682769775</t>
   </si>
   <si>
     <t xml:space="preserve">5.26922225952148</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25230646133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21001768112183</t>
+    <t xml:space="preserve">5.25230693817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21001720428467</t>
   </si>
   <si>
     <t xml:space="preserve">5.23539066314697</t>
@@ -1559,58 +1559,58 @@
     <t xml:space="preserve">5.31996917724609</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29459571838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48912525177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32842683792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16772937774658</t>
+    <t xml:space="preserve">5.29459619522095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48912572860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3284273147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16772794723511</t>
   </si>
   <si>
     <t xml:space="preserve">5.09160804748535</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17618656158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10852384567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91399383544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60105514526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49956083297729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56722354888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38115119934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5418496131897</t>
+    <t xml:space="preserve">5.17618560791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10852336883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91399335861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60105419158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49956035614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56722402572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38115072250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54185009002686</t>
   </si>
   <si>
     <t xml:space="preserve">4.52493381500244</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61796998977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46572923660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27120018005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14433240890503</t>
+    <t xml:space="preserve">4.61797094345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4657301902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27119922637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14433193206787</t>
   </si>
   <si>
     <t xml:space="preserve">4.22045278549194</t>
@@ -1619,10 +1619,10 @@
     <t xml:space="preserve">4.09358501434326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20353698730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15701866149902</t>
+    <t xml:space="preserve">4.20353651046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15701913833618</t>
   </si>
   <si>
     <t xml:space="preserve">4.39806652069092</t>
@@ -1631,133 +1631,133 @@
     <t xml:space="preserve">4.53339242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59259700775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6095118522644</t>
+    <t xml:space="preserve">4.59259653091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60951232910156</t>
   </si>
   <si>
     <t xml:space="preserve">4.63488578796387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41498136520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49110317230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42343997955322</t>
+    <t xml:space="preserve">4.41498231887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49110269546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42344045639038</t>
   </si>
   <si>
     <t xml:space="preserve">4.43189811706543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29657316207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3388614654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19507932662964</t>
+    <t xml:space="preserve">4.2965726852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33886241912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19507837295532</t>
   </si>
   <si>
     <t xml:space="preserve">4.04706764221191</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08512735366821</t>
+    <t xml:space="preserve">4.08512687683105</t>
   </si>
   <si>
     <t xml:space="preserve">4.10627222061157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15278959274292</t>
+    <t xml:space="preserve">4.15278911590576</t>
   </si>
   <si>
     <t xml:space="preserve">4.2373685836792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21622371673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16124725341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10204267501831</t>
+    <t xml:space="preserve">4.216224193573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16124773025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10204315185547</t>
   </si>
   <si>
     <t xml:space="preserve">4.03860950469971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30503082275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25428438186646</t>
+    <t xml:space="preserve">4.30503034591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2542839050293</t>
   </si>
   <si>
     <t xml:space="preserve">4.14010286331177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05129623413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14856100082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08935546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03438091278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94557332992554</t>
+    <t xml:space="preserve">4.0512957572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14856147766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08935642242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0343804359436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94557356834412</t>
   </si>
   <si>
     <t xml:space="preserve">4.35577774047852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3134880065918</t>
+    <t xml:space="preserve">4.31348896026611</t>
   </si>
   <si>
     <t xml:space="preserve">4.48264503479004</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65180110931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79558420181274</t>
+    <t xml:space="preserve">4.65180158615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79558515548706</t>
   </si>
   <si>
     <t xml:space="preserve">4.7871265411377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82095766067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86324691772461</t>
+    <t xml:space="preserve">4.82095813751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86324739456177</t>
   </si>
   <si>
     <t xml:space="preserve">4.90553617477417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88861989974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95628309249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00703048706055</t>
+    <t xml:space="preserve">4.88862037658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95628213882446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00702953338623</t>
   </si>
   <si>
     <t xml:space="preserve">5.01548719406128</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03240299224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05777740478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99011468887329</t>
+    <t xml:space="preserve">5.03240251541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05777645111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99011373519897</t>
   </si>
   <si>
     <t xml:space="preserve">4.97319889068604</t>
@@ -1766,79 +1766,79 @@
     <t xml:space="preserve">5.20156002044678</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12543869018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15927124023438</t>
+    <t xml:space="preserve">5.12543916702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15927028656006</t>
   </si>
   <si>
     <t xml:space="preserve">5.21847534179688</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34534215927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27767992019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40454816818237</t>
+    <t xml:space="preserve">5.34534311294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27767944335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40454769134521</t>
   </si>
   <si>
     <t xml:space="preserve">5.39608955383301</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47220993041992</t>
+    <t xml:space="preserve">5.47220945358276</t>
   </si>
   <si>
     <t xml:space="preserve">5.49758338928223</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42146253585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41300582885742</t>
+    <t xml:space="preserve">5.42146301269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41300535202026</t>
   </si>
   <si>
     <t xml:space="preserve">4.98165607452393</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11462545394897</t>
+    <t xml:space="preserve">5.11462497711182</t>
   </si>
   <si>
     <t xml:space="preserve">5.13193273544312</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01942920684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01077556610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06270027160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08866262435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0973162651062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14058780670166</t>
+    <t xml:space="preserve">5.01942873001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01077461242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06269931793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08866310119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09731578826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1405873298645</t>
   </si>
   <si>
     <t xml:space="preserve">5.20116710662842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17520475387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2271294593811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26174640655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23578357696533</t>
+    <t xml:space="preserve">5.17520427703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22712993621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26174592971802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23578310012817</t>
   </si>
   <si>
     <t xml:space="preserve">5.25309228897095</t>
@@ -1850,22 +1850,22 @@
     <t xml:space="preserve">5.46079254150391</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54733371734619</t>
+    <t xml:space="preserve">5.54733467102051</t>
   </si>
   <si>
     <t xml:space="preserve">5.42617607116699</t>
   </si>
   <si>
-    <t xml:space="preserve">5.330979347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40886688232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57329654693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52137136459351</t>
+    <t xml:space="preserve">5.33097982406616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40886735916138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57329702377319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52137184143066</t>
   </si>
   <si>
     <t xml:space="preserve">5.47810077667236</t>
@@ -1877,16 +1877,16 @@
     <t xml:space="preserve">5.7636890411377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74638080596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72907161712646</t>
+    <t xml:space="preserve">5.74638175964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72907209396362</t>
   </si>
   <si>
     <t xml:space="preserve">5.65118455886841</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7031102180481</t>
+    <t xml:space="preserve">5.70310974121094</t>
   </si>
   <si>
     <t xml:space="preserve">5.66849374771118</t>
@@ -1895,7 +1895,7 @@
     <t xml:space="preserve">5.59925937652588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49540901184082</t>
+    <t xml:space="preserve">5.49540948867798</t>
   </si>
   <si>
     <t xml:space="preserve">5.45213842391968</t>
@@ -1907,13 +1907,13 @@
     <t xml:space="preserve">5.73772668838501</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51271772384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2444372177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1838583946228</t>
+    <t xml:space="preserve">5.51271724700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24443769454956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18385791778564</t>
   </si>
   <si>
     <t xml:space="preserve">5.28770923614502</t>
@@ -1922,22 +1922,22 @@
     <t xml:space="preserve">5.19251251220703</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1232795715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2704005241394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08000755310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14924144744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16654968261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15789651870728</t>
+    <t xml:space="preserve">5.12327909469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27040004730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08000802993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14924192428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16655015945435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15789604187012</t>
   </si>
   <si>
     <t xml:space="preserve">5.29636287689209</t>
@@ -1946,13 +1946,13 @@
     <t xml:space="preserve">5.53868055343628</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44348430633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48675489425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40021324157715</t>
+    <t xml:space="preserve">5.44348382949829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48675537109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40021276473999</t>
   </si>
   <si>
     <t xml:space="preserve">5.36559677124023</t>
@@ -1973,28 +1973,28 @@
     <t xml:space="preserve">5.16222286224365</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03933334350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10597133636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15270376205444</t>
+    <t xml:space="preserve">5.03933382034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10597085952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15270328521729</t>
   </si>
   <si>
     <t xml:space="preserve">5.20895528793335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27905464172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34569120407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32665252685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27991962432861</t>
+    <t xml:space="preserve">5.27905416488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34569215774536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32665300369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27992010116577</t>
   </si>
   <si>
     <t xml:space="preserve">5.30588293075562</t>
@@ -2009,16 +2009,16 @@
     <t xml:space="preserve">5.21934080123901</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34309530258179</t>
+    <t xml:space="preserve">5.34309482574463</t>
   </si>
   <si>
     <t xml:space="preserve">5.48502397537231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43915700912476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31799793243408</t>
+    <t xml:space="preserve">5.4391565322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31799840927124</t>
   </si>
   <si>
     <t xml:space="preserve">5.51790952682495</t>
@@ -2027,46 +2027,46 @@
     <t xml:space="preserve">5.61656761169434</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51617956161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46252250671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42271375656128</t>
+    <t xml:space="preserve">5.51617908477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46252346038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42271423339844</t>
   </si>
   <si>
     <t xml:space="preserve">5.46771574020386</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44434928894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46944665908813</t>
+    <t xml:space="preserve">5.44434976577759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46944713592529</t>
   </si>
   <si>
     <t xml:space="preserve">5.78099727630615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0233154296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04062271118164</t>
+    <t xml:space="preserve">6.02331495285034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0406231880188</t>
   </si>
   <si>
     <t xml:space="preserve">6.04927730560303</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94456148147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76974678039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78272819519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75416946411133</t>
+    <t xml:space="preserve">5.94456195831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76974725723267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78272867202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75416898727417</t>
   </si>
   <si>
     <t xml:space="preserve">5.74118804931641</t>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">5.81042194366455</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90561723709106</t>
+    <t xml:space="preserve">5.90561771392822</t>
   </si>
   <si>
     <t xml:space="preserve">5.93331098556519</t>
@@ -2087,31 +2087,31 @@
     <t xml:space="preserve">5.94110012054443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91081047058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92638826370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85369205474854</t>
+    <t xml:space="preserve">5.9108099937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92638778686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85369253158569</t>
   </si>
   <si>
     <t xml:space="preserve">5.85628890991211</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68060922622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73253440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81907510757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90648317337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70570659637451</t>
+    <t xml:space="preserve">5.68060874938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73253393173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81907606124878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90648365020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7057056427002</t>
   </si>
   <si>
     <t xml:space="preserve">5.57502746582031</t>
@@ -2120,19 +2120,19 @@
     <t xml:space="preserve">5.75590038299561</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81561422348022</t>
+    <t xml:space="preserve">5.81561374664307</t>
   </si>
   <si>
     <t xml:space="preserve">5.76022720336914</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73513078689575</t>
+    <t xml:space="preserve">5.73512983322144</t>
   </si>
   <si>
     <t xml:space="preserve">5.72041845321655</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69791793823242</t>
+    <t xml:space="preserve">5.69791746139526</t>
   </si>
   <si>
     <t xml:space="preserve">5.69272470474243</t>
@@ -2141,58 +2141,58 @@
     <t xml:space="preserve">5.62868404388428</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75936222076416</t>
+    <t xml:space="preserve">5.759361743927</t>
   </si>
   <si>
     <t xml:space="preserve">5.65810775756836</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57243204116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62522172927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67282009124756</t>
+    <t xml:space="preserve">5.57243156433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62522220611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6728196144104</t>
   </si>
   <si>
     <t xml:space="preserve">5.58195114135742</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58454751968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6451268196106</t>
+    <t xml:space="preserve">5.58454704284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64512634277344</t>
   </si>
   <si>
     <t xml:space="preserve">5.72561073303223</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61483764648438</t>
+    <t xml:space="preserve">5.61483716964722</t>
   </si>
   <si>
     <t xml:space="preserve">5.60704898834229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65291595458984</t>
+    <t xml:space="preserve">5.65291547775269</t>
   </si>
   <si>
     <t xml:space="preserve">5.6555118560791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75503540039062</t>
+    <t xml:space="preserve">5.75503492355347</t>
   </si>
   <si>
     <t xml:space="preserve">5.84071111679077</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00600671768188</t>
+    <t xml:space="preserve">6.00600624084473</t>
   </si>
   <si>
     <t xml:space="preserve">5.92811822891235</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87619304656982</t>
+    <t xml:space="preserve">5.87619352340698</t>
   </si>
   <si>
     <t xml:space="preserve">5.71436071395874</t>
@@ -2204,34 +2204,34 @@
     <t xml:space="preserve">5.36213493347168</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19510889053345</t>
+    <t xml:space="preserve">5.19510936737061</t>
   </si>
   <si>
     <t xml:space="preserve">5.04019927978516</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1544337272644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18039703369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79615068435669</t>
+    <t xml:space="preserve">5.15443420410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18039655685425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79615020751953</t>
   </si>
   <si>
     <t xml:space="preserve">4.24358129501343</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30113124847412</t>
+    <t xml:space="preserve">4.3011302947998</t>
   </si>
   <si>
     <t xml:space="preserve">4.30718946456909</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94501137733459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11073923110962</t>
+    <t xml:space="preserve">3.94501113891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11073970794678</t>
   </si>
   <si>
     <t xml:space="preserve">3.98092603683472</t>
@@ -2246,13 +2246,13 @@
     <t xml:space="preserve">4.17564535140991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8238525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97486877441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07006502151489</t>
+    <t xml:space="preserve">3.82385277748108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9748682975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07006454467773</t>
   </si>
   <si>
     <t xml:space="preserve">4.27387046813965</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">4.11766242980957</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05665063858032</t>
+    <t xml:space="preserve">4.05665111541748</t>
   </si>
   <si>
     <t xml:space="preserve">4.25699520111084</t>
@@ -2273,34 +2273,34 @@
     <t xml:space="preserve">4.37036514282227</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17131853103638</t>
+    <t xml:space="preserve">4.17131900787354</t>
   </si>
   <si>
     <t xml:space="preserve">4.32709360122681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45690727233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6126823425293</t>
+    <t xml:space="preserve">4.45690679550171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61268186569214</t>
   </si>
   <si>
     <t xml:space="preserve">4.48286962509155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6299901008606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56941080093384</t>
+    <t xml:space="preserve">4.62999057769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56941175460815</t>
   </si>
   <si>
     <t xml:space="preserve">4.57806491851807</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5261402130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50017786026001</t>
+    <t xml:space="preserve">4.52614068984985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50017738342285</t>
   </si>
   <si>
     <t xml:space="preserve">4.74249505996704</t>
@@ -2309,19 +2309,19 @@
     <t xml:space="preserve">4.76845788955688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79442024230957</t>
+    <t xml:space="preserve">4.79441976547241</t>
   </si>
   <si>
     <t xml:space="preserve">4.94154119491577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91557836532593</t>
+    <t xml:space="preserve">4.91557884216309</t>
   </si>
   <si>
     <t xml:space="preserve">4.83769130706787</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58671951293945</t>
+    <t xml:space="preserve">4.58671998977661</t>
   </si>
   <si>
     <t xml:space="preserve">4.55210304260254</t>
@@ -2333,22 +2333,22 @@
     <t xml:space="preserve">4.67326164245605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80307483673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90961217880249</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.8030743598938</t>
   </si>
   <si>
+    <t xml:space="preserve">4.90961170196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80307388305664</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.73204898834229</t>
   </si>
   <si>
     <t xml:space="preserve">4.88297748565674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91848993301392</t>
+    <t xml:space="preserve">4.91849040985107</t>
   </si>
   <si>
     <t xml:space="preserve">5.10493087768555</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">5.22034645080566</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19371175765991</t>
+    <t xml:space="preserve">5.19371223449707</t>
   </si>
   <si>
     <t xml:space="preserve">5.39790964126587</t>
@@ -2366,10 +2366,10 @@
     <t xml:space="preserve">5.44230031967163</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3002495765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52220296859741</t>
+    <t xml:space="preserve">5.30025005340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52220344543457</t>
   </si>
   <si>
     <t xml:space="preserve">5.49556922912598</t>
@@ -2378,7 +2378,7 @@
     <t xml:space="preserve">5.60210657119751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72640132904053</t>
+    <t xml:space="preserve">5.72640085220337</t>
   </si>
   <si>
     <t xml:space="preserve">5.81518268585205</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">5.61098527908325</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65537595748901</t>
+    <t xml:space="preserve">5.65537548065186</t>
   </si>
   <si>
     <t xml:space="preserve">5.68201017379761</t>
@@ -2414,13 +2414,13 @@
     <t xml:space="preserve">5.61986303329468</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64649820327759</t>
+    <t xml:space="preserve">5.64649772644043</t>
   </si>
   <si>
     <t xml:space="preserve">5.71752262115479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5843505859375</t>
+    <t xml:space="preserve">5.58435106277466</t>
   </si>
   <si>
     <t xml:space="preserve">5.56659412384033</t>
@@ -2432,13 +2432,13 @@
     <t xml:space="preserve">5.4600567817688</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35351896286011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42454385757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41566610336304</t>
+    <t xml:space="preserve">5.35351943969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42454433441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4156665802002</t>
   </si>
   <si>
     <t xml:space="preserve">5.31800651550293</t>
@@ -2447,16 +2447,16 @@
     <t xml:space="preserve">5.38903141021729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29137182235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21146869659424</t>
+    <t xml:space="preserve">5.29137229919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2114691734314</t>
   </si>
   <si>
     <t xml:space="preserve">5.36239671707153</t>
   </si>
   <si>
-    <t xml:space="preserve">5.255859375</t>
+    <t xml:space="preserve">5.25585985183716</t>
   </si>
   <si>
     <t xml:space="preserve">5.26473760604858</t>
@@ -2465,7 +2465,7 @@
     <t xml:space="preserve">5.37127542495728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48669099807739</t>
+    <t xml:space="preserve">5.48669052124023</t>
   </si>
   <si>
     <t xml:space="preserve">5.59322881698608</t>
@@ -2477,25 +2477,25 @@
     <t xml:space="preserve">5.50444746017456</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38015270233154</t>
+    <t xml:space="preserve">5.3801531791687</t>
   </si>
   <si>
     <t xml:space="preserve">5.34464073181152</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28249359130859</t>
+    <t xml:space="preserve">5.28249311447144</t>
   </si>
   <si>
     <t xml:space="preserve">5.20259046554565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32688474655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33576250076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24698066711426</t>
+    <t xml:space="preserve">5.32688426971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3357629776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24698114395142</t>
   </si>
   <si>
     <t xml:space="preserve">5.15819978713989</t>
@@ -2507,25 +2507,25 @@
     <t xml:space="preserve">5.16707801818848</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1848349571228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02502775192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90073394775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61663341522217</t>
+    <t xml:space="preserve">5.18483448028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02502727508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90073347091675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61663293838501</t>
   </si>
   <si>
     <t xml:space="preserve">4.72317171096802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85634326934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99839401245117</t>
+    <t xml:space="preserve">4.85634279251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99839353561401</t>
   </si>
   <si>
     <t xml:space="preserve">5.00727128982544</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">4.89185619354248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98951530456543</t>
+    <t xml:space="preserve">4.98951482772827</t>
   </si>
   <si>
     <t xml:space="preserve">5.90396404266357</t>
@@ -2552,16 +2552,16 @@
     <t xml:space="preserve">6.09928274154663</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10816144943237</t>
+    <t xml:space="preserve">6.10816097259521</t>
   </si>
   <si>
     <t xml:space="preserve">6.35674858093262</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18806409835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24133348464966</t>
+    <t xml:space="preserve">6.188063621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">6.2857232093811</t>
@@ -2582,7 +2582,7 @@
     <t xml:space="preserve">6.11703872680664</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08152675628662</t>
+    <t xml:space="preserve">6.08152627944946</t>
   </si>
   <si>
     <t xml:space="preserve">6.06377029418945</t>
@@ -2591,13 +2591,13 @@
     <t xml:space="preserve">6.05489206314087</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98386716842651</t>
+    <t xml:space="preserve">5.98386669158936</t>
   </si>
   <si>
     <t xml:space="preserve">5.96611070632935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93947649002075</t>
+    <t xml:space="preserve">5.93947601318359</t>
   </si>
   <si>
     <t xml:space="preserve">5.94835376739502</t>
@@ -2609,25 +2609,25 @@
     <t xml:space="preserve">5.912841796875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23245477676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46328592300415</t>
+    <t xml:space="preserve">6.23245525360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46328639984131</t>
   </si>
   <si>
     <t xml:space="preserve">6.33011436462402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27684545516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20582008361816</t>
+    <t xml:space="preserve">6.27684593200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20581960678101</t>
   </si>
   <si>
     <t xml:space="preserve">6.04601383209229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37450456619263</t>
+    <t xml:space="preserve">6.37450504302979</t>
   </si>
   <si>
     <t xml:space="preserve">6.12591743469238</t>
@@ -2636,16 +2636,16 @@
     <t xml:space="preserve">6.21469879150391</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17918586730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26796770095825</t>
+    <t xml:space="preserve">6.17918634414673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26796722412109</t>
   </si>
   <si>
     <t xml:space="preserve">6.48104333877563</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66748380661011</t>
+    <t xml:space="preserve">6.66748428344727</t>
   </si>
   <si>
     <t xml:space="preserve">7.01373147964478</t>
@@ -2660,19 +2660,19 @@
     <t xml:space="preserve">7.59968900680542</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6352014541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68846940994263</t>
+    <t xml:space="preserve">7.63520193099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68846988677979</t>
   </si>
   <si>
     <t xml:space="preserve">7.52866315841675</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31558799743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30670928955078</t>
+    <t xml:space="preserve">7.31558847427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30670976638794</t>
   </si>
   <si>
     <t xml:space="preserve">7.18241596221924</t>
@@ -2687,19 +2687,19 @@
     <t xml:space="preserve">7.04924392700195</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19129467010498</t>
+    <t xml:space="preserve">7.19129419326782</t>
   </si>
   <si>
     <t xml:space="preserve">7.21792840957642</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3511004447937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4842734336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59080982208252</t>
+    <t xml:space="preserve">7.35110092163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48427295684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59081029891968</t>
   </si>
   <si>
     <t xml:space="preserve">7.58193206787109</t>
@@ -2714,25 +2714,25 @@
     <t xml:space="preserve">7.45763826370239</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17353773117065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61744499206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6795916557312</t>
+    <t xml:space="preserve">7.17353820800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61744546890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67959213256836</t>
   </si>
   <si>
     <t xml:space="preserve">7.76837253570557</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93705892562866</t>
+    <t xml:space="preserve">7.9370584487915</t>
   </si>
   <si>
     <t xml:space="preserve">8.19452381134033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09686470031738</t>
+    <t xml:space="preserve">8.09686374664307</t>
   </si>
   <si>
     <t xml:space="preserve">7.99920463562012</t>
@@ -2741,16 +2741,16 @@
     <t xml:space="preserve">8.17676734924316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20340251922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99032783508301</t>
+    <t xml:space="preserve">8.20340156555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99032735824585</t>
   </si>
   <si>
     <t xml:space="preserve">8.08798599243164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05247211456299</t>
+    <t xml:space="preserve">8.05247402191162</t>
   </si>
   <si>
     <t xml:space="preserve">8.0435962677002</t>
@@ -2762,7 +2762,7 @@
     <t xml:space="preserve">8.07910823822021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14125537872314</t>
+    <t xml:space="preserve">8.14125633239746</t>
   </si>
   <si>
     <t xml:space="preserve">8.07022953033447</t>
@@ -2771,10 +2771,10 @@
     <t xml:space="preserve">8.15013408660889</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38984298706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23891353607178</t>
+    <t xml:space="preserve">8.38984203338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23891448974609</t>
   </si>
   <si>
     <t xml:space="preserve">8.44311237335205</t>
@@ -2783,16 +2783,16 @@
     <t xml:space="preserve">8.3809642791748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51413726806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43423271179199</t>
+    <t xml:space="preserve">8.51413631439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43423366546631</t>
   </si>
   <si>
     <t xml:space="preserve">8.64730834960938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42535591125488</t>
+    <t xml:space="preserve">8.42535495758057</t>
   </si>
   <si>
     <t xml:space="preserve">8.47014427185059</t>
@@ -5019,6 +5019,9 @@
   </si>
   <si>
     <t xml:space="preserve">19.2800006866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3999996185303</t>
   </si>
 </sst>
 </file>
@@ -71605,7 +71608,7 @@
     </row>
     <row r="2549">
       <c r="A2549" s="1" t="n">
-        <v>46035.6910648148</v>
+        <v>46035.3333333333</v>
       </c>
       <c r="B2549" t="n">
         <v>234968</v>
@@ -71626,6 +71629,32 @@
         <v>1668</v>
       </c>
       <c r="H2549" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2550">
+      <c r="A2550" s="1" t="n">
+        <v>46036.6912847222</v>
+      </c>
+      <c r="B2550" t="n">
+        <v>97765</v>
+      </c>
+      <c r="C2550" t="n">
+        <v>19.6399993896484</v>
+      </c>
+      <c r="D2550" t="n">
+        <v>19.2399997711182</v>
+      </c>
+      <c r="E2550" t="n">
+        <v>19.2399997711182</v>
+      </c>
+      <c r="F2550" t="n">
+        <v>19.3999996185303</v>
+      </c>
+      <c r="G2550" t="s">
+        <v>1669</v>
+      </c>
+      <c r="H2550" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CEM.MI.xlsx
+++ b/data/CEM.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70432138442993</t>
+    <t xml:space="preserve">4.70432090759277</t>
   </si>
   <si>
     <t xml:space="preserve">CEM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68036079406738</t>
+    <t xml:space="preserve">4.68036031723022</t>
   </si>
   <si>
     <t xml:space="preserve">4.55656242370605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48867273330688</t>
+    <t xml:space="preserve">4.48867321014404</t>
   </si>
   <si>
     <t xml:space="preserve">4.32893371582031</t>
@@ -62,16 +62,16 @@
     <t xml:space="preserve">4.3249397277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28899955749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29299354553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06136989593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93597555160522</t>
+    <t xml:space="preserve">4.28899908065796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29299259185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06137084960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93597507476807</t>
   </si>
   <si>
     <t xml:space="preserve">3.97431254386902</t>
@@ -80,40 +80,40 @@
     <t xml:space="preserve">3.67560052871704</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83533930778503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94875502586365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88006591796875</t>
+    <t xml:space="preserve">3.83533978462219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94875431060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88006663322449</t>
   </si>
   <si>
     <t xml:space="preserve">3.91680693626404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846875190735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74588513374329</t>
+    <t xml:space="preserve">3.87846922874451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7458860874176</t>
   </si>
   <si>
     <t xml:space="preserve">3.93437814712524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87367653846741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73789882659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57815933227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59892559051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61969184875488</t>
+    <t xml:space="preserve">3.87367749214172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73789834976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57815909385681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59892535209656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61969113349915</t>
   </si>
   <si>
     <t xml:space="preserve">3.3513298034668</t>
@@ -122,217 +122,217 @@
     <t xml:space="preserve">3.15005779266357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25069427490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13088989257812</t>
+    <t xml:space="preserve">3.25069403648376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13088941574097</t>
   </si>
   <si>
     <t xml:space="preserve">3.20916175842285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44238066673279</t>
+    <t xml:space="preserve">3.44238090515137</t>
   </si>
   <si>
     <t xml:space="preserve">3.36251139640808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47592663764954</t>
+    <t xml:space="preserve">3.47592616081238</t>
   </si>
   <si>
     <t xml:space="preserve">3.55419850349426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34653759002686</t>
+    <t xml:space="preserve">3.34653782844543</t>
   </si>
   <si>
     <t xml:space="preserve">3.39126420021057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36730360984802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23951244354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29222583770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40244626998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58614635467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63406801223755</t>
+    <t xml:space="preserve">3.3673038482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23951196670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29222631454468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40244603157043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58614563941956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63406848907471</t>
   </si>
   <si>
     <t xml:space="preserve">3.55579590797424</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64365196228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56058788299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52065324783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4982898235321</t>
+    <t xml:space="preserve">3.64365220069885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56058812141418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52065348625183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49829030036926</t>
   </si>
   <si>
     <t xml:space="preserve">3.52544546127319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54940629005432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75227475166321</t>
+    <t xml:space="preserve">3.54940605163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75227451324463</t>
   </si>
   <si>
     <t xml:space="preserve">3.6133017539978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75387263298035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83214426040649</t>
+    <t xml:space="preserve">3.75387191772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83214497566223</t>
   </si>
   <si>
     <t xml:space="preserve">3.6708083152771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70754861831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6580286026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51745843887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57017278671265</t>
+    <t xml:space="preserve">3.70754790306091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65802884101868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51745867729187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57017254829407</t>
   </si>
   <si>
     <t xml:space="preserve">3.50947117805481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54301619529724</t>
+    <t xml:space="preserve">3.54301643371582</t>
   </si>
   <si>
     <t xml:space="preserve">3.57975649833679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45196509361267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41043305397034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37528991699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60052299499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48551034927368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54461455345154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59573006629944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77943086624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74428868293762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85770297050476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73949527740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74908041954041</t>
+    <t xml:space="preserve">3.45196533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41043329238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37529039382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60052275657654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48551082611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54461407661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5957305431366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77943062782288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74428772926331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85770320892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7394962310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74908018112183</t>
   </si>
   <si>
     <t xml:space="preserve">3.70595049858093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69317150115967</t>
+    <t xml:space="preserve">3.69317173957825</t>
   </si>
   <si>
     <t xml:space="preserve">3.67719769477844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79700231552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66601634025574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70115900039673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62608075141907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67400288581848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64205479621887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53023767471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45835447311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4743287563324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53193736076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62187004089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7575888633728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76085877418518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87531924247742</t>
+    <t xml:space="preserve">3.79700255393982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66601610183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70115876197815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62608122825623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6740026473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64205551147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53023743629456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45835471153259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47432851791382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53193688392639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62187075614929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75758862495422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7608585357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87532019615173</t>
   </si>
   <si>
     <t xml:space="preserve">3.88349556922913</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7772102355957</t>
+    <t xml:space="preserve">3.77720999717712</t>
   </si>
   <si>
     <t xml:space="preserve">3.75431847572327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7052640914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66929006576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59734344482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58426189422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55646419525146</t>
+    <t xml:space="preserve">3.7052628993988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66928958892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5973436832428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58426213264465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55646371841431</t>
   </si>
   <si>
     <t xml:space="preserve">3.38640832901001</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">3.31119108200073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29810976982117</t>
+    <t xml:space="preserve">3.29810929298401</t>
   </si>
   <si>
     <t xml:space="preserve">3.19672989845276</t>
@@ -350,19 +350,19 @@
     <t xml:space="preserve">3.15912127494812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00705170631409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15421628952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0348494052887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22289276123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35206985473633</t>
+    <t xml:space="preserve">3.00705194473267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15421605110168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03484964370728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22289228439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35206961631775</t>
   </si>
   <si>
     <t xml:space="preserve">3.1067967414856</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">2.82881999015808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82064414024353</t>
+    <t xml:space="preserve">2.82064390182495</t>
   </si>
   <si>
     <t xml:space="preserve">2.84026598930359</t>
@@ -383,22 +383,22 @@
     <t xml:space="preserve">3.04302525520325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95799684524536</t>
+    <t xml:space="preserve">2.95799732208252</t>
   </si>
   <si>
     <t xml:space="preserve">2.79611682891846</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76341390609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76831912994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84844183921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87787437438965</t>
+    <t xml:space="preserve">2.76341366767883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76831936836243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84844160079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87787485122681</t>
   </si>
   <si>
     <t xml:space="preserve">3.04139041900635</t>
@@ -407,10 +407,10 @@
     <t xml:space="preserve">3.00051140785217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21144652366638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13295912742615</t>
+    <t xml:space="preserve">3.2114462852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13295888900757</t>
   </si>
   <si>
     <t xml:space="preserve">3.07572841644287</t>
@@ -419,40 +419,40 @@
     <t xml:space="preserve">2.97434878349304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10843133926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9759840965271</t>
+    <t xml:space="preserve">3.1084315776825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97598385810852</t>
   </si>
   <si>
     <t xml:space="preserve">2.92856454849243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17547297477722</t>
+    <t xml:space="preserve">3.1754732131958</t>
   </si>
   <si>
     <t xml:space="preserve">3.18037867546082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15585064888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18855428695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09862065315247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12151312828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02503871917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11660766601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23760890960693</t>
+    <t xml:space="preserve">3.15585088729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18855452537537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09862089157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12151288986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02503895759583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11660742759705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23760914802551</t>
   </si>
   <si>
     <t xml:space="preserve">3.28012275695801</t>
@@ -461,184 +461,184 @@
     <t xml:space="preserve">3.32263708114624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43546295166016</t>
+    <t xml:space="preserve">3.43546271324158</t>
   </si>
   <si>
     <t xml:space="preserve">3.40602970123291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46653079986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43709802627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44854402542114</t>
+    <t xml:space="preserve">3.46653032302856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43709826469421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44854426383972</t>
   </si>
   <si>
     <t xml:space="preserve">3.67910146713257</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64639806747437</t>
+    <t xml:space="preserve">3.64639782905579</t>
   </si>
   <si>
     <t xml:space="preserve">3.71834468841553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69545292854309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74450659751892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85242772102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80827879905701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82299447059631</t>
+    <t xml:space="preserve">3.69545245170593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74450731277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85242748260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80827856063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82299470901489</t>
   </si>
   <si>
     <t xml:space="preserve">3.80337262153625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74287247657776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62350559234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56627535820007</t>
+    <t xml:space="preserve">3.7428719997406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62350630760193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56627583503723</t>
   </si>
   <si>
     <t xml:space="preserve">3.47470664978027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51558589935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65947914123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60551834106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54501843452454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64803314208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64476299285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38804340362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4828827381134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45344948768616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43382716178894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50740957260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56464076042175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55482888221741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56300449371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48451709747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54338335990906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62514066696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59080290794373</t>
+    <t xml:space="preserve">3.51558542251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65947937965393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60551857948303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54501819610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64803290367126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64476275444031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38804316520691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48288249969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45344924926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43382811546326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50741004943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56464052200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55482912063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56300497055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48451781272888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54338240623474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62514114379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59080243110657</t>
   </si>
   <si>
     <t xml:space="preserve">3.64149284362793</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68891191482544</t>
+    <t xml:space="preserve">3.68891167640686</t>
   </si>
   <si>
     <t xml:space="preserve">3.66111445426941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68727707862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53684234619141</t>
+    <t xml:space="preserve">3.68727660179138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53684258460999</t>
   </si>
   <si>
     <t xml:space="preserve">3.63004612922668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63822197914124</t>
+    <t xml:space="preserve">3.63822221755981</t>
   </si>
   <si>
     <t xml:space="preserve">3.43873310089111</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41747570037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41911101341248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33571791648865</t>
+    <t xml:space="preserve">3.41747617721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41911149024963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33571815490723</t>
   </si>
   <si>
     <t xml:space="preserve">3.37169194221497</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27521705627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22125744819641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20981097221375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17710852622986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21308159828186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14767551422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11333727836609</t>
+    <t xml:space="preserve">3.27521777153015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22125720977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2098114490509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1771080493927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21308207511902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14767527580261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11333751678467</t>
   </si>
   <si>
     <t xml:space="preserve">3.00541687011719</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0168628692627</t>
+    <t xml:space="preserve">3.01686310768127</t>
   </si>
   <si>
     <t xml:space="preserve">2.9530918598175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9187536239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96453762054443</t>
+    <t xml:space="preserve">2.91875338554382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96453809738159</t>
   </si>
   <si>
     <t xml:space="preserve">2.96780824661255</t>
@@ -647,52 +647,52 @@
     <t xml:space="preserve">2.95636200904846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04793095588684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17220282554626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18691897392273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31936645507812</t>
+    <t xml:space="preserve">3.04793071746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17220306396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18691921234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3193666934967</t>
   </si>
   <si>
     <t xml:space="preserve">3.2343385219574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45835494995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48778772354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4518141746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49923419952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57281565666199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4501793384552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61369514465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67746591567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58916711807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70362901687622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4861524105072</t>
+    <t xml:space="preserve">3.45835542678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48778748512268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45181488990784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4992344379425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57281637191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45017910003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61369466781616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67746543884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58916759490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70362830162048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48615288734436</t>
   </si>
   <si>
     <t xml:space="preserve">3.33244800567627</t>
@@ -701,58 +701,58 @@
     <t xml:space="preserve">3.28666353225708</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22943329811096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27031230926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24741959571838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23106813430786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2327036857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26213598251343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27685236930847</t>
+    <t xml:space="preserve">3.22943305969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27031207084656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24741983413696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23106789588928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23270320892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26213645935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27685284614563</t>
   </si>
   <si>
     <t xml:space="preserve">3.23597383499146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00122690200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04701137542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12876844406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16964769363403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17782354354858</t>
+    <t xml:space="preserve">4.00122785568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04701089859009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12876892089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16964817047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17782402038574</t>
   </si>
   <si>
     <t xml:space="preserve">4.06336307525635</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95707702636719</t>
+    <t xml:space="preserve">3.95707774162292</t>
   </si>
   <si>
     <t xml:space="preserve">4.19417572021484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28410863876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34542751312256</t>
+    <t xml:space="preserve">4.28410816192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3454270362854</t>
   </si>
   <si>
     <t xml:space="preserve">4.47215175628662</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">4.43944883346558</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41083383560181</t>
+    <t xml:space="preserve">4.41083335876465</t>
   </si>
   <si>
     <t xml:space="preserve">4.41492128372192</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">4.37404251098633</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26775741577148</t>
+    <t xml:space="preserve">4.26775693893433</t>
   </si>
   <si>
     <t xml:space="preserve">4.39039421081543</t>
@@ -779,16 +779,16 @@
     <t xml:space="preserve">4.3617787361145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37812995910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.386305809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56208562850952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42718458175659</t>
+    <t xml:space="preserve">4.3781304359436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38630628585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56208515167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42718410491943</t>
   </si>
   <si>
     <t xml:space="preserve">4.3290753364563</t>
@@ -803,43 +803,43 @@
     <t xml:space="preserve">4.30046033859253</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34951496124268</t>
+    <t xml:space="preserve">4.34951543807983</t>
   </si>
   <si>
     <t xml:space="preserve">4.24322986602783</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24731826782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21052598953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1451210975647</t>
+    <t xml:space="preserve">4.24731874465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21052694320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14512014389038</t>
   </si>
   <si>
     <t xml:space="preserve">4.10424089431763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22279071807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40674543380737</t>
+    <t xml:space="preserve">4.22279119491577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40674448013306</t>
   </si>
   <si>
     <t xml:space="preserve">4.36586666107178</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27593278884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30454778671265</t>
+    <t xml:space="preserve">4.27593231201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3045482635498</t>
   </si>
   <si>
     <t xml:space="preserve">4.28002119064331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44762420654297</t>
+    <t xml:space="preserve">4.44762516021729</t>
   </si>
   <si>
     <t xml:space="preserve">4.52938222885132</t>
@@ -863,76 +863,76 @@
     <t xml:space="preserve">4.73377656936646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81962299346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81144666671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65201807022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34133863449097</t>
+    <t xml:space="preserve">4.81962251663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81144714355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65201902389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34133958816528</t>
   </si>
   <si>
     <t xml:space="preserve">4.33725118637085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25958156585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40383434295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44966411590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41633415222168</t>
+    <t xml:space="preserve">4.25958108901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4038348197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44966506958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41633367538452</t>
   </si>
   <si>
     <t xml:space="preserve">4.37466955184937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36633682250977</t>
+    <t xml:space="preserve">4.36633729934692</t>
   </si>
   <si>
     <t xml:space="preserve">4.30384206771851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27467775344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25801181793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31634140014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26634502410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20801639556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33300638198853</t>
+    <t xml:space="preserve">4.27467823028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25801229476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31634092330933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26634550094604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20801591873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33300685882568</t>
   </si>
   <si>
     <t xml:space="preserve">4.37050342559814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34550619125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39133596420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29967594146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4288330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39966869354248</t>
+    <t xml:space="preserve">4.3455057144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39133548736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29967546463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42883253097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39966821670532</t>
   </si>
   <si>
     <t xml:space="preserve">4.3955020904541</t>
@@ -941,22 +941,22 @@
     <t xml:space="preserve">4.38300275802612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46633005142212</t>
+    <t xml:space="preserve">4.46632957458496</t>
   </si>
   <si>
     <t xml:space="preserve">4.48299503326416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56632137298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40800046920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34967184066772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69131374359131</t>
+    <t xml:space="preserve">4.56632280349731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40800094604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34967231750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69131278991699</t>
   </si>
   <si>
     <t xml:space="preserve">4.58298826217651</t>
@@ -965,19 +965,19 @@
     <t xml:space="preserve">4.85380029678345</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99962329864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0579514503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10794830322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24960374832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28710174560547</t>
+    <t xml:space="preserve">4.99962282180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05795192718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1079478263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24960422515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28710126876831</t>
   </si>
   <si>
     <t xml:space="preserve">5.25376987457275</t>
@@ -986,28 +986,28 @@
     <t xml:space="preserve">5.41625833511353</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30376672744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29960060119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34542989730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30793285369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22877311706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29126739501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29543399810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16211080551147</t>
+    <t xml:space="preserve">5.30376625061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29960012435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34543037414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30793237686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22877216339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29126787185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29543352127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16211128234863</t>
   </si>
   <si>
     <t xml:space="preserve">5.01628875732422</t>
@@ -1016,13 +1016,13 @@
     <t xml:space="preserve">5.05378580093384</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1246132850647</t>
+    <t xml:space="preserve">5.12461376190186</t>
   </si>
   <si>
     <t xml:space="preserve">5.20377445220947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07461786270142</t>
+    <t xml:space="preserve">5.07461738586426</t>
   </si>
   <si>
     <t xml:space="preserve">5.03295373916626</t>
@@ -1037,22 +1037,22 @@
     <t xml:space="preserve">4.96212530136108</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90796327590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94129419326782</t>
+    <t xml:space="preserve">4.90796279907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94129371643066</t>
   </si>
   <si>
     <t xml:space="preserve">4.89129734039307</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90379619598389</t>
+    <t xml:space="preserve">4.9037971496582</t>
   </si>
   <si>
     <t xml:space="preserve">4.9537935256958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94545984268188</t>
+    <t xml:space="preserve">4.9454607963562</t>
   </si>
   <si>
     <t xml:space="preserve">4.91629552841187</t>
@@ -1061,19 +1061,19 @@
     <t xml:space="preserve">5.02462100982666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04961967468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1162805557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17460918426514</t>
+    <t xml:space="preserve">5.0496187210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11628103256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17460966110229</t>
   </si>
   <si>
     <t xml:space="preserve">5.23293876647949</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17877578735352</t>
+    <t xml:space="preserve">5.17877674102783</t>
   </si>
   <si>
     <t xml:space="preserve">5.1329460144043</t>
@@ -1082,7 +1082,7 @@
     <t xml:space="preserve">5.33293056488037</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26627016067505</t>
+    <t xml:space="preserve">5.26626968383789</t>
   </si>
   <si>
     <t xml:space="preserve">5.22460603713989</t>
@@ -1094,31 +1094,31 @@
     <t xml:space="preserve">5.68707132339478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00371360778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80789470672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07454109191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01621341705322</t>
+    <t xml:space="preserve">6.0037145614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80789566040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0745415687561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01621294021606</t>
   </si>
   <si>
     <t xml:space="preserve">6.1662015914917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89122247695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94121837615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96621608734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03287792205811</t>
+    <t xml:space="preserve">5.89122295379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94121885299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96621704101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03287839889526</t>
   </si>
   <si>
     <t xml:space="preserve">5.99538135528564</t>
@@ -1127,19 +1127,19 @@
     <t xml:space="preserve">5.97038316726685</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91622066497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86205863952637</t>
+    <t xml:space="preserve">5.91622018814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86205768585205</t>
   </si>
   <si>
     <t xml:space="preserve">5.92871904373169</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89955568313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90372085571289</t>
+    <t xml:space="preserve">5.89955520629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90372133255005</t>
   </si>
   <si>
     <t xml:space="preserve">5.87455701828003</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">5.84539222717285</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00788068771362</t>
+    <t xml:space="preserve">6.00788021087646</t>
   </si>
   <si>
     <t xml:space="preserve">5.98288154602051</t>
@@ -1157,94 +1157,94 @@
     <t xml:space="preserve">6.03704452514648</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09120798110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02871227264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99954700469971</t>
+    <t xml:space="preserve">6.0912070274353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0287127494812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99954652786255</t>
   </si>
   <si>
     <t xml:space="preserve">6.04954385757446</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07870817184448</t>
+    <t xml:space="preserve">6.0787091255188</t>
   </si>
   <si>
     <t xml:space="preserve">6.29119253158569</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1745343208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19953298568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08287477493286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24536323547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21203136444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02454566955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09954023361206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1828670501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20786571502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22036409378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14536952972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95788431167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94538545608521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01204633712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02037906646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11620569229126</t>
+    <t xml:space="preserve">6.17453384399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1995325088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0828742980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24536180496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21203184127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02454614639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0995397567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18286657333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20786476135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22036457061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14537000656128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95788383483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94538497924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.012047290802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02037954330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1162052154541</t>
   </si>
   <si>
     <t xml:space="preserve">6.06204271316528</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04121112823486</t>
+    <t xml:space="preserve">6.04121065139771</t>
   </si>
   <si>
     <t xml:space="preserve">6.14953660964966</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09537315368652</t>
+    <t xml:space="preserve">6.095374584198</t>
   </si>
   <si>
     <t xml:space="preserve">6.35785436630249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22452974319458</t>
+    <t xml:space="preserve">6.2245306968689</t>
   </si>
   <si>
     <t xml:space="preserve">6.28285980224609</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58283710479736</t>
+    <t xml:space="preserve">6.58283662796021</t>
   </si>
   <si>
     <t xml:space="preserve">6.6161675453186</t>
@@ -1253,7 +1253,7 @@
     <t xml:space="preserve">6.57450389862061</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50784301757812</t>
+    <t xml:space="preserve">6.50784206390381</t>
   </si>
   <si>
     <t xml:space="preserve">6.49950981140137</t>
@@ -1262,46 +1262,46 @@
     <t xml:space="preserve">6.65783071517944</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74115896224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59116983413696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62449979782104</t>
+    <t xml:space="preserve">6.74115800857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5911693572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6245002746582</t>
   </si>
   <si>
     <t xml:space="preserve">6.6328330039978</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7078275680542</t>
+    <t xml:space="preserve">6.70782804489136</t>
   </si>
   <si>
     <t xml:space="preserve">6.52450752258301</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51617574691772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66616439819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54950618743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44951295852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29952478408813</t>
+    <t xml:space="preserve">6.51617479324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66616344451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54950666427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44951343536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29952573776245</t>
   </si>
   <si>
     <t xml:space="preserve">6.2328634262085</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90788745880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93288612365723</t>
+    <t xml:space="preserve">5.90788793563843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93288564682007</t>
   </si>
   <si>
     <t xml:space="preserve">6.53284072875977</t>
@@ -1313,28 +1313,28 @@
     <t xml:space="preserve">6.36618661880493</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33285570144653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1412034034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15786838531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06620931625366</t>
+    <t xml:space="preserve">6.33285522460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14120388031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1578688621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0662088394165</t>
   </si>
   <si>
     <t xml:space="preserve">5.94955110549927</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1328706741333</t>
+    <t xml:space="preserve">6.13287115097046</t>
   </si>
   <si>
     <t xml:space="preserve">6.0578761100769</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88288879394531</t>
+    <t xml:space="preserve">5.88289022445679</t>
   </si>
   <si>
     <t xml:space="preserve">5.84955883026123</t>
@@ -1343,13 +1343,13 @@
     <t xml:space="preserve">5.81622838973999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72456836700439</t>
+    <t xml:space="preserve">5.72456789016724</t>
   </si>
   <si>
     <t xml:space="preserve">5.75789880752563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76623201370239</t>
+    <t xml:space="preserve">5.76623153686523</t>
   </si>
   <si>
     <t xml:space="preserve">5.68290519714355</t>
@@ -1358,88 +1358,88 @@
     <t xml:space="preserve">5.82456064224243</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86622381210327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77456426620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78289747238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79122924804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6329083442688</t>
+    <t xml:space="preserve">5.86622428894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77456378936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78289651870728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79122972488403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63290929794312</t>
   </si>
   <si>
     <t xml:space="preserve">5.64982414245605</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68365478515625</t>
+    <t xml:space="preserve">5.68365573883057</t>
   </si>
   <si>
     <t xml:space="preserve">5.66673946380615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70057058334351</t>
+    <t xml:space="preserve">5.70057106018066</t>
   </si>
   <si>
     <t xml:space="preserve">5.48066854476929</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45529460906982</t>
+    <t xml:space="preserve">5.45529365539551</t>
   </si>
   <si>
     <t xml:space="preserve">5.54833078384399</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53987264633179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74285984039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58216190338135</t>
+    <t xml:space="preserve">5.53987312316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74286031723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58216142654419</t>
   </si>
   <si>
     <t xml:space="preserve">5.65828227996826</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70902919769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77669095993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91201591491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9035587310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89510011672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75131750106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78514909744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71748685836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81052255630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56524610519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50604104995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69211339950562</t>
+    <t xml:space="preserve">5.70902872085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77669143676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91201639175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90355825424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89510107040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75131845474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78514957427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71748733520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81052303314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56524658203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50604200363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69211292266846</t>
   </si>
   <si>
     <t xml:space="preserve">5.72594451904297</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">5.73440265655518</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60753536224365</t>
+    <t xml:space="preserve">5.60753583908081</t>
   </si>
   <si>
     <t xml:space="preserve">5.51449918746948</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">5.67519807815552</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01351022720337</t>
+    <t xml:space="preserve">6.01351070404053</t>
   </si>
   <si>
     <t xml:space="preserve">5.99659490585327</t>
@@ -1469,64 +1469,64 @@
     <t xml:space="preserve">5.75977563858032</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80206489562988</t>
+    <t xml:space="preserve">5.80206537246704</t>
   </si>
   <si>
     <t xml:space="preserve">5.79360723495483</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88664388656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87818479537964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92893266677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85281229019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76823377609253</t>
+    <t xml:space="preserve">5.88664293289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8781852722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92893218994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85281133651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76823425292969</t>
   </si>
   <si>
     <t xml:space="preserve">5.82743835449219</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83589649200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42992067337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38763189315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33688497543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26076459884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.303053855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43837928771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46375274658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44683599472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35379981994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3707160949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22693300247192</t>
+    <t xml:space="preserve">5.83589601516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42992115020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3876314163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33688449859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26076364517212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30305337905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43837881088257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46375226974487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44683694839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35380029678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37071657180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22693252563477</t>
   </si>
   <si>
     <t xml:space="preserve">5.14235496520996</t>
@@ -1535,16 +1535,16 @@
     <t xml:space="preserve">5.11698198318481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24384880065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13389730453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26922273635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25230646133423</t>
+    <t xml:space="preserve">5.24384832382202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13389778137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26922225952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25230693817139</t>
   </si>
   <si>
     <t xml:space="preserve">5.21001768112183</t>
@@ -1553,34 +1553,34 @@
     <t xml:space="preserve">5.23539066314697</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2861385345459</t>
+    <t xml:space="preserve">5.28613758087158</t>
   </si>
   <si>
     <t xml:space="preserve">5.31996917724609</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29459619522095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48912572860718</t>
+    <t xml:space="preserve">5.29459571838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48912620544434</t>
   </si>
   <si>
     <t xml:space="preserve">5.3284273147583</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16772937774658</t>
+    <t xml:space="preserve">5.16772890090942</t>
   </si>
   <si>
     <t xml:space="preserve">5.09160852432251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17618608474731</t>
+    <t xml:space="preserve">5.17618656158447</t>
   </si>
   <si>
     <t xml:space="preserve">5.10852384567261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91399383544922</t>
+    <t xml:space="preserve">4.91399335861206</t>
   </si>
   <si>
     <t xml:space="preserve">4.60105419158936</t>
@@ -1589,19 +1589,19 @@
     <t xml:space="preserve">4.49956083297729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.567223072052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38115072250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54184913635254</t>
+    <t xml:space="preserve">4.56722354888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38115119934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54185009002686</t>
   </si>
   <si>
     <t xml:space="preserve">4.5249342918396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61796998977661</t>
+    <t xml:space="preserve">4.61797094345093</t>
   </si>
   <si>
     <t xml:space="preserve">4.46572971343994</t>
@@ -1610,94 +1610,94 @@
     <t xml:space="preserve">4.27119970321655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14433193206787</t>
+    <t xml:space="preserve">4.14433240890503</t>
   </si>
   <si>
     <t xml:space="preserve">4.22045230865479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09358549118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20353746414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15701913833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39806652069092</t>
+    <t xml:space="preserve">4.09358501434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20353698730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15701866149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39806699752808</t>
   </si>
   <si>
     <t xml:space="preserve">4.53339195251465</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59259653091431</t>
+    <t xml:space="preserve">4.59259700775146</t>
   </si>
   <si>
     <t xml:space="preserve">4.60951232910156</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63488483428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41498184204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49110221862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42343997955322</t>
+    <t xml:space="preserve">4.63488578796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41498231887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49110269546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42344045639038</t>
   </si>
   <si>
     <t xml:space="preserve">4.43189764022827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2965726852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33886241912842</t>
+    <t xml:space="preserve">4.29657316207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33886194229126</t>
   </si>
   <si>
     <t xml:space="preserve">4.19507932662964</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04706716537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08512735366821</t>
+    <t xml:space="preserve">4.04706764221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08512687683105</t>
   </si>
   <si>
     <t xml:space="preserve">4.10627222061157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15279006958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23736810684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21622323989868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16124773025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10204267501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03860902786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30503129959106</t>
+    <t xml:space="preserve">4.15278911590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23736906051636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21622371673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16124820709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10204315185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03860950469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30503082275391</t>
   </si>
   <si>
     <t xml:space="preserve">4.25428438186646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14010334014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05129671096802</t>
+    <t xml:space="preserve">4.14010286331177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05129623413086</t>
   </si>
   <si>
     <t xml:space="preserve">4.14856100082397</t>
@@ -1706,19 +1706,19 @@
     <t xml:space="preserve">4.08935594558716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0343804359436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94557309150696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35577774047852</t>
+    <t xml:space="preserve">4.03437995910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9455738067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35577821731567</t>
   </si>
   <si>
     <t xml:space="preserve">4.31348848342896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4826455116272</t>
+    <t xml:space="preserve">4.48264503479004</t>
   </si>
   <si>
     <t xml:space="preserve">4.65180110931396</t>
@@ -1727,10 +1727,10 @@
     <t xml:space="preserve">4.79558420181274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78712606430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82095766067505</t>
+    <t xml:space="preserve">4.78712558746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82095718383789</t>
   </si>
   <si>
     <t xml:space="preserve">4.86324691772461</t>
@@ -1739,22 +1739,22 @@
     <t xml:space="preserve">4.90553569793701</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88862085342407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95628309249878</t>
+    <t xml:space="preserve">4.88861989974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95628213882446</t>
   </si>
   <si>
     <t xml:space="preserve">5.00703001022339</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0154881477356</t>
+    <t xml:space="preserve">5.01548719406128</t>
   </si>
   <si>
     <t xml:space="preserve">5.03240299224854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05777645111084</t>
+    <t xml:space="preserve">5.057776927948</t>
   </si>
   <si>
     <t xml:space="preserve">4.99011421203613</t>
@@ -1763,34 +1763,34 @@
     <t xml:space="preserve">4.97319841384888</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20156002044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12543964385986</t>
+    <t xml:space="preserve">5.20156049728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12543916702271</t>
   </si>
   <si>
     <t xml:space="preserve">5.15927076339722</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21847534179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34534311294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27768039703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40454816818237</t>
+    <t xml:space="preserve">5.21847486495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3453426361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27767944335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4045467376709</t>
   </si>
   <si>
     <t xml:space="preserve">5.39609003067017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47220945358276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49758386611938</t>
+    <t xml:space="preserve">5.47220897674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49758338928223</t>
   </si>
   <si>
     <t xml:space="preserve">5.42146348953247</t>
@@ -1802,34 +1802,34 @@
     <t xml:space="preserve">4.98165655136108</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11462497711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13193368911743</t>
+    <t xml:space="preserve">5.11462545394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13193273544312</t>
   </si>
   <si>
     <t xml:space="preserve">5.01942873001099</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01077508926392</t>
+    <t xml:space="preserve">5.01077556610107</t>
   </si>
   <si>
     <t xml:space="preserve">5.06269979476929</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08866262435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09731674194336</t>
+    <t xml:space="preserve">5.08866214752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09731721878052</t>
   </si>
   <si>
     <t xml:space="preserve">5.1405873298645</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20116710662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17520380020142</t>
+    <t xml:space="preserve">5.20116758346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17520475387573</t>
   </si>
   <si>
     <t xml:space="preserve">5.2271294593811</t>
@@ -1841,31 +1841,31 @@
     <t xml:space="preserve">5.23578357696533</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25309181213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33963394165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46079254150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54733467102051</t>
+    <t xml:space="preserve">5.25309228897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33963441848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46079206466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54733419418335</t>
   </si>
   <si>
     <t xml:space="preserve">5.42617607116699</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33097982406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40886783599854</t>
+    <t xml:space="preserve">5.330979347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40886688232422</t>
   </si>
   <si>
     <t xml:space="preserve">5.57329654693604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52137231826782</t>
+    <t xml:space="preserve">5.52137184143066</t>
   </si>
   <si>
     <t xml:space="preserve">5.47810029983521</t>
@@ -1874,25 +1874,25 @@
     <t xml:space="preserve">5.64253044128418</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76368856430054</t>
+    <t xml:space="preserve">5.7636890411377</t>
   </si>
   <si>
     <t xml:space="preserve">5.74638080596924</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72907257080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65118503570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7031102180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66849279403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59925889968872</t>
+    <t xml:space="preserve">5.72907209396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65118455886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70310974121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66849422454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59925937652588</t>
   </si>
   <si>
     <t xml:space="preserve">5.49540948867798</t>
@@ -1904,25 +1904,25 @@
     <t xml:space="preserve">5.56464290618896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73772668838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51271724700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24443817138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18385791778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28770923614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19251298904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12327909469604</t>
+    <t xml:space="preserve">5.73772621154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51271772384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24443769454956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1838583946228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28770875930786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19251203536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1232795715332</t>
   </si>
   <si>
     <t xml:space="preserve">5.2704005241394</t>
@@ -1934,10 +1934,10 @@
     <t xml:space="preserve">5.14924144744873</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16655015945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15789556503296</t>
+    <t xml:space="preserve">5.16654968261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15789604187012</t>
   </si>
   <si>
     <t xml:space="preserve">5.29636287689209</t>
@@ -1946,19 +1946,19 @@
     <t xml:space="preserve">5.53867959976196</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44348430633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48675537109375</t>
+    <t xml:space="preserve">5.44348478317261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48675489425659</t>
   </si>
   <si>
     <t xml:space="preserve">5.40021324157715</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36559677124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32232570648193</t>
+    <t xml:space="preserve">5.36559629440308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32232522964478</t>
   </si>
   <si>
     <t xml:space="preserve">5.38290452957153</t>
@@ -1967,55 +1967,55 @@
     <t xml:space="preserve">5.02808284759521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04539155960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16222381591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03933334350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10597038269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15270328521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20895528793335</t>
+    <t xml:space="preserve">5.04539108276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16222333908081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03933382034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10597085952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15270280838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20895576477051</t>
   </si>
   <si>
     <t xml:space="preserve">5.27905464172363</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34569215774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32665300369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27991962432861</t>
+    <t xml:space="preserve">5.3456916809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32665252685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27992010116577</t>
   </si>
   <si>
     <t xml:space="preserve">5.30588245391846</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26780462265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34742212295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21934127807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34309577941895</t>
+    <t xml:space="preserve">5.26780414581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34742259979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21934032440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34309530258179</t>
   </si>
   <si>
     <t xml:space="preserve">5.48502397537231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4391565322876</t>
+    <t xml:space="preserve">5.43915700912476</t>
   </si>
   <si>
     <t xml:space="preserve">5.31799840927124</t>
@@ -2024,13 +2024,13 @@
     <t xml:space="preserve">5.51791000366211</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61656761169434</t>
+    <t xml:space="preserve">5.61656808853149</t>
   </si>
   <si>
     <t xml:space="preserve">5.51617956161499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46252346038818</t>
+    <t xml:space="preserve">5.46252250671387</t>
   </si>
   <si>
     <t xml:space="preserve">5.42271423339844</t>
@@ -2045,10 +2045,10 @@
     <t xml:space="preserve">5.46944713592529</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78099775314331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0233154296875</t>
+    <t xml:space="preserve">5.78099679946899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02331495285034</t>
   </si>
   <si>
     <t xml:space="preserve">6.0406231880188</t>
@@ -2057,7 +2057,7 @@
     <t xml:space="preserve">6.04927682876587</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94456148147583</t>
+    <t xml:space="preserve">5.94456195831299</t>
   </si>
   <si>
     <t xml:space="preserve">5.76974678039551</t>
@@ -2066,19 +2066,19 @@
     <t xml:space="preserve">5.78272867202759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75416994094849</t>
+    <t xml:space="preserve">5.75416946411133</t>
   </si>
   <si>
     <t xml:space="preserve">5.74118804931641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73945760726929</t>
+    <t xml:space="preserve">5.73945713043213</t>
   </si>
   <si>
     <t xml:space="preserve">5.81042146682739</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90561771392822</t>
+    <t xml:space="preserve">5.90561723709106</t>
   </si>
   <si>
     <t xml:space="preserve">5.93331146240234</t>
@@ -2087,25 +2087,25 @@
     <t xml:space="preserve">5.94109964370728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9108099937439</t>
+    <t xml:space="preserve">5.91081047058105</t>
   </si>
   <si>
     <t xml:space="preserve">5.92638778686523</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85369300842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85628938674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68060922622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73253440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81907606124878</t>
+    <t xml:space="preserve">5.85369253158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85628890991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68060970306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73253393173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81907558441162</t>
   </si>
   <si>
     <t xml:space="preserve">5.90648317337036</t>
@@ -2114,13 +2114,13 @@
     <t xml:space="preserve">5.70570611953735</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57502794265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75590085983276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81561374664307</t>
+    <t xml:space="preserve">5.57502746582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75590038299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81561422348022</t>
   </si>
   <si>
     <t xml:space="preserve">5.7602276802063</t>
@@ -2129,13 +2129,13 @@
     <t xml:space="preserve">5.73513031005859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72041749954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69791746139526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69272518157959</t>
+    <t xml:space="preserve">5.72041845321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69791793823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69272422790527</t>
   </si>
   <si>
     <t xml:space="preserve">5.62868404388428</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">5.57243204116821</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62522268295288</t>
+    <t xml:space="preserve">5.62522172927856</t>
   </si>
   <si>
     <t xml:space="preserve">5.67282009124756</t>
@@ -2165,103 +2165,103 @@
     <t xml:space="preserve">5.64512634277344</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72561120986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61483716964722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60704851150513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65291547775269</t>
+    <t xml:space="preserve">5.72561073303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61483764648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60704803466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65291595458984</t>
   </si>
   <si>
     <t xml:space="preserve">5.65551137924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75503444671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84071111679077</t>
+    <t xml:space="preserve">5.75503540039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84071159362793</t>
   </si>
   <si>
     <t xml:space="preserve">6.00600624084473</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92811870574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87619304656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71436071395874</t>
+    <t xml:space="preserve">5.92811822891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87619352340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71436023712158</t>
   </si>
   <si>
     <t xml:space="preserve">5.4218487739563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36213445663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19510889053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.040198802948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15443420410156</t>
+    <t xml:space="preserve">5.36213493347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19510841369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04019927978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1544337272644</t>
   </si>
   <si>
     <t xml:space="preserve">5.18039703369141</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79615020751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24358034133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30113172531128</t>
+    <t xml:space="preserve">4.79615068435669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24358081817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30113124847412</t>
   </si>
   <si>
     <t xml:space="preserve">4.30718946456909</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94501113891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11073970794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9809262752533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77452349662781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89438486099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17564582824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82385277748108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97486805915833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07006454467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27387094497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11766290664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05665016174316</t>
+    <t xml:space="preserve">3.94501137733459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11073923110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98092651367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77452397346497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89438462257385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17564535140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82385301589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9748682975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07006502151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27387046813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11766242980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05665063858032</t>
   </si>
   <si>
     <t xml:space="preserve">4.256995677948</t>
@@ -2270,31 +2270,31 @@
     <t xml:space="preserve">4.30978584289551</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37036514282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17131900787354</t>
+    <t xml:space="preserve">4.37036466598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17131853103638</t>
   </si>
   <si>
     <t xml:space="preserve">4.32709360122681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45690631866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61268138885498</t>
+    <t xml:space="preserve">4.45690727233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6126823425293</t>
   </si>
   <si>
     <t xml:space="preserve">4.48286914825439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62999105453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56941175460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57806491851807</t>
+    <t xml:space="preserve">4.62999057769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56941080093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57806587219238</t>
   </si>
   <si>
     <t xml:space="preserve">4.5261402130127</t>
@@ -2303,25 +2303,25 @@
     <t xml:space="preserve">4.50017738342285</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74249410629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76845741271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79441976547241</t>
+    <t xml:space="preserve">4.74249505996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76845788955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79442024230957</t>
   </si>
   <si>
     <t xml:space="preserve">4.94154119491577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91557884216309</t>
+    <t xml:space="preserve">4.91557836532593</t>
   </si>
   <si>
     <t xml:space="preserve">4.83769083023071</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58671998977661</t>
+    <t xml:space="preserve">4.58671951293945</t>
   </si>
   <si>
     <t xml:space="preserve">4.55210304260254</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">4.62133646011353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67326164245605</t>
+    <t xml:space="preserve">4.67326068878174</t>
   </si>
   <si>
     <t xml:space="preserve">4.8030743598938</t>
@@ -2339,10 +2339,10 @@
     <t xml:space="preserve">4.90961217880249</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73204851150513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88297748565674</t>
+    <t xml:space="preserve">4.73204898834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88297700881958</t>
   </si>
   <si>
     <t xml:space="preserve">4.91848993301392</t>
@@ -2351,10 +2351,10 @@
     <t xml:space="preserve">5.10493087768555</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22034692764282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19371223449707</t>
+    <t xml:space="preserve">5.22034645080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19371175765991</t>
   </si>
   <si>
     <t xml:space="preserve">5.39790964126587</t>
@@ -2363,31 +2363,31 @@
     <t xml:space="preserve">5.44230031967163</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30025005340576</t>
+    <t xml:space="preserve">5.3002495765686</t>
   </si>
   <si>
     <t xml:space="preserve">5.52220344543457</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49556875228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60210704803467</t>
+    <t xml:space="preserve">5.49556922912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60210657119751</t>
   </si>
   <si>
     <t xml:space="preserve">5.72640085220337</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81518220901489</t>
+    <t xml:space="preserve">5.81518316268921</t>
   </si>
   <si>
     <t xml:space="preserve">5.63761949539185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30912780761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27361536026001</t>
+    <t xml:space="preserve">5.3091287612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27361583709717</t>
   </si>
   <si>
     <t xml:space="preserve">5.23810291290283</t>
@@ -2399,10 +2399,10 @@
     <t xml:space="preserve">5.73527956008911</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61098527908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65537548065186</t>
+    <t xml:space="preserve">5.61098575592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65537595748901</t>
   </si>
   <si>
     <t xml:space="preserve">5.68200969696045</t>
@@ -2411,19 +2411,19 @@
     <t xml:space="preserve">5.61986255645752</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64649772644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71752214431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5843505859375</t>
+    <t xml:space="preserve">5.64649820327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71752262115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58435106277466</t>
   </si>
   <si>
     <t xml:space="preserve">5.56659460067749</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53108215332031</t>
+    <t xml:space="preserve">5.53108167648315</t>
   </si>
   <si>
     <t xml:space="preserve">5.4600567817688</t>
@@ -2432,13 +2432,13 @@
     <t xml:space="preserve">5.35351896286011</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42454481124878</t>
+    <t xml:space="preserve">5.42454385757446</t>
   </si>
   <si>
     <t xml:space="preserve">5.41566610336304</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31800603866577</t>
+    <t xml:space="preserve">5.31800651550293</t>
   </si>
   <si>
     <t xml:space="preserve">5.38903141021729</t>
@@ -2453,10 +2453,10 @@
     <t xml:space="preserve">5.36239719390869</t>
   </si>
   <si>
-    <t xml:space="preserve">5.255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26473808288574</t>
+    <t xml:space="preserve">5.25585985183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26473712921143</t>
   </si>
   <si>
     <t xml:space="preserve">5.37127542495728</t>
@@ -2471,13 +2471,13 @@
     <t xml:space="preserve">5.53995990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50444746017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38015365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34464120864868</t>
+    <t xml:space="preserve">5.5044469833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3801531791687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34464073181152</t>
   </si>
   <si>
     <t xml:space="preserve">5.28249359130859</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">5.20259094238281</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32688474655151</t>
+    <t xml:space="preserve">5.32688426971436</t>
   </si>
   <si>
     <t xml:space="preserve">5.3357629776001</t>
@@ -2498,19 +2498,19 @@
     <t xml:space="preserve">5.15819978713989</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13156604766846</t>
+    <t xml:space="preserve">5.1315655708313</t>
   </si>
   <si>
     <t xml:space="preserve">5.16707849502563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18483400344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02502727508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90073347091675</t>
+    <t xml:space="preserve">5.1848349571228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02502775192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90073394775391</t>
   </si>
   <si>
     <t xml:space="preserve">4.61663293838501</t>
@@ -2522,25 +2522,25 @@
     <t xml:space="preserve">4.85634279251099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99839401245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0072717666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89185571670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98951482772827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90396308898926</t>
+    <t xml:space="preserve">4.99839353561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00727128982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89185619354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98951530456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90396404266357</t>
   </si>
   <si>
     <t xml:space="preserve">6.01050138473511</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01938009262085</t>
+    <t xml:space="preserve">6.01937961578369</t>
   </si>
   <si>
     <t xml:space="preserve">5.9927453994751</t>
@@ -2558,13 +2558,13 @@
     <t xml:space="preserve">6.188063621521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2413330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28572368621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32123613357544</t>
+    <t xml:space="preserve">6.24133348464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2857232093811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3212366104126</t>
   </si>
   <si>
     <t xml:space="preserve">6.25021123886108</t>
@@ -2573,7 +2573,7 @@
     <t xml:space="preserve">6.30348014831543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31235790252686</t>
+    <t xml:space="preserve">6.31235837936401</t>
   </si>
   <si>
     <t xml:space="preserve">6.1170392036438</t>
@@ -2582,16 +2582,16 @@
     <t xml:space="preserve">6.08152675628662</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06376981735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05489253997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98386669158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96611022949219</t>
+    <t xml:space="preserve">6.06377029418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05489206314087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98386716842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96611070632935</t>
   </si>
   <si>
     <t xml:space="preserve">5.93947649002075</t>
@@ -2603,19 +2603,19 @@
     <t xml:space="preserve">5.92172050476074</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91284132003784</t>
+    <t xml:space="preserve">5.912841796875</t>
   </si>
   <si>
     <t xml:space="preserve">6.23245477676392</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46328687667847</t>
+    <t xml:space="preserve">6.46328639984131</t>
   </si>
   <si>
     <t xml:space="preserve">6.33011436462402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27684593200684</t>
+    <t xml:space="preserve">6.27684545516968</t>
   </si>
   <si>
     <t xml:space="preserve">6.20582008361816</t>
@@ -2624,22 +2624,22 @@
     <t xml:space="preserve">6.04601383209229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37450504302979</t>
+    <t xml:space="preserve">6.37450456619263</t>
   </si>
   <si>
     <t xml:space="preserve">6.12591743469238</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21469926834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17918682098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26796722412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48104286193848</t>
+    <t xml:space="preserve">6.21469879150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17918586730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26796770095825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48104333877563</t>
   </si>
   <si>
     <t xml:space="preserve">6.66748380661011</t>
@@ -2648,103 +2648,103 @@
     <t xml:space="preserve">7.01373147964478</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43988227844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54642009735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59968948364258</t>
+    <t xml:space="preserve">7.4398832321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54641962051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59968852996826</t>
   </si>
   <si>
     <t xml:space="preserve">7.63520193099976</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68846940994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52866363525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31558752059937</t>
+    <t xml:space="preserve">7.68846988677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52866268157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31558799743652</t>
   </si>
   <si>
     <t xml:space="preserve">7.30670976638794</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1824164390564</t>
+    <t xml:space="preserve">7.18241596221924</t>
   </si>
   <si>
     <t xml:space="preserve">7.29783201217651</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13802528381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04924392700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19129419326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21792888641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3511004447937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48427248001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59081077575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58193159103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65295743942261</t>
+    <t xml:space="preserve">7.13802480697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04924345016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19129467010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21792840957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35109996795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4842734336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59081029891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58193206787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65295791625977</t>
   </si>
   <si>
     <t xml:space="preserve">7.5109076499939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45763731002808</t>
+    <t xml:space="preserve">7.45763826370239</t>
   </si>
   <si>
     <t xml:space="preserve">7.17353773117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61744451522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6795916557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76837348937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9370584487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19452381134033</t>
+    <t xml:space="preserve">7.61744499206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67959117889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76837301254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93705797195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19452285766602</t>
   </si>
   <si>
     <t xml:space="preserve">8.09686470031738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99920463562012</t>
+    <t xml:space="preserve">7.99920558929443</t>
   </si>
   <si>
     <t xml:space="preserve">8.17676830291748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20340061187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99032735824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08798503875732</t>
+    <t xml:space="preserve">8.20340156555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99032688140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08798599243164</t>
   </si>
   <si>
     <t xml:space="preserve">8.05247402191162</t>
@@ -2753,7 +2753,7 @@
     <t xml:space="preserve">8.0435962677002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00808334350586</t>
+    <t xml:space="preserve">8.00808429718018</t>
   </si>
   <si>
     <t xml:space="preserve">8.07910823822021</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">8.38984298706055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23891544342041</t>
+    <t xml:space="preserve">8.23891353607178</t>
   </si>
   <si>
     <t xml:space="preserve">8.44311237335205</t>
@@ -2783,13 +2783,13 @@
     <t xml:space="preserve">8.51413726806641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43423461914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64730834960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42535591125488</t>
+    <t xml:space="preserve">8.43423366546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64730930328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42535495758057</t>
   </si>
   <si>
     <t xml:space="preserve">8.47014427185059</t>
@@ -2798,19 +2798,19 @@
     <t xml:space="preserve">8.60530662536621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43410205841064</t>
+    <t xml:space="preserve">8.43410110473633</t>
   </si>
   <si>
     <t xml:space="preserve">8.4160795211792</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37102603912354</t>
+    <t xml:space="preserve">8.3710241317749</t>
   </si>
   <si>
     <t xml:space="preserve">8.56025218963623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31696033477783</t>
+    <t xml:space="preserve">8.31695938110352</t>
   </si>
   <si>
     <t xml:space="preserve">8.42509078979492</t>
@@ -2819,7 +2819,7 @@
     <t xml:space="preserve">8.62332725524902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75849056243896</t>
+    <t xml:space="preserve">8.75848960876465</t>
   </si>
   <si>
     <t xml:space="preserve">8.65937042236328</t>
@@ -2828,10 +2828,10 @@
     <t xml:space="preserve">8.70442390441895</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7404670715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68640422821045</t>
+    <t xml:space="preserve">8.74046802520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68640327453613</t>
   </si>
   <si>
     <t xml:space="preserve">8.47915554046631</t>
@@ -2843,28 +2843,28 @@
     <t xml:space="preserve">8.51519775390625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53321933746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46113300323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27190780639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10971355438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15476703643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08267974853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04663753509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05564880371094</t>
+    <t xml:space="preserve">8.5332202911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46113395690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27190685272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10971260070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15476608276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08268165588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0466365814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05564785003662</t>
   </si>
   <si>
     <t xml:space="preserve">7.95652914047241</t>
@@ -2873,28 +2873,28 @@
     <t xml:space="preserve">8.00158309936523</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74928140640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85741138458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.785325050354</t>
+    <t xml:space="preserve">7.74928188323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8574104309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78532457351685</t>
   </si>
   <si>
     <t xml:space="preserve">7.83938837051392</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74026966094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99257230758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92048645019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1727876663208</t>
+    <t xml:space="preserve">7.74027013778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99257278442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92048597335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17278861999512</t>
   </si>
   <si>
     <t xml:space="preserve">8.29893970489502</t>
@@ -2909,37 +2909,37 @@
     <t xml:space="preserve">7.96553993225098</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6051082611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07366847991943</t>
+    <t xml:space="preserve">7.60510778427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07366943359375</t>
   </si>
   <si>
     <t xml:space="preserve">8.24487400054932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12773418426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48816680908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38904666900635</t>
+    <t xml:space="preserve">8.12773513793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48816585540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38904762268066</t>
   </si>
   <si>
     <t xml:space="preserve">8.35300445556641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33498191833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71343612670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63233852386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23586463928223</t>
+    <t xml:space="preserve">8.33498287200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71343517303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63233947753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23586368560791</t>
   </si>
   <si>
     <t xml:space="preserve">8.30795097351074</t>
@@ -2948,16 +2948,16 @@
     <t xml:space="preserve">8.64134979248047</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77651023864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55124187469482</t>
+    <t xml:space="preserve">8.77651119232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55124092102051</t>
   </si>
   <si>
     <t xml:space="preserve">8.49717712402344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25388431549072</t>
+    <t xml:space="preserve">8.25388622283936</t>
   </si>
   <si>
     <t xml:space="preserve">8.19982051849365</t>
@@ -2966,28 +2966,28 @@
     <t xml:space="preserve">8.03762626647949</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92949771881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98356151580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01960468292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8844428062439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56906414031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63214015960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57807588577271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55104351043701</t>
+    <t xml:space="preserve">7.92949724197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98356103897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01960372924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88444232940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56906509399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63214111328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57807636260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55104446411133</t>
   </si>
   <si>
     <t xml:space="preserve">7.65917301177979</t>
@@ -2996,19 +2996,19 @@
     <t xml:space="preserve">7.67719507217407</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72224855422974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76730251312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71323871612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93850755691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2268533706665</t>
+    <t xml:space="preserve">7.72224950790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76730298995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71323776245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93850803375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22685241699219</t>
   </si>
   <si>
     <t xml:space="preserve">8.19080924987793</t>
@@ -3020,55 +3020,55 @@
     <t xml:space="preserve">8.38003635406494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18179893493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02861595153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8033447265625</t>
+    <t xml:space="preserve">8.18179798126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02861499786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80334568023682</t>
   </si>
   <si>
     <t xml:space="preserve">7.69521570205688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61411905288696</t>
+    <t xml:space="preserve">7.6141185760498</t>
   </si>
   <si>
     <t xml:space="preserve">7.37983798980713</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33478498458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37082767486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46093559265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36181688308716</t>
+    <t xml:space="preserve">7.33478450775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37082815170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46093511581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36181735992432</t>
   </si>
   <si>
     <t xml:space="preserve">7.35280609130859</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44291400909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65016222000122</t>
+    <t xml:space="preserve">7.4429144859314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65016174316406</t>
   </si>
   <si>
     <t xml:space="preserve">7.46994638442993</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39786052703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32577419281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27170944213867</t>
+    <t xml:space="preserve">7.39786005020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3257737159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27170896530151</t>
   </si>
   <si>
     <t xml:space="preserve">7.30775165557861</t>
@@ -3080,25 +3080,25 @@
     <t xml:space="preserve">7.26269865036011</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54203319549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64115142822266</t>
+    <t xml:space="preserve">7.54203224182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64115047454834</t>
   </si>
   <si>
     <t xml:space="preserve">7.62313032150269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53302097320557</t>
+    <t xml:space="preserve">7.53302145004272</t>
   </si>
   <si>
     <t xml:space="preserve">7.52401113510132</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31676244735718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38884878158569</t>
+    <t xml:space="preserve">7.31676292419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38884925842285</t>
   </si>
   <si>
     <t xml:space="preserve">7.45192527770996</t>
@@ -3107,55 +3107,55 @@
     <t xml:space="preserve">6.96534204483032</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92929887771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02841758728027</t>
+    <t xml:space="preserve">6.92929935455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02841806411743</t>
   </si>
   <si>
     <t xml:space="preserve">6.89325571060181</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01039600372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12753629684448</t>
+    <t xml:space="preserve">7.0103964805603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12753582000732</t>
   </si>
   <si>
     <t xml:space="preserve">7.11852550506592</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94732046127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88424491882324</t>
+    <t xml:space="preserve">6.94731998443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88424444198608</t>
   </si>
   <si>
     <t xml:space="preserve">6.90226602554321</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28071928024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22665548324585</t>
+    <t xml:space="preserve">7.28071975708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22665500640869</t>
   </si>
   <si>
     <t xml:space="preserve">7.03742837905884</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14555740356445</t>
+    <t xml:space="preserve">7.14555788040161</t>
   </si>
   <si>
     <t xml:space="preserve">7.19962215423584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00138521194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0734715461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80314779281616</t>
+    <t xml:space="preserve">7.00138568878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07347106933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80314826965332</t>
   </si>
   <si>
     <t xml:space="preserve">6.74007225036621</t>
@@ -3167,10 +3167,10 @@
     <t xml:space="preserve">6.3616189956665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59589958190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41568374633789</t>
+    <t xml:space="preserve">6.59590005874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41568422317505</t>
   </si>
   <si>
     <t xml:space="preserve">6.32557582855225</t>
@@ -3179,25 +3179,25 @@
     <t xml:space="preserve">6.13634920120239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85701513290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83899354934692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01019811630249</t>
+    <t xml:space="preserve">5.85701465606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83899307250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01019859313965</t>
   </si>
   <si>
     <t xml:space="preserve">6.28052139282227</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09129571914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14536046981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35260820388794</t>
+    <t xml:space="preserve">6.09129524230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14535999298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3526086807251</t>
   </si>
   <si>
     <t xml:space="preserve">6.23546838760376</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">6.31656503677368</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02822017669678</t>
+    <t xml:space="preserve">6.02821969985962</t>
   </si>
   <si>
     <t xml:space="preserve">6.11832761764526</t>
@@ -3227,31 +3227,31 @@
     <t xml:space="preserve">6.12733840942383</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27151155471802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26249980926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18140268325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29854345321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17239284515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84800338745117</t>
+    <t xml:space="preserve">6.27151107788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26250028610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18140363693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29854297637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17239236831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84800386428833</t>
   </si>
   <si>
     <t xml:space="preserve">5.86602544784546</t>
   </si>
   <si>
-    <t xml:space="preserve">5.920090675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89305782318115</t>
+    <t xml:space="preserve">5.92009019851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89305734634399</t>
   </si>
   <si>
     <t xml:space="preserve">5.93811178207397</t>
@@ -3275,10 +3275,10 @@
     <t xml:space="preserve">5.94712257385254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01920890808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9921760559082</t>
+    <t xml:space="preserve">6.0192084312439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99217700958252</t>
   </si>
   <si>
     <t xml:space="preserve">5.96514415740967</t>
@@ -3287,37 +3287,37 @@
     <t xml:space="preserve">5.97415494918823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95613288879395</t>
+    <t xml:space="preserve">5.9561333656311</t>
   </si>
   <si>
     <t xml:space="preserve">6.08228492736816</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07327318191528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03723001480103</t>
+    <t xml:space="preserve">6.07327365875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03723049163818</t>
   </si>
   <si>
     <t xml:space="preserve">6.04001379013062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94737529754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96590280532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1604437828064</t>
+    <t xml:space="preserve">5.94737577438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96590328216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16044425964355</t>
   </si>
   <si>
     <t xml:space="preserve">6.28087329864502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22528982162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20676231384277</t>
+    <t xml:space="preserve">6.22529029846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20676279067993</t>
   </si>
   <si>
     <t xml:space="preserve">6.17897176742554</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">5.9288477897644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89179277420044</t>
+    <t xml:space="preserve">5.8917932510376</t>
   </si>
   <si>
     <t xml:space="preserve">6.09559679031372</t>
@@ -3362,7 +3362,7 @@
     <t xml:space="preserve">5.68798828125</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78062629699707</t>
+    <t xml:space="preserve">5.78062677383423</t>
   </si>
   <si>
     <t xml:space="preserve">5.73430776596069</t>
@@ -3371,10 +3371,10 @@
     <t xml:space="preserve">5.72504377365112</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34522676467896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44712924957275</t>
+    <t xml:space="preserve">5.34522724151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4471287727356</t>
   </si>
   <si>
     <t xml:space="preserve">5.6046142578125</t>
@@ -3383,19 +3383,19 @@
     <t xml:space="preserve">5.75283527374268</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51197576522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85473728179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55829524993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71578025817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77136325836182</t>
+    <t xml:space="preserve">5.51197528839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85473775863647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55829477310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71578073501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77136278152466</t>
   </si>
   <si>
     <t xml:space="preserve">5.61387777328491</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">5.66019725799561</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8732647895813</t>
+    <t xml:space="preserve">5.87326526641846</t>
   </si>
   <si>
     <t xml:space="preserve">5.66946077346802</t>
@@ -3419,13 +3419,13 @@
     <t xml:space="preserve">6.04927778244019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86400127410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53976726531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49344825744629</t>
+    <t xml:space="preserve">5.86400079727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53976774215698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49344778060913</t>
   </si>
   <si>
     <t xml:space="preserve">5.47492074966431</t>
@@ -3434,7 +3434,7 @@
     <t xml:space="preserve">5.37301874160767</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39154624938965</t>
+    <t xml:space="preserve">5.39154672622681</t>
   </si>
   <si>
     <t xml:space="preserve">5.35449075698853</t>
@@ -3455,13 +3455,13 @@
     <t xml:space="preserve">5.19700622558594</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25258874893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38228273391724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1321587562561</t>
+    <t xml:space="preserve">5.25258922576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38228225708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13215923309326</t>
   </si>
   <si>
     <t xml:space="preserve">5.10436820983887</t>
@@ -3479,10 +3479,10 @@
     <t xml:space="preserve">5.08583974838257</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05804824829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01172971725464</t>
+    <t xml:space="preserve">5.05804872512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01172924041748</t>
   </si>
   <si>
     <t xml:space="preserve">5.02099323272705</t>
@@ -3491,22 +3491,22 @@
     <t xml:space="preserve">5.1784782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0487847328186</t>
+    <t xml:space="preserve">5.04878425598145</t>
   </si>
   <si>
     <t xml:space="preserve">5.15068674087524</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00246572494507</t>
+    <t xml:space="preserve">5.00246524810791</t>
   </si>
   <si>
     <t xml:space="preserve">4.8635082244873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91909122467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97467422485352</t>
+    <t xml:space="preserve">4.91909074783325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97467374801636</t>
   </si>
   <si>
     <t xml:space="preserve">4.96541023254395</t>
@@ -3524,10 +3524,10 @@
     <t xml:space="preserve">5.45639324188232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52123928070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29890775680542</t>
+    <t xml:space="preserve">5.52123975753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29890823364258</t>
   </si>
   <si>
     <t xml:space="preserve">5.46565675735474</t>
@@ -3539,7 +3539,7 @@
     <t xml:space="preserve">5.67872476577759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76209878921509</t>
+    <t xml:space="preserve">5.76209926605225</t>
   </si>
   <si>
     <t xml:space="preserve">5.90105676651001</t>
@@ -3587,7 +3587,7 @@
     <t xml:space="preserve">6.70700931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79964828491211</t>
+    <t xml:space="preserve">6.79964780807495</t>
   </si>
   <si>
     <t xml:space="preserve">6.82743883132935</t>
@@ -3596,19 +3596,19 @@
     <t xml:space="preserve">6.79038381576538</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89228630065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96639680862427</t>
+    <t xml:space="preserve">6.89228582382202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96639633178711</t>
   </si>
   <si>
     <t xml:space="preserve">7.23504734039307</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34621286392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38326787948608</t>
+    <t xml:space="preserve">7.34621334075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38326835632324</t>
   </si>
   <si>
     <t xml:space="preserve">7.46664333343506</t>
@@ -3620,10 +3620,10 @@
     <t xml:space="preserve">7.48517084121704</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42958831787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55928087234497</t>
+    <t xml:space="preserve">7.42958784103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55928134918213</t>
   </si>
   <si>
     <t xml:space="preserve">7.39253282546997</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">7.59633636474609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54075384140015</t>
+    <t xml:space="preserve">7.54075336456299</t>
   </si>
   <si>
     <t xml:space="preserve">7.64265584945679</t>
@@ -3641,10 +3641,10 @@
     <t xml:space="preserve">7.50369882583618</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63339138031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62412738800049</t>
+    <t xml:space="preserve">7.63339185714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62412786483765</t>
   </si>
   <si>
     <t xml:space="preserve">7.57780933380127</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">7.58707237243652</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45737934112549</t>
+    <t xml:space="preserve">7.45737981796265</t>
   </si>
   <si>
     <t xml:space="preserve">7.43885135650635</t>
@@ -3668,16 +3668,16 @@
     <t xml:space="preserve">7.10535383224487</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18872833251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42032432556152</t>
+    <t xml:space="preserve">7.18872785568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42032384872437</t>
   </si>
   <si>
     <t xml:space="preserve">7.30915784835815</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29062986373901</t>
+    <t xml:space="preserve">7.29063034057617</t>
   </si>
   <si>
     <t xml:space="preserve">7.16093683242798</t>
@@ -3686,7 +3686,7 @@
     <t xml:space="preserve">7.29989433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24431180953979</t>
+    <t xml:space="preserve">7.24431133270264</t>
   </si>
   <si>
     <t xml:space="preserve">7.21651983261108</t>
@@ -3695,40 +3695,40 @@
     <t xml:space="preserve">7.27210235595703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20725584030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33694982528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31842231750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26283931732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12388134002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04977130889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98492431640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07756233215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22578430175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19799184799194</t>
+    <t xml:space="preserve">7.20725631713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33694934844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31842184066772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26283884048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12388181686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04977083206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98492383956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07756185531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22578382492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1979923248291</t>
   </si>
   <si>
     <t xml:space="preserve">7.15167284011841</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11461734771729</t>
+    <t xml:space="preserve">7.11461782455444</t>
   </si>
   <si>
     <t xml:space="preserve">7.05903482437134</t>
@@ -71747,7 +71747,7 @@
     </row>
     <row r="2554">
       <c r="A2554" s="1" t="n">
-        <v>46042.6912384259</v>
+        <v>46042.3333333333</v>
       </c>
       <c r="B2554" t="n">
         <v>76086</v>
@@ -71768,6 +71768,32 @@
         <v>1672</v>
       </c>
       <c r="H2554" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2555">
+      <c r="A2555" s="1" t="n">
+        <v>46043.6911574074</v>
+      </c>
+      <c r="B2555" t="n">
+        <v>58402</v>
+      </c>
+      <c r="C2555" t="n">
+        <v>19.4200000762939</v>
+      </c>
+      <c r="D2555" t="n">
+        <v>19.0799999237061</v>
+      </c>
+      <c r="E2555" t="n">
+        <v>19.1800003051758</v>
+      </c>
+      <c r="F2555" t="n">
+        <v>19.3799991607666</v>
+      </c>
+      <c r="G2555" t="s">
+        <v>1671</v>
+      </c>
+      <c r="H2555" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CEM.MI.xlsx
+++ b/data/CEM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1678" uniqueCount="1678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1679" uniqueCount="1679">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,112 +38,112 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70432090759277</t>
+    <t xml:space="preserve">4.70432043075562</t>
   </si>
   <si>
     <t xml:space="preserve">CEM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68036079406738</t>
+    <t xml:space="preserve">4.68036031723022</t>
   </si>
   <si>
     <t xml:space="preserve">4.55656242370605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48867321014404</t>
+    <t xml:space="preserve">4.48867273330688</t>
   </si>
   <si>
     <t xml:space="preserve">4.32893419265747</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22110939025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32494020462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28899908065796</t>
+    <t xml:space="preserve">4.22110986709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32494068145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28899955749512</t>
   </si>
   <si>
     <t xml:space="preserve">4.29299259185791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06137084960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9359757900238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97431230545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67560076713562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83533978462219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94875431060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88006687164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91680645942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87846946716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7458860874176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93437767028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87367701530457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73789858818054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57815885543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59892559051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61969137191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3513298034668</t>
+    <t xml:space="preserve">4.06137037277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93597531318665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97431254386902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6756010055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83533954620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94875478744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88006663322449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91680669784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87846922874451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74588561058044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93437814712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87367677688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73789834976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57815957069397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59892511367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61969184875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35132956504822</t>
   </si>
   <si>
     <t xml:space="preserve">3.15005803108215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25069403648376</t>
+    <t xml:space="preserve">3.25069379806519</t>
   </si>
   <si>
     <t xml:space="preserve">3.13088917732239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20916175842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44238114356995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36251163482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47592663764954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55419874191284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3465371131897</t>
+    <t xml:space="preserve">3.20916199684143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44238090515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3625111579895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47592639923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55419826507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34653782844543</t>
   </si>
   <si>
     <t xml:space="preserve">3.39126443862915</t>
@@ -152,34 +152,34 @@
     <t xml:space="preserve">3.36730360984802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23951244354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29222655296326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40244650840759</t>
+    <t xml:space="preserve">3.23951196670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29222631454468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40244674682617</t>
   </si>
   <si>
     <t xml:space="preserve">3.58614611625671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63406753540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55579614639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64365267753601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56058788299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52065324783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4982898235321</t>
+    <t xml:space="preserve">3.63406872749329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55579662322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64365220069885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56058859825134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52065300941467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49828958511353</t>
   </si>
   <si>
     <t xml:space="preserve">3.52544546127319</t>
@@ -188,88 +188,88 @@
     <t xml:space="preserve">3.54940605163574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75227499008179</t>
+    <t xml:space="preserve">3.75227475166321</t>
   </si>
   <si>
     <t xml:space="preserve">3.61330199241638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75387215614319</t>
+    <t xml:space="preserve">3.75387239456177</t>
   </si>
   <si>
     <t xml:space="preserve">3.83214473724365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67080760002136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70754861831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65802836418152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51745867729187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57017183303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50947165489197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54301714897156</t>
+    <t xml:space="preserve">3.67080855369568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70754790306091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65802884101868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51745843887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57017254829407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50947141647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5430166721344</t>
   </si>
   <si>
     <t xml:space="preserve">3.57975673675537</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45196485519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41043329238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37529063224792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60052251815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48551058769226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54461407661438</t>
+    <t xml:space="preserve">3.45196533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4104335308075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3752908706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60052299499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48551106452942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54461431503296</t>
   </si>
   <si>
     <t xml:space="preserve">3.59573078155518</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77943086624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74428915977478</t>
+    <t xml:space="preserve">3.7794303894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74428796768188</t>
   </si>
   <si>
     <t xml:space="preserve">3.85770297050476</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73949575424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74907994270325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70595097541809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69317078590393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67719793319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79700207710266</t>
+    <t xml:space="preserve">3.73949646949768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74908018112183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70595026016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69317150115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67719769477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7970027923584</t>
   </si>
   <si>
     <t xml:space="preserve">3.66601634025574</t>
@@ -278,61 +278,61 @@
     <t xml:space="preserve">3.70115876197815</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62608075141907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67400312423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64205503463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53023791313171</t>
+    <t xml:space="preserve">3.62608122825623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6740026473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64205479621887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53023743629456</t>
   </si>
   <si>
     <t xml:space="preserve">3.45835494995117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4743287563324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53193759918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62187075614929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7575888633728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76085901260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87531971931458</t>
+    <t xml:space="preserve">3.47432899475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53193712234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62187004089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75758838653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76085877418518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87531924247742</t>
   </si>
   <si>
     <t xml:space="preserve">3.88349556922913</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7772102355957</t>
+    <t xml:space="preserve">3.77721047401428</t>
   </si>
   <si>
     <t xml:space="preserve">3.75431847572327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70526385307312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6692898273468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59734320640564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58426189422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55646419525146</t>
+    <t xml:space="preserve">3.70526337623596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66928958892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59734344482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58426117897034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55646395683289</t>
   </si>
   <si>
     <t xml:space="preserve">3.38640832901001</t>
@@ -350,61 +350,61 @@
     <t xml:space="preserve">3.15912127494812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00705170631409</t>
+    <t xml:space="preserve">3.00705194473267</t>
   </si>
   <si>
     <t xml:space="preserve">3.15421581268311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0348494052887</t>
+    <t xml:space="preserve">3.03484916687012</t>
   </si>
   <si>
     <t xml:space="preserve">3.22289252281189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35206961631775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10679626464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8288197517395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82064390182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84026622772217</t>
+    <t xml:space="preserve">3.35206985473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10679650306702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82881999015808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82064437866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84026598930359</t>
   </si>
   <si>
     <t xml:space="preserve">2.93510508537292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04302549362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9579975605011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79611682891846</t>
+    <t xml:space="preserve">3.04302525520325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95799732208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79611659049988</t>
   </si>
   <si>
     <t xml:space="preserve">2.76341390609741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76831912994385</t>
+    <t xml:space="preserve">2.76831936836243</t>
   </si>
   <si>
     <t xml:space="preserve">2.84844183921814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87787485122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04139041900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00051116943359</t>
+    <t xml:space="preserve">2.87787461280823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04139018058777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00051140785217</t>
   </si>
   <si>
     <t xml:space="preserve">3.2114462852478</t>
@@ -413,55 +413,55 @@
     <t xml:space="preserve">3.13295912742615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07572865486145</t>
+    <t xml:space="preserve">3.07572841644287</t>
   </si>
   <si>
     <t xml:space="preserve">2.97434878349304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10843181610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9759840965271</t>
+    <t xml:space="preserve">3.1084315776825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97598385810852</t>
   </si>
   <si>
     <t xml:space="preserve">2.92856431007385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17547297477722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18037891387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15585112571716</t>
+    <t xml:space="preserve">3.1754732131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18037867546082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15585088729858</t>
   </si>
   <si>
     <t xml:space="preserve">3.18855428695679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09862041473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12151312828064</t>
+    <t xml:space="preserve">3.09862089157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12151336669922</t>
   </si>
   <si>
     <t xml:space="preserve">3.02503848075867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11660718917847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23760914802551</t>
+    <t xml:space="preserve">3.11660742759705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23760890960693</t>
   </si>
   <si>
     <t xml:space="preserve">3.28012299537659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32263731956482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43546295166016</t>
+    <t xml:space="preserve">3.32263708114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43546319007874</t>
   </si>
   <si>
     <t xml:space="preserve">3.40602993965149</t>
@@ -470,67 +470,67 @@
     <t xml:space="preserve">3.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43709874153137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44854402542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67910075187683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64639806747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71834444999695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69545269012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74450778961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85242819786072</t>
+    <t xml:space="preserve">3.43709778785706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44854378700256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67910051345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64639759063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71834468841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69545245170593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7445080280304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85242795944214</t>
   </si>
   <si>
     <t xml:space="preserve">3.80827832221985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82299470901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80337333679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74287152290344</t>
+    <t xml:space="preserve">3.82299447059631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80337238311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74287247657776</t>
   </si>
   <si>
     <t xml:space="preserve">3.62350583076477</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56627488136292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47470641136169</t>
+    <t xml:space="preserve">3.56627535820007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47470617294312</t>
   </si>
   <si>
     <t xml:space="preserve">3.51558542251587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65947890281677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60551905632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54501795768738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64803338050842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64476346969604</t>
+    <t xml:space="preserve">3.65947914123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60551881790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54501819610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64803290367126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64476299285889</t>
   </si>
   <si>
     <t xml:space="preserve">3.38804340362549</t>
@@ -539,79 +539,79 @@
     <t xml:space="preserve">3.48288249969482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45344924926758</t>
+    <t xml:space="preserve">3.45344948768616</t>
   </si>
   <si>
     <t xml:space="preserve">3.4338276386261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50740885734558</t>
+    <t xml:space="preserve">3.50740957260132</t>
   </si>
   <si>
     <t xml:space="preserve">3.56464028358459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55482912063599</t>
+    <t xml:space="preserve">3.55482888221741</t>
   </si>
   <si>
     <t xml:space="preserve">3.56300449371338</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48451805114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54338335990906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62514066696167</t>
+    <t xml:space="preserve">3.4845175743103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54338359832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62514090538025</t>
   </si>
   <si>
     <t xml:space="preserve">3.5908031463623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64149260520935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68891191482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66111445426941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6872775554657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53684282302856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63004589080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63822197914124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43873310089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.417475938797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41911125183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33571791648865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37169170379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27521729469299</t>
+    <t xml:space="preserve">3.64149188995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68891167640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66111493110657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68727779388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53684210777283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63004684448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63822174072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43873286247253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41747617721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41911101341248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33571815490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37169122695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27521777153015</t>
   </si>
   <si>
     <t xml:space="preserve">3.22125744819641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2098114490509</t>
+    <t xml:space="preserve">3.20981121063232</t>
   </si>
   <si>
     <t xml:space="preserve">3.1771080493927</t>
@@ -620,82 +620,82 @@
     <t xml:space="preserve">3.21308159828186</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14767551422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11333751678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00541663169861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0168628692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95309138298035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9187536239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96453785896301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96780824661255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9563615322113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04793047904968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17220258712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18691897392273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31936693191528</t>
+    <t xml:space="preserve">3.14767527580261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11333727836609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00541687011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01686263084412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9530918598175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91875314712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96453762054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96780800819397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95636224746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04793071746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17220282554626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18691873550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31936645507812</t>
   </si>
   <si>
     <t xml:space="preserve">3.23433876037598</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48778772354126</t>
+    <t xml:space="preserve">3.48778748512268</t>
   </si>
   <si>
     <t xml:space="preserve">3.45181441307068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49923372268677</t>
+    <t xml:space="preserve">3.49923396110535</t>
   </si>
   <si>
     <t xml:space="preserve">3.57281565666199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45017886161804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61369514465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67746615409851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58916759490967</t>
+    <t xml:space="preserve">3.4501793384552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61369490623474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67746639251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58916687965393</t>
   </si>
   <si>
     <t xml:space="preserve">3.70362901687622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48615193367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33244800567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28666400909424</t>
+    <t xml:space="preserve">3.4861524105072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33244824409485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28666377067566</t>
   </si>
   <si>
     <t xml:space="preserve">3.22943329811096</t>
@@ -710,85 +710,85 @@
     <t xml:space="preserve">3.23106837272644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23270344734192</t>
+    <t xml:space="preserve">3.2327036857605</t>
   </si>
   <si>
     <t xml:space="preserve">3.26213645935059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27685260772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23597359657288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00122737884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04701137542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12876892089844</t>
+    <t xml:space="preserve">3.27685236930847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23597383499146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00122690200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04701089859009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1287693977356</t>
   </si>
   <si>
     <t xml:space="preserve">4.16964769363403</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17782402038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06336212158203</t>
+    <t xml:space="preserve">4.17782306671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06336164474487</t>
   </si>
   <si>
     <t xml:space="preserve">3.95707750320435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19417572021484</t>
+    <t xml:space="preserve">4.19417524337769</t>
   </si>
   <si>
     <t xml:space="preserve">4.28410816192627</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3454270362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47215223312378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43944835662842</t>
+    <t xml:space="preserve">4.34542655944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47215175628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43944787979126</t>
   </si>
   <si>
     <t xml:space="preserve">4.41083335876465</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41492128372192</t>
+    <t xml:space="preserve">4.41492176055908</t>
   </si>
   <si>
     <t xml:space="preserve">4.37404251098633</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26775693893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39039325714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36177921295166</t>
+    <t xml:space="preserve">4.26775741577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39039373397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36177825927734</t>
   </si>
   <si>
     <t xml:space="preserve">4.37812948226929</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38630628585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56208515167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42718458175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32907581329346</t>
+    <t xml:space="preserve">4.386305809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56208562850952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42718505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3290753364563</t>
   </si>
   <si>
     <t xml:space="preserve">4.2554931640625</t>
@@ -800,19 +800,19 @@
     <t xml:space="preserve">4.30046033859253</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34951543807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24323034286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24731779098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21052694320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14512014389038</t>
+    <t xml:space="preserve">4.34951448440552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24322986602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24731874465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21052646636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1451210975647</t>
   </si>
   <si>
     <t xml:space="preserve">4.10424137115479</t>
@@ -821,70 +821,70 @@
     <t xml:space="preserve">4.22279024124146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40674543380737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36586713790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27593278884888</t>
+    <t xml:space="preserve">4.40674495697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36586666107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27593326568604</t>
   </si>
   <si>
     <t xml:space="preserve">4.3045482635498</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28002166748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44762420654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52938222885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51711845397949</t>
+    <t xml:space="preserve">4.28002119064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44762468338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52938175201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51711893081665</t>
   </si>
   <si>
     <t xml:space="preserve">4.52120685577393</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68063402175903</t>
+    <t xml:space="preserve">4.68063354492188</t>
   </si>
   <si>
     <t xml:space="preserve">4.66019487380981</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71333742141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7337760925293</t>
+    <t xml:space="preserve">4.71333694458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73377656936646</t>
   </si>
   <si>
     <t xml:space="preserve">4.81962203979492</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81144618988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65201902389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34133911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33725070953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25958108901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40383386611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44966459274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41633415222168</t>
+    <t xml:space="preserve">4.81144714355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65201854705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34133958816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33725118637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25958156585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40383434295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44966506958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41633367538452</t>
   </si>
   <si>
     <t xml:space="preserve">4.37467002868652</t>
@@ -899,31 +899,31 @@
     <t xml:space="preserve">4.27467775344849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25801277160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31634044647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26634502410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20801591873169</t>
+    <t xml:space="preserve">4.25801181793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31634092330933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26634454727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20801639556885</t>
   </si>
   <si>
     <t xml:space="preserve">4.33300638198853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37050294876099</t>
+    <t xml:space="preserve">4.37050342559814</t>
   </si>
   <si>
     <t xml:space="preserve">4.3455057144165</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39133501052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29967546463013</t>
+    <t xml:space="preserve">4.39133596420288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29967594146729</t>
   </si>
   <si>
     <t xml:space="preserve">4.42883253097534</t>
@@ -935,22 +935,22 @@
     <t xml:space="preserve">4.3955020904541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38300275802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46633052825928</t>
+    <t xml:space="preserve">4.38300228118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46633005142212</t>
   </si>
   <si>
     <t xml:space="preserve">4.48299551010132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56632137298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40800046920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34967088699341</t>
+    <t xml:space="preserve">4.566321849823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40800094604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34967184066772</t>
   </si>
   <si>
     <t xml:space="preserve">4.69131326675415</t>
@@ -962,67 +962,67 @@
     <t xml:space="preserve">4.85380029678345</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99962329864502</t>
+    <t xml:space="preserve">4.99962282180786</t>
   </si>
   <si>
     <t xml:space="preserve">5.05795192718506</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10794878005981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24960470199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28710079193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2537693977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41625785827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30376672744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29960107803345</t>
+    <t xml:space="preserve">5.10794830322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24960422515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28710126876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25376987457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41625881195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30376625061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29960060119629</t>
   </si>
   <si>
     <t xml:space="preserve">5.34543037414551</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30793285369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22877264022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29126787185669</t>
+    <t xml:space="preserve">5.30793237686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22877216339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29126739501953</t>
   </si>
   <si>
     <t xml:space="preserve">5.29543399810791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16211032867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01628828048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05378580093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12461423873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20377349853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07461786270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03295373916626</t>
+    <t xml:space="preserve">5.16210985183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0162878036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05378532409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12461376190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20377397537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07461738586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0329532623291</t>
   </si>
   <si>
     <t xml:space="preserve">4.95795917510986</t>
@@ -1034,28 +1034,28 @@
     <t xml:space="preserve">4.96212577819824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90796375274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94129371643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89129781723022</t>
+    <t xml:space="preserve">4.90796279907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94129323959351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89129734039307</t>
   </si>
   <si>
     <t xml:space="preserve">4.90379667282104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95379304885864</t>
+    <t xml:space="preserve">4.95379257202148</t>
   </si>
   <si>
     <t xml:space="preserve">4.94546031951904</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91629505157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02462100982666</t>
+    <t xml:space="preserve">4.91629552841187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02462148666382</t>
   </si>
   <si>
     <t xml:space="preserve">5.0496187210083</t>
@@ -1067,10 +1067,10 @@
     <t xml:space="preserve">5.17461013793945</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23293876647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17877674102783</t>
+    <t xml:space="preserve">5.23293924331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17877626419067</t>
   </si>
   <si>
     <t xml:space="preserve">5.13294649124146</t>
@@ -1094,10 +1094,10 @@
     <t xml:space="preserve">6.00371360778809</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80789566040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0745415687561</t>
+    <t xml:space="preserve">5.80789470672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07454204559326</t>
   </si>
   <si>
     <t xml:space="preserve">6.01621294021606</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">5.89122200012207</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94121837615967</t>
+    <t xml:space="preserve">5.94121789932251</t>
   </si>
   <si>
     <t xml:space="preserve">5.96621656417847</t>
@@ -1121,10 +1121,10 @@
     <t xml:space="preserve">5.99538135528564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.970383644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91622066497803</t>
+    <t xml:space="preserve">5.97038316726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91621971130371</t>
   </si>
   <si>
     <t xml:space="preserve">5.86205768585205</t>
@@ -1136,28 +1136,28 @@
     <t xml:space="preserve">5.89955472946167</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90372133255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87455749511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84539175033569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00787973403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98288202285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03704452514648</t>
+    <t xml:space="preserve">5.90372180938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87455701828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84539222717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00788021087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98288154602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03704404830933</t>
   </si>
   <si>
     <t xml:space="preserve">6.09120750427246</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02871227264404</t>
+    <t xml:space="preserve">6.02871131896973</t>
   </si>
   <si>
     <t xml:space="preserve">5.99954748153687</t>
@@ -1166,46 +1166,46 @@
     <t xml:space="preserve">6.04954385757446</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07870817184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29119205474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17453384399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19953298568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0828742980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24536228179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21203184127808</t>
+    <t xml:space="preserve">6.07870864868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29119253158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17453336715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1995325088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08287477493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24536275863647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21203136444092</t>
   </si>
   <si>
     <t xml:space="preserve">6.02454566955566</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09954071044922</t>
+    <t xml:space="preserve">6.09954023361206</t>
   </si>
   <si>
     <t xml:space="preserve">6.18286657333374</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20786476135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22036457061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14537048339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95788431167603</t>
+    <t xml:space="preserve">6.2078652381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22036409378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14537000656128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95788383483887</t>
   </si>
   <si>
     <t xml:space="preserve">5.94538497924805</t>
@@ -1217,13 +1217,13 @@
     <t xml:space="preserve">6.02037954330444</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1162052154541</t>
+    <t xml:space="preserve">6.11620569229126</t>
   </si>
   <si>
     <t xml:space="preserve">6.06204271316528</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04121112823486</t>
+    <t xml:space="preserve">6.04121065139771</t>
   </si>
   <si>
     <t xml:space="preserve">6.14953660964966</t>
@@ -1232,55 +1232,55 @@
     <t xml:space="preserve">6.09537363052368</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35785341262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22453117370605</t>
+    <t xml:space="preserve">6.35785436630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22453022003174</t>
   </si>
   <si>
     <t xml:space="preserve">6.28285932540894</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58283662796021</t>
+    <t xml:space="preserve">6.58283710479736</t>
   </si>
   <si>
     <t xml:space="preserve">6.6161675453186</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57450437545776</t>
+    <t xml:space="preserve">6.57450389862061</t>
   </si>
   <si>
     <t xml:space="preserve">6.50784254074097</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49950981140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6578311920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74115753173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5911693572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62449979782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6328330039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70782709121704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52450752258301</t>
+    <t xml:space="preserve">6.49951028823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65783166885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7411584854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59116983413696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6245002746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63283348083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70782804489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52450799942017</t>
   </si>
   <si>
     <t xml:space="preserve">6.51617527008057</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66616439819336</t>
+    <t xml:space="preserve">6.66616344451904</t>
   </si>
   <si>
     <t xml:space="preserve">6.54950618743896</t>
@@ -1289,58 +1289,58 @@
     <t xml:space="preserve">6.44951343536377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29952430725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23286294937134</t>
+    <t xml:space="preserve">6.29952478408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2328634262085</t>
   </si>
   <si>
     <t xml:space="preserve">5.90788793563843</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93288612365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53284025192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26619386672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36618661880493</t>
+    <t xml:space="preserve">5.93288564682007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53284120559692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26619434356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36618614196777</t>
   </si>
   <si>
     <t xml:space="preserve">6.33285570144653</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1412034034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15786933898926</t>
+    <t xml:space="preserve">6.14120435714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15786838531494</t>
   </si>
   <si>
     <t xml:space="preserve">6.0662088394165</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94955062866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13287115097046</t>
+    <t xml:space="preserve">5.94955110549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1328706741333</t>
   </si>
   <si>
     <t xml:space="preserve">6.0578761100769</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88288927078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84955835342407</t>
+    <t xml:space="preserve">5.88288974761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84955883026123</t>
   </si>
   <si>
     <t xml:space="preserve">5.81622791290283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72456789016724</t>
+    <t xml:space="preserve">5.72456836700439</t>
   </si>
   <si>
     <t xml:space="preserve">5.75789928436279</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">5.82456016540527</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86622476577759</t>
+    <t xml:space="preserve">5.86622428894043</t>
   </si>
   <si>
     <t xml:space="preserve">5.77456426620483</t>
@@ -1364,13 +1364,13 @@
     <t xml:space="preserve">5.78289699554443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79122972488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63290882110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64982414245605</t>
+    <t xml:space="preserve">5.79122924804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63290929794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64982461929321</t>
   </si>
   <si>
     <t xml:space="preserve">5.68365526199341</t>
@@ -1379,13 +1379,13 @@
     <t xml:space="preserve">5.66673994064331</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70057058334351</t>
+    <t xml:space="preserve">5.70057106018066</t>
   </si>
   <si>
     <t xml:space="preserve">5.48066759109497</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45529365539551</t>
+    <t xml:space="preserve">5.45529460906982</t>
   </si>
   <si>
     <t xml:space="preserve">5.54833078384399</t>
@@ -1397,13 +1397,13 @@
     <t xml:space="preserve">5.74286031723022</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58216142654419</t>
+    <t xml:space="preserve">5.58216094970703</t>
   </si>
   <si>
     <t xml:space="preserve">5.65828227996826</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70902872085571</t>
+    <t xml:space="preserve">5.70902967453003</t>
   </si>
   <si>
     <t xml:space="preserve">5.77669143676758</t>
@@ -1412,13 +1412,13 @@
     <t xml:space="preserve">5.91201639175415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90355920791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89510107040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75131797790527</t>
+    <t xml:space="preserve">5.9035587310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89510059356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75131750106812</t>
   </si>
   <si>
     <t xml:space="preserve">5.78514909744263</t>
@@ -1430,31 +1430,31 @@
     <t xml:space="preserve">5.81052303314209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56524562835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50604104995728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69211292266846</t>
+    <t xml:space="preserve">5.56524610519409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50604152679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69211339950562</t>
   </si>
   <si>
     <t xml:space="preserve">5.72594451904297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73440265655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60753536224365</t>
+    <t xml:space="preserve">5.73440217971802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60753488540649</t>
   </si>
   <si>
     <t xml:space="preserve">5.51449871063232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67519760131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01351070404053</t>
+    <t xml:space="preserve">5.6751971244812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01351022720337</t>
   </si>
   <si>
     <t xml:space="preserve">5.99659538269043</t>
@@ -1463,10 +1463,10 @@
     <t xml:space="preserve">5.81898021697998</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75977516174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80206489562988</t>
+    <t xml:space="preserve">5.75977563858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80206537246704</t>
   </si>
   <si>
     <t xml:space="preserve">5.79360675811768</t>
@@ -1478,43 +1478,43 @@
     <t xml:space="preserve">5.8781852722168</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92893266677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85281181335449</t>
+    <t xml:space="preserve">5.92893218994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85281229019165</t>
   </si>
   <si>
     <t xml:space="preserve">5.76823425292969</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82743883132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83589696884155</t>
+    <t xml:space="preserve">5.82743835449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83589649200439</t>
   </si>
   <si>
     <t xml:space="preserve">5.42992067337036</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38763189315796</t>
+    <t xml:space="preserve">5.38763093948364</t>
   </si>
   <si>
     <t xml:space="preserve">5.33688497543335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26076412200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30305337905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43837881088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46375179290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44683647155762</t>
+    <t xml:space="preserve">5.26076459884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.303053855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43837833404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46375226974487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44683742523193</t>
   </si>
   <si>
     <t xml:space="preserve">5.35380029678345</t>
@@ -1523,13 +1523,13 @@
     <t xml:space="preserve">5.3707160949707</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22693300247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14235544204712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11698198318481</t>
+    <t xml:space="preserve">5.22693252563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14235496520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11698150634766</t>
   </si>
   <si>
     <t xml:space="preserve">5.24384832382202</t>
@@ -1556,7 +1556,7 @@
     <t xml:space="preserve">5.31996917724609</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29459571838379</t>
+    <t xml:space="preserve">5.29459619522095</t>
   </si>
   <si>
     <t xml:space="preserve">5.48912525177002</t>
@@ -1574,31 +1574,31 @@
     <t xml:space="preserve">5.17618560791016</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10852384567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91399431228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60105419158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49956083297729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.567223072052</t>
+    <t xml:space="preserve">5.10852336883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91399383544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6010537147522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49956035614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56722354888916</t>
   </si>
   <si>
     <t xml:space="preserve">4.38115072250366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5418496131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52493476867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61797046661377</t>
+    <t xml:space="preserve">4.54184913635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5249342918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61797094345093</t>
   </si>
   <si>
     <t xml:space="preserve">4.46572971343994</t>
@@ -1607,16 +1607,16 @@
     <t xml:space="preserve">4.27119970321655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14433193206787</t>
+    <t xml:space="preserve">4.14433240890503</t>
   </si>
   <si>
     <t xml:space="preserve">4.22045278549194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09358501434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20353651046753</t>
+    <t xml:space="preserve">4.09358549118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20353603363037</t>
   </si>
   <si>
     <t xml:space="preserve">4.15701866149902</t>
@@ -1631,28 +1631,28 @@
     <t xml:space="preserve">4.59259605407715</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6095118522644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63488578796387</t>
+    <t xml:space="preserve">4.60951232910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63488531112671</t>
   </si>
   <si>
     <t xml:space="preserve">4.41498231887817</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49110269546509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42343997955322</t>
+    <t xml:space="preserve">4.49110221862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42344045639038</t>
   </si>
   <si>
     <t xml:space="preserve">4.43189811706543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29657316207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33886241912842</t>
+    <t xml:space="preserve">4.2965726852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33886194229126</t>
   </si>
   <si>
     <t xml:space="preserve">4.19507884979248</t>
@@ -1664,16 +1664,16 @@
     <t xml:space="preserve">4.08512687683105</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10627222061157</t>
+    <t xml:space="preserve">4.10627174377441</t>
   </si>
   <si>
     <t xml:space="preserve">4.15278959274292</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2373685836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.216224193573</t>
+    <t xml:space="preserve">4.23736810684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21622371673584</t>
   </si>
   <si>
     <t xml:space="preserve">4.16124773025513</t>
@@ -1688,19 +1688,19 @@
     <t xml:space="preserve">4.30503082275391</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25428342819214</t>
+    <t xml:space="preserve">4.2542839050293</t>
   </si>
   <si>
     <t xml:space="preserve">4.14010286331177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0512957572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14856147766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08935594558716</t>
+    <t xml:space="preserve">4.05129623413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14856100082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08935642242432</t>
   </si>
   <si>
     <t xml:space="preserve">4.0343804359436</t>
@@ -1712,10 +1712,10 @@
     <t xml:space="preserve">4.35577774047852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31348848342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4826455116272</t>
+    <t xml:space="preserve">4.31348896026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48264503479004</t>
   </si>
   <si>
     <t xml:space="preserve">4.65180110931396</t>
@@ -1733,13 +1733,13 @@
     <t xml:space="preserve">4.86324691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90553617477417</t>
+    <t xml:space="preserve">4.90553665161133</t>
   </si>
   <si>
     <t xml:space="preserve">4.88862037658691</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95628261566162</t>
+    <t xml:space="preserve">4.95628309249878</t>
   </si>
   <si>
     <t xml:space="preserve">5.00703001022339</t>
@@ -1754,28 +1754,28 @@
     <t xml:space="preserve">5.05777645111084</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99011421203613</t>
+    <t xml:space="preserve">4.99011373519897</t>
   </si>
   <si>
     <t xml:space="preserve">4.97319889068604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20155954360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12543964385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15927028656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21847581863403</t>
+    <t xml:space="preserve">5.20156002044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12543916702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15927076339722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21847534179688</t>
   </si>
   <si>
     <t xml:space="preserve">5.34534311294556</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27767992019653</t>
+    <t xml:space="preserve">5.27767944335938</t>
   </si>
   <si>
     <t xml:space="preserve">5.40454769134521</t>
@@ -1796,67 +1796,67 @@
     <t xml:space="preserve">5.41300535202026</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98165607452393</t>
+    <t xml:space="preserve">4.98165655136108</t>
   </si>
   <si>
     <t xml:space="preserve">5.11462497711182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13193273544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01942920684814</t>
+    <t xml:space="preserve">5.13193321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01942873001099</t>
   </si>
   <si>
     <t xml:space="preserve">5.01077461242676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06269979476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08866310119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09731674194336</t>
+    <t xml:space="preserve">5.06270027160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08866214752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0973162651062</t>
   </si>
   <si>
     <t xml:space="preserve">5.14058780670166</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20116758346558</t>
+    <t xml:space="preserve">5.20116710662842</t>
   </si>
   <si>
     <t xml:space="preserve">5.17520427703857</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2271294593811</t>
+    <t xml:space="preserve">5.22712993621826</t>
   </si>
   <si>
     <t xml:space="preserve">5.26174592971802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23578405380249</t>
+    <t xml:space="preserve">5.23578357696533</t>
   </si>
   <si>
     <t xml:space="preserve">5.25309228897095</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33963346481323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46079254150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54733419418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42617559432983</t>
+    <t xml:space="preserve">5.33963394165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46079206466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54733467102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42617511749268</t>
   </si>
   <si>
     <t xml:space="preserve">5.330979347229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40886831283569</t>
+    <t xml:space="preserve">5.40886735916138</t>
   </si>
   <si>
     <t xml:space="preserve">5.57329702377319</t>
@@ -1865,37 +1865,37 @@
     <t xml:space="preserve">5.52137184143066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47810029983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64253044128418</t>
+    <t xml:space="preserve">5.47810125350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64253091812134</t>
   </si>
   <si>
     <t xml:space="preserve">5.7636890411377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74638032913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72907304763794</t>
+    <t xml:space="preserve">5.7463812828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72907209396362</t>
   </si>
   <si>
     <t xml:space="preserve">5.65118503570557</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7031102180481</t>
+    <t xml:space="preserve">5.70310974121094</t>
   </si>
   <si>
     <t xml:space="preserve">5.66849327087402</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59925985336304</t>
+    <t xml:space="preserve">5.59925937652588</t>
   </si>
   <si>
     <t xml:space="preserve">5.49540901184082</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45213794708252</t>
+    <t xml:space="preserve">5.45213842391968</t>
   </si>
   <si>
     <t xml:space="preserve">5.56464242935181</t>
@@ -1904,43 +1904,43 @@
     <t xml:space="preserve">5.73772668838501</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51271772384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2444372177124</t>
+    <t xml:space="preserve">5.51271724700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24443817138672</t>
   </si>
   <si>
     <t xml:space="preserve">5.18385791778564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28770923614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19251298904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1232795715332</t>
+    <t xml:space="preserve">5.28770875930786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19251251220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12327909469604</t>
   </si>
   <si>
     <t xml:space="preserve">5.27040004730225</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08000802993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14924144744873</t>
+    <t xml:space="preserve">5.0800085067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14924240112305</t>
   </si>
   <si>
     <t xml:space="preserve">5.16655015945435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15789556503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29636335372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53868055343628</t>
+    <t xml:space="preserve">5.15789604187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29636240005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53868007659912</t>
   </si>
   <si>
     <t xml:space="preserve">5.44348430633545</t>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">5.40021276473999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36559581756592</t>
+    <t xml:space="preserve">5.36559629440308</t>
   </si>
   <si>
     <t xml:space="preserve">5.32232570648193</t>
@@ -1967,10 +1967,10 @@
     <t xml:space="preserve">5.04539155960083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16222333908081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03933334350586</t>
+    <t xml:space="preserve">5.16222286224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03933382034302</t>
   </si>
   <si>
     <t xml:space="preserve">5.10597085952759</t>
@@ -1979,13 +1979,13 @@
     <t xml:space="preserve">5.15270328521729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20895528793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27905416488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34569215774536</t>
+    <t xml:space="preserve">5.20895576477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27905464172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3456916809082</t>
   </si>
   <si>
     <t xml:space="preserve">5.32665252685547</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">5.27992010116577</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30588245391846</t>
+    <t xml:space="preserve">5.30588293075562</t>
   </si>
   <si>
     <t xml:space="preserve">5.26780414581299</t>
@@ -2006,13 +2006,13 @@
     <t xml:space="preserve">5.21934080123901</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34309577941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48502397537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43915748596191</t>
+    <t xml:space="preserve">5.34309530258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48502445220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4391565322876</t>
   </si>
   <si>
     <t xml:space="preserve">5.31799840927124</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">5.61656808853149</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51617956161499</t>
+    <t xml:space="preserve">5.51617908477783</t>
   </si>
   <si>
     <t xml:space="preserve">5.46252298355103</t>
@@ -2033,19 +2033,19 @@
     <t xml:space="preserve">5.42271423339844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4677152633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44435024261475</t>
+    <t xml:space="preserve">5.46771621704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44434928894043</t>
   </si>
   <si>
     <t xml:space="preserve">5.46944665908813</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78099727630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02331447601318</t>
+    <t xml:space="preserve">5.78099775314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02331495285034</t>
   </si>
   <si>
     <t xml:space="preserve">6.0406231880188</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">6.04927730560303</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94456100463867</t>
+    <t xml:space="preserve">5.94456148147583</t>
   </si>
   <si>
     <t xml:space="preserve">5.76974725723267</t>
@@ -2063,19 +2063,19 @@
     <t xml:space="preserve">5.78272819519043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75417041778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74118804931641</t>
+    <t xml:space="preserve">5.75416898727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74118757247925</t>
   </si>
   <si>
     <t xml:space="preserve">5.73945713043213</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81042242050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90561819076538</t>
+    <t xml:space="preserve">5.81042194366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90561771392822</t>
   </si>
   <si>
     <t xml:space="preserve">5.93331146240234</t>
@@ -2087,7 +2087,7 @@
     <t xml:space="preserve">5.91081047058105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92638874053955</t>
+    <t xml:space="preserve">5.92638778686523</t>
   </si>
   <si>
     <t xml:space="preserve">5.85369253158569</t>
@@ -2102,19 +2102,19 @@
     <t xml:space="preserve">5.73253393173218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81907653808594</t>
+    <t xml:space="preserve">5.81907606124878</t>
   </si>
   <si>
     <t xml:space="preserve">5.90648317337036</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70570611953735</t>
+    <t xml:space="preserve">5.7057056427002</t>
   </si>
   <si>
     <t xml:space="preserve">5.57502746582031</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75590085983276</t>
+    <t xml:space="preserve">5.75590038299561</t>
   </si>
   <si>
     <t xml:space="preserve">5.81561374664307</t>
@@ -2126,19 +2126,19 @@
     <t xml:space="preserve">5.73512983322144</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72041797637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69791746139526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69272422790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62868404388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75936269760132</t>
+    <t xml:space="preserve">5.72041845321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69791793823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69272470474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62868356704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.759361743927</t>
   </si>
   <si>
     <t xml:space="preserve">5.65810823440552</t>
@@ -2147,37 +2147,37 @@
     <t xml:space="preserve">5.57243156433105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62522220611572</t>
+    <t xml:space="preserve">5.62522172927856</t>
   </si>
   <si>
     <t xml:space="preserve">5.6728196144104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58195114135742</t>
+    <t xml:space="preserve">5.58195161819458</t>
   </si>
   <si>
     <t xml:space="preserve">5.58454751968384</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64512634277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72561025619507</t>
+    <t xml:space="preserve">5.64512586593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72561120986938</t>
   </si>
   <si>
     <t xml:space="preserve">5.61483716964722</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60704898834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65291500091553</t>
+    <t xml:space="preserve">5.60704851150513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65291547775269</t>
   </si>
   <si>
     <t xml:space="preserve">5.6555118560791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75503492355347</t>
+    <t xml:space="preserve">5.75503444671631</t>
   </si>
   <si>
     <t xml:space="preserve">5.84071111679077</t>
@@ -2186,7 +2186,7 @@
     <t xml:space="preserve">6.00600671768188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92811870574951</t>
+    <t xml:space="preserve">5.92811822891235</t>
   </si>
   <si>
     <t xml:space="preserve">5.87619352340698</t>
@@ -2201,19 +2201,19 @@
     <t xml:space="preserve">5.36213493347168</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19510841369629</t>
+    <t xml:space="preserve">5.19510889053345</t>
   </si>
   <si>
     <t xml:space="preserve">5.040198802948</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1544337272644</t>
+    <t xml:space="preserve">5.15443420410156</t>
   </si>
   <si>
     <t xml:space="preserve">5.18039655685425</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79615116119385</t>
+    <t xml:space="preserve">4.79615020751953</t>
   </si>
   <si>
     <t xml:space="preserve">4.24358129501343</t>
@@ -2225,52 +2225,52 @@
     <t xml:space="preserve">4.30718946456909</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94501137733459</t>
+    <t xml:space="preserve">3.94501113891602</t>
   </si>
   <si>
     <t xml:space="preserve">4.11073923110962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9809262752533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77452397346497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89438486099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17564487457275</t>
+    <t xml:space="preserve">3.98092651367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77452373504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89438462257385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17564535140991</t>
   </si>
   <si>
     <t xml:space="preserve">3.82385277748108</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97486853599548</t>
+    <t xml:space="preserve">3.9748682975769</t>
   </si>
   <si>
     <t xml:space="preserve">4.07006454467773</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27386999130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11766242980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05665016174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25699520111084</t>
+    <t xml:space="preserve">4.27387094497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11766290664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05665063858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25699424743652</t>
   </si>
   <si>
     <t xml:space="preserve">4.30978584289551</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37036514282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17131853103638</t>
+    <t xml:space="preserve">4.37036561965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17131900787354</t>
   </si>
   <si>
     <t xml:space="preserve">4.32709407806396</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">4.62999057769775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.569411277771</t>
+    <t xml:space="preserve">4.56941175460815</t>
   </si>
   <si>
     <t xml:space="preserve">4.57806539535522</t>
@@ -2300,16 +2300,16 @@
     <t xml:space="preserve">4.50017738342285</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74249505996704</t>
+    <t xml:space="preserve">4.7424955368042</t>
   </si>
   <si>
     <t xml:space="preserve">4.76845741271973</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79441976547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94154167175293</t>
+    <t xml:space="preserve">4.79441928863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94154119491577</t>
   </si>
   <si>
     <t xml:space="preserve">4.91557884216309</t>
@@ -2327,22 +2327,22 @@
     <t xml:space="preserve">4.62133646011353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67326211929321</t>
+    <t xml:space="preserve">4.6732611656189</t>
   </si>
   <si>
     <t xml:space="preserve">4.80307483673096</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90961265563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8030743598938</t>
+    <t xml:space="preserve">4.90961170196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80307388305664</t>
   </si>
   <si>
     <t xml:space="preserve">4.73204946517944</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88297700881958</t>
+    <t xml:space="preserve">4.88297748565674</t>
   </si>
   <si>
     <t xml:space="preserve">4.91848993301392</t>
@@ -2351,16 +2351,16 @@
     <t xml:space="preserve">5.10493087768555</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22034740447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19371223449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39790916442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44230079650879</t>
+    <t xml:space="preserve">5.22034645080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19371271133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39790964126587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44230031967163</t>
   </si>
   <si>
     <t xml:space="preserve">5.30025005340576</t>
@@ -2372,13 +2372,13 @@
     <t xml:space="preserve">5.49556922912598</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60210704803467</t>
+    <t xml:space="preserve">5.60210657119751</t>
   </si>
   <si>
     <t xml:space="preserve">5.72640085220337</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81518220901489</t>
+    <t xml:space="preserve">5.81518268585205</t>
   </si>
   <si>
     <t xml:space="preserve">5.63761949539185</t>
@@ -2390,22 +2390,22 @@
     <t xml:space="preserve">5.27361583709717</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23810338973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55771636962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73527860641479</t>
+    <t xml:space="preserve">5.23810291290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55771684646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73527908325195</t>
   </si>
   <si>
     <t xml:space="preserve">5.61098527908325</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65537595748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68201065063477</t>
+    <t xml:space="preserve">5.65537548065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68201017379761</t>
   </si>
   <si>
     <t xml:space="preserve">5.61986303329468</t>
@@ -2420,13 +2420,13 @@
     <t xml:space="preserve">5.5843505859375</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56659460067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53108215332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4600567817688</t>
+    <t xml:space="preserve">5.56659364700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53108167648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46005725860596</t>
   </si>
   <si>
     <t xml:space="preserve">5.35351943969727</t>
@@ -2435,70 +2435,70 @@
     <t xml:space="preserve">5.42454433441162</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41566562652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31800603866577</t>
+    <t xml:space="preserve">5.41566610336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31800556182861</t>
   </si>
   <si>
     <t xml:space="preserve">5.38903188705444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29137229919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21146869659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36239671707153</t>
+    <t xml:space="preserve">5.29137277603149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2114691734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36239719390869</t>
   </si>
   <si>
     <t xml:space="preserve">5.25585985183716</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26473712921143</t>
+    <t xml:space="preserve">5.26473760604858</t>
   </si>
   <si>
     <t xml:space="preserve">5.37127542495728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48669099807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59322834014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53995943069458</t>
+    <t xml:space="preserve">5.48669052124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59322929382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53995990753174</t>
   </si>
   <si>
     <t xml:space="preserve">5.5044469833374</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3801531791687</t>
+    <t xml:space="preserve">5.38015365600586</t>
   </si>
   <si>
     <t xml:space="preserve">5.34464073181152</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28249311447144</t>
+    <t xml:space="preserve">5.28249359130859</t>
   </si>
   <si>
     <t xml:space="preserve">5.20259046554565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32688522338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33576345443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24698066711426</t>
+    <t xml:space="preserve">5.32688426971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3357629776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24698114395142</t>
   </si>
   <si>
     <t xml:space="preserve">5.15819978713989</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1315655708313</t>
+    <t xml:space="preserve">5.13156604766846</t>
   </si>
   <si>
     <t xml:space="preserve">5.16707801818848</t>
@@ -2507,31 +2507,31 @@
     <t xml:space="preserve">5.18483400344849</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02502822875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90073394775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61663341522217</t>
+    <t xml:space="preserve">5.02502775192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90073347091675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61663293838501</t>
   </si>
   <si>
     <t xml:space="preserve">4.7231707572937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85634231567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99839353561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0072717666626</t>
+    <t xml:space="preserve">4.85634279251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99839401245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00727128982544</t>
   </si>
   <si>
     <t xml:space="preserve">4.89185571670532</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98951482772827</t>
+    <t xml:space="preserve">4.98951435089111</t>
   </si>
   <si>
     <t xml:space="preserve">5.90396356582642</t>
@@ -2546,22 +2546,22 @@
     <t xml:space="preserve">5.9927453994751</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09928274154663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10816144943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35674810409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18806409835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2413330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28572368621826</t>
+    <t xml:space="preserve">6.09928226470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10816097259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35674858093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.188063621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24133348464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2857232093811</t>
   </si>
   <si>
     <t xml:space="preserve">6.32123613357544</t>
@@ -2573,7 +2573,7 @@
     <t xml:space="preserve">6.30348014831543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31235837936401</t>
+    <t xml:space="preserve">6.31235885620117</t>
   </si>
   <si>
     <t xml:space="preserve">6.11703872680664</t>
@@ -2585,10 +2585,10 @@
     <t xml:space="preserve">6.06377029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05489206314087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98386716842651</t>
+    <t xml:space="preserve">6.05489253997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98386669158936</t>
   </si>
   <si>
     <t xml:space="preserve">5.96611022949219</t>
@@ -2597,19 +2597,19 @@
     <t xml:space="preserve">5.93947601318359</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94835472106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92171955108643</t>
+    <t xml:space="preserve">5.94835376739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92172002792358</t>
   </si>
   <si>
     <t xml:space="preserve">5.912841796875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23245429992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46328639984131</t>
+    <t xml:space="preserve">6.23245477676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46328687667847</t>
   </si>
   <si>
     <t xml:space="preserve">6.33011436462402</t>
@@ -2618,16 +2618,16 @@
     <t xml:space="preserve">6.27684593200684</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20582056045532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04601383209229</t>
+    <t xml:space="preserve">6.20582008361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04601430892944</t>
   </si>
   <si>
     <t xml:space="preserve">6.37450551986694</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12591695785522</t>
+    <t xml:space="preserve">6.12591743469238</t>
   </si>
   <si>
     <t xml:space="preserve">6.21469879150391</t>
@@ -2636,34 +2636,34 @@
     <t xml:space="preserve">6.17918634414673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26796817779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48104333877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66748380661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01373100280762</t>
+    <t xml:space="preserve">6.26796722412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48104286193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66748428344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01373147964478</t>
   </si>
   <si>
     <t xml:space="preserve">7.43988227844238</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54641914367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59968900680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63520193099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68847036361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52866363525391</t>
+    <t xml:space="preserve">7.54641962051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59968948364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63520288467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68846893310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52866315841675</t>
   </si>
   <si>
     <t xml:space="preserve">7.31558799743652</t>
@@ -2678,7 +2678,7 @@
     <t xml:space="preserve">7.29783153533936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13802576065063</t>
+    <t xml:space="preserve">7.13802528381348</t>
   </si>
   <si>
     <t xml:space="preserve">7.04924345016479</t>
@@ -2687,139 +2687,139 @@
     <t xml:space="preserve">7.19129467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21792936325073</t>
+    <t xml:space="preserve">7.21792888641357</t>
   </si>
   <si>
     <t xml:space="preserve">7.3511004447937</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48427295684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59081077575684</t>
+    <t xml:space="preserve">7.4842734336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59081029891968</t>
   </si>
   <si>
     <t xml:space="preserve">7.58193206787109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65295743942261</t>
+    <t xml:space="preserve">7.65295791625977</t>
   </si>
   <si>
     <t xml:space="preserve">7.51090717315674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45763874053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17353773117065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61744403839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6795916557312</t>
+    <t xml:space="preserve">7.45763826370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17353820800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61744451522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67959213256836</t>
   </si>
   <si>
     <t xml:space="preserve">7.76837253570557</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93705701828003</t>
+    <t xml:space="preserve">7.93705749511719</t>
   </si>
   <si>
     <t xml:space="preserve">8.19452381134033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09686374664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99920511245728</t>
+    <t xml:space="preserve">8.09686470031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99920463562012</t>
   </si>
   <si>
     <t xml:space="preserve">8.17676734924316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20340156555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99032688140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08798694610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05247402191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0435962677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00808238983154</t>
+    <t xml:space="preserve">8.20340061187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99032735824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08798599243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05247497558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04359531402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00808334350586</t>
   </si>
   <si>
     <t xml:space="preserve">8.07910823822021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14125442504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07022953033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15013408660889</t>
+    <t xml:space="preserve">8.14125537872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07023048400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15013313293457</t>
   </si>
   <si>
     <t xml:space="preserve">8.38984298706055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23891353607178</t>
+    <t xml:space="preserve">8.23891448974609</t>
   </si>
   <si>
     <t xml:space="preserve">8.44311237335205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38096523284912</t>
+    <t xml:space="preserve">8.3809642791748</t>
   </si>
   <si>
     <t xml:space="preserve">8.51413726806641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43423366546631</t>
+    <t xml:space="preserve">8.43423461914062</t>
   </si>
   <si>
     <t xml:space="preserve">8.64730834960938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42535591125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47014331817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60530662536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43410015106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4160795211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37102508544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56025314331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31695938110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42508983612061</t>
+    <t xml:space="preserve">8.42535495758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47014427185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60530757904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43410110473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41608047485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37102603912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56025123596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31696033477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42509174346924</t>
   </si>
   <si>
     <t xml:space="preserve">8.62332725524902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75848960876465</t>
+    <t xml:space="preserve">8.75849056243896</t>
   </si>
   <si>
     <t xml:space="preserve">8.6593713760376</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">8.70442485809326</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7404670715332</t>
+    <t xml:space="preserve">8.74046802520752</t>
   </si>
   <si>
     <t xml:space="preserve">8.68640327453613</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">8.47915554046631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50618743896484</t>
+    <t xml:space="preserve">8.50618648529053</t>
   </si>
   <si>
     <t xml:space="preserve">8.51519775390625</t>
@@ -2849,10 +2849,10 @@
     <t xml:space="preserve">8.46113395690918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27190685272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10971260070801</t>
+    <t xml:space="preserve">8.27190780639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10971355438232</t>
   </si>
   <si>
     <t xml:space="preserve">8.15476608276367</t>
@@ -2864,13 +2864,13 @@
     <t xml:space="preserve">8.0466365814209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05564785003662</t>
+    <t xml:space="preserve">8.05564880371094</t>
   </si>
   <si>
     <t xml:space="preserve">7.95652914047241</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00158309936523</t>
+    <t xml:space="preserve">8.00158405303955</t>
   </si>
   <si>
     <t xml:space="preserve">7.74928140640259</t>
@@ -2879,37 +2879,37 @@
     <t xml:space="preserve">7.8574104309082</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78532457351685</t>
+    <t xml:space="preserve">7.78532409667969</t>
   </si>
   <si>
     <t xml:space="preserve">7.83938837051392</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74027013778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99257278442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92048597335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1727876663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29893970489502</t>
+    <t xml:space="preserve">7.74027109146118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99257135391235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.920485496521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17278671264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2989387512207</t>
   </si>
   <si>
     <t xml:space="preserve">8.16377830505371</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21784114837646</t>
+    <t xml:space="preserve">8.21784210205078</t>
   </si>
   <si>
     <t xml:space="preserve">7.96553993225098</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6051082611084</t>
+    <t xml:space="preserve">7.60510778427124</t>
   </si>
   <si>
     <t xml:space="preserve">8.07366943359375</t>
@@ -2918,22 +2918,22 @@
     <t xml:space="preserve">8.24487400054932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12773513793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4881649017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38904762268066</t>
+    <t xml:space="preserve">8.12773418426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48816585540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38904666900635</t>
   </si>
   <si>
     <t xml:space="preserve">8.35300445556641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33498382568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71343517303467</t>
+    <t xml:space="preserve">8.33498191833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71343612670898</t>
   </si>
   <si>
     <t xml:space="preserve">8.63233852386475</t>
@@ -2942,13 +2942,13 @@
     <t xml:space="preserve">8.23586463928223</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30795097351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64134883880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77651119232178</t>
+    <t xml:space="preserve">8.30795001983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64134979248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77651023864746</t>
   </si>
   <si>
     <t xml:space="preserve">8.55124187469482</t>
@@ -2960,55 +2960,55 @@
     <t xml:space="preserve">8.25388526916504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19982147216797</t>
+    <t xml:space="preserve">8.19982051849365</t>
   </si>
   <si>
     <t xml:space="preserve">8.03762626647949</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92949724197388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98356199264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01960468292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88444328308105</t>
+    <t xml:space="preserve">7.92949771881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98356151580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01960372924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88444185256958</t>
   </si>
   <si>
     <t xml:space="preserve">7.56906509399414</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63214111328125</t>
+    <t xml:space="preserve">7.63214015960693</t>
   </si>
   <si>
     <t xml:space="preserve">7.57807588577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55104351043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65917301177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67719554901123</t>
+    <t xml:space="preserve">7.55104398727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65917253494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67719459533691</t>
   </si>
   <si>
     <t xml:space="preserve">7.72224855422974</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7673020362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71323871612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93850803375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2268533706665</t>
+    <t xml:space="preserve">7.76730298995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71323823928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93850755691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22685146331787</t>
   </si>
   <si>
     <t xml:space="preserve">8.19080924987793</t>
@@ -3023,16 +3023,16 @@
     <t xml:space="preserve">8.18179893493652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02861595153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8033447265625</t>
+    <t xml:space="preserve">8.02861499786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80334520339966</t>
   </si>
   <si>
     <t xml:space="preserve">7.69521570205688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61411905288696</t>
+    <t xml:space="preserve">7.6141185760498</t>
   </si>
   <si>
     <t xml:space="preserve">7.37983798980713</t>
@@ -3041,25 +3041,25 @@
     <t xml:space="preserve">7.33478450775146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37082767486572</t>
+    <t xml:space="preserve">7.37082815170288</t>
   </si>
   <si>
     <t xml:space="preserve">7.46093559265137</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36181735992432</t>
+    <t xml:space="preserve">7.36181688308716</t>
   </si>
   <si>
     <t xml:space="preserve">7.35280609130859</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4429144859314</t>
+    <t xml:space="preserve">7.44291400909424</t>
   </si>
   <si>
     <t xml:space="preserve">7.65016174316406</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46994638442993</t>
+    <t xml:space="preserve">7.46994590759277</t>
   </si>
   <si>
     <t xml:space="preserve">7.39786005020142</t>
@@ -3068,49 +3068,49 @@
     <t xml:space="preserve">7.3257737159729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27170848846436</t>
+    <t xml:space="preserve">7.27170896530151</t>
   </si>
   <si>
     <t xml:space="preserve">7.30775165557861</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29874134063721</t>
+    <t xml:space="preserve">7.29874181747437</t>
   </si>
   <si>
     <t xml:space="preserve">7.26269865036011</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54203271865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64115047454834</t>
+    <t xml:space="preserve">7.54203224182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6411509513855</t>
   </si>
   <si>
     <t xml:space="preserve">7.62312984466553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53302145004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52401113510132</t>
+    <t xml:space="preserve">7.53302097320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52401065826416</t>
   </si>
   <si>
     <t xml:space="preserve">7.31676292419434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38884973526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4519248008728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96534204483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92929887771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02841806411743</t>
+    <t xml:space="preserve">7.38884878158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45192527770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96534252166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92929935455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02841758728027</t>
   </si>
   <si>
     <t xml:space="preserve">6.89325571060181</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">7.0103964805603</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12753582000732</t>
+    <t xml:space="preserve">7.12753629684448</t>
   </si>
   <si>
     <t xml:space="preserve">7.11852550506592</t>
@@ -3128,7 +3128,7 @@
     <t xml:space="preserve">6.94732046127319</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8842453956604</t>
+    <t xml:space="preserve">6.88424491882324</t>
   </si>
   <si>
     <t xml:space="preserve">6.90226650238037</t>
@@ -3140,37 +3140,37 @@
     <t xml:space="preserve">7.22665548324585</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03742790222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14555788040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19962215423584</t>
+    <t xml:space="preserve">7.03742837905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14555740356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.199622631073</t>
   </si>
   <si>
     <t xml:space="preserve">7.00138521194458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07347106933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80314779281616</t>
+    <t xml:space="preserve">7.0734715461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80314826965332</t>
   </si>
   <si>
     <t xml:space="preserve">6.74007177352905</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6679859161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36161947250366</t>
+    <t xml:space="preserve">6.66798639297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3616189956665</t>
   </si>
   <si>
     <t xml:space="preserve">6.59589958190918</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41568422317505</t>
+    <t xml:space="preserve">6.41568374633789</t>
   </si>
   <si>
     <t xml:space="preserve">6.32557582855225</t>
@@ -3182,16 +3182,16 @@
     <t xml:space="preserve">5.85701465606689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83899307250977</t>
+    <t xml:space="preserve">5.83899354934692</t>
   </si>
   <si>
     <t xml:space="preserve">6.01019811630249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28052139282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09129524230957</t>
+    <t xml:space="preserve">6.28052186965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09129571914673</t>
   </si>
   <si>
     <t xml:space="preserve">6.14535999298096</t>
@@ -3200,25 +3200,25 @@
     <t xml:space="preserve">6.35260820388794</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23546838760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46974849700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38865184783936</t>
+    <t xml:space="preserve">6.2354679107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46974802017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3886513710022</t>
   </si>
   <si>
     <t xml:space="preserve">6.37062978744507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28953313827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31656551361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02822017669678</t>
+    <t xml:space="preserve">6.28953266143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31656503677368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02821969985962</t>
   </si>
   <si>
     <t xml:space="preserve">6.11832761764526</t>
@@ -3230,22 +3230,22 @@
     <t xml:space="preserve">6.27151107788086</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26250028610229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18140363693237</t>
+    <t xml:space="preserve">6.26249980926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18140316009521</t>
   </si>
   <si>
     <t xml:space="preserve">6.29854297637939</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17239189147949</t>
+    <t xml:space="preserve">6.17239284515381</t>
   </si>
   <si>
     <t xml:space="preserve">5.84800386428833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86602544784546</t>
+    <t xml:space="preserve">5.86602592468262</t>
   </si>
   <si>
     <t xml:space="preserve">5.920090675354</t>
@@ -3254,7 +3254,7 @@
     <t xml:space="preserve">5.89305782318115</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93811178207397</t>
+    <t xml:space="preserve">5.93811225891113</t>
   </si>
   <si>
     <t xml:space="preserve">5.88404703140259</t>
@@ -3275,25 +3275,25 @@
     <t xml:space="preserve">5.94712257385254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0192084312439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99217653274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96514368057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97415542602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95613384246826</t>
+    <t xml:space="preserve">6.01920890808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99217700958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96514415740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97415494918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9561333656311</t>
   </si>
   <si>
     <t xml:space="preserve">6.08228492736816</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07327318191528</t>
+    <t xml:space="preserve">6.07327365875244</t>
   </si>
   <si>
     <t xml:space="preserve">6.03723001480103</t>
@@ -3305,22 +3305,22 @@
     <t xml:space="preserve">5.94737577438354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96590328216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1604437828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28087329864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22529029846191</t>
+    <t xml:space="preserve">5.96590280532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16044425964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28087377548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22528982162476</t>
   </si>
   <si>
     <t xml:space="preserve">6.20676231384277</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17897129058838</t>
+    <t xml:space="preserve">6.17897176742554</t>
   </si>
   <si>
     <t xml:space="preserve">6.29013729095459</t>
@@ -3338,13 +3338,13 @@
     <t xml:space="preserve">5.81768274307251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83620977401733</t>
+    <t xml:space="preserve">5.83621025085449</t>
   </si>
   <si>
     <t xml:space="preserve">5.92884826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89179277420044</t>
+    <t xml:space="preserve">5.8917932510376</t>
   </si>
   <si>
     <t xml:space="preserve">6.09559679031372</t>
@@ -3356,19 +3356,19 @@
     <t xml:space="preserve">5.95663928985596</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82694578170776</t>
+    <t xml:space="preserve">5.82694625854492</t>
   </si>
   <si>
     <t xml:space="preserve">5.68798828125</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78062677383423</t>
+    <t xml:space="preserve">5.78062629699707</t>
   </si>
   <si>
     <t xml:space="preserve">5.73430776596069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72504377365112</t>
+    <t xml:space="preserve">5.72504425048828</t>
   </si>
   <si>
     <t xml:space="preserve">5.34522676467896</t>
@@ -3377,25 +3377,25 @@
     <t xml:space="preserve">5.44712924957275</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60461473464966</t>
+    <t xml:space="preserve">5.6046142578125</t>
   </si>
   <si>
     <t xml:space="preserve">5.75283527374268</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51197576522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85473775863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55829477310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71578025817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77136325836182</t>
+    <t xml:space="preserve">5.51197528839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85473728179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55829524993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71578073501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77136278152466</t>
   </si>
   <si>
     <t xml:space="preserve">5.61387777328491</t>
@@ -3404,13 +3404,13 @@
     <t xml:space="preserve">5.66019725799561</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87326574325562</t>
+    <t xml:space="preserve">5.8732647895813</t>
   </si>
   <si>
     <t xml:space="preserve">5.66946077346802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80841827392578</t>
+    <t xml:space="preserve">5.80841875076294</t>
   </si>
   <si>
     <t xml:space="preserve">6.0307502746582</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">5.86400079727173</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53976726531982</t>
+    <t xml:space="preserve">5.53976774215698</t>
   </si>
   <si>
     <t xml:space="preserve">5.49344825744629</t>
@@ -3431,7 +3431,7 @@
     <t xml:space="preserve">5.47492074966431</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37301874160767</t>
+    <t xml:space="preserve">5.37301921844482</t>
   </si>
   <si>
     <t xml:space="preserve">5.39154624938965</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">5.15995073318481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21553325653076</t>
+    <t xml:space="preserve">5.21553373336792</t>
   </si>
   <si>
     <t xml:space="preserve">5.19700622558594</t>
@@ -3458,13 +3458,13 @@
     <t xml:space="preserve">5.25258874893188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38228178024292</t>
+    <t xml:space="preserve">5.38228273391724</t>
   </si>
   <si>
     <t xml:space="preserve">5.13215923309326</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10436773300171</t>
+    <t xml:space="preserve">5.10436820983887</t>
   </si>
   <si>
     <t xml:space="preserve">5.28038024902344</t>
@@ -3476,28 +3476,28 @@
     <t xml:space="preserve">5.2340612411499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08583974838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05804872512817</t>
+    <t xml:space="preserve">5.08583927154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05804824829102</t>
   </si>
   <si>
     <t xml:space="preserve">5.01172924041748</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02099323272705</t>
+    <t xml:space="preserve">5.02099370956421</t>
   </si>
   <si>
     <t xml:space="preserve">5.1784782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04878425598145</t>
+    <t xml:space="preserve">5.0487847328186</t>
   </si>
   <si>
     <t xml:space="preserve">5.15068674087524</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00246524810791</t>
+    <t xml:space="preserve">5.00246572494507</t>
   </si>
   <si>
     <t xml:space="preserve">4.8635082244873</t>
@@ -3512,19 +3512,19 @@
     <t xml:space="preserve">4.96541023254395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22479772567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3359637260437</t>
+    <t xml:space="preserve">5.22479724884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33596324920654</t>
   </si>
   <si>
     <t xml:space="preserve">5.30817174911499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45639276504517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52123975753784</t>
+    <t xml:space="preserve">5.45639324188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52123928070068</t>
   </si>
   <si>
     <t xml:space="preserve">5.29890775680542</t>
@@ -3539,22 +3539,22 @@
     <t xml:space="preserve">5.67872476577759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76209926605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90105628967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91958379745483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70651626586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74357175827026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65093278884888</t>
+    <t xml:space="preserve">5.76209878921509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90105676651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91958427429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70651578903198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74357128143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65093326568604</t>
   </si>
   <si>
     <t xml:space="preserve">5.63240575790405</t>
@@ -3566,10 +3566,10 @@
     <t xml:space="preserve">5.64166975021362</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88252878189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99369430541992</t>
+    <t xml:space="preserve">5.88252830505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99369478225708</t>
   </si>
   <si>
     <t xml:space="preserve">5.98443126678467</t>
@@ -3599,13 +3599,13 @@
     <t xml:space="preserve">6.89228582382202</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96639633178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23504686355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34621334075928</t>
+    <t xml:space="preserve">6.96639680862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23504734039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34621286392212</t>
   </si>
   <si>
     <t xml:space="preserve">7.38326835632324</t>
@@ -3623,13 +3623,13 @@
     <t xml:space="preserve">7.42958831787109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55928134918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39253234863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59633684158325</t>
+    <t xml:space="preserve">7.55928087234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39253282546997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59633636474609</t>
   </si>
   <si>
     <t xml:space="preserve">7.54075384140015</t>
@@ -3638,25 +3638,25 @@
     <t xml:space="preserve">7.64265584945679</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50369834899902</t>
+    <t xml:space="preserve">7.50369882583618</t>
   </si>
   <si>
     <t xml:space="preserve">7.63339185714722</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62412738800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57780885696411</t>
+    <t xml:space="preserve">7.62412786483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57780933380127</t>
   </si>
   <si>
     <t xml:space="preserve">7.58707237243652</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45737981796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43885135650635</t>
+    <t xml:space="preserve">7.45737934112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43885087966919</t>
   </si>
   <si>
     <t xml:space="preserve">7.08682632446289</t>
@@ -3665,19 +3665,19 @@
     <t xml:space="preserve">7.32768535614014</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10535430908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18872880935669</t>
+    <t xml:space="preserve">7.10535335540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18872833251953</t>
   </si>
   <si>
     <t xml:space="preserve">7.42032432556152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30915784835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29062986373901</t>
+    <t xml:space="preserve">7.30915832519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29063034057617</t>
   </si>
   <si>
     <t xml:space="preserve">7.16093683242798</t>
@@ -3686,7 +3686,7 @@
     <t xml:space="preserve">7.29989433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24431180953979</t>
+    <t xml:space="preserve">7.24431133270264</t>
   </si>
   <si>
     <t xml:space="preserve">7.21651983261108</t>
@@ -3695,13 +3695,13 @@
     <t xml:space="preserve">7.27210235595703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20725631713867</t>
+    <t xml:space="preserve">7.20725584030151</t>
   </si>
   <si>
     <t xml:space="preserve">7.33694934844971</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31842184066772</t>
+    <t xml:space="preserve">7.31842231750488</t>
   </si>
   <si>
     <t xml:space="preserve">7.26283884048462</t>
@@ -3710,28 +3710,28 @@
     <t xml:space="preserve">7.12388134002686</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04977083206177</t>
+    <t xml:space="preserve">7.04977130889893</t>
   </si>
   <si>
     <t xml:space="preserve">6.98492383956909</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07756280899048</t>
+    <t xml:space="preserve">7.07756233215332</t>
   </si>
   <si>
     <t xml:space="preserve">7.22578382492065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19799184799194</t>
+    <t xml:space="preserve">7.1979923248291</t>
   </si>
   <si>
     <t xml:space="preserve">7.15167284011841</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11461782455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05903434753418</t>
+    <t xml:space="preserve">7.11461734771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05903482437134</t>
   </si>
   <si>
     <t xml:space="preserve">7.06857395172119</t>
@@ -3746,34 +3746,34 @@
     <t xml:space="preserve">6.94456434249878</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86824989318848</t>
+    <t xml:space="preserve">6.86825037002563</t>
   </si>
   <si>
     <t xml:space="preserve">6.79193639755249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75377941131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84917163848877</t>
+    <t xml:space="preserve">6.75377893447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84917116165161</t>
   </si>
   <si>
     <t xml:space="preserve">6.99226045608521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95410346984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87778902053833</t>
+    <t xml:space="preserve">6.95410299301147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87778949737549</t>
   </si>
   <si>
     <t xml:space="preserve">6.98272132873535</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96364259719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03041744232178</t>
+    <t xml:space="preserve">6.96364307403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03041696548462</t>
   </si>
   <si>
     <t xml:space="preserve">7.01133871078491</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">6.78239727020264</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7251615524292</t>
+    <t xml:space="preserve">6.72516202926636</t>
   </si>
   <si>
     <t xml:space="preserve">7.00179958343506</t>
@@ -3812,19 +3812,19 @@
     <t xml:space="preserve">7.36429023742676</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28797674179077</t>
+    <t xml:space="preserve">7.28797626495361</t>
   </si>
   <si>
     <t xml:space="preserve">7.29751586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30705499649048</t>
+    <t xml:space="preserve">7.30705451965332</t>
   </si>
   <si>
     <t xml:space="preserve">7.53599691390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57415390014648</t>
+    <t xml:space="preserve">7.57415342330933</t>
   </si>
   <si>
     <t xml:space="preserve">7.66000652313232</t>
@@ -3833,10 +3833,10 @@
     <t xml:space="preserve">7.6981635093689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93664455413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98434066772461</t>
+    <t xml:space="preserve">7.93664407730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98434019088745</t>
   </si>
   <si>
     <t xml:space="preserve">8.18466472625732</t>
@@ -3854,19 +3854,19 @@
     <t xml:space="preserve">8.16558647155762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04157733917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8794093132019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97480154037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03203678131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90802717208862</t>
+    <t xml:space="preserve">8.04157638549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87940979003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9748010635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03203773498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90802669525146</t>
   </si>
   <si>
     <t xml:space="preserve">7.89848756790161</t>
@@ -3878,7 +3878,7 @@
     <t xml:space="preserve">7.84125232696533</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88894844055176</t>
+    <t xml:space="preserve">7.88894891738892</t>
   </si>
   <si>
     <t xml:space="preserve">7.78401708602905</t>
@@ -3887,7 +3887,7 @@
     <t xml:space="preserve">7.81263399124146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85079050064087</t>
+    <t xml:space="preserve">7.85079145431519</t>
   </si>
   <si>
     <t xml:space="preserve">7.77447748184204</t>
@@ -3902,13 +3902,13 @@
     <t xml:space="preserve">7.72678184509277</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64092874526978</t>
+    <t xml:space="preserve">7.64092826843262</t>
   </si>
   <si>
     <t xml:space="preserve">7.58369255065918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38336896896362</t>
+    <t xml:space="preserve">7.38336849212646</t>
   </si>
   <si>
     <t xml:space="preserve">7.3356728553772</t>
@@ -3929,7 +3929,7 @@
     <t xml:space="preserve">7.08765268325806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15442705154419</t>
+    <t xml:space="preserve">7.15442752838135</t>
   </si>
   <si>
     <t xml:space="preserve">7.03995656967163</t>
@@ -3941,7 +3941,7 @@
     <t xml:space="preserve">7.27843761444092</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41198635101318</t>
+    <t xml:space="preserve">7.41198682785034</t>
   </si>
   <si>
     <t xml:space="preserve">7.39290809631348</t>
@@ -3962,13 +3962,13 @@
     <t xml:space="preserve">7.45014333724976</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40244770050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50737857818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70770263671875</t>
+    <t xml:space="preserve">7.40244722366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50737905502319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70770311355591</t>
   </si>
   <si>
     <t xml:space="preserve">8.20374393463135</t>
@@ -3983,10 +3983,10 @@
     <t xml:space="preserve">8.10835075378418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08927249908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36591053009033</t>
+    <t xml:space="preserve">8.08927154541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36591148376465</t>
   </si>
   <si>
     <t xml:space="preserve">8.30867481231689</t>
@@ -4004,13 +4004,13 @@
     <t xml:space="preserve">8.60439205169678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40406703948975</t>
+    <t xml:space="preserve">8.40406799316406</t>
   </si>
   <si>
     <t xml:space="preserve">8.41360664367676</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26097774505615</t>
+    <t xml:space="preserve">8.26097869873047</t>
   </si>
   <si>
     <t xml:space="preserve">8.57577323913574</t>
@@ -4025,10 +4025,10 @@
     <t xml:space="preserve">8.76655769348145</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1576681137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19582462310791</t>
+    <t xml:space="preserve">9.15766716003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19582366943359</t>
   </si>
   <si>
     <t xml:space="preserve">9.11951065063477</t>
@@ -4037,13 +4037,13 @@
     <t xml:space="preserve">9.10043144226074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09089183807373</t>
+    <t xml:space="preserve">9.09089279174805</t>
   </si>
   <si>
     <t xml:space="preserve">8.72840118408203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87149047851562</t>
+    <t xml:space="preserve">8.87148952484131</t>
   </si>
   <si>
     <t xml:space="preserve">8.90964698791504</t>
@@ -4067,7 +4067,7 @@
     <t xml:space="preserve">9.00503826141357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20536327362061</t>
+    <t xml:space="preserve">9.20536231994629</t>
   </si>
   <si>
     <t xml:space="preserve">9.45338344573975</t>
@@ -4076,25 +4076,25 @@
     <t xml:space="preserve">9.50107955932617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52969741821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57739353179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47246170043945</t>
+    <t xml:space="preserve">9.52969646453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.577392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47246265411377</t>
   </si>
   <si>
     <t xml:space="preserve">9.36752986907959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30075454711914</t>
+    <t xml:space="preserve">9.30075550079346</t>
   </si>
   <si>
     <t xml:space="preserve">9.39614772796631</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44384288787842</t>
+    <t xml:space="preserve">9.44384384155273</t>
   </si>
   <si>
     <t xml:space="preserve">9.49153995513916</t>
@@ -4106,7 +4106,7 @@
     <t xml:space="preserve">8.69978332519531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55669498443604</t>
+    <t xml:space="preserve">8.55669593811035</t>
   </si>
   <si>
     <t xml:space="preserve">8.62346935272217</t>
@@ -4115,10 +4115,10 @@
     <t xml:space="preserve">8.48038101196289</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59485149383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70932292938232</t>
+    <t xml:space="preserve">8.59485244750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70932197570801</t>
   </si>
   <si>
     <t xml:space="preserve">8.77609729766846</t>
@@ -4130,10 +4130,10 @@
     <t xml:space="preserve">8.75701904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86195087432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89056777954102</t>
+    <t xml:space="preserve">8.8619499206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89056873321533</t>
   </si>
   <si>
     <t xml:space="preserve">8.67116546630859</t>
@@ -4148,10 +4148,10 @@
     <t xml:space="preserve">8.74748039245605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0145788192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92872428894043</t>
+    <t xml:space="preserve">9.01457786560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92872524261475</t>
   </si>
   <si>
     <t xml:space="preserve">8.97642135620117</t>
@@ -4163,28 +4163,28 @@
     <t xml:space="preserve">9.46292304992676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74910068511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78725719451904</t>
+    <t xml:space="preserve">9.74909973144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78725624084473</t>
   </si>
   <si>
     <t xml:space="preserve">9.92080497741699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99711894989014</t>
+    <t xml:space="preserve">9.99711990356445</t>
   </si>
   <si>
     <t xml:space="preserve">9.69186401367188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76817798614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80633449554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63462829589844</t>
+    <t xml:space="preserve">9.7681770324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80633544921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63462924957275</t>
   </si>
   <si>
     <t xml:space="preserve">9.67278575897217</t>
@@ -4193,10 +4193,10 @@
     <t xml:space="preserve">9.59647178649902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71094226837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52015686035156</t>
+    <t xml:space="preserve">9.7109432220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52015781402588</t>
   </si>
   <si>
     <t xml:space="preserve">9.43430519104004</t>
@@ -4205,13 +4205,13 @@
     <t xml:space="preserve">9.25305938720703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28167629241943</t>
+    <t xml:space="preserve">9.28167724609375</t>
   </si>
   <si>
     <t xml:space="preserve">9.34845161437988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41522693634033</t>
+    <t xml:space="preserve">9.41522598266602</t>
   </si>
   <si>
     <t xml:space="preserve">9.48200035095215</t>
@@ -4229,7 +4229,7 @@
     <t xml:space="preserve">9.65370750427246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86357116699219</t>
+    <t xml:space="preserve">9.86357021331787</t>
   </si>
   <si>
     <t xml:space="preserve">10.0204467773438</t>
@@ -5046,6 +5046,9 @@
   </si>
   <si>
     <t xml:space="preserve">18.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4400005340576</t>
   </si>
 </sst>
 </file>
@@ -72100,7 +72103,7 @@
     </row>
     <row r="2567">
       <c r="A2567" s="1" t="n">
-        <v>46059.6909722222</v>
+        <v>46059.3333333333</v>
       </c>
       <c r="B2567" t="n">
         <v>88379</v>
@@ -72121,6 +72124,32 @@
         <v>1675</v>
       </c>
       <c r="H2567" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2568">
+      <c r="A2568" s="1" t="n">
+        <v>46062.6911458333</v>
+      </c>
+      <c r="B2568" t="n">
+        <v>83323</v>
+      </c>
+      <c r="C2568" t="n">
+        <v>19.4400005340576</v>
+      </c>
+      <c r="D2568" t="n">
+        <v>18.8199996948242</v>
+      </c>
+      <c r="E2568" t="n">
+        <v>18.8199996948242</v>
+      </c>
+      <c r="F2568" t="n">
+        <v>19.4400005340576</v>
+      </c>
+      <c r="G2568" t="s">
+        <v>1678</v>
+      </c>
+      <c r="H2568" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CEM.MI.xlsx
+++ b/data/CEM.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">4.68035984039307</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55656242370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48867321014404</t>
+    <t xml:space="preserve">4.55656290054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48867273330688</t>
   </si>
   <si>
     <t xml:space="preserve">4.32893371582031</t>
@@ -65,55 +65,55 @@
     <t xml:space="preserve">4.2889986038208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29299211502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06137037277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93597626686096</t>
+    <t xml:space="preserve">4.29299306869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06137132644653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93597555160522</t>
   </si>
   <si>
     <t xml:space="preserve">3.97431302070618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67560005187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83533883094788</t>
+    <t xml:space="preserve">3.67560076713562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83533906936646</t>
   </si>
   <si>
     <t xml:space="preserve">3.94875431060791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88006615638733</t>
+    <t xml:space="preserve">3.88006639480591</t>
   </si>
   <si>
     <t xml:space="preserve">3.91680693626404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87846922874451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74588513374329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93437838554382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87367725372314</t>
+    <t xml:space="preserve">3.87846946716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74588584899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93437814712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87367677688599</t>
   </si>
   <si>
     <t xml:space="preserve">3.73789834976196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57815933227539</t>
+    <t xml:space="preserve">3.57815909385681</t>
   </si>
   <si>
     <t xml:space="preserve">3.59892582893372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61969184875488</t>
+    <t xml:space="preserve">3.6196916103363</t>
   </si>
   <si>
     <t xml:space="preserve">3.35132956504822</t>
@@ -122,28 +122,28 @@
     <t xml:space="preserve">3.15005803108215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25069379806519</t>
+    <t xml:space="preserve">3.25069403648376</t>
   </si>
   <si>
     <t xml:space="preserve">3.13088941574097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20916152000427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44238114356995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36251163482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47592663764954</t>
+    <t xml:space="preserve">3.20916199684143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44238090515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36251091957092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4759259223938</t>
   </si>
   <si>
     <t xml:space="preserve">3.55419826507568</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34653782844543</t>
+    <t xml:space="preserve">3.34653759002686</t>
   </si>
   <si>
     <t xml:space="preserve">3.39126420021057</t>
@@ -152,58 +152,58 @@
     <t xml:space="preserve">3.36730360984802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23951244354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2922260761261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40244626998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58614706993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63406777381897</t>
+    <t xml:space="preserve">3.2395122051239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29222631454468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40244603157043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58614587783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63406825065613</t>
   </si>
   <si>
     <t xml:space="preserve">3.55579614639282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64365196228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56058812141418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52065324783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49829030036926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52544546127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54940581321716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75227522850037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61330199241638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75387191772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83214521408081</t>
+    <t xml:space="preserve">3.64365243911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56058788299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52065300941467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4982898235321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52544498443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54940557479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75227499008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61330246925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75387239456177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83214426040649</t>
   </si>
   <si>
     <t xml:space="preserve">3.6708083152771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70754766464233</t>
+    <t xml:space="preserve">3.70754814147949</t>
   </si>
   <si>
     <t xml:space="preserve">3.65802931785583</t>
@@ -212,46 +212,46 @@
     <t xml:space="preserve">3.51745843887329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57017183303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50947141647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54301691055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57975673675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45196509361267</t>
+    <t xml:space="preserve">3.57017207145691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50947070121765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54301643371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57975697517395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45196533203125</t>
   </si>
   <si>
     <t xml:space="preserve">3.41043329238892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37529015541077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60052275657654</t>
+    <t xml:space="preserve">3.3752908706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60052251815796</t>
   </si>
   <si>
     <t xml:space="preserve">3.48551034927368</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54461431503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59573078155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7794303894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74428749084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85770320892334</t>
+    <t xml:space="preserve">3.54461407661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59573101997375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77943086624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74428868293762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85770273208618</t>
   </si>
   <si>
     <t xml:space="preserve">3.73949599266052</t>
@@ -260,85 +260,85 @@
     <t xml:space="preserve">3.74907994270325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70595002174377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69317173957825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67719841003418</t>
+    <t xml:space="preserve">3.70595097541809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69317126274109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67719745635986</t>
   </si>
   <si>
     <t xml:space="preserve">3.79700207710266</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66601586341858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70115804672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62608170509338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67400312423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64205455780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53023767471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45835518836975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47432851791382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53193759918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62187051773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75758910179138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76085948944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87531971931458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88349509239197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7772102355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75431776046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70526361465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66929006576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59734344482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58426213264465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55646419525146</t>
+    <t xml:space="preserve">3.6660168170929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70115900039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62608075141907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67400288581848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64205527305603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53023719787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45835471153259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4743287563324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53193688392639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62187027931213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75758814811707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76085877418518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87532019615173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88349556922913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77720975875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75431847572327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70526385307312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66929030418396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5973436832428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5842616558075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55646467208862</t>
   </si>
   <si>
     <t xml:space="preserve">3.38640809059143</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31119084358215</t>
+    <t xml:space="preserve">3.31119108200073</t>
   </si>
   <si>
     <t xml:space="preserve">3.29810953140259</t>
@@ -347,169 +347,169 @@
     <t xml:space="preserve">3.19673013687134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15912127494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00705170631409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15421605110168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03484964370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22289276123047</t>
+    <t xml:space="preserve">3.15912175178528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00705194473267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15421628952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0348494052887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22289228439331</t>
   </si>
   <si>
     <t xml:space="preserve">3.35206985473633</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10679650306702</t>
+    <t xml:space="preserve">3.1067967414856</t>
   </si>
   <si>
     <t xml:space="preserve">2.82881999015808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82064437866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84026575088501</t>
+    <t xml:space="preserve">2.82064414024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84026598930359</t>
   </si>
   <si>
     <t xml:space="preserve">2.9351053237915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04302525520325</t>
+    <t xml:space="preserve">3.04302549362183</t>
   </si>
   <si>
     <t xml:space="preserve">2.95799708366394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79611682891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76341366767883</t>
+    <t xml:space="preserve">2.79611706733704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76341390609741</t>
   </si>
   <si>
     <t xml:space="preserve">2.76831912994385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84844183921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87787461280823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04139018058777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00051140785217</t>
+    <t xml:space="preserve">2.84844136238098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87787485122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04139041900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00051164627075</t>
   </si>
   <si>
     <t xml:space="preserve">3.21144652366638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13295888900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07572865486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97434902191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1084315776825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97598361968994</t>
+    <t xml:space="preserve">3.13295865058899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07572841644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97434878349304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10843205451965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9759840965271</t>
   </si>
   <si>
     <t xml:space="preserve">2.92856431007385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17547297477722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18037915229797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15585088729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18855452537537</t>
+    <t xml:space="preserve">3.17547273635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18037867546082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15585112571716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18855428695679</t>
   </si>
   <si>
     <t xml:space="preserve">3.09862065315247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12151288986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02503871917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11660742759705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23760914802551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28012275695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32263708114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43546295166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40602970123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46653056144714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43709778785706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44854378700256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67910122871399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64639806747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71834468841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69545197486877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74450778961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85242700576782</t>
+    <t xml:space="preserve">3.12151265144348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02503848075867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11660718917847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23760890960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28012251853943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32263731956482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43546319007874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40602993965149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46653079986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43709826469421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44854402542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67910146713257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64639830589294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71834492683411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69545269012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7445068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85242772102356</t>
   </si>
   <si>
     <t xml:space="preserve">3.80827832221985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82299518585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80337309837341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7428719997406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62350583076477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56627535820007</t>
+    <t xml:space="preserve">3.82299447059631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80337262153625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74287247657776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62350606918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56627511978149</t>
   </si>
   <si>
     <t xml:space="preserve">3.47470664978027</t>
@@ -518,13 +518,13 @@
     <t xml:space="preserve">3.51558542251587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65947866439819</t>
+    <t xml:space="preserve">3.65947914123535</t>
   </si>
   <si>
     <t xml:space="preserve">3.60551881790161</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54501843452454</t>
+    <t xml:space="preserve">3.54501891136169</t>
   </si>
   <si>
     <t xml:space="preserve">3.64803290367126</t>
@@ -536,10 +536,10 @@
     <t xml:space="preserve">3.38804316520691</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48288249969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45344948768616</t>
+    <t xml:space="preserve">3.4828827381134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45344924926758</t>
   </si>
   <si>
     <t xml:space="preserve">3.4338276386261</t>
@@ -548,43 +548,43 @@
     <t xml:space="preserve">3.50740957260132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56463956832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55482935905457</t>
+    <t xml:space="preserve">3.56463980674744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55482864379883</t>
   </si>
   <si>
     <t xml:space="preserve">3.56300520896912</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48451733589172</t>
+    <t xml:space="preserve">3.48451781272888</t>
   </si>
   <si>
     <t xml:space="preserve">3.54338312149048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62514114379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5908031463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64149236679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68891191482544</t>
+    <t xml:space="preserve">3.62514066696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59080290794373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64149260520935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6889111995697</t>
   </si>
   <si>
     <t xml:space="preserve">3.66111445426941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68727684020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53684306144714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63004636764526</t>
+    <t xml:space="preserve">3.6872775554657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53684282302856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63004589080811</t>
   </si>
   <si>
     <t xml:space="preserve">3.63822197914124</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">3.43873310089111</t>
   </si>
   <si>
-    <t xml:space="preserve">3.417475938797</t>
+    <t xml:space="preserve">3.41747570037842</t>
   </si>
   <si>
     <t xml:space="preserve">3.41911149024963</t>
@@ -602,64 +602,64 @@
     <t xml:space="preserve">3.33571815490723</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37169194221497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27521753311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22125720977783</t>
+    <t xml:space="preserve">3.37169170379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27521777153015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22125744819641</t>
   </si>
   <si>
     <t xml:space="preserve">3.2098114490509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17710781097412</t>
+    <t xml:space="preserve">3.17710828781128</t>
   </si>
   <si>
     <t xml:space="preserve">3.21308159828186</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14767551422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11333703994751</t>
+    <t xml:space="preserve">3.14767575263977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11333727836609</t>
   </si>
   <si>
     <t xml:space="preserve">3.00541687011719</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0168628692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95309162139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91875314712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96453738212585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96780848503113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95636200904846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04793071746826</t>
+    <t xml:space="preserve">3.01686310768127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9530918598175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9187536239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96453785896301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96780824661255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9563615322113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04793047904968</t>
   </si>
   <si>
     <t xml:space="preserve">3.17220282554626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18691897392273</t>
+    <t xml:space="preserve">3.18691921234131</t>
   </si>
   <si>
     <t xml:space="preserve">3.3193666934967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23433828353882</t>
+    <t xml:space="preserve">3.23433876037598</t>
   </si>
   <si>
     <t xml:space="preserve">3.48778796195984</t>
@@ -668,13 +668,13 @@
     <t xml:space="preserve">3.45181441307068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49923419952393</t>
+    <t xml:space="preserve">3.49923372268677</t>
   </si>
   <si>
     <t xml:space="preserve">3.57281541824341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45017886161804</t>
+    <t xml:space="preserve">3.45017862319946</t>
   </si>
   <si>
     <t xml:space="preserve">3.61369466781616</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">3.67746567726135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58916759490967</t>
+    <t xml:space="preserve">3.58916735649109</t>
   </si>
   <si>
     <t xml:space="preserve">3.70362830162048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48615264892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33244848251343</t>
+    <t xml:space="preserve">3.4861524105072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33244824409485</t>
   </si>
   <si>
     <t xml:space="preserve">3.28666353225708</t>
@@ -701,10 +701,10 @@
     <t xml:space="preserve">3.22943305969238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27031207084656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24741959571838</t>
+    <t xml:space="preserve">3.27031183242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24741983413696</t>
   </si>
   <si>
     <t xml:space="preserve">3.23106813430786</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">3.23270344734192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26213598251343</t>
+    <t xml:space="preserve">3.26213645935059</t>
   </si>
   <si>
     <t xml:space="preserve">3.27685260772705</t>
@@ -731,91 +731,91 @@
     <t xml:space="preserve">4.12876892089844</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16964769363403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17782306671143</t>
+    <t xml:space="preserve">4.16964817047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1778244972229</t>
   </si>
   <si>
     <t xml:space="preserve">4.06336259841919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95707702636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19417476654053</t>
+    <t xml:space="preserve">3.95707821846008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19417524337769</t>
   </si>
   <si>
     <t xml:space="preserve">4.28410911560059</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3454270362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4721508026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43944835662842</t>
+    <t xml:space="preserve">4.34542751312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47215175628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43944787979126</t>
   </si>
   <si>
     <t xml:space="preserve">4.41083288192749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41492080688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37404203414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26775646209717</t>
+    <t xml:space="preserve">4.41492128372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37404251098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26775693893433</t>
   </si>
   <si>
     <t xml:space="preserve">4.39039373397827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36177921295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37812995910645</t>
+    <t xml:space="preserve">4.3617787361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3781304359436</t>
   </si>
   <si>
     <t xml:space="preserve">4.38630628585815</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56208515167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42718458175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32907581329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2554931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25140523910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30046081542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34951591491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24322986602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24731826782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21052742004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1451210975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10424137115479</t>
+    <t xml:space="preserve">4.56208562850952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42718505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3290753364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25549364089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25140571594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30045986175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34951543807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24322938919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24731874465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21052694320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14512014389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10424184799194</t>
   </si>
   <si>
     <t xml:space="preserve">4.22279024124146</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">4.40674543380737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36586666107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27593278884888</t>
+    <t xml:space="preserve">4.36586713790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27593326568604</t>
   </si>
   <si>
     <t xml:space="preserve">4.3045482635498</t>
@@ -839,13 +839,13 @@
     <t xml:space="preserve">4.44762468338013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52938222885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51711893081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52120590209961</t>
+    <t xml:space="preserve">4.52938175201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51711845397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52120637893677</t>
   </si>
   <si>
     <t xml:space="preserve">4.68063402175903</t>
@@ -854,40 +854,40 @@
     <t xml:space="preserve">4.66019487380981</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71333694458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73377656936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81962299346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81144714355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65201854705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34134006500244</t>
+    <t xml:space="preserve">4.71333742141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7337760925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81962251663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81144666671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65201902389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34133911132812</t>
   </si>
   <si>
     <t xml:space="preserve">4.33725118637085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25958156585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40383338928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44966459274292</t>
+    <t xml:space="preserve">4.25958108901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4038348197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44966506958008</t>
   </si>
   <si>
     <t xml:space="preserve">4.41633367538452</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37467002868652</t>
+    <t xml:space="preserve">4.37466955184937</t>
   </si>
   <si>
     <t xml:space="preserve">4.36633777618408</t>
@@ -896,13 +896,13 @@
     <t xml:space="preserve">4.30384206771851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27467727661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25801181793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31634140014648</t>
+    <t xml:space="preserve">4.27467775344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25801277160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31634092330933</t>
   </si>
   <si>
     <t xml:space="preserve">4.26634407043457</t>
@@ -911,16 +911,16 @@
     <t xml:space="preserve">4.20801591873169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33300590515137</t>
+    <t xml:space="preserve">4.33300685882568</t>
   </si>
   <si>
     <t xml:space="preserve">4.37050437927246</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34550523757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39133501052856</t>
+    <t xml:space="preserve">4.3455057144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39133596420288</t>
   </si>
   <si>
     <t xml:space="preserve">4.29967594146729</t>
@@ -932,31 +932,31 @@
     <t xml:space="preserve">4.39966821670532</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39550113677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38300323486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46633005142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48299503326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.566321849823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40800046920776</t>
+    <t xml:space="preserve">4.39550161361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38300228118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4663290977478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48299598693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56632232666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40800142288208</t>
   </si>
   <si>
     <t xml:space="preserve">4.34967136383057</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69131278991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5829873085022</t>
+    <t xml:space="preserve">4.69131326675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58298778533936</t>
   </si>
   <si>
     <t xml:space="preserve">4.85380029678345</t>
@@ -974,52 +974,52 @@
     <t xml:space="preserve">5.24960422515869</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28710079193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25377035140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41625785827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30376672744751</t>
+    <t xml:space="preserve">5.28710126876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25377082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41625881195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30376625061035</t>
   </si>
   <si>
     <t xml:space="preserve">5.29960060119629</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34542989730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30793333053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22877168655396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29126691818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29543495178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16211128234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01628875732422</t>
+    <t xml:space="preserve">5.34543085098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30793285369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22877216339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29126739501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29543447494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16211032867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01628828048706</t>
   </si>
   <si>
     <t xml:space="preserve">5.05378532409668</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1246132850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20377397537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07461786270142</t>
+    <t xml:space="preserve">5.12461280822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20377349853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07461738586426</t>
   </si>
   <si>
     <t xml:space="preserve">5.03295373916626</t>
@@ -1028,16 +1028,16 @@
     <t xml:space="preserve">4.95795965194702</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99129009246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96212577819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90796327590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94129371643066</t>
+    <t xml:space="preserve">4.99129056930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96212530136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90796279907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94129323959351</t>
   </si>
   <si>
     <t xml:space="preserve">4.89129781723022</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">4.9537935256958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94546031951904</t>
+    <t xml:space="preserve">4.94545984268188</t>
   </si>
   <si>
     <t xml:space="preserve">4.91629600524902</t>
@@ -1064,85 +1064,85 @@
     <t xml:space="preserve">5.1162805557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17460966110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23293876647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17877674102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13294553756714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33293056488037</t>
+    <t xml:space="preserve">5.17461013793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23293924331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17877578735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13294649124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33293151855469</t>
   </si>
   <si>
     <t xml:space="preserve">5.26626968383789</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22460651397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5829119682312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68707132339478</t>
+    <t xml:space="preserve">5.22460603713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58291149139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68707036972046</t>
   </si>
   <si>
     <t xml:space="preserve">6.00371360778809</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80789566040039</t>
+    <t xml:space="preserve">5.80789470672607</t>
   </si>
   <si>
     <t xml:space="preserve">6.0745415687561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01621341705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1662015914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89122295379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94121837615967</t>
+    <t xml:space="preserve">6.01621246337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16620111465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89122247695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94121885299683</t>
   </si>
   <si>
     <t xml:space="preserve">5.96621608734131</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03287839889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99538135528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97038316726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91621971130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86205816268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92871952056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89955520629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90372133255005</t>
+    <t xml:space="preserve">6.03287792205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9953818321228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97038269042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91622066497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86205720901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92871904373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89955425262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90372180938721</t>
   </si>
   <si>
     <t xml:space="preserve">5.87455749511719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84539222717285</t>
+    <t xml:space="preserve">5.84539270401001</t>
   </si>
   <si>
     <t xml:space="preserve">6.00788021087646</t>
@@ -1151,19 +1151,19 @@
     <t xml:space="preserve">5.98288249969482</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03704500198364</t>
+    <t xml:space="preserve">6.03704452514648</t>
   </si>
   <si>
     <t xml:space="preserve">6.0912070274353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0287127494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99954748153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04954433441162</t>
+    <t xml:space="preserve">6.02871179580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99954795837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0495433807373</t>
   </si>
   <si>
     <t xml:space="preserve">6.07870817184448</t>
@@ -1172,7 +1172,7 @@
     <t xml:space="preserve">6.29119205474854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1745343208313</t>
+    <t xml:space="preserve">6.17453479766846</t>
   </si>
   <si>
     <t xml:space="preserve">6.1995325088501</t>
@@ -1181,52 +1181,52 @@
     <t xml:space="preserve">6.08287477493286</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24536228179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21203088760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02454566955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0995397567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18286657333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20786428451538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22036409378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14536952972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95788383483887</t>
+    <t xml:space="preserve">6.24536180496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21203184127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02454614639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09954071044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1828670501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20786476135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22036457061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14537000656128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95788431167603</t>
   </si>
   <si>
     <t xml:space="preserve">5.94538545608521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01204681396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02037858963013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11620569229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06204223632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04121160507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1495361328125</t>
+    <t xml:space="preserve">6.01204586029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02037954330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1162052154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06204319000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04121065139771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14953660964966</t>
   </si>
   <si>
     <t xml:space="preserve">6.09537410736084</t>
@@ -1235,10 +1235,10 @@
     <t xml:space="preserve">6.35785388946533</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22453022003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28285884857178</t>
+    <t xml:space="preserve">6.22452974319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28285932540894</t>
   </si>
   <si>
     <t xml:space="preserve">6.58283662796021</t>
@@ -1247,16 +1247,16 @@
     <t xml:space="preserve">6.61616802215576</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57450389862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50784206390381</t>
+    <t xml:space="preserve">6.57450342178345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50784254074097</t>
   </si>
   <si>
     <t xml:space="preserve">6.49951028823853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65783071517944</t>
+    <t xml:space="preserve">6.65783166885376</t>
   </si>
   <si>
     <t xml:space="preserve">6.7411584854126</t>
@@ -1268,106 +1268,106 @@
     <t xml:space="preserve">6.6245002746582</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63283348083496</t>
+    <t xml:space="preserve">6.6328330039978</t>
   </si>
   <si>
     <t xml:space="preserve">6.7078275680542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52450799942017</t>
+    <t xml:space="preserve">6.52450752258301</t>
   </si>
   <si>
     <t xml:space="preserve">6.51617527008057</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6661639213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54950618743896</t>
+    <t xml:space="preserve">6.66616344451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54950571060181</t>
   </si>
   <si>
     <t xml:space="preserve">6.44951295852661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29952430725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2328634262085</t>
+    <t xml:space="preserve">6.29952526092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23286294937134</t>
   </si>
   <si>
     <t xml:space="preserve">5.90788793563843</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93288660049438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53284025192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26619386672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36618661880493</t>
+    <t xml:space="preserve">5.93288564682007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53284072875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26619434356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36618614196777</t>
   </si>
   <si>
     <t xml:space="preserve">6.33285570144653</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14120292663574</t>
+    <t xml:space="preserve">6.1412034034729</t>
   </si>
   <si>
     <t xml:space="preserve">6.15786933898926</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06620836257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94955062866211</t>
+    <t xml:space="preserve">6.06620931625366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94955110549927</t>
   </si>
   <si>
     <t xml:space="preserve">6.13287115097046</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0578761100769</t>
+    <t xml:space="preserve">6.05787706375122</t>
   </si>
   <si>
     <t xml:space="preserve">5.88288974761963</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84955883026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81622791290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72456789016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75789880752563</t>
+    <t xml:space="preserve">5.84955835342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81622838973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72456836700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75789928436279</t>
   </si>
   <si>
     <t xml:space="preserve">5.76623201370239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6829047203064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82455968856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86622428894043</t>
+    <t xml:space="preserve">5.68290519714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82456064224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86622476577759</t>
   </si>
   <si>
     <t xml:space="preserve">5.77456426620483</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78289747238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79123020172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6329083442688</t>
+    <t xml:space="preserve">5.78289699554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79122972488403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63290882110596</t>
   </si>
   <si>
     <t xml:space="preserve">5.64982414245605</t>
@@ -1376,37 +1376,37 @@
     <t xml:space="preserve">5.68365526199341</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66673946380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70057106018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48066806793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45529460906982</t>
+    <t xml:space="preserve">5.66673898696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70057058334351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48066759109497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45529365539551</t>
   </si>
   <si>
     <t xml:space="preserve">5.54833078384399</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5398736000061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74286031723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58216142654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6582818031311</t>
+    <t xml:space="preserve">5.53987264633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74285984039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58216190338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65828227996826</t>
   </si>
   <si>
     <t xml:space="preserve">5.70902872085571</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77669143676758</t>
+    <t xml:space="preserve">5.77669191360474</t>
   </si>
   <si>
     <t xml:space="preserve">5.91201686859131</t>
@@ -1415,25 +1415,25 @@
     <t xml:space="preserve">5.9035587310791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89510059356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75131797790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78514957427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71748733520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81052303314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56524562835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50604104995728</t>
+    <t xml:space="preserve">5.89510107040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75131845474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78515005111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71748685836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81052255630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56524610519409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50604152679443</t>
   </si>
   <si>
     <t xml:space="preserve">5.69211339950562</t>
@@ -1442,19 +1442,19 @@
     <t xml:space="preserve">5.72594451904297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73440313339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60753488540649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51449871063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67519760131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01351070404053</t>
+    <t xml:space="preserve">5.73440265655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60753536224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51449918746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67519807815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01351022720337</t>
   </si>
   <si>
     <t xml:space="preserve">5.99659490585327</t>
@@ -1463,19 +1463,19 @@
     <t xml:space="preserve">5.81898069381714</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75977516174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80206489562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79360771179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.886643409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87818479537964</t>
+    <t xml:space="preserve">5.75977563858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80206537246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79360675811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88664293289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87818574905396</t>
   </si>
   <si>
     <t xml:space="preserve">5.92893266677856</t>
@@ -1484,22 +1484,22 @@
     <t xml:space="preserve">5.85281181335449</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76823329925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82743835449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83589649200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42992162704468</t>
+    <t xml:space="preserve">5.76823377609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82743883132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83589601516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42992115020752</t>
   </si>
   <si>
     <t xml:space="preserve">5.3876314163208</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33688449859619</t>
+    <t xml:space="preserve">5.33688497543335</t>
   </si>
   <si>
     <t xml:space="preserve">5.26076412200928</t>
@@ -1514,13 +1514,13 @@
     <t xml:space="preserve">5.46375226974487</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44683647155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35380029678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37071561813354</t>
+    <t xml:space="preserve">5.44683694839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35380077362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3707160949707</t>
   </si>
   <si>
     <t xml:space="preserve">5.22693300247192</t>
@@ -1532,67 +1532,67 @@
     <t xml:space="preserve">5.11698198318481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24384927749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13389778137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26922225952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25230646133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21001720428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23539161682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28613758087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31996917724609</t>
+    <t xml:space="preserve">5.24384880065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13389730453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26922273635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25230741500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21001768112183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23539113998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28613805770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31996965408325</t>
   </si>
   <si>
     <t xml:space="preserve">5.29459619522095</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48912572860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32842779159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16772842407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09160804748535</t>
+    <t xml:space="preserve">5.48912525177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32842683792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16772890090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09160757064819</t>
   </si>
   <si>
     <t xml:space="preserve">5.17618608474731</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10852384567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91399383544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60105514526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49956083297729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.567223072052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38115072250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54185009002686</t>
+    <t xml:space="preserve">5.10852289199829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91399335861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60105419158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49956130981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56722354888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38115119934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5418496131897</t>
   </si>
   <si>
     <t xml:space="preserve">4.5249342918396</t>
@@ -1601,10 +1601,10 @@
     <t xml:space="preserve">4.61796998977661</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46572923660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27119970321655</t>
+    <t xml:space="preserve">4.46572971343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27120018005371</t>
   </si>
   <si>
     <t xml:space="preserve">4.14433240890503</t>
@@ -1616,34 +1616,34 @@
     <t xml:space="preserve">4.09358549118042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20353651046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15701866149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39806604385376</t>
+    <t xml:space="preserve">4.20353698730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15701913833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39806652069092</t>
   </si>
   <si>
     <t xml:space="preserve">4.53339195251465</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59259653091431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6095118522644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63488578796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41498184204102</t>
+    <t xml:space="preserve">4.59259605407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60951280593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63488531112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41498231887817</t>
   </si>
   <si>
     <t xml:space="preserve">4.49110269546509</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42344093322754</t>
+    <t xml:space="preserve">4.42343997955322</t>
   </si>
   <si>
     <t xml:space="preserve">4.43189811706543</t>
@@ -1652,25 +1652,25 @@
     <t xml:space="preserve">4.29657316207886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33886194229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19507932662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04706764221191</t>
+    <t xml:space="preserve">4.33886241912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19507884979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04706716537476</t>
   </si>
   <si>
     <t xml:space="preserve">4.08512735366821</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10627269744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15278959274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2373685836792</t>
+    <t xml:space="preserve">4.10627126693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15278911590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23736810684204</t>
   </si>
   <si>
     <t xml:space="preserve">4.21622371673584</t>
@@ -1685,16 +1685,16 @@
     <t xml:space="preserve">4.03860950469971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30503082275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25428342819214</t>
+    <t xml:space="preserve">4.30503034591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25428438186646</t>
   </si>
   <si>
     <t xml:space="preserve">4.14010334014893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0512957572937</t>
+    <t xml:space="preserve">4.05129623413086</t>
   </si>
   <si>
     <t xml:space="preserve">4.14856147766113</t>
@@ -1703,13 +1703,13 @@
     <t xml:space="preserve">4.08935642242432</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03438091278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94557356834412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35577821731567</t>
+    <t xml:space="preserve">4.0343804359436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9455738067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35577726364136</t>
   </si>
   <si>
     <t xml:space="preserve">4.31348848342896</t>
@@ -1727,19 +1727,19 @@
     <t xml:space="preserve">4.7871265411377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82095766067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86324691772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90553665161133</t>
+    <t xml:space="preserve">4.82095718383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86324644088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90553569793701</t>
   </si>
   <si>
     <t xml:space="preserve">4.88862037658691</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95628261566162</t>
+    <t xml:space="preserve">4.95628309249878</t>
   </si>
   <si>
     <t xml:space="preserve">5.00703001022339</t>
@@ -1748,91 +1748,91 @@
     <t xml:space="preserve">5.01548719406128</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03240299224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.057776927948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99011468887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97319841384888</t>
+    <t xml:space="preserve">5.03240346908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05777645111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99011421203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97319936752319</t>
   </si>
   <si>
     <t xml:space="preserve">5.20155954360962</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12543869018555</t>
+    <t xml:space="preserve">5.12543916702271</t>
   </si>
   <si>
     <t xml:space="preserve">5.15927076339722</t>
   </si>
   <si>
+    <t xml:space="preserve">5.21847534179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34534311294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27768039703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40454721450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39609003067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47220993041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49758386611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42146301269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41300535202026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98165607452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11462450027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13193273544312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01942873001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01077508926392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06269931793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08866310119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0973162651062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14058828353882</t>
+  </si>
+  <si>
     <t xml:space="preserve">5.21847581863403</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34534311294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27767992019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40454769134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39608955383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47220993041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49758338928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42146301269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41300535202026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98165655136108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11462545394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13193321228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0194296836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01077508926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06269979476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08866262435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09731674194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14058780670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21847534179688</t>
-  </si>
-  <si>
     <t xml:space="preserve">5.20116710662842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17520475387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2271294593811</t>
+    <t xml:space="preserve">5.17520380020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22712850570679</t>
   </si>
   <si>
     <t xml:space="preserve">5.26174640655518</t>
@@ -1844,7 +1844,7 @@
     <t xml:space="preserve">5.25309228897095</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33963441848755</t>
+    <t xml:space="preserve">5.33963394165039</t>
   </si>
   <si>
     <t xml:space="preserve">5.46079254150391</t>
@@ -1856,19 +1856,19 @@
     <t xml:space="preserve">5.42617607116699</t>
   </si>
   <si>
-    <t xml:space="preserve">5.330979347229</t>
+    <t xml:space="preserve">5.33097982406616</t>
   </si>
   <si>
     <t xml:space="preserve">5.40886735916138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57329654693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52137184143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47810077667236</t>
+    <t xml:space="preserve">5.57329750061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52137231826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47810125350952</t>
   </si>
   <si>
     <t xml:space="preserve">5.64253044128418</t>
@@ -1886,7 +1886,7 @@
     <t xml:space="preserve">5.65118455886841</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7031102180481</t>
+    <t xml:space="preserve">5.70310974121094</t>
   </si>
   <si>
     <t xml:space="preserve">5.66849327087402</t>
@@ -1898,13 +1898,13 @@
     <t xml:space="preserve">5.49540901184082</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45213842391968</t>
+    <t xml:space="preserve">5.45213794708252</t>
   </si>
   <si>
     <t xml:space="preserve">5.56464242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73772621154785</t>
+    <t xml:space="preserve">5.73772668838501</t>
   </si>
   <si>
     <t xml:space="preserve">5.51271724700928</t>
@@ -1916,10 +1916,10 @@
     <t xml:space="preserve">5.1838583946228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28770875930786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19251251220703</t>
+    <t xml:space="preserve">5.28770923614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19251298904419</t>
   </si>
   <si>
     <t xml:space="preserve">5.1232795715332</t>
@@ -1928,52 +1928,52 @@
     <t xml:space="preserve">5.2704005241394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08000802993774</t>
+    <t xml:space="preserve">5.08000755310059</t>
   </si>
   <si>
     <t xml:space="preserve">5.14924192428589</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16654920578003</t>
+    <t xml:space="preserve">5.16655015945435</t>
   </si>
   <si>
     <t xml:space="preserve">5.15789556503296</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29636240005493</t>
+    <t xml:space="preserve">5.29636287689209</t>
   </si>
   <si>
     <t xml:space="preserve">5.53868007659912</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44348430633545</t>
+    <t xml:space="preserve">5.44348478317261</t>
   </si>
   <si>
     <t xml:space="preserve">5.48675537109375</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40021276473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36559677124023</t>
+    <t xml:space="preserve">5.40021324157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36559629440308</t>
   </si>
   <si>
     <t xml:space="preserve">5.32232522964478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38290500640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02808332443237</t>
+    <t xml:space="preserve">5.38290452957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02808284759521</t>
   </si>
   <si>
     <t xml:space="preserve">5.04539108276367</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16222333908081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03933334350586</t>
+    <t xml:space="preserve">5.16222381591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03933429718018</t>
   </si>
   <si>
     <t xml:space="preserve">5.10597085952759</t>
@@ -1988,1438 +1988,1438 @@
     <t xml:space="preserve">5.27905464172363</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3456916809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32665252685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27991962432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3058819770813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26780462265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34742307662964</t>
+    <t xml:space="preserve">5.34569215774536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32665300369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27992010116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30588245391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26780414581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34742259979248</t>
   </si>
   <si>
     <t xml:space="preserve">5.21934032440186</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34309530258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48502445220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43915748596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31799840927124</t>
+    <t xml:space="preserve">5.34309577941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48502397537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4391565322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3179988861084</t>
   </si>
   <si>
     <t xml:space="preserve">5.51791000366211</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61656808853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51618003845215</t>
+    <t xml:space="preserve">5.61656761169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51617908477783</t>
   </si>
   <si>
     <t xml:space="preserve">5.46252298355103</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42271423339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46771574020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44434928894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46944665908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78099775314331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02331495285034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04062271118164</t>
+    <t xml:space="preserve">5.42271375656128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46771621704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44434976577759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46944713592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78099727630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02331447601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0406231880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04927730560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94456148147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76974678039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78272867202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75416994094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74118804931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73945760726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81042194366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90561723709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93331098556519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94110012054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91081047058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92638778686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85369253158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85628938674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68060922622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73253440856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81907606124878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90648317337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70570611953735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57502746582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75590038299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81561374664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76022815704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73512983322144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72041797637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69791746139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69272470474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62868452072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75936222076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65810775756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57243204116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62522268295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6728196144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58195066452026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58454751968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64512586593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72561120986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61483669281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60704898834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65291595458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65551137924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75503540039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84071159362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00600624084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92811822891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87619304656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71436023712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4218487739563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36213445663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19510841369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04019927978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15443420410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18039655685425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79615068435669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24358081817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30113124847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30718898773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94501161575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11073923110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9809262752533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77452373504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89438486099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17564535140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82385277748108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97486805915833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07006454467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27387046813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11766290664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05665063858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25699472427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30978584289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37036561965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17131853103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32709407806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45690631866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61268186569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48286914825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62999057769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56941175460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57806539535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5261402130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50017738342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74249458312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76845741271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79441928863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94154119491577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91557836532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83769083023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58671951293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55210304260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62133693695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67326164245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80307483673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90961217880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80307388305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73204898834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88297748565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91848945617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10493087768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22034740447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19371175765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39790964126587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44230031967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30025005340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52220344543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49556922912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60210704803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72640037536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81518268585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63761901855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30912780761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27361631393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23810338973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55771636962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73527908325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61098527908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65537548065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68201017379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61986351013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64649772644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71752309799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58435106277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56659460067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53108215332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46005630493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35351943969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42454433441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41566610336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31800651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38903188705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29137182235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21146821975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36239624023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25585985183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26473712921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37127590179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48669099807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59322834014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53995990753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5044469833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3801531791687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34464073181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28249406814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20259094238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32688474655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3357629776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24698066711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15819978713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1315655708313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16707849502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1848349571228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02502775192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90073347091675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61663293838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72317171096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85634326934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99839353561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00727128982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89185571670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98951530456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90396404266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01050138473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01937961578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99274492263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09928274154663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10816097259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35674905776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18806457519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2413330078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28572368621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3212366104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25021123886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30348062515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31235790252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1170392036438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08152627944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06377029418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05489253997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9838662147522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96611022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93947649002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94835376739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92172002792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.912841796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23245477676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46328687667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33011388778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27684545516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20582056045532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04601383209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37450504302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12591695785522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21469831466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17918586730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26796770095825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48104286193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66748428344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01373147964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43988275527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54642009735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59968900680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63520193099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68847036361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52866315841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31558799743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30670976638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1824164390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29783201217651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13802576065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04924392700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19129419326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21792840957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35110092163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4842734336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59081077575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58193254470825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65295696258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51090717315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45763826370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17353773117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61744499206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6795916557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76837396621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93705749511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19452381134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09686470031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99920511245728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17676734924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20340251922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99032735824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08798694610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05247497558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0435962677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00808429718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07910823822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14125537872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07022953033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15013313293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38984298706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23891544342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44311141967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38096618652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51413726806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43423366546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64730930328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4253568649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47014427185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60530567169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43410110473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4160795211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37102508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56025123596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31696033477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42508983612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62332725524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75848960876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6593713760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70442485809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74046802520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68640327453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47915554046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50618839263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51519775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53321933746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46113395690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27190685272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10971355438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15476703643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08268070220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0466365814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0556468963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95652961730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00158214569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74928140640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8574104309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78532409667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83938932418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74027013778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99257230758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92048597335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17278861999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29893970489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16377735137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2178430557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96553993225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60510730743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07366943359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24487400054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12773513793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48816585540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38904762268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35300350189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33498191833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71343517303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63233852386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23586368560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30795097351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64134883880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77651119232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55124187469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49717712402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25388526916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19982051849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03762722015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92949724197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98356151580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01960468292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88444328308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56906461715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63214063644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57807588577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55104398727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65917348861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67719507217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72224807739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7673020362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71323776245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93850755691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2268533706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19080924987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20883178710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38003635406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18179798126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02861595153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80334568023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69521617889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6141185760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37983798980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33478498458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37082767486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46093559265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36181735992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35280609130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4429144859314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65016174316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46994638442993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39786052703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3257737159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27170896530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30775213241577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29874134063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26269865036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54203224182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64115142822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62312984466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53302192687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52401113510132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31676292419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38884925842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4519248008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96534204483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92929840087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02841758728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89325618743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0103964805603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12753629684448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11852550506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94732046127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88424444198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90226650238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28071928024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22665500640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03742837905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14555788040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.199622631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00138521194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07347106933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80314826965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74007225036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6679859161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3616189956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59589958190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41568374633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32557582855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13634920120239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85701513290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83899307250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01019811630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28052186965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09129571914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14535999298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3526086807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2354679107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46974849700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3886513710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37062978744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28953266143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31656503677368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02821969985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11832761764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12733840942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27151107788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26250028610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18140316009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29854345321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17239236831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84800386428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86602544784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92009019851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89305830001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93811178207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88404703140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10030603408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21744632720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06426286697388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9831657409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9471230506897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0192084312439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99217700958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96514415740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97415494918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9561333656311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08228445053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07327318191528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03723001480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04001379013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94737577438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96590328216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16044425964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28087329864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22529029846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20676279067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17897176742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29013729095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23455429077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27160978317261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00295877456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81768226623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83620977401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9288477897644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8917932510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09559679031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01222229003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95663928985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82694625854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68798828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78062677383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73430776596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72504377365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34522724151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4471287727356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6046142578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75283527374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51197528839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85473775863647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55829477310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71578073501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77136278152466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61387777328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66019725799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87326526641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66946077346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80841875076294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0307502746582</t>
   </si>
   <si>
     <t xml:space="preserve">6.04927778244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94456148147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76974630355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78272867202759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75416946411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74118804931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73945760726929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81042194366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90561723709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93331146240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94109964370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9108099937439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92638778686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85369253158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85628938674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68060922622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73253393173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81907558441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90648317337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70570659637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57502698898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75590085983276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81561374664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7602276802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73513078689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72041845321655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69791746139526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69272470474243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62868356704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75936222076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65810823440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57243204116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62522172927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67282009124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58195209503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58454751968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64512634277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72561025619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61483764648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60704851150513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65291547775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65551233291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75503540039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84071111679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00600624084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92811918258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87619352340698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71436071395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4218487739563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36213541030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19510889053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04019927978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1544337272644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18039703369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79615068435669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24358129501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30113124847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30718946456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94501137733459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11073923110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9809262752533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77452373504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89438390731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17564535140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8238525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97486853599548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07006454467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27387046813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11766242980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05665063858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25699520111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30978584289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37036514282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17131805419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32709407806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45690679550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61268186569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48286914825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62999057769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.569411277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57806491851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52614068984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50017738342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74249505996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76845788955688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79442024230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94154119491577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91557836532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83769083023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58671951293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55210304260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62133693695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67326164245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80307483673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90961217880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8030743598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73204946517944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88297700881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91849040985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10493087768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22034692764282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19371175765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39790964126587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44230031967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3002495765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52220344543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49556970596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60210704803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72640132904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81518268585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63761901855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30912828445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27361631393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23810338973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55771636962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73527956008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61098575592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65537595748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68201017379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61986303329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64649772644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71752309799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5843505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56659460067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.531081199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46005630493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35351896286011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42454385757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41566562652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31800603866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38903188705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29137182235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21146821975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36239719390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25585985183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26473712921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37127494812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48669099807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59322881698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53995943069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50444746017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38015365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34464120864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28249311447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20259046554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32688474655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3357629776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24698114395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15819978713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1315655708313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16707849502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18483448028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02502775192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90073394775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61663293838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7231707572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85634279251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99839353561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0072717666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89185619354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98951530456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90396404266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01050138473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01937961578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9927453994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09928274154663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10816049575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35674810409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18806409835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2413330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2857232093811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32123613357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25021076202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30347967147827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31235885620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11703872680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08152675628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06377029418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05489253997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98386716842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96611070632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93947649002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94835472106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92172002792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.912841796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23245477676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46328639984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33011436462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27684593200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20582056045532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04601383209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37450456619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12591695785522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21469831466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17918586730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26796722412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48104333877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66748380661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01373147964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43988275527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54641962051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5996880531311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6352014541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68847036361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52866268157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31558799743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30670976638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1824164390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29783201217651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13802480697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04924345016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19129467010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21792888641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35110092163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48427248001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59081077575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58193206787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65295791625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5109076499939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45763874053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17353773117065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61744499206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6795916557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76837301254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93705797195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19452381134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09686374664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99920511245728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17676734924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20340156555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99032688140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08798694610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05247402191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0435962677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00808334350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07910823822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14125537872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07022953033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15013408660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38984203338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23891353607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44311332702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3809642791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51413726806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43423366546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64730930328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42535495758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47014427185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60530662536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43410110473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4160795211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3710241317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56025218963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31695938110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42509078979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44311237335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62332725524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75848960876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65937042236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70442390441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74046802520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68640327453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47915554046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50618743896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51519775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5332202911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46113395690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27190685272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10971260070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15476608276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08268165588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0466365814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05564785003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95652914047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00158309936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74928188323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8574104309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78532457351685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83938837051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74027013778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99257278442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92048597335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17278861999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29893970489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16377830505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21784210205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96553993225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60510778427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07366943359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24487400054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12773513793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48816585540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38904762268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35300445556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33498287200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71343517303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63233947753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23586368560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30795097351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64134979248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77651119232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55124092102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49717712402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25388622283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19982051849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03762626647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92949724197388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98356103897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01960372924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88444232940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56906509399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63214111328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57807636260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55104446411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65917301177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67719507217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72224950790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76730298995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71323776245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93850803375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22685241699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19080924987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20883083343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38003635406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18179798126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02861499786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80334568023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69521570205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6141185760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37983798980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33478450775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37082815170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46093511581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36181735992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35280609130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4429144859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65016174316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46994638442993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39786005020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3257737159729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27170896530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30775165557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29874181747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26269865036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54203224182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64115047454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62313032150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53302145004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52401113510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31676292419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38884925842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45192527770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96534204483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92929935455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02841806411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89325571060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0103964805603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12753582000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11852550506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94731998443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88424444198608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90226602554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28071975708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22665500640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03742837905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14555788040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19962215423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00138568878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07347106933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80314826965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74007225036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66798639297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3616189956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59590005874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41568422317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32557582855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13634920120239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85701465606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83899307250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01019859313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28052139282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09129524230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14535999298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3526086807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23546838760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46974802017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3886513710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37062978744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28953266143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31656503677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02821969985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11832761764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12733840942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27151107788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26250028610229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18140363693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29854297637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17239236831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84800386428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86602544784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92009019851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89305734634399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93811178207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88404703140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10030603408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21744632720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06426286697388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9831657409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94712257385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0192084312439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99217700958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96514415740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97415494918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9561333656311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08228492736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07327365875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03723049163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04001379013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94737577438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96590328216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16044425964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28087329864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22529029846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20676279067993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17897176742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29013729095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23455429077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27160978317261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00295877456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81768226623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83620977401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9288477897644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8917932510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09559679031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01222229003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95663928985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82694625854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68798828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78062677383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73430776596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72504377365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34522724151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4471287727356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6046142578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75283527374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51197528839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85473775863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55829477310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71578073501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77136278152466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61387777328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66019725799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87326526641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66946077346802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80841875076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0307502746582</t>
   </si>
   <si>
     <t xml:space="preserve">5.86400079727173</t>
@@ -41110,7 +41110,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G1373" t="s">
-        <v>935</v>
+        <v>921</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -41162,7 +41162,7 @@
         <v>9.56999969482422</v>
       </c>
       <c r="G1375" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -41188,7 +41188,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1376" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -41214,7 +41214,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G1377" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -41240,7 +41240,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G1378" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -41266,7 +41266,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1379" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -41292,7 +41292,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G1380" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -41318,7 +41318,7 @@
         <v>9.40999984741211</v>
       </c>
       <c r="G1381" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -41344,7 +41344,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1382" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -41370,7 +41370,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G1383" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -41396,7 +41396,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G1384" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -41422,7 +41422,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G1385" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -41474,7 +41474,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1387" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -41500,7 +41500,7 @@
         <v>9</v>
       </c>
       <c r="G1388" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -41526,7 +41526,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G1389" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -41552,7 +41552,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G1390" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -41578,7 +41578,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G1391" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -41604,7 +41604,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1392" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -41630,7 +41630,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G1393" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -41656,7 +41656,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G1394" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -41682,7 +41682,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1395" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -41708,7 +41708,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1396" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -41734,7 +41734,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1397" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -41760,7 +41760,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G1398" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -41786,7 +41786,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1399" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -41812,7 +41812,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G1400" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -41838,7 +41838,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G1401" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -41864,7 +41864,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1402" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -41890,7 +41890,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1403" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -41916,7 +41916,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G1404" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -41942,7 +41942,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G1405" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -41968,7 +41968,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G1406" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -41994,7 +41994,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1407" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -42020,7 +42020,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1408" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -42046,7 +42046,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1409" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -42072,7 +42072,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G1410" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -42098,7 +42098,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G1411" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -42124,7 +42124,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G1412" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -42150,7 +42150,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1413" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -42176,7 +42176,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1414" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -42202,7 +42202,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1415" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -42228,7 +42228,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1416" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -42254,7 +42254,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G1417" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -42306,7 +42306,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G1419" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -42332,7 +42332,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G1420" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -42358,7 +42358,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G1421" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -42384,7 +42384,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G1422" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -42410,7 +42410,7 @@
         <v>9.25</v>
       </c>
       <c r="G1423" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -42436,7 +42436,7 @@
         <v>9.25</v>
       </c>
       <c r="G1424" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -42462,7 +42462,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G1425" t="s">
-        <v>935</v>
+        <v>921</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -42488,7 +42488,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G1426" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -42514,7 +42514,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G1427" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -42540,7 +42540,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1428" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -42618,7 +42618,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G1431" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -42644,7 +42644,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1432" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -42670,7 +42670,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1433" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -42696,7 +42696,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1434" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -42748,7 +42748,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G1436" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -42774,7 +42774,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1437" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -42800,7 +42800,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G1438" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -42826,7 +42826,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G1439" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -42852,7 +42852,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G1440" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -42878,7 +42878,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G1441" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -42904,7 +42904,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G1442" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -42930,7 +42930,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G1443" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -42982,7 +42982,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G1445" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -43008,7 +43008,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G1446" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -43034,7 +43034,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G1447" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -43060,7 +43060,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1448" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -43086,7 +43086,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1449" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -43112,7 +43112,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G1450" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -43138,7 +43138,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G1451" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -43164,7 +43164,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G1452" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -43190,7 +43190,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -43216,7 +43216,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1454" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -43242,7 +43242,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1455" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -43268,7 +43268,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1456" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -43294,7 +43294,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1457" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -43320,7 +43320,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G1458" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -43346,7 +43346,7 @@
         <v>8.75</v>
       </c>
       <c r="G1459" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -43372,7 +43372,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1460" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -43398,7 +43398,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G1461" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -43424,7 +43424,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G1462" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -43450,7 +43450,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1463" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -43476,7 +43476,7 @@
         <v>8.5</v>
       </c>
       <c r="G1464" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -43502,7 +43502,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G1465" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -43528,7 +43528,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1466" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -43554,7 +43554,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G1467" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -43580,7 +43580,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1468" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -43606,7 +43606,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G1469" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -43632,7 +43632,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1470" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -43658,7 +43658,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G1471" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -43684,7 +43684,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G1472" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -43710,7 +43710,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G1473" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -43736,7 +43736,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G1474" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -43762,7 +43762,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1475" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -43788,7 +43788,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G1476" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -43814,7 +43814,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G1477" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -43840,7 +43840,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G1478" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -43866,7 +43866,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1479" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -43892,7 +43892,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G1480" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -43918,7 +43918,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1481" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -43944,7 +43944,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1482" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -43970,7 +43970,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G1483" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -43996,7 +43996,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1484" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -44022,7 +44022,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1485" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -44048,7 +44048,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G1486" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -44074,7 +44074,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1487" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -44100,7 +44100,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G1488" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -44126,7 +44126,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1489" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -44152,7 +44152,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1490" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -44178,7 +44178,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1491" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -44204,7 +44204,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1492" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -44230,7 +44230,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G1493" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -44256,7 +44256,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1494" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -44282,7 +44282,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G1495" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -44308,7 +44308,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1496" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -44334,7 +44334,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1497" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -44360,7 +44360,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1498" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -44386,7 +44386,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1499" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -44412,7 +44412,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1500" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -44438,7 +44438,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1501" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -44464,7 +44464,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1502" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -44490,7 +44490,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G1503" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -44516,7 +44516,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1504" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -44542,7 +44542,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1505" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -44568,7 +44568,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1506" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -44594,7 +44594,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G1507" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -44620,7 +44620,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1508" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -44646,7 +44646,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1509" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -44672,7 +44672,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G1510" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -44698,7 +44698,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G1511" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -44724,7 +44724,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G1512" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -44750,7 +44750,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1513" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -44776,7 +44776,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G1514" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -44802,7 +44802,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G1515" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -44828,7 +44828,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G1516" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -44854,7 +44854,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1517" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -44880,7 +44880,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1518" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -44906,7 +44906,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1519" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -44932,7 +44932,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G1520" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -44958,7 +44958,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1521" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -44984,7 +44984,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1522" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -45010,7 +45010,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1523" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -45036,7 +45036,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G1524" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -45062,7 +45062,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1525" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -45088,7 +45088,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1526" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -45114,7 +45114,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1527" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -45140,7 +45140,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G1528" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -45166,7 +45166,7 @@
         <v>8.47000026702881</v>
       </c>
       <c r="G1529" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -45192,7 +45192,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1530" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -45218,7 +45218,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G1531" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -45244,7 +45244,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1532" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -45270,7 +45270,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G1533" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -45296,7 +45296,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G1534" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -45322,7 +45322,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1535" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -45348,7 +45348,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1536" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -45374,7 +45374,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1537" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -45400,7 +45400,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1538" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -45426,7 +45426,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1539" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -45452,7 +45452,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G1540" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -45478,7 +45478,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1541" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -45504,7 +45504,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1542" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -45530,7 +45530,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1543" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -45556,7 +45556,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1544" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -45582,7 +45582,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1545" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -45608,7 +45608,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1546" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -45634,7 +45634,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1547" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -45660,7 +45660,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G1548" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -45686,7 +45686,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1549" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -45712,7 +45712,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1550" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -45738,7 +45738,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G1551" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -45764,7 +45764,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1552" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -45790,7 +45790,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1553" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -45816,7 +45816,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G1554" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -45842,7 +45842,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1555" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -45868,7 +45868,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G1556" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -45894,7 +45894,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1557" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -45920,7 +45920,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G1558" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -45946,7 +45946,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1559" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -45972,7 +45972,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1560" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -45998,7 +45998,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1561" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -46024,7 +46024,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1562" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -46050,7 +46050,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G1563" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -46076,7 +46076,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1564" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -46102,7 +46102,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1565" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -46128,7 +46128,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1566" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -46154,7 +46154,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1567" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -46180,7 +46180,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1568" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -46206,7 +46206,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1569" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -46232,7 +46232,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G1570" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -46258,7 +46258,7 @@
         <v>6.5</v>
       </c>
       <c r="G1571" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -46284,7 +46284,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1572" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -46310,7 +46310,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1573" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -46336,7 +46336,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1574" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -46362,7 +46362,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1575" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -46388,7 +46388,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G1576" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -46414,7 +46414,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G1577" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -46440,7 +46440,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1578" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -46466,7 +46466,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1579" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -46492,7 +46492,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G1580" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -46518,7 +46518,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1581" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -46544,7 +46544,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G1582" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -46570,7 +46570,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G1583" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -46596,7 +46596,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G1584" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -46622,7 +46622,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1585" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -46648,7 +46648,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G1586" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -46674,7 +46674,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1587" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -46700,7 +46700,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1588" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -46726,7 +46726,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1589" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -46752,7 +46752,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1590" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -46778,7 +46778,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G1591" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -46804,7 +46804,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1592" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -46830,7 +46830,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G1593" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -46856,7 +46856,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G1594" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -46882,7 +46882,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1595" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -46908,7 +46908,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G1596" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -46934,7 +46934,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G1597" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -46960,7 +46960,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G1598" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -46986,7 +46986,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G1599" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -47012,7 +47012,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G1600" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -47038,7 +47038,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G1601" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -47064,7 +47064,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G1602" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -47090,7 +47090,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G1603" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -47116,7 +47116,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1604" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -47142,7 +47142,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G1605" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -47168,7 +47168,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1606" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -47194,7 +47194,7 @@
         <v>6.57000017166138</v>
       </c>
       <c r="G1607" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -47220,7 +47220,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1608" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -47246,7 +47246,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G1609" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -47272,7 +47272,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1610" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -47298,7 +47298,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1611" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -47324,7 +47324,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G1612" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -47350,7 +47350,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G1613" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -47376,7 +47376,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1614" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -47402,7 +47402,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G1615" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -47428,7 +47428,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1616" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -47454,7 +47454,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1617" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -47480,7 +47480,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G1618" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -47506,7 +47506,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1619" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -47532,7 +47532,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G1620" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -47558,7 +47558,7 @@
         <v>6.75</v>
       </c>
       <c r="G1621" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -47584,7 +47584,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1622" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -47610,7 +47610,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1623" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -47636,7 +47636,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G1624" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -47662,7 +47662,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1625" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -47688,7 +47688,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G1626" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -47714,7 +47714,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1627" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -47740,7 +47740,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1628" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -47766,7 +47766,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1629" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -47792,7 +47792,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1630" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -47818,7 +47818,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1631" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -47844,7 +47844,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1632" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -47870,7 +47870,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G1633" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -47896,7 +47896,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1634" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -47922,7 +47922,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1635" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -47948,7 +47948,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G1636" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -47974,7 +47974,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1637" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -48000,7 +48000,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G1638" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -48026,7 +48026,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1639" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -48052,7 +48052,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G1640" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -48078,7 +48078,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1641" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -48104,7 +48104,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1642" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -48130,7 +48130,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1643" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -48156,7 +48156,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1644" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -48182,7 +48182,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G1645" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -48208,7 +48208,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G1646" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -48234,7 +48234,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G1647" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -48260,7 +48260,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1648" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -48286,7 +48286,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G1649" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -48312,7 +48312,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1650" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -48338,7 +48338,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1651" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -48364,7 +48364,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G1652" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -48390,7 +48390,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G1653" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -48416,7 +48416,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1654" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -48442,7 +48442,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1655" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -48468,7 +48468,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1656" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -48494,7 +48494,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1657" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -48520,7 +48520,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1658" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -48546,7 +48546,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1659" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -48572,7 +48572,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1660" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -48598,7 +48598,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G1661" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -48624,7 +48624,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1662" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -48650,7 +48650,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1663" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -48676,7 +48676,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1664" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -48702,7 +48702,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G1665" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -48728,7 +48728,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G1666" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -48754,7 +48754,7 @@
         <v>6</v>
       </c>
       <c r="G1667" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -48780,7 +48780,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1668" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -48806,7 +48806,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G1669" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -48832,7 +48832,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G1670" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -48858,7 +48858,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1671" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -48884,7 +48884,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G1672" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -48910,7 +48910,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1673" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -48936,7 +48936,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1674" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -48962,7 +48962,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1675" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -48988,7 +48988,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1676" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -49014,7 +49014,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G1677" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -49040,7 +49040,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1678" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -49066,7 +49066,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1679" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -49092,7 +49092,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1680" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -49118,7 +49118,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G1681" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -49144,7 +49144,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1682" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -49170,7 +49170,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1683" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -49196,7 +49196,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G1684" t="s">
-        <v>680</v>
+        <v>1135</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -49222,7 +49222,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1685" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -49248,7 +49248,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G1686" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -49300,7 +49300,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G1688" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -49352,7 +49352,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1690" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -49404,7 +49404,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1692" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -50600,7 +50600,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1738" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -50782,7 +50782,7 @@
         <v>6</v>
       </c>
       <c r="G1745" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -50808,7 +50808,7 @@
         <v>6</v>
       </c>
       <c r="G1746" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -50834,7 +50834,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1747" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -50886,7 +50886,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1749" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -50912,7 +50912,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G1750" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -50938,7 +50938,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G1751" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -50990,7 +50990,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1753" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -51042,7 +51042,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G1755" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -51068,7 +51068,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1756" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -51094,7 +51094,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1757" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -51146,7 +51146,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G1759" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -51172,7 +51172,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G1760" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -51198,7 +51198,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G1761" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -51380,7 +51380,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1768" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -51406,7 +51406,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1769" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -51432,7 +51432,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1770" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -51510,7 +51510,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1773" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -51614,7 +51614,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1777" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -51692,7 +51692,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G1780" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -51744,7 +51744,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1782" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -51796,7 +51796,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G1784" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -51874,7 +51874,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G1787" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -51926,7 +51926,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G1789" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -51952,7 +51952,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1790" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -51978,7 +51978,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1791" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -52004,7 +52004,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1792" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -52030,7 +52030,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1793" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -52108,7 +52108,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1796" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -52160,7 +52160,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1798" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -52186,7 +52186,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1799" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -52212,7 +52212,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G1800" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -52238,7 +52238,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1801" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -72500,7 +72500,7 @@
     </row>
     <row r="2581">
       <c r="A2581" s="1" t="n">
-        <v>46079.6910185185</v>
+        <v>46079.3333333333</v>
       </c>
       <c r="B2581" t="n">
         <v>394200</v>
@@ -72521,6 +72521,32 @@
         <v>1631</v>
       </c>
       <c r="H2581" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2582">
+      <c r="A2582" s="1" t="n">
+        <v>46080.6909837963</v>
+      </c>
+      <c r="B2582" t="n">
+        <v>167013</v>
+      </c>
+      <c r="C2582" t="n">
+        <v>16.2600002288818</v>
+      </c>
+      <c r="D2582" t="n">
+        <v>15.9399995803833</v>
+      </c>
+      <c r="E2582" t="n">
+        <v>16</v>
+      </c>
+      <c r="F2582" t="n">
+        <v>15.9799995422363</v>
+      </c>
+      <c r="G2582" t="s">
+        <v>1631</v>
+      </c>
+      <c r="H2582" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CEM.MI.xlsx
+++ b/data/CEM.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70432138442993</t>
+    <t xml:space="preserve">4.70432186126709</t>
   </si>
   <si>
     <t xml:space="preserve">CEM.MI</t>
@@ -47,109 +47,109 @@
     <t xml:space="preserve">4.68036031723022</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55656242370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48867273330688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32893419265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22110986709595</t>
+    <t xml:space="preserve">4.5565619468689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48867321014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32893371582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22111034393311</t>
   </si>
   <si>
     <t xml:space="preserve">4.32494068145752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2889986038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29299259185791</t>
+    <t xml:space="preserve">4.28899908065796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29299211502075</t>
   </si>
   <si>
     <t xml:space="preserve">4.06137084960938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93597531318665</t>
+    <t xml:space="preserve">3.93597507476807</t>
   </si>
   <si>
     <t xml:space="preserve">3.97431254386902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67560052871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83533978462219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94875431060791</t>
+    <t xml:space="preserve">3.67560005187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83534026145935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94875407218933</t>
   </si>
   <si>
     <t xml:space="preserve">3.88006687164307</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91680645942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87846946716309</t>
+    <t xml:space="preserve">3.91680717468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87846922874451</t>
   </si>
   <si>
     <t xml:space="preserve">3.74588584899902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93437790870667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87367677688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73789834976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57815980911255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59892535209656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6196916103363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35132956504822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15005803108215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25069355964661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13088917732239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20916152000427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44238138198853</t>
+    <t xml:space="preserve">3.93437838554382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87367630004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73789858818054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57815933227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59892559051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61969184875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3513298034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15005826950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25069379806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13088965415955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20916175842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44238090515137</t>
   </si>
   <si>
     <t xml:space="preserve">3.36251139640808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47592663764954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55419826507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34653759002686</t>
+    <t xml:space="preserve">3.4759259223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55419874191284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34653735160828</t>
   </si>
   <si>
     <t xml:space="preserve">3.39126396179199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36730360984802</t>
+    <t xml:space="preserve">3.3673038482666</t>
   </si>
   <si>
     <t xml:space="preserve">3.23951244354248</t>
@@ -158,136 +158,136 @@
     <t xml:space="preserve">3.29222655296326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40244650840759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58614659309387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63406777381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55579590797424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64365172386169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56058812141418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52065348625183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49828958511353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52544593811035</t>
+    <t xml:space="preserve">3.40244626998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58614611625671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63406872749329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55579543113708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64365196228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56058788299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52065300941467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49829006195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52544546127319</t>
   </si>
   <si>
     <t xml:space="preserve">3.54940605163574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75227546691895</t>
+    <t xml:space="preserve">3.75227475166321</t>
   </si>
   <si>
     <t xml:space="preserve">3.61330199241638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75387239456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83214497566223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67080807685852</t>
+    <t xml:space="preserve">3.75387263298035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83214473724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6708083152771</t>
   </si>
   <si>
     <t xml:space="preserve">3.70754837989807</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65802884101868</t>
+    <t xml:space="preserve">3.65802907943726</t>
   </si>
   <si>
     <t xml:space="preserve">3.51745843887329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57017183303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50947189331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5430166721344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57975649833679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45196580886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4104335308075</t>
+    <t xml:space="preserve">3.57017254829407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50947141647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54301619529724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57975673675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45196557044983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41043305397034</t>
   </si>
   <si>
     <t xml:space="preserve">3.37529015541077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60052227973938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48551058769226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54461431503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59573006629944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7794303894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74428844451904</t>
+    <t xml:space="preserve">3.60052275657654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48551082611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54461455345154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59573030471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77943086624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74428868293762</t>
   </si>
   <si>
     <t xml:space="preserve">3.8577024936676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73949575424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74907970428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70595002174377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69317197799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67719745635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7970027923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.666015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70115804672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62608170509338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6740026473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64205551147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53023767471313</t>
+    <t xml:space="preserve">3.73949551582336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74908018112183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70595073699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69317126274109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67719793319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79700231552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66601586341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70115900039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62608075141907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67400288581848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64205479621887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53023791313171</t>
   </si>
   <si>
     <t xml:space="preserve">3.45835494995117</t>
@@ -296,106 +296,106 @@
     <t xml:space="preserve">3.47432851791382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53193712234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62187075614929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75758862495422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76085877418518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87531971931458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88349604606628</t>
+    <t xml:space="preserve">3.53193736076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62187027931213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75758910179138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76085901260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.875319480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88349580764771</t>
   </si>
   <si>
     <t xml:space="preserve">3.7772102355957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75431799888611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70526361465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66928958892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59734344482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5842616558075</t>
+    <t xml:space="preserve">3.75431847572327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70526385307312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66929054260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59734320640564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58426189422607</t>
   </si>
   <si>
     <t xml:space="preserve">3.55646395683289</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38640832901001</t>
+    <t xml:space="preserve">3.38640809059143</t>
   </si>
   <si>
     <t xml:space="preserve">3.31119108200073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29810929298401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19672989845276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15912127494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00705194473267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15421628952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0348494052887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22289252281189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35207009315491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10679626464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82881999015808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82064414024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84026598930359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93510460853577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04302549362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95799732208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79611706733704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76341414451599</t>
+    <t xml:space="preserve">3.29810976982117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19673013687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1591215133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00705218315125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15421605110168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03484988212585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22289276123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35206961631775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10679650306702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82882022857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82064390182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84026575088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93510508537292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04302525520325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95799708366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79611682891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76341390609741</t>
   </si>
   <si>
     <t xml:space="preserve">2.76831889152527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84844160079956</t>
+    <t xml:space="preserve">2.84844183921814</t>
   </si>
   <si>
     <t xml:space="preserve">2.87787461280823</t>
@@ -407,67 +407,67 @@
     <t xml:space="preserve">3.00051140785217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21144604682922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13295936584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07572841644287</t>
+    <t xml:space="preserve">3.21144652366638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13295888900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07572865486145</t>
   </si>
   <si>
     <t xml:space="preserve">2.97434878349304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10843205451965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9759840965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92856431007385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17547297477722</t>
+    <t xml:space="preserve">3.10843181610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97598385810852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92856454849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17547273635864</t>
   </si>
   <si>
     <t xml:space="preserve">3.18037867546082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15585112571716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18855452537537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09862089157104</t>
+    <t xml:space="preserve">3.15585088729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18855428695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09862065315247</t>
   </si>
   <si>
     <t xml:space="preserve">3.12151288986206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0250391960144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11660766601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23760914802551</t>
+    <t xml:space="preserve">3.02503871917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11660718917847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23760890960693</t>
   </si>
   <si>
     <t xml:space="preserve">3.28012299537659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32263731956482</t>
+    <t xml:space="preserve">3.32263684272766</t>
   </si>
   <si>
     <t xml:space="preserve">3.43546295166016</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40602946281433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46653032302856</t>
+    <t xml:space="preserve">3.40602970123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46653056144714</t>
   </si>
   <si>
     <t xml:space="preserve">3.43709802627563</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">3.64639782905579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71834421157837</t>
+    <t xml:space="preserve">3.71834468841553</t>
   </si>
   <si>
     <t xml:space="preserve">3.69545221328735</t>
@@ -491,58 +491,58 @@
     <t xml:space="preserve">3.74450707435608</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85242772102356</t>
+    <t xml:space="preserve">3.8524272441864</t>
   </si>
   <si>
     <t xml:space="preserve">3.80827856063843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82299447059631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80337262153625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7428719997406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62350606918335</t>
+    <t xml:space="preserve">3.82299518585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80337238311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74287271499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62350583076477</t>
   </si>
   <si>
     <t xml:space="preserve">3.56627559661865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47470664978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51558542251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65947842597961</t>
+    <t xml:space="preserve">3.47470641136169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51558566093445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65947890281677</t>
   </si>
   <si>
     <t xml:space="preserve">3.60551857948303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54501867294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64803266525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64476299285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38804364204407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48288249969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45344972610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43382716178894</t>
+    <t xml:space="preserve">3.54501819610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64803338050842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64476275444031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38804340362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4828827381134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45344924926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4338276386261</t>
   </si>
   <si>
     <t xml:space="preserve">3.5074098110199</t>
@@ -551,10 +551,10 @@
     <t xml:space="preserve">3.56464028358459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55482935905457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56300497055054</t>
+    <t xml:space="preserve">3.55482864379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56300449371338</t>
   </si>
   <si>
     <t xml:space="preserve">3.48451733589172</t>
@@ -563,13 +563,13 @@
     <t xml:space="preserve">3.54338312149048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62514066696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59080266952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64149284362793</t>
+    <t xml:space="preserve">3.62514090538025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59080290794373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64149212837219</t>
   </si>
   <si>
     <t xml:space="preserve">3.68891215324402</t>
@@ -581,67 +581,67 @@
     <t xml:space="preserve">3.68727684020996</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53684210777283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63004684448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63822197914124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43873286247253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41747617721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41911149024963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33571839332581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37169146537781</t>
+    <t xml:space="preserve">3.53684258460999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63004660606384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63822221755981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43873310089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41747546195984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41911101341248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33571815490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37169170379639</t>
   </si>
   <si>
     <t xml:space="preserve">3.27521753311157</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22125744819641</t>
+    <t xml:space="preserve">3.22125720977783</t>
   </si>
   <si>
     <t xml:space="preserve">3.2098114490509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17710781097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21308183670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14767551422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11333727836609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00541687011719</t>
+    <t xml:space="preserve">3.17710828781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21308207511902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14767479896545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11333703994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00541710853577</t>
   </si>
   <si>
     <t xml:space="preserve">3.0168628692627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95309162139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9187536239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96453762054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96780824661255</t>
+    <t xml:space="preserve">2.9530918598175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91875386238098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96453785896301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96780800819397</t>
   </si>
   <si>
     <t xml:space="preserve">2.95636200904846</t>
@@ -656,10 +656,10 @@
     <t xml:space="preserve">3.18691897392273</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31936645507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23433899879456</t>
+    <t xml:space="preserve">3.31936693191528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23433828353882</t>
   </si>
   <si>
     <t xml:space="preserve">3.45835518836975</t>
@@ -668,31 +668,31 @@
     <t xml:space="preserve">3.48778772354126</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45181465148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4992344379425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57281541824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45017862319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61369466781616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67746639251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58916687965393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70362854003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48615264892578</t>
+    <t xml:space="preserve">3.4518141746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49923396110535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57281589508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45017910003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61369514465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67746567726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58916735649109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70362901687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4861524105072</t>
   </si>
   <si>
     <t xml:space="preserve">3.33244824409485</t>
@@ -701,22 +701,22 @@
     <t xml:space="preserve">3.28666353225708</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22943329811096</t>
+    <t xml:space="preserve">3.22943305969238</t>
   </si>
   <si>
     <t xml:space="preserve">3.27031183242798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24742007255554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23106813430786</t>
+    <t xml:space="preserve">3.24741983413696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23106837272644</t>
   </si>
   <si>
     <t xml:space="preserve">3.23270344734192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26213598251343</t>
+    <t xml:space="preserve">3.26213622093201</t>
   </si>
   <si>
     <t xml:space="preserve">3.27685260772705</t>
@@ -725,16 +725,16 @@
     <t xml:space="preserve">3.23597359657288</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00122690200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04701042175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12876844406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16964817047119</t>
+    <t xml:space="preserve">4.0012264251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04701137542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12876892089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16964721679688</t>
   </si>
   <si>
     <t xml:space="preserve">4.17782354354858</t>
@@ -743,88 +743,88 @@
     <t xml:space="preserve">4.06336259841919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95707845687866</t>
+    <t xml:space="preserve">3.95707774162292</t>
   </si>
   <si>
     <t xml:space="preserve">4.19417572021484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28410863876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3454270362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47215175628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43944835662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41083335876465</t>
+    <t xml:space="preserve">4.28410911560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34542655944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47215223312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43944787979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41083383560181</t>
   </si>
   <si>
     <t xml:space="preserve">4.41492176055908</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37404155731201</t>
+    <t xml:space="preserve">4.37404298782349</t>
   </si>
   <si>
     <t xml:space="preserve">4.26775693893433</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39039373397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3617787361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3781304359436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38630628585815</t>
+    <t xml:space="preserve">4.39039421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36177921295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37813091278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.386305809021</t>
   </si>
   <si>
     <t xml:space="preserve">4.56208515167236</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42718458175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3290753364563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2554931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25140571594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30046033859253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34951496124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24323081970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24731731414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21052694320679</t>
+    <t xml:space="preserve">4.42718505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32907581329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25549364089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25140523910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30046081542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34951543807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24323034286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24731779098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21052646636963</t>
   </si>
   <si>
     <t xml:space="preserve">4.14512062072754</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1042423248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22279024124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40674495697021</t>
+    <t xml:space="preserve">4.10424184799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2227897644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40674543380737</t>
   </si>
   <si>
     <t xml:space="preserve">4.36586713790894</t>
@@ -833,16 +833,16 @@
     <t xml:space="preserve">4.27593326568604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3045482635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28002119064331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44762420654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52938318252563</t>
+    <t xml:space="preserve">4.30454778671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28002166748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44762468338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52938079833984</t>
   </si>
   <si>
     <t xml:space="preserve">4.51711797714233</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">4.68063402175903</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66019439697266</t>
+    <t xml:space="preserve">4.66019487380981</t>
   </si>
   <si>
     <t xml:space="preserve">4.71333742141724</t>
@@ -866,19 +866,19 @@
     <t xml:space="preserve">4.81962251663208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81144762039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65201902389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34133958816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33725118637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25958156585693</t>
+    <t xml:space="preserve">4.81144618988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65201807022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34133911132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33725166320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25958108901978</t>
   </si>
   <si>
     <t xml:space="preserve">4.4038348197937</t>
@@ -887,43 +887,43 @@
     <t xml:space="preserve">4.44966506958008</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41633367538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37467002868652</t>
+    <t xml:space="preserve">4.41633415222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37467050552368</t>
   </si>
   <si>
     <t xml:space="preserve">4.36633729934692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30384206771851</t>
+    <t xml:space="preserve">4.30384159088135</t>
   </si>
   <si>
     <t xml:space="preserve">4.27467823028564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25801229476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31634092330933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26634454727173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20801544189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33300638198853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37050294876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34550476074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39133548736572</t>
+    <t xml:space="preserve">4.25801181793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31634140014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26634502410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20801591873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33300590515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3705039024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34550523757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39133501052856</t>
   </si>
   <si>
     <t xml:space="preserve">4.29967546463013</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">4.42883253097534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39966821670532</t>
+    <t xml:space="preserve">4.39966869354248</t>
   </si>
   <si>
     <t xml:space="preserve">4.3955020904541</t>
@@ -941,28 +941,28 @@
     <t xml:space="preserve">4.38300275802612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46633005142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.482994556427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56632280349731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40800046920776</t>
+    <t xml:space="preserve">4.46632957458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48299503326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56632232666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40800094604492</t>
   </si>
   <si>
     <t xml:space="preserve">4.34967184066772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69131374359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58298826217651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85380029678345</t>
+    <t xml:space="preserve">4.69131326675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58298778533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85380077362061</t>
   </si>
   <si>
     <t xml:space="preserve">4.99962329864502</t>
@@ -971,88 +971,88 @@
     <t xml:space="preserve">5.05795192718506</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10794878005981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24960470199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28710079193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25377035140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41625785827637</t>
+    <t xml:space="preserve">5.1079478263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24960422515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28710126876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25376987457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41625833511353</t>
   </si>
   <si>
     <t xml:space="preserve">5.30376672744751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29960060119629</t>
+    <t xml:space="preserve">5.29959964752197</t>
   </si>
   <si>
     <t xml:space="preserve">5.34542989730835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30793237686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22877216339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29126739501953</t>
+    <t xml:space="preserve">5.30793285369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22877264022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29126787185669</t>
   </si>
   <si>
     <t xml:space="preserve">5.29543399810791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16211128234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01628875732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.053786277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12461376190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20377349853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0746169090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03295373916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95795965194702</t>
+    <t xml:space="preserve">5.16211080551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01628828048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05378580093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1246132850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20377445220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07461738586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03295421600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95795869827271</t>
   </si>
   <si>
     <t xml:space="preserve">4.99129009246826</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96212530136108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90796327590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94129419326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89129781723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90379762649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95379257202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94545984268188</t>
+    <t xml:space="preserve">4.9621262550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90796375274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94129467010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89129734039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90379619598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9537935256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94546031951904</t>
   </si>
   <si>
     <t xml:space="preserve">4.91629600524902</t>
@@ -1061,52 +1061,52 @@
     <t xml:space="preserve">5.02462100982666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0496187210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11628103256226</t>
+    <t xml:space="preserve">5.04961919784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1162805557251</t>
   </si>
   <si>
     <t xml:space="preserve">5.17460966110229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23293924331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17877578735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13294553756714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33293151855469</t>
+    <t xml:space="preserve">5.23293876647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17877626419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1329460144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33293104171753</t>
   </si>
   <si>
     <t xml:space="preserve">5.26626968383789</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22460651397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5829119682312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68707132339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0037145614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80789566040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07454109191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01621294021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16620254516602</t>
+    <t xml:space="preserve">5.22460603713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58291244506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68707180023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00371313095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80789470672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07454204559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01621246337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1662015914917</t>
   </si>
   <si>
     <t xml:space="preserve">5.89122295379639</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">5.94121885299683</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96621656417847</t>
+    <t xml:space="preserve">5.96621608734131</t>
   </si>
   <si>
     <t xml:space="preserve">6.03287792205811</t>
@@ -1124,40 +1124,40 @@
     <t xml:space="preserve">5.9953818321228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97038316726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91622066497803</t>
+    <t xml:space="preserve">5.97038221359253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91622018814087</t>
   </si>
   <si>
     <t xml:space="preserve">5.86205768585205</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92871904373169</t>
+    <t xml:space="preserve">5.92871952056885</t>
   </si>
   <si>
     <t xml:space="preserve">5.89955472946167</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90372133255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87455749511719</t>
+    <t xml:space="preserve">5.90372228622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87455654144287</t>
   </si>
   <si>
     <t xml:space="preserve">5.84539270401001</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00788021087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98288106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03704404830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09120655059814</t>
+    <t xml:space="preserve">6.00788068771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98288249969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03704500198364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0912070274353</t>
   </si>
   <si>
     <t xml:space="preserve">6.02871227264404</t>
@@ -1166,31 +1166,31 @@
     <t xml:space="preserve">5.99954700469971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04954385757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07870864868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29119253158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1745343208313</t>
+    <t xml:space="preserve">6.0495433807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07870817184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29119157791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17453384399414</t>
   </si>
   <si>
     <t xml:space="preserve">6.1995325088501</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0828742980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24536275863647</t>
+    <t xml:space="preserve">6.08287477493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24536228179932</t>
   </si>
   <si>
     <t xml:space="preserve">6.21203136444092</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02454614639282</t>
+    <t xml:space="preserve">6.02454566955566</t>
   </si>
   <si>
     <t xml:space="preserve">6.0995397567749</t>
@@ -1208,37 +1208,37 @@
     <t xml:space="preserve">6.14536952972412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95788431167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94538497924805</t>
+    <t xml:space="preserve">5.95788383483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94538545608521</t>
   </si>
   <si>
     <t xml:space="preserve">6.01204633712769</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02037906646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11620569229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06204223632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04121065139771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1495361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09537410736084</t>
+    <t xml:space="preserve">6.02037954330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11620616912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06204271316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04121208190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14953660964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09537363052368</t>
   </si>
   <si>
     <t xml:space="preserve">6.35785436630249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2245306968689</t>
+    <t xml:space="preserve">6.22453022003174</t>
   </si>
   <si>
     <t xml:space="preserve">6.28285980224609</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">6.58283710479736</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61616706848145</t>
+    <t xml:space="preserve">6.61616802215576</t>
   </si>
   <si>
     <t xml:space="preserve">6.57450389862061</t>
@@ -1262,25 +1262,25 @@
     <t xml:space="preserve">6.65783071517944</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74115800857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59116888046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62449979782104</t>
+    <t xml:space="preserve">6.74115896224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5911693572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62449932098389</t>
   </si>
   <si>
     <t xml:space="preserve">6.63283348083496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7078275680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52450752258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51617479324341</t>
+    <t xml:space="preserve">6.70782804489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52450847625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51617527008057</t>
   </si>
   <si>
     <t xml:space="preserve">6.66616344451904</t>
@@ -1289,19 +1289,19 @@
     <t xml:space="preserve">6.54950666427612</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44951391220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29952478408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23286294937134</t>
+    <t xml:space="preserve">6.44951343536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29952526092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2328634262085</t>
   </si>
   <si>
     <t xml:space="preserve">5.90788793563843</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93288564682007</t>
+    <t xml:space="preserve">5.93288612365723</t>
   </si>
   <si>
     <t xml:space="preserve">6.53284072875977</t>
@@ -1313,46 +1313,46 @@
     <t xml:space="preserve">6.36618614196777</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33285522460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14120388031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1578688621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06620931625366</t>
+    <t xml:space="preserve">6.33285570144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14120292663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15786838531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0662088394165</t>
   </si>
   <si>
     <t xml:space="preserve">5.94955158233643</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13287115097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05787658691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88289022445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84955883026123</t>
+    <t xml:space="preserve">6.1328706741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0578761100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88288974761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84955930709839</t>
   </si>
   <si>
     <t xml:space="preserve">5.81622791290283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72456789016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75789833068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76623201370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6829047203064</t>
+    <t xml:space="preserve">5.72456836700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75789928436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76623249053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68290424346924</t>
   </si>
   <si>
     <t xml:space="preserve">5.82456064224243</t>
@@ -1361,10 +1361,10 @@
     <t xml:space="preserve">5.86622428894043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77456474304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78289747238159</t>
+    <t xml:space="preserve">5.77456426620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78289699554443</t>
   </si>
   <si>
     <t xml:space="preserve">5.79122924804688</t>
@@ -1373,31 +1373,31 @@
     <t xml:space="preserve">5.63290929794312</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6498236656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68365478515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66673946380615</t>
+    <t xml:space="preserve">5.64982414245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68365526199341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66673994064331</t>
   </si>
   <si>
     <t xml:space="preserve">5.70057058334351</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48066854476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45529413223267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54833078384399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53987264633179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74286031723022</t>
+    <t xml:space="preserve">5.48066806793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45529460906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54833030700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53987312316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74285984039307</t>
   </si>
   <si>
     <t xml:space="preserve">5.58216142654419</t>
@@ -1406,13 +1406,13 @@
     <t xml:space="preserve">5.65828227996826</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70902919769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77669095993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91201639175415</t>
+    <t xml:space="preserve">5.70902872085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77669143676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91201686859131</t>
   </si>
   <si>
     <t xml:space="preserve">5.9035587310791</t>
@@ -1421,13 +1421,13 @@
     <t xml:space="preserve">5.89510059356689</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75131750106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78514909744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71748685836792</t>
+    <t xml:space="preserve">5.75131845474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78514957427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71748733520508</t>
   </si>
   <si>
     <t xml:space="preserve">5.81052303314209</t>
@@ -1436,67 +1436,67 @@
     <t xml:space="preserve">5.56524658203125</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50604152679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69211292266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72594451904297</t>
+    <t xml:space="preserve">5.50604104995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69211339950562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72594499588013</t>
   </si>
   <si>
     <t xml:space="preserve">5.73440217971802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60753536224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51449871063232</t>
+    <t xml:space="preserve">5.60753488540649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51449918746948</t>
   </si>
   <si>
     <t xml:space="preserve">5.67519807815552</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01351022720337</t>
+    <t xml:space="preserve">6.01350975036621</t>
   </si>
   <si>
     <t xml:space="preserve">5.99659490585327</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81898021697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75977611541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80206489562988</t>
+    <t xml:space="preserve">5.81898069381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75977659225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80206537246704</t>
   </si>
   <si>
     <t xml:space="preserve">5.79360723495483</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88664293289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8781852722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92893218994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85281181335449</t>
+    <t xml:space="preserve">5.88664388656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87818479537964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92893171310425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85281229019165</t>
   </si>
   <si>
     <t xml:space="preserve">5.76823329925537</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82743835449219</t>
+    <t xml:space="preserve">5.82743787765503</t>
   </si>
   <si>
     <t xml:space="preserve">5.83589601516724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42992067337036</t>
+    <t xml:space="preserve">5.42992115020752</t>
   </si>
   <si>
     <t xml:space="preserve">5.38763189315796</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">5.33688497543335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26076364517212</t>
+    <t xml:space="preserve">5.26076412200928</t>
   </si>
   <si>
     <t xml:space="preserve">5.303053855896</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">5.46375226974487</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44683599472046</t>
+    <t xml:space="preserve">5.44683647155762</t>
   </si>
   <si>
     <t xml:space="preserve">5.35380029678345</t>
@@ -1526,22 +1526,22 @@
     <t xml:space="preserve">5.3707160949707</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22693252563477</t>
+    <t xml:space="preserve">5.22693300247192</t>
   </si>
   <si>
     <t xml:space="preserve">5.14235544204712</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11698198318481</t>
+    <t xml:space="preserve">5.11698150634766</t>
   </si>
   <si>
     <t xml:space="preserve">5.24384880065918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13389778137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26922225952148</t>
+    <t xml:space="preserve">5.13389730453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26922273635864</t>
   </si>
   <si>
     <t xml:space="preserve">5.25230646133423</t>
@@ -1559,16 +1559,16 @@
     <t xml:space="preserve">5.31996917724609</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29459619522095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48912572860718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32842683792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16772890090942</t>
+    <t xml:space="preserve">5.29459571838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48912525177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3284273147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16772842407227</t>
   </si>
   <si>
     <t xml:space="preserve">5.09160804748535</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">5.17618656158447</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10852384567261</t>
+    <t xml:space="preserve">5.10852432250977</t>
   </si>
   <si>
     <t xml:space="preserve">4.91399383544922</t>
@@ -1589,28 +1589,28 @@
     <t xml:space="preserve">4.49956083297729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.567223072052</t>
+    <t xml:space="preserve">4.56722354888916</t>
   </si>
   <si>
     <t xml:space="preserve">4.38115119934082</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54185009002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5249342918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61797046661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46572923660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27120018005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14433240890503</t>
+    <t xml:space="preserve">4.5418496131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52493476867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61796998977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46572971343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27119922637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14433145523071</t>
   </si>
   <si>
     <t xml:space="preserve">4.22045230865479</t>
@@ -1619,10 +1619,10 @@
     <t xml:space="preserve">4.09358501434326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20353746414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15701866149902</t>
+    <t xml:space="preserve">4.20353698730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15701913833618</t>
   </si>
   <si>
     <t xml:space="preserve">4.39806652069092</t>
@@ -1631,19 +1631,19 @@
     <t xml:space="preserve">4.53339195251465</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59259700775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60951232910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63488531112671</t>
+    <t xml:space="preserve">4.59259605407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60951280593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63488578796387</t>
   </si>
   <si>
     <t xml:space="preserve">4.41498231887817</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49110317230225</t>
+    <t xml:space="preserve">4.49110221862793</t>
   </si>
   <si>
     <t xml:space="preserve">4.42344045639038</t>
@@ -1652,16 +1652,16 @@
     <t xml:space="preserve">4.43189811706543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29657316207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33886241912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19507932662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04706764221191</t>
+    <t xml:space="preserve">4.2965726852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33886289596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19507884979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04706716537476</t>
   </si>
   <si>
     <t xml:space="preserve">4.08512735366821</t>
@@ -1670,19 +1670,19 @@
     <t xml:space="preserve">4.10627222061157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15279006958008</t>
+    <t xml:space="preserve">4.15279054641724</t>
   </si>
   <si>
     <t xml:space="preserve">4.2373685836792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21622371673584</t>
+    <t xml:space="preserve">4.21622323989868</t>
   </si>
   <si>
     <t xml:space="preserve">4.16124773025513</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10204315185547</t>
+    <t xml:space="preserve">4.10204267501831</t>
   </si>
   <si>
     <t xml:space="preserve">4.03860950469971</t>
@@ -1691,70 +1691,70 @@
     <t xml:space="preserve">4.30503082275391</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25428485870361</t>
+    <t xml:space="preserve">4.2542839050293</t>
   </si>
   <si>
     <t xml:space="preserve">4.14010334014893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05129623413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14856052398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08935642242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0343804359436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94557332992554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35577821731567</t>
+    <t xml:space="preserve">4.0512957572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14856100082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08935594558716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03437995910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9455738067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35577726364136</t>
   </si>
   <si>
     <t xml:space="preserve">4.3134880065918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48264503479004</t>
+    <t xml:space="preserve">4.4826455116272</t>
   </si>
   <si>
     <t xml:space="preserve">4.65180110931396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79558420181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78712606430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82095766067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86324691772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90553617477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88861989974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95628261566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00703001022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01548767089844</t>
+    <t xml:space="preserve">4.7955846786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78712701797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82095813751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86324644088745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90553569793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88862085342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95628356933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00702953338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0154881477356</t>
   </si>
   <si>
     <t xml:space="preserve">5.03240299224854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.057776927948</t>
+    <t xml:space="preserve">5.05777645111084</t>
   </si>
   <si>
     <t xml:space="preserve">4.99011421203613</t>
@@ -1763,58 +1763,58 @@
     <t xml:space="preserve">4.97319841384888</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20156002044678</t>
+    <t xml:space="preserve">5.20155954360962</t>
   </si>
   <si>
     <t xml:space="preserve">5.12543916702271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15927076339722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21847486495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34534215927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27767896652222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40454721450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39608955383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47220993041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49758338928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42146301269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41300487518311</t>
+    <t xml:space="preserve">5.15927028656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21847534179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3453426361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27767992019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40454769134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39608907699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47220945358276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49758386611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42146253585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41300535202026</t>
   </si>
   <si>
     <t xml:space="preserve">4.98165702819824</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11462545394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13193321228027</t>
+    <t xml:space="preserve">5.11462450027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13193368911743</t>
   </si>
   <si>
     <t xml:space="preserve">5.01942873001099</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01077556610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06270027160645</t>
+    <t xml:space="preserve">5.01077461242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06269979476929</t>
   </si>
   <si>
     <t xml:space="preserve">5.08866262435913</t>
@@ -1823,16 +1823,16 @@
     <t xml:space="preserve">5.09731721878052</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14058685302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20116758346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17520427703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2271294593811</t>
+    <t xml:space="preserve">5.14058780670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20116710662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17520380020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22712993621826</t>
   </si>
   <si>
     <t xml:space="preserve">5.26174640655518</t>
@@ -1841,34 +1841,34 @@
     <t xml:space="preserve">5.23578357696533</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25309276580811</t>
+    <t xml:space="preserve">5.25309228897095</t>
   </si>
   <si>
     <t xml:space="preserve">5.33963394165039</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46079254150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54733419418335</t>
+    <t xml:space="preserve">5.46079301834106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54733371734619</t>
   </si>
   <si>
     <t xml:space="preserve">5.42617607116699</t>
   </si>
   <si>
-    <t xml:space="preserve">5.330979347229</t>
+    <t xml:space="preserve">5.33097982406616</t>
   </si>
   <si>
     <t xml:space="preserve">5.40886735916138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57329607009888</t>
+    <t xml:space="preserve">5.57329702377319</t>
   </si>
   <si>
     <t xml:space="preserve">5.52137184143066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47810077667236</t>
+    <t xml:space="preserve">5.47810029983521</t>
   </si>
   <si>
     <t xml:space="preserve">5.64253044128418</t>
@@ -1880,19 +1880,19 @@
     <t xml:space="preserve">5.74638032913208</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72907161712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65118455886841</t>
+    <t xml:space="preserve">5.72907209396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65118503570557</t>
   </si>
   <si>
     <t xml:space="preserve">5.70310974121094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66849374771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59925937652588</t>
+    <t xml:space="preserve">5.66849327087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59925889968872</t>
   </si>
   <si>
     <t xml:space="preserve">5.49540948867798</t>
@@ -1916,13 +1916,13 @@
     <t xml:space="preserve">5.1838583946228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28770875930786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19251251220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12327909469604</t>
+    <t xml:space="preserve">5.2877082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19251298904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12327861785889</t>
   </si>
   <si>
     <t xml:space="preserve">5.2704005241394</t>
@@ -1931,10 +1931,10 @@
     <t xml:space="preserve">5.08000802993774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14924192428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16654968261719</t>
+    <t xml:space="preserve">5.14924144744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16655015945435</t>
   </si>
   <si>
     <t xml:space="preserve">5.15789556503296</t>
@@ -1943,16 +1943,16 @@
     <t xml:space="preserve">5.29636287689209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53867959976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44348478317261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48675441741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40021276473999</t>
+    <t xml:space="preserve">5.53868007659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44348430633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48675537109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40021324157715</t>
   </si>
   <si>
     <t xml:space="preserve">5.36559629440308</t>
@@ -1961,55 +1961,55 @@
     <t xml:space="preserve">5.32232522964478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38290405273438</t>
+    <t xml:space="preserve">5.38290452957153</t>
   </si>
   <si>
     <t xml:space="preserve">5.02808332443237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04539155960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16222381591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03933382034302</t>
+    <t xml:space="preserve">5.04539203643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16222333908081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03933334350586</t>
   </si>
   <si>
     <t xml:space="preserve">5.10597085952759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15270328521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20895576477051</t>
+    <t xml:space="preserve">5.15270376205444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20895528793335</t>
   </si>
   <si>
     <t xml:space="preserve">5.27905464172363</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34569215774536</t>
+    <t xml:space="preserve">5.3456916809082</t>
   </si>
   <si>
     <t xml:space="preserve">5.32665300369263</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27991962432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30588293075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26780414581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34742212295532</t>
+    <t xml:space="preserve">5.27992010116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30588245391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26780366897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34742259979248</t>
   </si>
   <si>
     <t xml:space="preserve">5.21934080123901</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34309530258179</t>
+    <t xml:space="preserve">5.34309577941895</t>
   </si>
   <si>
     <t xml:space="preserve">5.48502397537231</t>
@@ -2018,34 +2018,34 @@
     <t xml:space="preserve">5.43915700912476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31799840927124</t>
+    <t xml:space="preserve">5.31799793243408</t>
   </si>
   <si>
     <t xml:space="preserve">5.51791048049927</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61656808853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51617956161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46252346038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42271375656128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46771621704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44434976577759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46944713592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78099679946899</t>
+    <t xml:space="preserve">5.61656761169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51618003845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46252393722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42271423339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46771574020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44434928894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46944665908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78099727630615</t>
   </si>
   <si>
     <t xml:space="preserve">6.02331495285034</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">6.0406231880188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04927682876587</t>
+    <t xml:space="preserve">6.04927730560303</t>
   </si>
   <si>
     <t xml:space="preserve">5.94456195831299</t>
@@ -2063,10 +2063,10 @@
     <t xml:space="preserve">5.76974678039551</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78272867202759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75416946411133</t>
+    <t xml:space="preserve">5.78272819519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75416994094849</t>
   </si>
   <si>
     <t xml:space="preserve">5.74118804931641</t>
@@ -2075,55 +2075,55 @@
     <t xml:space="preserve">5.73945713043213</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81042098999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90561771392822</t>
+    <t xml:space="preserve">5.81042194366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90561723709106</t>
   </si>
   <si>
     <t xml:space="preserve">5.93331146240234</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94109964370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91081047058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92638778686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85369253158569</t>
+    <t xml:space="preserve">5.94110012054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9108099937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92638826370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85369300842285</t>
   </si>
   <si>
     <t xml:space="preserve">5.85628890991211</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68060970306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73253440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81907606124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90648317337036</t>
+    <t xml:space="preserve">5.68060922622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73253393173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81907558441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90648365020752</t>
   </si>
   <si>
     <t xml:space="preserve">5.70570611953735</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57502746582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75590038299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81561374664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76022720336914</t>
+    <t xml:space="preserve">5.57502794265747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75589990615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81561422348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7602276802063</t>
   </si>
   <si>
     <t xml:space="preserve">5.73513031005859</t>
@@ -2147,19 +2147,19 @@
     <t xml:space="preserve">5.65810823440552</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57243204116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62522172927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67282009124756</t>
+    <t xml:space="preserve">5.57243156433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62522268295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67282056808472</t>
   </si>
   <si>
     <t xml:space="preserve">5.58195114135742</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58454704284668</t>
+    <t xml:space="preserve">5.58454751968384</t>
   </si>
   <si>
     <t xml:space="preserve">5.64512634277344</t>
@@ -2168,109 +2168,109 @@
     <t xml:space="preserve">5.72561073303223</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61483669281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60704803466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65291595458984</t>
+    <t xml:space="preserve">5.61483716964722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60704851150513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65291547775269</t>
   </si>
   <si>
     <t xml:space="preserve">5.65551137924194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75503492355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84071111679077</t>
+    <t xml:space="preserve">5.75503540039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84071207046509</t>
   </si>
   <si>
     <t xml:space="preserve">6.00600624084473</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92811822891235</t>
+    <t xml:space="preserve">5.92811870574951</t>
   </si>
   <si>
     <t xml:space="preserve">5.87619352340698</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71436023712158</t>
+    <t xml:space="preserve">5.71436071395874</t>
   </si>
   <si>
     <t xml:space="preserve">5.42184829711914</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36213493347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19510889053345</t>
+    <t xml:space="preserve">5.36213445663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19510936737061</t>
   </si>
   <si>
     <t xml:space="preserve">5.04019927978516</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15443420410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18039655685425</t>
+    <t xml:space="preserve">5.15443468093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18039703369141</t>
   </si>
   <si>
     <t xml:space="preserve">4.79615068435669</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24358081817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30113172531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30718994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94501185417175</t>
+    <t xml:space="preserve">4.24358129501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30113124847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30718898773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94501137733459</t>
   </si>
   <si>
     <t xml:space="preserve">4.11073923110962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98092603683472</t>
+    <t xml:space="preserve">3.98092675209045</t>
   </si>
   <si>
     <t xml:space="preserve">3.77452397346497</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89438462257385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17564535140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82385301589966</t>
+    <t xml:space="preserve">3.89438486099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17564582824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82385277748108</t>
   </si>
   <si>
     <t xml:space="preserve">3.9748682975769</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07006502151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27387094497681</t>
+    <t xml:space="preserve">4.07006454467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27387046813965</t>
   </si>
   <si>
     <t xml:space="preserve">4.11766242980957</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05665016174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.256995677948</t>
+    <t xml:space="preserve">4.05665063858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25699520111084</t>
   </si>
   <si>
     <t xml:space="preserve">4.30978584289551</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37036514282227</t>
+    <t xml:space="preserve">4.37036466598511</t>
   </si>
   <si>
     <t xml:space="preserve">4.17131853103638</t>
@@ -2279,19 +2279,19 @@
     <t xml:space="preserve">4.32709360122681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45690727233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6126823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48286914825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62999105453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56941080093384</t>
+    <t xml:space="preserve">4.45690631866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61268138885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48286962509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62999057769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.569411277771</t>
   </si>
   <si>
     <t xml:space="preserve">4.57806539535522</t>
@@ -2303,34 +2303,34 @@
     <t xml:space="preserve">4.50017738342285</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74249458312988</t>
+    <t xml:space="preserve">4.74249505996704</t>
   </si>
   <si>
     <t xml:space="preserve">4.76845788955688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79441976547241</t>
+    <t xml:space="preserve">4.79441928863525</t>
   </si>
   <si>
     <t xml:space="preserve">4.94154119491577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91557836532593</t>
+    <t xml:space="preserve">4.91557884216309</t>
   </si>
   <si>
     <t xml:space="preserve">4.83769083023071</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58671951293945</t>
+    <t xml:space="preserve">4.58671998977661</t>
   </si>
   <si>
     <t xml:space="preserve">4.55210304260254</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62133598327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6732611656189</t>
+    <t xml:space="preserve">4.62133693695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67326211929321</t>
   </si>
   <si>
     <t xml:space="preserve">4.80307483673096</t>
@@ -2339,16 +2339,19 @@
     <t xml:space="preserve">4.90961217880249</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73204898834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88297748565674</t>
+    <t xml:space="preserve">4.8030743598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73204803466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8829779624939</t>
   </si>
   <si>
     <t xml:space="preserve">4.91848945617676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10493087768555</t>
+    <t xml:space="preserve">5.10493040084839</t>
   </si>
   <si>
     <t xml:space="preserve">5.22034692764282</t>
@@ -2366,7 +2369,7 @@
     <t xml:space="preserve">5.3002495765686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52220296859741</t>
+    <t xml:space="preserve">5.52220344543457</t>
   </si>
   <si>
     <t xml:space="preserve">5.49556922912598</t>
@@ -2384,19 +2387,19 @@
     <t xml:space="preserve">5.63761949539185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30912828445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27361536026001</t>
+    <t xml:space="preserve">5.30912780761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27361583709717</t>
   </si>
   <si>
     <t xml:space="preserve">5.23810291290283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55771684646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73527956008911</t>
+    <t xml:space="preserve">5.55771636962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73527908325195</t>
   </si>
   <si>
     <t xml:space="preserve">5.61098527908325</t>
@@ -2405,25 +2408,25 @@
     <t xml:space="preserve">5.65537595748901</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68200969696045</t>
+    <t xml:space="preserve">5.68201017379761</t>
   </si>
   <si>
     <t xml:space="preserve">5.61986303329468</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64649772644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71752214431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58435106277466</t>
+    <t xml:space="preserve">5.64649724960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71752262115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5843505859375</t>
   </si>
   <si>
     <t xml:space="preserve">5.56659460067749</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53108167648315</t>
+    <t xml:space="preserve">5.53108215332031</t>
   </si>
   <si>
     <t xml:space="preserve">5.4600567817688</t>
@@ -2444,13 +2447,13 @@
     <t xml:space="preserve">5.38903188705444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29137134552002</t>
+    <t xml:space="preserve">5.29137182235718</t>
   </si>
   <si>
     <t xml:space="preserve">5.21146869659424</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36239719390869</t>
+    <t xml:space="preserve">5.36239767074585</t>
   </si>
   <si>
     <t xml:space="preserve">5.255859375</t>
@@ -2468,7 +2471,7 @@
     <t xml:space="preserve">5.59322881698608</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53995943069458</t>
+    <t xml:space="preserve">5.53995990753174</t>
   </si>
   <si>
     <t xml:space="preserve">5.5044469833374</t>
@@ -2480,10 +2483,10 @@
     <t xml:space="preserve">5.34464073181152</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28249406814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20259046554565</t>
+    <t xml:space="preserve">5.28249359130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20259094238281</t>
   </si>
   <si>
     <t xml:space="preserve">5.32688474655151</t>
@@ -2498,7 +2501,7 @@
     <t xml:space="preserve">5.15820026397705</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1315655708313</t>
+    <t xml:space="preserve">5.13156604766846</t>
   </si>
   <si>
     <t xml:space="preserve">5.16707801818848</t>
@@ -2507,10 +2510,10 @@
     <t xml:space="preserve">5.18483448028564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02502775192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90073394775391</t>
+    <t xml:space="preserve">5.02502822875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90073347091675</t>
   </si>
   <si>
     <t xml:space="preserve">4.61663293838501</t>
@@ -2519,7 +2522,7 @@
     <t xml:space="preserve">4.72317123413086</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85634326934814</t>
+    <t xml:space="preserve">4.85634279251099</t>
   </si>
   <si>
     <t xml:space="preserve">4.99839353561401</t>
@@ -2528,13 +2531,13 @@
     <t xml:space="preserve">5.00727128982544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89185619354248</t>
+    <t xml:space="preserve">4.89185571670532</t>
   </si>
   <si>
     <t xml:space="preserve">4.98951530456543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90396356582642</t>
+    <t xml:space="preserve">5.90396404266357</t>
   </si>
   <si>
     <t xml:space="preserve">6.01050138473511</t>
@@ -2549,16 +2552,16 @@
     <t xml:space="preserve">6.09928274154663</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10816049575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35674905776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.188063621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24133348464966</t>
+    <t xml:space="preserve">6.10816097259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35674858093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18806409835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2413330078125</t>
   </si>
   <si>
     <t xml:space="preserve">6.28572368621826</t>
@@ -2567,46 +2570,46 @@
     <t xml:space="preserve">6.3212366104126</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25021171569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30348014831543</t>
+    <t xml:space="preserve">6.25021123886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30347967147827</t>
   </si>
   <si>
     <t xml:space="preserve">6.31235790252686</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1170392036438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08152675628662</t>
+    <t xml:space="preserve">6.11703872680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08152627944946</t>
   </si>
   <si>
     <t xml:space="preserve">6.06377029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05489158630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98386669158936</t>
+    <t xml:space="preserve">6.05489206314087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9838662147522</t>
   </si>
   <si>
     <t xml:space="preserve">5.96611022949219</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93947696685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94835376739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92172050476074</t>
+    <t xml:space="preserve">5.93947649002075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94835472106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92172002792358</t>
   </si>
   <si>
     <t xml:space="preserve">5.912841796875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23245477676392</t>
+    <t xml:space="preserve">6.23245573043823</t>
   </si>
   <si>
     <t xml:space="preserve">6.46328639984131</t>
@@ -2615,55 +2618,55 @@
     <t xml:space="preserve">6.33011484146118</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27684545516968</t>
+    <t xml:space="preserve">6.27684640884399</t>
   </si>
   <si>
     <t xml:space="preserve">6.20582008361816</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04601383209229</t>
+    <t xml:space="preserve">6.04601430892944</t>
   </si>
   <si>
     <t xml:space="preserve">6.37450504302979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12591743469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21469879150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17918586730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26796817779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48104286193848</t>
+    <t xml:space="preserve">6.12591695785522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21469831466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17918634414673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26796722412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48104333877563</t>
   </si>
   <si>
     <t xml:space="preserve">6.66748380661011</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01373195648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43988275527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54641914367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59968948364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63520193099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68846893310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52866363525391</t>
+    <t xml:space="preserve">7.01373147964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43988227844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54641962051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59968900680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6352014541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68846940994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52866315841675</t>
   </si>
   <si>
     <t xml:space="preserve">7.31558752059937</t>
@@ -2672,7 +2675,7 @@
     <t xml:space="preserve">7.30670928955078</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1824164390564</t>
+    <t xml:space="preserve">7.18241596221924</t>
   </si>
   <si>
     <t xml:space="preserve">7.29783201217651</t>
@@ -2681,13 +2684,13 @@
     <t xml:space="preserve">7.13802528381348</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04924392700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19129467010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21792840957642</t>
+    <t xml:space="preserve">7.04924440383911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19129419326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21792888641357</t>
   </si>
   <si>
     <t xml:space="preserve">7.35109996795654</t>
@@ -2696,43 +2699,43 @@
     <t xml:space="preserve">7.48427295684814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59081029891968</t>
+    <t xml:space="preserve">7.59080982208252</t>
   </si>
   <si>
     <t xml:space="preserve">7.58193206787109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65295648574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5109076499939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45763778686523</t>
+    <t xml:space="preserve">7.65295743942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51090669631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45763826370239</t>
   </si>
   <si>
     <t xml:space="preserve">7.17353773117065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61744451522827</t>
+    <t xml:space="preserve">7.61744499206543</t>
   </si>
   <si>
     <t xml:space="preserve">7.67959117889404</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76837396621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93705797195435</t>
+    <t xml:space="preserve">7.76837348937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9370584487915</t>
   </si>
   <si>
     <t xml:space="preserve">8.19452381134033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09686470031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99920558929443</t>
+    <t xml:space="preserve">8.09686374664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99920463562012</t>
   </si>
   <si>
     <t xml:space="preserve">8.17676830291748</t>
@@ -2741,7 +2744,7 @@
     <t xml:space="preserve">8.20340156555176</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99032688140869</t>
+    <t xml:space="preserve">7.99032735824585</t>
   </si>
   <si>
     <t xml:space="preserve">8.08798599243164</t>
@@ -2750,7 +2753,7 @@
     <t xml:space="preserve">8.05247402191162</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04359531402588</t>
+    <t xml:space="preserve">8.04359722137451</t>
   </si>
   <si>
     <t xml:space="preserve">8.00808334350586</t>
@@ -2759,7 +2762,7 @@
     <t xml:space="preserve">8.07910919189453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14125442504883</t>
+    <t xml:space="preserve">8.14125537872314</t>
   </si>
   <si>
     <t xml:space="preserve">8.07022953033447</t>
@@ -2768,13 +2771,13 @@
     <t xml:space="preserve">8.15013313293457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38984298706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23891448974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44311141967773</t>
+    <t xml:space="preserve">8.38984203338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23891353607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44311237335205</t>
   </si>
   <si>
     <t xml:space="preserve">8.38096523284912</t>
@@ -2783,19 +2786,19 @@
     <t xml:space="preserve">8.51413822174072</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43423461914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64730930328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42535495758057</t>
+    <t xml:space="preserve">8.43423366546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64730834960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42535591125488</t>
   </si>
   <si>
     <t xml:space="preserve">8.47014427185059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60530567169189</t>
+    <t xml:space="preserve">8.60530662536621</t>
   </si>
   <si>
     <t xml:space="preserve">8.43410110473633</t>
@@ -2804,19 +2807,16 @@
     <t xml:space="preserve">8.4160795211792</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37102508544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56025314331055</t>
+    <t xml:space="preserve">8.37102603912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56025218963623</t>
   </si>
   <si>
     <t xml:space="preserve">8.31696033477783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42508983612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44311237335205</t>
+    <t xml:space="preserve">8.42509078979492</t>
   </si>
   <si>
     <t xml:space="preserve">8.62332725524902</t>
@@ -2828,25 +2828,25 @@
     <t xml:space="preserve">8.65937042236328</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70442485809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74046802520752</t>
+    <t xml:space="preserve">8.70442390441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7404670715332</t>
   </si>
   <si>
     <t xml:space="preserve">8.68640327453613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47915554046631</t>
+    <t xml:space="preserve">8.47915458679199</t>
   </si>
   <si>
     <t xml:space="preserve">8.50618743896484</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51519775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5332202911377</t>
+    <t xml:space="preserve">8.51519870758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53321933746338</t>
   </si>
   <si>
     <t xml:space="preserve">8.46113395690918</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">8.15476608276367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08267974853516</t>
+    <t xml:space="preserve">8.08268070220947</t>
   </si>
   <si>
     <t xml:space="preserve">8.0466365814209</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">8.05564785003662</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95653009414673</t>
+    <t xml:space="preserve">7.95652914047241</t>
   </si>
   <si>
     <t xml:space="preserve">8.00158309936523</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">7.74928188323975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85741138458252</t>
+    <t xml:space="preserve">7.85741090774536</t>
   </si>
   <si>
     <t xml:space="preserve">7.78532457351685</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">7.83938837051392</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74027013778687</t>
+    <t xml:space="preserve">7.74026966094971</t>
   </si>
   <si>
     <t xml:space="preserve">7.99257278442383</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">7.92048597335815</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17278861999512</t>
+    <t xml:space="preserve">8.1727876663208</t>
   </si>
   <si>
     <t xml:space="preserve">8.29893970489502</t>
@@ -2906,13 +2906,13 @@
     <t xml:space="preserve">8.16377735137939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21784210205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96553993225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6051082611084</t>
+    <t xml:space="preserve">8.21784114837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96554040908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60510873794556</t>
   </si>
   <si>
     <t xml:space="preserve">8.07366943359375</t>
@@ -2921,7 +2921,7 @@
     <t xml:space="preserve">8.24487400054932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12773418426514</t>
+    <t xml:space="preserve">8.12773513793945</t>
   </si>
   <si>
     <t xml:space="preserve">8.48816585540771</t>
@@ -2939,31 +2939,31 @@
     <t xml:space="preserve">8.71343612670898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63233852386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23586368560791</t>
+    <t xml:space="preserve">8.63233757019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23586463928223</t>
   </si>
   <si>
     <t xml:space="preserve">8.30795001983643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64135074615479</t>
+    <t xml:space="preserve">8.64134979248047</t>
   </si>
   <si>
     <t xml:space="preserve">8.77651119232178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55124092102051</t>
+    <t xml:space="preserve">8.55124187469482</t>
   </si>
   <si>
     <t xml:space="preserve">8.49717712402344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25388526916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19982147216797</t>
+    <t xml:space="preserve">8.25388431549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19982051849365</t>
   </si>
   <si>
     <t xml:space="preserve">8.03762626647949</t>
@@ -2972,19 +2972,19 @@
     <t xml:space="preserve">7.92949724197388</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98356008529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01960468292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88444328308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56906461715698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63214111328125</t>
+    <t xml:space="preserve">7.98356056213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01960563659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8844428062439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56906414031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63214015960693</t>
   </si>
   <si>
     <t xml:space="preserve">7.57807588577271</t>
@@ -2993,25 +2993,25 @@
     <t xml:space="preserve">7.55104398727417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65917253494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67719554901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72224855422974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76730155944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71323871612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93850803375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2268533706665</t>
+    <t xml:space="preserve">7.65917301177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67719507217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72224807739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76730251312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71323823928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93850755691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22685241699219</t>
   </si>
   <si>
     <t xml:space="preserve">8.19080924987793</t>
@@ -3029,28 +3029,28 @@
     <t xml:space="preserve">8.02861595153809</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8033447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69521570205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6141185760498</t>
+    <t xml:space="preserve">7.80334615707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69521617889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61411905288696</t>
   </si>
   <si>
     <t xml:space="preserve">7.37983798980713</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33478450775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37082815170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46093511581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36181688308716</t>
+    <t xml:space="preserve">7.33478498458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37082767486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46093463897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36181735992432</t>
   </si>
   <si>
     <t xml:space="preserve">7.35280561447144</t>
@@ -3074,28 +3074,28 @@
     <t xml:space="preserve">7.27170848846436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30775165557861</t>
+    <t xml:space="preserve">7.30775213241577</t>
   </si>
   <si>
     <t xml:space="preserve">7.29874181747437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26269865036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54203319549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64115142822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62313032150269</t>
+    <t xml:space="preserve">7.26269817352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54203271865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64115190505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62312984466553</t>
   </si>
   <si>
     <t xml:space="preserve">7.53302145004272</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52401113510132</t>
+    <t xml:space="preserve">7.52401161193848</t>
   </si>
   <si>
     <t xml:space="preserve">7.31676292419434</t>
@@ -3110,19 +3110,19 @@
     <t xml:space="preserve">6.96534204483032</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92929887771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02841854095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89325571060181</t>
+    <t xml:space="preserve">6.92929935455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02841758728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89325618743896</t>
   </si>
   <si>
     <t xml:space="preserve">7.01039600372314</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12753582000732</t>
+    <t xml:space="preserve">7.12753629684448</t>
   </si>
   <si>
     <t xml:space="preserve">7.11852598190308</t>
@@ -3146,7 +3146,7 @@
     <t xml:space="preserve">7.03742837905884</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14555740356445</t>
+    <t xml:space="preserve">7.14555788040161</t>
   </si>
   <si>
     <t xml:space="preserve">7.19962215423584</t>
@@ -3155,7 +3155,7 @@
     <t xml:space="preserve">7.00138521194458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07347106933594</t>
+    <t xml:space="preserve">7.0734715461731</t>
   </si>
   <si>
     <t xml:space="preserve">6.80314779281616</t>
@@ -3167,13 +3167,13 @@
     <t xml:space="preserve">6.66798639297485</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36161947250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59590005874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41568422317505</t>
+    <t xml:space="preserve">6.36161851882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59589910507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41568374633789</t>
   </si>
   <si>
     <t xml:space="preserve">6.32557582855225</t>
@@ -3182,10 +3182,10 @@
     <t xml:space="preserve">6.13634920120239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85701465606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83899307250977</t>
+    <t xml:space="preserve">5.85701513290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83899354934692</t>
   </si>
   <si>
     <t xml:space="preserve">6.01019859313965</t>
@@ -3203,19 +3203,19 @@
     <t xml:space="preserve">6.35260820388794</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2354679107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46974849700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3886513710022</t>
+    <t xml:space="preserve">6.23546838760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46974802017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38865089416504</t>
   </si>
   <si>
     <t xml:space="preserve">6.37062978744507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28953266143799</t>
+    <t xml:space="preserve">6.28953313827515</t>
   </si>
   <si>
     <t xml:space="preserve">6.31656503677368</t>
@@ -3236,7 +3236,7 @@
     <t xml:space="preserve">6.26250028610229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18140316009521</t>
+    <t xml:space="preserve">6.18140363693237</t>
   </si>
   <si>
     <t xml:space="preserve">6.29854297637939</t>
@@ -3245,7 +3245,7 @@
     <t xml:space="preserve">6.17239236831665</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84800386428833</t>
+    <t xml:space="preserve">5.84800338745117</t>
   </si>
   <si>
     <t xml:space="preserve">5.86602544784546</t>
@@ -3254,7 +3254,7 @@
     <t xml:space="preserve">5.92009019851685</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89305734634399</t>
+    <t xml:space="preserve">5.89305782318115</t>
   </si>
   <si>
     <t xml:space="preserve">5.93811178207397</t>
@@ -3266,25 +3266,25 @@
     <t xml:space="preserve">6.10030603408813</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21744632720947</t>
+    <t xml:space="preserve">6.21744680404663</t>
   </si>
   <si>
     <t xml:space="preserve">6.06426286697388</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98316526412964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94712209701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0192084312439</t>
+    <t xml:space="preserve">5.9831657409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94712257385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01920890808105</t>
   </si>
   <si>
     <t xml:space="preserve">5.99217653274536</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96514368057251</t>
+    <t xml:space="preserve">5.96514463424683</t>
   </si>
   <si>
     <t xml:space="preserve">5.97415494918823</t>
@@ -3293,10 +3293,10 @@
     <t xml:space="preserve">5.9561333656311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08228492736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07327318191528</t>
+    <t xml:space="preserve">6.08228445053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07327365875244</t>
   </si>
   <si>
     <t xml:space="preserve">6.03723001480103</t>
@@ -3305,10 +3305,10 @@
     <t xml:space="preserve">6.04001379013062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94737529754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96590280532837</t>
+    <t xml:space="preserve">5.94737577438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96590328216553</t>
   </si>
   <si>
     <t xml:space="preserve">6.1604437828064</t>
@@ -3317,13 +3317,13 @@
     <t xml:space="preserve">6.28087329864502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22528982162476</t>
+    <t xml:space="preserve">6.22529029846191</t>
   </si>
   <si>
     <t xml:space="preserve">6.20676231384277</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17897176742554</t>
+    <t xml:space="preserve">6.17897129058838</t>
   </si>
   <si>
     <t xml:space="preserve">6.29013729095459</t>
@@ -3359,13 +3359,13 @@
     <t xml:space="preserve">5.95663928985596</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82694625854492</t>
+    <t xml:space="preserve">5.82694578170776</t>
   </si>
   <si>
     <t xml:space="preserve">5.68798828125</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78062629699707</t>
+    <t xml:space="preserve">5.78062677383423</t>
   </si>
   <si>
     <t xml:space="preserve">5.73430776596069</t>
@@ -3395,22 +3395,22 @@
     <t xml:space="preserve">5.55829524993896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71578025817871</t>
+    <t xml:space="preserve">5.71577978134155</t>
   </si>
   <si>
     <t xml:space="preserve">5.77136325836182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61387777328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66019725799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8732647895813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66946077346802</t>
+    <t xml:space="preserve">5.61387825012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66019678115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87326526641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66946125030518</t>
   </si>
   <si>
     <t xml:space="preserve">5.80841875076294</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">6.0307502746582</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04927778244019</t>
+    <t xml:space="preserve">6.04927825927734</t>
   </si>
   <si>
     <t xml:space="preserve">5.86400127410889</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">5.53976726531982</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49344825744629</t>
+    <t xml:space="preserve">5.49344778060913</t>
   </si>
   <si>
     <t xml:space="preserve">5.47492074966431</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">5.15995073318481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21553373336792</t>
+    <t xml:space="preserve">5.21553325653076</t>
   </si>
   <si>
     <t xml:space="preserve">5.19700622558594</t>
@@ -3461,13 +3461,13 @@
     <t xml:space="preserve">5.25258874893188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38228273391724</t>
+    <t xml:space="preserve">5.38228225708008</t>
   </si>
   <si>
     <t xml:space="preserve">5.1321587562561</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10436820983887</t>
+    <t xml:space="preserve">5.10436773300171</t>
   </si>
   <si>
     <t xml:space="preserve">5.28038024902344</t>
@@ -3479,13 +3479,13 @@
     <t xml:space="preserve">5.2340612411499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08583974838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05804824829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01172971725464</t>
+    <t xml:space="preserve">5.08584022521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05804872512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01172924041748</t>
   </si>
   <si>
     <t xml:space="preserve">5.02099323272705</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">5.1784782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0487847328186</t>
+    <t xml:space="preserve">5.04878425598145</t>
   </si>
   <si>
     <t xml:space="preserve">5.15068674087524</t>
@@ -3515,16 +3515,16 @@
     <t xml:space="preserve">4.96541023254395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22479724884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33596324920654</t>
+    <t xml:space="preserve">5.22479772567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3359637260437</t>
   </si>
   <si>
     <t xml:space="preserve">5.30817174911499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45639324188232</t>
+    <t xml:space="preserve">5.45639276504517</t>
   </si>
   <si>
     <t xml:space="preserve">5.52123928070068</t>
@@ -3545,13 +3545,13 @@
     <t xml:space="preserve">5.76209878921509</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90105676651001</t>
+    <t xml:space="preserve">5.90105628967285</t>
   </si>
   <si>
     <t xml:space="preserve">5.91958427429199</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70651578903198</t>
+    <t xml:space="preserve">5.70651626586914</t>
   </si>
   <si>
     <t xml:space="preserve">5.74357128143311</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">5.63240575790405</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54903125762939</t>
+    <t xml:space="preserve">5.54903078079224</t>
   </si>
   <si>
     <t xml:space="preserve">5.64166975021362</t>
@@ -3587,7 +3587,7 @@
     <t xml:space="preserve">6.74406480789185</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70700931549072</t>
+    <t xml:space="preserve">6.70700883865356</t>
   </si>
   <si>
     <t xml:space="preserve">6.79964828491211</t>
@@ -3596,22 +3596,22 @@
     <t xml:space="preserve">6.82743883132935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79038381576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89228630065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96639680862427</t>
+    <t xml:space="preserve">6.79038333892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89228582382202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96639633178711</t>
   </si>
   <si>
     <t xml:space="preserve">7.23504734039307</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34621286392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38326787948608</t>
+    <t xml:space="preserve">7.34621334075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38326835632324</t>
   </si>
   <si>
     <t xml:space="preserve">7.46664333343506</t>
@@ -3629,7 +3629,7 @@
     <t xml:space="preserve">7.55928087234497</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39253282546997</t>
+    <t xml:space="preserve">7.39253234863281</t>
   </si>
   <si>
     <t xml:space="preserve">7.59633636474609</t>
@@ -3641,22 +3641,22 @@
     <t xml:space="preserve">7.64265584945679</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50369882583618</t>
+    <t xml:space="preserve">7.50369834899902</t>
   </si>
   <si>
     <t xml:space="preserve">7.63339138031006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62412738800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57780933380127</t>
+    <t xml:space="preserve">7.62412786483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57780885696411</t>
   </si>
   <si>
     <t xml:space="preserve">7.58707237243652</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45737934112549</t>
+    <t xml:space="preserve">7.45737981796265</t>
   </si>
   <si>
     <t xml:space="preserve">7.43885135650635</t>
@@ -3668,7 +3668,7 @@
     <t xml:space="preserve">7.32768535614014</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10535383224487</t>
+    <t xml:space="preserve">7.10535430908203</t>
   </si>
   <si>
     <t xml:space="preserve">7.18872833251953</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">7.30915784835815</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29062986373901</t>
+    <t xml:space="preserve">7.29063034057617</t>
   </si>
   <si>
     <t xml:space="preserve">7.16093683242798</t>
@@ -3698,10 +3698,10 @@
     <t xml:space="preserve">7.27210235595703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20725584030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33694982528687</t>
+    <t xml:space="preserve">7.20725631713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33694934844971</t>
   </si>
   <si>
     <t xml:space="preserve">7.31842231750488</t>
@@ -3710,19 +3710,19 @@
     <t xml:space="preserve">7.26283931732178</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12388134002686</t>
+    <t xml:space="preserve">7.12388181686401</t>
   </si>
   <si>
     <t xml:space="preserve">7.04977130889893</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98492431640625</t>
+    <t xml:space="preserve">6.98492383956909</t>
   </si>
   <si>
     <t xml:space="preserve">7.07756233215332</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22578430175781</t>
+    <t xml:space="preserve">7.22578382492065</t>
   </si>
   <si>
     <t xml:space="preserve">7.19799184799194</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">7.11461734771729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05903482437134</t>
+    <t xml:space="preserve">7.05903434753418</t>
   </si>
   <si>
     <t xml:space="preserve">7.06857395172119</t>
@@ -3749,34 +3749,34 @@
     <t xml:space="preserve">6.94456434249878</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86825037002563</t>
+    <t xml:space="preserve">6.86824989318848</t>
   </si>
   <si>
     <t xml:space="preserve">6.79193639755249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75377893447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84917116165161</t>
+    <t xml:space="preserve">6.75377941131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84917163848877</t>
   </si>
   <si>
     <t xml:space="preserve">6.99226045608521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95410299301147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87778949737549</t>
+    <t xml:space="preserve">6.95410346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87778902053833</t>
   </si>
   <si>
     <t xml:space="preserve">6.98272132873535</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96364307403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03041696548462</t>
+    <t xml:space="preserve">6.96364259719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03041744232178</t>
   </si>
   <si>
     <t xml:space="preserve">7.01133871078491</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">6.78239727020264</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72516202926636</t>
+    <t xml:space="preserve">6.7251615524292</t>
   </si>
   <si>
     <t xml:space="preserve">7.00179958343506</t>
@@ -3815,19 +3815,19 @@
     <t xml:space="preserve">7.36429023742676</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28797626495361</t>
+    <t xml:space="preserve">7.28797674179077</t>
   </si>
   <si>
     <t xml:space="preserve">7.29751586914062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30705451965332</t>
+    <t xml:space="preserve">7.30705499649048</t>
   </si>
   <si>
     <t xml:space="preserve">7.53599691390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57415342330933</t>
+    <t xml:space="preserve">7.57415390014648</t>
   </si>
   <si>
     <t xml:space="preserve">7.66000652313232</t>
@@ -3836,10 +3836,10 @@
     <t xml:space="preserve">7.6981635093689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93664407730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98434019088745</t>
+    <t xml:space="preserve">7.93664455413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98434066772461</t>
   </si>
   <si>
     <t xml:space="preserve">8.18466472625732</t>
@@ -3857,19 +3857,19 @@
     <t xml:space="preserve">8.16558647155762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04157638549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87940979003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9748010635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03203773498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90802669525146</t>
+    <t xml:space="preserve">8.04157733917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8794093132019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97480154037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03203678131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90802717208862</t>
   </si>
   <si>
     <t xml:space="preserve">7.89848756790161</t>
@@ -3881,7 +3881,7 @@
     <t xml:space="preserve">7.84125232696533</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88894891738892</t>
+    <t xml:space="preserve">7.88894844055176</t>
   </si>
   <si>
     <t xml:space="preserve">7.78401708602905</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">7.81263399124146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85079145431519</t>
+    <t xml:space="preserve">7.85079050064087</t>
   </si>
   <si>
     <t xml:space="preserve">7.77447748184204</t>
@@ -3905,13 +3905,13 @@
     <t xml:space="preserve">7.72678184509277</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64092826843262</t>
+    <t xml:space="preserve">7.64092874526978</t>
   </si>
   <si>
     <t xml:space="preserve">7.58369255065918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38336849212646</t>
+    <t xml:space="preserve">7.38336896896362</t>
   </si>
   <si>
     <t xml:space="preserve">7.3356728553772</t>
@@ -3932,7 +3932,7 @@
     <t xml:space="preserve">7.08765268325806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15442752838135</t>
+    <t xml:space="preserve">7.15442705154419</t>
   </si>
   <si>
     <t xml:space="preserve">7.03995656967163</t>
@@ -3944,7 +3944,7 @@
     <t xml:space="preserve">7.27843761444092</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41198682785034</t>
+    <t xml:space="preserve">7.41198635101318</t>
   </si>
   <si>
     <t xml:space="preserve">7.39290809631348</t>
@@ -3965,13 +3965,13 @@
     <t xml:space="preserve">7.45014333724976</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40244722366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50737905502319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70770311355591</t>
+    <t xml:space="preserve">7.40244770050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50737857818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70770263671875</t>
   </si>
   <si>
     <t xml:space="preserve">8.20374393463135</t>
@@ -3986,10 +3986,10 @@
     <t xml:space="preserve">8.10835075378418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08927154541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36591148376465</t>
+    <t xml:space="preserve">8.08927249908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36591053009033</t>
   </si>
   <si>
     <t xml:space="preserve">8.30867481231689</t>
@@ -4007,13 +4007,13 @@
     <t xml:space="preserve">8.60439205169678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40406799316406</t>
+    <t xml:space="preserve">8.40406703948975</t>
   </si>
   <si>
     <t xml:space="preserve">8.41360664367676</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26097869873047</t>
+    <t xml:space="preserve">8.26097774505615</t>
   </si>
   <si>
     <t xml:space="preserve">8.57577323913574</t>
@@ -4028,10 +4028,10 @@
     <t xml:space="preserve">8.76655769348145</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15766716003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19582366943359</t>
+    <t xml:space="preserve">9.1576681137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19582462310791</t>
   </si>
   <si>
     <t xml:space="preserve">9.11951065063477</t>
@@ -4040,13 +4040,13 @@
     <t xml:space="preserve">9.10043144226074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09089279174805</t>
+    <t xml:space="preserve">9.09089183807373</t>
   </si>
   <si>
     <t xml:space="preserve">8.72840118408203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87148952484131</t>
+    <t xml:space="preserve">8.87149047851562</t>
   </si>
   <si>
     <t xml:space="preserve">8.90964698791504</t>
@@ -4070,7 +4070,7 @@
     <t xml:space="preserve">9.00503826141357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20536231994629</t>
+    <t xml:space="preserve">9.20536327362061</t>
   </si>
   <si>
     <t xml:space="preserve">9.45338344573975</t>
@@ -4079,25 +4079,25 @@
     <t xml:space="preserve">9.50107955932617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52969646453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.577392578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47246265411377</t>
+    <t xml:space="preserve">9.52969741821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57739353179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47246170043945</t>
   </si>
   <si>
     <t xml:space="preserve">9.36752986907959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30075550079346</t>
+    <t xml:space="preserve">9.30075454711914</t>
   </si>
   <si>
     <t xml:space="preserve">9.39614772796631</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44384384155273</t>
+    <t xml:space="preserve">9.44384288787842</t>
   </si>
   <si>
     <t xml:space="preserve">9.49153995513916</t>
@@ -4109,7 +4109,7 @@
     <t xml:space="preserve">8.69978332519531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55669593811035</t>
+    <t xml:space="preserve">8.55669498443604</t>
   </si>
   <si>
     <t xml:space="preserve">8.62346935272217</t>
@@ -4118,10 +4118,10 @@
     <t xml:space="preserve">8.48038101196289</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59485244750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70932197570801</t>
+    <t xml:space="preserve">8.59485149383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70932292938232</t>
   </si>
   <si>
     <t xml:space="preserve">8.77609729766846</t>
@@ -4133,10 +4133,10 @@
     <t xml:space="preserve">8.75701904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8619499206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89056873321533</t>
+    <t xml:space="preserve">8.86195087432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89056777954102</t>
   </si>
   <si>
     <t xml:space="preserve">8.67116546630859</t>
@@ -4151,10 +4151,10 @@
     <t xml:space="preserve">8.74748039245605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01457786560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92872524261475</t>
+    <t xml:space="preserve">9.0145788192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92872428894043</t>
   </si>
   <si>
     <t xml:space="preserve">8.97642135620117</t>
@@ -4166,28 +4166,28 @@
     <t xml:space="preserve">9.46292304992676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74909973144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78725624084473</t>
+    <t xml:space="preserve">9.74910068511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78725719451904</t>
   </si>
   <si>
     <t xml:space="preserve">9.92080497741699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99711990356445</t>
+    <t xml:space="preserve">9.99711894989014</t>
   </si>
   <si>
     <t xml:space="preserve">9.69186401367188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7681770324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80633544921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63462924957275</t>
+    <t xml:space="preserve">9.76817798614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80633449554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63462829589844</t>
   </si>
   <si>
     <t xml:space="preserve">9.67278575897217</t>
@@ -4196,10 +4196,10 @@
     <t xml:space="preserve">9.59647178649902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7109432220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52015781402588</t>
+    <t xml:space="preserve">9.71094226837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52015686035156</t>
   </si>
   <si>
     <t xml:space="preserve">9.43430519104004</t>
@@ -4208,13 +4208,13 @@
     <t xml:space="preserve">9.25305938720703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28167724609375</t>
+    <t xml:space="preserve">9.28167629241943</t>
   </si>
   <si>
     <t xml:space="preserve">9.34845161437988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41522598266602</t>
+    <t xml:space="preserve">9.41522693634033</t>
   </si>
   <si>
     <t xml:space="preserve">9.48200035095215</t>
@@ -4232,7 +4232,7 @@
     <t xml:space="preserve">9.65370750427246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86357021331787</t>
+    <t xml:space="preserve">9.86357116699219</t>
   </si>
   <si>
     <t xml:space="preserve">10.0204467773438</t>
@@ -5102,10 +5102,10 @@
     <t xml:space="preserve">14.5200004577637</t>
   </si>
   <si>
+    <t xml:space="preserve">14.8400001525879</t>
+  </si>
+  <si>
     <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8400001525879</t>
   </si>
 </sst>
 </file>
@@ -34322,7 +34322,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1111" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -34348,7 +34348,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1112" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -34374,7 +34374,7 @@
         <v>5.5</v>
       </c>
       <c r="G1113" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -34400,7 +34400,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1114" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -34426,7 +34426,7 @@
         <v>5.75</v>
       </c>
       <c r="G1115" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -34452,7 +34452,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1116" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -34478,7 +34478,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1117" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -34504,7 +34504,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1118" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -34530,7 +34530,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1119" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -34556,7 +34556,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1120" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -34582,7 +34582,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1121" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -34608,7 +34608,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G1122" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -34634,7 +34634,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G1123" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -34660,7 +34660,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1124" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -34686,7 +34686,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1125" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -34712,7 +34712,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G1126" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -34738,7 +34738,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G1127" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -34764,7 +34764,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1128" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -34790,7 +34790,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1129" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -34816,7 +34816,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1130" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -34842,7 +34842,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G1131" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -34868,7 +34868,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1132" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -34894,7 +34894,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1133" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -34920,7 +34920,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G1134" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -34946,7 +34946,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1135" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -34972,7 +34972,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1136" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -34998,7 +34998,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1137" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -35024,7 +35024,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1138" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -35050,7 +35050,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1139" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -35076,7 +35076,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1140" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -35102,7 +35102,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1141" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -35128,7 +35128,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1142" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -35154,7 +35154,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1143" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -35180,7 +35180,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1144" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -35206,7 +35206,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G1145" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -35232,7 +35232,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1146" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -35258,7 +35258,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1147" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -35284,7 +35284,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1148" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -35310,7 +35310,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G1149" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -35336,7 +35336,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1150" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -35362,7 +35362,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1151" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -35388,7 +35388,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1152" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -35414,7 +35414,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G1153" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -35440,7 +35440,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1154" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -35466,7 +35466,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G1155" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -35492,7 +35492,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1156" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -35518,7 +35518,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G1157" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -35544,7 +35544,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G1158" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -35570,7 +35570,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1159" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -35596,7 +35596,7 @@
         <v>5.75</v>
       </c>
       <c r="G1160" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -35622,7 +35622,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1161" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -35648,7 +35648,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1162" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -35674,7 +35674,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1163" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -35700,7 +35700,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1164" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -35726,7 +35726,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1165" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -35752,7 +35752,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G1166" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -35778,7 +35778,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1167" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -35804,7 +35804,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1168" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -35830,7 +35830,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1169" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -35856,7 +35856,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G1170" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -35882,7 +35882,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1171" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -35908,7 +35908,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1172" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -35934,7 +35934,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1173" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -35960,7 +35960,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1174" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -35986,7 +35986,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1175" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -36012,7 +36012,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1176" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -36038,7 +36038,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1177" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -36064,7 +36064,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1178" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -36090,7 +36090,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1179" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -36116,7 +36116,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1180" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -36142,7 +36142,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1181" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -36168,7 +36168,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1182" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -36194,7 +36194,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1183" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -36220,7 +36220,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1184" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -36246,7 +36246,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1185" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -36272,7 +36272,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1186" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -36298,7 +36298,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G1187" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -36324,7 +36324,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1188" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -36350,7 +36350,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1189" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -36376,7 +36376,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G1190" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -36402,7 +36402,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1191" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -36428,7 +36428,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G1192" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -36454,7 +36454,7 @@
         <v>6</v>
       </c>
       <c r="G1193" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -36480,7 +36480,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1194" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -36506,7 +36506,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1195" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -36532,7 +36532,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1196" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -36558,7 +36558,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1197" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -36584,7 +36584,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1198" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -36610,7 +36610,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1199" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -36636,7 +36636,7 @@
         <v>6</v>
       </c>
       <c r="G1200" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -36662,7 +36662,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G1201" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -36688,7 +36688,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G1202" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -36714,7 +36714,7 @@
         <v>6</v>
       </c>
       <c r="G1203" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -36740,7 +36740,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G1204" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -36766,7 +36766,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1205" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -36792,7 +36792,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1206" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -36818,7 +36818,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1207" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -36844,7 +36844,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1208" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -36870,7 +36870,7 @@
         <v>5.75</v>
       </c>
       <c r="G1209" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -36896,7 +36896,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1210" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -36922,7 +36922,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1211" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -36948,7 +36948,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1212" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -36974,7 +36974,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1213" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -37000,7 +37000,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1214" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -37026,7 +37026,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1215" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -37052,7 +37052,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G1216" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -37078,7 +37078,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1217" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -37104,7 +37104,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1218" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -37130,7 +37130,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1219" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -37156,7 +37156,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1220" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -37182,7 +37182,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1221" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -37208,7 +37208,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1222" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -37234,7 +37234,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G1223" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -37260,7 +37260,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1224" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -37286,7 +37286,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1225" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -37312,7 +37312,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1226" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -37338,7 +37338,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1227" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -37364,7 +37364,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1228" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -37390,7 +37390,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1229" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -37416,7 +37416,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1230" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -37442,7 +37442,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1231" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -37468,7 +37468,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1232" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -37494,7 +37494,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1233" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -37520,7 +37520,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G1234" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -37546,7 +37546,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1235" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -37572,7 +37572,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1236" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -37598,7 +37598,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G1237" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -37624,7 +37624,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1238" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -37650,7 +37650,7 @@
         <v>6.75</v>
       </c>
       <c r="G1239" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -37676,7 +37676,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1240" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -37702,7 +37702,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1241" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -37728,7 +37728,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1242" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -37754,7 +37754,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1243" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -37780,7 +37780,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1244" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -37806,7 +37806,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1245" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -37832,7 +37832,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1246" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -37858,7 +37858,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G1247" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -37884,7 +37884,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1248" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -37910,7 +37910,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1249" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -37936,7 +37936,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G1250" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -37962,7 +37962,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G1251" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -37988,7 +37988,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1252" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -38014,7 +38014,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1253" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -38040,7 +38040,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1254" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -38066,7 +38066,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1255" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -38092,7 +38092,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G1256" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -38118,7 +38118,7 @@
         <v>6.75</v>
       </c>
       <c r="G1257" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -38144,7 +38144,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1258" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -38170,7 +38170,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1259" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -38196,7 +38196,7 @@
         <v>6.75</v>
       </c>
       <c r="G1260" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -38222,7 +38222,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1261" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -38248,7 +38248,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1262" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -38274,7 +38274,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1263" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -38300,7 +38300,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1264" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -38326,7 +38326,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1265" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -38352,7 +38352,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1266" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -38378,7 +38378,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1267" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -38404,7 +38404,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1268" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -38430,7 +38430,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1269" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -38456,7 +38456,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1270" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -38482,7 +38482,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1271" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -38508,7 +38508,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1272" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -38534,7 +38534,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1273" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -38560,7 +38560,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1274" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -38586,7 +38586,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1275" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -38612,7 +38612,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1276" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -38638,7 +38638,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1277" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -38664,7 +38664,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1278" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -38690,7 +38690,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G1279" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -38716,7 +38716,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1280" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -38742,7 +38742,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1281" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -38768,7 +38768,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1282" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -38794,7 +38794,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1283" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -38820,7 +38820,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G1284" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -38846,7 +38846,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G1285" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -38872,7 +38872,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1286" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -38898,7 +38898,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1287" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -38924,7 +38924,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1288" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -38950,7 +38950,7 @@
         <v>7</v>
       </c>
       <c r="G1289" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -38976,7 +38976,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1290" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -39002,7 +39002,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1291" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -39028,7 +39028,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1292" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -39054,7 +39054,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G1293" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -39080,7 +39080,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1294" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -39106,7 +39106,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1295" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -39132,7 +39132,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1296" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -39158,7 +39158,7 @@
         <v>8.5</v>
       </c>
       <c r="G1297" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -39184,7 +39184,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1298" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -39210,7 +39210,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1299" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -39236,7 +39236,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1300" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -39262,7 +39262,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1301" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -39288,7 +39288,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1302" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -39314,7 +39314,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1303" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -39340,7 +39340,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1304" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -39366,7 +39366,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1305" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -39392,7 +39392,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1306" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -39418,7 +39418,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G1307" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -39444,7 +39444,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1308" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -39470,7 +39470,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1309" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -39496,7 +39496,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1310" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -39522,7 +39522,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1311" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -39548,7 +39548,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1312" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -39574,7 +39574,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1313" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -39600,7 +39600,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1314" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -39626,7 +39626,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G1315" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -39652,7 +39652,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1316" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -39678,7 +39678,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1317" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -39704,7 +39704,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1318" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -39730,7 +39730,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1319" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -39756,7 +39756,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1320" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -39782,7 +39782,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1321" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -39808,7 +39808,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1322" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -39834,7 +39834,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1323" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -39860,7 +39860,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1324" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -39886,7 +39886,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1325" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -39912,7 +39912,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1326" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -39938,7 +39938,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G1327" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -39964,7 +39964,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1328" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -39990,7 +39990,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1329" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -40016,7 +40016,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G1330" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -40042,7 +40042,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1331" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -40068,7 +40068,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1332" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -40094,7 +40094,7 @@
         <v>8.75</v>
       </c>
       <c r="G1333" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -40120,7 +40120,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1334" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -40146,7 +40146,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G1335" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -40172,7 +40172,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1336" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -40198,7 +40198,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G1337" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -40224,7 +40224,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G1338" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -40250,7 +40250,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1339" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -40276,7 +40276,7 @@
         <v>9</v>
       </c>
       <c r="G1340" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -40302,7 +40302,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G1341" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -40328,7 +40328,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G1342" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -40354,7 +40354,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1343" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -40380,7 +40380,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G1344" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -40406,7 +40406,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1345" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -40432,7 +40432,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1346" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -40458,7 +40458,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1347" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -40484,7 +40484,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1348" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -40510,7 +40510,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G1349" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -40536,7 +40536,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G1350" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -40562,7 +40562,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1351" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -40588,7 +40588,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G1352" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -40614,7 +40614,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G1353" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -40640,7 +40640,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G1354" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -40666,7 +40666,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1355" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -40692,7 +40692,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G1356" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -40718,7 +40718,7 @@
         <v>9.5</v>
       </c>
       <c r="G1357" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -40744,7 +40744,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G1358" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -40770,7 +40770,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G1359" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -40796,7 +40796,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G1360" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -40822,7 +40822,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G1361" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -40848,7 +40848,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G1362" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -40874,7 +40874,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G1363" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -40900,7 +40900,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1364" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -40926,7 +40926,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G1365" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -40952,7 +40952,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G1366" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -40978,7 +40978,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1367" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -41004,7 +41004,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G1368" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -41030,7 +41030,7 @@
         <v>9.5</v>
       </c>
       <c r="G1369" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -41056,7 +41056,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G1370" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -41082,7 +41082,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1371" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -41108,7 +41108,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G1372" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -41134,7 +41134,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G1373" t="s">
-        <v>934</v>
+        <v>921</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -41160,7 +41160,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1374" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -41472,7 +41472,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1386" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -42304,7 +42304,7 @@
         <v>9.5</v>
       </c>
       <c r="G1418" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -42486,7 +42486,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G1425" t="s">
-        <v>934</v>
+        <v>921</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -42590,7 +42590,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1429" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -42616,7 +42616,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G1430" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -42746,7 +42746,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1435" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -42980,7 +42980,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1444" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -72850,7 +72850,9 @@
       <c r="E2593" t="n">
         <v>14.4399995803833</v>
       </c>
-      <c r="F2593"/>
+      <c r="F2593" t="n">
+        <v>14.8400001525879</v>
+      </c>
       <c r="G2593" t="s">
         <v>1696</v>
       </c>
@@ -72860,27 +72862,51 @@
     </row>
     <row r="2594">
       <c r="A2594" s="1" t="n">
-        <v>46097.6911226852</v>
+        <v>46098.3333333333</v>
       </c>
       <c r="B2594" t="n">
-        <v>146105</v>
+        <v>97297</v>
       </c>
       <c r="C2594" t="n">
-        <v>14.8999996185303</v>
+        <v>14.9399995803833</v>
       </c>
       <c r="D2594" t="n">
-        <v>14.3999996185303</v>
+        <v>14.6000003814697</v>
       </c>
       <c r="E2594" t="n">
-        <v>14.4399995803833</v>
-      </c>
-      <c r="F2594" t="n">
-        <v>14.8400001525879</v>
-      </c>
+        <v>14.7399997711182</v>
+      </c>
+      <c r="F2594"/>
       <c r="G2594" t="s">
         <v>1697</v>
       </c>
       <c r="H2594" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2595">
+      <c r="A2595" s="1" t="n">
+        <v>46098.6911458333</v>
+      </c>
+      <c r="B2595" t="n">
+        <v>97297</v>
+      </c>
+      <c r="C2595" t="n">
+        <v>14.9399995803833</v>
+      </c>
+      <c r="D2595" t="n">
+        <v>14.6000003814697</v>
+      </c>
+      <c r="E2595" t="n">
+        <v>14.7399997711182</v>
+      </c>
+      <c r="F2595" t="n">
+        <v>14.7200002670288</v>
+      </c>
+      <c r="G2595" t="s">
+        <v>1583</v>
+      </c>
+      <c r="H2595" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CEM.MI.xlsx
+++ b/data/CEM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="1701">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1702" uniqueCount="1702">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -53,55 +53,55 @@
     <t xml:space="preserve">4.48867273330688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32893371582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22110939025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32493925094604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28899908065796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29299259185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06137037277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93597483634949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97431206703186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6756010055542</t>
+    <t xml:space="preserve">4.32893419265747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22110986709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32494068145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28899955749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29299163818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06137084960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93597555160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97431254386902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67560052871704</t>
   </si>
   <si>
     <t xml:space="preserve">3.83533930778503</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94875502586365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88006663322449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91680645942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87846827507019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74588561058044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93437767028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87367677688599</t>
+    <t xml:space="preserve">3.94875335693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88006639480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91680693626404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87846851348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74588537216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9343786239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87367725372314</t>
   </si>
   <si>
     <t xml:space="preserve">3.73789858818054</t>
@@ -110,22 +110,22 @@
     <t xml:space="preserve">3.57815957069397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59892511367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61969137191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35132956504822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15005803108215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25069403648376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13088965415955</t>
+    <t xml:space="preserve">3.59892535209656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61969184875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3513298034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15005826950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25069379806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13088941574097</t>
   </si>
   <si>
     <t xml:space="preserve">3.20916199684143</t>
@@ -134,178 +134,178 @@
     <t xml:space="preserve">3.44238066673279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3625111579895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47592639923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55419898033142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34653735160828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39126420021057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3673038482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23951244354248</t>
+    <t xml:space="preserve">3.36251139640808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47592687606812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55419850349426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34653759002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39126396179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36730337142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2395122051239</t>
   </si>
   <si>
     <t xml:space="preserve">3.29222583770752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40244674682617</t>
-  </si>
-  <si>
-    <t xml:spa